--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -109,17 +109,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,69 +641,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51739</v>
+        <v>52041</v>
       </c>
       <c r="C2" t="n">
-        <v>52233</v>
+        <v>52300</v>
       </c>
       <c r="D2" t="n">
-        <v>51698</v>
+        <v>51420</v>
       </c>
       <c r="E2" t="n">
-        <v>52044</v>
+        <v>51519</v>
       </c>
       <c r="F2" t="n">
-        <v>302</v>
+        <v>-525</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0101</v>
       </c>
       <c r="H2" t="n">
-        <v>535</v>
+        <v>880</v>
       </c>
       <c r="I2" t="n">
-        <v>50884</v>
+        <v>51163</v>
       </c>
       <c r="J2" t="n">
-        <v>51198</v>
+        <v>51548.25</v>
       </c>
       <c r="K2" t="n">
-        <v>51464</v>
+        <v>51776.5</v>
       </c>
       <c r="L2" t="n">
-        <v>51730</v>
+        <v>52004.75</v>
       </c>
       <c r="M2" t="n">
-        <v>52020</v>
+        <v>52311.5</v>
       </c>
       <c r="N2" t="n">
-        <v>52310</v>
+        <v>52618.25</v>
       </c>
       <c r="O2" t="n">
-        <v>52552</v>
+        <v>52768</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -713,144 +715,146 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>52041</v>
+        <v>51621</v>
       </c>
       <c r="C3" t="n">
-        <v>52300</v>
+        <v>51962</v>
       </c>
       <c r="D3" t="n">
-        <v>51420</v>
+        <v>51587</v>
       </c>
       <c r="E3" t="n">
-        <v>51519</v>
+        <v>51962</v>
       </c>
       <c r="F3" t="n">
-        <v>-525</v>
+        <v>443</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0101</v>
+        <v>0.0086</v>
       </c>
       <c r="H3" t="n">
-        <v>880</v>
+        <v>375</v>
       </c>
       <c r="I3" t="n">
-        <v>51163</v>
+        <v>50540</v>
       </c>
       <c r="J3" t="n">
-        <v>51548.25</v>
+        <v>50468.5</v>
       </c>
       <c r="K3" t="n">
-        <v>51776.5</v>
+        <v>51079</v>
       </c>
       <c r="L3" t="n">
-        <v>52004.75</v>
+        <v>51689.5</v>
       </c>
       <c r="M3" t="n">
-        <v>52311.5</v>
+        <v>51959</v>
       </c>
       <c r="N3" t="n">
-        <v>52618.25</v>
+        <v>52228.5</v>
       </c>
       <c r="O3" t="n">
-        <v>52768</v>
+        <v>53180</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>51621</v>
+        <v>51870</v>
       </c>
       <c r="C4" t="n">
-        <v>51962</v>
+        <v>52305</v>
       </c>
       <c r="D4" t="n">
-        <v>51587</v>
+        <v>51712</v>
       </c>
       <c r="E4" t="n">
-        <v>51962</v>
+        <v>52119</v>
       </c>
       <c r="F4" t="n">
-        <v>443</v>
+        <v>157</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0086</v>
+        <v>0.003</v>
       </c>
       <c r="H4" t="n">
-        <v>375</v>
+        <v>593</v>
       </c>
       <c r="I4" t="n">
-        <v>50540</v>
+        <v>51212</v>
       </c>
       <c r="J4" t="n">
-        <v>50468.5</v>
+        <v>51680.75</v>
       </c>
       <c r="K4" t="n">
-        <v>51079</v>
+        <v>51774.5</v>
       </c>
       <c r="L4" t="n">
-        <v>51689.5</v>
+        <v>51868.25</v>
       </c>
       <c r="M4" t="n">
-        <v>51959</v>
+        <v>52149.5</v>
       </c>
       <c r="N4" t="n">
-        <v>52228.5</v>
+        <v>52430.75</v>
       </c>
       <c r="O4" t="n">
-        <v>53180</v>
+        <v>52337</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -858,10 +862,12 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -877,64 +883,64 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51870</v>
+        <v>52165</v>
       </c>
       <c r="C5" t="n">
-        <v>52305</v>
+        <v>52281</v>
       </c>
       <c r="D5" t="n">
-        <v>51712</v>
+        <v>51691</v>
       </c>
       <c r="E5" t="n">
-        <v>52119</v>
+        <v>52082</v>
       </c>
       <c r="F5" t="n">
-        <v>157</v>
+        <v>-37</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0007</v>
       </c>
       <c r="H5" t="n">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="I5" t="n">
-        <v>51212</v>
+        <v>51119</v>
       </c>
       <c r="J5" t="n">
-        <v>51680.75</v>
+        <v>51581.25</v>
       </c>
       <c r="K5" t="n">
-        <v>51774.5</v>
+        <v>51822.5</v>
       </c>
       <c r="L5" t="n">
-        <v>51868.25</v>
+        <v>52063.75</v>
       </c>
       <c r="M5" t="n">
-        <v>52149.5</v>
+        <v>52415.5</v>
       </c>
       <c r="N5" t="n">
-        <v>52430.75</v>
+        <v>52767.25</v>
       </c>
       <c r="O5" t="n">
-        <v>52337</v>
+        <v>52898</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -947,15 +953,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -963,64 +967,60 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52165</v>
+        <v>52119</v>
       </c>
       <c r="C6" t="n">
-        <v>52281</v>
+        <v>52676</v>
       </c>
       <c r="D6" t="n">
-        <v>51691</v>
+        <v>51933</v>
       </c>
       <c r="E6" t="n">
-        <v>52082</v>
+        <v>52279</v>
       </c>
       <c r="F6" t="n">
-        <v>-37</v>
+        <v>197</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0007</v>
+        <v>0.0038</v>
       </c>
       <c r="H6" t="n">
-        <v>590</v>
+        <v>743</v>
       </c>
       <c r="I6" t="n">
-        <v>51119</v>
+        <v>51101</v>
       </c>
       <c r="J6" t="n">
-        <v>51581.25</v>
+        <v>51540</v>
       </c>
       <c r="K6" t="n">
-        <v>51822.5</v>
+        <v>51787</v>
       </c>
       <c r="L6" t="n">
-        <v>52063.75</v>
+        <v>52034</v>
       </c>
       <c r="M6" t="n">
-        <v>52415.5</v>
+        <v>52377</v>
       </c>
       <c r="N6" t="n">
-        <v>52767.25</v>
+        <v>52720</v>
       </c>
       <c r="O6" t="n">
-        <v>52898</v>
+        <v>52871</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1028,18 +1028,18 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1047,60 +1047,64 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>52119</v>
+        <v>52381</v>
       </c>
       <c r="C7" t="n">
-        <v>52676</v>
+        <v>53097</v>
       </c>
       <c r="D7" t="n">
-        <v>51933</v>
+        <v>52215</v>
       </c>
       <c r="E7" t="n">
-        <v>52279</v>
+        <v>52339</v>
       </c>
       <c r="F7" t="n">
-        <v>197</v>
+        <v>60</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.0011</v>
       </c>
       <c r="H7" t="n">
-        <v>743</v>
+        <v>882</v>
       </c>
       <c r="I7" t="n">
-        <v>51101</v>
+        <v>51190</v>
       </c>
       <c r="J7" t="n">
-        <v>51540</v>
+        <v>51523.25</v>
       </c>
       <c r="K7" t="n">
-        <v>51787</v>
+        <v>51907.5</v>
       </c>
       <c r="L7" t="n">
-        <v>52034</v>
+        <v>52291.75</v>
       </c>
       <c r="M7" t="n">
-        <v>52377</v>
+        <v>52650.5</v>
       </c>
       <c r="N7" t="n">
-        <v>52720</v>
+        <v>53009.25</v>
       </c>
       <c r="O7" t="n">
-        <v>52871</v>
+        <v>53419</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1111,23 +1115,25 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1141,50 +1147,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52381</v>
+        <v>52439</v>
       </c>
       <c r="C8" t="n">
-        <v>53097</v>
+        <v>52542</v>
       </c>
       <c r="D8" t="n">
-        <v>52215</v>
+        <v>52008</v>
       </c>
       <c r="E8" t="n">
-        <v>52339</v>
+        <v>52209</v>
       </c>
       <c r="F8" t="n">
-        <v>60</v>
+        <v>-130</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0011</v>
+        <v>-0.0025</v>
       </c>
       <c r="H8" t="n">
-        <v>882</v>
+        <v>534</v>
       </c>
       <c r="I8" t="n">
-        <v>51190</v>
+        <v>51333</v>
       </c>
       <c r="J8" t="n">
-        <v>51523.25</v>
+        <v>51298.5</v>
       </c>
       <c r="K8" t="n">
-        <v>51907.5</v>
+        <v>51898</v>
       </c>
       <c r="L8" t="n">
-        <v>52291.75</v>
+        <v>52497.5</v>
       </c>
       <c r="M8" t="n">
-        <v>52650.5</v>
+        <v>52780</v>
       </c>
       <c r="N8" t="n">
-        <v>53009.25</v>
+        <v>53062.5</v>
       </c>
       <c r="O8" t="n">
-        <v>53419</v>
+        <v>53979</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1197,80 +1203,72 @@
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52439</v>
+        <v>52183</v>
       </c>
       <c r="C9" t="n">
-        <v>52542</v>
+        <v>52700</v>
       </c>
       <c r="D9" t="n">
-        <v>52008</v>
+        <v>52179</v>
       </c>
       <c r="E9" t="n">
-        <v>52209</v>
+        <v>52572</v>
       </c>
       <c r="F9" t="n">
-        <v>-130</v>
+        <v>363</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.007</v>
       </c>
       <c r="H9" t="n">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="I9" t="n">
-        <v>51333</v>
+        <v>51474</v>
       </c>
       <c r="J9" t="n">
-        <v>51298.5</v>
+        <v>51642</v>
       </c>
       <c r="K9" t="n">
-        <v>51898</v>
+        <v>51942</v>
       </c>
       <c r="L9" t="n">
-        <v>52497.5</v>
+        <v>52242</v>
       </c>
       <c r="M9" t="n">
-        <v>52780</v>
+        <v>52476</v>
       </c>
       <c r="N9" t="n">
-        <v>53062.5</v>
+        <v>52710</v>
       </c>
       <c r="O9" t="n">
-        <v>53979</v>
+        <v>53076</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1283,11 +1281,13 @@
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1295,60 +1295,64 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52183</v>
+        <v>52554</v>
       </c>
       <c r="C10" t="n">
-        <v>52700</v>
+        <v>52763</v>
       </c>
       <c r="D10" t="n">
-        <v>52179</v>
+        <v>52383</v>
       </c>
       <c r="E10" t="n">
-        <v>52572</v>
+        <v>52670</v>
       </c>
       <c r="F10" t="n">
-        <v>363</v>
+        <v>98</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.007</v>
+        <v>0.0019</v>
       </c>
       <c r="H10" t="n">
-        <v>521</v>
+        <v>380</v>
       </c>
       <c r="I10" t="n">
-        <v>51474</v>
+        <v>51658</v>
       </c>
       <c r="J10" t="n">
-        <v>51642</v>
+        <v>52117.25</v>
       </c>
       <c r="K10" t="n">
-        <v>51942</v>
+        <v>52311.5</v>
       </c>
       <c r="L10" t="n">
-        <v>52242</v>
+        <v>52505.75</v>
       </c>
       <c r="M10" t="n">
-        <v>52476</v>
+        <v>52832.5</v>
       </c>
       <c r="N10" t="n">
-        <v>52710</v>
+        <v>53159.25</v>
       </c>
       <c r="O10" t="n">
-        <v>53076</v>
+        <v>53221</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1359,7 +1363,7 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="7" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1375,7 +1379,7 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1389,50 +1393,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>52554</v>
+        <v>52546</v>
       </c>
       <c r="C11" t="n">
-        <v>52763</v>
+        <v>53105</v>
       </c>
       <c r="D11" t="n">
-        <v>52383</v>
+        <v>52381</v>
       </c>
       <c r="E11" t="n">
-        <v>52670</v>
+        <v>52668</v>
       </c>
       <c r="F11" t="n">
-        <v>98</v>
+        <v>-2</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>380</v>
+        <v>724</v>
       </c>
       <c r="I11" t="n">
-        <v>51658</v>
+        <v>52003</v>
       </c>
       <c r="J11" t="n">
-        <v>52117.25</v>
+        <v>52338.5</v>
       </c>
       <c r="K11" t="n">
-        <v>52311.5</v>
+        <v>52480</v>
       </c>
       <c r="L11" t="n">
-        <v>52505.75</v>
+        <v>52621.5</v>
       </c>
       <c r="M11" t="n">
-        <v>52832.5</v>
+        <v>52860</v>
       </c>
       <c r="N11" t="n">
-        <v>53159.25</v>
+        <v>53098.5</v>
       </c>
       <c r="O11" t="n">
-        <v>53221</v>
+        <v>53143</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1440,83 +1444,87 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52546</v>
+        <v>52640</v>
       </c>
       <c r="C12" t="n">
-        <v>53105</v>
+        <v>53218</v>
       </c>
       <c r="D12" t="n">
-        <v>52381</v>
+        <v>52551</v>
       </c>
       <c r="E12" t="n">
-        <v>52668</v>
+        <v>53183</v>
       </c>
       <c r="F12" t="n">
-        <v>-2</v>
+        <v>515</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0</v>
+        <v>0.0098</v>
       </c>
       <c r="H12" t="n">
-        <v>724</v>
+        <v>667</v>
       </c>
       <c r="I12" t="n">
-        <v>52003</v>
+        <v>51657</v>
       </c>
       <c r="J12" t="n">
-        <v>52338.5</v>
+        <v>51906.5</v>
       </c>
       <c r="K12" t="n">
-        <v>52480</v>
+        <v>52306</v>
       </c>
       <c r="L12" t="n">
-        <v>52621.5</v>
+        <v>52705.5</v>
       </c>
       <c r="M12" t="n">
-        <v>52860</v>
+        <v>53030</v>
       </c>
       <c r="N12" t="n">
-        <v>53098.5</v>
+        <v>53354.5</v>
       </c>
       <c r="O12" t="n">
-        <v>53143</v>
+        <v>53829</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1524,87 +1532,83 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>52640</v>
+        <v>53230</v>
       </c>
       <c r="C13" t="n">
-        <v>53218</v>
+        <v>53421</v>
       </c>
       <c r="D13" t="n">
-        <v>52551</v>
+        <v>52962</v>
       </c>
       <c r="E13" t="n">
-        <v>53183</v>
+        <v>53372</v>
       </c>
       <c r="F13" t="n">
-        <v>515</v>
+        <v>189</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0036</v>
       </c>
       <c r="H13" t="n">
-        <v>667</v>
+        <v>459</v>
       </c>
       <c r="I13" t="n">
-        <v>51657</v>
+        <v>51884</v>
       </c>
       <c r="J13" t="n">
-        <v>51906.5</v>
+        <v>52665.25</v>
       </c>
       <c r="K13" t="n">
-        <v>52306</v>
+        <v>52849.5</v>
       </c>
       <c r="L13" t="n">
-        <v>52705.5</v>
+        <v>53033.75</v>
       </c>
       <c r="M13" t="n">
-        <v>53030</v>
+        <v>53516.5</v>
       </c>
       <c r="N13" t="n">
-        <v>53354.5</v>
+        <v>53999.25</v>
       </c>
       <c r="O13" t="n">
-        <v>53829</v>
+        <v>53885</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1615,7 +1619,7 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1631,7 +1635,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1645,50 +1649,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>53230</v>
+        <v>53405</v>
       </c>
       <c r="C14" t="n">
-        <v>53421</v>
+        <v>53656</v>
       </c>
       <c r="D14" t="n">
-        <v>52962</v>
+        <v>53076</v>
       </c>
       <c r="E14" t="n">
-        <v>53372</v>
+        <v>53197</v>
       </c>
       <c r="F14" t="n">
-        <v>189</v>
+        <v>-175</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0036</v>
+        <v>-0.0033</v>
       </c>
       <c r="H14" t="n">
-        <v>459</v>
+        <v>580</v>
       </c>
       <c r="I14" t="n">
-        <v>51884</v>
+        <v>52503</v>
       </c>
       <c r="J14" t="n">
-        <v>52665.25</v>
+        <v>53003.25</v>
       </c>
       <c r="K14" t="n">
-        <v>52849.5</v>
+        <v>53142.5</v>
       </c>
       <c r="L14" t="n">
-        <v>53033.75</v>
+        <v>53281.75</v>
       </c>
       <c r="M14" t="n">
-        <v>53516.5</v>
+        <v>53601.5</v>
       </c>
       <c r="N14" t="n">
-        <v>53999.25</v>
+        <v>53921.25</v>
       </c>
       <c r="O14" t="n">
-        <v>53885</v>
+        <v>53880</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1696,17 +1700,19 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U14" s="8" t="n">
@@ -1715,85 +1721,87 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>53405</v>
+        <v>53166</v>
       </c>
       <c r="C15" t="n">
-        <v>53656</v>
+        <v>53207</v>
       </c>
       <c r="D15" t="n">
-        <v>53076</v>
+        <v>52343</v>
       </c>
       <c r="E15" t="n">
-        <v>53197</v>
+        <v>52624</v>
       </c>
       <c r="F15" t="n">
-        <v>-175</v>
+        <v>-573</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0108</v>
       </c>
       <c r="H15" t="n">
-        <v>580</v>
+        <v>864</v>
       </c>
       <c r="I15" t="n">
-        <v>52503</v>
+        <v>52496</v>
       </c>
       <c r="J15" t="n">
-        <v>53003.25</v>
+        <v>52532.5</v>
       </c>
       <c r="K15" t="n">
-        <v>53142.5</v>
+        <v>52907</v>
       </c>
       <c r="L15" t="n">
-        <v>53281.75</v>
+        <v>53281.5</v>
       </c>
       <c r="M15" t="n">
-        <v>53601.5</v>
+        <v>53487</v>
       </c>
       <c r="N15" t="n">
-        <v>53921.25</v>
+        <v>53692.5</v>
       </c>
       <c r="O15" t="n">
-        <v>53880</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
+        <v>54236</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1801,83 +1809,73 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>53166</v>
+        <v>52541</v>
       </c>
       <c r="C16" t="n">
-        <v>53207</v>
+        <v>52865</v>
       </c>
       <c r="D16" t="n">
-        <v>52343</v>
+        <v>52501</v>
       </c>
       <c r="E16" t="n">
-        <v>52624</v>
+        <v>52761</v>
       </c>
       <c r="F16" t="n">
-        <v>-573</v>
+        <v>137</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0108</v>
+        <v>0.0026</v>
       </c>
       <c r="H16" t="n">
-        <v>864</v>
+        <v>364</v>
       </c>
       <c r="I16" t="n">
-        <v>52496</v>
+        <v>51479</v>
       </c>
       <c r="J16" t="n">
-        <v>52532.5</v>
+        <v>51684.5</v>
       </c>
       <c r="K16" t="n">
-        <v>52907</v>
+        <v>52192</v>
       </c>
       <c r="L16" t="n">
-        <v>53281.5</v>
+        <v>52699.5</v>
       </c>
       <c r="M16" t="n">
-        <v>53487</v>
+        <v>53056</v>
       </c>
       <c r="N16" t="n">
-        <v>53692.5</v>
+        <v>53412.5</v>
       </c>
       <c r="O16" t="n">
-        <v>54236</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>54071</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1889,60 +1887,64 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52541</v>
+        <v>52753</v>
       </c>
       <c r="C17" t="n">
-        <v>52865</v>
+        <v>52992</v>
       </c>
       <c r="D17" t="n">
-        <v>52501</v>
+        <v>52506</v>
       </c>
       <c r="E17" t="n">
-        <v>52761</v>
+        <v>52906</v>
       </c>
       <c r="F17" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0027</v>
       </c>
       <c r="H17" t="n">
-        <v>364</v>
+        <v>486</v>
       </c>
       <c r="I17" t="n">
-        <v>51479</v>
+        <v>52137</v>
       </c>
       <c r="J17" t="n">
-        <v>51684.5</v>
+        <v>52436</v>
       </c>
       <c r="K17" t="n">
-        <v>52192</v>
+        <v>52579</v>
       </c>
       <c r="L17" t="n">
-        <v>52699.5</v>
+        <v>52722</v>
       </c>
       <c r="M17" t="n">
-        <v>53056</v>
+        <v>52943</v>
       </c>
       <c r="N17" t="n">
-        <v>53412.5</v>
+        <v>53164</v>
       </c>
       <c r="O17" t="n">
-        <v>54071</v>
+        <v>53229</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1950,16 +1952,20 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1967,64 +1973,64 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52753</v>
+        <v>52844</v>
       </c>
       <c r="C18" t="n">
-        <v>52992</v>
+        <v>53113</v>
       </c>
       <c r="D18" t="n">
-        <v>52506</v>
+        <v>52603</v>
       </c>
       <c r="E18" t="n">
-        <v>52906</v>
+        <v>52764</v>
       </c>
       <c r="F18" t="n">
-        <v>145</v>
+        <v>-142</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0027</v>
       </c>
       <c r="H18" t="n">
-        <v>486</v>
+        <v>510</v>
       </c>
       <c r="I18" t="n">
-        <v>52137</v>
+        <v>52020</v>
       </c>
       <c r="J18" t="n">
-        <v>52436</v>
+        <v>52498.5</v>
       </c>
       <c r="K18" t="n">
-        <v>52579</v>
+        <v>52663</v>
       </c>
       <c r="L18" t="n">
-        <v>52722</v>
+        <v>52827.5</v>
       </c>
       <c r="M18" t="n">
-        <v>52943</v>
+        <v>53149</v>
       </c>
       <c r="N18" t="n">
-        <v>53164</v>
+        <v>53470.5</v>
       </c>
       <c r="O18" t="n">
-        <v>53229</v>
+        <v>53478</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2039,13 +2045,11 @@
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2053,64 +2057,64 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>52844</v>
+        <v>52731</v>
       </c>
       <c r="C19" t="n">
-        <v>53113</v>
+        <v>52981</v>
       </c>
       <c r="D19" t="n">
-        <v>52603</v>
+        <v>52255</v>
       </c>
       <c r="E19" t="n">
-        <v>52764</v>
+        <v>52791</v>
       </c>
       <c r="F19" t="n">
-        <v>-142</v>
+        <v>27</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0005</v>
       </c>
       <c r="H19" t="n">
-        <v>510</v>
+        <v>726</v>
       </c>
       <c r="I19" t="n">
-        <v>52020</v>
+        <v>52093</v>
       </c>
       <c r="J19" t="n">
-        <v>52498.5</v>
+        <v>52207</v>
       </c>
       <c r="K19" t="n">
-        <v>52663</v>
+        <v>52509</v>
       </c>
       <c r="L19" t="n">
-        <v>52827.5</v>
+        <v>52811</v>
       </c>
       <c r="M19" t="n">
-        <v>53149</v>
+        <v>53019</v>
       </c>
       <c r="N19" t="n">
-        <v>53470.5</v>
+        <v>53227</v>
       </c>
       <c r="O19" t="n">
-        <v>53478</v>
+        <v>53623</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2123,7 +2127,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="S19" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2137,64 +2141,64 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>52731</v>
+        <v>52792</v>
       </c>
       <c r="C20" t="n">
-        <v>52981</v>
+        <v>53088</v>
       </c>
       <c r="D20" t="n">
-        <v>52255</v>
+        <v>52680</v>
       </c>
       <c r="E20" t="n">
-        <v>52791</v>
+        <v>52900</v>
       </c>
       <c r="F20" t="n">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0021</v>
       </c>
       <c r="H20" t="n">
-        <v>726</v>
+        <v>408</v>
       </c>
       <c r="I20" t="n">
-        <v>52093</v>
+        <v>51529</v>
       </c>
       <c r="J20" t="n">
-        <v>52207</v>
+        <v>52151.5</v>
       </c>
       <c r="K20" t="n">
-        <v>52509</v>
+        <v>52428</v>
       </c>
       <c r="L20" t="n">
-        <v>52811</v>
+        <v>52704.5</v>
       </c>
       <c r="M20" t="n">
-        <v>53019</v>
+        <v>53154</v>
       </c>
       <c r="N20" t="n">
-        <v>53227</v>
+        <v>53603.5</v>
       </c>
       <c r="O20" t="n">
-        <v>53623</v>
+        <v>53707</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2202,14 +2206,12 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R20" s="6" t="n">
+        <v/>
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2221,64 +2223,64 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>52792</v>
+        <v>52919</v>
       </c>
       <c r="C21" t="n">
-        <v>53088</v>
+        <v>53108</v>
       </c>
       <c r="D21" t="n">
-        <v>52680</v>
+        <v>52607</v>
       </c>
       <c r="E21" t="n">
-        <v>52900</v>
+        <v>52786</v>
       </c>
       <c r="F21" t="n">
-        <v>109</v>
+        <v>-114</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0022</v>
       </c>
       <c r="H21" t="n">
-        <v>408</v>
+        <v>501</v>
       </c>
       <c r="I21" t="n">
-        <v>51529</v>
+        <v>52272</v>
       </c>
       <c r="J21" t="n">
-        <v>52151.5</v>
+        <v>52500</v>
       </c>
       <c r="K21" t="n">
-        <v>52428</v>
+        <v>52696</v>
       </c>
       <c r="L21" t="n">
-        <v>52704.5</v>
+        <v>52892</v>
       </c>
       <c r="M21" t="n">
-        <v>53154</v>
+        <v>53104</v>
       </c>
       <c r="N21" t="n">
-        <v>53603.5</v>
+        <v>53316</v>
       </c>
       <c r="O21" t="n">
-        <v>53707</v>
+        <v>53496</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2286,16 +2288,20 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2303,85 +2309,85 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>52919</v>
+        <v>52778</v>
       </c>
       <c r="C22" t="n">
-        <v>53108</v>
+        <v>52835</v>
       </c>
       <c r="D22" t="n">
-        <v>52607</v>
+        <v>52174</v>
       </c>
       <c r="E22" t="n">
-        <v>52786</v>
+        <v>52375</v>
       </c>
       <c r="F22" t="n">
-        <v>-114</v>
+        <v>-411</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0078</v>
       </c>
       <c r="H22" t="n">
-        <v>501</v>
+        <v>661</v>
       </c>
       <c r="I22" t="n">
-        <v>52272</v>
+        <v>52106</v>
       </c>
       <c r="J22" t="n">
-        <v>52500</v>
+        <v>52249.25</v>
       </c>
       <c r="K22" t="n">
-        <v>52696</v>
+        <v>52535.5</v>
       </c>
       <c r="L22" t="n">
-        <v>52892</v>
+        <v>52821.75</v>
       </c>
       <c r="M22" t="n">
-        <v>53104</v>
+        <v>53036.5</v>
       </c>
       <c r="N22" t="n">
-        <v>53316</v>
+        <v>53251.25</v>
       </c>
       <c r="O22" t="n">
-        <v>53496</v>
+        <v>53609</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2389,79 +2395,73 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>52778</v>
+        <v>52300</v>
       </c>
       <c r="C23" t="n">
-        <v>52835</v>
+        <v>52633</v>
       </c>
       <c r="D23" t="n">
-        <v>52174</v>
+        <v>51999</v>
       </c>
       <c r="E23" t="n">
-        <v>52375</v>
+        <v>52073</v>
       </c>
       <c r="F23" t="n">
-        <v>-411</v>
+        <v>-302</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0078</v>
+        <v>-0.0058</v>
       </c>
       <c r="H23" t="n">
-        <v>661</v>
+        <v>634</v>
       </c>
       <c r="I23" t="n">
-        <v>52106</v>
+        <v>51513</v>
       </c>
       <c r="J23" t="n">
-        <v>52249.25</v>
+        <v>51649.25</v>
       </c>
       <c r="K23" t="n">
-        <v>52535.5</v>
+        <v>52044.5</v>
       </c>
       <c r="L23" t="n">
-        <v>52821.75</v>
+        <v>52439.75</v>
       </c>
       <c r="M23" t="n">
-        <v>53036.5</v>
+        <v>52705.5</v>
       </c>
       <c r="N23" t="n">
-        <v>53251.25</v>
+        <v>52971.25</v>
       </c>
       <c r="O23" t="n">
-        <v>53609</v>
+        <v>53496</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2475,7 +2475,7 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2485,50 +2485,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>52300</v>
+        <v>52091</v>
       </c>
       <c r="C24" t="n">
-        <v>52633</v>
+        <v>52590</v>
       </c>
       <c r="D24" t="n">
-        <v>51999</v>
+        <v>52035</v>
       </c>
       <c r="E24" t="n">
-        <v>52073</v>
+        <v>52443</v>
       </c>
       <c r="F24" t="n">
-        <v>-302</v>
+        <v>370</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.0071</v>
       </c>
       <c r="H24" t="n">
-        <v>634</v>
+        <v>555</v>
       </c>
       <c r="I24" t="n">
-        <v>51513</v>
+        <v>51365</v>
       </c>
       <c r="J24" t="n">
-        <v>51649.25</v>
+        <v>51317.5</v>
       </c>
       <c r="K24" t="n">
-        <v>52044.5</v>
+        <v>51756</v>
       </c>
       <c r="L24" t="n">
-        <v>52439.75</v>
+        <v>52194.5</v>
       </c>
       <c r="M24" t="n">
-        <v>52705.5</v>
+        <v>52390</v>
       </c>
       <c r="N24" t="n">
-        <v>52971.25</v>
+        <v>52585.5</v>
       </c>
       <c r="O24" t="n">
-        <v>53496</v>
+        <v>53267</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2536,79 +2536,85 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>52091</v>
+        <v>52431</v>
       </c>
       <c r="C25" t="n">
-        <v>52590</v>
+        <v>52721</v>
       </c>
       <c r="D25" t="n">
-        <v>52035</v>
+        <v>52262</v>
       </c>
       <c r="E25" t="n">
-        <v>52443</v>
+        <v>52449</v>
       </c>
       <c r="F25" t="n">
-        <v>370</v>
+        <v>6</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0001</v>
       </c>
       <c r="H25" t="n">
-        <v>555</v>
+        <v>459</v>
       </c>
       <c r="I25" t="n">
-        <v>51365</v>
+        <v>51480</v>
       </c>
       <c r="J25" t="n">
-        <v>51317.5</v>
+        <v>51953.25</v>
       </c>
       <c r="K25" t="n">
-        <v>51756</v>
+        <v>52165.5</v>
       </c>
       <c r="L25" t="n">
-        <v>52194.5</v>
+        <v>52377.75</v>
       </c>
       <c r="M25" t="n">
-        <v>52390</v>
+        <v>52720.5</v>
       </c>
       <c r="N25" t="n">
-        <v>52585.5</v>
+        <v>53063.25</v>
       </c>
       <c r="O25" t="n">
-        <v>53267</v>
+        <v>53145</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2619,101 +2625,103 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>52431</v>
+        <v>52430</v>
       </c>
       <c r="C26" t="n">
-        <v>52721</v>
+        <v>52515</v>
       </c>
       <c r="D26" t="n">
-        <v>52262</v>
+        <v>51720</v>
       </c>
       <c r="E26" t="n">
-        <v>52449</v>
+        <v>51894</v>
       </c>
       <c r="F26" t="n">
-        <v>6</v>
+        <v>-555</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0106</v>
       </c>
       <c r="H26" t="n">
-        <v>459</v>
+        <v>795</v>
       </c>
       <c r="I26" t="n">
-        <v>51480</v>
+        <v>51803</v>
       </c>
       <c r="J26" t="n">
-        <v>51953.25</v>
+        <v>51968.75</v>
       </c>
       <c r="K26" t="n">
-        <v>52165.5</v>
+        <v>52219.5</v>
       </c>
       <c r="L26" t="n">
-        <v>52377.75</v>
+        <v>52470.25</v>
       </c>
       <c r="M26" t="n">
-        <v>52720.5</v>
+        <v>52678.5</v>
       </c>
       <c r="N26" t="n">
-        <v>53063.25</v>
+        <v>52886.75</v>
       </c>
       <c r="O26" t="n">
-        <v>53145</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+        <v>53180</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2721,148 +2729,144 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>52430</v>
+        <v>51920</v>
       </c>
       <c r="C27" t="n">
-        <v>52515</v>
+        <v>52314</v>
       </c>
       <c r="D27" t="n">
-        <v>51720</v>
+        <v>51846</v>
       </c>
       <c r="E27" t="n">
-        <v>51894</v>
+        <v>52124</v>
       </c>
       <c r="F27" t="n">
-        <v>-555</v>
+        <v>230</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0044</v>
       </c>
       <c r="H27" t="n">
-        <v>795</v>
+        <v>468</v>
       </c>
       <c r="I27" t="n">
-        <v>51803</v>
+        <v>50925</v>
       </c>
       <c r="J27" t="n">
-        <v>51968.75</v>
+        <v>50987.25</v>
       </c>
       <c r="K27" t="n">
-        <v>52219.5</v>
+        <v>51496.5</v>
       </c>
       <c r="L27" t="n">
-        <v>52470.25</v>
+        <v>52005.75</v>
       </c>
       <c r="M27" t="n">
-        <v>52678.5</v>
+        <v>52291.5</v>
       </c>
       <c r="N27" t="n">
-        <v>52886.75</v>
+        <v>52577.25</v>
       </c>
       <c r="O27" t="n">
-        <v>53180</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
+        <v>53310</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
       <c r="U27" s="8" t="n">
         <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>51920</v>
+        <v>52299</v>
       </c>
       <c r="C28" t="n">
-        <v>52314</v>
+        <v>52790</v>
       </c>
       <c r="D28" t="n">
-        <v>51846</v>
+        <v>52173</v>
       </c>
       <c r="E28" t="n">
-        <v>52124</v>
+        <v>52382</v>
       </c>
       <c r="F28" t="n">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0049</v>
       </c>
       <c r="H28" t="n">
-        <v>468</v>
+        <v>617</v>
       </c>
       <c r="I28" t="n">
-        <v>50925</v>
+        <v>51378</v>
       </c>
       <c r="J28" t="n">
-        <v>50987.25</v>
+        <v>51678</v>
       </c>
       <c r="K28" t="n">
-        <v>51496.5</v>
+        <v>51890</v>
       </c>
       <c r="L28" t="n">
-        <v>52005.75</v>
+        <v>52102</v>
       </c>
       <c r="M28" t="n">
-        <v>52291.5</v>
+        <v>52358</v>
       </c>
       <c r="N28" t="n">
-        <v>52577.25</v>
+        <v>52614</v>
       </c>
       <c r="O28" t="n">
-        <v>53310</v>
+        <v>52782</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2873,80 +2877,84 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>52299</v>
+        <v>52405</v>
       </c>
       <c r="C29" t="n">
-        <v>52790</v>
+        <v>53105</v>
       </c>
       <c r="D29" t="n">
-        <v>52173</v>
+        <v>52290</v>
       </c>
       <c r="E29" t="n">
-        <v>52382</v>
+        <v>52944</v>
       </c>
       <c r="F29" t="n">
-        <v>258</v>
+        <v>562</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0107</v>
       </c>
       <c r="H29" t="n">
-        <v>617</v>
+        <v>815</v>
       </c>
       <c r="I29" t="n">
-        <v>51378</v>
+        <v>51556</v>
       </c>
       <c r="J29" t="n">
-        <v>51678</v>
+        <v>51715.25</v>
       </c>
       <c r="K29" t="n">
-        <v>51890</v>
+        <v>52073.5</v>
       </c>
       <c r="L29" t="n">
-        <v>52102</v>
+        <v>52431.75</v>
       </c>
       <c r="M29" t="n">
-        <v>52358</v>
+        <v>52690.5</v>
       </c>
       <c r="N29" t="n">
-        <v>52614</v>
+        <v>52949.25</v>
       </c>
       <c r="O29" t="n">
-        <v>52782</v>
+        <v>53407</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2957,27 +2965,25 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="V29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2991,220 +2997,218 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>52405</v>
+        <v>52915</v>
       </c>
       <c r="C30" t="n">
-        <v>53105</v>
+        <v>53033</v>
       </c>
       <c r="D30" t="n">
-        <v>52290</v>
+        <v>51630</v>
       </c>
       <c r="E30" t="n">
-        <v>52944</v>
+        <v>51765</v>
       </c>
       <c r="F30" t="n">
-        <v>562</v>
+        <v>-1179</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0223</v>
       </c>
       <c r="H30" t="n">
-        <v>815</v>
+        <v>1403</v>
       </c>
       <c r="I30" t="n">
-        <v>51556</v>
+        <v>51475</v>
       </c>
       <c r="J30" t="n">
-        <v>51715.25</v>
+        <v>52252.25</v>
       </c>
       <c r="K30" t="n">
-        <v>52073.5</v>
+        <v>52536.5</v>
       </c>
       <c r="L30" t="n">
-        <v>52431.75</v>
+        <v>52820.75</v>
       </c>
       <c r="M30" t="n">
-        <v>52690.5</v>
+        <v>53351.5</v>
       </c>
       <c r="N30" t="n">
-        <v>52949.25</v>
+        <v>53882.25</v>
       </c>
       <c r="O30" t="n">
-        <v>53407</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+        <v>53920</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>52915</v>
+        <v>51759</v>
       </c>
       <c r="C31" t="n">
-        <v>53033</v>
+        <v>52484</v>
       </c>
       <c r="D31" t="n">
-        <v>51630</v>
+        <v>51732</v>
       </c>
       <c r="E31" t="n">
-        <v>51765</v>
+        <v>52380</v>
       </c>
       <c r="F31" t="n">
-        <v>-1179</v>
+        <v>615</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0119</v>
       </c>
       <c r="H31" t="n">
-        <v>1403</v>
+        <v>752</v>
       </c>
       <c r="I31" t="n">
-        <v>51475</v>
+        <v>50227</v>
       </c>
       <c r="J31" t="n">
-        <v>52252.25</v>
+        <v>50078.75</v>
       </c>
       <c r="K31" t="n">
-        <v>52536.5</v>
+        <v>51063.5</v>
       </c>
       <c r="L31" t="n">
-        <v>52820.75</v>
+        <v>52048.25</v>
       </c>
       <c r="M31" t="n">
-        <v>53351.5</v>
+        <v>52466.5</v>
       </c>
       <c r="N31" t="n">
-        <v>53882.25</v>
+        <v>52884.75</v>
       </c>
       <c r="O31" t="n">
-        <v>53920</v>
-      </c>
-      <c r="P31" s="6" t="inlineStr">
+        <v>54436</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>51759</v>
+        <v>52395</v>
       </c>
       <c r="C32" t="n">
-        <v>52484</v>
+        <v>52772</v>
       </c>
       <c r="D32" t="n">
-        <v>51732</v>
+        <v>52124</v>
       </c>
       <c r="E32" t="n">
-        <v>52380</v>
+        <v>52635</v>
       </c>
       <c r="F32" t="n">
-        <v>615</v>
+        <v>255</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0119</v>
+        <v>0.0049</v>
       </c>
       <c r="H32" t="n">
-        <v>752</v>
+        <v>648</v>
       </c>
       <c r="I32" t="n">
-        <v>50227</v>
+        <v>50980</v>
       </c>
       <c r="J32" t="n">
-        <v>50078.75</v>
+        <v>51764</v>
       </c>
       <c r="K32" t="n">
-        <v>51063.5</v>
+        <v>52004</v>
       </c>
       <c r="L32" t="n">
-        <v>52048.25</v>
+        <v>52244</v>
       </c>
       <c r="M32" t="n">
-        <v>52466.5</v>
+        <v>52756</v>
       </c>
       <c r="N32" t="n">
-        <v>52884.75</v>
+        <v>53268</v>
       </c>
       <c r="O32" t="n">
-        <v>54436</v>
+        <v>53236</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3215,7 +3219,7 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3231,64 +3235,64 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>52395</v>
+        <v>52780</v>
       </c>
       <c r="C33" t="n">
-        <v>52772</v>
+        <v>53414</v>
       </c>
       <c r="D33" t="n">
-        <v>52124</v>
+        <v>52777</v>
       </c>
       <c r="E33" t="n">
-        <v>52635</v>
+        <v>53334</v>
       </c>
       <c r="F33" t="n">
-        <v>255</v>
+        <v>699</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0133</v>
       </c>
       <c r="H33" t="n">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="I33" t="n">
-        <v>50980</v>
+        <v>51476</v>
       </c>
       <c r="J33" t="n">
-        <v>51764</v>
+        <v>52080.5</v>
       </c>
       <c r="K33" t="n">
-        <v>52004</v>
+        <v>52311</v>
       </c>
       <c r="L33" t="n">
-        <v>52244</v>
+        <v>52541.5</v>
       </c>
       <c r="M33" t="n">
-        <v>52756</v>
+        <v>52959</v>
       </c>
       <c r="N33" t="n">
-        <v>53268</v>
+        <v>53376.5</v>
       </c>
       <c r="O33" t="n">
-        <v>53236</v>
+        <v>53420</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3299,23 +3303,25 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
+      <c r="S33" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3329,50 +3335,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>52780</v>
+        <v>53381</v>
       </c>
       <c r="C34" t="n">
-        <v>53414</v>
+        <v>54423</v>
       </c>
       <c r="D34" t="n">
-        <v>52777</v>
+        <v>53267</v>
       </c>
       <c r="E34" t="n">
-        <v>53334</v>
+        <v>54268</v>
       </c>
       <c r="F34" t="n">
-        <v>699</v>
+        <v>934</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0175</v>
       </c>
       <c r="H34" t="n">
-        <v>637</v>
+        <v>1156</v>
       </c>
       <c r="I34" t="n">
-        <v>51476</v>
+        <v>52140</v>
       </c>
       <c r="J34" t="n">
-        <v>52080.5</v>
+        <v>52816.25</v>
       </c>
       <c r="K34" t="n">
-        <v>52311</v>
+        <v>53015.5</v>
       </c>
       <c r="L34" t="n">
-        <v>52541.5</v>
+        <v>53214.75</v>
       </c>
       <c r="M34" t="n">
-        <v>52959</v>
+        <v>53652.5</v>
       </c>
       <c r="N34" t="n">
-        <v>53376.5</v>
+        <v>54090.25</v>
       </c>
       <c r="O34" t="n">
-        <v>53420</v>
+        <v>54051</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3383,7 +3389,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3398,67 +3404,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V34" s="8" t="n">
-        <v/>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W34" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>53381</v>
+        <v>54369</v>
       </c>
       <c r="C35" t="n">
-        <v>54423</v>
+        <v>54884</v>
       </c>
       <c r="D35" t="n">
-        <v>53267</v>
+        <v>54342</v>
       </c>
       <c r="E35" t="n">
-        <v>54268</v>
+        <v>54494</v>
       </c>
       <c r="F35" t="n">
-        <v>934</v>
+        <v>226</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0042</v>
       </c>
       <c r="H35" t="n">
-        <v>1156</v>
+        <v>542</v>
       </c>
       <c r="I35" t="n">
-        <v>52140</v>
+        <v>52111</v>
       </c>
       <c r="J35" t="n">
-        <v>52816.25</v>
+        <v>53323.5</v>
       </c>
       <c r="K35" t="n">
-        <v>53015.5</v>
+        <v>53690</v>
       </c>
       <c r="L35" t="n">
-        <v>53214.75</v>
+        <v>54056.5</v>
       </c>
       <c r="M35" t="n">
-        <v>53652.5</v>
+        <v>54846</v>
       </c>
       <c r="N35" t="n">
-        <v>54090.25</v>
+        <v>55635.5</v>
       </c>
       <c r="O35" t="n">
-        <v>54051</v>
+        <v>55579</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3469,27 +3473,23 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3499,69 +3499,71 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>54369</v>
+        <v>54555</v>
       </c>
       <c r="C36" t="n">
-        <v>54884</v>
+        <v>54678</v>
       </c>
       <c r="D36" t="n">
-        <v>54342</v>
+        <v>53952</v>
       </c>
       <c r="E36" t="n">
-        <v>54494</v>
+        <v>54013</v>
       </c>
       <c r="F36" t="n">
-        <v>226</v>
+        <v>-481</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>542</v>
+        <v>726</v>
       </c>
       <c r="I36" t="n">
-        <v>52111</v>
+        <v>53800</v>
       </c>
       <c r="J36" t="n">
-        <v>53323.5</v>
+        <v>53892.5</v>
       </c>
       <c r="K36" t="n">
-        <v>53690</v>
+        <v>54223</v>
       </c>
       <c r="L36" t="n">
-        <v>54056.5</v>
+        <v>54553.5</v>
       </c>
       <c r="M36" t="n">
-        <v>54846</v>
+        <v>54765</v>
       </c>
       <c r="N36" t="n">
-        <v>55635.5</v>
+        <v>54976.5</v>
       </c>
       <c r="O36" t="n">
-        <v>55579</v>
+        <v>55426</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3569,77 +3571,77 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>54555</v>
+        <v>54040</v>
       </c>
       <c r="C37" t="n">
-        <v>54678</v>
+        <v>54202</v>
       </c>
       <c r="D37" t="n">
-        <v>53952</v>
+        <v>53879</v>
       </c>
       <c r="E37" t="n">
-        <v>54013</v>
+        <v>54152</v>
       </c>
       <c r="F37" t="n">
-        <v>-481</v>
+        <v>139</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0026</v>
       </c>
       <c r="H37" t="n">
-        <v>726</v>
+        <v>323</v>
       </c>
       <c r="I37" t="n">
-        <v>53800</v>
+        <v>53226</v>
       </c>
       <c r="J37" t="n">
-        <v>53892.5</v>
+        <v>53136</v>
       </c>
       <c r="K37" t="n">
-        <v>54223</v>
+        <v>53650</v>
       </c>
       <c r="L37" t="n">
-        <v>54553.5</v>
+        <v>54164</v>
       </c>
       <c r="M37" t="n">
-        <v>54765</v>
+        <v>54376</v>
       </c>
       <c r="N37" t="n">
-        <v>54976.5</v>
+        <v>54588</v>
       </c>
       <c r="O37" t="n">
-        <v>55426</v>
+        <v>55404</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3651,64 +3653,64 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>54040</v>
+        <v>54133</v>
       </c>
       <c r="C38" t="n">
-        <v>54202</v>
+        <v>54170</v>
       </c>
       <c r="D38" t="n">
-        <v>53879</v>
+        <v>53952</v>
       </c>
       <c r="E38" t="n">
-        <v>54152</v>
+        <v>54063</v>
       </c>
       <c r="F38" t="n">
-        <v>139</v>
+        <v>-89</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0016</v>
       </c>
       <c r="H38" t="n">
-        <v>323</v>
+        <v>218</v>
       </c>
       <c r="I38" t="n">
-        <v>53226</v>
+        <v>53556</v>
       </c>
       <c r="J38" t="n">
-        <v>53136</v>
+        <v>53884.75</v>
       </c>
       <c r="K38" t="n">
-        <v>53650</v>
+        <v>53990.5</v>
       </c>
       <c r="L38" t="n">
-        <v>54164</v>
+        <v>54096.25</v>
       </c>
       <c r="M38" t="n">
-        <v>54376</v>
+        <v>54313.5</v>
       </c>
       <c r="N38" t="n">
-        <v>54588</v>
+        <v>54530.75</v>
       </c>
       <c r="O38" t="n">
-        <v>55404</v>
+        <v>54525</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3716,10 +3718,12 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3733,7 +3737,7 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3747,77 +3751,83 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>54133</v>
+        <v>54049</v>
       </c>
       <c r="C39" t="n">
-        <v>54170</v>
+        <v>54336</v>
       </c>
       <c r="D39" t="n">
-        <v>53952</v>
+        <v>53855</v>
       </c>
       <c r="E39" t="n">
-        <v>54063</v>
+        <v>53880</v>
       </c>
       <c r="F39" t="n">
-        <v>-89</v>
+        <v>-183</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0034</v>
       </c>
       <c r="H39" t="n">
-        <v>218</v>
+        <v>481</v>
       </c>
       <c r="I39" t="n">
-        <v>53556</v>
+        <v>53734</v>
       </c>
       <c r="J39" t="n">
-        <v>53884.75</v>
+        <v>53846</v>
       </c>
       <c r="K39" t="n">
-        <v>53990.5</v>
+        <v>53954</v>
       </c>
       <c r="L39" t="n">
-        <v>54096.25</v>
+        <v>54062</v>
       </c>
       <c r="M39" t="n">
-        <v>54313.5</v>
+        <v>54172</v>
       </c>
       <c r="N39" t="n">
-        <v>54530.75</v>
+        <v>54282</v>
       </c>
       <c r="O39" t="n">
-        <v>54525</v>
+        <v>54388</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3831,140 +3841,134 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>54049</v>
+        <v>53903</v>
       </c>
       <c r="C40" t="n">
-        <v>54336</v>
+        <v>54150</v>
       </c>
       <c r="D40" t="n">
-        <v>53855</v>
+        <v>53830</v>
       </c>
       <c r="E40" t="n">
-        <v>53880</v>
+        <v>53871</v>
       </c>
       <c r="F40" t="n">
-        <v>-183</v>
+        <v>-9</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0002</v>
       </c>
       <c r="H40" t="n">
-        <v>481</v>
+        <v>320</v>
       </c>
       <c r="I40" t="n">
-        <v>53734</v>
+        <v>53374</v>
       </c>
       <c r="J40" t="n">
-        <v>53846</v>
+        <v>53291.25</v>
       </c>
       <c r="K40" t="n">
-        <v>53954</v>
+        <v>53639.5</v>
       </c>
       <c r="L40" t="n">
-        <v>54062</v>
+        <v>53987.75</v>
       </c>
       <c r="M40" t="n">
-        <v>54172</v>
+        <v>54120.5</v>
       </c>
       <c r="N40" t="n">
-        <v>54282</v>
+        <v>54253.25</v>
       </c>
       <c r="O40" t="n">
-        <v>54388</v>
+        <v>54817</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>53903</v>
+        <v>53905</v>
       </c>
       <c r="C41" t="n">
-        <v>54150</v>
+        <v>54149</v>
       </c>
       <c r="D41" t="n">
-        <v>53830</v>
+        <v>53715</v>
       </c>
       <c r="E41" t="n">
-        <v>53871</v>
+        <v>53935</v>
       </c>
       <c r="F41" t="n">
-        <v>-9</v>
+        <v>64</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0012</v>
       </c>
       <c r="H41" t="n">
-        <v>320</v>
+        <v>434</v>
       </c>
       <c r="I41" t="n">
-        <v>53374</v>
+        <v>53510</v>
       </c>
       <c r="J41" t="n">
-        <v>53291.25</v>
+        <v>53491.5</v>
       </c>
       <c r="K41" t="n">
-        <v>53639.5</v>
+        <v>53711</v>
       </c>
       <c r="L41" t="n">
-        <v>53987.75</v>
+        <v>53930.5</v>
       </c>
       <c r="M41" t="n">
-        <v>54120.5</v>
+        <v>54031</v>
       </c>
       <c r="N41" t="n">
-        <v>54253.25</v>
+        <v>54131.5</v>
       </c>
       <c r="O41" t="n">
-        <v>54817</v>
+        <v>54470</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3977,7 +3981,7 @@
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
@@ -3985,70 +3989,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U41" s="8" t="n">
-        <v/>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>53905</v>
+        <v>53961</v>
       </c>
       <c r="C42" t="n">
-        <v>54149</v>
+        <v>53999</v>
       </c>
       <c r="D42" t="n">
-        <v>53715</v>
+        <v>53745</v>
       </c>
       <c r="E42" t="n">
-        <v>53935</v>
+        <v>53807</v>
       </c>
       <c r="F42" t="n">
-        <v>64</v>
+        <v>-128</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0024</v>
       </c>
       <c r="H42" t="n">
-        <v>434</v>
+        <v>254</v>
       </c>
       <c r="I42" t="n">
-        <v>53510</v>
+        <v>53281</v>
       </c>
       <c r="J42" t="n">
-        <v>53491.5</v>
+        <v>53502.5</v>
       </c>
       <c r="K42" t="n">
-        <v>53711</v>
+        <v>53718</v>
       </c>
       <c r="L42" t="n">
-        <v>53930.5</v>
+        <v>53933.5</v>
       </c>
       <c r="M42" t="n">
-        <v>54031</v>
+        <v>54152</v>
       </c>
       <c r="N42" t="n">
-        <v>54131.5</v>
+        <v>54370.5</v>
       </c>
       <c r="O42" t="n">
-        <v>54470</v>
+        <v>54583</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4056,28 +4062,26 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4091,63 +4095,67 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>53961</v>
+        <v>53790</v>
       </c>
       <c r="C43" t="n">
-        <v>53999</v>
+        <v>53840</v>
       </c>
       <c r="D43" t="n">
-        <v>53745</v>
+        <v>53464</v>
       </c>
       <c r="E43" t="n">
-        <v>53807</v>
+        <v>53544</v>
       </c>
       <c r="F43" t="n">
-        <v>-128</v>
+        <v>-263</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0049</v>
       </c>
       <c r="H43" t="n">
-        <v>254</v>
+        <v>376</v>
       </c>
       <c r="I43" t="n">
-        <v>53281</v>
+        <v>53491</v>
       </c>
       <c r="J43" t="n">
-        <v>53502.5</v>
+        <v>53520.5</v>
       </c>
       <c r="K43" t="n">
-        <v>53718</v>
+        <v>53680</v>
       </c>
       <c r="L43" t="n">
-        <v>53933.5</v>
+        <v>53839.5</v>
       </c>
       <c r="M43" t="n">
-        <v>54152</v>
+        <v>53934</v>
       </c>
       <c r="N43" t="n">
-        <v>54370.5</v>
+        <v>54028.5</v>
       </c>
       <c r="O43" t="n">
-        <v>54583</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
+        <v>54253</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4161,81 +4169,77 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>53790</v>
+        <v>53501</v>
       </c>
       <c r="C44" t="n">
-        <v>53840</v>
+        <v>53594</v>
       </c>
       <c r="D44" t="n">
-        <v>53464</v>
+        <v>53311</v>
       </c>
       <c r="E44" t="n">
-        <v>53544</v>
+        <v>53403</v>
       </c>
       <c r="F44" t="n">
-        <v>-263</v>
+        <v>-141</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0026</v>
       </c>
       <c r="H44" t="n">
-        <v>376</v>
+        <v>283</v>
       </c>
       <c r="I44" t="n">
-        <v>53491</v>
+        <v>53088</v>
       </c>
       <c r="J44" t="n">
-        <v>53520.5</v>
+        <v>53114</v>
       </c>
       <c r="K44" t="n">
-        <v>53680</v>
+        <v>53356</v>
       </c>
       <c r="L44" t="n">
-        <v>53839.5</v>
+        <v>53598</v>
       </c>
       <c r="M44" t="n">
-        <v>53934</v>
+        <v>53732</v>
       </c>
       <c r="N44" t="n">
-        <v>54028.5</v>
+        <v>53866</v>
       </c>
       <c r="O44" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
+        <v>54216</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
+      <c r="S44" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4249,7 +4253,7 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4263,50 +4267,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>53501</v>
+        <v>53408</v>
       </c>
       <c r="C45" t="n">
-        <v>53594</v>
+        <v>53780</v>
       </c>
       <c r="D45" t="n">
-        <v>53311</v>
+        <v>53337</v>
       </c>
       <c r="E45" t="n">
-        <v>53403</v>
+        <v>53530</v>
       </c>
       <c r="F45" t="n">
-        <v>-141</v>
+        <v>127</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0026</v>
+        <v>0.0024</v>
       </c>
       <c r="H45" t="n">
-        <v>283</v>
+        <v>443</v>
       </c>
       <c r="I45" t="n">
-        <v>53088</v>
+        <v>53028</v>
       </c>
       <c r="J45" t="n">
-        <v>53114</v>
+        <v>53095.25</v>
       </c>
       <c r="K45" t="n">
-        <v>53356</v>
+        <v>53261.5</v>
       </c>
       <c r="L45" t="n">
-        <v>53598</v>
+        <v>53427.75</v>
       </c>
       <c r="M45" t="n">
-        <v>53732</v>
+        <v>53544.5</v>
       </c>
       <c r="N45" t="n">
-        <v>53866</v>
+        <v>53661.25</v>
       </c>
       <c r="O45" t="n">
-        <v>54216</v>
+        <v>53877</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4314,114 +4318,114 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>53408</v>
+        <v>53529</v>
       </c>
       <c r="C46" t="n">
-        <v>53780</v>
+        <v>53589</v>
       </c>
       <c r="D46" t="n">
-        <v>53337</v>
+        <v>52812</v>
       </c>
       <c r="E46" t="n">
-        <v>53530</v>
+        <v>52849</v>
       </c>
       <c r="F46" t="n">
-        <v>127</v>
+        <v>-681</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0127</v>
       </c>
       <c r="H46" t="n">
-        <v>443</v>
+        <v>777</v>
       </c>
       <c r="I46" t="n">
-        <v>53028</v>
+        <v>52894</v>
       </c>
       <c r="J46" t="n">
-        <v>53095.25</v>
+        <v>53072.75</v>
       </c>
       <c r="K46" t="n">
-        <v>53261.5</v>
+        <v>53308.5</v>
       </c>
       <c r="L46" t="n">
-        <v>53427.75</v>
+        <v>53544.25</v>
       </c>
       <c r="M46" t="n">
-        <v>53544.5</v>
+        <v>53751.5</v>
       </c>
       <c r="N46" t="n">
-        <v>53661.25</v>
+        <v>53958.75</v>
       </c>
       <c r="O46" t="n">
-        <v>53877</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+        <v>54223</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
       <c r="W46" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr"/>
@@ -4429,134 +4433,136 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>53529</v>
+        <v>52876</v>
       </c>
       <c r="C47" t="n">
-        <v>53589</v>
+        <v>53418</v>
       </c>
       <c r="D47" t="n">
-        <v>52812</v>
+        <v>52838</v>
       </c>
       <c r="E47" t="n">
-        <v>52849</v>
+        <v>53353</v>
       </c>
       <c r="F47" t="n">
-        <v>-681</v>
+        <v>504</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0095</v>
       </c>
       <c r="H47" t="n">
-        <v>777</v>
+        <v>580</v>
       </c>
       <c r="I47" t="n">
-        <v>52894</v>
+        <v>52035</v>
       </c>
       <c r="J47" t="n">
-        <v>53072.75</v>
+        <v>51896.25</v>
       </c>
       <c r="K47" t="n">
-        <v>53308.5</v>
+        <v>52460.5</v>
       </c>
       <c r="L47" t="n">
-        <v>53544.25</v>
+        <v>53024.75</v>
       </c>
       <c r="M47" t="n">
-        <v>53751.5</v>
+        <v>53237.5</v>
       </c>
       <c r="N47" t="n">
-        <v>53958.75</v>
+        <v>53450.25</v>
       </c>
       <c r="O47" t="n">
-        <v>54223</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
+        <v>54366</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>52876</v>
+        <v>53367</v>
       </c>
       <c r="C48" t="n">
-        <v>53418</v>
+        <v>53567</v>
       </c>
       <c r="D48" t="n">
-        <v>52838</v>
+        <v>53210</v>
       </c>
       <c r="E48" t="n">
-        <v>53353</v>
+        <v>53489</v>
       </c>
       <c r="F48" t="n">
-        <v>504</v>
+        <v>136</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.0025</v>
       </c>
       <c r="H48" t="n">
-        <v>580</v>
+        <v>357</v>
       </c>
       <c r="I48" t="n">
-        <v>52035</v>
+        <v>52258</v>
       </c>
       <c r="J48" t="n">
-        <v>51896.25</v>
+        <v>52885.5</v>
       </c>
       <c r="K48" t="n">
-        <v>52460.5</v>
+        <v>53063</v>
       </c>
       <c r="L48" t="n">
-        <v>53024.75</v>
+        <v>53240.5</v>
       </c>
       <c r="M48" t="n">
-        <v>53237.5</v>
+        <v>53643</v>
       </c>
       <c r="N48" t="n">
-        <v>53450.25</v>
+        <v>54045.5</v>
       </c>
       <c r="O48" t="n">
-        <v>54366</v>
+        <v>53998</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4567,82 +4573,80 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
+      <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>53367</v>
+        <v>53524</v>
       </c>
       <c r="C49" t="n">
-        <v>53567</v>
+        <v>53797</v>
       </c>
       <c r="D49" t="n">
-        <v>53210</v>
+        <v>53426</v>
       </c>
       <c r="E49" t="n">
-        <v>53489</v>
+        <v>53645</v>
       </c>
       <c r="F49" t="n">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0029</v>
       </c>
       <c r="H49" t="n">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="I49" t="n">
-        <v>52258</v>
+        <v>52853</v>
       </c>
       <c r="J49" t="n">
-        <v>52885.5</v>
+        <v>53182.25</v>
       </c>
       <c r="K49" t="n">
-        <v>53063</v>
+        <v>53310.5</v>
       </c>
       <c r="L49" t="n">
-        <v>53240.5</v>
+        <v>53438.75</v>
       </c>
       <c r="M49" t="n">
-        <v>53643</v>
+        <v>53667.5</v>
       </c>
       <c r="N49" t="n">
-        <v>54045.5</v>
+        <v>53896.25</v>
       </c>
       <c r="O49" t="n">
-        <v>53998</v>
+        <v>53924</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4653,7 +4657,7 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="7" t="inlineStr">
+      <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4669,7 +4673,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4683,50 +4687,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>53524</v>
+        <v>53643</v>
       </c>
       <c r="C50" t="n">
-        <v>53797</v>
+        <v>53778</v>
       </c>
       <c r="D50" t="n">
-        <v>53426</v>
+        <v>53435</v>
       </c>
       <c r="E50" t="n">
-        <v>53645</v>
+        <v>53521</v>
       </c>
       <c r="F50" t="n">
-        <v>156</v>
+        <v>-124</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0023</v>
       </c>
       <c r="H50" t="n">
-        <v>371</v>
+        <v>343</v>
       </c>
       <c r="I50" t="n">
-        <v>52853</v>
+        <v>53055</v>
       </c>
       <c r="J50" t="n">
-        <v>53182.25</v>
+        <v>53290.75</v>
       </c>
       <c r="K50" t="n">
-        <v>53310.5</v>
+        <v>53459.5</v>
       </c>
       <c r="L50" t="n">
-        <v>53438.75</v>
+        <v>53628.25</v>
       </c>
       <c r="M50" t="n">
-        <v>53667.5</v>
+        <v>53830.5</v>
       </c>
       <c r="N50" t="n">
-        <v>53896.25</v>
+        <v>54032.75</v>
       </c>
       <c r="O50" t="n">
-        <v>53924</v>
+        <v>54168</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4734,18 +4738,18 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4753,64 +4757,64 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>53643</v>
+        <v>53724</v>
       </c>
       <c r="C51" t="n">
-        <v>53778</v>
+        <v>53811</v>
       </c>
       <c r="D51" t="n">
-        <v>53435</v>
+        <v>53369</v>
       </c>
       <c r="E51" t="n">
-        <v>53521</v>
+        <v>53621</v>
       </c>
       <c r="F51" t="n">
-        <v>-124</v>
+        <v>100</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0019</v>
       </c>
       <c r="H51" t="n">
-        <v>343</v>
+        <v>442</v>
       </c>
       <c r="I51" t="n">
-        <v>53055</v>
+        <v>53092</v>
       </c>
       <c r="J51" t="n">
-        <v>53290.75</v>
+        <v>53135.25</v>
       </c>
       <c r="K51" t="n">
-        <v>53459.5</v>
+        <v>53349.5</v>
       </c>
       <c r="L51" t="n">
-        <v>53628.25</v>
+        <v>53563.75</v>
       </c>
       <c r="M51" t="n">
-        <v>53830.5</v>
+        <v>53692.5</v>
       </c>
       <c r="N51" t="n">
-        <v>54032.75</v>
+        <v>53821.25</v>
       </c>
       <c r="O51" t="n">
-        <v>54168</v>
+        <v>54121</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4818,18 +4822,18 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R51" s="6" t="n">
+        <v/>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4837,64 +4841,64 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>53724</v>
+        <v>53608</v>
       </c>
       <c r="C52" t="n">
-        <v>53811</v>
+        <v>53862</v>
       </c>
       <c r="D52" t="n">
-        <v>53369</v>
+        <v>53513</v>
       </c>
       <c r="E52" t="n">
-        <v>53621</v>
+        <v>53584</v>
       </c>
       <c r="F52" t="n">
-        <v>100</v>
+        <v>-37</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0007</v>
       </c>
       <c r="H52" t="n">
-        <v>442</v>
+        <v>349</v>
       </c>
       <c r="I52" t="n">
-        <v>53092</v>
+        <v>52927</v>
       </c>
       <c r="J52" t="n">
-        <v>53135.25</v>
+        <v>53194.5</v>
       </c>
       <c r="K52" t="n">
-        <v>53349.5</v>
+        <v>53400</v>
       </c>
       <c r="L52" t="n">
-        <v>53563.75</v>
+        <v>53605.5</v>
       </c>
       <c r="M52" t="n">
-        <v>53692.5</v>
+        <v>53842</v>
       </c>
       <c r="N52" t="n">
-        <v>53821.25</v>
+        <v>54078.5</v>
       </c>
       <c r="O52" t="n">
-        <v>54121</v>
+        <v>54253</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4907,7 +4911,7 @@
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
@@ -4921,7 +4925,7 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4935,151 +4939,147 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>53608</v>
+        <v>53664</v>
       </c>
       <c r="C53" t="n">
-        <v>53862</v>
+        <v>53664</v>
       </c>
       <c r="D53" t="n">
-        <v>53513</v>
+        <v>53149</v>
       </c>
       <c r="E53" t="n">
-        <v>53584</v>
+        <v>53240</v>
       </c>
       <c r="F53" t="n">
-        <v>-37</v>
+        <v>-344</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0064</v>
       </c>
       <c r="H53" t="n">
-        <v>349</v>
+        <v>515</v>
       </c>
       <c r="I53" t="n">
-        <v>52927</v>
+        <v>53164</v>
       </c>
       <c r="J53" t="n">
-        <v>53194.5</v>
+        <v>53183.25</v>
       </c>
       <c r="K53" t="n">
-        <v>53400</v>
+        <v>53409.5</v>
       </c>
       <c r="L53" t="n">
-        <v>53605.5</v>
+        <v>53635.75</v>
       </c>
       <c r="M53" t="n">
-        <v>53842</v>
+        <v>53758.5</v>
       </c>
       <c r="N53" t="n">
-        <v>54078.5</v>
+        <v>53881.25</v>
       </c>
       <c r="O53" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
+        <v>54211</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
       <c r="U53" s="8" t="n">
         <v/>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>53664</v>
+        <v>53259</v>
       </c>
       <c r="C54" t="n">
-        <v>53664</v>
+        <v>53343</v>
       </c>
       <c r="D54" t="n">
-        <v>53149</v>
+        <v>52747</v>
       </c>
       <c r="E54" t="n">
-        <v>53240</v>
+        <v>52828</v>
       </c>
       <c r="F54" t="n">
-        <v>-344</v>
+        <v>-412</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0064</v>
+        <v>-0.0077</v>
       </c>
       <c r="H54" t="n">
-        <v>515</v>
+        <v>596</v>
       </c>
       <c r="I54" t="n">
-        <v>53164</v>
+        <v>52634</v>
       </c>
       <c r="J54" t="n">
-        <v>53183.25</v>
+        <v>52641.75</v>
       </c>
       <c r="K54" t="n">
-        <v>53409.5</v>
+        <v>52982.5</v>
       </c>
       <c r="L54" t="n">
-        <v>53635.75</v>
+        <v>53323.25</v>
       </c>
       <c r="M54" t="n">
-        <v>53758.5</v>
+        <v>53497.5</v>
       </c>
       <c r="N54" t="n">
-        <v>53881.25</v>
+        <v>53671.75</v>
       </c>
       <c r="O54" t="n">
-        <v>54211</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q54" s="6" t="inlineStr">
+        <v>54179</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
+      <c r="S54" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5093,7 +5093,7 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5103,50 +5103,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>53259</v>
+        <v>52844</v>
       </c>
       <c r="C55" t="n">
-        <v>53343</v>
+        <v>53283</v>
       </c>
       <c r="D55" t="n">
-        <v>52747</v>
+        <v>52720</v>
       </c>
       <c r="E55" t="n">
-        <v>52828</v>
+        <v>53121</v>
       </c>
       <c r="F55" t="n">
-        <v>-412</v>
+        <v>293</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0077</v>
+        <v>0.0055</v>
       </c>
       <c r="H55" t="n">
-        <v>596</v>
+        <v>563</v>
       </c>
       <c r="I55" t="n">
-        <v>52634</v>
+        <v>52151</v>
       </c>
       <c r="J55" t="n">
-        <v>52641.75</v>
+        <v>52123.5</v>
       </c>
       <c r="K55" t="n">
-        <v>52982.5</v>
+        <v>52530</v>
       </c>
       <c r="L55" t="n">
-        <v>53323.25</v>
+        <v>52936.5</v>
       </c>
       <c r="M55" t="n">
-        <v>53497.5</v>
+        <v>53126</v>
       </c>
       <c r="N55" t="n">
-        <v>53671.75</v>
+        <v>53315.5</v>
       </c>
       <c r="O55" t="n">
-        <v>54179</v>
+        <v>53939</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5154,79 +5154,83 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
       <c r="U55" s="8" t="n">
         <v/>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>52844</v>
+        <v>53120</v>
       </c>
       <c r="C56" t="n">
-        <v>53283</v>
+        <v>53827</v>
       </c>
       <c r="D56" t="n">
-        <v>52720</v>
+        <v>53093</v>
       </c>
       <c r="E56" t="n">
-        <v>53121</v>
+        <v>53745</v>
       </c>
       <c r="F56" t="n">
-        <v>293</v>
+        <v>624</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0117</v>
       </c>
       <c r="H56" t="n">
-        <v>563</v>
+        <v>734</v>
       </c>
       <c r="I56" t="n">
-        <v>52151</v>
+        <v>52157</v>
       </c>
       <c r="J56" t="n">
-        <v>52123.5</v>
+        <v>52617.75</v>
       </c>
       <c r="K56" t="n">
-        <v>52530</v>
+        <v>52839.5</v>
       </c>
       <c r="L56" t="n">
-        <v>52936.5</v>
+        <v>53061.25</v>
       </c>
       <c r="M56" t="n">
-        <v>53126</v>
+        <v>53402.5</v>
       </c>
       <c r="N56" t="n">
-        <v>53315.5</v>
+        <v>53743.75</v>
       </c>
       <c r="O56" t="n">
-        <v>53939</v>
+        <v>53846</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5237,80 +5241,78 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="7" t="inlineStr">
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
       <c r="W56" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>53120</v>
+        <v>53707</v>
       </c>
       <c r="C57" t="n">
-        <v>53827</v>
+        <v>53772</v>
       </c>
       <c r="D57" t="n">
-        <v>53093</v>
+        <v>53235</v>
       </c>
       <c r="E57" t="n">
-        <v>53745</v>
+        <v>53440</v>
       </c>
       <c r="F57" t="n">
-        <v>624</v>
+        <v>-305</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0117</v>
+        <v>-0.0057</v>
       </c>
       <c r="H57" t="n">
-        <v>734</v>
+        <v>537</v>
       </c>
       <c r="I57" t="n">
-        <v>52157</v>
+        <v>52359</v>
       </c>
       <c r="J57" t="n">
-        <v>52617.75</v>
+        <v>53153.5</v>
       </c>
       <c r="K57" t="n">
-        <v>52839.5</v>
+        <v>53378</v>
       </c>
       <c r="L57" t="n">
-        <v>53061.25</v>
+        <v>53602.5</v>
       </c>
       <c r="M57" t="n">
-        <v>53402.5</v>
+        <v>54112</v>
       </c>
       <c r="N57" t="n">
-        <v>53743.75</v>
+        <v>54621.5</v>
       </c>
       <c r="O57" t="n">
-        <v>53846</v>
+        <v>54561</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5318,94 +5320,98 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>53707</v>
+        <v>53261</v>
       </c>
       <c r="C58" t="n">
-        <v>53772</v>
+        <v>53336</v>
       </c>
       <c r="D58" t="n">
-        <v>53235</v>
+        <v>52758</v>
       </c>
       <c r="E58" t="n">
-        <v>53440</v>
+        <v>52832</v>
       </c>
       <c r="F58" t="n">
-        <v>-305</v>
+        <v>-608</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0057</v>
+        <v>-0.0114</v>
       </c>
       <c r="H58" t="n">
-        <v>537</v>
+        <v>578</v>
       </c>
       <c r="I58" t="n">
-        <v>52359</v>
+        <v>52698</v>
       </c>
       <c r="J58" t="n">
-        <v>53153.5</v>
+        <v>52871.25</v>
       </c>
       <c r="K58" t="n">
-        <v>53378</v>
+        <v>53171.5</v>
       </c>
       <c r="L58" t="n">
-        <v>53602.5</v>
+        <v>53471.75</v>
       </c>
       <c r="M58" t="n">
-        <v>54112</v>
+        <v>53708.5</v>
       </c>
       <c r="N58" t="n">
-        <v>54621.5</v>
+        <v>53945.25</v>
       </c>
       <c r="O58" t="n">
-        <v>54561</v>
+        <v>54309</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5421,77 +5427,71 @@
       </c>
       <c r="W58" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>53261</v>
+        <v>52817</v>
       </c>
       <c r="C59" t="n">
-        <v>53336</v>
+        <v>52859</v>
       </c>
       <c r="D59" t="n">
-        <v>52758</v>
+        <v>52339</v>
       </c>
       <c r="E59" t="n">
-        <v>52832</v>
+        <v>52425</v>
       </c>
       <c r="F59" t="n">
-        <v>-608</v>
+        <v>-407</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0114</v>
+        <v>-0.0077</v>
       </c>
       <c r="H59" t="n">
-        <v>578</v>
+        <v>520</v>
       </c>
       <c r="I59" t="n">
-        <v>52698</v>
+        <v>52180</v>
       </c>
       <c r="J59" t="n">
-        <v>52871.25</v>
+        <v>52146.5</v>
       </c>
       <c r="K59" t="n">
-        <v>53171.5</v>
+        <v>52543</v>
       </c>
       <c r="L59" t="n">
-        <v>53471.75</v>
+        <v>52939.5</v>
       </c>
       <c r="M59" t="n">
-        <v>53708.5</v>
+        <v>53121</v>
       </c>
       <c r="N59" t="n">
-        <v>53945.25</v>
+        <v>53302.5</v>
       </c>
       <c r="O59" t="n">
-        <v>54309</v>
+        <v>53914</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S59" s="10" t="inlineStr">
+      <c r="S59" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5505,7 +5505,7 @@
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="11" t="inlineStr">
+      <c r="W59" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5515,50 +5515,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>52817</v>
+        <v>52473</v>
       </c>
       <c r="C60" t="n">
-        <v>52859</v>
+        <v>52676</v>
       </c>
       <c r="D60" t="n">
-        <v>52339</v>
+        <v>51992</v>
       </c>
       <c r="E60" t="n">
-        <v>52425</v>
+        <v>52095</v>
       </c>
       <c r="F60" t="n">
-        <v>-407</v>
+        <v>-330</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0077</v>
+        <v>-0.0063</v>
       </c>
       <c r="H60" t="n">
-        <v>520</v>
+        <v>684</v>
       </c>
       <c r="I60" t="n">
-        <v>52180</v>
+        <v>51819</v>
       </c>
       <c r="J60" t="n">
-        <v>52146.5</v>
+        <v>51818</v>
       </c>
       <c r="K60" t="n">
-        <v>52543</v>
+        <v>52165</v>
       </c>
       <c r="L60" t="n">
-        <v>52939.5</v>
+        <v>52512</v>
       </c>
       <c r="M60" t="n">
-        <v>53121</v>
+        <v>52685</v>
       </c>
       <c r="N60" t="n">
-        <v>53302.5</v>
+        <v>52858</v>
       </c>
       <c r="O60" t="n">
-        <v>53914</v>
+        <v>53379</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5571,7 +5571,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S60" s="10" t="inlineStr">
+      <c r="S60" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5585,7 +5585,7 @@
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="11" t="inlineStr">
+      <c r="W60" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5595,50 +5595,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>52473</v>
+        <v>52059</v>
       </c>
       <c r="C61" t="n">
-        <v>52676</v>
+        <v>52739</v>
       </c>
       <c r="D61" t="n">
-        <v>51992</v>
+        <v>52059</v>
       </c>
       <c r="E61" t="n">
-        <v>52095</v>
+        <v>52576</v>
       </c>
       <c r="F61" t="n">
-        <v>-330</v>
+        <v>481</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0063</v>
+        <v>0.0092</v>
       </c>
       <c r="H61" t="n">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="I61" t="n">
-        <v>51819</v>
+        <v>51308</v>
       </c>
       <c r="J61" t="n">
-        <v>51818</v>
+        <v>51291.5</v>
       </c>
       <c r="K61" t="n">
-        <v>52165</v>
+        <v>51753</v>
       </c>
       <c r="L61" t="n">
-        <v>52512</v>
+        <v>52214.5</v>
       </c>
       <c r="M61" t="n">
-        <v>52685</v>
+        <v>52437</v>
       </c>
       <c r="N61" t="n">
-        <v>52858</v>
+        <v>52659.5</v>
       </c>
       <c r="O61" t="n">
-        <v>53379</v>
+        <v>53360</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5646,143 +5646,63 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="11" t="inlineStr">
+      <c r="W61" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>52059</v>
-      </c>
-      <c r="C62" t="n">
-        <v>52739</v>
-      </c>
-      <c r="D62" t="n">
-        <v>52059</v>
-      </c>
-      <c r="E62" t="n">
-        <v>52576</v>
-      </c>
-      <c r="F62" t="n">
-        <v>481</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0.0092</v>
-      </c>
-      <c r="H62" t="n">
-        <v>680</v>
-      </c>
-      <c r="I62" t="n">
-        <v>51308</v>
-      </c>
-      <c r="J62" t="n">
-        <v>51291.5</v>
-      </c>
-      <c r="K62" t="n">
-        <v>51753</v>
-      </c>
-      <c r="L62" t="n">
-        <v>52214.5</v>
-      </c>
-      <c r="M62" t="n">
-        <v>52437</v>
-      </c>
-      <c r="N62" t="n">
-        <v>52659.5</v>
-      </c>
-      <c r="O62" t="n">
-        <v>53360</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I63" s="13" t="n">
+      <c r="I62" s="13" t="n">
         <v>51379</v>
       </c>
-      <c r="J63" s="13" t="n">
+      <c r="J62" s="13" t="n">
         <v>51984.5</v>
       </c>
-      <c r="K63" s="13" t="n">
+      <c r="K62" s="13" t="n">
         <v>52236</v>
       </c>
-      <c r="L63" s="13" t="n">
+      <c r="L62" s="13" t="n">
         <v>52487.5</v>
       </c>
-      <c r="M63" s="13" t="n">
+      <c r="M62" s="13" t="n">
         <v>52916</v>
       </c>
-      <c r="N63" s="13" t="n">
+      <c r="N62" s="13" t="n">
         <v>53344.5</v>
       </c>
-      <c r="O63" s="13" t="n">
+      <c r="O62" s="13" t="n">
         <v>53419</v>
       </c>
     </row>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -109,17 +109,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -641,72 +641,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52041</v>
+        <v>51621</v>
       </c>
       <c r="C2" t="n">
-        <v>52300</v>
+        <v>51962</v>
       </c>
       <c r="D2" t="n">
-        <v>51420</v>
+        <v>51587</v>
       </c>
       <c r="E2" t="n">
-        <v>51519</v>
+        <v>51962</v>
       </c>
       <c r="F2" t="n">
-        <v>-525</v>
+        <v>443</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0101</v>
+        <v>0.0086</v>
       </c>
       <c r="H2" t="n">
-        <v>880</v>
+        <v>375</v>
       </c>
       <c r="I2" t="n">
-        <v>51163</v>
+        <v>50540</v>
       </c>
       <c r="J2" t="n">
-        <v>51548.25</v>
+        <v>50468.5</v>
       </c>
       <c r="K2" t="n">
-        <v>51776.5</v>
+        <v>51079</v>
       </c>
       <c r="L2" t="n">
-        <v>52004.75</v>
+        <v>51689.5</v>
       </c>
       <c r="M2" t="n">
-        <v>52311.5</v>
+        <v>51959</v>
       </c>
       <c r="N2" t="n">
-        <v>52618.25</v>
+        <v>52228.5</v>
       </c>
       <c r="O2" t="n">
-        <v>52768</v>
+        <v>53180</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
@@ -715,7 +713,7 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -727,50 +725,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>51621</v>
+        <v>51870</v>
       </c>
       <c r="C3" t="n">
-        <v>51962</v>
+        <v>52305</v>
       </c>
       <c r="D3" t="n">
-        <v>51587</v>
+        <v>51712</v>
       </c>
       <c r="E3" t="n">
-        <v>51962</v>
+        <v>52119</v>
       </c>
       <c r="F3" t="n">
-        <v>443</v>
+        <v>157</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0086</v>
+        <v>0.003</v>
       </c>
       <c r="H3" t="n">
-        <v>375</v>
+        <v>593</v>
       </c>
       <c r="I3" t="n">
-        <v>50540</v>
+        <v>51212</v>
       </c>
       <c r="J3" t="n">
-        <v>50468.5</v>
+        <v>51680.75</v>
       </c>
       <c r="K3" t="n">
-        <v>51079</v>
+        <v>51774.5</v>
       </c>
       <c r="L3" t="n">
-        <v>51689.5</v>
+        <v>51868.25</v>
       </c>
       <c r="M3" t="n">
-        <v>51959</v>
+        <v>52149.5</v>
       </c>
       <c r="N3" t="n">
-        <v>52228.5</v>
+        <v>52430.75</v>
       </c>
       <c r="O3" t="n">
-        <v>53180</v>
+        <v>52337</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -778,10 +776,12 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -799,62 +799,58 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>51870</v>
+        <v>52165</v>
       </c>
       <c r="C4" t="n">
-        <v>52305</v>
+        <v>52281</v>
       </c>
       <c r="D4" t="n">
-        <v>51712</v>
+        <v>51691</v>
       </c>
       <c r="E4" t="n">
-        <v>52119</v>
+        <v>52082</v>
       </c>
       <c r="F4" t="n">
-        <v>157</v>
+        <v>-37</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0007</v>
       </c>
       <c r="H4" t="n">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="I4" t="n">
-        <v>51212</v>
+        <v>51119</v>
       </c>
       <c r="J4" t="n">
-        <v>51680.75</v>
+        <v>51581.25</v>
       </c>
       <c r="K4" t="n">
-        <v>51774.5</v>
+        <v>51822.5</v>
       </c>
       <c r="L4" t="n">
-        <v>51868.25</v>
+        <v>52063.75</v>
       </c>
       <c r="M4" t="n">
-        <v>52149.5</v>
+        <v>52415.5</v>
       </c>
       <c r="N4" t="n">
-        <v>52430.75</v>
+        <v>52767.25</v>
       </c>
       <c r="O4" t="n">
-        <v>52337</v>
+        <v>52898</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -867,15 +863,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -885,7 +879,7 @@
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -897,50 +891,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52165</v>
+        <v>52119</v>
       </c>
       <c r="C5" t="n">
-        <v>52281</v>
+        <v>52676</v>
       </c>
       <c r="D5" t="n">
-        <v>51691</v>
+        <v>51933</v>
       </c>
       <c r="E5" t="n">
-        <v>52082</v>
+        <v>52279</v>
       </c>
       <c r="F5" t="n">
-        <v>-37</v>
+        <v>197</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0007</v>
+        <v>0.0038</v>
       </c>
       <c r="H5" t="n">
-        <v>590</v>
+        <v>743</v>
       </c>
       <c r="I5" t="n">
-        <v>51119</v>
+        <v>51101</v>
       </c>
       <c r="J5" t="n">
-        <v>51581.25</v>
+        <v>51540</v>
       </c>
       <c r="K5" t="n">
-        <v>51822.5</v>
+        <v>51787</v>
       </c>
       <c r="L5" t="n">
-        <v>52063.75</v>
+        <v>52034</v>
       </c>
       <c r="M5" t="n">
-        <v>52415.5</v>
+        <v>52377</v>
       </c>
       <c r="N5" t="n">
-        <v>52767.25</v>
+        <v>52720</v>
       </c>
       <c r="O5" t="n">
-        <v>52898</v>
+        <v>52871</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -948,18 +942,18 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -969,7 +963,7 @@
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -977,50 +971,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52119</v>
+        <v>52381</v>
       </c>
       <c r="C6" t="n">
-        <v>52676</v>
+        <v>53097</v>
       </c>
       <c r="D6" t="n">
-        <v>51933</v>
+        <v>52215</v>
       </c>
       <c r="E6" t="n">
-        <v>52279</v>
+        <v>52339</v>
       </c>
       <c r="F6" t="n">
-        <v>197</v>
+        <v>60</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.0011</v>
       </c>
       <c r="H6" t="n">
-        <v>743</v>
+        <v>882</v>
       </c>
       <c r="I6" t="n">
-        <v>51101</v>
+        <v>51190</v>
       </c>
       <c r="J6" t="n">
-        <v>51540</v>
+        <v>51523.25</v>
       </c>
       <c r="K6" t="n">
-        <v>51787</v>
+        <v>51907.5</v>
       </c>
       <c r="L6" t="n">
-        <v>52034</v>
+        <v>52291.75</v>
       </c>
       <c r="M6" t="n">
-        <v>52377</v>
+        <v>52650.5</v>
       </c>
       <c r="N6" t="n">
-        <v>52720</v>
+        <v>53009.25</v>
       </c>
       <c r="O6" t="n">
-        <v>52871</v>
+        <v>53419</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1031,80 +1025,78 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>52381</v>
+        <v>52439</v>
       </c>
       <c r="C7" t="n">
-        <v>53097</v>
+        <v>52542</v>
       </c>
       <c r="D7" t="n">
-        <v>52215</v>
+        <v>52008</v>
       </c>
       <c r="E7" t="n">
-        <v>52339</v>
+        <v>52209</v>
       </c>
       <c r="F7" t="n">
-        <v>60</v>
+        <v>-130</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0011</v>
+        <v>-0.0025</v>
       </c>
       <c r="H7" t="n">
-        <v>882</v>
+        <v>534</v>
       </c>
       <c r="I7" t="n">
-        <v>51190</v>
+        <v>51333</v>
       </c>
       <c r="J7" t="n">
-        <v>51523.25</v>
+        <v>51298.5</v>
       </c>
       <c r="K7" t="n">
-        <v>51907.5</v>
+        <v>51898</v>
       </c>
       <c r="L7" t="n">
-        <v>52291.75</v>
+        <v>52497.5</v>
       </c>
       <c r="M7" t="n">
-        <v>52650.5</v>
+        <v>52780</v>
       </c>
       <c r="N7" t="n">
-        <v>53009.25</v>
+        <v>53062.5</v>
       </c>
       <c r="O7" t="n">
-        <v>53419</v>
+        <v>53979</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1117,25 +1109,21 @@
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1147,50 +1135,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52439</v>
+        <v>52183</v>
       </c>
       <c r="C8" t="n">
-        <v>52542</v>
+        <v>52700</v>
       </c>
       <c r="D8" t="n">
-        <v>52008</v>
+        <v>52179</v>
       </c>
       <c r="E8" t="n">
-        <v>52209</v>
+        <v>52572</v>
       </c>
       <c r="F8" t="n">
-        <v>-130</v>
+        <v>363</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.007</v>
       </c>
       <c r="H8" t="n">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="I8" t="n">
-        <v>51333</v>
+        <v>51474</v>
       </c>
       <c r="J8" t="n">
-        <v>51298.5</v>
+        <v>51642</v>
       </c>
       <c r="K8" t="n">
-        <v>51898</v>
+        <v>51942</v>
       </c>
       <c r="L8" t="n">
-        <v>52497.5</v>
+        <v>52242</v>
       </c>
       <c r="M8" t="n">
-        <v>52780</v>
+        <v>52476</v>
       </c>
       <c r="N8" t="n">
-        <v>53062.5</v>
+        <v>52710</v>
       </c>
       <c r="O8" t="n">
-        <v>53979</v>
+        <v>53076</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1203,11 +1191,13 @@
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1217,7 +1207,7 @@
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
@@ -1225,50 +1215,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52183</v>
+        <v>52554</v>
       </c>
       <c r="C9" t="n">
-        <v>52700</v>
+        <v>52763</v>
       </c>
       <c r="D9" t="n">
-        <v>52179</v>
+        <v>52383</v>
       </c>
       <c r="E9" t="n">
-        <v>52572</v>
+        <v>52670</v>
       </c>
       <c r="F9" t="n">
-        <v>363</v>
+        <v>98</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.007</v>
+        <v>0.0019</v>
       </c>
       <c r="H9" t="n">
-        <v>521</v>
+        <v>380</v>
       </c>
       <c r="I9" t="n">
-        <v>51474</v>
+        <v>51658</v>
       </c>
       <c r="J9" t="n">
-        <v>51642</v>
+        <v>52117.25</v>
       </c>
       <c r="K9" t="n">
-        <v>51942</v>
+        <v>52311.5</v>
       </c>
       <c r="L9" t="n">
-        <v>52242</v>
+        <v>52505.75</v>
       </c>
       <c r="M9" t="n">
-        <v>52476</v>
+        <v>52832.5</v>
       </c>
       <c r="N9" t="n">
-        <v>52710</v>
+        <v>53159.25</v>
       </c>
       <c r="O9" t="n">
-        <v>53076</v>
+        <v>53221</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1279,7 +1269,7 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1297,62 +1287,58 @@
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52554</v>
+        <v>52546</v>
       </c>
       <c r="C10" t="n">
-        <v>52763</v>
+        <v>53105</v>
       </c>
       <c r="D10" t="n">
-        <v>52383</v>
+        <v>52381</v>
       </c>
       <c r="E10" t="n">
-        <v>52670</v>
+        <v>52668</v>
       </c>
       <c r="F10" t="n">
-        <v>98</v>
+        <v>-2</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>380</v>
+        <v>724</v>
       </c>
       <c r="I10" t="n">
-        <v>51658</v>
+        <v>52003</v>
       </c>
       <c r="J10" t="n">
-        <v>52117.25</v>
+        <v>52338.5</v>
       </c>
       <c r="K10" t="n">
-        <v>52311.5</v>
+        <v>52480</v>
       </c>
       <c r="L10" t="n">
-        <v>52505.75</v>
+        <v>52621.5</v>
       </c>
       <c r="M10" t="n">
-        <v>52832.5</v>
+        <v>52860</v>
       </c>
       <c r="N10" t="n">
-        <v>53159.25</v>
+        <v>53098.5</v>
       </c>
       <c r="O10" t="n">
-        <v>53221</v>
+        <v>53143</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1360,83 +1346,87 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>52546</v>
+        <v>52640</v>
       </c>
       <c r="C11" t="n">
-        <v>53105</v>
+        <v>53218</v>
       </c>
       <c r="D11" t="n">
-        <v>52381</v>
+        <v>52551</v>
       </c>
       <c r="E11" t="n">
-        <v>52668</v>
+        <v>53183</v>
       </c>
       <c r="F11" t="n">
-        <v>-2</v>
+        <v>515</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0</v>
+        <v>0.0098</v>
       </c>
       <c r="H11" t="n">
-        <v>724</v>
+        <v>667</v>
       </c>
       <c r="I11" t="n">
-        <v>52003</v>
+        <v>51657</v>
       </c>
       <c r="J11" t="n">
-        <v>52338.5</v>
+        <v>51906.5</v>
       </c>
       <c r="K11" t="n">
-        <v>52480</v>
+        <v>52306</v>
       </c>
       <c r="L11" t="n">
-        <v>52621.5</v>
+        <v>52705.5</v>
       </c>
       <c r="M11" t="n">
-        <v>52860</v>
+        <v>53030</v>
       </c>
       <c r="N11" t="n">
-        <v>53098.5</v>
+        <v>53354.5</v>
       </c>
       <c r="O11" t="n">
-        <v>53143</v>
+        <v>53829</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1444,87 +1434,79 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52640</v>
+        <v>53230</v>
       </c>
       <c r="C12" t="n">
-        <v>53218</v>
+        <v>53421</v>
       </c>
       <c r="D12" t="n">
-        <v>52551</v>
+        <v>52962</v>
       </c>
       <c r="E12" t="n">
-        <v>53183</v>
+        <v>53372</v>
       </c>
       <c r="F12" t="n">
-        <v>515</v>
+        <v>189</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0036</v>
       </c>
       <c r="H12" t="n">
-        <v>667</v>
+        <v>459</v>
       </c>
       <c r="I12" t="n">
-        <v>51657</v>
+        <v>51884</v>
       </c>
       <c r="J12" t="n">
-        <v>51906.5</v>
+        <v>52665.25</v>
       </c>
       <c r="K12" t="n">
-        <v>52306</v>
+        <v>52849.5</v>
       </c>
       <c r="L12" t="n">
-        <v>52705.5</v>
+        <v>53033.75</v>
       </c>
       <c r="M12" t="n">
-        <v>53030</v>
+        <v>53516.5</v>
       </c>
       <c r="N12" t="n">
-        <v>53354.5</v>
+        <v>53999.25</v>
       </c>
       <c r="O12" t="n">
-        <v>53829</v>
+        <v>53885</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1535,7 +1517,7 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1553,62 +1535,58 @@
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>53230</v>
+        <v>53405</v>
       </c>
       <c r="C13" t="n">
-        <v>53421</v>
+        <v>53656</v>
       </c>
       <c r="D13" t="n">
-        <v>52962</v>
+        <v>53076</v>
       </c>
       <c r="E13" t="n">
-        <v>53372</v>
+        <v>53197</v>
       </c>
       <c r="F13" t="n">
-        <v>189</v>
+        <v>-175</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0036</v>
+        <v>-0.0033</v>
       </c>
       <c r="H13" t="n">
-        <v>459</v>
+        <v>580</v>
       </c>
       <c r="I13" t="n">
-        <v>51884</v>
+        <v>52503</v>
       </c>
       <c r="J13" t="n">
-        <v>52665.25</v>
+        <v>53003.25</v>
       </c>
       <c r="K13" t="n">
-        <v>52849.5</v>
+        <v>53142.5</v>
       </c>
       <c r="L13" t="n">
-        <v>53033.75</v>
+        <v>53281.75</v>
       </c>
       <c r="M13" t="n">
-        <v>53516.5</v>
+        <v>53601.5</v>
       </c>
       <c r="N13" t="n">
-        <v>53999.25</v>
+        <v>53921.25</v>
       </c>
       <c r="O13" t="n">
-        <v>53885</v>
+        <v>53880</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1616,17 +1594,19 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U13" s="8" t="n">
@@ -1637,83 +1617,85 @@
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>53405</v>
+        <v>53166</v>
       </c>
       <c r="C14" t="n">
-        <v>53656</v>
+        <v>53207</v>
       </c>
       <c r="D14" t="n">
-        <v>53076</v>
+        <v>52343</v>
       </c>
       <c r="E14" t="n">
-        <v>53197</v>
+        <v>52624</v>
       </c>
       <c r="F14" t="n">
-        <v>-175</v>
+        <v>-573</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0108</v>
       </c>
       <c r="H14" t="n">
-        <v>580</v>
+        <v>864</v>
       </c>
       <c r="I14" t="n">
-        <v>52503</v>
+        <v>52496</v>
       </c>
       <c r="J14" t="n">
-        <v>53003.25</v>
+        <v>52532.5</v>
       </c>
       <c r="K14" t="n">
-        <v>53142.5</v>
+        <v>52907</v>
       </c>
       <c r="L14" t="n">
-        <v>53281.75</v>
+        <v>53281.5</v>
       </c>
       <c r="M14" t="n">
-        <v>53601.5</v>
+        <v>53487</v>
       </c>
       <c r="N14" t="n">
-        <v>53921.25</v>
+        <v>53692.5</v>
       </c>
       <c r="O14" t="n">
-        <v>53880</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
+        <v>54236</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1723,81 +1705,75 @@
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>53166</v>
+        <v>52541</v>
       </c>
       <c r="C15" t="n">
-        <v>53207</v>
+        <v>52865</v>
       </c>
       <c r="D15" t="n">
-        <v>52343</v>
+        <v>52501</v>
       </c>
       <c r="E15" t="n">
-        <v>52624</v>
+        <v>52761</v>
       </c>
       <c r="F15" t="n">
-        <v>-573</v>
+        <v>137</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0108</v>
+        <v>0.0026</v>
       </c>
       <c r="H15" t="n">
-        <v>864</v>
+        <v>364</v>
       </c>
       <c r="I15" t="n">
-        <v>52496</v>
+        <v>51479</v>
       </c>
       <c r="J15" t="n">
-        <v>52532.5</v>
+        <v>51684.5</v>
       </c>
       <c r="K15" t="n">
-        <v>52907</v>
+        <v>52192</v>
       </c>
       <c r="L15" t="n">
-        <v>53281.5</v>
+        <v>52699.5</v>
       </c>
       <c r="M15" t="n">
-        <v>53487</v>
+        <v>53056</v>
       </c>
       <c r="N15" t="n">
-        <v>53692.5</v>
+        <v>53412.5</v>
       </c>
       <c r="O15" t="n">
-        <v>54236</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>54071</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1811,58 +1787,62 @@
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>52541</v>
+        <v>52753</v>
       </c>
       <c r="C16" t="n">
-        <v>52865</v>
+        <v>52992</v>
       </c>
       <c r="D16" t="n">
-        <v>52501</v>
+        <v>52506</v>
       </c>
       <c r="E16" t="n">
-        <v>52761</v>
+        <v>52906</v>
       </c>
       <c r="F16" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0027</v>
       </c>
       <c r="H16" t="n">
-        <v>364</v>
+        <v>486</v>
       </c>
       <c r="I16" t="n">
-        <v>51479</v>
+        <v>52137</v>
       </c>
       <c r="J16" t="n">
-        <v>51684.5</v>
+        <v>52436</v>
       </c>
       <c r="K16" t="n">
-        <v>52192</v>
+        <v>52579</v>
       </c>
       <c r="L16" t="n">
-        <v>52699.5</v>
+        <v>52722</v>
       </c>
       <c r="M16" t="n">
-        <v>53056</v>
+        <v>52943</v>
       </c>
       <c r="N16" t="n">
-        <v>53412.5</v>
+        <v>53164</v>
       </c>
       <c r="O16" t="n">
-        <v>54071</v>
+        <v>53229</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1870,16 +1850,20 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1889,62 +1873,58 @@
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52753</v>
+        <v>52844</v>
       </c>
       <c r="C17" t="n">
-        <v>52992</v>
+        <v>53113</v>
       </c>
       <c r="D17" t="n">
-        <v>52506</v>
+        <v>52603</v>
       </c>
       <c r="E17" t="n">
-        <v>52906</v>
+        <v>52764</v>
       </c>
       <c r="F17" t="n">
-        <v>145</v>
+        <v>-142</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0027</v>
       </c>
       <c r="H17" t="n">
-        <v>486</v>
+        <v>510</v>
       </c>
       <c r="I17" t="n">
-        <v>52137</v>
+        <v>52020</v>
       </c>
       <c r="J17" t="n">
-        <v>52436</v>
+        <v>52498.5</v>
       </c>
       <c r="K17" t="n">
-        <v>52579</v>
+        <v>52663</v>
       </c>
       <c r="L17" t="n">
-        <v>52722</v>
+        <v>52827.5</v>
       </c>
       <c r="M17" t="n">
-        <v>52943</v>
+        <v>53149</v>
       </c>
       <c r="N17" t="n">
-        <v>53164</v>
+        <v>53470.5</v>
       </c>
       <c r="O17" t="n">
-        <v>53229</v>
+        <v>53478</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1959,13 +1939,11 @@
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1975,62 +1953,62 @@
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52844</v>
+        <v>52731</v>
       </c>
       <c r="C18" t="n">
-        <v>53113</v>
+        <v>52981</v>
       </c>
       <c r="D18" t="n">
-        <v>52603</v>
+        <v>52255</v>
       </c>
       <c r="E18" t="n">
-        <v>52764</v>
+        <v>52791</v>
       </c>
       <c r="F18" t="n">
-        <v>-142</v>
+        <v>27</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0005</v>
       </c>
       <c r="H18" t="n">
-        <v>510</v>
+        <v>726</v>
       </c>
       <c r="I18" t="n">
-        <v>52020</v>
+        <v>52093</v>
       </c>
       <c r="J18" t="n">
-        <v>52498.5</v>
+        <v>52207</v>
       </c>
       <c r="K18" t="n">
-        <v>52663</v>
+        <v>52509</v>
       </c>
       <c r="L18" t="n">
-        <v>52827.5</v>
+        <v>52811</v>
       </c>
       <c r="M18" t="n">
-        <v>53149</v>
+        <v>53019</v>
       </c>
       <c r="N18" t="n">
-        <v>53470.5</v>
+        <v>53227</v>
       </c>
       <c r="O18" t="n">
-        <v>53478</v>
+        <v>53623</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2043,7 +2021,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S18" s="7" t="inlineStr">
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2059,7 +2037,7 @@
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -2071,50 +2049,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>52731</v>
+        <v>52792</v>
       </c>
       <c r="C19" t="n">
-        <v>52981</v>
+        <v>53088</v>
       </c>
       <c r="D19" t="n">
-        <v>52255</v>
+        <v>52680</v>
       </c>
       <c r="E19" t="n">
-        <v>52791</v>
+        <v>52900</v>
       </c>
       <c r="F19" t="n">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0021</v>
       </c>
       <c r="H19" t="n">
-        <v>726</v>
+        <v>408</v>
       </c>
       <c r="I19" t="n">
-        <v>52093</v>
+        <v>51529</v>
       </c>
       <c r="J19" t="n">
-        <v>52207</v>
+        <v>52151.5</v>
       </c>
       <c r="K19" t="n">
-        <v>52509</v>
+        <v>52428</v>
       </c>
       <c r="L19" t="n">
-        <v>52811</v>
+        <v>52704.5</v>
       </c>
       <c r="M19" t="n">
-        <v>53019</v>
+        <v>53154</v>
       </c>
       <c r="N19" t="n">
-        <v>53227</v>
+        <v>53603.5</v>
       </c>
       <c r="O19" t="n">
-        <v>53623</v>
+        <v>53707</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2122,14 +2100,12 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R19" s="6" t="n">
+        <v/>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2143,62 +2119,58 @@
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>52792</v>
+        <v>52919</v>
       </c>
       <c r="C20" t="n">
-        <v>53088</v>
+        <v>53108</v>
       </c>
       <c r="D20" t="n">
-        <v>52680</v>
+        <v>52607</v>
       </c>
       <c r="E20" t="n">
-        <v>52900</v>
+        <v>52786</v>
       </c>
       <c r="F20" t="n">
-        <v>109</v>
+        <v>-114</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0022</v>
       </c>
       <c r="H20" t="n">
-        <v>408</v>
+        <v>501</v>
       </c>
       <c r="I20" t="n">
-        <v>51529</v>
+        <v>52272</v>
       </c>
       <c r="J20" t="n">
-        <v>52151.5</v>
+        <v>52500</v>
       </c>
       <c r="K20" t="n">
-        <v>52428</v>
+        <v>52696</v>
       </c>
       <c r="L20" t="n">
-        <v>52704.5</v>
+        <v>52892</v>
       </c>
       <c r="M20" t="n">
-        <v>53154</v>
+        <v>53104</v>
       </c>
       <c r="N20" t="n">
-        <v>53603.5</v>
+        <v>53316</v>
       </c>
       <c r="O20" t="n">
-        <v>53707</v>
+        <v>53496</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2206,16 +2178,20 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2225,83 +2201,83 @@
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>52919</v>
+        <v>52778</v>
       </c>
       <c r="C21" t="n">
-        <v>53108</v>
+        <v>52835</v>
       </c>
       <c r="D21" t="n">
-        <v>52607</v>
+        <v>52174</v>
       </c>
       <c r="E21" t="n">
-        <v>52786</v>
+        <v>52375</v>
       </c>
       <c r="F21" t="n">
-        <v>-114</v>
+        <v>-411</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0078</v>
       </c>
       <c r="H21" t="n">
-        <v>501</v>
+        <v>661</v>
       </c>
       <c r="I21" t="n">
-        <v>52272</v>
+        <v>52106</v>
       </c>
       <c r="J21" t="n">
-        <v>52500</v>
+        <v>52249.25</v>
       </c>
       <c r="K21" t="n">
-        <v>52696</v>
+        <v>52535.5</v>
       </c>
       <c r="L21" t="n">
-        <v>52892</v>
+        <v>52821.75</v>
       </c>
       <c r="M21" t="n">
-        <v>53104</v>
+        <v>53036.5</v>
       </c>
       <c r="N21" t="n">
-        <v>53316</v>
+        <v>53251.25</v>
       </c>
       <c r="O21" t="n">
-        <v>53496</v>
+        <v>53609</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T21" s="8" t="n">
+        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2311,77 +2287,75 @@
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>52778</v>
+        <v>52300</v>
       </c>
       <c r="C22" t="n">
-        <v>52835</v>
+        <v>52633</v>
       </c>
       <c r="D22" t="n">
-        <v>52174</v>
+        <v>51999</v>
       </c>
       <c r="E22" t="n">
-        <v>52375</v>
+        <v>52073</v>
       </c>
       <c r="F22" t="n">
-        <v>-411</v>
+        <v>-302</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0078</v>
+        <v>-0.0058</v>
       </c>
       <c r="H22" t="n">
-        <v>661</v>
+        <v>634</v>
       </c>
       <c r="I22" t="n">
-        <v>52106</v>
+        <v>51513</v>
       </c>
       <c r="J22" t="n">
-        <v>52249.25</v>
+        <v>51649.25</v>
       </c>
       <c r="K22" t="n">
-        <v>52535.5</v>
+        <v>52044.5</v>
       </c>
       <c r="L22" t="n">
-        <v>52821.75</v>
+        <v>52439.75</v>
       </c>
       <c r="M22" t="n">
-        <v>53036.5</v>
+        <v>52705.5</v>
       </c>
       <c r="N22" t="n">
-        <v>53251.25</v>
+        <v>52971.25</v>
       </c>
       <c r="O22" t="n">
-        <v>53609</v>
+        <v>53496</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2397,58 +2371,62 @@
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>52300</v>
+        <v>52091</v>
       </c>
       <c r="C23" t="n">
-        <v>52633</v>
+        <v>52590</v>
       </c>
       <c r="D23" t="n">
-        <v>51999</v>
+        <v>52035</v>
       </c>
       <c r="E23" t="n">
-        <v>52073</v>
+        <v>52443</v>
       </c>
       <c r="F23" t="n">
-        <v>-302</v>
+        <v>370</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.0071</v>
       </c>
       <c r="H23" t="n">
-        <v>634</v>
+        <v>555</v>
       </c>
       <c r="I23" t="n">
-        <v>51513</v>
+        <v>51365</v>
       </c>
       <c r="J23" t="n">
-        <v>51649.25</v>
+        <v>51317.5</v>
       </c>
       <c r="K23" t="n">
-        <v>52044.5</v>
+        <v>51756</v>
       </c>
       <c r="L23" t="n">
-        <v>52439.75</v>
+        <v>52194.5</v>
       </c>
       <c r="M23" t="n">
-        <v>52705.5</v>
+        <v>52390</v>
       </c>
       <c r="N23" t="n">
-        <v>52971.25</v>
+        <v>52585.5</v>
       </c>
       <c r="O23" t="n">
-        <v>53496</v>
+        <v>53267</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2456,79 +2434,85 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>52091</v>
+        <v>52431</v>
       </c>
       <c r="C24" t="n">
-        <v>52590</v>
+        <v>52721</v>
       </c>
       <c r="D24" t="n">
-        <v>52035</v>
+        <v>52262</v>
       </c>
       <c r="E24" t="n">
-        <v>52443</v>
+        <v>52449</v>
       </c>
       <c r="F24" t="n">
-        <v>370</v>
+        <v>6</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0001</v>
       </c>
       <c r="H24" t="n">
-        <v>555</v>
+        <v>459</v>
       </c>
       <c r="I24" t="n">
-        <v>51365</v>
+        <v>51480</v>
       </c>
       <c r="J24" t="n">
-        <v>51317.5</v>
+        <v>51953.25</v>
       </c>
       <c r="K24" t="n">
-        <v>51756</v>
+        <v>52165.5</v>
       </c>
       <c r="L24" t="n">
-        <v>52194.5</v>
+        <v>52377.75</v>
       </c>
       <c r="M24" t="n">
-        <v>52390</v>
+        <v>52720.5</v>
       </c>
       <c r="N24" t="n">
-        <v>52585.5</v>
+        <v>53063.25</v>
       </c>
       <c r="O24" t="n">
-        <v>53267</v>
+        <v>53145</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2539,101 +2523,99 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>52431</v>
+        <v>52430</v>
       </c>
       <c r="C25" t="n">
-        <v>52721</v>
+        <v>52515</v>
       </c>
       <c r="D25" t="n">
-        <v>52262</v>
+        <v>51720</v>
       </c>
       <c r="E25" t="n">
-        <v>52449</v>
+        <v>51894</v>
       </c>
       <c r="F25" t="n">
-        <v>6</v>
+        <v>-555</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0106</v>
       </c>
       <c r="H25" t="n">
-        <v>459</v>
+        <v>795</v>
       </c>
       <c r="I25" t="n">
-        <v>51480</v>
+        <v>51803</v>
       </c>
       <c r="J25" t="n">
-        <v>51953.25</v>
+        <v>51968.75</v>
       </c>
       <c r="K25" t="n">
-        <v>52165.5</v>
+        <v>52219.5</v>
       </c>
       <c r="L25" t="n">
-        <v>52377.75</v>
+        <v>52470.25</v>
       </c>
       <c r="M25" t="n">
-        <v>52720.5</v>
+        <v>52678.5</v>
       </c>
       <c r="N25" t="n">
-        <v>53063.25</v>
+        <v>52886.75</v>
       </c>
       <c r="O25" t="n">
-        <v>53145</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+        <v>53180</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2641,148 +2623,144 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>52430</v>
+        <v>51920</v>
       </c>
       <c r="C26" t="n">
-        <v>52515</v>
+        <v>52314</v>
       </c>
       <c r="D26" t="n">
-        <v>51720</v>
+        <v>51846</v>
       </c>
       <c r="E26" t="n">
-        <v>51894</v>
+        <v>52124</v>
       </c>
       <c r="F26" t="n">
-        <v>-555</v>
+        <v>230</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0044</v>
       </c>
       <c r="H26" t="n">
-        <v>795</v>
+        <v>468</v>
       </c>
       <c r="I26" t="n">
-        <v>51803</v>
+        <v>50925</v>
       </c>
       <c r="J26" t="n">
-        <v>51968.75</v>
+        <v>50987.25</v>
       </c>
       <c r="K26" t="n">
-        <v>52219.5</v>
+        <v>51496.5</v>
       </c>
       <c r="L26" t="n">
-        <v>52470.25</v>
+        <v>52005.75</v>
       </c>
       <c r="M26" t="n">
-        <v>52678.5</v>
+        <v>52291.5</v>
       </c>
       <c r="N26" t="n">
-        <v>52886.75</v>
+        <v>52577.25</v>
       </c>
       <c r="O26" t="n">
-        <v>53180</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
+        <v>53310</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
       <c r="U26" s="8" t="n">
         <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>51920</v>
+        <v>52299</v>
       </c>
       <c r="C27" t="n">
-        <v>52314</v>
+        <v>52790</v>
       </c>
       <c r="D27" t="n">
-        <v>51846</v>
+        <v>52173</v>
       </c>
       <c r="E27" t="n">
-        <v>52124</v>
+        <v>52382</v>
       </c>
       <c r="F27" t="n">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0049</v>
       </c>
       <c r="H27" t="n">
-        <v>468</v>
+        <v>617</v>
       </c>
       <c r="I27" t="n">
-        <v>50925</v>
+        <v>51378</v>
       </c>
       <c r="J27" t="n">
-        <v>50987.25</v>
+        <v>51678</v>
       </c>
       <c r="K27" t="n">
-        <v>51496.5</v>
+        <v>51890</v>
       </c>
       <c r="L27" t="n">
-        <v>52005.75</v>
+        <v>52102</v>
       </c>
       <c r="M27" t="n">
-        <v>52291.5</v>
+        <v>52358</v>
       </c>
       <c r="N27" t="n">
-        <v>52577.25</v>
+        <v>52614</v>
       </c>
       <c r="O27" t="n">
-        <v>53310</v>
+        <v>52782</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2793,80 +2771,84 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>52299</v>
+        <v>52405</v>
       </c>
       <c r="C28" t="n">
-        <v>52790</v>
+        <v>53105</v>
       </c>
       <c r="D28" t="n">
-        <v>52173</v>
+        <v>52290</v>
       </c>
       <c r="E28" t="n">
-        <v>52382</v>
+        <v>52944</v>
       </c>
       <c r="F28" t="n">
-        <v>258</v>
+        <v>562</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0107</v>
       </c>
       <c r="H28" t="n">
-        <v>617</v>
+        <v>815</v>
       </c>
       <c r="I28" t="n">
-        <v>51378</v>
+        <v>51556</v>
       </c>
       <c r="J28" t="n">
-        <v>51678</v>
+        <v>51715.25</v>
       </c>
       <c r="K28" t="n">
-        <v>51890</v>
+        <v>52073.5</v>
       </c>
       <c r="L28" t="n">
-        <v>52102</v>
+        <v>52431.75</v>
       </c>
       <c r="M28" t="n">
-        <v>52358</v>
+        <v>52690.5</v>
       </c>
       <c r="N28" t="n">
-        <v>52614</v>
+        <v>52949.25</v>
       </c>
       <c r="O28" t="n">
-        <v>52782</v>
+        <v>53407</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2877,27 +2859,25 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
+      <c r="S28" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="V28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2911,220 +2891,218 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>52405</v>
+        <v>52915</v>
       </c>
       <c r="C29" t="n">
-        <v>53105</v>
+        <v>53033</v>
       </c>
       <c r="D29" t="n">
-        <v>52290</v>
+        <v>51630</v>
       </c>
       <c r="E29" t="n">
-        <v>52944</v>
+        <v>51765</v>
       </c>
       <c r="F29" t="n">
-        <v>562</v>
+        <v>-1179</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0223</v>
       </c>
       <c r="H29" t="n">
-        <v>815</v>
+        <v>1403</v>
       </c>
       <c r="I29" t="n">
-        <v>51556</v>
+        <v>51475</v>
       </c>
       <c r="J29" t="n">
-        <v>51715.25</v>
+        <v>52252.25</v>
       </c>
       <c r="K29" t="n">
-        <v>52073.5</v>
+        <v>52536.5</v>
       </c>
       <c r="L29" t="n">
-        <v>52431.75</v>
+        <v>52820.75</v>
       </c>
       <c r="M29" t="n">
-        <v>52690.5</v>
+        <v>53351.5</v>
       </c>
       <c r="N29" t="n">
-        <v>52949.25</v>
+        <v>53882.25</v>
       </c>
       <c r="O29" t="n">
-        <v>53407</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+        <v>53920</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>52915</v>
+        <v>51759</v>
       </c>
       <c r="C30" t="n">
-        <v>53033</v>
+        <v>52484</v>
       </c>
       <c r="D30" t="n">
-        <v>51630</v>
+        <v>51732</v>
       </c>
       <c r="E30" t="n">
-        <v>51765</v>
+        <v>52380</v>
       </c>
       <c r="F30" t="n">
-        <v>-1179</v>
+        <v>615</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0119</v>
       </c>
       <c r="H30" t="n">
-        <v>1403</v>
+        <v>752</v>
       </c>
       <c r="I30" t="n">
-        <v>51475</v>
+        <v>50227</v>
       </c>
       <c r="J30" t="n">
-        <v>52252.25</v>
+        <v>50078.75</v>
       </c>
       <c r="K30" t="n">
-        <v>52536.5</v>
+        <v>51063.5</v>
       </c>
       <c r="L30" t="n">
-        <v>52820.75</v>
+        <v>52048.25</v>
       </c>
       <c r="M30" t="n">
-        <v>53351.5</v>
+        <v>52466.5</v>
       </c>
       <c r="N30" t="n">
-        <v>53882.25</v>
+        <v>52884.75</v>
       </c>
       <c r="O30" t="n">
-        <v>53920</v>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
+        <v>54436</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>51759</v>
+        <v>52395</v>
       </c>
       <c r="C31" t="n">
-        <v>52484</v>
+        <v>52772</v>
       </c>
       <c r="D31" t="n">
-        <v>51732</v>
+        <v>52124</v>
       </c>
       <c r="E31" t="n">
-        <v>52380</v>
+        <v>52635</v>
       </c>
       <c r="F31" t="n">
-        <v>615</v>
+        <v>255</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0119</v>
+        <v>0.0049</v>
       </c>
       <c r="H31" t="n">
-        <v>752</v>
+        <v>648</v>
       </c>
       <c r="I31" t="n">
-        <v>50227</v>
+        <v>50980</v>
       </c>
       <c r="J31" t="n">
-        <v>50078.75</v>
+        <v>51764</v>
       </c>
       <c r="K31" t="n">
-        <v>51063.5</v>
+        <v>52004</v>
       </c>
       <c r="L31" t="n">
-        <v>52048.25</v>
+        <v>52244</v>
       </c>
       <c r="M31" t="n">
-        <v>52466.5</v>
+        <v>52756</v>
       </c>
       <c r="N31" t="n">
-        <v>52884.75</v>
+        <v>53268</v>
       </c>
       <c r="O31" t="n">
-        <v>54436</v>
+        <v>53236</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3135,7 +3113,7 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3151,64 +3129,64 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>52395</v>
+        <v>52780</v>
       </c>
       <c r="C32" t="n">
-        <v>52772</v>
+        <v>53414</v>
       </c>
       <c r="D32" t="n">
-        <v>52124</v>
+        <v>52777</v>
       </c>
       <c r="E32" t="n">
-        <v>52635</v>
+        <v>53334</v>
       </c>
       <c r="F32" t="n">
-        <v>255</v>
+        <v>699</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0133</v>
       </c>
       <c r="H32" t="n">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="I32" t="n">
-        <v>50980</v>
+        <v>51476</v>
       </c>
       <c r="J32" t="n">
-        <v>51764</v>
+        <v>52080.5</v>
       </c>
       <c r="K32" t="n">
-        <v>52004</v>
+        <v>52311</v>
       </c>
       <c r="L32" t="n">
-        <v>52244</v>
+        <v>52541.5</v>
       </c>
       <c r="M32" t="n">
-        <v>52756</v>
+        <v>52959</v>
       </c>
       <c r="N32" t="n">
-        <v>53268</v>
+        <v>53376.5</v>
       </c>
       <c r="O32" t="n">
-        <v>53236</v>
+        <v>53420</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3219,23 +3197,25 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3249,50 +3229,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>52780</v>
+        <v>53381</v>
       </c>
       <c r="C33" t="n">
-        <v>53414</v>
+        <v>54423</v>
       </c>
       <c r="D33" t="n">
-        <v>52777</v>
+        <v>53267</v>
       </c>
       <c r="E33" t="n">
-        <v>53334</v>
+        <v>54268</v>
       </c>
       <c r="F33" t="n">
-        <v>699</v>
+        <v>934</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0175</v>
       </c>
       <c r="H33" t="n">
-        <v>637</v>
+        <v>1156</v>
       </c>
       <c r="I33" t="n">
-        <v>51476</v>
+        <v>52140</v>
       </c>
       <c r="J33" t="n">
-        <v>52080.5</v>
+        <v>52816.25</v>
       </c>
       <c r="K33" t="n">
-        <v>52311</v>
+        <v>53015.5</v>
       </c>
       <c r="L33" t="n">
-        <v>52541.5</v>
+        <v>53214.75</v>
       </c>
       <c r="M33" t="n">
-        <v>52959</v>
+        <v>53652.5</v>
       </c>
       <c r="N33" t="n">
-        <v>53376.5</v>
+        <v>54090.25</v>
       </c>
       <c r="O33" t="n">
-        <v>53420</v>
+        <v>54051</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3303,7 +3283,7 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3318,67 +3298,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V33" s="8" t="n">
-        <v/>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>53381</v>
+        <v>54369</v>
       </c>
       <c r="C34" t="n">
-        <v>54423</v>
+        <v>54884</v>
       </c>
       <c r="D34" t="n">
-        <v>53267</v>
+        <v>54342</v>
       </c>
       <c r="E34" t="n">
-        <v>54268</v>
+        <v>54494</v>
       </c>
       <c r="F34" t="n">
-        <v>934</v>
+        <v>226</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0042</v>
       </c>
       <c r="H34" t="n">
-        <v>1156</v>
+        <v>542</v>
       </c>
       <c r="I34" t="n">
-        <v>52140</v>
+        <v>52111</v>
       </c>
       <c r="J34" t="n">
-        <v>52816.25</v>
+        <v>53323.5</v>
       </c>
       <c r="K34" t="n">
-        <v>53015.5</v>
+        <v>53690</v>
       </c>
       <c r="L34" t="n">
-        <v>53214.75</v>
+        <v>54056.5</v>
       </c>
       <c r="M34" t="n">
-        <v>53652.5</v>
+        <v>54846</v>
       </c>
       <c r="N34" t="n">
-        <v>54090.25</v>
+        <v>55635.5</v>
       </c>
       <c r="O34" t="n">
-        <v>54051</v>
+        <v>55579</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3389,27 +3367,23 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3419,69 +3393,71 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>54369</v>
+        <v>54555</v>
       </c>
       <c r="C35" t="n">
-        <v>54884</v>
+        <v>54678</v>
       </c>
       <c r="D35" t="n">
-        <v>54342</v>
+        <v>53952</v>
       </c>
       <c r="E35" t="n">
-        <v>54494</v>
+        <v>54013</v>
       </c>
       <c r="F35" t="n">
-        <v>226</v>
+        <v>-481</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>542</v>
+        <v>726</v>
       </c>
       <c r="I35" t="n">
-        <v>52111</v>
+        <v>53800</v>
       </c>
       <c r="J35" t="n">
-        <v>53323.5</v>
+        <v>53892.5</v>
       </c>
       <c r="K35" t="n">
-        <v>53690</v>
+        <v>54223</v>
       </c>
       <c r="L35" t="n">
-        <v>54056.5</v>
+        <v>54553.5</v>
       </c>
       <c r="M35" t="n">
-        <v>54846</v>
+        <v>54765</v>
       </c>
       <c r="N35" t="n">
-        <v>55635.5</v>
+        <v>54976.5</v>
       </c>
       <c r="O35" t="n">
-        <v>55579</v>
+        <v>55426</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3489,77 +3465,77 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>54555</v>
+        <v>54040</v>
       </c>
       <c r="C36" t="n">
-        <v>54678</v>
+        <v>54202</v>
       </c>
       <c r="D36" t="n">
-        <v>53952</v>
+        <v>53879</v>
       </c>
       <c r="E36" t="n">
-        <v>54013</v>
+        <v>54152</v>
       </c>
       <c r="F36" t="n">
-        <v>-481</v>
+        <v>139</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0026</v>
       </c>
       <c r="H36" t="n">
-        <v>726</v>
+        <v>323</v>
       </c>
       <c r="I36" t="n">
-        <v>53800</v>
+        <v>53226</v>
       </c>
       <c r="J36" t="n">
-        <v>53892.5</v>
+        <v>53136</v>
       </c>
       <c r="K36" t="n">
-        <v>54223</v>
+        <v>53650</v>
       </c>
       <c r="L36" t="n">
-        <v>54553.5</v>
+        <v>54164</v>
       </c>
       <c r="M36" t="n">
-        <v>54765</v>
+        <v>54376</v>
       </c>
       <c r="N36" t="n">
-        <v>54976.5</v>
+        <v>54588</v>
       </c>
       <c r="O36" t="n">
-        <v>55426</v>
+        <v>55404</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3571,64 +3547,64 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>54040</v>
+        <v>54133</v>
       </c>
       <c r="C37" t="n">
-        <v>54202</v>
+        <v>54170</v>
       </c>
       <c r="D37" t="n">
-        <v>53879</v>
+        <v>53952</v>
       </c>
       <c r="E37" t="n">
-        <v>54152</v>
+        <v>54063</v>
       </c>
       <c r="F37" t="n">
-        <v>139</v>
+        <v>-89</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0016</v>
       </c>
       <c r="H37" t="n">
-        <v>323</v>
+        <v>218</v>
       </c>
       <c r="I37" t="n">
-        <v>53226</v>
+        <v>53556</v>
       </c>
       <c r="J37" t="n">
-        <v>53136</v>
+        <v>53884.75</v>
       </c>
       <c r="K37" t="n">
-        <v>53650</v>
+        <v>53990.5</v>
       </c>
       <c r="L37" t="n">
-        <v>54164</v>
+        <v>54096.25</v>
       </c>
       <c r="M37" t="n">
-        <v>54376</v>
+        <v>54313.5</v>
       </c>
       <c r="N37" t="n">
-        <v>54588</v>
+        <v>54530.75</v>
       </c>
       <c r="O37" t="n">
-        <v>55404</v>
+        <v>54525</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3636,10 +3612,12 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3653,7 +3631,7 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3667,77 +3645,83 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>54133</v>
+        <v>54049</v>
       </c>
       <c r="C38" t="n">
-        <v>54170</v>
+        <v>54336</v>
       </c>
       <c r="D38" t="n">
-        <v>53952</v>
+        <v>53855</v>
       </c>
       <c r="E38" t="n">
-        <v>54063</v>
+        <v>53880</v>
       </c>
       <c r="F38" t="n">
-        <v>-89</v>
+        <v>-183</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0034</v>
       </c>
       <c r="H38" t="n">
-        <v>218</v>
+        <v>481</v>
       </c>
       <c r="I38" t="n">
-        <v>53556</v>
+        <v>53734</v>
       </c>
       <c r="J38" t="n">
-        <v>53884.75</v>
+        <v>53846</v>
       </c>
       <c r="K38" t="n">
-        <v>53990.5</v>
+        <v>53954</v>
       </c>
       <c r="L38" t="n">
-        <v>54096.25</v>
+        <v>54062</v>
       </c>
       <c r="M38" t="n">
-        <v>54313.5</v>
+        <v>54172</v>
       </c>
       <c r="N38" t="n">
-        <v>54530.75</v>
+        <v>54282</v>
       </c>
       <c r="O38" t="n">
-        <v>54525</v>
+        <v>54388</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3751,140 +3735,134 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>54049</v>
+        <v>53903</v>
       </c>
       <c r="C39" t="n">
-        <v>54336</v>
+        <v>54150</v>
       </c>
       <c r="D39" t="n">
-        <v>53855</v>
+        <v>53830</v>
       </c>
       <c r="E39" t="n">
-        <v>53880</v>
+        <v>53871</v>
       </c>
       <c r="F39" t="n">
-        <v>-183</v>
+        <v>-9</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0002</v>
       </c>
       <c r="H39" t="n">
-        <v>481</v>
+        <v>320</v>
       </c>
       <c r="I39" t="n">
-        <v>53734</v>
+        <v>53374</v>
       </c>
       <c r="J39" t="n">
-        <v>53846</v>
+        <v>53291.25</v>
       </c>
       <c r="K39" t="n">
-        <v>53954</v>
+        <v>53639.5</v>
       </c>
       <c r="L39" t="n">
-        <v>54062</v>
+        <v>53987.75</v>
       </c>
       <c r="M39" t="n">
-        <v>54172</v>
+        <v>54120.5</v>
       </c>
       <c r="N39" t="n">
-        <v>54282</v>
+        <v>54253.25</v>
       </c>
       <c r="O39" t="n">
-        <v>54388</v>
+        <v>54817</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>53903</v>
+        <v>53905</v>
       </c>
       <c r="C40" t="n">
-        <v>54150</v>
+        <v>54149</v>
       </c>
       <c r="D40" t="n">
-        <v>53830</v>
+        <v>53715</v>
       </c>
       <c r="E40" t="n">
-        <v>53871</v>
+        <v>53935</v>
       </c>
       <c r="F40" t="n">
-        <v>-9</v>
+        <v>64</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0012</v>
       </c>
       <c r="H40" t="n">
-        <v>320</v>
+        <v>434</v>
       </c>
       <c r="I40" t="n">
-        <v>53374</v>
+        <v>53510</v>
       </c>
       <c r="J40" t="n">
-        <v>53291.25</v>
+        <v>53491.5</v>
       </c>
       <c r="K40" t="n">
-        <v>53639.5</v>
+        <v>53711</v>
       </c>
       <c r="L40" t="n">
-        <v>53987.75</v>
+        <v>53930.5</v>
       </c>
       <c r="M40" t="n">
-        <v>54120.5</v>
+        <v>54031</v>
       </c>
       <c r="N40" t="n">
-        <v>54253.25</v>
+        <v>54131.5</v>
       </c>
       <c r="O40" t="n">
-        <v>54817</v>
+        <v>54470</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3897,7 +3875,7 @@
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
@@ -3905,70 +3883,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U40" s="8" t="n">
-        <v/>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>53905</v>
+        <v>53961</v>
       </c>
       <c r="C41" t="n">
-        <v>54149</v>
+        <v>53999</v>
       </c>
       <c r="D41" t="n">
-        <v>53715</v>
+        <v>53745</v>
       </c>
       <c r="E41" t="n">
-        <v>53935</v>
+        <v>53807</v>
       </c>
       <c r="F41" t="n">
-        <v>64</v>
+        <v>-128</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0024</v>
       </c>
       <c r="H41" t="n">
-        <v>434</v>
+        <v>254</v>
       </c>
       <c r="I41" t="n">
-        <v>53510</v>
+        <v>53281</v>
       </c>
       <c r="J41" t="n">
-        <v>53491.5</v>
+        <v>53502.5</v>
       </c>
       <c r="K41" t="n">
-        <v>53711</v>
+        <v>53718</v>
       </c>
       <c r="L41" t="n">
-        <v>53930.5</v>
+        <v>53933.5</v>
       </c>
       <c r="M41" t="n">
-        <v>54031</v>
+        <v>54152</v>
       </c>
       <c r="N41" t="n">
-        <v>54131.5</v>
+        <v>54370.5</v>
       </c>
       <c r="O41" t="n">
-        <v>54470</v>
+        <v>54583</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3976,28 +3956,26 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4011,63 +3989,67 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>53961</v>
+        <v>53790</v>
       </c>
       <c r="C42" t="n">
-        <v>53999</v>
+        <v>53840</v>
       </c>
       <c r="D42" t="n">
-        <v>53745</v>
+        <v>53464</v>
       </c>
       <c r="E42" t="n">
-        <v>53807</v>
+        <v>53544</v>
       </c>
       <c r="F42" t="n">
-        <v>-128</v>
+        <v>-263</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0049</v>
       </c>
       <c r="H42" t="n">
-        <v>254</v>
+        <v>376</v>
       </c>
       <c r="I42" t="n">
-        <v>53281</v>
+        <v>53491</v>
       </c>
       <c r="J42" t="n">
-        <v>53502.5</v>
+        <v>53520.5</v>
       </c>
       <c r="K42" t="n">
-        <v>53718</v>
+        <v>53680</v>
       </c>
       <c r="L42" t="n">
-        <v>53933.5</v>
+        <v>53839.5</v>
       </c>
       <c r="M42" t="n">
-        <v>54152</v>
+        <v>53934</v>
       </c>
       <c r="N42" t="n">
-        <v>54370.5</v>
+        <v>54028.5</v>
       </c>
       <c r="O42" t="n">
-        <v>54583</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
+        <v>54253</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4081,81 +4063,77 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>53790</v>
+        <v>53501</v>
       </c>
       <c r="C43" t="n">
-        <v>53840</v>
+        <v>53594</v>
       </c>
       <c r="D43" t="n">
-        <v>53464</v>
+        <v>53311</v>
       </c>
       <c r="E43" t="n">
-        <v>53544</v>
+        <v>53403</v>
       </c>
       <c r="F43" t="n">
-        <v>-263</v>
+        <v>-141</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0026</v>
       </c>
       <c r="H43" t="n">
-        <v>376</v>
+        <v>283</v>
       </c>
       <c r="I43" t="n">
-        <v>53491</v>
+        <v>53088</v>
       </c>
       <c r="J43" t="n">
-        <v>53520.5</v>
+        <v>53114</v>
       </c>
       <c r="K43" t="n">
-        <v>53680</v>
+        <v>53356</v>
       </c>
       <c r="L43" t="n">
-        <v>53839.5</v>
+        <v>53598</v>
       </c>
       <c r="M43" t="n">
-        <v>53934</v>
+        <v>53732</v>
       </c>
       <c r="N43" t="n">
-        <v>54028.5</v>
+        <v>53866</v>
       </c>
       <c r="O43" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
+        <v>54216</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4169,7 +4147,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4183,50 +4161,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>53501</v>
+        <v>53408</v>
       </c>
       <c r="C44" t="n">
-        <v>53594</v>
+        <v>53780</v>
       </c>
       <c r="D44" t="n">
-        <v>53311</v>
+        <v>53337</v>
       </c>
       <c r="E44" t="n">
-        <v>53403</v>
+        <v>53530</v>
       </c>
       <c r="F44" t="n">
-        <v>-141</v>
+        <v>127</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0026</v>
+        <v>0.0024</v>
       </c>
       <c r="H44" t="n">
-        <v>283</v>
+        <v>443</v>
       </c>
       <c r="I44" t="n">
-        <v>53088</v>
+        <v>53028</v>
       </c>
       <c r="J44" t="n">
-        <v>53114</v>
+        <v>53095.25</v>
       </c>
       <c r="K44" t="n">
-        <v>53356</v>
+        <v>53261.5</v>
       </c>
       <c r="L44" t="n">
-        <v>53598</v>
+        <v>53427.75</v>
       </c>
       <c r="M44" t="n">
-        <v>53732</v>
+        <v>53544.5</v>
       </c>
       <c r="N44" t="n">
-        <v>53866</v>
+        <v>53661.25</v>
       </c>
       <c r="O44" t="n">
-        <v>54216</v>
+        <v>53877</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4234,114 +4212,114 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>53408</v>
+        <v>53529</v>
       </c>
       <c r="C45" t="n">
-        <v>53780</v>
+        <v>53589</v>
       </c>
       <c r="D45" t="n">
-        <v>53337</v>
+        <v>52812</v>
       </c>
       <c r="E45" t="n">
-        <v>53530</v>
+        <v>52849</v>
       </c>
       <c r="F45" t="n">
-        <v>127</v>
+        <v>-681</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0127</v>
       </c>
       <c r="H45" t="n">
-        <v>443</v>
+        <v>777</v>
       </c>
       <c r="I45" t="n">
-        <v>53028</v>
+        <v>52894</v>
       </c>
       <c r="J45" t="n">
-        <v>53095.25</v>
+        <v>53072.75</v>
       </c>
       <c r="K45" t="n">
-        <v>53261.5</v>
+        <v>53308.5</v>
       </c>
       <c r="L45" t="n">
-        <v>53427.75</v>
+        <v>53544.25</v>
       </c>
       <c r="M45" t="n">
-        <v>53544.5</v>
+        <v>53751.5</v>
       </c>
       <c r="N45" t="n">
-        <v>53661.25</v>
+        <v>53958.75</v>
       </c>
       <c r="O45" t="n">
-        <v>53877</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+        <v>54223</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
       <c r="W45" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X45" t="inlineStr"/>
@@ -4349,134 +4327,136 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>53529</v>
+        <v>52876</v>
       </c>
       <c r="C46" t="n">
-        <v>53589</v>
+        <v>53418</v>
       </c>
       <c r="D46" t="n">
-        <v>52812</v>
+        <v>52838</v>
       </c>
       <c r="E46" t="n">
-        <v>52849</v>
+        <v>53353</v>
       </c>
       <c r="F46" t="n">
-        <v>-681</v>
+        <v>504</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0095</v>
       </c>
       <c r="H46" t="n">
-        <v>777</v>
+        <v>580</v>
       </c>
       <c r="I46" t="n">
-        <v>52894</v>
+        <v>52035</v>
       </c>
       <c r="J46" t="n">
-        <v>53072.75</v>
+        <v>51896.25</v>
       </c>
       <c r="K46" t="n">
-        <v>53308.5</v>
+        <v>52460.5</v>
       </c>
       <c r="L46" t="n">
-        <v>53544.25</v>
+        <v>53024.75</v>
       </c>
       <c r="M46" t="n">
-        <v>53751.5</v>
+        <v>53237.5</v>
       </c>
       <c r="N46" t="n">
-        <v>53958.75</v>
+        <v>53450.25</v>
       </c>
       <c r="O46" t="n">
-        <v>54223</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
+        <v>54366</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>52876</v>
+        <v>53367</v>
       </c>
       <c r="C47" t="n">
-        <v>53418</v>
+        <v>53567</v>
       </c>
       <c r="D47" t="n">
-        <v>52838</v>
+        <v>53210</v>
       </c>
       <c r="E47" t="n">
-        <v>53353</v>
+        <v>53489</v>
       </c>
       <c r="F47" t="n">
-        <v>504</v>
+        <v>136</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.0025</v>
       </c>
       <c r="H47" t="n">
-        <v>580</v>
+        <v>357</v>
       </c>
       <c r="I47" t="n">
-        <v>52035</v>
+        <v>52258</v>
       </c>
       <c r="J47" t="n">
-        <v>51896.25</v>
+        <v>52885.5</v>
       </c>
       <c r="K47" t="n">
-        <v>52460.5</v>
+        <v>53063</v>
       </c>
       <c r="L47" t="n">
-        <v>53024.75</v>
+        <v>53240.5</v>
       </c>
       <c r="M47" t="n">
-        <v>53237.5</v>
+        <v>53643</v>
       </c>
       <c r="N47" t="n">
-        <v>53450.25</v>
+        <v>54045.5</v>
       </c>
       <c r="O47" t="n">
-        <v>54366</v>
+        <v>53998</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4487,82 +4467,80 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="S47" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>53367</v>
+        <v>53524</v>
       </c>
       <c r="C48" t="n">
-        <v>53567</v>
+        <v>53797</v>
       </c>
       <c r="D48" t="n">
-        <v>53210</v>
+        <v>53426</v>
       </c>
       <c r="E48" t="n">
-        <v>53489</v>
+        <v>53645</v>
       </c>
       <c r="F48" t="n">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0029</v>
       </c>
       <c r="H48" t="n">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="I48" t="n">
-        <v>52258</v>
+        <v>52853</v>
       </c>
       <c r="J48" t="n">
-        <v>52885.5</v>
+        <v>53182.25</v>
       </c>
       <c r="K48" t="n">
-        <v>53063</v>
+        <v>53310.5</v>
       </c>
       <c r="L48" t="n">
-        <v>53240.5</v>
+        <v>53438.75</v>
       </c>
       <c r="M48" t="n">
-        <v>53643</v>
+        <v>53667.5</v>
       </c>
       <c r="N48" t="n">
-        <v>54045.5</v>
+        <v>53896.25</v>
       </c>
       <c r="O48" t="n">
-        <v>53998</v>
+        <v>53924</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4573,7 +4551,7 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="10" t="inlineStr">
+      <c r="S48" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4589,7 +4567,7 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4603,50 +4581,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>53524</v>
+        <v>53643</v>
       </c>
       <c r="C49" t="n">
-        <v>53797</v>
+        <v>53778</v>
       </c>
       <c r="D49" t="n">
-        <v>53426</v>
+        <v>53435</v>
       </c>
       <c r="E49" t="n">
-        <v>53645</v>
+        <v>53521</v>
       </c>
       <c r="F49" t="n">
-        <v>156</v>
+        <v>-124</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0023</v>
       </c>
       <c r="H49" t="n">
-        <v>371</v>
+        <v>343</v>
       </c>
       <c r="I49" t="n">
-        <v>52853</v>
+        <v>53055</v>
       </c>
       <c r="J49" t="n">
-        <v>53182.25</v>
+        <v>53290.75</v>
       </c>
       <c r="K49" t="n">
-        <v>53310.5</v>
+        <v>53459.5</v>
       </c>
       <c r="L49" t="n">
-        <v>53438.75</v>
+        <v>53628.25</v>
       </c>
       <c r="M49" t="n">
-        <v>53667.5</v>
+        <v>53830.5</v>
       </c>
       <c r="N49" t="n">
-        <v>53896.25</v>
+        <v>54032.75</v>
       </c>
       <c r="O49" t="n">
-        <v>53924</v>
+        <v>54168</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4654,18 +4632,18 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4673,64 +4651,64 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>53643</v>
+        <v>53724</v>
       </c>
       <c r="C50" t="n">
-        <v>53778</v>
+        <v>53811</v>
       </c>
       <c r="D50" t="n">
-        <v>53435</v>
+        <v>53369</v>
       </c>
       <c r="E50" t="n">
-        <v>53521</v>
+        <v>53621</v>
       </c>
       <c r="F50" t="n">
-        <v>-124</v>
+        <v>100</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0019</v>
       </c>
       <c r="H50" t="n">
-        <v>343</v>
+        <v>442</v>
       </c>
       <c r="I50" t="n">
-        <v>53055</v>
+        <v>53092</v>
       </c>
       <c r="J50" t="n">
-        <v>53290.75</v>
+        <v>53135.25</v>
       </c>
       <c r="K50" t="n">
-        <v>53459.5</v>
+        <v>53349.5</v>
       </c>
       <c r="L50" t="n">
-        <v>53628.25</v>
+        <v>53563.75</v>
       </c>
       <c r="M50" t="n">
-        <v>53830.5</v>
+        <v>53692.5</v>
       </c>
       <c r="N50" t="n">
-        <v>54032.75</v>
+        <v>53821.25</v>
       </c>
       <c r="O50" t="n">
-        <v>54168</v>
+        <v>54121</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4738,18 +4716,18 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R50" s="6" t="n">
+        <v/>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4757,64 +4735,64 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>53724</v>
+        <v>53608</v>
       </c>
       <c r="C51" t="n">
-        <v>53811</v>
+        <v>53862</v>
       </c>
       <c r="D51" t="n">
-        <v>53369</v>
+        <v>53513</v>
       </c>
       <c r="E51" t="n">
-        <v>53621</v>
+        <v>53584</v>
       </c>
       <c r="F51" t="n">
-        <v>100</v>
+        <v>-37</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0007</v>
       </c>
       <c r="H51" t="n">
-        <v>442</v>
+        <v>349</v>
       </c>
       <c r="I51" t="n">
-        <v>53092</v>
+        <v>52927</v>
       </c>
       <c r="J51" t="n">
-        <v>53135.25</v>
+        <v>53194.5</v>
       </c>
       <c r="K51" t="n">
-        <v>53349.5</v>
+        <v>53400</v>
       </c>
       <c r="L51" t="n">
-        <v>53563.75</v>
+        <v>53605.5</v>
       </c>
       <c r="M51" t="n">
-        <v>53692.5</v>
+        <v>53842</v>
       </c>
       <c r="N51" t="n">
-        <v>53821.25</v>
+        <v>54078.5</v>
       </c>
       <c r="O51" t="n">
-        <v>54121</v>
+        <v>54253</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4827,7 +4805,7 @@
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
@@ -4841,7 +4819,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4855,151 +4833,147 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>53608</v>
+        <v>53664</v>
       </c>
       <c r="C52" t="n">
-        <v>53862</v>
+        <v>53664</v>
       </c>
       <c r="D52" t="n">
-        <v>53513</v>
+        <v>53149</v>
       </c>
       <c r="E52" t="n">
-        <v>53584</v>
+        <v>53240</v>
       </c>
       <c r="F52" t="n">
-        <v>-37</v>
+        <v>-344</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0064</v>
       </c>
       <c r="H52" t="n">
-        <v>349</v>
+        <v>515</v>
       </c>
       <c r="I52" t="n">
-        <v>52927</v>
+        <v>53164</v>
       </c>
       <c r="J52" t="n">
-        <v>53194.5</v>
+        <v>53183.25</v>
       </c>
       <c r="K52" t="n">
-        <v>53400</v>
+        <v>53409.5</v>
       </c>
       <c r="L52" t="n">
-        <v>53605.5</v>
+        <v>53635.75</v>
       </c>
       <c r="M52" t="n">
-        <v>53842</v>
+        <v>53758.5</v>
       </c>
       <c r="N52" t="n">
-        <v>54078.5</v>
+        <v>53881.25</v>
       </c>
       <c r="O52" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
+        <v>54211</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
       <c r="U52" s="8" t="n">
         <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>53664</v>
+        <v>53259</v>
       </c>
       <c r="C53" t="n">
-        <v>53664</v>
+        <v>53343</v>
       </c>
       <c r="D53" t="n">
-        <v>53149</v>
+        <v>52747</v>
       </c>
       <c r="E53" t="n">
-        <v>53240</v>
+        <v>52828</v>
       </c>
       <c r="F53" t="n">
-        <v>-344</v>
+        <v>-412</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0064</v>
+        <v>-0.0077</v>
       </c>
       <c r="H53" t="n">
-        <v>515</v>
+        <v>596</v>
       </c>
       <c r="I53" t="n">
-        <v>53164</v>
+        <v>52634</v>
       </c>
       <c r="J53" t="n">
-        <v>53183.25</v>
+        <v>52641.75</v>
       </c>
       <c r="K53" t="n">
-        <v>53409.5</v>
+        <v>52982.5</v>
       </c>
       <c r="L53" t="n">
-        <v>53635.75</v>
+        <v>53323.25</v>
       </c>
       <c r="M53" t="n">
-        <v>53758.5</v>
+        <v>53497.5</v>
       </c>
       <c r="N53" t="n">
-        <v>53881.25</v>
+        <v>53671.75</v>
       </c>
       <c r="O53" t="n">
-        <v>54211</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q53" s="6" t="inlineStr">
+        <v>54179</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
+      <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5013,7 +4987,7 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5023,50 +4997,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>53259</v>
+        <v>52844</v>
       </c>
       <c r="C54" t="n">
-        <v>53343</v>
+        <v>53283</v>
       </c>
       <c r="D54" t="n">
-        <v>52747</v>
+        <v>52720</v>
       </c>
       <c r="E54" t="n">
-        <v>52828</v>
+        <v>53121</v>
       </c>
       <c r="F54" t="n">
-        <v>-412</v>
+        <v>293</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0077</v>
+        <v>0.0055</v>
       </c>
       <c r="H54" t="n">
-        <v>596</v>
+        <v>563</v>
       </c>
       <c r="I54" t="n">
-        <v>52634</v>
+        <v>52151</v>
       </c>
       <c r="J54" t="n">
-        <v>52641.75</v>
+        <v>52123.5</v>
       </c>
       <c r="K54" t="n">
-        <v>52982.5</v>
+        <v>52530</v>
       </c>
       <c r="L54" t="n">
-        <v>53323.25</v>
+        <v>52936.5</v>
       </c>
       <c r="M54" t="n">
-        <v>53497.5</v>
+        <v>53126</v>
       </c>
       <c r="N54" t="n">
-        <v>53671.75</v>
+        <v>53315.5</v>
       </c>
       <c r="O54" t="n">
-        <v>54179</v>
+        <v>53939</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5074,79 +5048,83 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
       <c r="U54" s="8" t="n">
         <v/>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>52844</v>
+        <v>53120</v>
       </c>
       <c r="C55" t="n">
-        <v>53283</v>
+        <v>53827</v>
       </c>
       <c r="D55" t="n">
-        <v>52720</v>
+        <v>53093</v>
       </c>
       <c r="E55" t="n">
-        <v>53121</v>
+        <v>53745</v>
       </c>
       <c r="F55" t="n">
-        <v>293</v>
+        <v>624</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0117</v>
       </c>
       <c r="H55" t="n">
-        <v>563</v>
+        <v>734</v>
       </c>
       <c r="I55" t="n">
-        <v>52151</v>
+        <v>52157</v>
       </c>
       <c r="J55" t="n">
-        <v>52123.5</v>
+        <v>52617.75</v>
       </c>
       <c r="K55" t="n">
-        <v>52530</v>
+        <v>52839.5</v>
       </c>
       <c r="L55" t="n">
-        <v>52936.5</v>
+        <v>53061.25</v>
       </c>
       <c r="M55" t="n">
-        <v>53126</v>
+        <v>53402.5</v>
       </c>
       <c r="N55" t="n">
-        <v>53315.5</v>
+        <v>53743.75</v>
       </c>
       <c r="O55" t="n">
-        <v>53939</v>
+        <v>53846</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5157,80 +5135,78 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="10" t="inlineStr">
+      <c r="S55" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
       <c r="W55" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>53120</v>
+        <v>53707</v>
       </c>
       <c r="C56" t="n">
-        <v>53827</v>
+        <v>53772</v>
       </c>
       <c r="D56" t="n">
-        <v>53093</v>
+        <v>53235</v>
       </c>
       <c r="E56" t="n">
-        <v>53745</v>
+        <v>53440</v>
       </c>
       <c r="F56" t="n">
-        <v>624</v>
+        <v>-305</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0117</v>
+        <v>-0.0057</v>
       </c>
       <c r="H56" t="n">
-        <v>734</v>
+        <v>537</v>
       </c>
       <c r="I56" t="n">
-        <v>52157</v>
+        <v>52359</v>
       </c>
       <c r="J56" t="n">
-        <v>52617.75</v>
+        <v>53153.5</v>
       </c>
       <c r="K56" t="n">
-        <v>52839.5</v>
+        <v>53378</v>
       </c>
       <c r="L56" t="n">
-        <v>53061.25</v>
+        <v>53602.5</v>
       </c>
       <c r="M56" t="n">
-        <v>53402.5</v>
+        <v>54112</v>
       </c>
       <c r="N56" t="n">
-        <v>53743.75</v>
+        <v>54621.5</v>
       </c>
       <c r="O56" t="n">
-        <v>53846</v>
+        <v>54561</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5238,94 +5214,98 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>53707</v>
+        <v>53261</v>
       </c>
       <c r="C57" t="n">
-        <v>53772</v>
+        <v>53336</v>
       </c>
       <c r="D57" t="n">
-        <v>53235</v>
+        <v>52758</v>
       </c>
       <c r="E57" t="n">
-        <v>53440</v>
+        <v>52832</v>
       </c>
       <c r="F57" t="n">
-        <v>-305</v>
+        <v>-608</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0057</v>
+        <v>-0.0114</v>
       </c>
       <c r="H57" t="n">
-        <v>537</v>
+        <v>578</v>
       </c>
       <c r="I57" t="n">
-        <v>52359</v>
+        <v>52698</v>
       </c>
       <c r="J57" t="n">
-        <v>53153.5</v>
+        <v>52871.25</v>
       </c>
       <c r="K57" t="n">
-        <v>53378</v>
+        <v>53171.5</v>
       </c>
       <c r="L57" t="n">
-        <v>53602.5</v>
+        <v>53471.75</v>
       </c>
       <c r="M57" t="n">
-        <v>54112</v>
+        <v>53708.5</v>
       </c>
       <c r="N57" t="n">
-        <v>54621.5</v>
+        <v>53945.25</v>
       </c>
       <c r="O57" t="n">
-        <v>54561</v>
+        <v>54309</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5341,77 +5321,71 @@
       </c>
       <c r="W57" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>53261</v>
+        <v>52817</v>
       </c>
       <c r="C58" t="n">
-        <v>53336</v>
+        <v>52859</v>
       </c>
       <c r="D58" t="n">
-        <v>52758</v>
+        <v>52339</v>
       </c>
       <c r="E58" t="n">
-        <v>52832</v>
+        <v>52425</v>
       </c>
       <c r="F58" t="n">
-        <v>-608</v>
+        <v>-407</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0114</v>
+        <v>-0.0077</v>
       </c>
       <c r="H58" t="n">
-        <v>578</v>
+        <v>520</v>
       </c>
       <c r="I58" t="n">
-        <v>52698</v>
+        <v>52180</v>
       </c>
       <c r="J58" t="n">
-        <v>52871.25</v>
+        <v>52146.5</v>
       </c>
       <c r="K58" t="n">
-        <v>53171.5</v>
+        <v>52543</v>
       </c>
       <c r="L58" t="n">
-        <v>53471.75</v>
+        <v>52939.5</v>
       </c>
       <c r="M58" t="n">
-        <v>53708.5</v>
+        <v>53121</v>
       </c>
       <c r="N58" t="n">
-        <v>53945.25</v>
+        <v>53302.5</v>
       </c>
       <c r="O58" t="n">
-        <v>54309</v>
+        <v>53914</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
+      <c r="S58" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5425,7 +5399,7 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5435,50 +5409,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>52817</v>
+        <v>52473</v>
       </c>
       <c r="C59" t="n">
-        <v>52859</v>
+        <v>52676</v>
       </c>
       <c r="D59" t="n">
-        <v>52339</v>
+        <v>51992</v>
       </c>
       <c r="E59" t="n">
-        <v>52425</v>
+        <v>52095</v>
       </c>
       <c r="F59" t="n">
-        <v>-407</v>
+        <v>-330</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0077</v>
+        <v>-0.0063</v>
       </c>
       <c r="H59" t="n">
-        <v>520</v>
+        <v>684</v>
       </c>
       <c r="I59" t="n">
-        <v>52180</v>
+        <v>51819</v>
       </c>
       <c r="J59" t="n">
-        <v>52146.5</v>
+        <v>51818</v>
       </c>
       <c r="K59" t="n">
-        <v>52543</v>
+        <v>52165</v>
       </c>
       <c r="L59" t="n">
-        <v>52939.5</v>
+        <v>52512</v>
       </c>
       <c r="M59" t="n">
-        <v>53121</v>
+        <v>52685</v>
       </c>
       <c r="N59" t="n">
-        <v>53302.5</v>
+        <v>52858</v>
       </c>
       <c r="O59" t="n">
-        <v>53914</v>
+        <v>53379</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5491,7 +5465,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S59" s="7" t="inlineStr">
+      <c r="S59" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5505,7 +5479,7 @@
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="9" t="inlineStr">
+      <c r="W59" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5515,50 +5489,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>52473</v>
+        <v>52059</v>
       </c>
       <c r="C60" t="n">
-        <v>52676</v>
+        <v>52739</v>
       </c>
       <c r="D60" t="n">
-        <v>51992</v>
+        <v>52059</v>
       </c>
       <c r="E60" t="n">
-        <v>52095</v>
+        <v>52585</v>
       </c>
       <c r="F60" t="n">
-        <v>-330</v>
+        <v>490</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0063</v>
+        <v>0.0094</v>
       </c>
       <c r="H60" t="n">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="I60" t="n">
-        <v>51819</v>
+        <v>51308</v>
       </c>
       <c r="J60" t="n">
-        <v>51818</v>
+        <v>51291.5</v>
       </c>
       <c r="K60" t="n">
-        <v>52165</v>
+        <v>51753</v>
       </c>
       <c r="L60" t="n">
-        <v>52512</v>
+        <v>52214.5</v>
       </c>
       <c r="M60" t="n">
-        <v>52685</v>
+        <v>52437</v>
       </c>
       <c r="N60" t="n">
-        <v>52858</v>
+        <v>52659.5</v>
       </c>
       <c r="O60" t="n">
-        <v>53379</v>
+        <v>53360</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5566,79 +5540,85 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="inlineStr">
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U60" s="8" t="n">
-        <v/>
-      </c>
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="9" t="inlineStr">
+      <c r="W60" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>52059</v>
+        <v>52836</v>
       </c>
       <c r="C61" t="n">
-        <v>52739</v>
+        <v>53090</v>
       </c>
       <c r="D61" t="n">
-        <v>52059</v>
+        <v>52642</v>
       </c>
       <c r="E61" t="n">
-        <v>52576</v>
+        <v>52894</v>
       </c>
       <c r="F61" t="n">
-        <v>481</v>
+        <v>309</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0092</v>
+        <v>0.0059</v>
       </c>
       <c r="H61" t="n">
-        <v>680</v>
+        <v>448</v>
       </c>
       <c r="I61" t="n">
-        <v>51308</v>
+        <v>51379</v>
       </c>
       <c r="J61" t="n">
-        <v>51291.5</v>
+        <v>51998</v>
       </c>
       <c r="K61" t="n">
-        <v>51753</v>
+        <v>52245</v>
       </c>
       <c r="L61" t="n">
-        <v>52214.5</v>
+        <v>52492</v>
       </c>
       <c r="M61" t="n">
-        <v>52437</v>
+        <v>52925</v>
       </c>
       <c r="N61" t="n">
-        <v>52659.5</v>
+        <v>53358</v>
       </c>
       <c r="O61" t="n">
-        <v>53360</v>
+        <v>53419</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5649,25 +5629,23 @@
       <c r="R61" s="6" t="n">
         <v/>
       </c>
-      <c r="S61" s="10" t="inlineStr">
+      <c r="S61" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T61" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="9" t="inlineStr">
+      <c r="W61" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5685,25 +5663,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>51379</v>
+        <v>52194</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>51984.5</v>
+        <v>52460</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>52236</v>
+        <v>52670</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>52487.5</v>
+        <v>52880</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>52916</v>
+        <v>53118</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>53344.5</v>
+        <v>53356</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>53419</v>
+        <v>53538</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -5579,25 +5579,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>52836</v>
+        <v>52906</v>
       </c>
       <c r="C61" t="n">
-        <v>53090</v>
+        <v>52906</v>
       </c>
       <c r="D61" t="n">
-        <v>52642</v>
+        <v>52833</v>
       </c>
       <c r="E61" t="n">
-        <v>52894</v>
+        <v>52835</v>
       </c>
       <c r="F61" t="n">
-        <v>309</v>
+        <v>250</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0048</v>
       </c>
       <c r="H61" t="n">
-        <v>448</v>
+        <v>73</v>
       </c>
       <c r="I61" t="n">
         <v>51379</v>
@@ -5663,25 +5663,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>52194</v>
+        <v>52760</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>52460</v>
+        <v>52744.75</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>52670</v>
+        <v>52798.5</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>52880</v>
+        <v>52852.25</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>53118</v>
+        <v>52871.5</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>53356</v>
+        <v>52890.75</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>53538</v>
+        <v>52979</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -5585,19 +5585,19 @@
         <v>52906</v>
       </c>
       <c r="D61" t="n">
-        <v>52833</v>
+        <v>52803</v>
       </c>
       <c r="E61" t="n">
-        <v>52835</v>
+        <v>52820</v>
       </c>
       <c r="F61" t="n">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0048</v>
+        <v>0.0045</v>
       </c>
       <c r="H61" t="n">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="I61" t="n">
         <v>51379</v>
@@ -5663,25 +5663,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>52760</v>
+        <v>52700</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>52744.75</v>
+        <v>52699.75</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>52798.5</v>
+        <v>52768.5</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>52852.25</v>
+        <v>52837.25</v>
       </c>
       <c r="M62" s="13" t="n">
         <v>52871.5</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>52890.75</v>
+        <v>52905.75</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>52979</v>
+        <v>53009</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -5585,19 +5585,19 @@
         <v>52906</v>
       </c>
       <c r="D61" t="n">
-        <v>52803</v>
+        <v>52763</v>
       </c>
       <c r="E61" t="n">
-        <v>52820</v>
+        <v>52763</v>
       </c>
       <c r="F61" t="n">
-        <v>235</v>
+        <v>178</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0045</v>
+        <v>0.0034</v>
       </c>
       <c r="H61" t="n">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="I61" t="n">
         <v>51379</v>
@@ -5663,25 +5663,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>52700</v>
+        <v>52620</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>52699.75</v>
+        <v>52584.25</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>52768.5</v>
+        <v>52691.5</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>52837.25</v>
+        <v>52798.75</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>52871.5</v>
+        <v>52834.5</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>52905.75</v>
+        <v>52870.25</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>53009</v>
+        <v>53049</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5579,25 +5579,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>52906</v>
+        <v>52376</v>
       </c>
       <c r="C61" t="n">
-        <v>52906</v>
+        <v>52672</v>
       </c>
       <c r="D61" t="n">
-        <v>52763</v>
+        <v>52226</v>
       </c>
       <c r="E61" t="n">
-        <v>52763</v>
+        <v>52440</v>
       </c>
       <c r="F61" t="n">
-        <v>178</v>
+        <v>-145</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0034</v>
+        <v>-0.0028</v>
       </c>
       <c r="H61" t="n">
-        <v>143</v>
+        <v>446</v>
       </c>
       <c r="I61" t="n">
         <v>51379</v>
@@ -5626,62 +5626,148 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W61" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>52906</v>
+      </c>
+      <c r="C62" t="n">
+        <v>52906</v>
+      </c>
+      <c r="D62" t="n">
+        <v>52713</v>
+      </c>
+      <c r="E62" t="n">
+        <v>52713</v>
+      </c>
+      <c r="F62" t="n">
+        <v>273</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="H62" t="n">
+        <v>193</v>
+      </c>
+      <c r="I62" t="n">
+        <v>51780</v>
+      </c>
+      <c r="J62" t="n">
+        <v>51989.5</v>
+      </c>
+      <c r="K62" t="n">
+        <v>52217</v>
+      </c>
+      <c r="L62" t="n">
+        <v>52444.5</v>
+      </c>
+      <c r="M62" t="n">
+        <v>52663</v>
+      </c>
+      <c r="N62" t="n">
+        <v>52881.5</v>
+      </c>
+      <c r="O62" t="n">
+        <v>53118</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T61" s="8" t="inlineStr">
+      <c r="T62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W61" s="11" t="inlineStr">
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>強警訊</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I62" s="13" t="n">
-        <v>52620</v>
-      </c>
-      <c r="J62" s="13" t="n">
-        <v>52584.25</v>
-      </c>
-      <c r="K62" s="13" t="n">
-        <v>52691.5</v>
-      </c>
-      <c r="L62" s="13" t="n">
-        <v>52798.75</v>
-      </c>
-      <c r="M62" s="13" t="n">
-        <v>52834.5</v>
-      </c>
-      <c r="N62" s="13" t="n">
-        <v>52870.25</v>
-      </c>
-      <c r="O62" s="13" t="n">
-        <v>53049</v>
+      <c r="I63" s="13" t="n">
+        <v>52520</v>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>52471.75</v>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>52616.5</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>52761.25</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>52809.5</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>52857.75</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>53099</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51621</v>
+        <v>51870</v>
       </c>
       <c r="C2" t="n">
-        <v>51962</v>
+        <v>52305</v>
       </c>
       <c r="D2" t="n">
-        <v>51587</v>
+        <v>51712</v>
       </c>
       <c r="E2" t="n">
-        <v>51962</v>
+        <v>52119</v>
       </c>
       <c r="F2" t="n">
-        <v>443</v>
+        <v>157</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0086</v>
+        <v>0.003</v>
       </c>
       <c r="H2" t="n">
-        <v>375</v>
+        <v>593</v>
       </c>
       <c r="I2" t="n">
-        <v>50540</v>
+        <v>51212</v>
       </c>
       <c r="J2" t="n">
-        <v>50468.5</v>
+        <v>51680.75</v>
       </c>
       <c r="K2" t="n">
-        <v>51079</v>
+        <v>51774.5</v>
       </c>
       <c r="L2" t="n">
-        <v>51689.5</v>
+        <v>51868.25</v>
       </c>
       <c r="M2" t="n">
-        <v>51959</v>
+        <v>52149.5</v>
       </c>
       <c r="N2" t="n">
-        <v>52228.5</v>
+        <v>52430.75</v>
       </c>
       <c r="O2" t="n">
-        <v>53180</v>
+        <v>52337</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -692,8 +692,10 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -716,59 +718,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>51870</v>
+        <v>52165</v>
       </c>
       <c r="C3" t="n">
-        <v>52305</v>
+        <v>52281</v>
       </c>
       <c r="D3" t="n">
-        <v>51712</v>
+        <v>51691</v>
       </c>
       <c r="E3" t="n">
-        <v>52119</v>
+        <v>52082</v>
       </c>
       <c r="F3" t="n">
-        <v>157</v>
+        <v>-37</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0007</v>
       </c>
       <c r="H3" t="n">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="I3" t="n">
-        <v>51212</v>
+        <v>51119</v>
       </c>
       <c r="J3" t="n">
-        <v>51680.75</v>
+        <v>51581.25</v>
       </c>
       <c r="K3" t="n">
-        <v>51774.5</v>
+        <v>51822.5</v>
       </c>
       <c r="L3" t="n">
-        <v>51868.25</v>
+        <v>52063.75</v>
       </c>
       <c r="M3" t="n">
-        <v>52149.5</v>
+        <v>52415.5</v>
       </c>
       <c r="N3" t="n">
-        <v>52430.75</v>
+        <v>52767.25</v>
       </c>
       <c r="O3" t="n">
-        <v>52337</v>
+        <v>52898</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -783,13 +781,11 @@
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -802,55 +798,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>52165</v>
+        <v>52119</v>
       </c>
       <c r="C4" t="n">
-        <v>52281</v>
+        <v>52676</v>
       </c>
       <c r="D4" t="n">
-        <v>51691</v>
+        <v>51933</v>
       </c>
       <c r="E4" t="n">
-        <v>52082</v>
+        <v>52279</v>
       </c>
       <c r="F4" t="n">
-        <v>-37</v>
+        <v>197</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0007</v>
+        <v>0.0038</v>
       </c>
       <c r="H4" t="n">
-        <v>590</v>
+        <v>743</v>
       </c>
       <c r="I4" t="n">
-        <v>51119</v>
+        <v>51101</v>
       </c>
       <c r="J4" t="n">
-        <v>51581.25</v>
+        <v>51540</v>
       </c>
       <c r="K4" t="n">
-        <v>51822.5</v>
+        <v>51787</v>
       </c>
       <c r="L4" t="n">
-        <v>52063.75</v>
+        <v>52034</v>
       </c>
       <c r="M4" t="n">
-        <v>52415.5</v>
+        <v>52377</v>
       </c>
       <c r="N4" t="n">
-        <v>52767.25</v>
+        <v>52720</v>
       </c>
       <c r="O4" t="n">
-        <v>52898</v>
+        <v>52871</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -858,18 +858,18 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R4" s="6" t="n">
+        <v/>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -882,59 +882,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52119</v>
+        <v>52381</v>
       </c>
       <c r="C5" t="n">
-        <v>52676</v>
+        <v>53097</v>
       </c>
       <c r="D5" t="n">
-        <v>51933</v>
+        <v>52215</v>
       </c>
       <c r="E5" t="n">
-        <v>52279</v>
+        <v>52339</v>
       </c>
       <c r="F5" t="n">
-        <v>197</v>
+        <v>60</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.0011</v>
       </c>
       <c r="H5" t="n">
-        <v>743</v>
+        <v>882</v>
       </c>
       <c r="I5" t="n">
-        <v>51101</v>
+        <v>51190</v>
       </c>
       <c r="J5" t="n">
-        <v>51540</v>
+        <v>51523.25</v>
       </c>
       <c r="K5" t="n">
-        <v>51787</v>
+        <v>51907.5</v>
       </c>
       <c r="L5" t="n">
-        <v>52034</v>
+        <v>52291.75</v>
       </c>
       <c r="M5" t="n">
-        <v>52377</v>
+        <v>52650.5</v>
       </c>
       <c r="N5" t="n">
-        <v>52720</v>
+        <v>53009.25</v>
       </c>
       <c r="O5" t="n">
-        <v>52871</v>
+        <v>53419</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -947,16 +943,18 @@
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -971,50 +969,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52381</v>
+        <v>52439</v>
       </c>
       <c r="C6" t="n">
-        <v>53097</v>
+        <v>52542</v>
       </c>
       <c r="D6" t="n">
-        <v>52215</v>
+        <v>52008</v>
       </c>
       <c r="E6" t="n">
-        <v>52339</v>
+        <v>52209</v>
       </c>
       <c r="F6" t="n">
-        <v>60</v>
+        <v>-130</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0011</v>
+        <v>-0.0025</v>
       </c>
       <c r="H6" t="n">
-        <v>882</v>
+        <v>534</v>
       </c>
       <c r="I6" t="n">
-        <v>51190</v>
+        <v>51333</v>
       </c>
       <c r="J6" t="n">
-        <v>51523.25</v>
+        <v>51298.5</v>
       </c>
       <c r="K6" t="n">
-        <v>51907.5</v>
+        <v>51898</v>
       </c>
       <c r="L6" t="n">
-        <v>52291.75</v>
+        <v>52497.5</v>
       </c>
       <c r="M6" t="n">
-        <v>52650.5</v>
+        <v>52780</v>
       </c>
       <c r="N6" t="n">
-        <v>53009.25</v>
+        <v>53062.5</v>
       </c>
       <c r="O6" t="n">
-        <v>53419</v>
+        <v>53979</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1025,20 +1023,16 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
@@ -1048,55 +1042,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>52439</v>
+        <v>52183</v>
       </c>
       <c r="C7" t="n">
-        <v>52542</v>
+        <v>52700</v>
       </c>
       <c r="D7" t="n">
-        <v>52008</v>
+        <v>52179</v>
       </c>
       <c r="E7" t="n">
-        <v>52209</v>
+        <v>52572</v>
       </c>
       <c r="F7" t="n">
-        <v>-130</v>
+        <v>363</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.007</v>
       </c>
       <c r="H7" t="n">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="I7" t="n">
-        <v>51333</v>
+        <v>51474</v>
       </c>
       <c r="J7" t="n">
-        <v>51298.5</v>
+        <v>51642</v>
       </c>
       <c r="K7" t="n">
-        <v>51898</v>
+        <v>51942</v>
       </c>
       <c r="L7" t="n">
-        <v>52497.5</v>
+        <v>52242</v>
       </c>
       <c r="M7" t="n">
-        <v>52780</v>
+        <v>52476</v>
       </c>
       <c r="N7" t="n">
-        <v>53062.5</v>
+        <v>52710</v>
       </c>
       <c r="O7" t="n">
-        <v>53979</v>
+        <v>53076</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1107,13 +1105,15 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1126,59 +1126,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52183</v>
+        <v>52554</v>
       </c>
       <c r="C8" t="n">
-        <v>52700</v>
+        <v>52763</v>
       </c>
       <c r="D8" t="n">
-        <v>52179</v>
+        <v>52383</v>
       </c>
       <c r="E8" t="n">
-        <v>52572</v>
+        <v>52670</v>
       </c>
       <c r="F8" t="n">
-        <v>363</v>
+        <v>98</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.007</v>
+        <v>0.0019</v>
       </c>
       <c r="H8" t="n">
-        <v>521</v>
+        <v>380</v>
       </c>
       <c r="I8" t="n">
-        <v>51474</v>
+        <v>51658</v>
       </c>
       <c r="J8" t="n">
-        <v>51642</v>
+        <v>52117.25</v>
       </c>
       <c r="K8" t="n">
-        <v>51942</v>
+        <v>52311.5</v>
       </c>
       <c r="L8" t="n">
-        <v>52242</v>
+        <v>52505.75</v>
       </c>
       <c r="M8" t="n">
-        <v>52476</v>
+        <v>52832.5</v>
       </c>
       <c r="N8" t="n">
-        <v>52710</v>
+        <v>53159.25</v>
       </c>
       <c r="O8" t="n">
-        <v>53076</v>
+        <v>53221</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1215,50 +1211,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52554</v>
+        <v>52546</v>
       </c>
       <c r="C9" t="n">
-        <v>52763</v>
+        <v>53105</v>
       </c>
       <c r="D9" t="n">
-        <v>52383</v>
+        <v>52381</v>
       </c>
       <c r="E9" t="n">
-        <v>52670</v>
+        <v>52668</v>
       </c>
       <c r="F9" t="n">
-        <v>98</v>
+        <v>-2</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
-        <v>380</v>
+        <v>724</v>
       </c>
       <c r="I9" t="n">
-        <v>51658</v>
+        <v>52003</v>
       </c>
       <c r="J9" t="n">
-        <v>52117.25</v>
+        <v>52338.5</v>
       </c>
       <c r="K9" t="n">
-        <v>52311.5</v>
+        <v>52480</v>
       </c>
       <c r="L9" t="n">
-        <v>52505.75</v>
+        <v>52621.5</v>
       </c>
       <c r="M9" t="n">
-        <v>52832.5</v>
+        <v>52860</v>
       </c>
       <c r="N9" t="n">
-        <v>53159.25</v>
+        <v>53098.5</v>
       </c>
       <c r="O9" t="n">
-        <v>53221</v>
+        <v>53143</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1266,21 +1262,25 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1290,55 +1290,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52546</v>
+        <v>52640</v>
       </c>
       <c r="C10" t="n">
-        <v>53105</v>
+        <v>53218</v>
       </c>
       <c r="D10" t="n">
-        <v>52381</v>
+        <v>52551</v>
       </c>
       <c r="E10" t="n">
-        <v>52668</v>
+        <v>53183</v>
       </c>
       <c r="F10" t="n">
-        <v>-2</v>
+        <v>515</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0</v>
+        <v>0.0098</v>
       </c>
       <c r="H10" t="n">
-        <v>724</v>
+        <v>667</v>
       </c>
       <c r="I10" t="n">
-        <v>52003</v>
+        <v>51657</v>
       </c>
       <c r="J10" t="n">
-        <v>52338.5</v>
+        <v>51906.5</v>
       </c>
       <c r="K10" t="n">
-        <v>52480</v>
+        <v>52306</v>
       </c>
       <c r="L10" t="n">
-        <v>52621.5</v>
+        <v>52705.5</v>
       </c>
       <c r="M10" t="n">
-        <v>52860</v>
+        <v>53030</v>
       </c>
       <c r="N10" t="n">
-        <v>53098.5</v>
+        <v>53354.5</v>
       </c>
       <c r="O10" t="n">
-        <v>53143</v>
+        <v>53829</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1346,25 +1350,21 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1374,59 +1374,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>52640</v>
+        <v>53230</v>
       </c>
       <c r="C11" t="n">
-        <v>53218</v>
+        <v>53421</v>
       </c>
       <c r="D11" t="n">
-        <v>52551</v>
+        <v>52962</v>
       </c>
       <c r="E11" t="n">
-        <v>53183</v>
+        <v>53372</v>
       </c>
       <c r="F11" t="n">
-        <v>515</v>
+        <v>189</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0036</v>
       </c>
       <c r="H11" t="n">
-        <v>667</v>
+        <v>459</v>
       </c>
       <c r="I11" t="n">
-        <v>51657</v>
+        <v>51884</v>
       </c>
       <c r="J11" t="n">
-        <v>51906.5</v>
+        <v>52665.25</v>
       </c>
       <c r="K11" t="n">
-        <v>52306</v>
+        <v>52849.5</v>
       </c>
       <c r="L11" t="n">
-        <v>52705.5</v>
+        <v>53033.75</v>
       </c>
       <c r="M11" t="n">
-        <v>53030</v>
+        <v>53516.5</v>
       </c>
       <c r="N11" t="n">
-        <v>53354.5</v>
+        <v>53999.25</v>
       </c>
       <c r="O11" t="n">
-        <v>53829</v>
+        <v>53885</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1463,50 +1459,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>53230</v>
+        <v>53405</v>
       </c>
       <c r="C12" t="n">
-        <v>53421</v>
+        <v>53656</v>
       </c>
       <c r="D12" t="n">
-        <v>52962</v>
+        <v>53076</v>
       </c>
       <c r="E12" t="n">
-        <v>53372</v>
+        <v>53197</v>
       </c>
       <c r="F12" t="n">
-        <v>189</v>
+        <v>-175</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0036</v>
+        <v>-0.0033</v>
       </c>
       <c r="H12" t="n">
-        <v>459</v>
+        <v>580</v>
       </c>
       <c r="I12" t="n">
-        <v>51884</v>
+        <v>52503</v>
       </c>
       <c r="J12" t="n">
-        <v>52665.25</v>
+        <v>53003.25</v>
       </c>
       <c r="K12" t="n">
-        <v>52849.5</v>
+        <v>53142.5</v>
       </c>
       <c r="L12" t="n">
-        <v>53033.75</v>
+        <v>53281.75</v>
       </c>
       <c r="M12" t="n">
-        <v>53516.5</v>
+        <v>53601.5</v>
       </c>
       <c r="N12" t="n">
-        <v>53999.25</v>
+        <v>53921.25</v>
       </c>
       <c r="O12" t="n">
-        <v>53885</v>
+        <v>53880</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1514,17 +1510,19 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U12" s="8" t="n">
@@ -1538,65 +1536,73 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>53405</v>
+        <v>53166</v>
       </c>
       <c r="C13" t="n">
-        <v>53656</v>
+        <v>53207</v>
       </c>
       <c r="D13" t="n">
-        <v>53076</v>
+        <v>52343</v>
       </c>
       <c r="E13" t="n">
-        <v>53197</v>
+        <v>52624</v>
       </c>
       <c r="F13" t="n">
-        <v>-175</v>
+        <v>-573</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0108</v>
       </c>
       <c r="H13" t="n">
-        <v>580</v>
+        <v>864</v>
       </c>
       <c r="I13" t="n">
-        <v>52503</v>
+        <v>52496</v>
       </c>
       <c r="J13" t="n">
-        <v>53003.25</v>
+        <v>52532.5</v>
       </c>
       <c r="K13" t="n">
-        <v>53142.5</v>
+        <v>52907</v>
       </c>
       <c r="L13" t="n">
-        <v>53281.75</v>
+        <v>53281.5</v>
       </c>
       <c r="M13" t="n">
-        <v>53601.5</v>
+        <v>53487</v>
       </c>
       <c r="N13" t="n">
-        <v>53921.25</v>
+        <v>53692.5</v>
       </c>
       <c r="O13" t="n">
-        <v>53880</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
+        <v>54236</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
@@ -1604,10 +1610,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1622,76 +1626,70 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>53166</v>
+        <v>52541</v>
       </c>
       <c r="C14" t="n">
-        <v>53207</v>
+        <v>52865</v>
       </c>
       <c r="D14" t="n">
-        <v>52343</v>
+        <v>52501</v>
       </c>
       <c r="E14" t="n">
-        <v>52624</v>
+        <v>52761</v>
       </c>
       <c r="F14" t="n">
-        <v>-573</v>
+        <v>137</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0108</v>
+        <v>0.0026</v>
       </c>
       <c r="H14" t="n">
-        <v>864</v>
+        <v>364</v>
       </c>
       <c r="I14" t="n">
-        <v>52496</v>
+        <v>51479</v>
       </c>
       <c r="J14" t="n">
-        <v>52532.5</v>
+        <v>51684.5</v>
       </c>
       <c r="K14" t="n">
-        <v>52907</v>
+        <v>52192</v>
       </c>
       <c r="L14" t="n">
-        <v>53281.5</v>
+        <v>52699.5</v>
       </c>
       <c r="M14" t="n">
-        <v>53487</v>
+        <v>53056</v>
       </c>
       <c r="N14" t="n">
-        <v>53692.5</v>
+        <v>53412.5</v>
       </c>
       <c r="O14" t="n">
-        <v>54236</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>54071</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1710,57 +1708,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52541</v>
+        <v>52753</v>
       </c>
       <c r="C15" t="n">
-        <v>52865</v>
+        <v>52992</v>
       </c>
       <c r="D15" t="n">
-        <v>52501</v>
+        <v>52506</v>
       </c>
       <c r="E15" t="n">
-        <v>52761</v>
+        <v>52906</v>
       </c>
       <c r="F15" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0027</v>
       </c>
       <c r="H15" t="n">
-        <v>364</v>
+        <v>486</v>
       </c>
       <c r="I15" t="n">
-        <v>51479</v>
+        <v>52137</v>
       </c>
       <c r="J15" t="n">
-        <v>51684.5</v>
+        <v>52436</v>
       </c>
       <c r="K15" t="n">
-        <v>52192</v>
+        <v>52579</v>
       </c>
       <c r="L15" t="n">
-        <v>52699.5</v>
+        <v>52722</v>
       </c>
       <c r="M15" t="n">
-        <v>53056</v>
+        <v>52943</v>
       </c>
       <c r="N15" t="n">
-        <v>53412.5</v>
+        <v>53164</v>
       </c>
       <c r="O15" t="n">
-        <v>54071</v>
+        <v>53229</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1768,16 +1766,20 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1790,59 +1792,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>52753</v>
+        <v>52844</v>
       </c>
       <c r="C16" t="n">
-        <v>52992</v>
+        <v>53113</v>
       </c>
       <c r="D16" t="n">
-        <v>52506</v>
+        <v>52603</v>
       </c>
       <c r="E16" t="n">
-        <v>52906</v>
+        <v>52764</v>
       </c>
       <c r="F16" t="n">
-        <v>145</v>
+        <v>-142</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0027</v>
       </c>
       <c r="H16" t="n">
-        <v>486</v>
+        <v>510</v>
       </c>
       <c r="I16" t="n">
-        <v>52137</v>
+        <v>52020</v>
       </c>
       <c r="J16" t="n">
-        <v>52436</v>
+        <v>52498.5</v>
       </c>
       <c r="K16" t="n">
-        <v>52579</v>
+        <v>52663</v>
       </c>
       <c r="L16" t="n">
-        <v>52722</v>
+        <v>52827.5</v>
       </c>
       <c r="M16" t="n">
-        <v>52943</v>
+        <v>53149</v>
       </c>
       <c r="N16" t="n">
-        <v>53164</v>
+        <v>53470.5</v>
       </c>
       <c r="O16" t="n">
-        <v>53229</v>
+        <v>53478</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1855,15 +1853,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1876,55 +1872,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52844</v>
+        <v>52731</v>
       </c>
       <c r="C17" t="n">
-        <v>53113</v>
+        <v>52981</v>
       </c>
       <c r="D17" t="n">
-        <v>52603</v>
+        <v>52255</v>
       </c>
       <c r="E17" t="n">
-        <v>52764</v>
+        <v>52791</v>
       </c>
       <c r="F17" t="n">
-        <v>-142</v>
+        <v>27</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0005</v>
       </c>
       <c r="H17" t="n">
-        <v>510</v>
+        <v>726</v>
       </c>
       <c r="I17" t="n">
-        <v>52020</v>
+        <v>52093</v>
       </c>
       <c r="J17" t="n">
-        <v>52498.5</v>
+        <v>52207</v>
       </c>
       <c r="K17" t="n">
-        <v>52663</v>
+        <v>52509</v>
       </c>
       <c r="L17" t="n">
-        <v>52827.5</v>
+        <v>52811</v>
       </c>
       <c r="M17" t="n">
-        <v>53149</v>
+        <v>53019</v>
       </c>
       <c r="N17" t="n">
-        <v>53470.5</v>
+        <v>53227</v>
       </c>
       <c r="O17" t="n">
-        <v>53478</v>
+        <v>53623</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1958,57 +1958,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52731</v>
+        <v>52792</v>
       </c>
       <c r="C18" t="n">
-        <v>52981</v>
+        <v>53088</v>
       </c>
       <c r="D18" t="n">
-        <v>52255</v>
+        <v>52680</v>
       </c>
       <c r="E18" t="n">
-        <v>52791</v>
+        <v>52900</v>
       </c>
       <c r="F18" t="n">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0021</v>
       </c>
       <c r="H18" t="n">
-        <v>726</v>
+        <v>408</v>
       </c>
       <c r="I18" t="n">
-        <v>52093</v>
+        <v>51529</v>
       </c>
       <c r="J18" t="n">
-        <v>52207</v>
+        <v>52151.5</v>
       </c>
       <c r="K18" t="n">
-        <v>52509</v>
+        <v>52428</v>
       </c>
       <c r="L18" t="n">
-        <v>52811</v>
+        <v>52704.5</v>
       </c>
       <c r="M18" t="n">
-        <v>53019</v>
+        <v>53154</v>
       </c>
       <c r="N18" t="n">
-        <v>53227</v>
+        <v>53603.5</v>
       </c>
       <c r="O18" t="n">
-        <v>53623</v>
+        <v>53707</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2016,14 +2016,12 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2040,59 +2038,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>52792</v>
+        <v>52919</v>
       </c>
       <c r="C19" t="n">
-        <v>53088</v>
+        <v>53108</v>
       </c>
       <c r="D19" t="n">
-        <v>52680</v>
+        <v>52607</v>
       </c>
       <c r="E19" t="n">
-        <v>52900</v>
+        <v>52786</v>
       </c>
       <c r="F19" t="n">
-        <v>109</v>
+        <v>-114</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0022</v>
       </c>
       <c r="H19" t="n">
-        <v>408</v>
+        <v>501</v>
       </c>
       <c r="I19" t="n">
-        <v>51529</v>
+        <v>52272</v>
       </c>
       <c r="J19" t="n">
-        <v>52151.5</v>
+        <v>52500</v>
       </c>
       <c r="K19" t="n">
-        <v>52428</v>
+        <v>52696</v>
       </c>
       <c r="L19" t="n">
-        <v>52704.5</v>
+        <v>52892</v>
       </c>
       <c r="M19" t="n">
-        <v>53154</v>
+        <v>53104</v>
       </c>
       <c r="N19" t="n">
-        <v>53603.5</v>
+        <v>53316</v>
       </c>
       <c r="O19" t="n">
-        <v>53707</v>
+        <v>53496</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2100,16 +2094,20 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2122,65 +2120,71 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>52919</v>
+        <v>52778</v>
       </c>
       <c r="C20" t="n">
-        <v>53108</v>
+        <v>52835</v>
       </c>
       <c r="D20" t="n">
-        <v>52607</v>
+        <v>52174</v>
       </c>
       <c r="E20" t="n">
-        <v>52786</v>
+        <v>52375</v>
       </c>
       <c r="F20" t="n">
-        <v>-114</v>
+        <v>-411</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0078</v>
       </c>
       <c r="H20" t="n">
-        <v>501</v>
+        <v>661</v>
       </c>
       <c r="I20" t="n">
-        <v>52272</v>
+        <v>52106</v>
       </c>
       <c r="J20" t="n">
-        <v>52500</v>
+        <v>52249.25</v>
       </c>
       <c r="K20" t="n">
-        <v>52696</v>
+        <v>52535.5</v>
       </c>
       <c r="L20" t="n">
-        <v>52892</v>
+        <v>52821.75</v>
       </c>
       <c r="M20" t="n">
-        <v>53104</v>
+        <v>53036.5</v>
       </c>
       <c r="N20" t="n">
-        <v>53316</v>
+        <v>53251.25</v>
       </c>
       <c r="O20" t="n">
-        <v>53496</v>
+        <v>53609</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S20" s="10" t="inlineStr">
@@ -2188,10 +2192,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2206,69 +2208,67 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>52778</v>
+        <v>52300</v>
       </c>
       <c r="C21" t="n">
-        <v>52835</v>
+        <v>52633</v>
       </c>
       <c r="D21" t="n">
-        <v>52174</v>
+        <v>51999</v>
       </c>
       <c r="E21" t="n">
-        <v>52375</v>
+        <v>52073</v>
       </c>
       <c r="F21" t="n">
-        <v>-411</v>
+        <v>-302</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0078</v>
+        <v>-0.0058</v>
       </c>
       <c r="H21" t="n">
-        <v>661</v>
+        <v>634</v>
       </c>
       <c r="I21" t="n">
-        <v>52106</v>
+        <v>51513</v>
       </c>
       <c r="J21" t="n">
-        <v>52249.25</v>
+        <v>51649.25</v>
       </c>
       <c r="K21" t="n">
-        <v>52535.5</v>
+        <v>52044.5</v>
       </c>
       <c r="L21" t="n">
-        <v>52821.75</v>
+        <v>52439.75</v>
       </c>
       <c r="M21" t="n">
-        <v>53036.5</v>
+        <v>52705.5</v>
       </c>
       <c r="N21" t="n">
-        <v>53251.25</v>
+        <v>52971.25</v>
       </c>
       <c r="O21" t="n">
-        <v>53609</v>
+        <v>53496</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S21" s="10" t="inlineStr">
@@ -2299,50 +2299,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>52300</v>
+        <v>52091</v>
       </c>
       <c r="C22" t="n">
-        <v>52633</v>
+        <v>52590</v>
       </c>
       <c r="D22" t="n">
-        <v>51999</v>
+        <v>52035</v>
       </c>
       <c r="E22" t="n">
-        <v>52073</v>
+        <v>52443</v>
       </c>
       <c r="F22" t="n">
-        <v>-302</v>
+        <v>370</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.0071</v>
       </c>
       <c r="H22" t="n">
-        <v>634</v>
+        <v>555</v>
       </c>
       <c r="I22" t="n">
-        <v>51513</v>
+        <v>51365</v>
       </c>
       <c r="J22" t="n">
-        <v>51649.25</v>
+        <v>51317.5</v>
       </c>
       <c r="K22" t="n">
-        <v>52044.5</v>
+        <v>51756</v>
       </c>
       <c r="L22" t="n">
-        <v>52439.75</v>
+        <v>52194.5</v>
       </c>
       <c r="M22" t="n">
-        <v>52705.5</v>
+        <v>52390</v>
       </c>
       <c r="N22" t="n">
-        <v>52971.25</v>
+        <v>52585.5</v>
       </c>
       <c r="O22" t="n">
-        <v>53496</v>
+        <v>53267</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2350,21 +2350,23 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2376,57 +2378,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>52091</v>
+        <v>52431</v>
       </c>
       <c r="C23" t="n">
-        <v>52590</v>
+        <v>52721</v>
       </c>
       <c r="D23" t="n">
-        <v>52035</v>
+        <v>52262</v>
       </c>
       <c r="E23" t="n">
-        <v>52443</v>
+        <v>52449</v>
       </c>
       <c r="F23" t="n">
-        <v>370</v>
+        <v>6</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0001</v>
       </c>
       <c r="H23" t="n">
-        <v>555</v>
+        <v>459</v>
       </c>
       <c r="I23" t="n">
-        <v>51365</v>
+        <v>51480</v>
       </c>
       <c r="J23" t="n">
-        <v>51317.5</v>
+        <v>51953.25</v>
       </c>
       <c r="K23" t="n">
-        <v>51756</v>
+        <v>52165.5</v>
       </c>
       <c r="L23" t="n">
-        <v>52194.5</v>
+        <v>52377.75</v>
       </c>
       <c r="M23" t="n">
-        <v>52390</v>
+        <v>52720.5</v>
       </c>
       <c r="N23" t="n">
-        <v>52585.5</v>
+        <v>53063.25</v>
       </c>
       <c r="O23" t="n">
-        <v>53267</v>
+        <v>53145</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2439,19 +2441,17 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
@@ -2460,88 +2460,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>52431</v>
+        <v>52430</v>
       </c>
       <c r="C24" t="n">
-        <v>52721</v>
+        <v>52515</v>
       </c>
       <c r="D24" t="n">
-        <v>52262</v>
+        <v>51720</v>
       </c>
       <c r="E24" t="n">
-        <v>52449</v>
+        <v>51894</v>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>-555</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0106</v>
       </c>
       <c r="H24" t="n">
-        <v>459</v>
+        <v>795</v>
       </c>
       <c r="I24" t="n">
-        <v>51480</v>
+        <v>51803</v>
       </c>
       <c r="J24" t="n">
-        <v>51953.25</v>
+        <v>51968.75</v>
       </c>
       <c r="K24" t="n">
-        <v>52165.5</v>
+        <v>52219.5</v>
       </c>
       <c r="L24" t="n">
-        <v>52377.75</v>
+        <v>52470.25</v>
       </c>
       <c r="M24" t="n">
-        <v>52720.5</v>
+        <v>52678.5</v>
       </c>
       <c r="N24" t="n">
-        <v>53063.25</v>
+        <v>52886.75</v>
       </c>
       <c r="O24" t="n">
-        <v>53145</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
+        <v>53180</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W24" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
@@ -2549,74 +2549,70 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>52430</v>
+        <v>51920</v>
       </c>
       <c r="C25" t="n">
-        <v>52515</v>
+        <v>52314</v>
       </c>
       <c r="D25" t="n">
-        <v>51720</v>
+        <v>51846</v>
       </c>
       <c r="E25" t="n">
-        <v>51894</v>
+        <v>52124</v>
       </c>
       <c r="F25" t="n">
-        <v>-555</v>
+        <v>230</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0044</v>
       </c>
       <c r="H25" t="n">
-        <v>795</v>
+        <v>468</v>
       </c>
       <c r="I25" t="n">
-        <v>51803</v>
+        <v>50925</v>
       </c>
       <c r="J25" t="n">
-        <v>51968.75</v>
+        <v>50987.25</v>
       </c>
       <c r="K25" t="n">
-        <v>52219.5</v>
+        <v>51496.5</v>
       </c>
       <c r="L25" t="n">
-        <v>52470.25</v>
+        <v>52005.75</v>
       </c>
       <c r="M25" t="n">
-        <v>52678.5</v>
+        <v>52291.5</v>
       </c>
       <c r="N25" t="n">
-        <v>52886.75</v>
+        <v>52577.25</v>
       </c>
       <c r="O25" t="n">
-        <v>53180</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
+        <v>53310</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
       <c r="U25" s="8" t="n">
         <v/>
       </c>
@@ -2628,55 +2624,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>51920</v>
+        <v>52299</v>
       </c>
       <c r="C26" t="n">
-        <v>52314</v>
+        <v>52790</v>
       </c>
       <c r="D26" t="n">
-        <v>51846</v>
+        <v>52173</v>
       </c>
       <c r="E26" t="n">
-        <v>52124</v>
+        <v>52382</v>
       </c>
       <c r="F26" t="n">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0049</v>
       </c>
       <c r="H26" t="n">
-        <v>468</v>
+        <v>617</v>
       </c>
       <c r="I26" t="n">
-        <v>50925</v>
+        <v>51378</v>
       </c>
       <c r="J26" t="n">
-        <v>50987.25</v>
+        <v>51678</v>
       </c>
       <c r="K26" t="n">
-        <v>51496.5</v>
+        <v>51890</v>
       </c>
       <c r="L26" t="n">
-        <v>52005.75</v>
+        <v>52102</v>
       </c>
       <c r="M26" t="n">
-        <v>52291.5</v>
+        <v>52358</v>
       </c>
       <c r="N26" t="n">
-        <v>52577.25</v>
+        <v>52614</v>
       </c>
       <c r="O26" t="n">
-        <v>53310</v>
+        <v>52782</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2689,19 +2689,23 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v/>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W26" s="11" t="inlineStr">
         <is>
@@ -2710,57 +2714,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>52299</v>
+        <v>52405</v>
       </c>
       <c r="C27" t="n">
-        <v>52790</v>
+        <v>53105</v>
       </c>
       <c r="D27" t="n">
-        <v>52173</v>
+        <v>52290</v>
       </c>
       <c r="E27" t="n">
-        <v>52382</v>
+        <v>52944</v>
       </c>
       <c r="F27" t="n">
-        <v>258</v>
+        <v>562</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0107</v>
       </c>
       <c r="H27" t="n">
-        <v>617</v>
+        <v>815</v>
       </c>
       <c r="I27" t="n">
-        <v>51378</v>
+        <v>51556</v>
       </c>
       <c r="J27" t="n">
-        <v>51678</v>
+        <v>51715.25</v>
       </c>
       <c r="K27" t="n">
-        <v>51890</v>
+        <v>52073.5</v>
       </c>
       <c r="L27" t="n">
-        <v>52102</v>
+        <v>52431.75</v>
       </c>
       <c r="M27" t="n">
-        <v>52358</v>
+        <v>52690.5</v>
       </c>
       <c r="N27" t="n">
-        <v>52614</v>
+        <v>52949.25</v>
       </c>
       <c r="O27" t="n">
-        <v>52782</v>
+        <v>53407</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2778,18 +2782,16 @@
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V27" s="8" t="n">
+        <v/>
       </c>
       <c r="W27" s="11" t="inlineStr">
         <is>
@@ -2805,74 +2807,76 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>52405</v>
+        <v>52915</v>
       </c>
       <c r="C28" t="n">
-        <v>53105</v>
+        <v>53033</v>
       </c>
       <c r="D28" t="n">
-        <v>52290</v>
+        <v>51630</v>
       </c>
       <c r="E28" t="n">
-        <v>52944</v>
+        <v>51765</v>
       </c>
       <c r="F28" t="n">
-        <v>562</v>
+        <v>-1179</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0223</v>
       </c>
       <c r="H28" t="n">
-        <v>815</v>
+        <v>1403</v>
       </c>
       <c r="I28" t="n">
-        <v>51556</v>
+        <v>51475</v>
       </c>
       <c r="J28" t="n">
-        <v>51715.25</v>
+        <v>52252.25</v>
       </c>
       <c r="K28" t="n">
-        <v>52073.5</v>
+        <v>52536.5</v>
       </c>
       <c r="L28" t="n">
-        <v>52431.75</v>
+        <v>52820.75</v>
       </c>
       <c r="M28" t="n">
-        <v>52690.5</v>
+        <v>53351.5</v>
       </c>
       <c r="N28" t="n">
-        <v>52949.25</v>
+        <v>53882.25</v>
       </c>
       <c r="O28" t="n">
-        <v>53407</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
+        <v>53920</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2882,83 +2886,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>52915</v>
+        <v>51759</v>
       </c>
       <c r="C29" t="n">
-        <v>53033</v>
+        <v>52484</v>
       </c>
       <c r="D29" t="n">
-        <v>51630</v>
+        <v>51732</v>
       </c>
       <c r="E29" t="n">
-        <v>51765</v>
+        <v>52380</v>
       </c>
       <c r="F29" t="n">
-        <v>-1179</v>
+        <v>615</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0119</v>
       </c>
       <c r="H29" t="n">
-        <v>1403</v>
+        <v>752</v>
       </c>
       <c r="I29" t="n">
-        <v>51475</v>
+        <v>50227</v>
       </c>
       <c r="J29" t="n">
-        <v>52252.25</v>
+        <v>50078.75</v>
       </c>
       <c r="K29" t="n">
-        <v>52536.5</v>
+        <v>51063.5</v>
       </c>
       <c r="L29" t="n">
-        <v>52820.75</v>
+        <v>52048.25</v>
       </c>
       <c r="M29" t="n">
-        <v>53351.5</v>
+        <v>52466.5</v>
       </c>
       <c r="N29" t="n">
-        <v>53882.25</v>
+        <v>52884.75</v>
       </c>
       <c r="O29" t="n">
-        <v>53920</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
+        <v>54436</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
       <c r="U29" s="8" t="n">
         <v/>
       </c>
@@ -2970,55 +2966,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>51759</v>
+        <v>52395</v>
       </c>
       <c r="C30" t="n">
-        <v>52484</v>
+        <v>52772</v>
       </c>
       <c r="D30" t="n">
-        <v>51732</v>
+        <v>52124</v>
       </c>
       <c r="E30" t="n">
-        <v>52380</v>
+        <v>52635</v>
       </c>
       <c r="F30" t="n">
-        <v>615</v>
+        <v>255</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0119</v>
+        <v>0.0049</v>
       </c>
       <c r="H30" t="n">
-        <v>752</v>
+        <v>648</v>
       </c>
       <c r="I30" t="n">
-        <v>50227</v>
+        <v>50980</v>
       </c>
       <c r="J30" t="n">
-        <v>50078.75</v>
+        <v>51764</v>
       </c>
       <c r="K30" t="n">
-        <v>51063.5</v>
+        <v>52004</v>
       </c>
       <c r="L30" t="n">
-        <v>52048.25</v>
+        <v>52244</v>
       </c>
       <c r="M30" t="n">
-        <v>52466.5</v>
+        <v>52756</v>
       </c>
       <c r="N30" t="n">
-        <v>52884.75</v>
+        <v>53268</v>
       </c>
       <c r="O30" t="n">
-        <v>54436</v>
+        <v>53236</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3052,57 +3052,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>52395</v>
+        <v>52780</v>
       </c>
       <c r="C31" t="n">
-        <v>52772</v>
+        <v>53414</v>
       </c>
       <c r="D31" t="n">
-        <v>52124</v>
+        <v>52777</v>
       </c>
       <c r="E31" t="n">
-        <v>52635</v>
+        <v>53334</v>
       </c>
       <c r="F31" t="n">
-        <v>255</v>
+        <v>699</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0133</v>
       </c>
       <c r="H31" t="n">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="I31" t="n">
-        <v>50980</v>
+        <v>51476</v>
       </c>
       <c r="J31" t="n">
-        <v>51764</v>
+        <v>52080.5</v>
       </c>
       <c r="K31" t="n">
-        <v>52004</v>
+        <v>52311</v>
       </c>
       <c r="L31" t="n">
-        <v>52244</v>
+        <v>52541.5</v>
       </c>
       <c r="M31" t="n">
-        <v>52756</v>
+        <v>52959</v>
       </c>
       <c r="N31" t="n">
-        <v>53268</v>
+        <v>53376.5</v>
       </c>
       <c r="O31" t="n">
-        <v>53236</v>
+        <v>53420</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3120,11 +3120,13 @@
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3143,50 +3145,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>52780</v>
+        <v>53381</v>
       </c>
       <c r="C32" t="n">
-        <v>53414</v>
+        <v>54423</v>
       </c>
       <c r="D32" t="n">
-        <v>52777</v>
+        <v>53267</v>
       </c>
       <c r="E32" t="n">
-        <v>53334</v>
+        <v>54268</v>
       </c>
       <c r="F32" t="n">
-        <v>699</v>
+        <v>934</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0175</v>
       </c>
       <c r="H32" t="n">
-        <v>637</v>
+        <v>1156</v>
       </c>
       <c r="I32" t="n">
-        <v>51476</v>
+        <v>52140</v>
       </c>
       <c r="J32" t="n">
-        <v>52080.5</v>
+        <v>52816.25</v>
       </c>
       <c r="K32" t="n">
-        <v>52311</v>
+        <v>53015.5</v>
       </c>
       <c r="L32" t="n">
-        <v>52541.5</v>
+        <v>53214.75</v>
       </c>
       <c r="M32" t="n">
-        <v>52959</v>
+        <v>53652.5</v>
       </c>
       <c r="N32" t="n">
-        <v>53376.5</v>
+        <v>54090.25</v>
       </c>
       <c r="O32" t="n">
-        <v>53420</v>
+        <v>54051</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3212,67 +3214,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W32" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W32" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>53381</v>
+        <v>54369</v>
       </c>
       <c r="C33" t="n">
-        <v>54423</v>
+        <v>54884</v>
       </c>
       <c r="D33" t="n">
-        <v>53267</v>
+        <v>54342</v>
       </c>
       <c r="E33" t="n">
-        <v>54268</v>
+        <v>54494</v>
       </c>
       <c r="F33" t="n">
-        <v>934</v>
+        <v>226</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0042</v>
       </c>
       <c r="H33" t="n">
-        <v>1156</v>
+        <v>542</v>
       </c>
       <c r="I33" t="n">
-        <v>52140</v>
+        <v>52111</v>
       </c>
       <c r="J33" t="n">
-        <v>52816.25</v>
+        <v>53323.5</v>
       </c>
       <c r="K33" t="n">
-        <v>53015.5</v>
+        <v>53690</v>
       </c>
       <c r="L33" t="n">
-        <v>53214.75</v>
+        <v>54056.5</v>
       </c>
       <c r="M33" t="n">
-        <v>53652.5</v>
+        <v>54846</v>
       </c>
       <c r="N33" t="n">
-        <v>54090.25</v>
+        <v>55635.5</v>
       </c>
       <c r="O33" t="n">
-        <v>54051</v>
+        <v>55579</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3290,18 +3290,14 @@
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
@@ -3313,70 +3309,72 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>54369</v>
+        <v>54555</v>
       </c>
       <c r="C34" t="n">
-        <v>54884</v>
+        <v>54678</v>
       </c>
       <c r="D34" t="n">
-        <v>54342</v>
+        <v>53952</v>
       </c>
       <c r="E34" t="n">
-        <v>54494</v>
+        <v>54013</v>
       </c>
       <c r="F34" t="n">
-        <v>226</v>
+        <v>-481</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>542</v>
+        <v>726</v>
       </c>
       <c r="I34" t="n">
-        <v>52111</v>
+        <v>53800</v>
       </c>
       <c r="J34" t="n">
-        <v>53323.5</v>
+        <v>53892.5</v>
       </c>
       <c r="K34" t="n">
-        <v>53690</v>
+        <v>54223</v>
       </c>
       <c r="L34" t="n">
-        <v>54056.5</v>
+        <v>54553.5</v>
       </c>
       <c r="M34" t="n">
-        <v>54846</v>
+        <v>54765</v>
       </c>
       <c r="N34" t="n">
-        <v>55635.5</v>
+        <v>54976.5</v>
       </c>
       <c r="O34" t="n">
-        <v>55579</v>
+        <v>55426</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
+      <c r="Q34" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
@@ -3388,72 +3386,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>54555</v>
+        <v>54040</v>
       </c>
       <c r="C35" t="n">
-        <v>54678</v>
+        <v>54202</v>
       </c>
       <c r="D35" t="n">
-        <v>53952</v>
+        <v>53879</v>
       </c>
       <c r="E35" t="n">
-        <v>54013</v>
+        <v>54152</v>
       </c>
       <c r="F35" t="n">
-        <v>-481</v>
+        <v>139</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0026</v>
       </c>
       <c r="H35" t="n">
-        <v>726</v>
+        <v>323</v>
       </c>
       <c r="I35" t="n">
-        <v>53800</v>
+        <v>53226</v>
       </c>
       <c r="J35" t="n">
-        <v>53892.5</v>
+        <v>53136</v>
       </c>
       <c r="K35" t="n">
-        <v>54223</v>
+        <v>53650</v>
       </c>
       <c r="L35" t="n">
-        <v>54553.5</v>
+        <v>54164</v>
       </c>
       <c r="M35" t="n">
-        <v>54765</v>
+        <v>54376</v>
       </c>
       <c r="N35" t="n">
-        <v>54976.5</v>
+        <v>54588</v>
       </c>
       <c r="O35" t="n">
-        <v>55426</v>
+        <v>55404</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3472,57 +3470,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>54040</v>
+        <v>54133</v>
       </c>
       <c r="C36" t="n">
-        <v>54202</v>
+        <v>54170</v>
       </c>
       <c r="D36" t="n">
-        <v>53879</v>
+        <v>53952</v>
       </c>
       <c r="E36" t="n">
-        <v>54152</v>
+        <v>54063</v>
       </c>
       <c r="F36" t="n">
-        <v>139</v>
+        <v>-89</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0016</v>
       </c>
       <c r="H36" t="n">
-        <v>323</v>
+        <v>218</v>
       </c>
       <c r="I36" t="n">
-        <v>53226</v>
+        <v>53556</v>
       </c>
       <c r="J36" t="n">
-        <v>53136</v>
+        <v>53884.75</v>
       </c>
       <c r="K36" t="n">
-        <v>53650</v>
+        <v>53990.5</v>
       </c>
       <c r="L36" t="n">
-        <v>54164</v>
+        <v>54096.25</v>
       </c>
       <c r="M36" t="n">
-        <v>54376</v>
+        <v>54313.5</v>
       </c>
       <c r="N36" t="n">
-        <v>54588</v>
+        <v>54530.75</v>
       </c>
       <c r="O36" t="n">
-        <v>55404</v>
+        <v>54525</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3530,8 +3528,10 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
@@ -3561,56 +3561,58 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>54133</v>
+        <v>54049</v>
       </c>
       <c r="C37" t="n">
-        <v>54170</v>
+        <v>54336</v>
       </c>
       <c r="D37" t="n">
-        <v>53952</v>
+        <v>53855</v>
       </c>
       <c r="E37" t="n">
-        <v>54063</v>
+        <v>53880</v>
       </c>
       <c r="F37" t="n">
-        <v>-89</v>
+        <v>-183</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0034</v>
       </c>
       <c r="H37" t="n">
-        <v>218</v>
+        <v>481</v>
       </c>
       <c r="I37" t="n">
-        <v>53556</v>
+        <v>53734</v>
       </c>
       <c r="J37" t="n">
-        <v>53884.75</v>
+        <v>53846</v>
       </c>
       <c r="K37" t="n">
-        <v>53990.5</v>
+        <v>53954</v>
       </c>
       <c r="L37" t="n">
-        <v>54096.25</v>
+        <v>54062</v>
       </c>
       <c r="M37" t="n">
-        <v>54313.5</v>
+        <v>54172</v>
       </c>
       <c r="N37" t="n">
-        <v>54530.75</v>
+        <v>54282</v>
       </c>
       <c r="O37" t="n">
-        <v>54525</v>
+        <v>54388</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
@@ -3619,14 +3621,18 @@
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3645,78 +3651,72 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>54049</v>
+        <v>53903</v>
       </c>
       <c r="C38" t="n">
-        <v>54336</v>
+        <v>54150</v>
       </c>
       <c r="D38" t="n">
-        <v>53855</v>
+        <v>53830</v>
       </c>
       <c r="E38" t="n">
-        <v>53880</v>
+        <v>53871</v>
       </c>
       <c r="F38" t="n">
-        <v>-183</v>
+        <v>-9</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0002</v>
       </c>
       <c r="H38" t="n">
-        <v>481</v>
+        <v>320</v>
       </c>
       <c r="I38" t="n">
-        <v>53734</v>
+        <v>53374</v>
       </c>
       <c r="J38" t="n">
-        <v>53846</v>
+        <v>53291.25</v>
       </c>
       <c r="K38" t="n">
-        <v>53954</v>
+        <v>53639.5</v>
       </c>
       <c r="L38" t="n">
-        <v>54062</v>
+        <v>53987.75</v>
       </c>
       <c r="M38" t="n">
-        <v>54172</v>
+        <v>54120.5</v>
       </c>
       <c r="N38" t="n">
-        <v>54282</v>
+        <v>54253.25</v>
       </c>
       <c r="O38" t="n">
-        <v>54388</v>
+        <v>54817</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3728,57 +3728,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>53903</v>
+        <v>53905</v>
       </c>
       <c r="C39" t="n">
-        <v>54150</v>
+        <v>54149</v>
       </c>
       <c r="D39" t="n">
-        <v>53830</v>
+        <v>53715</v>
       </c>
       <c r="E39" t="n">
-        <v>53871</v>
+        <v>53935</v>
       </c>
       <c r="F39" t="n">
-        <v>-9</v>
+        <v>64</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0012</v>
       </c>
       <c r="H39" t="n">
-        <v>320</v>
+        <v>434</v>
       </c>
       <c r="I39" t="n">
-        <v>53374</v>
+        <v>53510</v>
       </c>
       <c r="J39" t="n">
-        <v>53291.25</v>
+        <v>53491.5</v>
       </c>
       <c r="K39" t="n">
-        <v>53639.5</v>
+        <v>53711</v>
       </c>
       <c r="L39" t="n">
-        <v>53987.75</v>
+        <v>53930.5</v>
       </c>
       <c r="M39" t="n">
-        <v>54120.5</v>
+        <v>54031</v>
       </c>
       <c r="N39" t="n">
-        <v>54253.25</v>
+        <v>54131.5</v>
       </c>
       <c r="O39" t="n">
-        <v>54817</v>
+        <v>54470</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3789,9 +3789,9 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
@@ -3799,8 +3799,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U39" s="8" t="n">
-        <v/>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3812,57 +3814,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>53905</v>
+        <v>53961</v>
       </c>
       <c r="C40" t="n">
-        <v>54149</v>
+        <v>53999</v>
       </c>
       <c r="D40" t="n">
-        <v>53715</v>
+        <v>53745</v>
       </c>
       <c r="E40" t="n">
-        <v>53935</v>
+        <v>53807</v>
       </c>
       <c r="F40" t="n">
-        <v>64</v>
+        <v>-128</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0024</v>
       </c>
       <c r="H40" t="n">
-        <v>434</v>
+        <v>254</v>
       </c>
       <c r="I40" t="n">
-        <v>53510</v>
+        <v>53281</v>
       </c>
       <c r="J40" t="n">
-        <v>53491.5</v>
+        <v>53502.5</v>
       </c>
       <c r="K40" t="n">
-        <v>53711</v>
+        <v>53718</v>
       </c>
       <c r="L40" t="n">
-        <v>53930.5</v>
+        <v>53933.5</v>
       </c>
       <c r="M40" t="n">
-        <v>54031</v>
+        <v>54152</v>
       </c>
       <c r="N40" t="n">
-        <v>54131.5</v>
+        <v>54370.5</v>
       </c>
       <c r="O40" t="n">
-        <v>54470</v>
+        <v>54583</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3870,23 +3872,21 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3905,60 +3905,64 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>53961</v>
+        <v>53790</v>
       </c>
       <c r="C41" t="n">
-        <v>53999</v>
+        <v>53840</v>
       </c>
       <c r="D41" t="n">
-        <v>53745</v>
+        <v>53464</v>
       </c>
       <c r="E41" t="n">
-        <v>53807</v>
+        <v>53544</v>
       </c>
       <c r="F41" t="n">
-        <v>-128</v>
+        <v>-263</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0049</v>
       </c>
       <c r="H41" t="n">
-        <v>254</v>
+        <v>376</v>
       </c>
       <c r="I41" t="n">
-        <v>53281</v>
+        <v>53491</v>
       </c>
       <c r="J41" t="n">
-        <v>53502.5</v>
+        <v>53520.5</v>
       </c>
       <c r="K41" t="n">
-        <v>53718</v>
+        <v>53680</v>
       </c>
       <c r="L41" t="n">
-        <v>53933.5</v>
+        <v>53839.5</v>
       </c>
       <c r="M41" t="n">
-        <v>54152</v>
+        <v>53934</v>
       </c>
       <c r="N41" t="n">
-        <v>54370.5</v>
+        <v>54028.5</v>
       </c>
       <c r="O41" t="n">
-        <v>54583</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
+        <v>54253</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
@@ -3982,71 +3986,67 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>53790</v>
+        <v>53501</v>
       </c>
       <c r="C42" t="n">
-        <v>53840</v>
+        <v>53594</v>
       </c>
       <c r="D42" t="n">
-        <v>53464</v>
+        <v>53311</v>
       </c>
       <c r="E42" t="n">
-        <v>53544</v>
+        <v>53403</v>
       </c>
       <c r="F42" t="n">
-        <v>-263</v>
+        <v>-141</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0026</v>
       </c>
       <c r="H42" t="n">
-        <v>376</v>
+        <v>283</v>
       </c>
       <c r="I42" t="n">
-        <v>53491</v>
+        <v>53088</v>
       </c>
       <c r="J42" t="n">
-        <v>53520.5</v>
+        <v>53114</v>
       </c>
       <c r="K42" t="n">
-        <v>53680</v>
+        <v>53356</v>
       </c>
       <c r="L42" t="n">
-        <v>53839.5</v>
+        <v>53598</v>
       </c>
       <c r="M42" t="n">
-        <v>53934</v>
+        <v>53732</v>
       </c>
       <c r="N42" t="n">
-        <v>54028.5</v>
+        <v>53866</v>
       </c>
       <c r="O42" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
+        <v>54216</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
@@ -4077,50 +4077,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>53501</v>
+        <v>53408</v>
       </c>
       <c r="C43" t="n">
-        <v>53594</v>
+        <v>53780</v>
       </c>
       <c r="D43" t="n">
-        <v>53311</v>
+        <v>53337</v>
       </c>
       <c r="E43" t="n">
-        <v>53403</v>
+        <v>53530</v>
       </c>
       <c r="F43" t="n">
-        <v>-141</v>
+        <v>127</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0026</v>
+        <v>0.0024</v>
       </c>
       <c r="H43" t="n">
-        <v>283</v>
+        <v>443</v>
       </c>
       <c r="I43" t="n">
-        <v>53088</v>
+        <v>53028</v>
       </c>
       <c r="J43" t="n">
-        <v>53114</v>
+        <v>53095.25</v>
       </c>
       <c r="K43" t="n">
-        <v>53356</v>
+        <v>53261.5</v>
       </c>
       <c r="L43" t="n">
-        <v>53598</v>
+        <v>53427.75</v>
       </c>
       <c r="M43" t="n">
-        <v>53732</v>
+        <v>53544.5</v>
       </c>
       <c r="N43" t="n">
-        <v>53866</v>
+        <v>53661.25</v>
       </c>
       <c r="O43" t="n">
-        <v>54216</v>
+        <v>53877</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4128,21 +4128,23 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4152,90 +4154,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>53408</v>
+        <v>53529</v>
       </c>
       <c r="C44" t="n">
-        <v>53780</v>
+        <v>53589</v>
       </c>
       <c r="D44" t="n">
-        <v>53337</v>
+        <v>52812</v>
       </c>
       <c r="E44" t="n">
-        <v>53530</v>
+        <v>52849</v>
       </c>
       <c r="F44" t="n">
-        <v>127</v>
+        <v>-681</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0127</v>
       </c>
       <c r="H44" t="n">
-        <v>443</v>
+        <v>777</v>
       </c>
       <c r="I44" t="n">
-        <v>53028</v>
+        <v>52894</v>
       </c>
       <c r="J44" t="n">
-        <v>53095.25</v>
+        <v>53072.75</v>
       </c>
       <c r="K44" t="n">
-        <v>53261.5</v>
+        <v>53308.5</v>
       </c>
       <c r="L44" t="n">
-        <v>53427.75</v>
+        <v>53544.25</v>
       </c>
       <c r="M44" t="n">
-        <v>53544.5</v>
+        <v>53751.5</v>
       </c>
       <c r="N44" t="n">
-        <v>53661.25</v>
+        <v>53958.75</v>
       </c>
       <c r="O44" t="n">
-        <v>53877</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
+        <v>54223</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U44" s="8" t="inlineStr">
+      <c r="Q44" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W44" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X44" t="inlineStr"/>
@@ -4243,77 +4243,75 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>53529</v>
+        <v>52876</v>
       </c>
       <c r="C45" t="n">
-        <v>53589</v>
+        <v>53418</v>
       </c>
       <c r="D45" t="n">
-        <v>52812</v>
+        <v>52838</v>
       </c>
       <c r="E45" t="n">
-        <v>52849</v>
+        <v>53353</v>
       </c>
       <c r="F45" t="n">
-        <v>-681</v>
+        <v>504</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0095</v>
       </c>
       <c r="H45" t="n">
-        <v>777</v>
+        <v>580</v>
       </c>
       <c r="I45" t="n">
-        <v>52894</v>
+        <v>52035</v>
       </c>
       <c r="J45" t="n">
-        <v>53072.75</v>
+        <v>51896.25</v>
       </c>
       <c r="K45" t="n">
-        <v>53308.5</v>
+        <v>52460.5</v>
       </c>
       <c r="L45" t="n">
-        <v>53544.25</v>
+        <v>53024.75</v>
       </c>
       <c r="M45" t="n">
-        <v>53751.5</v>
+        <v>53237.5</v>
       </c>
       <c r="N45" t="n">
-        <v>53958.75</v>
+        <v>53450.25</v>
       </c>
       <c r="O45" t="n">
-        <v>54223</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
+        <v>54366</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
@@ -4322,55 +4320,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>52876</v>
+        <v>53367</v>
       </c>
       <c r="C46" t="n">
-        <v>53418</v>
+        <v>53567</v>
       </c>
       <c r="D46" t="n">
-        <v>52838</v>
+        <v>53210</v>
       </c>
       <c r="E46" t="n">
-        <v>53353</v>
+        <v>53489</v>
       </c>
       <c r="F46" t="n">
-        <v>504</v>
+        <v>136</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.0025</v>
       </c>
       <c r="H46" t="n">
-        <v>580</v>
+        <v>357</v>
       </c>
       <c r="I46" t="n">
-        <v>52035</v>
+        <v>52258</v>
       </c>
       <c r="J46" t="n">
-        <v>51896.25</v>
+        <v>52885.5</v>
       </c>
       <c r="K46" t="n">
-        <v>52460.5</v>
+        <v>53063</v>
       </c>
       <c r="L46" t="n">
-        <v>53024.75</v>
+        <v>53240.5</v>
       </c>
       <c r="M46" t="n">
-        <v>53237.5</v>
+        <v>53643</v>
       </c>
       <c r="N46" t="n">
-        <v>53450.25</v>
+        <v>54045.5</v>
       </c>
       <c r="O46" t="n">
-        <v>54366</v>
+        <v>53998</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4388,14 +4390,12 @@
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
@@ -4406,57 +4406,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>53367</v>
+        <v>53524</v>
       </c>
       <c r="C47" t="n">
-        <v>53567</v>
+        <v>53797</v>
       </c>
       <c r="D47" t="n">
-        <v>53210</v>
+        <v>53426</v>
       </c>
       <c r="E47" t="n">
-        <v>53489</v>
+        <v>53645</v>
       </c>
       <c r="F47" t="n">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0029</v>
       </c>
       <c r="H47" t="n">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="I47" t="n">
-        <v>52258</v>
+        <v>52853</v>
       </c>
       <c r="J47" t="n">
-        <v>52885.5</v>
+        <v>53182.25</v>
       </c>
       <c r="K47" t="n">
-        <v>53063</v>
+        <v>53310.5</v>
       </c>
       <c r="L47" t="n">
-        <v>53240.5</v>
+        <v>53438.75</v>
       </c>
       <c r="M47" t="n">
-        <v>53643</v>
+        <v>53667.5</v>
       </c>
       <c r="N47" t="n">
-        <v>54045.5</v>
+        <v>53896.25</v>
       </c>
       <c r="O47" t="n">
-        <v>53998</v>
+        <v>53924</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4497,50 +4497,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>53524</v>
+        <v>53643</v>
       </c>
       <c r="C48" t="n">
-        <v>53797</v>
+        <v>53778</v>
       </c>
       <c r="D48" t="n">
-        <v>53426</v>
+        <v>53435</v>
       </c>
       <c r="E48" t="n">
-        <v>53645</v>
+        <v>53521</v>
       </c>
       <c r="F48" t="n">
-        <v>156</v>
+        <v>-124</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0023</v>
       </c>
       <c r="H48" t="n">
-        <v>371</v>
+        <v>343</v>
       </c>
       <c r="I48" t="n">
-        <v>52853</v>
+        <v>53055</v>
       </c>
       <c r="J48" t="n">
-        <v>53182.25</v>
+        <v>53290.75</v>
       </c>
       <c r="K48" t="n">
-        <v>53310.5</v>
+        <v>53459.5</v>
       </c>
       <c r="L48" t="n">
-        <v>53438.75</v>
+        <v>53628.25</v>
       </c>
       <c r="M48" t="n">
-        <v>53667.5</v>
+        <v>53830.5</v>
       </c>
       <c r="N48" t="n">
-        <v>53896.25</v>
+        <v>54032.75</v>
       </c>
       <c r="O48" t="n">
-        <v>53924</v>
+        <v>54168</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4548,19 +4548,19 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
+      <c r="R48" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
       <c r="U48" s="8" t="n">
         <v/>
       </c>
@@ -4574,57 +4574,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>53643</v>
+        <v>53724</v>
       </c>
       <c r="C49" t="n">
-        <v>53778</v>
+        <v>53811</v>
       </c>
       <c r="D49" t="n">
-        <v>53435</v>
+        <v>53369</v>
       </c>
       <c r="E49" t="n">
-        <v>53521</v>
+        <v>53621</v>
       </c>
       <c r="F49" t="n">
-        <v>-124</v>
+        <v>100</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0019</v>
       </c>
       <c r="H49" t="n">
-        <v>343</v>
+        <v>442</v>
       </c>
       <c r="I49" t="n">
-        <v>53055</v>
+        <v>53092</v>
       </c>
       <c r="J49" t="n">
-        <v>53290.75</v>
+        <v>53135.25</v>
       </c>
       <c r="K49" t="n">
-        <v>53459.5</v>
+        <v>53349.5</v>
       </c>
       <c r="L49" t="n">
-        <v>53628.25</v>
+        <v>53563.75</v>
       </c>
       <c r="M49" t="n">
-        <v>53830.5</v>
+        <v>53692.5</v>
       </c>
       <c r="N49" t="n">
-        <v>54032.75</v>
+        <v>53821.25</v>
       </c>
       <c r="O49" t="n">
-        <v>54168</v>
+        <v>54121</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4632,18 +4632,18 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4658,57 +4658,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>53724</v>
+        <v>53608</v>
       </c>
       <c r="C50" t="n">
-        <v>53811</v>
+        <v>53862</v>
       </c>
       <c r="D50" t="n">
-        <v>53369</v>
+        <v>53513</v>
       </c>
       <c r="E50" t="n">
-        <v>53621</v>
+        <v>53584</v>
       </c>
       <c r="F50" t="n">
-        <v>100</v>
+        <v>-37</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0007</v>
       </c>
       <c r="H50" t="n">
-        <v>442</v>
+        <v>349</v>
       </c>
       <c r="I50" t="n">
-        <v>53092</v>
+        <v>52927</v>
       </c>
       <c r="J50" t="n">
-        <v>53135.25</v>
+        <v>53194.5</v>
       </c>
       <c r="K50" t="n">
-        <v>53349.5</v>
+        <v>53400</v>
       </c>
       <c r="L50" t="n">
-        <v>53563.75</v>
+        <v>53605.5</v>
       </c>
       <c r="M50" t="n">
-        <v>53692.5</v>
+        <v>53842</v>
       </c>
       <c r="N50" t="n">
-        <v>53821.25</v>
+        <v>54078.5</v>
       </c>
       <c r="O50" t="n">
-        <v>54121</v>
+        <v>54253</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4719,9 +4719,9 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
@@ -4749,69 +4749,73 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>53608</v>
+        <v>53664</v>
       </c>
       <c r="C51" t="n">
-        <v>53862</v>
+        <v>53664</v>
       </c>
       <c r="D51" t="n">
-        <v>53513</v>
+        <v>53149</v>
       </c>
       <c r="E51" t="n">
-        <v>53584</v>
+        <v>53240</v>
       </c>
       <c r="F51" t="n">
-        <v>-37</v>
+        <v>-344</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0064</v>
       </c>
       <c r="H51" t="n">
-        <v>349</v>
+        <v>515</v>
       </c>
       <c r="I51" t="n">
-        <v>52927</v>
+        <v>53164</v>
       </c>
       <c r="J51" t="n">
-        <v>53194.5</v>
+        <v>53183.25</v>
       </c>
       <c r="K51" t="n">
-        <v>53400</v>
+        <v>53409.5</v>
       </c>
       <c r="L51" t="n">
-        <v>53605.5</v>
+        <v>53635.75</v>
       </c>
       <c r="M51" t="n">
-        <v>53842</v>
+        <v>53758.5</v>
       </c>
       <c r="N51" t="n">
-        <v>54078.5</v>
+        <v>53881.25</v>
       </c>
       <c r="O51" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+        <v>54211</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4824,73 +4828,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>53664</v>
+        <v>53259</v>
       </c>
       <c r="C52" t="n">
-        <v>53664</v>
+        <v>53343</v>
       </c>
       <c r="D52" t="n">
-        <v>53149</v>
+        <v>52747</v>
       </c>
       <c r="E52" t="n">
-        <v>53240</v>
+        <v>52828</v>
       </c>
       <c r="F52" t="n">
-        <v>-344</v>
+        <v>-412</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0064</v>
+        <v>-0.0077</v>
       </c>
       <c r="H52" t="n">
-        <v>515</v>
+        <v>596</v>
       </c>
       <c r="I52" t="n">
-        <v>53164</v>
+        <v>52634</v>
       </c>
       <c r="J52" t="n">
-        <v>53183.25</v>
+        <v>52641.75</v>
       </c>
       <c r="K52" t="n">
-        <v>53409.5</v>
+        <v>52982.5</v>
       </c>
       <c r="L52" t="n">
-        <v>53635.75</v>
+        <v>53323.25</v>
       </c>
       <c r="M52" t="n">
-        <v>53758.5</v>
+        <v>53497.5</v>
       </c>
       <c r="N52" t="n">
-        <v>53881.25</v>
+        <v>53671.75</v>
       </c>
       <c r="O52" t="n">
-        <v>54211</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q52" s="6" t="inlineStr">
+        <v>54179</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
@@ -4917,50 +4913,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>53259</v>
+        <v>52844</v>
       </c>
       <c r="C53" t="n">
-        <v>53343</v>
+        <v>53283</v>
       </c>
       <c r="D53" t="n">
-        <v>52747</v>
+        <v>52720</v>
       </c>
       <c r="E53" t="n">
-        <v>52828</v>
+        <v>53121</v>
       </c>
       <c r="F53" t="n">
-        <v>-412</v>
+        <v>293</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0077</v>
+        <v>0.0055</v>
       </c>
       <c r="H53" t="n">
-        <v>596</v>
+        <v>563</v>
       </c>
       <c r="I53" t="n">
-        <v>52634</v>
+        <v>52151</v>
       </c>
       <c r="J53" t="n">
-        <v>52641.75</v>
+        <v>52123.5</v>
       </c>
       <c r="K53" t="n">
-        <v>52982.5</v>
+        <v>52530</v>
       </c>
       <c r="L53" t="n">
-        <v>53323.25</v>
+        <v>52936.5</v>
       </c>
       <c r="M53" t="n">
-        <v>53497.5</v>
+        <v>53126</v>
       </c>
       <c r="N53" t="n">
-        <v>53671.75</v>
+        <v>53315.5</v>
       </c>
       <c r="O53" t="n">
-        <v>54179</v>
+        <v>53939</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4968,19 +4964,19 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
       <c r="U53" s="8" t="n">
         <v/>
       </c>
@@ -4992,55 +4988,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>52844</v>
+        <v>53120</v>
       </c>
       <c r="C54" t="n">
-        <v>53283</v>
+        <v>53827</v>
       </c>
       <c r="D54" t="n">
-        <v>52720</v>
+        <v>53093</v>
       </c>
       <c r="E54" t="n">
-        <v>53121</v>
+        <v>53745</v>
       </c>
       <c r="F54" t="n">
-        <v>293</v>
+        <v>624</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0117</v>
       </c>
       <c r="H54" t="n">
-        <v>563</v>
+        <v>734</v>
       </c>
       <c r="I54" t="n">
-        <v>52151</v>
+        <v>52157</v>
       </c>
       <c r="J54" t="n">
-        <v>52123.5</v>
+        <v>52617.75</v>
       </c>
       <c r="K54" t="n">
-        <v>52530</v>
+        <v>52839.5</v>
       </c>
       <c r="L54" t="n">
-        <v>52936.5</v>
+        <v>53061.25</v>
       </c>
       <c r="M54" t="n">
-        <v>53126</v>
+        <v>53402.5</v>
       </c>
       <c r="N54" t="n">
-        <v>53315.5</v>
+        <v>53743.75</v>
       </c>
       <c r="O54" t="n">
-        <v>53939</v>
+        <v>53846</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5058,73 +5058,71 @@
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W54" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>53120</v>
+        <v>53707</v>
       </c>
       <c r="C55" t="n">
-        <v>53827</v>
+        <v>53772</v>
       </c>
       <c r="D55" t="n">
-        <v>53093</v>
+        <v>53235</v>
       </c>
       <c r="E55" t="n">
-        <v>53745</v>
+        <v>53440</v>
       </c>
       <c r="F55" t="n">
-        <v>624</v>
+        <v>-305</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0117</v>
+        <v>-0.0057</v>
       </c>
       <c r="H55" t="n">
-        <v>734</v>
+        <v>537</v>
       </c>
       <c r="I55" t="n">
-        <v>52157</v>
+        <v>52359</v>
       </c>
       <c r="J55" t="n">
-        <v>52617.75</v>
+        <v>53153.5</v>
       </c>
       <c r="K55" t="n">
-        <v>52839.5</v>
+        <v>53378</v>
       </c>
       <c r="L55" t="n">
-        <v>53061.25</v>
+        <v>53602.5</v>
       </c>
       <c r="M55" t="n">
-        <v>53402.5</v>
+        <v>54112</v>
       </c>
       <c r="N55" t="n">
-        <v>53743.75</v>
+        <v>54621.5</v>
       </c>
       <c r="O55" t="n">
-        <v>53846</v>
+        <v>54561</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5132,24 +5130,22 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
+      <c r="R55" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
@@ -5158,65 +5154,71 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>53707</v>
+        <v>53261</v>
       </c>
       <c r="C56" t="n">
-        <v>53772</v>
+        <v>53336</v>
       </c>
       <c r="D56" t="n">
-        <v>53235</v>
+        <v>52758</v>
       </c>
       <c r="E56" t="n">
-        <v>53440</v>
+        <v>52832</v>
       </c>
       <c r="F56" t="n">
-        <v>-305</v>
+        <v>-608</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0057</v>
+        <v>-0.0114</v>
       </c>
       <c r="H56" t="n">
-        <v>537</v>
+        <v>578</v>
       </c>
       <c r="I56" t="n">
-        <v>52359</v>
+        <v>52698</v>
       </c>
       <c r="J56" t="n">
-        <v>53153.5</v>
+        <v>52871.25</v>
       </c>
       <c r="K56" t="n">
-        <v>53378</v>
+        <v>53171.5</v>
       </c>
       <c r="L56" t="n">
-        <v>53602.5</v>
+        <v>53471.75</v>
       </c>
       <c r="M56" t="n">
-        <v>54112</v>
+        <v>53708.5</v>
       </c>
       <c r="N56" t="n">
-        <v>54621.5</v>
+        <v>53945.25</v>
       </c>
       <c r="O56" t="n">
-        <v>54561</v>
+        <v>54309</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
@@ -5233,76 +5235,70 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W56" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>53261</v>
+        <v>52817</v>
       </c>
       <c r="C57" t="n">
-        <v>53336</v>
+        <v>52859</v>
       </c>
       <c r="D57" t="n">
-        <v>52758</v>
+        <v>52339</v>
       </c>
       <c r="E57" t="n">
-        <v>52832</v>
+        <v>52425</v>
       </c>
       <c r="F57" t="n">
-        <v>-608</v>
+        <v>-407</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0114</v>
+        <v>-0.0077</v>
       </c>
       <c r="H57" t="n">
-        <v>578</v>
+        <v>520</v>
       </c>
       <c r="I57" t="n">
-        <v>52698</v>
+        <v>52180</v>
       </c>
       <c r="J57" t="n">
-        <v>52871.25</v>
+        <v>52146.5</v>
       </c>
       <c r="K57" t="n">
-        <v>53171.5</v>
+        <v>52543</v>
       </c>
       <c r="L57" t="n">
-        <v>53471.75</v>
+        <v>52939.5</v>
       </c>
       <c r="M57" t="n">
-        <v>53708.5</v>
+        <v>53121</v>
       </c>
       <c r="N57" t="n">
-        <v>53945.25</v>
+        <v>53302.5</v>
       </c>
       <c r="O57" t="n">
-        <v>54309</v>
+        <v>53914</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
@@ -5329,50 +5325,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>52817</v>
+        <v>52473</v>
       </c>
       <c r="C58" t="n">
-        <v>52859</v>
+        <v>52676</v>
       </c>
       <c r="D58" t="n">
-        <v>52339</v>
+        <v>51992</v>
       </c>
       <c r="E58" t="n">
-        <v>52425</v>
+        <v>52095</v>
       </c>
       <c r="F58" t="n">
-        <v>-407</v>
+        <v>-330</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0077</v>
+        <v>-0.0063</v>
       </c>
       <c r="H58" t="n">
-        <v>520</v>
+        <v>684</v>
       </c>
       <c r="I58" t="n">
-        <v>52180</v>
+        <v>51819</v>
       </c>
       <c r="J58" t="n">
-        <v>52146.5</v>
+        <v>51818</v>
       </c>
       <c r="K58" t="n">
-        <v>52543</v>
+        <v>52165</v>
       </c>
       <c r="L58" t="n">
-        <v>52939.5</v>
+        <v>52512</v>
       </c>
       <c r="M58" t="n">
-        <v>53121</v>
+        <v>52685</v>
       </c>
       <c r="N58" t="n">
-        <v>53302.5</v>
+        <v>52858</v>
       </c>
       <c r="O58" t="n">
-        <v>53914</v>
+        <v>53379</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5409,50 +5405,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>52473</v>
+        <v>52059</v>
       </c>
       <c r="C59" t="n">
-        <v>52676</v>
+        <v>52739</v>
       </c>
       <c r="D59" t="n">
-        <v>51992</v>
+        <v>52059</v>
       </c>
       <c r="E59" t="n">
-        <v>52095</v>
+        <v>52585</v>
       </c>
       <c r="F59" t="n">
-        <v>-330</v>
+        <v>490</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0063</v>
+        <v>0.0094</v>
       </c>
       <c r="H59" t="n">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="I59" t="n">
-        <v>51819</v>
+        <v>51308</v>
       </c>
       <c r="J59" t="n">
-        <v>51818</v>
+        <v>51291.5</v>
       </c>
       <c r="K59" t="n">
-        <v>52165</v>
+        <v>51753</v>
       </c>
       <c r="L59" t="n">
-        <v>52512</v>
+        <v>52214.5</v>
       </c>
       <c r="M59" t="n">
-        <v>52685</v>
+        <v>52437</v>
       </c>
       <c r="N59" t="n">
-        <v>52858</v>
+        <v>52659.5</v>
       </c>
       <c r="O59" t="n">
-        <v>53379</v>
+        <v>53360</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5460,22 +5456,24 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="inlineStr">
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U59" s="8" t="n">
-        <v/>
-      </c>
       <c r="V59" s="8" t="n">
         <v/>
       </c>
@@ -5484,55 +5482,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>52059</v>
+        <v>52376</v>
       </c>
       <c r="C60" t="n">
-        <v>52739</v>
+        <v>52672</v>
       </c>
       <c r="D60" t="n">
-        <v>52059</v>
+        <v>52226</v>
       </c>
       <c r="E60" t="n">
-        <v>52585</v>
+        <v>52440</v>
       </c>
       <c r="F60" t="n">
-        <v>490</v>
+        <v>-145</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0094</v>
+        <v>-0.0028</v>
       </c>
       <c r="H60" t="n">
-        <v>680</v>
+        <v>446</v>
       </c>
       <c r="I60" t="n">
-        <v>51308</v>
+        <v>51379</v>
       </c>
       <c r="J60" t="n">
-        <v>51291.5</v>
+        <v>51998</v>
       </c>
       <c r="K60" t="n">
-        <v>51753</v>
+        <v>52245</v>
       </c>
       <c r="L60" t="n">
-        <v>52214.5</v>
+        <v>52492</v>
       </c>
       <c r="M60" t="n">
-        <v>52437</v>
+        <v>52925</v>
       </c>
       <c r="N60" t="n">
-        <v>52659.5</v>
+        <v>53358</v>
       </c>
       <c r="O60" t="n">
-        <v>53360</v>
+        <v>53419</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5540,23 +5542,21 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
+      <c r="R60" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
@@ -5568,57 +5568,57 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>52376</v>
+        <v>52906</v>
       </c>
       <c r="C61" t="n">
-        <v>52672</v>
+        <v>52906</v>
       </c>
       <c r="D61" t="n">
-        <v>52226</v>
+        <v>52317</v>
       </c>
       <c r="E61" t="n">
-        <v>52440</v>
+        <v>52571</v>
       </c>
       <c r="F61" t="n">
-        <v>-145</v>
+        <v>131</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0028</v>
+        <v>0.0025</v>
       </c>
       <c r="H61" t="n">
-        <v>446</v>
+        <v>589</v>
       </c>
       <c r="I61" t="n">
-        <v>51379</v>
+        <v>51780</v>
       </c>
       <c r="J61" t="n">
-        <v>51998</v>
+        <v>51989.5</v>
       </c>
       <c r="K61" t="n">
-        <v>52245</v>
+        <v>52217</v>
       </c>
       <c r="L61" t="n">
-        <v>52492</v>
+        <v>52444.5</v>
       </c>
       <c r="M61" t="n">
-        <v>52925</v>
+        <v>52663</v>
       </c>
       <c r="N61" t="n">
-        <v>53358</v>
+        <v>52881.5</v>
       </c>
       <c r="O61" t="n">
-        <v>53419</v>
+        <v>53118</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5626,22 +5626,24 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
       <c r="V61" s="8" t="n">
         <v/>
       </c>
@@ -5652,122 +5654,36 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>52906</v>
-      </c>
-      <c r="C62" t="n">
-        <v>52906</v>
-      </c>
-      <c r="D62" t="n">
-        <v>52713</v>
-      </c>
-      <c r="E62" t="n">
-        <v>52713</v>
-      </c>
-      <c r="F62" t="n">
-        <v>273</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0.0052</v>
-      </c>
-      <c r="H62" t="n">
-        <v>193</v>
-      </c>
-      <c r="I62" t="n">
-        <v>51780</v>
-      </c>
-      <c r="J62" t="n">
-        <v>51989.5</v>
-      </c>
-      <c r="K62" t="n">
-        <v>52217</v>
-      </c>
-      <c r="L62" t="n">
-        <v>52444.5</v>
-      </c>
-      <c r="M62" t="n">
-        <v>52663</v>
-      </c>
-      <c r="N62" t="n">
-        <v>52881.5</v>
-      </c>
-      <c r="O62" t="n">
-        <v>53118</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I63" s="13" t="n">
-        <v>52520</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>52471.75</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>52616.5</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>52761.25</v>
-      </c>
-      <c r="M63" s="13" t="n">
-        <v>52809.5</v>
-      </c>
-      <c r="N63" s="13" t="n">
-        <v>52857.75</v>
-      </c>
-      <c r="O63" s="13" t="n">
-        <v>53099</v>
+      <c r="I62" s="13" t="n">
+        <v>51728</v>
+      </c>
+      <c r="J62" s="13" t="n">
+        <v>51961.75</v>
+      </c>
+      <c r="K62" s="13" t="n">
+        <v>52276.5</v>
+      </c>
+      <c r="L62" s="13" t="n">
+        <v>52591.25</v>
+      </c>
+      <c r="M62" s="13" t="n">
+        <v>52865.5</v>
+      </c>
+      <c r="N62" s="13" t="n">
+        <v>53139.75</v>
+      </c>
+      <c r="O62" s="13" t="n">
+        <v>53495</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -5579,25 +5579,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>52906</v>
+        <v>52576</v>
       </c>
       <c r="C61" t="n">
-        <v>52906</v>
+        <v>52622</v>
       </c>
       <c r="D61" t="n">
-        <v>52317</v>
+        <v>52560</v>
       </c>
       <c r="E61" t="n">
-        <v>52571</v>
+        <v>52573</v>
       </c>
       <c r="F61" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G61" s="5" t="n">
         <v>0.0025</v>
       </c>
       <c r="H61" t="n">
-        <v>589</v>
+        <v>62</v>
       </c>
       <c r="I61" t="n">
         <v>51780</v>
@@ -5639,10 +5639,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U61" s="8" t="n">
+        <v/>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
@@ -5654,7 +5652,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -5665,25 +5663,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>51728</v>
+        <v>52498</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>51961.75</v>
+        <v>52502</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>52276.5</v>
+        <v>52542</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>52591.25</v>
+        <v>52582</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>52865.5</v>
+        <v>52604</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>53139.75</v>
+        <v>52626</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>53495</v>
+        <v>52684</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5579,25 +5579,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>52576</v>
+        <v>52499</v>
       </c>
       <c r="C61" t="n">
-        <v>52622</v>
+        <v>52499</v>
       </c>
       <c r="D61" t="n">
-        <v>52560</v>
+        <v>51908</v>
       </c>
       <c r="E61" t="n">
-        <v>52573</v>
+        <v>52115</v>
       </c>
       <c r="F61" t="n">
-        <v>133</v>
+        <v>-325</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0062</v>
       </c>
       <c r="H61" t="n">
-        <v>62</v>
+        <v>591</v>
       </c>
       <c r="I61" t="n">
         <v>51780</v>
@@ -5623,65 +5623,149 @@
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W61" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>52576</v>
+      </c>
+      <c r="C62" t="n">
+        <v>52678</v>
+      </c>
+      <c r="D62" t="n">
+        <v>52557</v>
+      </c>
+      <c r="E62" t="n">
+        <v>52617</v>
+      </c>
+      <c r="F62" t="n">
+        <v>502</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="H62" t="n">
+        <v>121</v>
+      </c>
+      <c r="I62" t="n">
+        <v>51317</v>
+      </c>
+      <c r="J62" t="n">
+        <v>51479.75</v>
+      </c>
+      <c r="K62" t="n">
+        <v>51819.5</v>
+      </c>
+      <c r="L62" t="n">
+        <v>52159.25</v>
+      </c>
+      <c r="M62" t="n">
+        <v>52410.5</v>
+      </c>
+      <c r="N62" t="n">
+        <v>52661.75</v>
+      </c>
+      <c r="O62" t="n">
+        <v>53090</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T61" s="8" t="inlineStr">
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W61" s="11" t="inlineStr">
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I62" s="13" t="n">
-        <v>52498</v>
-      </c>
-      <c r="J62" s="13" t="n">
-        <v>52502</v>
-      </c>
-      <c r="K62" s="13" t="n">
-        <v>52542</v>
-      </c>
-      <c r="L62" s="13" t="n">
-        <v>52582</v>
-      </c>
-      <c r="M62" s="13" t="n">
-        <v>52604</v>
-      </c>
-      <c r="N62" s="13" t="n">
-        <v>52626</v>
-      </c>
-      <c r="O62" s="13" t="n">
-        <v>52684</v>
+      <c r="I63" s="13" t="n">
+        <v>52436</v>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>52495.75</v>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>52556.5</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>52617.25</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>52677.5</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>52737.75</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>52799</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -5664,22 +5664,22 @@
         <v>52576</v>
       </c>
       <c r="C62" t="n">
-        <v>52678</v>
+        <v>52687</v>
       </c>
       <c r="D62" t="n">
-        <v>52557</v>
+        <v>52524</v>
       </c>
       <c r="E62" t="n">
-        <v>52617</v>
+        <v>52644</v>
       </c>
       <c r="F62" t="n">
-        <v>502</v>
+        <v>529</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.0102</v>
       </c>
       <c r="H62" t="n">
-        <v>121</v>
+        <v>163</v>
       </c>
       <c r="I62" t="n">
         <v>51317</v>
@@ -5747,25 +5747,25 @@
         </is>
       </c>
       <c r="I63" s="13" t="n">
-        <v>52436</v>
+        <v>52361</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>52495.75</v>
+        <v>52500.25</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>52556.5</v>
+        <v>52562.5</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>52617.25</v>
+        <v>52624.75</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>52677.5</v>
+        <v>52725.5</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>52737.75</v>
+        <v>52826.25</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>52799</v>
+        <v>52850</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -5664,22 +5664,22 @@
         <v>52576</v>
       </c>
       <c r="C62" t="n">
-        <v>52687</v>
+        <v>52697</v>
       </c>
       <c r="D62" t="n">
         <v>52524</v>
       </c>
       <c r="E62" t="n">
-        <v>52644</v>
+        <v>52695</v>
       </c>
       <c r="F62" t="n">
-        <v>529</v>
+        <v>580</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0111</v>
       </c>
       <c r="H62" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="I62" t="n">
         <v>51317</v>
@@ -5729,16 +5729,12 @@
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W62" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
@@ -5747,25 +5743,25 @@
         </is>
       </c>
       <c r="I63" s="13" t="n">
-        <v>52361</v>
+        <v>52351</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>52500.25</v>
+        <v>52564.25</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>52562.5</v>
+        <v>52608.5</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>52624.75</v>
+        <v>52652.75</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>52725.5</v>
+        <v>52781.5</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>52826.25</v>
+        <v>52910.25</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>52850</v>
+        <v>52870</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -5664,22 +5664,22 @@
         <v>52576</v>
       </c>
       <c r="C62" t="n">
-        <v>52697</v>
+        <v>52709</v>
       </c>
       <c r="D62" t="n">
         <v>52524</v>
       </c>
       <c r="E62" t="n">
-        <v>52695</v>
+        <v>52693</v>
       </c>
       <c r="F62" t="n">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="G62" s="5" t="n">
         <v>0.0111</v>
       </c>
       <c r="H62" t="n">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="I62" t="n">
         <v>51317</v>
@@ -5743,25 +5743,25 @@
         </is>
       </c>
       <c r="I63" s="13" t="n">
-        <v>52351</v>
+        <v>52339</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>52564.25</v>
+        <v>52546.25</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>52608.5</v>
+        <v>52600.5</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>52652.75</v>
+        <v>52654.75</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>52781.5</v>
+        <v>52785.5</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>52910.25</v>
+        <v>52916.25</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>52870</v>
+        <v>52894</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51870</v>
+        <v>52165</v>
       </c>
       <c r="C2" t="n">
-        <v>52305</v>
+        <v>52281</v>
       </c>
       <c r="D2" t="n">
-        <v>51712</v>
+        <v>51691</v>
       </c>
       <c r="E2" t="n">
-        <v>52119</v>
+        <v>52082</v>
       </c>
       <c r="F2" t="n">
-        <v>157</v>
+        <v>-37</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.0007</v>
       </c>
       <c r="H2" t="n">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="I2" t="n">
-        <v>51212</v>
+        <v>51119</v>
       </c>
       <c r="J2" t="n">
-        <v>51680.75</v>
+        <v>51581.25</v>
       </c>
       <c r="K2" t="n">
-        <v>51774.5</v>
+        <v>51822.5</v>
       </c>
       <c r="L2" t="n">
-        <v>51868.25</v>
+        <v>52063.75</v>
       </c>
       <c r="M2" t="n">
-        <v>52149.5</v>
+        <v>52415.5</v>
       </c>
       <c r="N2" t="n">
-        <v>52430.75</v>
+        <v>52767.25</v>
       </c>
       <c r="O2" t="n">
-        <v>52337</v>
+        <v>52898</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -699,13 +699,11 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -718,55 +716,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>52165</v>
+        <v>52119</v>
       </c>
       <c r="C3" t="n">
-        <v>52281</v>
+        <v>52676</v>
       </c>
       <c r="D3" t="n">
-        <v>51691</v>
+        <v>51933</v>
       </c>
       <c r="E3" t="n">
-        <v>52082</v>
+        <v>52279</v>
       </c>
       <c r="F3" t="n">
-        <v>-37</v>
+        <v>197</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0007</v>
+        <v>0.0038</v>
       </c>
       <c r="H3" t="n">
-        <v>590</v>
+        <v>743</v>
       </c>
       <c r="I3" t="n">
-        <v>51119</v>
+        <v>51101</v>
       </c>
       <c r="J3" t="n">
-        <v>51581.25</v>
+        <v>51540</v>
       </c>
       <c r="K3" t="n">
-        <v>51822.5</v>
+        <v>51787</v>
       </c>
       <c r="L3" t="n">
-        <v>52063.75</v>
+        <v>52034</v>
       </c>
       <c r="M3" t="n">
-        <v>52415.5</v>
+        <v>52377</v>
       </c>
       <c r="N3" t="n">
-        <v>52767.25</v>
+        <v>52720</v>
       </c>
       <c r="O3" t="n">
-        <v>52898</v>
+        <v>52871</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -774,18 +776,18 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R3" s="6" t="n">
+        <v/>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -798,59 +800,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>52119</v>
+        <v>52381</v>
       </c>
       <c r="C4" t="n">
-        <v>52676</v>
+        <v>53097</v>
       </c>
       <c r="D4" t="n">
-        <v>51933</v>
+        <v>52215</v>
       </c>
       <c r="E4" t="n">
-        <v>52279</v>
+        <v>52339</v>
       </c>
       <c r="F4" t="n">
-        <v>197</v>
+        <v>60</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.0011</v>
       </c>
       <c r="H4" t="n">
-        <v>743</v>
+        <v>882</v>
       </c>
       <c r="I4" t="n">
-        <v>51101</v>
+        <v>51190</v>
       </c>
       <c r="J4" t="n">
-        <v>51540</v>
+        <v>51523.25</v>
       </c>
       <c r="K4" t="n">
-        <v>51787</v>
+        <v>51907.5</v>
       </c>
       <c r="L4" t="n">
-        <v>52034</v>
+        <v>52291.75</v>
       </c>
       <c r="M4" t="n">
-        <v>52377</v>
+        <v>52650.5</v>
       </c>
       <c r="N4" t="n">
-        <v>52720</v>
+        <v>53009.25</v>
       </c>
       <c r="O4" t="n">
-        <v>52871</v>
+        <v>53419</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -863,16 +861,18 @@
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
@@ -887,50 +887,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52381</v>
+        <v>52439</v>
       </c>
       <c r="C5" t="n">
-        <v>53097</v>
+        <v>52542</v>
       </c>
       <c r="D5" t="n">
-        <v>52215</v>
+        <v>52008</v>
       </c>
       <c r="E5" t="n">
-        <v>52339</v>
+        <v>52209</v>
       </c>
       <c r="F5" t="n">
-        <v>60</v>
+        <v>-130</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0011</v>
+        <v>-0.0025</v>
       </c>
       <c r="H5" t="n">
-        <v>882</v>
+        <v>534</v>
       </c>
       <c r="I5" t="n">
-        <v>51190</v>
+        <v>51333</v>
       </c>
       <c r="J5" t="n">
-        <v>51523.25</v>
+        <v>51298.5</v>
       </c>
       <c r="K5" t="n">
-        <v>51907.5</v>
+        <v>51898</v>
       </c>
       <c r="L5" t="n">
-        <v>52291.75</v>
+        <v>52497.5</v>
       </c>
       <c r="M5" t="n">
-        <v>52650.5</v>
+        <v>52780</v>
       </c>
       <c r="N5" t="n">
-        <v>53009.25</v>
+        <v>53062.5</v>
       </c>
       <c r="O5" t="n">
-        <v>53419</v>
+        <v>53979</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -941,20 +941,16 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -964,55 +960,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52439</v>
+        <v>52183</v>
       </c>
       <c r="C6" t="n">
-        <v>52542</v>
+        <v>52700</v>
       </c>
       <c r="D6" t="n">
-        <v>52008</v>
+        <v>52179</v>
       </c>
       <c r="E6" t="n">
-        <v>52209</v>
+        <v>52572</v>
       </c>
       <c r="F6" t="n">
-        <v>-130</v>
+        <v>363</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.007</v>
       </c>
       <c r="H6" t="n">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="I6" t="n">
-        <v>51333</v>
+        <v>51474</v>
       </c>
       <c r="J6" t="n">
-        <v>51298.5</v>
+        <v>51642</v>
       </c>
       <c r="K6" t="n">
-        <v>51898</v>
+        <v>51942</v>
       </c>
       <c r="L6" t="n">
-        <v>52497.5</v>
+        <v>52242</v>
       </c>
       <c r="M6" t="n">
-        <v>52780</v>
+        <v>52476</v>
       </c>
       <c r="N6" t="n">
-        <v>53062.5</v>
+        <v>52710</v>
       </c>
       <c r="O6" t="n">
-        <v>53979</v>
+        <v>53076</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1023,13 +1023,15 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1042,59 +1044,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>52183</v>
+        <v>52554</v>
       </c>
       <c r="C7" t="n">
-        <v>52700</v>
+        <v>52763</v>
       </c>
       <c r="D7" t="n">
-        <v>52179</v>
+        <v>52383</v>
       </c>
       <c r="E7" t="n">
-        <v>52572</v>
+        <v>52670</v>
       </c>
       <c r="F7" t="n">
-        <v>363</v>
+        <v>98</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.007</v>
+        <v>0.0019</v>
       </c>
       <c r="H7" t="n">
-        <v>521</v>
+        <v>380</v>
       </c>
       <c r="I7" t="n">
-        <v>51474</v>
+        <v>51658</v>
       </c>
       <c r="J7" t="n">
-        <v>51642</v>
+        <v>52117.25</v>
       </c>
       <c r="K7" t="n">
-        <v>51942</v>
+        <v>52311.5</v>
       </c>
       <c r="L7" t="n">
-        <v>52242</v>
+        <v>52505.75</v>
       </c>
       <c r="M7" t="n">
-        <v>52476</v>
+        <v>52832.5</v>
       </c>
       <c r="N7" t="n">
-        <v>52710</v>
+        <v>53159.25</v>
       </c>
       <c r="O7" t="n">
-        <v>53076</v>
+        <v>53221</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1131,50 +1129,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52554</v>
+        <v>52546</v>
       </c>
       <c r="C8" t="n">
-        <v>52763</v>
+        <v>53105</v>
       </c>
       <c r="D8" t="n">
-        <v>52383</v>
+        <v>52381</v>
       </c>
       <c r="E8" t="n">
-        <v>52670</v>
+        <v>52668</v>
       </c>
       <c r="F8" t="n">
-        <v>98</v>
+        <v>-2</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0</v>
       </c>
       <c r="H8" t="n">
-        <v>380</v>
+        <v>724</v>
       </c>
       <c r="I8" t="n">
-        <v>51658</v>
+        <v>52003</v>
       </c>
       <c r="J8" t="n">
-        <v>52117.25</v>
+        <v>52338.5</v>
       </c>
       <c r="K8" t="n">
-        <v>52311.5</v>
+        <v>52480</v>
       </c>
       <c r="L8" t="n">
-        <v>52505.75</v>
+        <v>52621.5</v>
       </c>
       <c r="M8" t="n">
-        <v>52832.5</v>
+        <v>52860</v>
       </c>
       <c r="N8" t="n">
-        <v>53159.25</v>
+        <v>53098.5</v>
       </c>
       <c r="O8" t="n">
-        <v>53221</v>
+        <v>53143</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1182,21 +1180,25 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1206,55 +1208,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52546</v>
+        <v>52640</v>
       </c>
       <c r="C9" t="n">
-        <v>53105</v>
+        <v>53218</v>
       </c>
       <c r="D9" t="n">
-        <v>52381</v>
+        <v>52551</v>
       </c>
       <c r="E9" t="n">
-        <v>52668</v>
+        <v>53183</v>
       </c>
       <c r="F9" t="n">
-        <v>-2</v>
+        <v>515</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0</v>
+        <v>0.0098</v>
       </c>
       <c r="H9" t="n">
-        <v>724</v>
+        <v>667</v>
       </c>
       <c r="I9" t="n">
-        <v>52003</v>
+        <v>51657</v>
       </c>
       <c r="J9" t="n">
-        <v>52338.5</v>
+        <v>51906.5</v>
       </c>
       <c r="K9" t="n">
-        <v>52480</v>
+        <v>52306</v>
       </c>
       <c r="L9" t="n">
-        <v>52621.5</v>
+        <v>52705.5</v>
       </c>
       <c r="M9" t="n">
-        <v>52860</v>
+        <v>53030</v>
       </c>
       <c r="N9" t="n">
-        <v>53098.5</v>
+        <v>53354.5</v>
       </c>
       <c r="O9" t="n">
-        <v>53143</v>
+        <v>53829</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1262,25 +1268,21 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R9" s="6" t="n">
+        <v/>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1290,59 +1292,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52640</v>
+        <v>53230</v>
       </c>
       <c r="C10" t="n">
-        <v>53218</v>
+        <v>53421</v>
       </c>
       <c r="D10" t="n">
-        <v>52551</v>
+        <v>52962</v>
       </c>
       <c r="E10" t="n">
-        <v>53183</v>
+        <v>53372</v>
       </c>
       <c r="F10" t="n">
-        <v>515</v>
+        <v>189</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0036</v>
       </c>
       <c r="H10" t="n">
-        <v>667</v>
+        <v>459</v>
       </c>
       <c r="I10" t="n">
-        <v>51657</v>
+        <v>51884</v>
       </c>
       <c r="J10" t="n">
-        <v>51906.5</v>
+        <v>52665.25</v>
       </c>
       <c r="K10" t="n">
-        <v>52306</v>
+        <v>52849.5</v>
       </c>
       <c r="L10" t="n">
-        <v>52705.5</v>
+        <v>53033.75</v>
       </c>
       <c r="M10" t="n">
-        <v>53030</v>
+        <v>53516.5</v>
       </c>
       <c r="N10" t="n">
-        <v>53354.5</v>
+        <v>53999.25</v>
       </c>
       <c r="O10" t="n">
-        <v>53829</v>
+        <v>53885</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1379,50 +1377,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>53230</v>
+        <v>53405</v>
       </c>
       <c r="C11" t="n">
-        <v>53421</v>
+        <v>53656</v>
       </c>
       <c r="D11" t="n">
-        <v>52962</v>
+        <v>53076</v>
       </c>
       <c r="E11" t="n">
-        <v>53372</v>
+        <v>53197</v>
       </c>
       <c r="F11" t="n">
-        <v>189</v>
+        <v>-175</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0036</v>
+        <v>-0.0033</v>
       </c>
       <c r="H11" t="n">
-        <v>459</v>
+        <v>580</v>
       </c>
       <c r="I11" t="n">
-        <v>51884</v>
+        <v>52503</v>
       </c>
       <c r="J11" t="n">
-        <v>52665.25</v>
+        <v>53003.25</v>
       </c>
       <c r="K11" t="n">
-        <v>52849.5</v>
+        <v>53142.5</v>
       </c>
       <c r="L11" t="n">
-        <v>53033.75</v>
+        <v>53281.75</v>
       </c>
       <c r="M11" t="n">
-        <v>53516.5</v>
+        <v>53601.5</v>
       </c>
       <c r="N11" t="n">
-        <v>53999.25</v>
+        <v>53921.25</v>
       </c>
       <c r="O11" t="n">
-        <v>53885</v>
+        <v>53880</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1430,17 +1428,19 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U11" s="8" t="n">
@@ -1454,65 +1454,73 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>53405</v>
+        <v>53166</v>
       </c>
       <c r="C12" t="n">
-        <v>53656</v>
+        <v>53207</v>
       </c>
       <c r="D12" t="n">
-        <v>53076</v>
+        <v>52343</v>
       </c>
       <c r="E12" t="n">
-        <v>53197</v>
+        <v>52624</v>
       </c>
       <c r="F12" t="n">
-        <v>-175</v>
+        <v>-573</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0108</v>
       </c>
       <c r="H12" t="n">
-        <v>580</v>
+        <v>864</v>
       </c>
       <c r="I12" t="n">
-        <v>52503</v>
+        <v>52496</v>
       </c>
       <c r="J12" t="n">
-        <v>53003.25</v>
+        <v>52532.5</v>
       </c>
       <c r="K12" t="n">
-        <v>53142.5</v>
+        <v>52907</v>
       </c>
       <c r="L12" t="n">
-        <v>53281.75</v>
+        <v>53281.5</v>
       </c>
       <c r="M12" t="n">
-        <v>53601.5</v>
+        <v>53487</v>
       </c>
       <c r="N12" t="n">
-        <v>53921.25</v>
+        <v>53692.5</v>
       </c>
       <c r="O12" t="n">
-        <v>53880</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
+        <v>54236</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
@@ -1520,10 +1528,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1538,76 +1544,70 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>53166</v>
+        <v>52541</v>
       </c>
       <c r="C13" t="n">
-        <v>53207</v>
+        <v>52865</v>
       </c>
       <c r="D13" t="n">
-        <v>52343</v>
+        <v>52501</v>
       </c>
       <c r="E13" t="n">
-        <v>52624</v>
+        <v>52761</v>
       </c>
       <c r="F13" t="n">
-        <v>-573</v>
+        <v>137</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0108</v>
+        <v>0.0026</v>
       </c>
       <c r="H13" t="n">
-        <v>864</v>
+        <v>364</v>
       </c>
       <c r="I13" t="n">
-        <v>52496</v>
+        <v>51479</v>
       </c>
       <c r="J13" t="n">
-        <v>52532.5</v>
+        <v>51684.5</v>
       </c>
       <c r="K13" t="n">
-        <v>52907</v>
+        <v>52192</v>
       </c>
       <c r="L13" t="n">
-        <v>53281.5</v>
+        <v>52699.5</v>
       </c>
       <c r="M13" t="n">
-        <v>53487</v>
+        <v>53056</v>
       </c>
       <c r="N13" t="n">
-        <v>53692.5</v>
+        <v>53412.5</v>
       </c>
       <c r="O13" t="n">
-        <v>54236</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>54071</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1626,57 +1626,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>52541</v>
+        <v>52753</v>
       </c>
       <c r="C14" t="n">
-        <v>52865</v>
+        <v>52992</v>
       </c>
       <c r="D14" t="n">
-        <v>52501</v>
+        <v>52506</v>
       </c>
       <c r="E14" t="n">
-        <v>52761</v>
+        <v>52906</v>
       </c>
       <c r="F14" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0027</v>
       </c>
       <c r="H14" t="n">
-        <v>364</v>
+        <v>486</v>
       </c>
       <c r="I14" t="n">
-        <v>51479</v>
+        <v>52137</v>
       </c>
       <c r="J14" t="n">
-        <v>51684.5</v>
+        <v>52436</v>
       </c>
       <c r="K14" t="n">
-        <v>52192</v>
+        <v>52579</v>
       </c>
       <c r="L14" t="n">
-        <v>52699.5</v>
+        <v>52722</v>
       </c>
       <c r="M14" t="n">
-        <v>53056</v>
+        <v>52943</v>
       </c>
       <c r="N14" t="n">
-        <v>53412.5</v>
+        <v>53164</v>
       </c>
       <c r="O14" t="n">
-        <v>54071</v>
+        <v>53229</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1684,16 +1684,20 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1706,59 +1710,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52753</v>
+        <v>52844</v>
       </c>
       <c r="C15" t="n">
-        <v>52992</v>
+        <v>53113</v>
       </c>
       <c r="D15" t="n">
-        <v>52506</v>
+        <v>52603</v>
       </c>
       <c r="E15" t="n">
-        <v>52906</v>
+        <v>52764</v>
       </c>
       <c r="F15" t="n">
-        <v>145</v>
+        <v>-142</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0027</v>
       </c>
       <c r="H15" t="n">
-        <v>486</v>
+        <v>510</v>
       </c>
       <c r="I15" t="n">
-        <v>52137</v>
+        <v>52020</v>
       </c>
       <c r="J15" t="n">
-        <v>52436</v>
+        <v>52498.5</v>
       </c>
       <c r="K15" t="n">
-        <v>52579</v>
+        <v>52663</v>
       </c>
       <c r="L15" t="n">
-        <v>52722</v>
+        <v>52827.5</v>
       </c>
       <c r="M15" t="n">
-        <v>52943</v>
+        <v>53149</v>
       </c>
       <c r="N15" t="n">
-        <v>53164</v>
+        <v>53470.5</v>
       </c>
       <c r="O15" t="n">
-        <v>53229</v>
+        <v>53478</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1771,15 +1771,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1792,55 +1790,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>52844</v>
+        <v>52731</v>
       </c>
       <c r="C16" t="n">
-        <v>53113</v>
+        <v>52981</v>
       </c>
       <c r="D16" t="n">
-        <v>52603</v>
+        <v>52255</v>
       </c>
       <c r="E16" t="n">
-        <v>52764</v>
+        <v>52791</v>
       </c>
       <c r="F16" t="n">
-        <v>-142</v>
+        <v>27</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0005</v>
       </c>
       <c r="H16" t="n">
-        <v>510</v>
+        <v>726</v>
       </c>
       <c r="I16" t="n">
-        <v>52020</v>
+        <v>52093</v>
       </c>
       <c r="J16" t="n">
-        <v>52498.5</v>
+        <v>52207</v>
       </c>
       <c r="K16" t="n">
-        <v>52663</v>
+        <v>52509</v>
       </c>
       <c r="L16" t="n">
-        <v>52827.5</v>
+        <v>52811</v>
       </c>
       <c r="M16" t="n">
-        <v>53149</v>
+        <v>53019</v>
       </c>
       <c r="N16" t="n">
-        <v>53470.5</v>
+        <v>53227</v>
       </c>
       <c r="O16" t="n">
-        <v>53478</v>
+        <v>53623</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1874,57 +1876,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52731</v>
+        <v>52792</v>
       </c>
       <c r="C17" t="n">
-        <v>52981</v>
+        <v>53088</v>
       </c>
       <c r="D17" t="n">
-        <v>52255</v>
+        <v>52680</v>
       </c>
       <c r="E17" t="n">
-        <v>52791</v>
+        <v>52900</v>
       </c>
       <c r="F17" t="n">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0021</v>
       </c>
       <c r="H17" t="n">
-        <v>726</v>
+        <v>408</v>
       </c>
       <c r="I17" t="n">
-        <v>52093</v>
+        <v>51529</v>
       </c>
       <c r="J17" t="n">
-        <v>52207</v>
+        <v>52151.5</v>
       </c>
       <c r="K17" t="n">
-        <v>52509</v>
+        <v>52428</v>
       </c>
       <c r="L17" t="n">
-        <v>52811</v>
+        <v>52704.5</v>
       </c>
       <c r="M17" t="n">
-        <v>53019</v>
+        <v>53154</v>
       </c>
       <c r="N17" t="n">
-        <v>53227</v>
+        <v>53603.5</v>
       </c>
       <c r="O17" t="n">
-        <v>53623</v>
+        <v>53707</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1932,14 +1934,12 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1956,59 +1956,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52792</v>
+        <v>52919</v>
       </c>
       <c r="C18" t="n">
-        <v>53088</v>
+        <v>53108</v>
       </c>
       <c r="D18" t="n">
-        <v>52680</v>
+        <v>52607</v>
       </c>
       <c r="E18" t="n">
-        <v>52900</v>
+        <v>52786</v>
       </c>
       <c r="F18" t="n">
-        <v>109</v>
+        <v>-114</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0022</v>
       </c>
       <c r="H18" t="n">
-        <v>408</v>
+        <v>501</v>
       </c>
       <c r="I18" t="n">
-        <v>51529</v>
+        <v>52272</v>
       </c>
       <c r="J18" t="n">
-        <v>52151.5</v>
+        <v>52500</v>
       </c>
       <c r="K18" t="n">
-        <v>52428</v>
+        <v>52696</v>
       </c>
       <c r="L18" t="n">
-        <v>52704.5</v>
+        <v>52892</v>
       </c>
       <c r="M18" t="n">
-        <v>53154</v>
+        <v>53104</v>
       </c>
       <c r="N18" t="n">
-        <v>53603.5</v>
+        <v>53316</v>
       </c>
       <c r="O18" t="n">
-        <v>53707</v>
+        <v>53496</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2016,16 +2012,20 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2038,65 +2038,71 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>52919</v>
+        <v>52778</v>
       </c>
       <c r="C19" t="n">
-        <v>53108</v>
+        <v>52835</v>
       </c>
       <c r="D19" t="n">
-        <v>52607</v>
+        <v>52174</v>
       </c>
       <c r="E19" t="n">
-        <v>52786</v>
+        <v>52375</v>
       </c>
       <c r="F19" t="n">
-        <v>-114</v>
+        <v>-411</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0078</v>
       </c>
       <c r="H19" t="n">
-        <v>501</v>
+        <v>661</v>
       </c>
       <c r="I19" t="n">
-        <v>52272</v>
+        <v>52106</v>
       </c>
       <c r="J19" t="n">
-        <v>52500</v>
+        <v>52249.25</v>
       </c>
       <c r="K19" t="n">
-        <v>52696</v>
+        <v>52535.5</v>
       </c>
       <c r="L19" t="n">
-        <v>52892</v>
+        <v>52821.75</v>
       </c>
       <c r="M19" t="n">
-        <v>53104</v>
+        <v>53036.5</v>
       </c>
       <c r="N19" t="n">
-        <v>53316</v>
+        <v>53251.25</v>
       </c>
       <c r="O19" t="n">
-        <v>53496</v>
+        <v>53609</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
@@ -2104,10 +2110,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2122,69 +2126,67 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>52778</v>
+        <v>52300</v>
       </c>
       <c r="C20" t="n">
-        <v>52835</v>
+        <v>52633</v>
       </c>
       <c r="D20" t="n">
-        <v>52174</v>
+        <v>51999</v>
       </c>
       <c r="E20" t="n">
-        <v>52375</v>
+        <v>52073</v>
       </c>
       <c r="F20" t="n">
-        <v>-411</v>
+        <v>-302</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0078</v>
+        <v>-0.0058</v>
       </c>
       <c r="H20" t="n">
-        <v>661</v>
+        <v>634</v>
       </c>
       <c r="I20" t="n">
-        <v>52106</v>
+        <v>51513</v>
       </c>
       <c r="J20" t="n">
-        <v>52249.25</v>
+        <v>51649.25</v>
       </c>
       <c r="K20" t="n">
-        <v>52535.5</v>
+        <v>52044.5</v>
       </c>
       <c r="L20" t="n">
-        <v>52821.75</v>
+        <v>52439.75</v>
       </c>
       <c r="M20" t="n">
-        <v>53036.5</v>
+        <v>52705.5</v>
       </c>
       <c r="N20" t="n">
-        <v>53251.25</v>
+        <v>52971.25</v>
       </c>
       <c r="O20" t="n">
-        <v>53609</v>
+        <v>53496</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S20" s="10" t="inlineStr">
@@ -2215,50 +2217,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>52300</v>
+        <v>52091</v>
       </c>
       <c r="C21" t="n">
-        <v>52633</v>
+        <v>52590</v>
       </c>
       <c r="D21" t="n">
-        <v>51999</v>
+        <v>52035</v>
       </c>
       <c r="E21" t="n">
-        <v>52073</v>
+        <v>52443</v>
       </c>
       <c r="F21" t="n">
-        <v>-302</v>
+        <v>370</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.0071</v>
       </c>
       <c r="H21" t="n">
-        <v>634</v>
+        <v>555</v>
       </c>
       <c r="I21" t="n">
-        <v>51513</v>
+        <v>51365</v>
       </c>
       <c r="J21" t="n">
-        <v>51649.25</v>
+        <v>51317.5</v>
       </c>
       <c r="K21" t="n">
-        <v>52044.5</v>
+        <v>51756</v>
       </c>
       <c r="L21" t="n">
-        <v>52439.75</v>
+        <v>52194.5</v>
       </c>
       <c r="M21" t="n">
-        <v>52705.5</v>
+        <v>52390</v>
       </c>
       <c r="N21" t="n">
-        <v>52971.25</v>
+        <v>52585.5</v>
       </c>
       <c r="O21" t="n">
-        <v>53496</v>
+        <v>53267</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2266,21 +2268,23 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2292,57 +2296,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>52091</v>
+        <v>52431</v>
       </c>
       <c r="C22" t="n">
-        <v>52590</v>
+        <v>52721</v>
       </c>
       <c r="D22" t="n">
-        <v>52035</v>
+        <v>52262</v>
       </c>
       <c r="E22" t="n">
-        <v>52443</v>
+        <v>52449</v>
       </c>
       <c r="F22" t="n">
-        <v>370</v>
+        <v>6</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0001</v>
       </c>
       <c r="H22" t="n">
-        <v>555</v>
+        <v>459</v>
       </c>
       <c r="I22" t="n">
-        <v>51365</v>
+        <v>51480</v>
       </c>
       <c r="J22" t="n">
-        <v>51317.5</v>
+        <v>51953.25</v>
       </c>
       <c r="K22" t="n">
-        <v>51756</v>
+        <v>52165.5</v>
       </c>
       <c r="L22" t="n">
-        <v>52194.5</v>
+        <v>52377.75</v>
       </c>
       <c r="M22" t="n">
-        <v>52390</v>
+        <v>52720.5</v>
       </c>
       <c r="N22" t="n">
-        <v>52585.5</v>
+        <v>53063.25</v>
       </c>
       <c r="O22" t="n">
-        <v>53267</v>
+        <v>53145</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2355,19 +2359,17 @@
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
@@ -2376,88 +2378,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>52431</v>
+        <v>52430</v>
       </c>
       <c r="C23" t="n">
-        <v>52721</v>
+        <v>52515</v>
       </c>
       <c r="D23" t="n">
-        <v>52262</v>
+        <v>51720</v>
       </c>
       <c r="E23" t="n">
-        <v>52449</v>
+        <v>51894</v>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>-555</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0106</v>
       </c>
       <c r="H23" t="n">
-        <v>459</v>
+        <v>795</v>
       </c>
       <c r="I23" t="n">
-        <v>51480</v>
+        <v>51803</v>
       </c>
       <c r="J23" t="n">
-        <v>51953.25</v>
+        <v>51968.75</v>
       </c>
       <c r="K23" t="n">
-        <v>52165.5</v>
+        <v>52219.5</v>
       </c>
       <c r="L23" t="n">
-        <v>52377.75</v>
+        <v>52470.25</v>
       </c>
       <c r="M23" t="n">
-        <v>52720.5</v>
+        <v>52678.5</v>
       </c>
       <c r="N23" t="n">
-        <v>53063.25</v>
+        <v>52886.75</v>
       </c>
       <c r="O23" t="n">
-        <v>53145</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
+        <v>53180</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W23" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
@@ -2465,74 +2467,70 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>52430</v>
+        <v>51920</v>
       </c>
       <c r="C24" t="n">
-        <v>52515</v>
+        <v>52314</v>
       </c>
       <c r="D24" t="n">
-        <v>51720</v>
+        <v>51846</v>
       </c>
       <c r="E24" t="n">
-        <v>51894</v>
+        <v>52124</v>
       </c>
       <c r="F24" t="n">
-        <v>-555</v>
+        <v>230</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0044</v>
       </c>
       <c r="H24" t="n">
-        <v>795</v>
+        <v>468</v>
       </c>
       <c r="I24" t="n">
-        <v>51803</v>
+        <v>50925</v>
       </c>
       <c r="J24" t="n">
-        <v>51968.75</v>
+        <v>50987.25</v>
       </c>
       <c r="K24" t="n">
-        <v>52219.5</v>
+        <v>51496.5</v>
       </c>
       <c r="L24" t="n">
-        <v>52470.25</v>
+        <v>52005.75</v>
       </c>
       <c r="M24" t="n">
-        <v>52678.5</v>
+        <v>52291.5</v>
       </c>
       <c r="N24" t="n">
-        <v>52886.75</v>
+        <v>52577.25</v>
       </c>
       <c r="O24" t="n">
-        <v>53180</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
+        <v>53310</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
@@ -2544,55 +2542,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>51920</v>
+        <v>52299</v>
       </c>
       <c r="C25" t="n">
-        <v>52314</v>
+        <v>52790</v>
       </c>
       <c r="D25" t="n">
-        <v>51846</v>
+        <v>52173</v>
       </c>
       <c r="E25" t="n">
-        <v>52124</v>
+        <v>52382</v>
       </c>
       <c r="F25" t="n">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0049</v>
       </c>
       <c r="H25" t="n">
-        <v>468</v>
+        <v>617</v>
       </c>
       <c r="I25" t="n">
-        <v>50925</v>
+        <v>51378</v>
       </c>
       <c r="J25" t="n">
-        <v>50987.25</v>
+        <v>51678</v>
       </c>
       <c r="K25" t="n">
-        <v>51496.5</v>
+        <v>51890</v>
       </c>
       <c r="L25" t="n">
-        <v>52005.75</v>
+        <v>52102</v>
       </c>
       <c r="M25" t="n">
-        <v>52291.5</v>
+        <v>52358</v>
       </c>
       <c r="N25" t="n">
-        <v>52577.25</v>
+        <v>52614</v>
       </c>
       <c r="O25" t="n">
-        <v>53310</v>
+        <v>52782</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2605,19 +2607,23 @@
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v/>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W25" s="11" t="inlineStr">
         <is>
@@ -2626,57 +2632,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>52299</v>
+        <v>52405</v>
       </c>
       <c r="C26" t="n">
-        <v>52790</v>
+        <v>53105</v>
       </c>
       <c r="D26" t="n">
-        <v>52173</v>
+        <v>52290</v>
       </c>
       <c r="E26" t="n">
-        <v>52382</v>
+        <v>52944</v>
       </c>
       <c r="F26" t="n">
-        <v>258</v>
+        <v>562</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0107</v>
       </c>
       <c r="H26" t="n">
-        <v>617</v>
+        <v>815</v>
       </c>
       <c r="I26" t="n">
-        <v>51378</v>
+        <v>51556</v>
       </c>
       <c r="J26" t="n">
-        <v>51678</v>
+        <v>51715.25</v>
       </c>
       <c r="K26" t="n">
-        <v>51890</v>
+        <v>52073.5</v>
       </c>
       <c r="L26" t="n">
-        <v>52102</v>
+        <v>52431.75</v>
       </c>
       <c r="M26" t="n">
-        <v>52358</v>
+        <v>52690.5</v>
       </c>
       <c r="N26" t="n">
-        <v>52614</v>
+        <v>52949.25</v>
       </c>
       <c r="O26" t="n">
-        <v>52782</v>
+        <v>53407</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2694,18 +2700,16 @@
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V26" s="8" t="n">
+        <v/>
       </c>
       <c r="W26" s="11" t="inlineStr">
         <is>
@@ -2721,74 +2725,76 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>52405</v>
+        <v>52915</v>
       </c>
       <c r="C27" t="n">
-        <v>53105</v>
+        <v>53033</v>
       </c>
       <c r="D27" t="n">
-        <v>52290</v>
+        <v>51630</v>
       </c>
       <c r="E27" t="n">
-        <v>52944</v>
+        <v>51765</v>
       </c>
       <c r="F27" t="n">
-        <v>562</v>
+        <v>-1179</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0223</v>
       </c>
       <c r="H27" t="n">
-        <v>815</v>
+        <v>1403</v>
       </c>
       <c r="I27" t="n">
-        <v>51556</v>
+        <v>51475</v>
       </c>
       <c r="J27" t="n">
-        <v>51715.25</v>
+        <v>52252.25</v>
       </c>
       <c r="K27" t="n">
-        <v>52073.5</v>
+        <v>52536.5</v>
       </c>
       <c r="L27" t="n">
-        <v>52431.75</v>
+        <v>52820.75</v>
       </c>
       <c r="M27" t="n">
-        <v>52690.5</v>
+        <v>53351.5</v>
       </c>
       <c r="N27" t="n">
-        <v>52949.25</v>
+        <v>53882.25</v>
       </c>
       <c r="O27" t="n">
-        <v>53407</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
+        <v>53920</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2798,83 +2804,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>52915</v>
+        <v>51759</v>
       </c>
       <c r="C28" t="n">
-        <v>53033</v>
+        <v>52484</v>
       </c>
       <c r="D28" t="n">
-        <v>51630</v>
+        <v>51732</v>
       </c>
       <c r="E28" t="n">
-        <v>51765</v>
+        <v>52380</v>
       </c>
       <c r="F28" t="n">
-        <v>-1179</v>
+        <v>615</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0119</v>
       </c>
       <c r="H28" t="n">
-        <v>1403</v>
+        <v>752</v>
       </c>
       <c r="I28" t="n">
-        <v>51475</v>
+        <v>50227</v>
       </c>
       <c r="J28" t="n">
-        <v>52252.25</v>
+        <v>50078.75</v>
       </c>
       <c r="K28" t="n">
-        <v>52536.5</v>
+        <v>51063.5</v>
       </c>
       <c r="L28" t="n">
-        <v>52820.75</v>
+        <v>52048.25</v>
       </c>
       <c r="M28" t="n">
-        <v>53351.5</v>
+        <v>52466.5</v>
       </c>
       <c r="N28" t="n">
-        <v>53882.25</v>
+        <v>52884.75</v>
       </c>
       <c r="O28" t="n">
-        <v>53920</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
+        <v>54436</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
       <c r="U28" s="8" t="n">
         <v/>
       </c>
@@ -2886,55 +2884,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>51759</v>
+        <v>52395</v>
       </c>
       <c r="C29" t="n">
-        <v>52484</v>
+        <v>52772</v>
       </c>
       <c r="D29" t="n">
-        <v>51732</v>
+        <v>52124</v>
       </c>
       <c r="E29" t="n">
-        <v>52380</v>
+        <v>52635</v>
       </c>
       <c r="F29" t="n">
-        <v>615</v>
+        <v>255</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0119</v>
+        <v>0.0049</v>
       </c>
       <c r="H29" t="n">
-        <v>752</v>
+        <v>648</v>
       </c>
       <c r="I29" t="n">
-        <v>50227</v>
+        <v>50980</v>
       </c>
       <c r="J29" t="n">
-        <v>50078.75</v>
+        <v>51764</v>
       </c>
       <c r="K29" t="n">
-        <v>51063.5</v>
+        <v>52004</v>
       </c>
       <c r="L29" t="n">
-        <v>52048.25</v>
+        <v>52244</v>
       </c>
       <c r="M29" t="n">
-        <v>52466.5</v>
+        <v>52756</v>
       </c>
       <c r="N29" t="n">
-        <v>52884.75</v>
+        <v>53268</v>
       </c>
       <c r="O29" t="n">
-        <v>54436</v>
+        <v>53236</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2968,57 +2970,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>52395</v>
+        <v>52780</v>
       </c>
       <c r="C30" t="n">
-        <v>52772</v>
+        <v>53414</v>
       </c>
       <c r="D30" t="n">
-        <v>52124</v>
+        <v>52777</v>
       </c>
       <c r="E30" t="n">
-        <v>52635</v>
+        <v>53334</v>
       </c>
       <c r="F30" t="n">
-        <v>255</v>
+        <v>699</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0133</v>
       </c>
       <c r="H30" t="n">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="I30" t="n">
-        <v>50980</v>
+        <v>51476</v>
       </c>
       <c r="J30" t="n">
-        <v>51764</v>
+        <v>52080.5</v>
       </c>
       <c r="K30" t="n">
-        <v>52004</v>
+        <v>52311</v>
       </c>
       <c r="L30" t="n">
-        <v>52244</v>
+        <v>52541.5</v>
       </c>
       <c r="M30" t="n">
-        <v>52756</v>
+        <v>52959</v>
       </c>
       <c r="N30" t="n">
-        <v>53268</v>
+        <v>53376.5</v>
       </c>
       <c r="O30" t="n">
-        <v>53236</v>
+        <v>53420</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3036,11 +3038,13 @@
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3059,50 +3063,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>52780</v>
+        <v>53381</v>
       </c>
       <c r="C31" t="n">
-        <v>53414</v>
+        <v>54423</v>
       </c>
       <c r="D31" t="n">
-        <v>52777</v>
+        <v>53267</v>
       </c>
       <c r="E31" t="n">
-        <v>53334</v>
+        <v>54268</v>
       </c>
       <c r="F31" t="n">
-        <v>699</v>
+        <v>934</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0175</v>
       </c>
       <c r="H31" t="n">
-        <v>637</v>
+        <v>1156</v>
       </c>
       <c r="I31" t="n">
-        <v>51476</v>
+        <v>52140</v>
       </c>
       <c r="J31" t="n">
-        <v>52080.5</v>
+        <v>52816.25</v>
       </c>
       <c r="K31" t="n">
-        <v>52311</v>
+        <v>53015.5</v>
       </c>
       <c r="L31" t="n">
-        <v>52541.5</v>
+        <v>53214.75</v>
       </c>
       <c r="M31" t="n">
-        <v>52959</v>
+        <v>53652.5</v>
       </c>
       <c r="N31" t="n">
-        <v>53376.5</v>
+        <v>54090.25</v>
       </c>
       <c r="O31" t="n">
-        <v>53420</v>
+        <v>54051</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3128,67 +3132,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W31" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W31" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>53381</v>
+        <v>54369</v>
       </c>
       <c r="C32" t="n">
-        <v>54423</v>
+        <v>54884</v>
       </c>
       <c r="D32" t="n">
-        <v>53267</v>
+        <v>54342</v>
       </c>
       <c r="E32" t="n">
-        <v>54268</v>
+        <v>54494</v>
       </c>
       <c r="F32" t="n">
-        <v>934</v>
+        <v>226</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0042</v>
       </c>
       <c r="H32" t="n">
-        <v>1156</v>
+        <v>542</v>
       </c>
       <c r="I32" t="n">
-        <v>52140</v>
+        <v>52111</v>
       </c>
       <c r="J32" t="n">
-        <v>52816.25</v>
+        <v>53323.5</v>
       </c>
       <c r="K32" t="n">
-        <v>53015.5</v>
+        <v>53690</v>
       </c>
       <c r="L32" t="n">
-        <v>53214.75</v>
+        <v>54056.5</v>
       </c>
       <c r="M32" t="n">
-        <v>53652.5</v>
+        <v>54846</v>
       </c>
       <c r="N32" t="n">
-        <v>54090.25</v>
+        <v>55635.5</v>
       </c>
       <c r="O32" t="n">
-        <v>54051</v>
+        <v>55579</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3206,18 +3208,14 @@
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
       </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
@@ -3229,70 +3227,72 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>54369</v>
+        <v>54555</v>
       </c>
       <c r="C33" t="n">
-        <v>54884</v>
+        <v>54678</v>
       </c>
       <c r="D33" t="n">
-        <v>54342</v>
+        <v>53952</v>
       </c>
       <c r="E33" t="n">
-        <v>54494</v>
+        <v>54013</v>
       </c>
       <c r="F33" t="n">
-        <v>226</v>
+        <v>-481</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>542</v>
+        <v>726</v>
       </c>
       <c r="I33" t="n">
-        <v>52111</v>
+        <v>53800</v>
       </c>
       <c r="J33" t="n">
-        <v>53323.5</v>
+        <v>53892.5</v>
       </c>
       <c r="K33" t="n">
-        <v>53690</v>
+        <v>54223</v>
       </c>
       <c r="L33" t="n">
-        <v>54056.5</v>
+        <v>54553.5</v>
       </c>
       <c r="M33" t="n">
-        <v>54846</v>
+        <v>54765</v>
       </c>
       <c r="N33" t="n">
-        <v>55635.5</v>
+        <v>54976.5</v>
       </c>
       <c r="O33" t="n">
-        <v>55579</v>
+        <v>55426</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
+      <c r="Q33" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
@@ -3304,72 +3304,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>54555</v>
+        <v>54040</v>
       </c>
       <c r="C34" t="n">
-        <v>54678</v>
+        <v>54202</v>
       </c>
       <c r="D34" t="n">
-        <v>53952</v>
+        <v>53879</v>
       </c>
       <c r="E34" t="n">
-        <v>54013</v>
+        <v>54152</v>
       </c>
       <c r="F34" t="n">
-        <v>-481</v>
+        <v>139</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0026</v>
       </c>
       <c r="H34" t="n">
-        <v>726</v>
+        <v>323</v>
       </c>
       <c r="I34" t="n">
-        <v>53800</v>
+        <v>53226</v>
       </c>
       <c r="J34" t="n">
-        <v>53892.5</v>
+        <v>53136</v>
       </c>
       <c r="K34" t="n">
-        <v>54223</v>
+        <v>53650</v>
       </c>
       <c r="L34" t="n">
-        <v>54553.5</v>
+        <v>54164</v>
       </c>
       <c r="M34" t="n">
-        <v>54765</v>
+        <v>54376</v>
       </c>
       <c r="N34" t="n">
-        <v>54976.5</v>
+        <v>54588</v>
       </c>
       <c r="O34" t="n">
-        <v>55426</v>
+        <v>55404</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3388,57 +3388,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>54040</v>
+        <v>54133</v>
       </c>
       <c r="C35" t="n">
-        <v>54202</v>
+        <v>54170</v>
       </c>
       <c r="D35" t="n">
-        <v>53879</v>
+        <v>53952</v>
       </c>
       <c r="E35" t="n">
-        <v>54152</v>
+        <v>54063</v>
       </c>
       <c r="F35" t="n">
-        <v>139</v>
+        <v>-89</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0016</v>
       </c>
       <c r="H35" t="n">
-        <v>323</v>
+        <v>218</v>
       </c>
       <c r="I35" t="n">
-        <v>53226</v>
+        <v>53556</v>
       </c>
       <c r="J35" t="n">
-        <v>53136</v>
+        <v>53884.75</v>
       </c>
       <c r="K35" t="n">
-        <v>53650</v>
+        <v>53990.5</v>
       </c>
       <c r="L35" t="n">
-        <v>54164</v>
+        <v>54096.25</v>
       </c>
       <c r="M35" t="n">
-        <v>54376</v>
+        <v>54313.5</v>
       </c>
       <c r="N35" t="n">
-        <v>54588</v>
+        <v>54530.75</v>
       </c>
       <c r="O35" t="n">
-        <v>55404</v>
+        <v>54525</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3446,8 +3446,10 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
@@ -3477,56 +3479,58 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>54133</v>
+        <v>54049</v>
       </c>
       <c r="C36" t="n">
-        <v>54170</v>
+        <v>54336</v>
       </c>
       <c r="D36" t="n">
-        <v>53952</v>
+        <v>53855</v>
       </c>
       <c r="E36" t="n">
-        <v>54063</v>
+        <v>53880</v>
       </c>
       <c r="F36" t="n">
-        <v>-89</v>
+        <v>-183</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0034</v>
       </c>
       <c r="H36" t="n">
-        <v>218</v>
+        <v>481</v>
       </c>
       <c r="I36" t="n">
-        <v>53556</v>
+        <v>53734</v>
       </c>
       <c r="J36" t="n">
-        <v>53884.75</v>
+        <v>53846</v>
       </c>
       <c r="K36" t="n">
-        <v>53990.5</v>
+        <v>53954</v>
       </c>
       <c r="L36" t="n">
-        <v>54096.25</v>
+        <v>54062</v>
       </c>
       <c r="M36" t="n">
-        <v>54313.5</v>
+        <v>54172</v>
       </c>
       <c r="N36" t="n">
-        <v>54530.75</v>
+        <v>54282</v>
       </c>
       <c r="O36" t="n">
-        <v>54525</v>
+        <v>54388</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
@@ -3535,14 +3539,18 @@
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3561,78 +3569,72 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>54049</v>
+        <v>53903</v>
       </c>
       <c r="C37" t="n">
-        <v>54336</v>
+        <v>54150</v>
       </c>
       <c r="D37" t="n">
-        <v>53855</v>
+        <v>53830</v>
       </c>
       <c r="E37" t="n">
-        <v>53880</v>
+        <v>53871</v>
       </c>
       <c r="F37" t="n">
-        <v>-183</v>
+        <v>-9</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0002</v>
       </c>
       <c r="H37" t="n">
-        <v>481</v>
+        <v>320</v>
       </c>
       <c r="I37" t="n">
-        <v>53734</v>
+        <v>53374</v>
       </c>
       <c r="J37" t="n">
-        <v>53846</v>
+        <v>53291.25</v>
       </c>
       <c r="K37" t="n">
-        <v>53954</v>
+        <v>53639.5</v>
       </c>
       <c r="L37" t="n">
-        <v>54062</v>
+        <v>53987.75</v>
       </c>
       <c r="M37" t="n">
-        <v>54172</v>
+        <v>54120.5</v>
       </c>
       <c r="N37" t="n">
-        <v>54282</v>
+        <v>54253.25</v>
       </c>
       <c r="O37" t="n">
-        <v>54388</v>
+        <v>54817</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3644,57 +3646,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>53903</v>
+        <v>53905</v>
       </c>
       <c r="C38" t="n">
-        <v>54150</v>
+        <v>54149</v>
       </c>
       <c r="D38" t="n">
-        <v>53830</v>
+        <v>53715</v>
       </c>
       <c r="E38" t="n">
-        <v>53871</v>
+        <v>53935</v>
       </c>
       <c r="F38" t="n">
-        <v>-9</v>
+        <v>64</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0012</v>
       </c>
       <c r="H38" t="n">
-        <v>320</v>
+        <v>434</v>
       </c>
       <c r="I38" t="n">
-        <v>53374</v>
+        <v>53510</v>
       </c>
       <c r="J38" t="n">
-        <v>53291.25</v>
+        <v>53491.5</v>
       </c>
       <c r="K38" t="n">
-        <v>53639.5</v>
+        <v>53711</v>
       </c>
       <c r="L38" t="n">
-        <v>53987.75</v>
+        <v>53930.5</v>
       </c>
       <c r="M38" t="n">
-        <v>54120.5</v>
+        <v>54031</v>
       </c>
       <c r="N38" t="n">
-        <v>54253.25</v>
+        <v>54131.5</v>
       </c>
       <c r="O38" t="n">
-        <v>54817</v>
+        <v>54470</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3705,9 +3707,9 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
@@ -3715,8 +3717,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U38" s="8" t="n">
-        <v/>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3728,57 +3732,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>53905</v>
+        <v>53961</v>
       </c>
       <c r="C39" t="n">
-        <v>54149</v>
+        <v>53999</v>
       </c>
       <c r="D39" t="n">
-        <v>53715</v>
+        <v>53745</v>
       </c>
       <c r="E39" t="n">
-        <v>53935</v>
+        <v>53807</v>
       </c>
       <c r="F39" t="n">
-        <v>64</v>
+        <v>-128</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0024</v>
       </c>
       <c r="H39" t="n">
-        <v>434</v>
+        <v>254</v>
       </c>
       <c r="I39" t="n">
-        <v>53510</v>
+        <v>53281</v>
       </c>
       <c r="J39" t="n">
-        <v>53491.5</v>
+        <v>53502.5</v>
       </c>
       <c r="K39" t="n">
-        <v>53711</v>
+        <v>53718</v>
       </c>
       <c r="L39" t="n">
-        <v>53930.5</v>
+        <v>53933.5</v>
       </c>
       <c r="M39" t="n">
-        <v>54031</v>
+        <v>54152</v>
       </c>
       <c r="N39" t="n">
-        <v>54131.5</v>
+        <v>54370.5</v>
       </c>
       <c r="O39" t="n">
-        <v>54470</v>
+        <v>54583</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3786,23 +3790,21 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3821,60 +3823,64 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>53961</v>
+        <v>53790</v>
       </c>
       <c r="C40" t="n">
-        <v>53999</v>
+        <v>53840</v>
       </c>
       <c r="D40" t="n">
-        <v>53745</v>
+        <v>53464</v>
       </c>
       <c r="E40" t="n">
-        <v>53807</v>
+        <v>53544</v>
       </c>
       <c r="F40" t="n">
-        <v>-128</v>
+        <v>-263</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0049</v>
       </c>
       <c r="H40" t="n">
-        <v>254</v>
+        <v>376</v>
       </c>
       <c r="I40" t="n">
-        <v>53281</v>
+        <v>53491</v>
       </c>
       <c r="J40" t="n">
-        <v>53502.5</v>
+        <v>53520.5</v>
       </c>
       <c r="K40" t="n">
-        <v>53718</v>
+        <v>53680</v>
       </c>
       <c r="L40" t="n">
-        <v>53933.5</v>
+        <v>53839.5</v>
       </c>
       <c r="M40" t="n">
-        <v>54152</v>
+        <v>53934</v>
       </c>
       <c r="N40" t="n">
-        <v>54370.5</v>
+        <v>54028.5</v>
       </c>
       <c r="O40" t="n">
-        <v>54583</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
+        <v>54253</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
@@ -3898,71 +3904,67 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>53790</v>
+        <v>53501</v>
       </c>
       <c r="C41" t="n">
-        <v>53840</v>
+        <v>53594</v>
       </c>
       <c r="D41" t="n">
-        <v>53464</v>
+        <v>53311</v>
       </c>
       <c r="E41" t="n">
-        <v>53544</v>
+        <v>53403</v>
       </c>
       <c r="F41" t="n">
-        <v>-263</v>
+        <v>-141</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0026</v>
       </c>
       <c r="H41" t="n">
-        <v>376</v>
+        <v>283</v>
       </c>
       <c r="I41" t="n">
-        <v>53491</v>
+        <v>53088</v>
       </c>
       <c r="J41" t="n">
-        <v>53520.5</v>
+        <v>53114</v>
       </c>
       <c r="K41" t="n">
-        <v>53680</v>
+        <v>53356</v>
       </c>
       <c r="L41" t="n">
-        <v>53839.5</v>
+        <v>53598</v>
       </c>
       <c r="M41" t="n">
-        <v>53934</v>
+        <v>53732</v>
       </c>
       <c r="N41" t="n">
-        <v>54028.5</v>
+        <v>53866</v>
       </c>
       <c r="O41" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
+        <v>54216</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
@@ -3993,50 +3995,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>53501</v>
+        <v>53408</v>
       </c>
       <c r="C42" t="n">
-        <v>53594</v>
+        <v>53780</v>
       </c>
       <c r="D42" t="n">
-        <v>53311</v>
+        <v>53337</v>
       </c>
       <c r="E42" t="n">
-        <v>53403</v>
+        <v>53530</v>
       </c>
       <c r="F42" t="n">
-        <v>-141</v>
+        <v>127</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0026</v>
+        <v>0.0024</v>
       </c>
       <c r="H42" t="n">
-        <v>283</v>
+        <v>443</v>
       </c>
       <c r="I42" t="n">
-        <v>53088</v>
+        <v>53028</v>
       </c>
       <c r="J42" t="n">
-        <v>53114</v>
+        <v>53095.25</v>
       </c>
       <c r="K42" t="n">
-        <v>53356</v>
+        <v>53261.5</v>
       </c>
       <c r="L42" t="n">
-        <v>53598</v>
+        <v>53427.75</v>
       </c>
       <c r="M42" t="n">
-        <v>53732</v>
+        <v>53544.5</v>
       </c>
       <c r="N42" t="n">
-        <v>53866</v>
+        <v>53661.25</v>
       </c>
       <c r="O42" t="n">
-        <v>54216</v>
+        <v>53877</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4044,21 +4046,23 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
@@ -4068,90 +4072,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>53408</v>
+        <v>53529</v>
       </c>
       <c r="C43" t="n">
-        <v>53780</v>
+        <v>53589</v>
       </c>
       <c r="D43" t="n">
-        <v>53337</v>
+        <v>52812</v>
       </c>
       <c r="E43" t="n">
-        <v>53530</v>
+        <v>52849</v>
       </c>
       <c r="F43" t="n">
-        <v>127</v>
+        <v>-681</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0127</v>
       </c>
       <c r="H43" t="n">
-        <v>443</v>
+        <v>777</v>
       </c>
       <c r="I43" t="n">
-        <v>53028</v>
+        <v>52894</v>
       </c>
       <c r="J43" t="n">
-        <v>53095.25</v>
+        <v>53072.75</v>
       </c>
       <c r="K43" t="n">
-        <v>53261.5</v>
+        <v>53308.5</v>
       </c>
       <c r="L43" t="n">
-        <v>53427.75</v>
+        <v>53544.25</v>
       </c>
       <c r="M43" t="n">
-        <v>53544.5</v>
+        <v>53751.5</v>
       </c>
       <c r="N43" t="n">
-        <v>53661.25</v>
+        <v>53958.75</v>
       </c>
       <c r="O43" t="n">
-        <v>53877</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
+        <v>54223</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U43" s="8" t="inlineStr">
+      <c r="Q43" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
+      </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W43" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X43" t="inlineStr"/>
@@ -4159,77 +4161,75 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>53529</v>
+        <v>52876</v>
       </c>
       <c r="C44" t="n">
-        <v>53589</v>
+        <v>53418</v>
       </c>
       <c r="D44" t="n">
-        <v>52812</v>
+        <v>52838</v>
       </c>
       <c r="E44" t="n">
-        <v>52849</v>
+        <v>53353</v>
       </c>
       <c r="F44" t="n">
-        <v>-681</v>
+        <v>504</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0095</v>
       </c>
       <c r="H44" t="n">
-        <v>777</v>
+        <v>580</v>
       </c>
       <c r="I44" t="n">
-        <v>52894</v>
+        <v>52035</v>
       </c>
       <c r="J44" t="n">
-        <v>53072.75</v>
+        <v>51896.25</v>
       </c>
       <c r="K44" t="n">
-        <v>53308.5</v>
+        <v>52460.5</v>
       </c>
       <c r="L44" t="n">
-        <v>53544.25</v>
+        <v>53024.75</v>
       </c>
       <c r="M44" t="n">
-        <v>53751.5</v>
+        <v>53237.5</v>
       </c>
       <c r="N44" t="n">
-        <v>53958.75</v>
+        <v>53450.25</v>
       </c>
       <c r="O44" t="n">
-        <v>54223</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
+        <v>54366</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
@@ -4238,55 +4238,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>52876</v>
+        <v>53367</v>
       </c>
       <c r="C45" t="n">
-        <v>53418</v>
+        <v>53567</v>
       </c>
       <c r="D45" t="n">
-        <v>52838</v>
+        <v>53210</v>
       </c>
       <c r="E45" t="n">
-        <v>53353</v>
+        <v>53489</v>
       </c>
       <c r="F45" t="n">
-        <v>504</v>
+        <v>136</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.0025</v>
       </c>
       <c r="H45" t="n">
-        <v>580</v>
+        <v>357</v>
       </c>
       <c r="I45" t="n">
-        <v>52035</v>
+        <v>52258</v>
       </c>
       <c r="J45" t="n">
-        <v>51896.25</v>
+        <v>52885.5</v>
       </c>
       <c r="K45" t="n">
-        <v>52460.5</v>
+        <v>53063</v>
       </c>
       <c r="L45" t="n">
-        <v>53024.75</v>
+        <v>53240.5</v>
       </c>
       <c r="M45" t="n">
-        <v>53237.5</v>
+        <v>53643</v>
       </c>
       <c r="N45" t="n">
-        <v>53450.25</v>
+        <v>54045.5</v>
       </c>
       <c r="O45" t="n">
-        <v>54366</v>
+        <v>53998</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4304,14 +4308,12 @@
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U45" s="8" t="n">
+        <v/>
+      </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
@@ -4322,57 +4324,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>53367</v>
+        <v>53524</v>
       </c>
       <c r="C46" t="n">
-        <v>53567</v>
+        <v>53797</v>
       </c>
       <c r="D46" t="n">
-        <v>53210</v>
+        <v>53426</v>
       </c>
       <c r="E46" t="n">
-        <v>53489</v>
+        <v>53645</v>
       </c>
       <c r="F46" t="n">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0029</v>
       </c>
       <c r="H46" t="n">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="I46" t="n">
-        <v>52258</v>
+        <v>52853</v>
       </c>
       <c r="J46" t="n">
-        <v>52885.5</v>
+        <v>53182.25</v>
       </c>
       <c r="K46" t="n">
-        <v>53063</v>
+        <v>53310.5</v>
       </c>
       <c r="L46" t="n">
-        <v>53240.5</v>
+        <v>53438.75</v>
       </c>
       <c r="M46" t="n">
-        <v>53643</v>
+        <v>53667.5</v>
       </c>
       <c r="N46" t="n">
-        <v>54045.5</v>
+        <v>53896.25</v>
       </c>
       <c r="O46" t="n">
-        <v>53998</v>
+        <v>53924</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4413,50 +4415,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>53524</v>
+        <v>53643</v>
       </c>
       <c r="C47" t="n">
-        <v>53797</v>
+        <v>53778</v>
       </c>
       <c r="D47" t="n">
-        <v>53426</v>
+        <v>53435</v>
       </c>
       <c r="E47" t="n">
-        <v>53645</v>
+        <v>53521</v>
       </c>
       <c r="F47" t="n">
-        <v>156</v>
+        <v>-124</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0023</v>
       </c>
       <c r="H47" t="n">
-        <v>371</v>
+        <v>343</v>
       </c>
       <c r="I47" t="n">
-        <v>52853</v>
+        <v>53055</v>
       </c>
       <c r="J47" t="n">
-        <v>53182.25</v>
+        <v>53290.75</v>
       </c>
       <c r="K47" t="n">
-        <v>53310.5</v>
+        <v>53459.5</v>
       </c>
       <c r="L47" t="n">
-        <v>53438.75</v>
+        <v>53628.25</v>
       </c>
       <c r="M47" t="n">
-        <v>53667.5</v>
+        <v>53830.5</v>
       </c>
       <c r="N47" t="n">
-        <v>53896.25</v>
+        <v>54032.75</v>
       </c>
       <c r="O47" t="n">
-        <v>53924</v>
+        <v>54168</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4464,19 +4466,19 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
+      <c r="R47" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
       <c r="U47" s="8" t="n">
         <v/>
       </c>
@@ -4490,57 +4492,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>53643</v>
+        <v>53724</v>
       </c>
       <c r="C48" t="n">
-        <v>53778</v>
+        <v>53811</v>
       </c>
       <c r="D48" t="n">
-        <v>53435</v>
+        <v>53369</v>
       </c>
       <c r="E48" t="n">
-        <v>53521</v>
+        <v>53621</v>
       </c>
       <c r="F48" t="n">
-        <v>-124</v>
+        <v>100</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0019</v>
       </c>
       <c r="H48" t="n">
-        <v>343</v>
+        <v>442</v>
       </c>
       <c r="I48" t="n">
-        <v>53055</v>
+        <v>53092</v>
       </c>
       <c r="J48" t="n">
-        <v>53290.75</v>
+        <v>53135.25</v>
       </c>
       <c r="K48" t="n">
-        <v>53459.5</v>
+        <v>53349.5</v>
       </c>
       <c r="L48" t="n">
-        <v>53628.25</v>
+        <v>53563.75</v>
       </c>
       <c r="M48" t="n">
-        <v>53830.5</v>
+        <v>53692.5</v>
       </c>
       <c r="N48" t="n">
-        <v>54032.75</v>
+        <v>53821.25</v>
       </c>
       <c r="O48" t="n">
-        <v>54168</v>
+        <v>54121</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4548,18 +4550,18 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4574,57 +4576,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>53724</v>
+        <v>53608</v>
       </c>
       <c r="C49" t="n">
-        <v>53811</v>
+        <v>53862</v>
       </c>
       <c r="D49" t="n">
-        <v>53369</v>
+        <v>53513</v>
       </c>
       <c r="E49" t="n">
-        <v>53621</v>
+        <v>53584</v>
       </c>
       <c r="F49" t="n">
-        <v>100</v>
+        <v>-37</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0007</v>
       </c>
       <c r="H49" t="n">
-        <v>442</v>
+        <v>349</v>
       </c>
       <c r="I49" t="n">
-        <v>53092</v>
+        <v>52927</v>
       </c>
       <c r="J49" t="n">
-        <v>53135.25</v>
+        <v>53194.5</v>
       </c>
       <c r="K49" t="n">
-        <v>53349.5</v>
+        <v>53400</v>
       </c>
       <c r="L49" t="n">
-        <v>53563.75</v>
+        <v>53605.5</v>
       </c>
       <c r="M49" t="n">
-        <v>53692.5</v>
+        <v>53842</v>
       </c>
       <c r="N49" t="n">
-        <v>53821.25</v>
+        <v>54078.5</v>
       </c>
       <c r="O49" t="n">
-        <v>54121</v>
+        <v>54253</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4635,9 +4637,9 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
@@ -4665,69 +4667,73 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>53608</v>
+        <v>53664</v>
       </c>
       <c r="C50" t="n">
-        <v>53862</v>
+        <v>53664</v>
       </c>
       <c r="D50" t="n">
-        <v>53513</v>
+        <v>53149</v>
       </c>
       <c r="E50" t="n">
-        <v>53584</v>
+        <v>53240</v>
       </c>
       <c r="F50" t="n">
-        <v>-37</v>
+        <v>-344</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0064</v>
       </c>
       <c r="H50" t="n">
-        <v>349</v>
+        <v>515</v>
       </c>
       <c r="I50" t="n">
-        <v>52927</v>
+        <v>53164</v>
       </c>
       <c r="J50" t="n">
-        <v>53194.5</v>
+        <v>53183.25</v>
       </c>
       <c r="K50" t="n">
-        <v>53400</v>
+        <v>53409.5</v>
       </c>
       <c r="L50" t="n">
-        <v>53605.5</v>
+        <v>53635.75</v>
       </c>
       <c r="M50" t="n">
-        <v>53842</v>
+        <v>53758.5</v>
       </c>
       <c r="N50" t="n">
-        <v>54078.5</v>
+        <v>53881.25</v>
       </c>
       <c r="O50" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+        <v>54211</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4740,73 +4746,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>53664</v>
+        <v>53259</v>
       </c>
       <c r="C51" t="n">
-        <v>53664</v>
+        <v>53343</v>
       </c>
       <c r="D51" t="n">
-        <v>53149</v>
+        <v>52747</v>
       </c>
       <c r="E51" t="n">
-        <v>53240</v>
+        <v>52828</v>
       </c>
       <c r="F51" t="n">
-        <v>-344</v>
+        <v>-412</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0064</v>
+        <v>-0.0077</v>
       </c>
       <c r="H51" t="n">
-        <v>515</v>
+        <v>596</v>
       </c>
       <c r="I51" t="n">
-        <v>53164</v>
+        <v>52634</v>
       </c>
       <c r="J51" t="n">
-        <v>53183.25</v>
+        <v>52641.75</v>
       </c>
       <c r="K51" t="n">
-        <v>53409.5</v>
+        <v>52982.5</v>
       </c>
       <c r="L51" t="n">
-        <v>53635.75</v>
+        <v>53323.25</v>
       </c>
       <c r="M51" t="n">
-        <v>53758.5</v>
+        <v>53497.5</v>
       </c>
       <c r="N51" t="n">
-        <v>53881.25</v>
+        <v>53671.75</v>
       </c>
       <c r="O51" t="n">
-        <v>54211</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q51" s="6" t="inlineStr">
+        <v>54179</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
@@ -4833,50 +4831,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>53259</v>
+        <v>52844</v>
       </c>
       <c r="C52" t="n">
-        <v>53343</v>
+        <v>53283</v>
       </c>
       <c r="D52" t="n">
-        <v>52747</v>
+        <v>52720</v>
       </c>
       <c r="E52" t="n">
-        <v>52828</v>
+        <v>53121</v>
       </c>
       <c r="F52" t="n">
-        <v>-412</v>
+        <v>293</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0077</v>
+        <v>0.0055</v>
       </c>
       <c r="H52" t="n">
-        <v>596</v>
+        <v>563</v>
       </c>
       <c r="I52" t="n">
-        <v>52634</v>
+        <v>52151</v>
       </c>
       <c r="J52" t="n">
-        <v>52641.75</v>
+        <v>52123.5</v>
       </c>
       <c r="K52" t="n">
-        <v>52982.5</v>
+        <v>52530</v>
       </c>
       <c r="L52" t="n">
-        <v>53323.25</v>
+        <v>52936.5</v>
       </c>
       <c r="M52" t="n">
-        <v>53497.5</v>
+        <v>53126</v>
       </c>
       <c r="N52" t="n">
-        <v>53671.75</v>
+        <v>53315.5</v>
       </c>
       <c r="O52" t="n">
-        <v>54179</v>
+        <v>53939</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4884,19 +4882,19 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
       <c r="U52" s="8" t="n">
         <v/>
       </c>
@@ -4908,55 +4906,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>52844</v>
+        <v>53120</v>
       </c>
       <c r="C53" t="n">
-        <v>53283</v>
+        <v>53827</v>
       </c>
       <c r="D53" t="n">
-        <v>52720</v>
+        <v>53093</v>
       </c>
       <c r="E53" t="n">
-        <v>53121</v>
+        <v>53745</v>
       </c>
       <c r="F53" t="n">
-        <v>293</v>
+        <v>624</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0117</v>
       </c>
       <c r="H53" t="n">
-        <v>563</v>
+        <v>734</v>
       </c>
       <c r="I53" t="n">
-        <v>52151</v>
+        <v>52157</v>
       </c>
       <c r="J53" t="n">
-        <v>52123.5</v>
+        <v>52617.75</v>
       </c>
       <c r="K53" t="n">
-        <v>52530</v>
+        <v>52839.5</v>
       </c>
       <c r="L53" t="n">
-        <v>52936.5</v>
+        <v>53061.25</v>
       </c>
       <c r="M53" t="n">
-        <v>53126</v>
+        <v>53402.5</v>
       </c>
       <c r="N53" t="n">
-        <v>53315.5</v>
+        <v>53743.75</v>
       </c>
       <c r="O53" t="n">
-        <v>53939</v>
+        <v>53846</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4974,73 +4976,71 @@
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W53" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>53120</v>
+        <v>53707</v>
       </c>
       <c r="C54" t="n">
-        <v>53827</v>
+        <v>53772</v>
       </c>
       <c r="D54" t="n">
-        <v>53093</v>
+        <v>53235</v>
       </c>
       <c r="E54" t="n">
-        <v>53745</v>
+        <v>53440</v>
       </c>
       <c r="F54" t="n">
-        <v>624</v>
+        <v>-305</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0117</v>
+        <v>-0.0057</v>
       </c>
       <c r="H54" t="n">
-        <v>734</v>
+        <v>537</v>
       </c>
       <c r="I54" t="n">
-        <v>52157</v>
+        <v>52359</v>
       </c>
       <c r="J54" t="n">
-        <v>52617.75</v>
+        <v>53153.5</v>
       </c>
       <c r="K54" t="n">
-        <v>52839.5</v>
+        <v>53378</v>
       </c>
       <c r="L54" t="n">
-        <v>53061.25</v>
+        <v>53602.5</v>
       </c>
       <c r="M54" t="n">
-        <v>53402.5</v>
+        <v>54112</v>
       </c>
       <c r="N54" t="n">
-        <v>53743.75</v>
+        <v>54621.5</v>
       </c>
       <c r="O54" t="n">
-        <v>53846</v>
+        <v>54561</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5048,24 +5048,22 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
@@ -5074,65 +5072,71 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>53707</v>
+        <v>53261</v>
       </c>
       <c r="C55" t="n">
-        <v>53772</v>
+        <v>53336</v>
       </c>
       <c r="D55" t="n">
-        <v>53235</v>
+        <v>52758</v>
       </c>
       <c r="E55" t="n">
-        <v>53440</v>
+        <v>52832</v>
       </c>
       <c r="F55" t="n">
-        <v>-305</v>
+        <v>-608</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0057</v>
+        <v>-0.0114</v>
       </c>
       <c r="H55" t="n">
-        <v>537</v>
+        <v>578</v>
       </c>
       <c r="I55" t="n">
-        <v>52359</v>
+        <v>52698</v>
       </c>
       <c r="J55" t="n">
-        <v>53153.5</v>
+        <v>52871.25</v>
       </c>
       <c r="K55" t="n">
-        <v>53378</v>
+        <v>53171.5</v>
       </c>
       <c r="L55" t="n">
-        <v>53602.5</v>
+        <v>53471.75</v>
       </c>
       <c r="M55" t="n">
-        <v>54112</v>
+        <v>53708.5</v>
       </c>
       <c r="N55" t="n">
-        <v>54621.5</v>
+        <v>53945.25</v>
       </c>
       <c r="O55" t="n">
-        <v>54561</v>
+        <v>54309</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
@@ -5149,76 +5153,70 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W55" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>53261</v>
+        <v>52817</v>
       </c>
       <c r="C56" t="n">
-        <v>53336</v>
+        <v>52859</v>
       </c>
       <c r="D56" t="n">
-        <v>52758</v>
+        <v>52339</v>
       </c>
       <c r="E56" t="n">
-        <v>52832</v>
+        <v>52425</v>
       </c>
       <c r="F56" t="n">
-        <v>-608</v>
+        <v>-407</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0114</v>
+        <v>-0.0077</v>
       </c>
       <c r="H56" t="n">
-        <v>578</v>
+        <v>520</v>
       </c>
       <c r="I56" t="n">
-        <v>52698</v>
+        <v>52180</v>
       </c>
       <c r="J56" t="n">
-        <v>52871.25</v>
+        <v>52146.5</v>
       </c>
       <c r="K56" t="n">
-        <v>53171.5</v>
+        <v>52543</v>
       </c>
       <c r="L56" t="n">
-        <v>53471.75</v>
+        <v>52939.5</v>
       </c>
       <c r="M56" t="n">
-        <v>53708.5</v>
+        <v>53121</v>
       </c>
       <c r="N56" t="n">
-        <v>53945.25</v>
+        <v>53302.5</v>
       </c>
       <c r="O56" t="n">
-        <v>54309</v>
+        <v>53914</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
@@ -5245,50 +5243,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>52817</v>
+        <v>52473</v>
       </c>
       <c r="C57" t="n">
-        <v>52859</v>
+        <v>52676</v>
       </c>
       <c r="D57" t="n">
-        <v>52339</v>
+        <v>51992</v>
       </c>
       <c r="E57" t="n">
-        <v>52425</v>
+        <v>52095</v>
       </c>
       <c r="F57" t="n">
-        <v>-407</v>
+        <v>-330</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0077</v>
+        <v>-0.0063</v>
       </c>
       <c r="H57" t="n">
-        <v>520</v>
+        <v>684</v>
       </c>
       <c r="I57" t="n">
-        <v>52180</v>
+        <v>51819</v>
       </c>
       <c r="J57" t="n">
-        <v>52146.5</v>
+        <v>51818</v>
       </c>
       <c r="K57" t="n">
-        <v>52543</v>
+        <v>52165</v>
       </c>
       <c r="L57" t="n">
-        <v>52939.5</v>
+        <v>52512</v>
       </c>
       <c r="M57" t="n">
-        <v>53121</v>
+        <v>52685</v>
       </c>
       <c r="N57" t="n">
-        <v>53302.5</v>
+        <v>52858</v>
       </c>
       <c r="O57" t="n">
-        <v>53914</v>
+        <v>53379</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5325,50 +5323,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>52473</v>
+        <v>52059</v>
       </c>
       <c r="C58" t="n">
-        <v>52676</v>
+        <v>52739</v>
       </c>
       <c r="D58" t="n">
-        <v>51992</v>
+        <v>52059</v>
       </c>
       <c r="E58" t="n">
-        <v>52095</v>
+        <v>52585</v>
       </c>
       <c r="F58" t="n">
-        <v>-330</v>
+        <v>490</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0063</v>
+        <v>0.0094</v>
       </c>
       <c r="H58" t="n">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="I58" t="n">
-        <v>51819</v>
+        <v>51308</v>
       </c>
       <c r="J58" t="n">
-        <v>51818</v>
+        <v>51291.5</v>
       </c>
       <c r="K58" t="n">
-        <v>52165</v>
+        <v>51753</v>
       </c>
       <c r="L58" t="n">
-        <v>52512</v>
+        <v>52214.5</v>
       </c>
       <c r="M58" t="n">
-        <v>52685</v>
+        <v>52437</v>
       </c>
       <c r="N58" t="n">
-        <v>52858</v>
+        <v>52659.5</v>
       </c>
       <c r="O58" t="n">
-        <v>53379</v>
+        <v>53360</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5376,22 +5374,24 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
       <c r="V58" s="8" t="n">
         <v/>
       </c>
@@ -5400,55 +5400,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>52059</v>
+        <v>52376</v>
       </c>
       <c r="C59" t="n">
-        <v>52739</v>
+        <v>52672</v>
       </c>
       <c r="D59" t="n">
-        <v>52059</v>
+        <v>52226</v>
       </c>
       <c r="E59" t="n">
-        <v>52585</v>
+        <v>52440</v>
       </c>
       <c r="F59" t="n">
-        <v>490</v>
+        <v>-145</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0094</v>
+        <v>-0.0028</v>
       </c>
       <c r="H59" t="n">
-        <v>680</v>
+        <v>446</v>
       </c>
       <c r="I59" t="n">
-        <v>51308</v>
+        <v>51379</v>
       </c>
       <c r="J59" t="n">
-        <v>51291.5</v>
+        <v>51998</v>
       </c>
       <c r="K59" t="n">
-        <v>51753</v>
+        <v>52245</v>
       </c>
       <c r="L59" t="n">
-        <v>52214.5</v>
+        <v>52492</v>
       </c>
       <c r="M59" t="n">
-        <v>52437</v>
+        <v>52925</v>
       </c>
       <c r="N59" t="n">
-        <v>52659.5</v>
+        <v>53358</v>
       </c>
       <c r="O59" t="n">
-        <v>53360</v>
+        <v>53419</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5456,23 +5460,21 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
+      <c r="R59" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v/>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
@@ -5484,72 +5486,74 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>52376</v>
+        <v>52499</v>
       </c>
       <c r="C60" t="n">
-        <v>52672</v>
+        <v>52499</v>
       </c>
       <c r="D60" t="n">
-        <v>52226</v>
+        <v>51908</v>
       </c>
       <c r="E60" t="n">
-        <v>52440</v>
+        <v>52115</v>
       </c>
       <c r="F60" t="n">
-        <v>-145</v>
+        <v>-325</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0028</v>
+        <v>-0.0062</v>
       </c>
       <c r="H60" t="n">
-        <v>446</v>
+        <v>591</v>
       </c>
       <c r="I60" t="n">
-        <v>51379</v>
+        <v>51780</v>
       </c>
       <c r="J60" t="n">
-        <v>51998</v>
+        <v>51989.5</v>
       </c>
       <c r="K60" t="n">
-        <v>52245</v>
+        <v>52217</v>
       </c>
       <c r="L60" t="n">
-        <v>52492</v>
+        <v>52444.5</v>
       </c>
       <c r="M60" t="n">
-        <v>52925</v>
+        <v>52663</v>
       </c>
       <c r="N60" t="n">
-        <v>53358</v>
+        <v>52881.5</v>
       </c>
       <c r="O60" t="n">
-        <v>53419</v>
+        <v>53118</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5566,67 +5570,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>52499</v>
+        <v>51894</v>
       </c>
       <c r="C61" t="n">
-        <v>52499</v>
+        <v>51914</v>
       </c>
       <c r="D61" t="n">
-        <v>51908</v>
+        <v>51838</v>
       </c>
       <c r="E61" t="n">
-        <v>52115</v>
+        <v>51891</v>
       </c>
       <c r="F61" t="n">
-        <v>-325</v>
+        <v>-224</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0062</v>
+        <v>-0.0043</v>
       </c>
       <c r="H61" t="n">
-        <v>591</v>
+        <v>76</v>
       </c>
       <c r="I61" t="n">
-        <v>51780</v>
+        <v>51317</v>
       </c>
       <c r="J61" t="n">
-        <v>51989.5</v>
+        <v>51479.75</v>
       </c>
       <c r="K61" t="n">
-        <v>52217</v>
+        <v>51819.5</v>
       </c>
       <c r="L61" t="n">
-        <v>52444.5</v>
+        <v>52159.25</v>
       </c>
       <c r="M61" t="n">
-        <v>52663</v>
+        <v>52410.5</v>
       </c>
       <c r="N61" t="n">
-        <v>52881.5</v>
+        <v>52661.75</v>
       </c>
       <c r="O61" t="n">
-        <v>53118</v>
+        <v>53090</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q61" s="6" t="n">
+        <v/>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
@@ -5655,113 +5653,31 @@
       <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>52576</v>
-      </c>
-      <c r="C62" t="n">
-        <v>52709</v>
-      </c>
-      <c r="D62" t="n">
-        <v>52524</v>
-      </c>
-      <c r="E62" t="n">
-        <v>52693</v>
-      </c>
-      <c r="F62" t="n">
-        <v>578</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0.0111</v>
-      </c>
-      <c r="H62" t="n">
-        <v>185</v>
-      </c>
-      <c r="I62" t="n">
-        <v>51317</v>
-      </c>
-      <c r="J62" t="n">
-        <v>51479.75</v>
-      </c>
-      <c r="K62" t="n">
-        <v>51819.5</v>
-      </c>
-      <c r="L62" t="n">
-        <v>52159.25</v>
-      </c>
-      <c r="M62" t="n">
-        <v>52410.5</v>
-      </c>
-      <c r="N62" t="n">
-        <v>52661.75</v>
-      </c>
-      <c r="O62" t="n">
-        <v>53090</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I63" s="13" t="n">
-        <v>52339</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>52546.25</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>52600.5</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>52654.75</v>
-      </c>
-      <c r="M63" s="13" t="n">
-        <v>52785.5</v>
-      </c>
-      <c r="N63" s="13" t="n">
-        <v>52916.25</v>
-      </c>
-      <c r="O63" s="13" t="n">
-        <v>52894</v>
+      <c r="I62" s="13" t="n">
+        <v>51762</v>
+      </c>
+      <c r="J62" s="13" t="n">
+        <v>51822.5</v>
+      </c>
+      <c r="K62" s="13" t="n">
+        <v>51853</v>
+      </c>
+      <c r="L62" s="13" t="n">
+        <v>51883.5</v>
+      </c>
+      <c r="M62" s="13" t="n">
+        <v>51929</v>
+      </c>
+      <c r="N62" s="13" t="n">
+        <v>51974.5</v>
+      </c>
+      <c r="O62" s="13" t="n">
+        <v>51990</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -5582,22 +5582,22 @@
         <v>51894</v>
       </c>
       <c r="C61" t="n">
-        <v>51914</v>
+        <v>52253</v>
       </c>
       <c r="D61" t="n">
         <v>51838</v>
       </c>
       <c r="E61" t="n">
-        <v>51891</v>
+        <v>52203</v>
       </c>
       <c r="F61" t="n">
-        <v>-224</v>
+        <v>88</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0017</v>
       </c>
       <c r="H61" t="n">
-        <v>76</v>
+        <v>415</v>
       </c>
       <c r="I61" t="n">
         <v>51317</v>
@@ -5626,14 +5626,12 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5650,7 +5648,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -5659,25 +5661,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>51762</v>
+        <v>51423</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>51822.5</v>
+        <v>51866.75</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>51853</v>
+        <v>51995.5</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>51883.5</v>
+        <v>52124.25</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>51929</v>
+        <v>52410.5</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>51974.5</v>
+        <v>52696.75</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>51990</v>
+        <v>52668</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5579,25 +5579,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>51894</v>
+        <v>52162</v>
       </c>
       <c r="C61" t="n">
-        <v>52253</v>
+        <v>52298</v>
       </c>
       <c r="D61" t="n">
-        <v>51838</v>
+        <v>51209</v>
       </c>
       <c r="E61" t="n">
-        <v>52203</v>
+        <v>51507</v>
       </c>
       <c r="F61" t="n">
-        <v>88</v>
+        <v>-608</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0117</v>
       </c>
       <c r="H61" t="n">
-        <v>415</v>
+        <v>1089</v>
       </c>
       <c r="I61" t="n">
         <v>51317</v>
@@ -5620,18 +5620,24 @@
       <c r="O61" t="n">
         <v>53090</v>
       </c>
-      <c r="P61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5648,38 +5654,118 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>52201</v>
+      </c>
+      <c r="C62" t="n">
+        <v>52207</v>
+      </c>
+      <c r="D62" t="n">
+        <v>52185</v>
+      </c>
+      <c r="E62" t="n">
+        <v>52197</v>
+      </c>
+      <c r="F62" t="n">
+        <v>690</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.0134</v>
+      </c>
+      <c r="H62" t="n">
+        <v>22</v>
+      </c>
+      <c r="I62" t="n">
+        <v>50120</v>
+      </c>
+      <c r="J62" t="n">
+        <v>50294.75</v>
+      </c>
+      <c r="K62" t="n">
+        <v>50962.5</v>
+      </c>
+      <c r="L62" t="n">
+        <v>51630.25</v>
+      </c>
+      <c r="M62" t="n">
+        <v>52051.5</v>
+      </c>
+      <c r="N62" t="n">
+        <v>52472.75</v>
+      </c>
+      <c r="O62" t="n">
+        <v>53387</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I62" s="13" t="n">
-        <v>51423</v>
-      </c>
-      <c r="J62" s="13" t="n">
-        <v>51866.75</v>
-      </c>
-      <c r="K62" s="13" t="n">
-        <v>51995.5</v>
-      </c>
-      <c r="L62" s="13" t="n">
-        <v>52124.25</v>
-      </c>
-      <c r="M62" s="13" t="n">
-        <v>52410.5</v>
-      </c>
-      <c r="N62" s="13" t="n">
-        <v>52696.75</v>
-      </c>
-      <c r="O62" s="13" t="n">
-        <v>52668</v>
+      <c r="I63" s="13" t="n">
+        <v>52163</v>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>52175.5</v>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>52186</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>52196.5</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>52208</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>52219.5</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>52229</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -5669,19 +5669,19 @@
         <v>52207</v>
       </c>
       <c r="D62" t="n">
-        <v>52185</v>
+        <v>52147</v>
       </c>
       <c r="E62" t="n">
-        <v>52197</v>
+        <v>52174</v>
       </c>
       <c r="F62" t="n">
-        <v>690</v>
+        <v>667</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0129</v>
       </c>
       <c r="H62" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="I62" t="n">
         <v>50120</v>
@@ -5747,25 +5747,25 @@
         </is>
       </c>
       <c r="I63" s="13" t="n">
-        <v>52163</v>
+        <v>52087</v>
       </c>
       <c r="J63" s="13" t="n">
+        <v>52112.5</v>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>52144</v>
+      </c>
+      <c r="L63" s="13" t="n">
         <v>52175.5</v>
       </c>
-      <c r="K63" s="13" t="n">
-        <v>52186</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>52196.5</v>
-      </c>
       <c r="M63" s="13" t="n">
-        <v>52208</v>
+        <v>52204</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>52219.5</v>
+        <v>52232.5</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>52229</v>
+        <v>52267</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,8 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5666,22 +5659,22 @@
         <v>52201</v>
       </c>
       <c r="C62" t="n">
-        <v>52207</v>
+        <v>52209</v>
       </c>
       <c r="D62" t="n">
         <v>52147</v>
       </c>
       <c r="E62" t="n">
-        <v>52174</v>
+        <v>52193</v>
       </c>
       <c r="F62" t="n">
-        <v>667</v>
+        <v>686</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0129</v>
+        <v>0.0133</v>
       </c>
       <c r="H62" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="I62" t="n">
         <v>50120</v>
@@ -5738,34 +5731,6 @@
         <is>
           <t>中警訊</t>
         </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>明日預測</t>
-        </is>
-      </c>
-      <c r="I63" s="13" t="n">
-        <v>52087</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>52112.5</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>52144</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>52175.5</v>
-      </c>
-      <c r="M63" s="13" t="n">
-        <v>52204</v>
-      </c>
-      <c r="N63" s="13" t="n">
-        <v>52232.5</v>
-      </c>
-      <c r="O63" s="13" t="n">
-        <v>52267</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -5659,22 +5659,22 @@
         <v>52201</v>
       </c>
       <c r="C62" t="n">
-        <v>52209</v>
+        <v>52224</v>
       </c>
       <c r="D62" t="n">
         <v>52147</v>
       </c>
       <c r="E62" t="n">
-        <v>52193</v>
+        <v>52205</v>
       </c>
       <c r="F62" t="n">
-        <v>686</v>
+        <v>698</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0136</v>
       </c>
       <c r="H62" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="I62" t="n">
         <v>50120</v>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52165</v>
+        <v>52119</v>
       </c>
       <c r="C2" t="n">
-        <v>52281</v>
+        <v>52676</v>
       </c>
       <c r="D2" t="n">
-        <v>51691</v>
+        <v>51933</v>
       </c>
       <c r="E2" t="n">
-        <v>52082</v>
+        <v>52279</v>
       </c>
       <c r="F2" t="n">
-        <v>-37</v>
+        <v>197</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0007</v>
+        <v>0.0038</v>
       </c>
       <c r="H2" t="n">
-        <v>590</v>
+        <v>743</v>
       </c>
       <c r="I2" t="n">
-        <v>51119</v>
+        <v>51101</v>
       </c>
       <c r="J2" t="n">
-        <v>51581.25</v>
+        <v>51540</v>
       </c>
       <c r="K2" t="n">
-        <v>51822.5</v>
+        <v>51787</v>
       </c>
       <c r="L2" t="n">
-        <v>52063.75</v>
+        <v>52034</v>
       </c>
       <c r="M2" t="n">
-        <v>52415.5</v>
+        <v>52377</v>
       </c>
       <c r="N2" t="n">
-        <v>52767.25</v>
+        <v>52720</v>
       </c>
       <c r="O2" t="n">
-        <v>52898</v>
+        <v>52871</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,18 +685,18 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -709,59 +709,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>52119</v>
+        <v>52381</v>
       </c>
       <c r="C3" t="n">
-        <v>52676</v>
+        <v>53097</v>
       </c>
       <c r="D3" t="n">
-        <v>51933</v>
+        <v>52215</v>
       </c>
       <c r="E3" t="n">
-        <v>52279</v>
+        <v>52339</v>
       </c>
       <c r="F3" t="n">
-        <v>197</v>
+        <v>60</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.0011</v>
       </c>
       <c r="H3" t="n">
-        <v>743</v>
+        <v>882</v>
       </c>
       <c r="I3" t="n">
-        <v>51101</v>
+        <v>51190</v>
       </c>
       <c r="J3" t="n">
-        <v>51540</v>
+        <v>51523.25</v>
       </c>
       <c r="K3" t="n">
-        <v>51787</v>
+        <v>51907.5</v>
       </c>
       <c r="L3" t="n">
-        <v>52034</v>
+        <v>52291.75</v>
       </c>
       <c r="M3" t="n">
-        <v>52377</v>
+        <v>52650.5</v>
       </c>
       <c r="N3" t="n">
-        <v>52720</v>
+        <v>53009.25</v>
       </c>
       <c r="O3" t="n">
-        <v>52871</v>
+        <v>53419</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -774,16 +770,18 @@
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -798,50 +796,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>52381</v>
+        <v>52439</v>
       </c>
       <c r="C4" t="n">
-        <v>53097</v>
+        <v>52542</v>
       </c>
       <c r="D4" t="n">
-        <v>52215</v>
+        <v>52008</v>
       </c>
       <c r="E4" t="n">
-        <v>52339</v>
+        <v>52209</v>
       </c>
       <c r="F4" t="n">
-        <v>60</v>
+        <v>-130</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0011</v>
+        <v>-0.0025</v>
       </c>
       <c r="H4" t="n">
-        <v>882</v>
+        <v>534</v>
       </c>
       <c r="I4" t="n">
-        <v>51190</v>
+        <v>51333</v>
       </c>
       <c r="J4" t="n">
-        <v>51523.25</v>
+        <v>51298.5</v>
       </c>
       <c r="K4" t="n">
-        <v>51907.5</v>
+        <v>51898</v>
       </c>
       <c r="L4" t="n">
-        <v>52291.75</v>
+        <v>52497.5</v>
       </c>
       <c r="M4" t="n">
-        <v>52650.5</v>
+        <v>52780</v>
       </c>
       <c r="N4" t="n">
-        <v>53009.25</v>
+        <v>53062.5</v>
       </c>
       <c r="O4" t="n">
-        <v>53419</v>
+        <v>53979</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -852,20 +850,16 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
@@ -875,55 +869,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52439</v>
+        <v>52183</v>
       </c>
       <c r="C5" t="n">
-        <v>52542</v>
+        <v>52700</v>
       </c>
       <c r="D5" t="n">
-        <v>52008</v>
+        <v>52179</v>
       </c>
       <c r="E5" t="n">
-        <v>52209</v>
+        <v>52572</v>
       </c>
       <c r="F5" t="n">
-        <v>-130</v>
+        <v>363</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.007</v>
       </c>
       <c r="H5" t="n">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="I5" t="n">
-        <v>51333</v>
+        <v>51474</v>
       </c>
       <c r="J5" t="n">
-        <v>51298.5</v>
+        <v>51642</v>
       </c>
       <c r="K5" t="n">
-        <v>51898</v>
+        <v>51942</v>
       </c>
       <c r="L5" t="n">
-        <v>52497.5</v>
+        <v>52242</v>
       </c>
       <c r="M5" t="n">
-        <v>52780</v>
+        <v>52476</v>
       </c>
       <c r="N5" t="n">
-        <v>53062.5</v>
+        <v>52710</v>
       </c>
       <c r="O5" t="n">
-        <v>53979</v>
+        <v>53076</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -934,13 +932,15 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -953,59 +953,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52183</v>
+        <v>52554</v>
       </c>
       <c r="C6" t="n">
-        <v>52700</v>
+        <v>52763</v>
       </c>
       <c r="D6" t="n">
-        <v>52179</v>
+        <v>52383</v>
       </c>
       <c r="E6" t="n">
-        <v>52572</v>
+        <v>52670</v>
       </c>
       <c r="F6" t="n">
-        <v>363</v>
+        <v>98</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.007</v>
+        <v>0.0019</v>
       </c>
       <c r="H6" t="n">
-        <v>521</v>
+        <v>380</v>
       </c>
       <c r="I6" t="n">
-        <v>51474</v>
+        <v>51658</v>
       </c>
       <c r="J6" t="n">
-        <v>51642</v>
+        <v>52117.25</v>
       </c>
       <c r="K6" t="n">
-        <v>51942</v>
+        <v>52311.5</v>
       </c>
       <c r="L6" t="n">
-        <v>52242</v>
+        <v>52505.75</v>
       </c>
       <c r="M6" t="n">
-        <v>52476</v>
+        <v>52832.5</v>
       </c>
       <c r="N6" t="n">
-        <v>52710</v>
+        <v>53159.25</v>
       </c>
       <c r="O6" t="n">
-        <v>53076</v>
+        <v>53221</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1042,50 +1038,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>52554</v>
+        <v>52546</v>
       </c>
       <c r="C7" t="n">
-        <v>52763</v>
+        <v>53105</v>
       </c>
       <c r="D7" t="n">
-        <v>52383</v>
+        <v>52381</v>
       </c>
       <c r="E7" t="n">
-        <v>52670</v>
+        <v>52668</v>
       </c>
       <c r="F7" t="n">
-        <v>98</v>
+        <v>-2</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
-        <v>380</v>
+        <v>724</v>
       </c>
       <c r="I7" t="n">
-        <v>51658</v>
+        <v>52003</v>
       </c>
       <c r="J7" t="n">
-        <v>52117.25</v>
+        <v>52338.5</v>
       </c>
       <c r="K7" t="n">
-        <v>52311.5</v>
+        <v>52480</v>
       </c>
       <c r="L7" t="n">
-        <v>52505.75</v>
+        <v>52621.5</v>
       </c>
       <c r="M7" t="n">
-        <v>52832.5</v>
+        <v>52860</v>
       </c>
       <c r="N7" t="n">
-        <v>53159.25</v>
+        <v>53098.5</v>
       </c>
       <c r="O7" t="n">
-        <v>53221</v>
+        <v>53143</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1093,21 +1089,25 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1117,55 +1117,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52546</v>
+        <v>52640</v>
       </c>
       <c r="C8" t="n">
-        <v>53105</v>
+        <v>53218</v>
       </c>
       <c r="D8" t="n">
-        <v>52381</v>
+        <v>52551</v>
       </c>
       <c r="E8" t="n">
-        <v>52668</v>
+        <v>53183</v>
       </c>
       <c r="F8" t="n">
-        <v>-2</v>
+        <v>515</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0</v>
+        <v>0.0098</v>
       </c>
       <c r="H8" t="n">
-        <v>724</v>
+        <v>667</v>
       </c>
       <c r="I8" t="n">
-        <v>52003</v>
+        <v>51657</v>
       </c>
       <c r="J8" t="n">
-        <v>52338.5</v>
+        <v>51906.5</v>
       </c>
       <c r="K8" t="n">
-        <v>52480</v>
+        <v>52306</v>
       </c>
       <c r="L8" t="n">
-        <v>52621.5</v>
+        <v>52705.5</v>
       </c>
       <c r="M8" t="n">
-        <v>52860</v>
+        <v>53030</v>
       </c>
       <c r="N8" t="n">
-        <v>53098.5</v>
+        <v>53354.5</v>
       </c>
       <c r="O8" t="n">
-        <v>53143</v>
+        <v>53829</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1173,25 +1177,21 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R8" s="6" t="n">
+        <v/>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1201,59 +1201,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52640</v>
+        <v>53230</v>
       </c>
       <c r="C9" t="n">
-        <v>53218</v>
+        <v>53421</v>
       </c>
       <c r="D9" t="n">
-        <v>52551</v>
+        <v>52962</v>
       </c>
       <c r="E9" t="n">
-        <v>53183</v>
+        <v>53372</v>
       </c>
       <c r="F9" t="n">
-        <v>515</v>
+        <v>189</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0036</v>
       </c>
       <c r="H9" t="n">
-        <v>667</v>
+        <v>459</v>
       </c>
       <c r="I9" t="n">
-        <v>51657</v>
+        <v>51884</v>
       </c>
       <c r="J9" t="n">
-        <v>51906.5</v>
+        <v>52665.25</v>
       </c>
       <c r="K9" t="n">
-        <v>52306</v>
+        <v>52849.5</v>
       </c>
       <c r="L9" t="n">
-        <v>52705.5</v>
+        <v>53033.75</v>
       </c>
       <c r="M9" t="n">
-        <v>53030</v>
+        <v>53516.5</v>
       </c>
       <c r="N9" t="n">
-        <v>53354.5</v>
+        <v>53999.25</v>
       </c>
       <c r="O9" t="n">
-        <v>53829</v>
+        <v>53885</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1290,50 +1286,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53230</v>
+        <v>53405</v>
       </c>
       <c r="C10" t="n">
-        <v>53421</v>
+        <v>53656</v>
       </c>
       <c r="D10" t="n">
-        <v>52962</v>
+        <v>53076</v>
       </c>
       <c r="E10" t="n">
-        <v>53372</v>
+        <v>53197</v>
       </c>
       <c r="F10" t="n">
-        <v>189</v>
+        <v>-175</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0036</v>
+        <v>-0.0033</v>
       </c>
       <c r="H10" t="n">
-        <v>459</v>
+        <v>580</v>
       </c>
       <c r="I10" t="n">
-        <v>51884</v>
+        <v>52503</v>
       </c>
       <c r="J10" t="n">
-        <v>52665.25</v>
+        <v>53003.25</v>
       </c>
       <c r="K10" t="n">
-        <v>52849.5</v>
+        <v>53142.5</v>
       </c>
       <c r="L10" t="n">
-        <v>53033.75</v>
+        <v>53281.75</v>
       </c>
       <c r="M10" t="n">
-        <v>53516.5</v>
+        <v>53601.5</v>
       </c>
       <c r="N10" t="n">
-        <v>53999.25</v>
+        <v>53921.25</v>
       </c>
       <c r="O10" t="n">
-        <v>53885</v>
+        <v>53880</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1341,17 +1337,19 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U10" s="8" t="n">
@@ -1365,65 +1363,73 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>53405</v>
+        <v>53166</v>
       </c>
       <c r="C11" t="n">
-        <v>53656</v>
+        <v>53207</v>
       </c>
       <c r="D11" t="n">
-        <v>53076</v>
+        <v>52343</v>
       </c>
       <c r="E11" t="n">
-        <v>53197</v>
+        <v>52624</v>
       </c>
       <c r="F11" t="n">
-        <v>-175</v>
+        <v>-573</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0108</v>
       </c>
       <c r="H11" t="n">
-        <v>580</v>
+        <v>864</v>
       </c>
       <c r="I11" t="n">
-        <v>52503</v>
+        <v>52496</v>
       </c>
       <c r="J11" t="n">
-        <v>53003.25</v>
+        <v>52532.5</v>
       </c>
       <c r="K11" t="n">
-        <v>53142.5</v>
+        <v>52907</v>
       </c>
       <c r="L11" t="n">
-        <v>53281.75</v>
+        <v>53281.5</v>
       </c>
       <c r="M11" t="n">
-        <v>53601.5</v>
+        <v>53487</v>
       </c>
       <c r="N11" t="n">
-        <v>53921.25</v>
+        <v>53692.5</v>
       </c>
       <c r="O11" t="n">
-        <v>53880</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
+        <v>54236</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
@@ -1431,10 +1437,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1449,76 +1453,70 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>53166</v>
+        <v>52541</v>
       </c>
       <c r="C12" t="n">
-        <v>53207</v>
+        <v>52865</v>
       </c>
       <c r="D12" t="n">
-        <v>52343</v>
+        <v>52501</v>
       </c>
       <c r="E12" t="n">
-        <v>52624</v>
+        <v>52761</v>
       </c>
       <c r="F12" t="n">
-        <v>-573</v>
+        <v>137</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0108</v>
+        <v>0.0026</v>
       </c>
       <c r="H12" t="n">
-        <v>864</v>
+        <v>364</v>
       </c>
       <c r="I12" t="n">
-        <v>52496</v>
+        <v>51479</v>
       </c>
       <c r="J12" t="n">
-        <v>52532.5</v>
+        <v>51684.5</v>
       </c>
       <c r="K12" t="n">
-        <v>52907</v>
+        <v>52192</v>
       </c>
       <c r="L12" t="n">
-        <v>53281.5</v>
+        <v>52699.5</v>
       </c>
       <c r="M12" t="n">
-        <v>53487</v>
+        <v>53056</v>
       </c>
       <c r="N12" t="n">
-        <v>53692.5</v>
+        <v>53412.5</v>
       </c>
       <c r="O12" t="n">
-        <v>54236</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>54071</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1537,57 +1535,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>52541</v>
+        <v>52753</v>
       </c>
       <c r="C13" t="n">
-        <v>52865</v>
+        <v>52992</v>
       </c>
       <c r="D13" t="n">
-        <v>52501</v>
+        <v>52506</v>
       </c>
       <c r="E13" t="n">
-        <v>52761</v>
+        <v>52906</v>
       </c>
       <c r="F13" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0027</v>
       </c>
       <c r="H13" t="n">
-        <v>364</v>
+        <v>486</v>
       </c>
       <c r="I13" t="n">
-        <v>51479</v>
+        <v>52137</v>
       </c>
       <c r="J13" t="n">
-        <v>51684.5</v>
+        <v>52436</v>
       </c>
       <c r="K13" t="n">
-        <v>52192</v>
+        <v>52579</v>
       </c>
       <c r="L13" t="n">
-        <v>52699.5</v>
+        <v>52722</v>
       </c>
       <c r="M13" t="n">
-        <v>53056</v>
+        <v>52943</v>
       </c>
       <c r="N13" t="n">
-        <v>53412.5</v>
+        <v>53164</v>
       </c>
       <c r="O13" t="n">
-        <v>54071</v>
+        <v>53229</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1595,16 +1593,20 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1617,59 +1619,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>52753</v>
+        <v>52844</v>
       </c>
       <c r="C14" t="n">
-        <v>52992</v>
+        <v>53113</v>
       </c>
       <c r="D14" t="n">
-        <v>52506</v>
+        <v>52603</v>
       </c>
       <c r="E14" t="n">
-        <v>52906</v>
+        <v>52764</v>
       </c>
       <c r="F14" t="n">
-        <v>145</v>
+        <v>-142</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0027</v>
       </c>
       <c r="H14" t="n">
-        <v>486</v>
+        <v>510</v>
       </c>
       <c r="I14" t="n">
-        <v>52137</v>
+        <v>52020</v>
       </c>
       <c r="J14" t="n">
-        <v>52436</v>
+        <v>52498.5</v>
       </c>
       <c r="K14" t="n">
-        <v>52579</v>
+        <v>52663</v>
       </c>
       <c r="L14" t="n">
-        <v>52722</v>
+        <v>52827.5</v>
       </c>
       <c r="M14" t="n">
-        <v>52943</v>
+        <v>53149</v>
       </c>
       <c r="N14" t="n">
-        <v>53164</v>
+        <v>53470.5</v>
       </c>
       <c r="O14" t="n">
-        <v>53229</v>
+        <v>53478</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1682,15 +1680,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1703,55 +1699,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52844</v>
+        <v>52731</v>
       </c>
       <c r="C15" t="n">
-        <v>53113</v>
+        <v>52981</v>
       </c>
       <c r="D15" t="n">
-        <v>52603</v>
+        <v>52255</v>
       </c>
       <c r="E15" t="n">
-        <v>52764</v>
+        <v>52791</v>
       </c>
       <c r="F15" t="n">
-        <v>-142</v>
+        <v>27</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0005</v>
       </c>
       <c r="H15" t="n">
-        <v>510</v>
+        <v>726</v>
       </c>
       <c r="I15" t="n">
-        <v>52020</v>
+        <v>52093</v>
       </c>
       <c r="J15" t="n">
-        <v>52498.5</v>
+        <v>52207</v>
       </c>
       <c r="K15" t="n">
-        <v>52663</v>
+        <v>52509</v>
       </c>
       <c r="L15" t="n">
-        <v>52827.5</v>
+        <v>52811</v>
       </c>
       <c r="M15" t="n">
-        <v>53149</v>
+        <v>53019</v>
       </c>
       <c r="N15" t="n">
-        <v>53470.5</v>
+        <v>53227</v>
       </c>
       <c r="O15" t="n">
-        <v>53478</v>
+        <v>53623</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1785,57 +1785,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>52731</v>
+        <v>52792</v>
       </c>
       <c r="C16" t="n">
-        <v>52981</v>
+        <v>53088</v>
       </c>
       <c r="D16" t="n">
-        <v>52255</v>
+        <v>52680</v>
       </c>
       <c r="E16" t="n">
-        <v>52791</v>
+        <v>52900</v>
       </c>
       <c r="F16" t="n">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0021</v>
       </c>
       <c r="H16" t="n">
-        <v>726</v>
+        <v>408</v>
       </c>
       <c r="I16" t="n">
-        <v>52093</v>
+        <v>51529</v>
       </c>
       <c r="J16" t="n">
-        <v>52207</v>
+        <v>52151.5</v>
       </c>
       <c r="K16" t="n">
-        <v>52509</v>
+        <v>52428</v>
       </c>
       <c r="L16" t="n">
-        <v>52811</v>
+        <v>52704.5</v>
       </c>
       <c r="M16" t="n">
-        <v>53019</v>
+        <v>53154</v>
       </c>
       <c r="N16" t="n">
-        <v>53227</v>
+        <v>53603.5</v>
       </c>
       <c r="O16" t="n">
-        <v>53623</v>
+        <v>53707</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1843,14 +1843,12 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1867,59 +1865,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52792</v>
+        <v>52919</v>
       </c>
       <c r="C17" t="n">
-        <v>53088</v>
+        <v>53108</v>
       </c>
       <c r="D17" t="n">
-        <v>52680</v>
+        <v>52607</v>
       </c>
       <c r="E17" t="n">
-        <v>52900</v>
+        <v>52786</v>
       </c>
       <c r="F17" t="n">
-        <v>109</v>
+        <v>-114</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0022</v>
       </c>
       <c r="H17" t="n">
-        <v>408</v>
+        <v>501</v>
       </c>
       <c r="I17" t="n">
-        <v>51529</v>
+        <v>52272</v>
       </c>
       <c r="J17" t="n">
-        <v>52151.5</v>
+        <v>52500</v>
       </c>
       <c r="K17" t="n">
-        <v>52428</v>
+        <v>52696</v>
       </c>
       <c r="L17" t="n">
-        <v>52704.5</v>
+        <v>52892</v>
       </c>
       <c r="M17" t="n">
-        <v>53154</v>
+        <v>53104</v>
       </c>
       <c r="N17" t="n">
-        <v>53603.5</v>
+        <v>53316</v>
       </c>
       <c r="O17" t="n">
-        <v>53707</v>
+        <v>53496</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1927,16 +1921,20 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1949,65 +1947,71 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52919</v>
+        <v>52778</v>
       </c>
       <c r="C18" t="n">
-        <v>53108</v>
+        <v>52835</v>
       </c>
       <c r="D18" t="n">
-        <v>52607</v>
+        <v>52174</v>
       </c>
       <c r="E18" t="n">
-        <v>52786</v>
+        <v>52375</v>
       </c>
       <c r="F18" t="n">
-        <v>-114</v>
+        <v>-411</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0078</v>
       </c>
       <c r="H18" t="n">
-        <v>501</v>
+        <v>661</v>
       </c>
       <c r="I18" t="n">
-        <v>52272</v>
+        <v>52106</v>
       </c>
       <c r="J18" t="n">
-        <v>52500</v>
+        <v>52249.25</v>
       </c>
       <c r="K18" t="n">
-        <v>52696</v>
+        <v>52535.5</v>
       </c>
       <c r="L18" t="n">
-        <v>52892</v>
+        <v>52821.75</v>
       </c>
       <c r="M18" t="n">
-        <v>53104</v>
+        <v>53036.5</v>
       </c>
       <c r="N18" t="n">
-        <v>53316</v>
+        <v>53251.25</v>
       </c>
       <c r="O18" t="n">
-        <v>53496</v>
+        <v>53609</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S18" s="10" t="inlineStr">
@@ -2015,10 +2019,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2033,69 +2035,67 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>52778</v>
+        <v>52300</v>
       </c>
       <c r="C19" t="n">
-        <v>52835</v>
+        <v>52633</v>
       </c>
       <c r="D19" t="n">
-        <v>52174</v>
+        <v>51999</v>
       </c>
       <c r="E19" t="n">
-        <v>52375</v>
+        <v>52073</v>
       </c>
       <c r="F19" t="n">
-        <v>-411</v>
+        <v>-302</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0078</v>
+        <v>-0.0058</v>
       </c>
       <c r="H19" t="n">
-        <v>661</v>
+        <v>634</v>
       </c>
       <c r="I19" t="n">
-        <v>52106</v>
+        <v>51513</v>
       </c>
       <c r="J19" t="n">
-        <v>52249.25</v>
+        <v>51649.25</v>
       </c>
       <c r="K19" t="n">
-        <v>52535.5</v>
+        <v>52044.5</v>
       </c>
       <c r="L19" t="n">
-        <v>52821.75</v>
+        <v>52439.75</v>
       </c>
       <c r="M19" t="n">
-        <v>53036.5</v>
+        <v>52705.5</v>
       </c>
       <c r="N19" t="n">
-        <v>53251.25</v>
+        <v>52971.25</v>
       </c>
       <c r="O19" t="n">
-        <v>53609</v>
+        <v>53496</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
@@ -2126,50 +2126,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>52300</v>
+        <v>52091</v>
       </c>
       <c r="C20" t="n">
-        <v>52633</v>
+        <v>52590</v>
       </c>
       <c r="D20" t="n">
-        <v>51999</v>
+        <v>52035</v>
       </c>
       <c r="E20" t="n">
-        <v>52073</v>
+        <v>52443</v>
       </c>
       <c r="F20" t="n">
-        <v>-302</v>
+        <v>370</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.0071</v>
       </c>
       <c r="H20" t="n">
-        <v>634</v>
+        <v>555</v>
       </c>
       <c r="I20" t="n">
-        <v>51513</v>
+        <v>51365</v>
       </c>
       <c r="J20" t="n">
-        <v>51649.25</v>
+        <v>51317.5</v>
       </c>
       <c r="K20" t="n">
-        <v>52044.5</v>
+        <v>51756</v>
       </c>
       <c r="L20" t="n">
-        <v>52439.75</v>
+        <v>52194.5</v>
       </c>
       <c r="M20" t="n">
-        <v>52705.5</v>
+        <v>52390</v>
       </c>
       <c r="N20" t="n">
-        <v>52971.25</v>
+        <v>52585.5</v>
       </c>
       <c r="O20" t="n">
-        <v>53496</v>
+        <v>53267</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2177,21 +2177,23 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2203,57 +2205,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>52091</v>
+        <v>52431</v>
       </c>
       <c r="C21" t="n">
-        <v>52590</v>
+        <v>52721</v>
       </c>
       <c r="D21" t="n">
-        <v>52035</v>
+        <v>52262</v>
       </c>
       <c r="E21" t="n">
-        <v>52443</v>
+        <v>52449</v>
       </c>
       <c r="F21" t="n">
-        <v>370</v>
+        <v>6</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0001</v>
       </c>
       <c r="H21" t="n">
-        <v>555</v>
+        <v>459</v>
       </c>
       <c r="I21" t="n">
-        <v>51365</v>
+        <v>51480</v>
       </c>
       <c r="J21" t="n">
-        <v>51317.5</v>
+        <v>51953.25</v>
       </c>
       <c r="K21" t="n">
-        <v>51756</v>
+        <v>52165.5</v>
       </c>
       <c r="L21" t="n">
-        <v>52194.5</v>
+        <v>52377.75</v>
       </c>
       <c r="M21" t="n">
-        <v>52390</v>
+        <v>52720.5</v>
       </c>
       <c r="N21" t="n">
-        <v>52585.5</v>
+        <v>53063.25</v>
       </c>
       <c r="O21" t="n">
-        <v>53267</v>
+        <v>53145</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2266,19 +2268,17 @@
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
@@ -2287,88 +2287,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>52431</v>
+        <v>52430</v>
       </c>
       <c r="C22" t="n">
-        <v>52721</v>
+        <v>52515</v>
       </c>
       <c r="D22" t="n">
-        <v>52262</v>
+        <v>51720</v>
       </c>
       <c r="E22" t="n">
-        <v>52449</v>
+        <v>51894</v>
       </c>
       <c r="F22" t="n">
-        <v>6</v>
+        <v>-555</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0106</v>
       </c>
       <c r="H22" t="n">
-        <v>459</v>
+        <v>795</v>
       </c>
       <c r="I22" t="n">
-        <v>51480</v>
+        <v>51803</v>
       </c>
       <c r="J22" t="n">
-        <v>51953.25</v>
+        <v>51968.75</v>
       </c>
       <c r="K22" t="n">
-        <v>52165.5</v>
+        <v>52219.5</v>
       </c>
       <c r="L22" t="n">
-        <v>52377.75</v>
+        <v>52470.25</v>
       </c>
       <c r="M22" t="n">
-        <v>52720.5</v>
+        <v>52678.5</v>
       </c>
       <c r="N22" t="n">
-        <v>53063.25</v>
+        <v>52886.75</v>
       </c>
       <c r="O22" t="n">
-        <v>53145</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
+        <v>53180</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
       <c r="U22" s="8" t="n">
         <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W22" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
@@ -2376,74 +2376,70 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>52430</v>
+        <v>51920</v>
       </c>
       <c r="C23" t="n">
-        <v>52515</v>
+        <v>52314</v>
       </c>
       <c r="D23" t="n">
-        <v>51720</v>
+        <v>51846</v>
       </c>
       <c r="E23" t="n">
-        <v>51894</v>
+        <v>52124</v>
       </c>
       <c r="F23" t="n">
-        <v>-555</v>
+        <v>230</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0044</v>
       </c>
       <c r="H23" t="n">
-        <v>795</v>
+        <v>468</v>
       </c>
       <c r="I23" t="n">
-        <v>51803</v>
+        <v>50925</v>
       </c>
       <c r="J23" t="n">
-        <v>51968.75</v>
+        <v>50987.25</v>
       </c>
       <c r="K23" t="n">
-        <v>52219.5</v>
+        <v>51496.5</v>
       </c>
       <c r="L23" t="n">
-        <v>52470.25</v>
+        <v>52005.75</v>
       </c>
       <c r="M23" t="n">
-        <v>52678.5</v>
+        <v>52291.5</v>
       </c>
       <c r="N23" t="n">
-        <v>52886.75</v>
+        <v>52577.25</v>
       </c>
       <c r="O23" t="n">
-        <v>53180</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
+        <v>53310</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
@@ -2455,55 +2451,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>51920</v>
+        <v>52299</v>
       </c>
       <c r="C24" t="n">
-        <v>52314</v>
+        <v>52790</v>
       </c>
       <c r="D24" t="n">
-        <v>51846</v>
+        <v>52173</v>
       </c>
       <c r="E24" t="n">
-        <v>52124</v>
+        <v>52382</v>
       </c>
       <c r="F24" t="n">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0049</v>
       </c>
       <c r="H24" t="n">
-        <v>468</v>
+        <v>617</v>
       </c>
       <c r="I24" t="n">
-        <v>50925</v>
+        <v>51378</v>
       </c>
       <c r="J24" t="n">
-        <v>50987.25</v>
+        <v>51678</v>
       </c>
       <c r="K24" t="n">
-        <v>51496.5</v>
+        <v>51890</v>
       </c>
       <c r="L24" t="n">
-        <v>52005.75</v>
+        <v>52102</v>
       </c>
       <c r="M24" t="n">
-        <v>52291.5</v>
+        <v>52358</v>
       </c>
       <c r="N24" t="n">
-        <v>52577.25</v>
+        <v>52614</v>
       </c>
       <c r="O24" t="n">
-        <v>53310</v>
+        <v>52782</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2516,19 +2516,23 @@
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W24" s="11" t="inlineStr">
         <is>
@@ -2537,57 +2541,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>52299</v>
+        <v>52405</v>
       </c>
       <c r="C25" t="n">
-        <v>52790</v>
+        <v>53105</v>
       </c>
       <c r="D25" t="n">
-        <v>52173</v>
+        <v>52290</v>
       </c>
       <c r="E25" t="n">
-        <v>52382</v>
+        <v>52944</v>
       </c>
       <c r="F25" t="n">
-        <v>258</v>
+        <v>562</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0107</v>
       </c>
       <c r="H25" t="n">
-        <v>617</v>
+        <v>815</v>
       </c>
       <c r="I25" t="n">
-        <v>51378</v>
+        <v>51556</v>
       </c>
       <c r="J25" t="n">
-        <v>51678</v>
+        <v>51715.25</v>
       </c>
       <c r="K25" t="n">
-        <v>51890</v>
+        <v>52073.5</v>
       </c>
       <c r="L25" t="n">
-        <v>52102</v>
+        <v>52431.75</v>
       </c>
       <c r="M25" t="n">
-        <v>52358</v>
+        <v>52690.5</v>
       </c>
       <c r="N25" t="n">
-        <v>52614</v>
+        <v>52949.25</v>
       </c>
       <c r="O25" t="n">
-        <v>52782</v>
+        <v>53407</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2605,18 +2609,16 @@
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V25" s="8" t="n">
+        <v/>
       </c>
       <c r="W25" s="11" t="inlineStr">
         <is>
@@ -2632,74 +2634,76 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>52405</v>
+        <v>52915</v>
       </c>
       <c r="C26" t="n">
-        <v>53105</v>
+        <v>53033</v>
       </c>
       <c r="D26" t="n">
-        <v>52290</v>
+        <v>51630</v>
       </c>
       <c r="E26" t="n">
-        <v>52944</v>
+        <v>51765</v>
       </c>
       <c r="F26" t="n">
-        <v>562</v>
+        <v>-1179</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0223</v>
       </c>
       <c r="H26" t="n">
-        <v>815</v>
+        <v>1403</v>
       </c>
       <c r="I26" t="n">
-        <v>51556</v>
+        <v>51475</v>
       </c>
       <c r="J26" t="n">
-        <v>51715.25</v>
+        <v>52252.25</v>
       </c>
       <c r="K26" t="n">
-        <v>52073.5</v>
+        <v>52536.5</v>
       </c>
       <c r="L26" t="n">
-        <v>52431.75</v>
+        <v>52820.75</v>
       </c>
       <c r="M26" t="n">
-        <v>52690.5</v>
+        <v>53351.5</v>
       </c>
       <c r="N26" t="n">
-        <v>52949.25</v>
+        <v>53882.25</v>
       </c>
       <c r="O26" t="n">
-        <v>53407</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
+        <v>53920</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2709,83 +2713,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>52915</v>
+        <v>51759</v>
       </c>
       <c r="C27" t="n">
-        <v>53033</v>
+        <v>52484</v>
       </c>
       <c r="D27" t="n">
-        <v>51630</v>
+        <v>51732</v>
       </c>
       <c r="E27" t="n">
-        <v>51765</v>
+        <v>52380</v>
       </c>
       <c r="F27" t="n">
-        <v>-1179</v>
+        <v>615</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0119</v>
       </c>
       <c r="H27" t="n">
-        <v>1403</v>
+        <v>752</v>
       </c>
       <c r="I27" t="n">
-        <v>51475</v>
+        <v>50227</v>
       </c>
       <c r="J27" t="n">
-        <v>52252.25</v>
+        <v>50078.75</v>
       </c>
       <c r="K27" t="n">
-        <v>52536.5</v>
+        <v>51063.5</v>
       </c>
       <c r="L27" t="n">
-        <v>52820.75</v>
+        <v>52048.25</v>
       </c>
       <c r="M27" t="n">
-        <v>53351.5</v>
+        <v>52466.5</v>
       </c>
       <c r="N27" t="n">
-        <v>53882.25</v>
+        <v>52884.75</v>
       </c>
       <c r="O27" t="n">
-        <v>53920</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
+        <v>54436</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
       <c r="U27" s="8" t="n">
         <v/>
       </c>
@@ -2797,55 +2793,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>51759</v>
+        <v>52395</v>
       </c>
       <c r="C28" t="n">
-        <v>52484</v>
+        <v>52772</v>
       </c>
       <c r="D28" t="n">
-        <v>51732</v>
+        <v>52124</v>
       </c>
       <c r="E28" t="n">
-        <v>52380</v>
+        <v>52635</v>
       </c>
       <c r="F28" t="n">
-        <v>615</v>
+        <v>255</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0119</v>
+        <v>0.0049</v>
       </c>
       <c r="H28" t="n">
-        <v>752</v>
+        <v>648</v>
       </c>
       <c r="I28" t="n">
-        <v>50227</v>
+        <v>50980</v>
       </c>
       <c r="J28" t="n">
-        <v>50078.75</v>
+        <v>51764</v>
       </c>
       <c r="K28" t="n">
-        <v>51063.5</v>
+        <v>52004</v>
       </c>
       <c r="L28" t="n">
-        <v>52048.25</v>
+        <v>52244</v>
       </c>
       <c r="M28" t="n">
-        <v>52466.5</v>
+        <v>52756</v>
       </c>
       <c r="N28" t="n">
-        <v>52884.75</v>
+        <v>53268</v>
       </c>
       <c r="O28" t="n">
-        <v>54436</v>
+        <v>53236</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2879,57 +2879,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>52395</v>
+        <v>52780</v>
       </c>
       <c r="C29" t="n">
-        <v>52772</v>
+        <v>53414</v>
       </c>
       <c r="D29" t="n">
-        <v>52124</v>
+        <v>52777</v>
       </c>
       <c r="E29" t="n">
-        <v>52635</v>
+        <v>53334</v>
       </c>
       <c r="F29" t="n">
-        <v>255</v>
+        <v>699</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0133</v>
       </c>
       <c r="H29" t="n">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="I29" t="n">
-        <v>50980</v>
+        <v>51476</v>
       </c>
       <c r="J29" t="n">
-        <v>51764</v>
+        <v>52080.5</v>
       </c>
       <c r="K29" t="n">
-        <v>52004</v>
+        <v>52311</v>
       </c>
       <c r="L29" t="n">
-        <v>52244</v>
+        <v>52541.5</v>
       </c>
       <c r="M29" t="n">
-        <v>52756</v>
+        <v>52959</v>
       </c>
       <c r="N29" t="n">
-        <v>53268</v>
+        <v>53376.5</v>
       </c>
       <c r="O29" t="n">
-        <v>53236</v>
+        <v>53420</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2947,11 +2947,13 @@
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2970,50 +2972,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>52780</v>
+        <v>53381</v>
       </c>
       <c r="C30" t="n">
-        <v>53414</v>
+        <v>54423</v>
       </c>
       <c r="D30" t="n">
-        <v>52777</v>
+        <v>53267</v>
       </c>
       <c r="E30" t="n">
-        <v>53334</v>
+        <v>54268</v>
       </c>
       <c r="F30" t="n">
-        <v>699</v>
+        <v>934</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0175</v>
       </c>
       <c r="H30" t="n">
-        <v>637</v>
+        <v>1156</v>
       </c>
       <c r="I30" t="n">
-        <v>51476</v>
+        <v>52140</v>
       </c>
       <c r="J30" t="n">
-        <v>52080.5</v>
+        <v>52816.25</v>
       </c>
       <c r="K30" t="n">
-        <v>52311</v>
+        <v>53015.5</v>
       </c>
       <c r="L30" t="n">
-        <v>52541.5</v>
+        <v>53214.75</v>
       </c>
       <c r="M30" t="n">
-        <v>52959</v>
+        <v>53652.5</v>
       </c>
       <c r="N30" t="n">
-        <v>53376.5</v>
+        <v>54090.25</v>
       </c>
       <c r="O30" t="n">
-        <v>53420</v>
+        <v>54051</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3039,67 +3041,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W30" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W30" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>53381</v>
+        <v>54369</v>
       </c>
       <c r="C31" t="n">
-        <v>54423</v>
+        <v>54884</v>
       </c>
       <c r="D31" t="n">
-        <v>53267</v>
+        <v>54342</v>
       </c>
       <c r="E31" t="n">
-        <v>54268</v>
+        <v>54494</v>
       </c>
       <c r="F31" t="n">
-        <v>934</v>
+        <v>226</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0042</v>
       </c>
       <c r="H31" t="n">
-        <v>1156</v>
+        <v>542</v>
       </c>
       <c r="I31" t="n">
-        <v>52140</v>
+        <v>52111</v>
       </c>
       <c r="J31" t="n">
-        <v>52816.25</v>
+        <v>53323.5</v>
       </c>
       <c r="K31" t="n">
-        <v>53015.5</v>
+        <v>53690</v>
       </c>
       <c r="L31" t="n">
-        <v>53214.75</v>
+        <v>54056.5</v>
       </c>
       <c r="M31" t="n">
-        <v>53652.5</v>
+        <v>54846</v>
       </c>
       <c r="N31" t="n">
-        <v>54090.25</v>
+        <v>55635.5</v>
       </c>
       <c r="O31" t="n">
-        <v>54051</v>
+        <v>55579</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3117,18 +3117,14 @@
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v/>
       </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
@@ -3140,70 +3136,72 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>54369</v>
+        <v>54555</v>
       </c>
       <c r="C32" t="n">
-        <v>54884</v>
+        <v>54678</v>
       </c>
       <c r="D32" t="n">
-        <v>54342</v>
+        <v>53952</v>
       </c>
       <c r="E32" t="n">
-        <v>54494</v>
+        <v>54013</v>
       </c>
       <c r="F32" t="n">
-        <v>226</v>
+        <v>-481</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>542</v>
+        <v>726</v>
       </c>
       <c r="I32" t="n">
-        <v>52111</v>
+        <v>53800</v>
       </c>
       <c r="J32" t="n">
-        <v>53323.5</v>
+        <v>53892.5</v>
       </c>
       <c r="K32" t="n">
-        <v>53690</v>
+        <v>54223</v>
       </c>
       <c r="L32" t="n">
-        <v>54056.5</v>
+        <v>54553.5</v>
       </c>
       <c r="M32" t="n">
-        <v>54846</v>
+        <v>54765</v>
       </c>
       <c r="N32" t="n">
-        <v>55635.5</v>
+        <v>54976.5</v>
       </c>
       <c r="O32" t="n">
-        <v>55579</v>
+        <v>55426</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
+      <c r="Q32" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
@@ -3215,72 +3213,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>54555</v>
+        <v>54040</v>
       </c>
       <c r="C33" t="n">
-        <v>54678</v>
+        <v>54202</v>
       </c>
       <c r="D33" t="n">
-        <v>53952</v>
+        <v>53879</v>
       </c>
       <c r="E33" t="n">
-        <v>54013</v>
+        <v>54152</v>
       </c>
       <c r="F33" t="n">
-        <v>-481</v>
+        <v>139</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0026</v>
       </c>
       <c r="H33" t="n">
-        <v>726</v>
+        <v>323</v>
       </c>
       <c r="I33" t="n">
-        <v>53800</v>
+        <v>53226</v>
       </c>
       <c r="J33" t="n">
-        <v>53892.5</v>
+        <v>53136</v>
       </c>
       <c r="K33" t="n">
-        <v>54223</v>
+        <v>53650</v>
       </c>
       <c r="L33" t="n">
-        <v>54553.5</v>
+        <v>54164</v>
       </c>
       <c r="M33" t="n">
-        <v>54765</v>
+        <v>54376</v>
       </c>
       <c r="N33" t="n">
-        <v>54976.5</v>
+        <v>54588</v>
       </c>
       <c r="O33" t="n">
-        <v>55426</v>
+        <v>55404</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3299,57 +3297,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>54040</v>
+        <v>54133</v>
       </c>
       <c r="C34" t="n">
-        <v>54202</v>
+        <v>54170</v>
       </c>
       <c r="D34" t="n">
-        <v>53879</v>
+        <v>53952</v>
       </c>
       <c r="E34" t="n">
-        <v>54152</v>
+        <v>54063</v>
       </c>
       <c r="F34" t="n">
-        <v>139</v>
+        <v>-89</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0016</v>
       </c>
       <c r="H34" t="n">
-        <v>323</v>
+        <v>218</v>
       </c>
       <c r="I34" t="n">
-        <v>53226</v>
+        <v>53556</v>
       </c>
       <c r="J34" t="n">
-        <v>53136</v>
+        <v>53884.75</v>
       </c>
       <c r="K34" t="n">
-        <v>53650</v>
+        <v>53990.5</v>
       </c>
       <c r="L34" t="n">
-        <v>54164</v>
+        <v>54096.25</v>
       </c>
       <c r="M34" t="n">
-        <v>54376</v>
+        <v>54313.5</v>
       </c>
       <c r="N34" t="n">
-        <v>54588</v>
+        <v>54530.75</v>
       </c>
       <c r="O34" t="n">
-        <v>55404</v>
+        <v>54525</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3357,8 +3355,10 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
@@ -3388,56 +3388,58 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>54133</v>
+        <v>54049</v>
       </c>
       <c r="C35" t="n">
-        <v>54170</v>
+        <v>54336</v>
       </c>
       <c r="D35" t="n">
-        <v>53952</v>
+        <v>53855</v>
       </c>
       <c r="E35" t="n">
-        <v>54063</v>
+        <v>53880</v>
       </c>
       <c r="F35" t="n">
-        <v>-89</v>
+        <v>-183</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0034</v>
       </c>
       <c r="H35" t="n">
-        <v>218</v>
+        <v>481</v>
       </c>
       <c r="I35" t="n">
-        <v>53556</v>
+        <v>53734</v>
       </c>
       <c r="J35" t="n">
-        <v>53884.75</v>
+        <v>53846</v>
       </c>
       <c r="K35" t="n">
-        <v>53990.5</v>
+        <v>53954</v>
       </c>
       <c r="L35" t="n">
-        <v>54096.25</v>
+        <v>54062</v>
       </c>
       <c r="M35" t="n">
-        <v>54313.5</v>
+        <v>54172</v>
       </c>
       <c r="N35" t="n">
-        <v>54530.75</v>
+        <v>54282</v>
       </c>
       <c r="O35" t="n">
-        <v>54525</v>
+        <v>54388</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
@@ -3446,14 +3448,18 @@
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3472,78 +3478,72 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>54049</v>
+        <v>53903</v>
       </c>
       <c r="C36" t="n">
-        <v>54336</v>
+        <v>54150</v>
       </c>
       <c r="D36" t="n">
-        <v>53855</v>
+        <v>53830</v>
       </c>
       <c r="E36" t="n">
-        <v>53880</v>
+        <v>53871</v>
       </c>
       <c r="F36" t="n">
-        <v>-183</v>
+        <v>-9</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0002</v>
       </c>
       <c r="H36" t="n">
-        <v>481</v>
+        <v>320</v>
       </c>
       <c r="I36" t="n">
-        <v>53734</v>
+        <v>53374</v>
       </c>
       <c r="J36" t="n">
-        <v>53846</v>
+        <v>53291.25</v>
       </c>
       <c r="K36" t="n">
-        <v>53954</v>
+        <v>53639.5</v>
       </c>
       <c r="L36" t="n">
-        <v>54062</v>
+        <v>53987.75</v>
       </c>
       <c r="M36" t="n">
-        <v>54172</v>
+        <v>54120.5</v>
       </c>
       <c r="N36" t="n">
-        <v>54282</v>
+        <v>54253.25</v>
       </c>
       <c r="O36" t="n">
-        <v>54388</v>
+        <v>54817</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3555,57 +3555,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>53903</v>
+        <v>53905</v>
       </c>
       <c r="C37" t="n">
-        <v>54150</v>
+        <v>54149</v>
       </c>
       <c r="D37" t="n">
-        <v>53830</v>
+        <v>53715</v>
       </c>
       <c r="E37" t="n">
-        <v>53871</v>
+        <v>53935</v>
       </c>
       <c r="F37" t="n">
-        <v>-9</v>
+        <v>64</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0012</v>
       </c>
       <c r="H37" t="n">
-        <v>320</v>
+        <v>434</v>
       </c>
       <c r="I37" t="n">
-        <v>53374</v>
+        <v>53510</v>
       </c>
       <c r="J37" t="n">
-        <v>53291.25</v>
+        <v>53491.5</v>
       </c>
       <c r="K37" t="n">
-        <v>53639.5</v>
+        <v>53711</v>
       </c>
       <c r="L37" t="n">
-        <v>53987.75</v>
+        <v>53930.5</v>
       </c>
       <c r="M37" t="n">
-        <v>54120.5</v>
+        <v>54031</v>
       </c>
       <c r="N37" t="n">
-        <v>54253.25</v>
+        <v>54131.5</v>
       </c>
       <c r="O37" t="n">
-        <v>54817</v>
+        <v>54470</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3616,9 +3616,9 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
@@ -3626,8 +3626,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U37" s="8" t="n">
-        <v/>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3639,57 +3641,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>53905</v>
+        <v>53961</v>
       </c>
       <c r="C38" t="n">
-        <v>54149</v>
+        <v>53999</v>
       </c>
       <c r="D38" t="n">
-        <v>53715</v>
+        <v>53745</v>
       </c>
       <c r="E38" t="n">
-        <v>53935</v>
+        <v>53807</v>
       </c>
       <c r="F38" t="n">
-        <v>64</v>
+        <v>-128</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0024</v>
       </c>
       <c r="H38" t="n">
-        <v>434</v>
+        <v>254</v>
       </c>
       <c r="I38" t="n">
-        <v>53510</v>
+        <v>53281</v>
       </c>
       <c r="J38" t="n">
-        <v>53491.5</v>
+        <v>53502.5</v>
       </c>
       <c r="K38" t="n">
-        <v>53711</v>
+        <v>53718</v>
       </c>
       <c r="L38" t="n">
-        <v>53930.5</v>
+        <v>53933.5</v>
       </c>
       <c r="M38" t="n">
-        <v>54031</v>
+        <v>54152</v>
       </c>
       <c r="N38" t="n">
-        <v>54131.5</v>
+        <v>54370.5</v>
       </c>
       <c r="O38" t="n">
-        <v>54470</v>
+        <v>54583</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3697,23 +3699,21 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3732,60 +3732,64 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>53961</v>
+        <v>53790</v>
       </c>
       <c r="C39" t="n">
-        <v>53999</v>
+        <v>53840</v>
       </c>
       <c r="D39" t="n">
-        <v>53745</v>
+        <v>53464</v>
       </c>
       <c r="E39" t="n">
-        <v>53807</v>
+        <v>53544</v>
       </c>
       <c r="F39" t="n">
-        <v>-128</v>
+        <v>-263</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0049</v>
       </c>
       <c r="H39" t="n">
-        <v>254</v>
+        <v>376</v>
       </c>
       <c r="I39" t="n">
-        <v>53281</v>
+        <v>53491</v>
       </c>
       <c r="J39" t="n">
-        <v>53502.5</v>
+        <v>53520.5</v>
       </c>
       <c r="K39" t="n">
-        <v>53718</v>
+        <v>53680</v>
       </c>
       <c r="L39" t="n">
-        <v>53933.5</v>
+        <v>53839.5</v>
       </c>
       <c r="M39" t="n">
-        <v>54152</v>
+        <v>53934</v>
       </c>
       <c r="N39" t="n">
-        <v>54370.5</v>
+        <v>54028.5</v>
       </c>
       <c r="O39" t="n">
-        <v>54583</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
+        <v>54253</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
@@ -3809,71 +3813,67 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>53790</v>
+        <v>53501</v>
       </c>
       <c r="C40" t="n">
-        <v>53840</v>
+        <v>53594</v>
       </c>
       <c r="D40" t="n">
-        <v>53464</v>
+        <v>53311</v>
       </c>
       <c r="E40" t="n">
-        <v>53544</v>
+        <v>53403</v>
       </c>
       <c r="F40" t="n">
-        <v>-263</v>
+        <v>-141</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0026</v>
       </c>
       <c r="H40" t="n">
-        <v>376</v>
+        <v>283</v>
       </c>
       <c r="I40" t="n">
-        <v>53491</v>
+        <v>53088</v>
       </c>
       <c r="J40" t="n">
-        <v>53520.5</v>
+        <v>53114</v>
       </c>
       <c r="K40" t="n">
-        <v>53680</v>
+        <v>53356</v>
       </c>
       <c r="L40" t="n">
-        <v>53839.5</v>
+        <v>53598</v>
       </c>
       <c r="M40" t="n">
-        <v>53934</v>
+        <v>53732</v>
       </c>
       <c r="N40" t="n">
-        <v>54028.5</v>
+        <v>53866</v>
       </c>
       <c r="O40" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q40" s="6" t="inlineStr">
+        <v>54216</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
@@ -3904,50 +3904,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>53501</v>
+        <v>53408</v>
       </c>
       <c r="C41" t="n">
-        <v>53594</v>
+        <v>53780</v>
       </c>
       <c r="D41" t="n">
-        <v>53311</v>
+        <v>53337</v>
       </c>
       <c r="E41" t="n">
-        <v>53403</v>
+        <v>53530</v>
       </c>
       <c r="F41" t="n">
-        <v>-141</v>
+        <v>127</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0026</v>
+        <v>0.0024</v>
       </c>
       <c r="H41" t="n">
-        <v>283</v>
+        <v>443</v>
       </c>
       <c r="I41" t="n">
-        <v>53088</v>
+        <v>53028</v>
       </c>
       <c r="J41" t="n">
-        <v>53114</v>
+        <v>53095.25</v>
       </c>
       <c r="K41" t="n">
-        <v>53356</v>
+        <v>53261.5</v>
       </c>
       <c r="L41" t="n">
-        <v>53598</v>
+        <v>53427.75</v>
       </c>
       <c r="M41" t="n">
-        <v>53732</v>
+        <v>53544.5</v>
       </c>
       <c r="N41" t="n">
-        <v>53866</v>
+        <v>53661.25</v>
       </c>
       <c r="O41" t="n">
-        <v>54216</v>
+        <v>53877</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3955,21 +3955,23 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3979,90 +3981,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>53408</v>
+        <v>53529</v>
       </c>
       <c r="C42" t="n">
-        <v>53780</v>
+        <v>53589</v>
       </c>
       <c r="D42" t="n">
-        <v>53337</v>
+        <v>52812</v>
       </c>
       <c r="E42" t="n">
-        <v>53530</v>
+        <v>52849</v>
       </c>
       <c r="F42" t="n">
-        <v>127</v>
+        <v>-681</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0127</v>
       </c>
       <c r="H42" t="n">
-        <v>443</v>
+        <v>777</v>
       </c>
       <c r="I42" t="n">
-        <v>53028</v>
+        <v>52894</v>
       </c>
       <c r="J42" t="n">
-        <v>53095.25</v>
+        <v>53072.75</v>
       </c>
       <c r="K42" t="n">
-        <v>53261.5</v>
+        <v>53308.5</v>
       </c>
       <c r="L42" t="n">
-        <v>53427.75</v>
+        <v>53544.25</v>
       </c>
       <c r="M42" t="n">
-        <v>53544.5</v>
+        <v>53751.5</v>
       </c>
       <c r="N42" t="n">
-        <v>53661.25</v>
+        <v>53958.75</v>
       </c>
       <c r="O42" t="n">
-        <v>53877</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
+        <v>54223</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U42" s="8" t="inlineStr">
+      <c r="Q42" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W42" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr"/>
@@ -4070,77 +4070,75 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>53529</v>
+        <v>52876</v>
       </c>
       <c r="C43" t="n">
-        <v>53589</v>
+        <v>53418</v>
       </c>
       <c r="D43" t="n">
-        <v>52812</v>
+        <v>52838</v>
       </c>
       <c r="E43" t="n">
-        <v>52849</v>
+        <v>53353</v>
       </c>
       <c r="F43" t="n">
-        <v>-681</v>
+        <v>504</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0095</v>
       </c>
       <c r="H43" t="n">
-        <v>777</v>
+        <v>580</v>
       </c>
       <c r="I43" t="n">
-        <v>52894</v>
+        <v>52035</v>
       </c>
       <c r="J43" t="n">
-        <v>53072.75</v>
+        <v>51896.25</v>
       </c>
       <c r="K43" t="n">
-        <v>53308.5</v>
+        <v>52460.5</v>
       </c>
       <c r="L43" t="n">
-        <v>53544.25</v>
+        <v>53024.75</v>
       </c>
       <c r="M43" t="n">
-        <v>53751.5</v>
+        <v>53237.5</v>
       </c>
       <c r="N43" t="n">
-        <v>53958.75</v>
+        <v>53450.25</v>
       </c>
       <c r="O43" t="n">
-        <v>54223</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
+        <v>54366</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
@@ -4149,55 +4147,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>52876</v>
+        <v>53367</v>
       </c>
       <c r="C44" t="n">
-        <v>53418</v>
+        <v>53567</v>
       </c>
       <c r="D44" t="n">
-        <v>52838</v>
+        <v>53210</v>
       </c>
       <c r="E44" t="n">
-        <v>53353</v>
+        <v>53489</v>
       </c>
       <c r="F44" t="n">
-        <v>504</v>
+        <v>136</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.0025</v>
       </c>
       <c r="H44" t="n">
-        <v>580</v>
+        <v>357</v>
       </c>
       <c r="I44" t="n">
-        <v>52035</v>
+        <v>52258</v>
       </c>
       <c r="J44" t="n">
-        <v>51896.25</v>
+        <v>52885.5</v>
       </c>
       <c r="K44" t="n">
-        <v>52460.5</v>
+        <v>53063</v>
       </c>
       <c r="L44" t="n">
-        <v>53024.75</v>
+        <v>53240.5</v>
       </c>
       <c r="M44" t="n">
-        <v>53237.5</v>
+        <v>53643</v>
       </c>
       <c r="N44" t="n">
-        <v>53450.25</v>
+        <v>54045.5</v>
       </c>
       <c r="O44" t="n">
-        <v>54366</v>
+        <v>53998</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4215,14 +4217,12 @@
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
@@ -4233,57 +4233,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>53367</v>
+        <v>53524</v>
       </c>
       <c r="C45" t="n">
-        <v>53567</v>
+        <v>53797</v>
       </c>
       <c r="D45" t="n">
-        <v>53210</v>
+        <v>53426</v>
       </c>
       <c r="E45" t="n">
-        <v>53489</v>
+        <v>53645</v>
       </c>
       <c r="F45" t="n">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0029</v>
       </c>
       <c r="H45" t="n">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="I45" t="n">
-        <v>52258</v>
+        <v>52853</v>
       </c>
       <c r="J45" t="n">
-        <v>52885.5</v>
+        <v>53182.25</v>
       </c>
       <c r="K45" t="n">
-        <v>53063</v>
+        <v>53310.5</v>
       </c>
       <c r="L45" t="n">
-        <v>53240.5</v>
+        <v>53438.75</v>
       </c>
       <c r="M45" t="n">
-        <v>53643</v>
+        <v>53667.5</v>
       </c>
       <c r="N45" t="n">
-        <v>54045.5</v>
+        <v>53896.25</v>
       </c>
       <c r="O45" t="n">
-        <v>53998</v>
+        <v>53924</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4324,50 +4324,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>53524</v>
+        <v>53643</v>
       </c>
       <c r="C46" t="n">
-        <v>53797</v>
+        <v>53778</v>
       </c>
       <c r="D46" t="n">
-        <v>53426</v>
+        <v>53435</v>
       </c>
       <c r="E46" t="n">
-        <v>53645</v>
+        <v>53521</v>
       </c>
       <c r="F46" t="n">
-        <v>156</v>
+        <v>-124</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0023</v>
       </c>
       <c r="H46" t="n">
-        <v>371</v>
+        <v>343</v>
       </c>
       <c r="I46" t="n">
-        <v>52853</v>
+        <v>53055</v>
       </c>
       <c r="J46" t="n">
-        <v>53182.25</v>
+        <v>53290.75</v>
       </c>
       <c r="K46" t="n">
-        <v>53310.5</v>
+        <v>53459.5</v>
       </c>
       <c r="L46" t="n">
-        <v>53438.75</v>
+        <v>53628.25</v>
       </c>
       <c r="M46" t="n">
-        <v>53667.5</v>
+        <v>53830.5</v>
       </c>
       <c r="N46" t="n">
-        <v>53896.25</v>
+        <v>54032.75</v>
       </c>
       <c r="O46" t="n">
-        <v>53924</v>
+        <v>54168</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4375,19 +4375,19 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
@@ -4401,57 +4401,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>53643</v>
+        <v>53724</v>
       </c>
       <c r="C47" t="n">
-        <v>53778</v>
+        <v>53811</v>
       </c>
       <c r="D47" t="n">
-        <v>53435</v>
+        <v>53369</v>
       </c>
       <c r="E47" t="n">
-        <v>53521</v>
+        <v>53621</v>
       </c>
       <c r="F47" t="n">
-        <v>-124</v>
+        <v>100</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0019</v>
       </c>
       <c r="H47" t="n">
-        <v>343</v>
+        <v>442</v>
       </c>
       <c r="I47" t="n">
-        <v>53055</v>
+        <v>53092</v>
       </c>
       <c r="J47" t="n">
-        <v>53290.75</v>
+        <v>53135.25</v>
       </c>
       <c r="K47" t="n">
-        <v>53459.5</v>
+        <v>53349.5</v>
       </c>
       <c r="L47" t="n">
-        <v>53628.25</v>
+        <v>53563.75</v>
       </c>
       <c r="M47" t="n">
-        <v>53830.5</v>
+        <v>53692.5</v>
       </c>
       <c r="N47" t="n">
-        <v>54032.75</v>
+        <v>53821.25</v>
       </c>
       <c r="O47" t="n">
-        <v>54168</v>
+        <v>54121</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4459,18 +4459,18 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4485,57 +4485,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>53724</v>
+        <v>53608</v>
       </c>
       <c r="C48" t="n">
-        <v>53811</v>
+        <v>53862</v>
       </c>
       <c r="D48" t="n">
-        <v>53369</v>
+        <v>53513</v>
       </c>
       <c r="E48" t="n">
-        <v>53621</v>
+        <v>53584</v>
       </c>
       <c r="F48" t="n">
-        <v>100</v>
+        <v>-37</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0007</v>
       </c>
       <c r="H48" t="n">
-        <v>442</v>
+        <v>349</v>
       </c>
       <c r="I48" t="n">
-        <v>53092</v>
+        <v>52927</v>
       </c>
       <c r="J48" t="n">
-        <v>53135.25</v>
+        <v>53194.5</v>
       </c>
       <c r="K48" t="n">
-        <v>53349.5</v>
+        <v>53400</v>
       </c>
       <c r="L48" t="n">
-        <v>53563.75</v>
+        <v>53605.5</v>
       </c>
       <c r="M48" t="n">
-        <v>53692.5</v>
+        <v>53842</v>
       </c>
       <c r="N48" t="n">
-        <v>53821.25</v>
+        <v>54078.5</v>
       </c>
       <c r="O48" t="n">
-        <v>54121</v>
+        <v>54253</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4546,9 +4546,9 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
@@ -4576,69 +4576,73 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>53608</v>
+        <v>53664</v>
       </c>
       <c r="C49" t="n">
-        <v>53862</v>
+        <v>53664</v>
       </c>
       <c r="D49" t="n">
-        <v>53513</v>
+        <v>53149</v>
       </c>
       <c r="E49" t="n">
-        <v>53584</v>
+        <v>53240</v>
       </c>
       <c r="F49" t="n">
-        <v>-37</v>
+        <v>-344</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0064</v>
       </c>
       <c r="H49" t="n">
-        <v>349</v>
+        <v>515</v>
       </c>
       <c r="I49" t="n">
-        <v>52927</v>
+        <v>53164</v>
       </c>
       <c r="J49" t="n">
-        <v>53194.5</v>
+        <v>53183.25</v>
       </c>
       <c r="K49" t="n">
-        <v>53400</v>
+        <v>53409.5</v>
       </c>
       <c r="L49" t="n">
-        <v>53605.5</v>
+        <v>53635.75</v>
       </c>
       <c r="M49" t="n">
-        <v>53842</v>
+        <v>53758.5</v>
       </c>
       <c r="N49" t="n">
-        <v>54078.5</v>
+        <v>53881.25</v>
       </c>
       <c r="O49" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+        <v>54211</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4651,73 +4655,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>53664</v>
+        <v>53259</v>
       </c>
       <c r="C50" t="n">
-        <v>53664</v>
+        <v>53343</v>
       </c>
       <c r="D50" t="n">
-        <v>53149</v>
+        <v>52747</v>
       </c>
       <c r="E50" t="n">
-        <v>53240</v>
+        <v>52828</v>
       </c>
       <c r="F50" t="n">
-        <v>-344</v>
+        <v>-412</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0064</v>
+        <v>-0.0077</v>
       </c>
       <c r="H50" t="n">
-        <v>515</v>
+        <v>596</v>
       </c>
       <c r="I50" t="n">
-        <v>53164</v>
+        <v>52634</v>
       </c>
       <c r="J50" t="n">
-        <v>53183.25</v>
+        <v>52641.75</v>
       </c>
       <c r="K50" t="n">
-        <v>53409.5</v>
+        <v>52982.5</v>
       </c>
       <c r="L50" t="n">
-        <v>53635.75</v>
+        <v>53323.25</v>
       </c>
       <c r="M50" t="n">
-        <v>53758.5</v>
+        <v>53497.5</v>
       </c>
       <c r="N50" t="n">
-        <v>53881.25</v>
+        <v>53671.75</v>
       </c>
       <c r="O50" t="n">
-        <v>54211</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q50" s="6" t="inlineStr">
+        <v>54179</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
@@ -4744,50 +4740,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>53259</v>
+        <v>52844</v>
       </c>
       <c r="C51" t="n">
-        <v>53343</v>
+        <v>53283</v>
       </c>
       <c r="D51" t="n">
-        <v>52747</v>
+        <v>52720</v>
       </c>
       <c r="E51" t="n">
-        <v>52828</v>
+        <v>53121</v>
       </c>
       <c r="F51" t="n">
-        <v>-412</v>
+        <v>293</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0077</v>
+        <v>0.0055</v>
       </c>
       <c r="H51" t="n">
-        <v>596</v>
+        <v>563</v>
       </c>
       <c r="I51" t="n">
-        <v>52634</v>
+        <v>52151</v>
       </c>
       <c r="J51" t="n">
-        <v>52641.75</v>
+        <v>52123.5</v>
       </c>
       <c r="K51" t="n">
-        <v>52982.5</v>
+        <v>52530</v>
       </c>
       <c r="L51" t="n">
-        <v>53323.25</v>
+        <v>52936.5</v>
       </c>
       <c r="M51" t="n">
-        <v>53497.5</v>
+        <v>53126</v>
       </c>
       <c r="N51" t="n">
-        <v>53671.75</v>
+        <v>53315.5</v>
       </c>
       <c r="O51" t="n">
-        <v>54179</v>
+        <v>53939</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4795,19 +4791,19 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
       <c r="U51" s="8" t="n">
         <v/>
       </c>
@@ -4819,55 +4815,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>52844</v>
+        <v>53120</v>
       </c>
       <c r="C52" t="n">
-        <v>53283</v>
+        <v>53827</v>
       </c>
       <c r="D52" t="n">
-        <v>52720</v>
+        <v>53093</v>
       </c>
       <c r="E52" t="n">
-        <v>53121</v>
+        <v>53745</v>
       </c>
       <c r="F52" t="n">
-        <v>293</v>
+        <v>624</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0117</v>
       </c>
       <c r="H52" t="n">
-        <v>563</v>
+        <v>734</v>
       </c>
       <c r="I52" t="n">
-        <v>52151</v>
+        <v>52157</v>
       </c>
       <c r="J52" t="n">
-        <v>52123.5</v>
+        <v>52617.75</v>
       </c>
       <c r="K52" t="n">
-        <v>52530</v>
+        <v>52839.5</v>
       </c>
       <c r="L52" t="n">
-        <v>52936.5</v>
+        <v>53061.25</v>
       </c>
       <c r="M52" t="n">
-        <v>53126</v>
+        <v>53402.5</v>
       </c>
       <c r="N52" t="n">
-        <v>53315.5</v>
+        <v>53743.75</v>
       </c>
       <c r="O52" t="n">
-        <v>53939</v>
+        <v>53846</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4885,73 +4885,71 @@
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W52" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>53120</v>
+        <v>53707</v>
       </c>
       <c r="C53" t="n">
-        <v>53827</v>
+        <v>53772</v>
       </c>
       <c r="D53" t="n">
-        <v>53093</v>
+        <v>53235</v>
       </c>
       <c r="E53" t="n">
-        <v>53745</v>
+        <v>53440</v>
       </c>
       <c r="F53" t="n">
-        <v>624</v>
+        <v>-305</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0117</v>
+        <v>-0.0057</v>
       </c>
       <c r="H53" t="n">
-        <v>734</v>
+        <v>537</v>
       </c>
       <c r="I53" t="n">
-        <v>52157</v>
+        <v>52359</v>
       </c>
       <c r="J53" t="n">
-        <v>52617.75</v>
+        <v>53153.5</v>
       </c>
       <c r="K53" t="n">
-        <v>52839.5</v>
+        <v>53378</v>
       </c>
       <c r="L53" t="n">
-        <v>53061.25</v>
+        <v>53602.5</v>
       </c>
       <c r="M53" t="n">
-        <v>53402.5</v>
+        <v>54112</v>
       </c>
       <c r="N53" t="n">
-        <v>53743.75</v>
+        <v>54621.5</v>
       </c>
       <c r="O53" t="n">
-        <v>53846</v>
+        <v>54561</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4959,24 +4957,22 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
@@ -4985,65 +4981,71 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>53707</v>
+        <v>53261</v>
       </c>
       <c r="C54" t="n">
-        <v>53772</v>
+        <v>53336</v>
       </c>
       <c r="D54" t="n">
-        <v>53235</v>
+        <v>52758</v>
       </c>
       <c r="E54" t="n">
-        <v>53440</v>
+        <v>52832</v>
       </c>
       <c r="F54" t="n">
-        <v>-305</v>
+        <v>-608</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0057</v>
+        <v>-0.0114</v>
       </c>
       <c r="H54" t="n">
-        <v>537</v>
+        <v>578</v>
       </c>
       <c r="I54" t="n">
-        <v>52359</v>
+        <v>52698</v>
       </c>
       <c r="J54" t="n">
-        <v>53153.5</v>
+        <v>52871.25</v>
       </c>
       <c r="K54" t="n">
-        <v>53378</v>
+        <v>53171.5</v>
       </c>
       <c r="L54" t="n">
-        <v>53602.5</v>
+        <v>53471.75</v>
       </c>
       <c r="M54" t="n">
-        <v>54112</v>
+        <v>53708.5</v>
       </c>
       <c r="N54" t="n">
-        <v>54621.5</v>
+        <v>53945.25</v>
       </c>
       <c r="O54" t="n">
-        <v>54561</v>
+        <v>54309</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
@@ -5060,76 +5062,70 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W54" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>53261</v>
+        <v>52817</v>
       </c>
       <c r="C55" t="n">
-        <v>53336</v>
+        <v>52859</v>
       </c>
       <c r="D55" t="n">
-        <v>52758</v>
+        <v>52339</v>
       </c>
       <c r="E55" t="n">
-        <v>52832</v>
+        <v>52425</v>
       </c>
       <c r="F55" t="n">
-        <v>-608</v>
+        <v>-407</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0114</v>
+        <v>-0.0077</v>
       </c>
       <c r="H55" t="n">
-        <v>578</v>
+        <v>520</v>
       </c>
       <c r="I55" t="n">
-        <v>52698</v>
+        <v>52180</v>
       </c>
       <c r="J55" t="n">
-        <v>52871.25</v>
+        <v>52146.5</v>
       </c>
       <c r="K55" t="n">
-        <v>53171.5</v>
+        <v>52543</v>
       </c>
       <c r="L55" t="n">
-        <v>53471.75</v>
+        <v>52939.5</v>
       </c>
       <c r="M55" t="n">
-        <v>53708.5</v>
+        <v>53121</v>
       </c>
       <c r="N55" t="n">
-        <v>53945.25</v>
+        <v>53302.5</v>
       </c>
       <c r="O55" t="n">
-        <v>54309</v>
+        <v>53914</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
@@ -5156,50 +5152,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>52817</v>
+        <v>52473</v>
       </c>
       <c r="C56" t="n">
-        <v>52859</v>
+        <v>52676</v>
       </c>
       <c r="D56" t="n">
-        <v>52339</v>
+        <v>51992</v>
       </c>
       <c r="E56" t="n">
-        <v>52425</v>
+        <v>52095</v>
       </c>
       <c r="F56" t="n">
-        <v>-407</v>
+        <v>-330</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0077</v>
+        <v>-0.0063</v>
       </c>
       <c r="H56" t="n">
-        <v>520</v>
+        <v>684</v>
       </c>
       <c r="I56" t="n">
-        <v>52180</v>
+        <v>51819</v>
       </c>
       <c r="J56" t="n">
-        <v>52146.5</v>
+        <v>51818</v>
       </c>
       <c r="K56" t="n">
-        <v>52543</v>
+        <v>52165</v>
       </c>
       <c r="L56" t="n">
-        <v>52939.5</v>
+        <v>52512</v>
       </c>
       <c r="M56" t="n">
-        <v>53121</v>
+        <v>52685</v>
       </c>
       <c r="N56" t="n">
-        <v>53302.5</v>
+        <v>52858</v>
       </c>
       <c r="O56" t="n">
-        <v>53914</v>
+        <v>53379</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5236,50 +5232,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>52473</v>
+        <v>52059</v>
       </c>
       <c r="C57" t="n">
-        <v>52676</v>
+        <v>52739</v>
       </c>
       <c r="D57" t="n">
-        <v>51992</v>
+        <v>52059</v>
       </c>
       <c r="E57" t="n">
-        <v>52095</v>
+        <v>52585</v>
       </c>
       <c r="F57" t="n">
-        <v>-330</v>
+        <v>490</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0063</v>
+        <v>0.0094</v>
       </c>
       <c r="H57" t="n">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="I57" t="n">
-        <v>51819</v>
+        <v>51308</v>
       </c>
       <c r="J57" t="n">
-        <v>51818</v>
+        <v>51291.5</v>
       </c>
       <c r="K57" t="n">
-        <v>52165</v>
+        <v>51753</v>
       </c>
       <c r="L57" t="n">
-        <v>52512</v>
+        <v>52214.5</v>
       </c>
       <c r="M57" t="n">
-        <v>52685</v>
+        <v>52437</v>
       </c>
       <c r="N57" t="n">
-        <v>52858</v>
+        <v>52659.5</v>
       </c>
       <c r="O57" t="n">
-        <v>53379</v>
+        <v>53360</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5287,22 +5283,24 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
@@ -5311,55 +5309,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>52059</v>
+        <v>52376</v>
       </c>
       <c r="C58" t="n">
-        <v>52739</v>
+        <v>52672</v>
       </c>
       <c r="D58" t="n">
-        <v>52059</v>
+        <v>52226</v>
       </c>
       <c r="E58" t="n">
-        <v>52585</v>
+        <v>52440</v>
       </c>
       <c r="F58" t="n">
-        <v>490</v>
+        <v>-145</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0094</v>
+        <v>-0.0028</v>
       </c>
       <c r="H58" t="n">
-        <v>680</v>
+        <v>446</v>
       </c>
       <c r="I58" t="n">
-        <v>51308</v>
+        <v>51379</v>
       </c>
       <c r="J58" t="n">
-        <v>51291.5</v>
+        <v>51998</v>
       </c>
       <c r="K58" t="n">
-        <v>51753</v>
+        <v>52245</v>
       </c>
       <c r="L58" t="n">
-        <v>52214.5</v>
+        <v>52492</v>
       </c>
       <c r="M58" t="n">
-        <v>52437</v>
+        <v>52925</v>
       </c>
       <c r="N58" t="n">
-        <v>52659.5</v>
+        <v>53358</v>
       </c>
       <c r="O58" t="n">
-        <v>53360</v>
+        <v>53419</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5367,23 +5369,21 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
@@ -5395,72 +5395,74 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>52376</v>
+        <v>52499</v>
       </c>
       <c r="C59" t="n">
-        <v>52672</v>
+        <v>52499</v>
       </c>
       <c r="D59" t="n">
-        <v>52226</v>
+        <v>51908</v>
       </c>
       <c r="E59" t="n">
-        <v>52440</v>
+        <v>52115</v>
       </c>
       <c r="F59" t="n">
-        <v>-145</v>
+        <v>-325</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0028</v>
+        <v>-0.0062</v>
       </c>
       <c r="H59" t="n">
-        <v>446</v>
+        <v>591</v>
       </c>
       <c r="I59" t="n">
-        <v>51379</v>
+        <v>51780</v>
       </c>
       <c r="J59" t="n">
-        <v>51998</v>
+        <v>51989.5</v>
       </c>
       <c r="K59" t="n">
-        <v>52245</v>
+        <v>52217</v>
       </c>
       <c r="L59" t="n">
-        <v>52492</v>
+        <v>52444.5</v>
       </c>
       <c r="M59" t="n">
-        <v>52925</v>
+        <v>52663</v>
       </c>
       <c r="N59" t="n">
-        <v>53358</v>
+        <v>52881.5</v>
       </c>
       <c r="O59" t="n">
-        <v>53419</v>
+        <v>53118</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5477,71 +5479,69 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>52499</v>
+        <v>52162</v>
       </c>
       <c r="C60" t="n">
-        <v>52499</v>
+        <v>52298</v>
       </c>
       <c r="D60" t="n">
-        <v>51908</v>
+        <v>51209</v>
       </c>
       <c r="E60" t="n">
-        <v>52115</v>
+        <v>51507</v>
       </c>
       <c r="F60" t="n">
-        <v>-325</v>
+        <v>-608</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0062</v>
+        <v>-0.0117</v>
       </c>
       <c r="H60" t="n">
-        <v>591</v>
+        <v>1089</v>
       </c>
       <c r="I60" t="n">
-        <v>51780</v>
+        <v>51317</v>
       </c>
       <c r="J60" t="n">
-        <v>51989.5</v>
+        <v>51479.75</v>
       </c>
       <c r="K60" t="n">
-        <v>52217</v>
+        <v>51819.5</v>
       </c>
       <c r="L60" t="n">
-        <v>52444.5</v>
+        <v>52159.25</v>
       </c>
       <c r="M60" t="n">
-        <v>52663</v>
+        <v>52410.5</v>
       </c>
       <c r="N60" t="n">
-        <v>52881.5</v>
+        <v>52661.75</v>
       </c>
       <c r="O60" t="n">
-        <v>53118</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v/>
+        <v>53090</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q60" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="S60" s="10" t="inlineStr">
@@ -5568,74 +5568,70 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>52162</v>
+        <v>51486</v>
       </c>
       <c r="C61" t="n">
-        <v>52298</v>
+        <v>52169</v>
       </c>
       <c r="D61" t="n">
-        <v>51209</v>
+        <v>51455</v>
       </c>
       <c r="E61" t="n">
-        <v>51507</v>
+        <v>51807</v>
       </c>
       <c r="F61" t="n">
-        <v>-608</v>
+        <v>300</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0117</v>
+        <v>0.0058</v>
       </c>
       <c r="H61" t="n">
-        <v>1089</v>
+        <v>714</v>
       </c>
       <c r="I61" t="n">
-        <v>51317</v>
+        <v>50120</v>
       </c>
       <c r="J61" t="n">
-        <v>51479.75</v>
+        <v>50294.75</v>
       </c>
       <c r="K61" t="n">
-        <v>51819.5</v>
+        <v>50962.5</v>
       </c>
       <c r="L61" t="n">
-        <v>52159.25</v>
+        <v>51630.25</v>
       </c>
       <c r="M61" t="n">
-        <v>52410.5</v>
+        <v>52051.5</v>
       </c>
       <c r="N61" t="n">
-        <v>52661.75</v>
+        <v>52472.75</v>
       </c>
       <c r="O61" t="n">
-        <v>53090</v>
-      </c>
-      <c r="P61" s="6" t="inlineStr">
+        <v>53387</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
       <c r="U61" s="8" t="n">
         <v/>
       </c>
@@ -5647,55 +5643,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>52201</v>
+        <v>51800</v>
       </c>
       <c r="C62" t="n">
-        <v>52224</v>
+        <v>51957</v>
       </c>
       <c r="D62" t="n">
-        <v>52147</v>
+        <v>51576</v>
       </c>
       <c r="E62" t="n">
-        <v>52205</v>
+        <v>51761</v>
       </c>
       <c r="F62" t="n">
-        <v>698</v>
+        <v>-46</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.0009</v>
       </c>
       <c r="H62" t="n">
-        <v>77</v>
+        <v>381</v>
       </c>
       <c r="I62" t="n">
-        <v>50120</v>
+        <v>50741</v>
       </c>
       <c r="J62" t="n">
-        <v>50294.75</v>
+        <v>51090.5</v>
       </c>
       <c r="K62" t="n">
-        <v>50962.5</v>
+        <v>51450</v>
       </c>
       <c r="L62" t="n">
-        <v>51630.25</v>
+        <v>51809.5</v>
       </c>
       <c r="M62" t="n">
-        <v>52051.5</v>
+        <v>52164</v>
       </c>
       <c r="N62" t="n">
-        <v>52472.75</v>
+        <v>52518.5</v>
       </c>
       <c r="O62" t="n">
-        <v>53387</v>
+        <v>52883</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5706,30 +5706,114 @@
       <c r="R62" s="6" t="n">
         <v/>
       </c>
-      <c r="S62" s="7" t="inlineStr">
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>52085</v>
+      </c>
+      <c r="C63" t="n">
+        <v>52140</v>
+      </c>
+      <c r="D63" t="n">
+        <v>52080</v>
+      </c>
+      <c r="E63" t="n">
+        <v>52079</v>
+      </c>
+      <c r="F63" t="n">
+        <v>318</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="H63" t="n">
+        <v>60</v>
+      </c>
+      <c r="I63" t="n">
+        <v>51195</v>
+      </c>
+      <c r="J63" t="n">
+        <v>51377.25</v>
+      </c>
+      <c r="K63" t="n">
+        <v>51570.5</v>
+      </c>
+      <c r="L63" t="n">
+        <v>51763.75</v>
+      </c>
+      <c r="M63" t="n">
+        <v>51951.5</v>
+      </c>
+      <c r="N63" t="n">
+        <v>52139.25</v>
+      </c>
+      <c r="O63" t="n">
+        <v>52338</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T62" s="8" t="inlineStr">
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="11" t="inlineStr">
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>中警訊</t>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52119</v>
+        <v>52381</v>
       </c>
       <c r="C2" t="n">
-        <v>52676</v>
+        <v>53097</v>
       </c>
       <c r="D2" t="n">
-        <v>51933</v>
+        <v>52215</v>
       </c>
       <c r="E2" t="n">
-        <v>52279</v>
+        <v>52339</v>
       </c>
       <c r="F2" t="n">
-        <v>197</v>
+        <v>60</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.0011</v>
       </c>
       <c r="H2" t="n">
-        <v>743</v>
+        <v>882</v>
       </c>
       <c r="I2" t="n">
-        <v>51101</v>
+        <v>51190</v>
       </c>
       <c r="J2" t="n">
-        <v>51540</v>
+        <v>51523.25</v>
       </c>
       <c r="K2" t="n">
-        <v>51787</v>
+        <v>51907.5</v>
       </c>
       <c r="L2" t="n">
-        <v>52034</v>
+        <v>52291.75</v>
       </c>
       <c r="M2" t="n">
-        <v>52377</v>
+        <v>52650.5</v>
       </c>
       <c r="N2" t="n">
-        <v>52720</v>
+        <v>53009.25</v>
       </c>
       <c r="O2" t="n">
-        <v>52871</v>
+        <v>53419</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,16 +690,18 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -714,50 +716,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>52381</v>
+        <v>52439</v>
       </c>
       <c r="C3" t="n">
-        <v>53097</v>
+        <v>52542</v>
       </c>
       <c r="D3" t="n">
-        <v>52215</v>
+        <v>52008</v>
       </c>
       <c r="E3" t="n">
-        <v>52339</v>
+        <v>52209</v>
       </c>
       <c r="F3" t="n">
-        <v>60</v>
+        <v>-130</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0011</v>
+        <v>-0.0025</v>
       </c>
       <c r="H3" t="n">
-        <v>882</v>
+        <v>534</v>
       </c>
       <c r="I3" t="n">
-        <v>51190</v>
+        <v>51333</v>
       </c>
       <c r="J3" t="n">
-        <v>51523.25</v>
+        <v>51298.5</v>
       </c>
       <c r="K3" t="n">
-        <v>51907.5</v>
+        <v>51898</v>
       </c>
       <c r="L3" t="n">
-        <v>52291.75</v>
+        <v>52497.5</v>
       </c>
       <c r="M3" t="n">
-        <v>52650.5</v>
+        <v>52780</v>
       </c>
       <c r="N3" t="n">
-        <v>53009.25</v>
+        <v>53062.5</v>
       </c>
       <c r="O3" t="n">
-        <v>53419</v>
+        <v>53979</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -768,20 +770,16 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -791,55 +789,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>52439</v>
+        <v>52183</v>
       </c>
       <c r="C4" t="n">
-        <v>52542</v>
+        <v>52700</v>
       </c>
       <c r="D4" t="n">
-        <v>52008</v>
+        <v>52179</v>
       </c>
       <c r="E4" t="n">
-        <v>52209</v>
+        <v>52572</v>
       </c>
       <c r="F4" t="n">
-        <v>-130</v>
+        <v>363</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.007</v>
       </c>
       <c r="H4" t="n">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="I4" t="n">
-        <v>51333</v>
+        <v>51474</v>
       </c>
       <c r="J4" t="n">
-        <v>51298.5</v>
+        <v>51642</v>
       </c>
       <c r="K4" t="n">
-        <v>51898</v>
+        <v>51942</v>
       </c>
       <c r="L4" t="n">
-        <v>52497.5</v>
+        <v>52242</v>
       </c>
       <c r="M4" t="n">
-        <v>52780</v>
+        <v>52476</v>
       </c>
       <c r="N4" t="n">
-        <v>53062.5</v>
+        <v>52710</v>
       </c>
       <c r="O4" t="n">
-        <v>53979</v>
+        <v>53076</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -850,13 +852,15 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -869,59 +873,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52183</v>
+        <v>52554</v>
       </c>
       <c r="C5" t="n">
-        <v>52700</v>
+        <v>52763</v>
       </c>
       <c r="D5" t="n">
-        <v>52179</v>
+        <v>52383</v>
       </c>
       <c r="E5" t="n">
-        <v>52572</v>
+        <v>52670</v>
       </c>
       <c r="F5" t="n">
-        <v>363</v>
+        <v>98</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.007</v>
+        <v>0.0019</v>
       </c>
       <c r="H5" t="n">
-        <v>521</v>
+        <v>380</v>
       </c>
       <c r="I5" t="n">
-        <v>51474</v>
+        <v>51658</v>
       </c>
       <c r="J5" t="n">
-        <v>51642</v>
+        <v>52117.25</v>
       </c>
       <c r="K5" t="n">
-        <v>51942</v>
+        <v>52311.5</v>
       </c>
       <c r="L5" t="n">
-        <v>52242</v>
+        <v>52505.75</v>
       </c>
       <c r="M5" t="n">
-        <v>52476</v>
+        <v>52832.5</v>
       </c>
       <c r="N5" t="n">
-        <v>52710</v>
+        <v>53159.25</v>
       </c>
       <c r="O5" t="n">
-        <v>53076</v>
+        <v>53221</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -958,50 +958,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52554</v>
+        <v>52546</v>
       </c>
       <c r="C6" t="n">
-        <v>52763</v>
+        <v>53105</v>
       </c>
       <c r="D6" t="n">
-        <v>52383</v>
+        <v>52381</v>
       </c>
       <c r="E6" t="n">
-        <v>52670</v>
+        <v>52668</v>
       </c>
       <c r="F6" t="n">
-        <v>98</v>
+        <v>-2</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0</v>
       </c>
       <c r="H6" t="n">
-        <v>380</v>
+        <v>724</v>
       </c>
       <c r="I6" t="n">
-        <v>51658</v>
+        <v>52003</v>
       </c>
       <c r="J6" t="n">
-        <v>52117.25</v>
+        <v>52338.5</v>
       </c>
       <c r="K6" t="n">
-        <v>52311.5</v>
+        <v>52480</v>
       </c>
       <c r="L6" t="n">
-        <v>52505.75</v>
+        <v>52621.5</v>
       </c>
       <c r="M6" t="n">
-        <v>52832.5</v>
+        <v>52860</v>
       </c>
       <c r="N6" t="n">
-        <v>53159.25</v>
+        <v>53098.5</v>
       </c>
       <c r="O6" t="n">
-        <v>53221</v>
+        <v>53143</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1009,21 +1009,25 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
@@ -1033,55 +1037,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>52546</v>
+        <v>52640</v>
       </c>
       <c r="C7" t="n">
-        <v>53105</v>
+        <v>53218</v>
       </c>
       <c r="D7" t="n">
-        <v>52381</v>
+        <v>52551</v>
       </c>
       <c r="E7" t="n">
-        <v>52668</v>
+        <v>53183</v>
       </c>
       <c r="F7" t="n">
-        <v>-2</v>
+        <v>515</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0</v>
+        <v>0.0098</v>
       </c>
       <c r="H7" t="n">
-        <v>724</v>
+        <v>667</v>
       </c>
       <c r="I7" t="n">
-        <v>52003</v>
+        <v>51657</v>
       </c>
       <c r="J7" t="n">
-        <v>52338.5</v>
+        <v>51906.5</v>
       </c>
       <c r="K7" t="n">
-        <v>52480</v>
+        <v>52306</v>
       </c>
       <c r="L7" t="n">
-        <v>52621.5</v>
+        <v>52705.5</v>
       </c>
       <c r="M7" t="n">
-        <v>52860</v>
+        <v>53030</v>
       </c>
       <c r="N7" t="n">
-        <v>53098.5</v>
+        <v>53354.5</v>
       </c>
       <c r="O7" t="n">
-        <v>53143</v>
+        <v>53829</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1089,25 +1097,21 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R7" s="6" t="n">
+        <v/>
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1117,59 +1121,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52640</v>
+        <v>53230</v>
       </c>
       <c r="C8" t="n">
-        <v>53218</v>
+        <v>53421</v>
       </c>
       <c r="D8" t="n">
-        <v>52551</v>
+        <v>52962</v>
       </c>
       <c r="E8" t="n">
-        <v>53183</v>
+        <v>53372</v>
       </c>
       <c r="F8" t="n">
-        <v>515</v>
+        <v>189</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0036</v>
       </c>
       <c r="H8" t="n">
-        <v>667</v>
+        <v>459</v>
       </c>
       <c r="I8" t="n">
-        <v>51657</v>
+        <v>51884</v>
       </c>
       <c r="J8" t="n">
-        <v>51906.5</v>
+        <v>52665.25</v>
       </c>
       <c r="K8" t="n">
-        <v>52306</v>
+        <v>52849.5</v>
       </c>
       <c r="L8" t="n">
-        <v>52705.5</v>
+        <v>53033.75</v>
       </c>
       <c r="M8" t="n">
-        <v>53030</v>
+        <v>53516.5</v>
       </c>
       <c r="N8" t="n">
-        <v>53354.5</v>
+        <v>53999.25</v>
       </c>
       <c r="O8" t="n">
-        <v>53829</v>
+        <v>53885</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1206,50 +1206,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53230</v>
+        <v>53405</v>
       </c>
       <c r="C9" t="n">
-        <v>53421</v>
+        <v>53656</v>
       </c>
       <c r="D9" t="n">
-        <v>52962</v>
+        <v>53076</v>
       </c>
       <c r="E9" t="n">
-        <v>53372</v>
+        <v>53197</v>
       </c>
       <c r="F9" t="n">
-        <v>189</v>
+        <v>-175</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0036</v>
+        <v>-0.0033</v>
       </c>
       <c r="H9" t="n">
-        <v>459</v>
+        <v>580</v>
       </c>
       <c r="I9" t="n">
-        <v>51884</v>
+        <v>52503</v>
       </c>
       <c r="J9" t="n">
-        <v>52665.25</v>
+        <v>53003.25</v>
       </c>
       <c r="K9" t="n">
-        <v>52849.5</v>
+        <v>53142.5</v>
       </c>
       <c r="L9" t="n">
-        <v>53033.75</v>
+        <v>53281.75</v>
       </c>
       <c r="M9" t="n">
-        <v>53516.5</v>
+        <v>53601.5</v>
       </c>
       <c r="N9" t="n">
-        <v>53999.25</v>
+        <v>53921.25</v>
       </c>
       <c r="O9" t="n">
-        <v>53885</v>
+        <v>53880</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1257,17 +1257,19 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U9" s="8" t="n">
@@ -1281,65 +1283,73 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53405</v>
+        <v>53166</v>
       </c>
       <c r="C10" t="n">
-        <v>53656</v>
+        <v>53207</v>
       </c>
       <c r="D10" t="n">
-        <v>53076</v>
+        <v>52343</v>
       </c>
       <c r="E10" t="n">
-        <v>53197</v>
+        <v>52624</v>
       </c>
       <c r="F10" t="n">
-        <v>-175</v>
+        <v>-573</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0108</v>
       </c>
       <c r="H10" t="n">
-        <v>580</v>
+        <v>864</v>
       </c>
       <c r="I10" t="n">
-        <v>52503</v>
+        <v>52496</v>
       </c>
       <c r="J10" t="n">
-        <v>53003.25</v>
+        <v>52532.5</v>
       </c>
       <c r="K10" t="n">
-        <v>53142.5</v>
+        <v>52907</v>
       </c>
       <c r="L10" t="n">
-        <v>53281.75</v>
+        <v>53281.5</v>
       </c>
       <c r="M10" t="n">
-        <v>53601.5</v>
+        <v>53487</v>
       </c>
       <c r="N10" t="n">
-        <v>53921.25</v>
+        <v>53692.5</v>
       </c>
       <c r="O10" t="n">
-        <v>53880</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
+        <v>54236</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
@@ -1347,10 +1357,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1365,76 +1373,70 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>53166</v>
+        <v>52541</v>
       </c>
       <c r="C11" t="n">
-        <v>53207</v>
+        <v>52865</v>
       </c>
       <c r="D11" t="n">
-        <v>52343</v>
+        <v>52501</v>
       </c>
       <c r="E11" t="n">
-        <v>52624</v>
+        <v>52761</v>
       </c>
       <c r="F11" t="n">
-        <v>-573</v>
+        <v>137</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0108</v>
+        <v>0.0026</v>
       </c>
       <c r="H11" t="n">
-        <v>864</v>
+        <v>364</v>
       </c>
       <c r="I11" t="n">
-        <v>52496</v>
+        <v>51479</v>
       </c>
       <c r="J11" t="n">
-        <v>52532.5</v>
+        <v>51684.5</v>
       </c>
       <c r="K11" t="n">
-        <v>52907</v>
+        <v>52192</v>
       </c>
       <c r="L11" t="n">
-        <v>53281.5</v>
+        <v>52699.5</v>
       </c>
       <c r="M11" t="n">
-        <v>53487</v>
+        <v>53056</v>
       </c>
       <c r="N11" t="n">
-        <v>53692.5</v>
+        <v>53412.5</v>
       </c>
       <c r="O11" t="n">
-        <v>54236</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>54071</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1453,57 +1455,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52541</v>
+        <v>52753</v>
       </c>
       <c r="C12" t="n">
-        <v>52865</v>
+        <v>52992</v>
       </c>
       <c r="D12" t="n">
-        <v>52501</v>
+        <v>52506</v>
       </c>
       <c r="E12" t="n">
-        <v>52761</v>
+        <v>52906</v>
       </c>
       <c r="F12" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0027</v>
       </c>
       <c r="H12" t="n">
-        <v>364</v>
+        <v>486</v>
       </c>
       <c r="I12" t="n">
-        <v>51479</v>
+        <v>52137</v>
       </c>
       <c r="J12" t="n">
-        <v>51684.5</v>
+        <v>52436</v>
       </c>
       <c r="K12" t="n">
-        <v>52192</v>
+        <v>52579</v>
       </c>
       <c r="L12" t="n">
-        <v>52699.5</v>
+        <v>52722</v>
       </c>
       <c r="M12" t="n">
-        <v>53056</v>
+        <v>52943</v>
       </c>
       <c r="N12" t="n">
-        <v>53412.5</v>
+        <v>53164</v>
       </c>
       <c r="O12" t="n">
-        <v>54071</v>
+        <v>53229</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1511,16 +1513,20 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1533,59 +1539,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>52753</v>
+        <v>52844</v>
       </c>
       <c r="C13" t="n">
-        <v>52992</v>
+        <v>53113</v>
       </c>
       <c r="D13" t="n">
-        <v>52506</v>
+        <v>52603</v>
       </c>
       <c r="E13" t="n">
-        <v>52906</v>
+        <v>52764</v>
       </c>
       <c r="F13" t="n">
-        <v>145</v>
+        <v>-142</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0027</v>
       </c>
       <c r="H13" t="n">
-        <v>486</v>
+        <v>510</v>
       </c>
       <c r="I13" t="n">
-        <v>52137</v>
+        <v>52020</v>
       </c>
       <c r="J13" t="n">
-        <v>52436</v>
+        <v>52498.5</v>
       </c>
       <c r="K13" t="n">
-        <v>52579</v>
+        <v>52663</v>
       </c>
       <c r="L13" t="n">
-        <v>52722</v>
+        <v>52827.5</v>
       </c>
       <c r="M13" t="n">
-        <v>52943</v>
+        <v>53149</v>
       </c>
       <c r="N13" t="n">
-        <v>53164</v>
+        <v>53470.5</v>
       </c>
       <c r="O13" t="n">
-        <v>53229</v>
+        <v>53478</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1598,15 +1600,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1619,55 +1619,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>52844</v>
+        <v>52731</v>
       </c>
       <c r="C14" t="n">
-        <v>53113</v>
+        <v>52981</v>
       </c>
       <c r="D14" t="n">
-        <v>52603</v>
+        <v>52255</v>
       </c>
       <c r="E14" t="n">
-        <v>52764</v>
+        <v>52791</v>
       </c>
       <c r="F14" t="n">
-        <v>-142</v>
+        <v>27</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0005</v>
       </c>
       <c r="H14" t="n">
-        <v>510</v>
+        <v>726</v>
       </c>
       <c r="I14" t="n">
-        <v>52020</v>
+        <v>52093</v>
       </c>
       <c r="J14" t="n">
-        <v>52498.5</v>
+        <v>52207</v>
       </c>
       <c r="K14" t="n">
-        <v>52663</v>
+        <v>52509</v>
       </c>
       <c r="L14" t="n">
-        <v>52827.5</v>
+        <v>52811</v>
       </c>
       <c r="M14" t="n">
-        <v>53149</v>
+        <v>53019</v>
       </c>
       <c r="N14" t="n">
-        <v>53470.5</v>
+        <v>53227</v>
       </c>
       <c r="O14" t="n">
-        <v>53478</v>
+        <v>53623</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1701,57 +1705,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52731</v>
+        <v>52792</v>
       </c>
       <c r="C15" t="n">
-        <v>52981</v>
+        <v>53088</v>
       </c>
       <c r="D15" t="n">
-        <v>52255</v>
+        <v>52680</v>
       </c>
       <c r="E15" t="n">
-        <v>52791</v>
+        <v>52900</v>
       </c>
       <c r="F15" t="n">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0021</v>
       </c>
       <c r="H15" t="n">
-        <v>726</v>
+        <v>408</v>
       </c>
       <c r="I15" t="n">
-        <v>52093</v>
+        <v>51529</v>
       </c>
       <c r="J15" t="n">
-        <v>52207</v>
+        <v>52151.5</v>
       </c>
       <c r="K15" t="n">
-        <v>52509</v>
+        <v>52428</v>
       </c>
       <c r="L15" t="n">
-        <v>52811</v>
+        <v>52704.5</v>
       </c>
       <c r="M15" t="n">
-        <v>53019</v>
+        <v>53154</v>
       </c>
       <c r="N15" t="n">
-        <v>53227</v>
+        <v>53603.5</v>
       </c>
       <c r="O15" t="n">
-        <v>53623</v>
+        <v>53707</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1759,14 +1763,12 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1783,59 +1785,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>52792</v>
+        <v>52919</v>
       </c>
       <c r="C16" t="n">
-        <v>53088</v>
+        <v>53108</v>
       </c>
       <c r="D16" t="n">
-        <v>52680</v>
+        <v>52607</v>
       </c>
       <c r="E16" t="n">
-        <v>52900</v>
+        <v>52786</v>
       </c>
       <c r="F16" t="n">
-        <v>109</v>
+        <v>-114</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0022</v>
       </c>
       <c r="H16" t="n">
-        <v>408</v>
+        <v>501</v>
       </c>
       <c r="I16" t="n">
-        <v>51529</v>
+        <v>52272</v>
       </c>
       <c r="J16" t="n">
-        <v>52151.5</v>
+        <v>52500</v>
       </c>
       <c r="K16" t="n">
-        <v>52428</v>
+        <v>52696</v>
       </c>
       <c r="L16" t="n">
-        <v>52704.5</v>
+        <v>52892</v>
       </c>
       <c r="M16" t="n">
-        <v>53154</v>
+        <v>53104</v>
       </c>
       <c r="N16" t="n">
-        <v>53603.5</v>
+        <v>53316</v>
       </c>
       <c r="O16" t="n">
-        <v>53707</v>
+        <v>53496</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1843,16 +1841,20 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1865,65 +1867,71 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52919</v>
+        <v>52778</v>
       </c>
       <c r="C17" t="n">
-        <v>53108</v>
+        <v>52835</v>
       </c>
       <c r="D17" t="n">
-        <v>52607</v>
+        <v>52174</v>
       </c>
       <c r="E17" t="n">
-        <v>52786</v>
+        <v>52375</v>
       </c>
       <c r="F17" t="n">
-        <v>-114</v>
+        <v>-411</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0078</v>
       </c>
       <c r="H17" t="n">
-        <v>501</v>
+        <v>661</v>
       </c>
       <c r="I17" t="n">
-        <v>52272</v>
+        <v>52106</v>
       </c>
       <c r="J17" t="n">
-        <v>52500</v>
+        <v>52249.25</v>
       </c>
       <c r="K17" t="n">
-        <v>52696</v>
+        <v>52535.5</v>
       </c>
       <c r="L17" t="n">
-        <v>52892</v>
+        <v>52821.75</v>
       </c>
       <c r="M17" t="n">
-        <v>53104</v>
+        <v>53036.5</v>
       </c>
       <c r="N17" t="n">
-        <v>53316</v>
+        <v>53251.25</v>
       </c>
       <c r="O17" t="n">
-        <v>53496</v>
+        <v>53609</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S17" s="10" t="inlineStr">
@@ -1931,10 +1939,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1949,69 +1955,67 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52778</v>
+        <v>52300</v>
       </c>
       <c r="C18" t="n">
-        <v>52835</v>
+        <v>52633</v>
       </c>
       <c r="D18" t="n">
-        <v>52174</v>
+        <v>51999</v>
       </c>
       <c r="E18" t="n">
-        <v>52375</v>
+        <v>52073</v>
       </c>
       <c r="F18" t="n">
-        <v>-411</v>
+        <v>-302</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0078</v>
+        <v>-0.0058</v>
       </c>
       <c r="H18" t="n">
-        <v>661</v>
+        <v>634</v>
       </c>
       <c r="I18" t="n">
-        <v>52106</v>
+        <v>51513</v>
       </c>
       <c r="J18" t="n">
-        <v>52249.25</v>
+        <v>51649.25</v>
       </c>
       <c r="K18" t="n">
-        <v>52535.5</v>
+        <v>52044.5</v>
       </c>
       <c r="L18" t="n">
-        <v>52821.75</v>
+        <v>52439.75</v>
       </c>
       <c r="M18" t="n">
-        <v>53036.5</v>
+        <v>52705.5</v>
       </c>
       <c r="N18" t="n">
-        <v>53251.25</v>
+        <v>52971.25</v>
       </c>
       <c r="O18" t="n">
-        <v>53609</v>
+        <v>53496</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S18" s="10" t="inlineStr">
@@ -2042,50 +2046,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>52300</v>
+        <v>52091</v>
       </c>
       <c r="C19" t="n">
-        <v>52633</v>
+        <v>52590</v>
       </c>
       <c r="D19" t="n">
-        <v>51999</v>
+        <v>52035</v>
       </c>
       <c r="E19" t="n">
-        <v>52073</v>
+        <v>52443</v>
       </c>
       <c r="F19" t="n">
-        <v>-302</v>
+        <v>370</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.0071</v>
       </c>
       <c r="H19" t="n">
-        <v>634</v>
+        <v>555</v>
       </c>
       <c r="I19" t="n">
-        <v>51513</v>
+        <v>51365</v>
       </c>
       <c r="J19" t="n">
-        <v>51649.25</v>
+        <v>51317.5</v>
       </c>
       <c r="K19" t="n">
-        <v>52044.5</v>
+        <v>51756</v>
       </c>
       <c r="L19" t="n">
-        <v>52439.75</v>
+        <v>52194.5</v>
       </c>
       <c r="M19" t="n">
-        <v>52705.5</v>
+        <v>52390</v>
       </c>
       <c r="N19" t="n">
-        <v>52971.25</v>
+        <v>52585.5</v>
       </c>
       <c r="O19" t="n">
-        <v>53496</v>
+        <v>53267</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2093,21 +2097,23 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2119,57 +2125,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>52091</v>
+        <v>52431</v>
       </c>
       <c r="C20" t="n">
-        <v>52590</v>
+        <v>52721</v>
       </c>
       <c r="D20" t="n">
-        <v>52035</v>
+        <v>52262</v>
       </c>
       <c r="E20" t="n">
-        <v>52443</v>
+        <v>52449</v>
       </c>
       <c r="F20" t="n">
-        <v>370</v>
+        <v>6</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0001</v>
       </c>
       <c r="H20" t="n">
-        <v>555</v>
+        <v>459</v>
       </c>
       <c r="I20" t="n">
-        <v>51365</v>
+        <v>51480</v>
       </c>
       <c r="J20" t="n">
-        <v>51317.5</v>
+        <v>51953.25</v>
       </c>
       <c r="K20" t="n">
-        <v>51756</v>
+        <v>52165.5</v>
       </c>
       <c r="L20" t="n">
-        <v>52194.5</v>
+        <v>52377.75</v>
       </c>
       <c r="M20" t="n">
-        <v>52390</v>
+        <v>52720.5</v>
       </c>
       <c r="N20" t="n">
-        <v>52585.5</v>
+        <v>53063.25</v>
       </c>
       <c r="O20" t="n">
-        <v>53267</v>
+        <v>53145</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2182,19 +2188,17 @@
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
@@ -2203,88 +2207,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>52431</v>
+        <v>52430</v>
       </c>
       <c r="C21" t="n">
-        <v>52721</v>
+        <v>52515</v>
       </c>
       <c r="D21" t="n">
-        <v>52262</v>
+        <v>51720</v>
       </c>
       <c r="E21" t="n">
-        <v>52449</v>
+        <v>51894</v>
       </c>
       <c r="F21" t="n">
-        <v>6</v>
+        <v>-555</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0106</v>
       </c>
       <c r="H21" t="n">
-        <v>459</v>
+        <v>795</v>
       </c>
       <c r="I21" t="n">
-        <v>51480</v>
+        <v>51803</v>
       </c>
       <c r="J21" t="n">
-        <v>51953.25</v>
+        <v>51968.75</v>
       </c>
       <c r="K21" t="n">
-        <v>52165.5</v>
+        <v>52219.5</v>
       </c>
       <c r="L21" t="n">
-        <v>52377.75</v>
+        <v>52470.25</v>
       </c>
       <c r="M21" t="n">
-        <v>52720.5</v>
+        <v>52678.5</v>
       </c>
       <c r="N21" t="n">
-        <v>53063.25</v>
+        <v>52886.75</v>
       </c>
       <c r="O21" t="n">
-        <v>53145</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
+        <v>53180</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W21" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
@@ -2292,74 +2296,70 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>52430</v>
+        <v>51920</v>
       </c>
       <c r="C22" t="n">
-        <v>52515</v>
+        <v>52314</v>
       </c>
       <c r="D22" t="n">
-        <v>51720</v>
+        <v>51846</v>
       </c>
       <c r="E22" t="n">
-        <v>51894</v>
+        <v>52124</v>
       </c>
       <c r="F22" t="n">
-        <v>-555</v>
+        <v>230</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0044</v>
       </c>
       <c r="H22" t="n">
-        <v>795</v>
+        <v>468</v>
       </c>
       <c r="I22" t="n">
-        <v>51803</v>
+        <v>50925</v>
       </c>
       <c r="J22" t="n">
-        <v>51968.75</v>
+        <v>50987.25</v>
       </c>
       <c r="K22" t="n">
-        <v>52219.5</v>
+        <v>51496.5</v>
       </c>
       <c r="L22" t="n">
-        <v>52470.25</v>
+        <v>52005.75</v>
       </c>
       <c r="M22" t="n">
-        <v>52678.5</v>
+        <v>52291.5</v>
       </c>
       <c r="N22" t="n">
-        <v>52886.75</v>
+        <v>52577.25</v>
       </c>
       <c r="O22" t="n">
-        <v>53180</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
+        <v>53310</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
       <c r="U22" s="8" t="n">
         <v/>
       </c>
@@ -2371,55 +2371,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>51920</v>
+        <v>52299</v>
       </c>
       <c r="C23" t="n">
-        <v>52314</v>
+        <v>52790</v>
       </c>
       <c r="D23" t="n">
-        <v>51846</v>
+        <v>52173</v>
       </c>
       <c r="E23" t="n">
-        <v>52124</v>
+        <v>52382</v>
       </c>
       <c r="F23" t="n">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0049</v>
       </c>
       <c r="H23" t="n">
-        <v>468</v>
+        <v>617</v>
       </c>
       <c r="I23" t="n">
-        <v>50925</v>
+        <v>51378</v>
       </c>
       <c r="J23" t="n">
-        <v>50987.25</v>
+        <v>51678</v>
       </c>
       <c r="K23" t="n">
-        <v>51496.5</v>
+        <v>51890</v>
       </c>
       <c r="L23" t="n">
-        <v>52005.75</v>
+        <v>52102</v>
       </c>
       <c r="M23" t="n">
-        <v>52291.5</v>
+        <v>52358</v>
       </c>
       <c r="N23" t="n">
-        <v>52577.25</v>
+        <v>52614</v>
       </c>
       <c r="O23" t="n">
-        <v>53310</v>
+        <v>52782</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2432,19 +2436,23 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v/>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W23" s="11" t="inlineStr">
         <is>
@@ -2453,57 +2461,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>52299</v>
+        <v>52405</v>
       </c>
       <c r="C24" t="n">
-        <v>52790</v>
+        <v>53105</v>
       </c>
       <c r="D24" t="n">
-        <v>52173</v>
+        <v>52290</v>
       </c>
       <c r="E24" t="n">
-        <v>52382</v>
+        <v>52944</v>
       </c>
       <c r="F24" t="n">
-        <v>258</v>
+        <v>562</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0107</v>
       </c>
       <c r="H24" t="n">
-        <v>617</v>
+        <v>815</v>
       </c>
       <c r="I24" t="n">
-        <v>51378</v>
+        <v>51556</v>
       </c>
       <c r="J24" t="n">
-        <v>51678</v>
+        <v>51715.25</v>
       </c>
       <c r="K24" t="n">
-        <v>51890</v>
+        <v>52073.5</v>
       </c>
       <c r="L24" t="n">
-        <v>52102</v>
+        <v>52431.75</v>
       </c>
       <c r="M24" t="n">
-        <v>52358</v>
+        <v>52690.5</v>
       </c>
       <c r="N24" t="n">
-        <v>52614</v>
+        <v>52949.25</v>
       </c>
       <c r="O24" t="n">
-        <v>52782</v>
+        <v>53407</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2521,18 +2529,16 @@
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V24" s="8" t="n">
+        <v/>
       </c>
       <c r="W24" s="11" t="inlineStr">
         <is>
@@ -2548,74 +2554,76 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>52405</v>
+        <v>52915</v>
       </c>
       <c r="C25" t="n">
-        <v>53105</v>
+        <v>53033</v>
       </c>
       <c r="D25" t="n">
-        <v>52290</v>
+        <v>51630</v>
       </c>
       <c r="E25" t="n">
-        <v>52944</v>
+        <v>51765</v>
       </c>
       <c r="F25" t="n">
-        <v>562</v>
+        <v>-1179</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0223</v>
       </c>
       <c r="H25" t="n">
-        <v>815</v>
+        <v>1403</v>
       </c>
       <c r="I25" t="n">
-        <v>51556</v>
+        <v>51475</v>
       </c>
       <c r="J25" t="n">
-        <v>51715.25</v>
+        <v>52252.25</v>
       </c>
       <c r="K25" t="n">
-        <v>52073.5</v>
+        <v>52536.5</v>
       </c>
       <c r="L25" t="n">
-        <v>52431.75</v>
+        <v>52820.75</v>
       </c>
       <c r="M25" t="n">
-        <v>52690.5</v>
+        <v>53351.5</v>
       </c>
       <c r="N25" t="n">
-        <v>52949.25</v>
+        <v>53882.25</v>
       </c>
       <c r="O25" t="n">
-        <v>53407</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
+        <v>53920</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2625,83 +2633,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>52915</v>
+        <v>51759</v>
       </c>
       <c r="C26" t="n">
-        <v>53033</v>
+        <v>52484</v>
       </c>
       <c r="D26" t="n">
-        <v>51630</v>
+        <v>51732</v>
       </c>
       <c r="E26" t="n">
-        <v>51765</v>
+        <v>52380</v>
       </c>
       <c r="F26" t="n">
-        <v>-1179</v>
+        <v>615</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0119</v>
       </c>
       <c r="H26" t="n">
-        <v>1403</v>
+        <v>752</v>
       </c>
       <c r="I26" t="n">
-        <v>51475</v>
+        <v>50227</v>
       </c>
       <c r="J26" t="n">
-        <v>52252.25</v>
+        <v>50078.75</v>
       </c>
       <c r="K26" t="n">
-        <v>52536.5</v>
+        <v>51063.5</v>
       </c>
       <c r="L26" t="n">
-        <v>52820.75</v>
+        <v>52048.25</v>
       </c>
       <c r="M26" t="n">
-        <v>53351.5</v>
+        <v>52466.5</v>
       </c>
       <c r="N26" t="n">
-        <v>53882.25</v>
+        <v>52884.75</v>
       </c>
       <c r="O26" t="n">
-        <v>53920</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
+        <v>54436</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
       <c r="U26" s="8" t="n">
         <v/>
       </c>
@@ -2713,55 +2713,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>51759</v>
+        <v>52395</v>
       </c>
       <c r="C27" t="n">
-        <v>52484</v>
+        <v>52772</v>
       </c>
       <c r="D27" t="n">
-        <v>51732</v>
+        <v>52124</v>
       </c>
       <c r="E27" t="n">
-        <v>52380</v>
+        <v>52635</v>
       </c>
       <c r="F27" t="n">
-        <v>615</v>
+        <v>255</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0119</v>
+        <v>0.0049</v>
       </c>
       <c r="H27" t="n">
-        <v>752</v>
+        <v>648</v>
       </c>
       <c r="I27" t="n">
-        <v>50227</v>
+        <v>50980</v>
       </c>
       <c r="J27" t="n">
-        <v>50078.75</v>
+        <v>51764</v>
       </c>
       <c r="K27" t="n">
-        <v>51063.5</v>
+        <v>52004</v>
       </c>
       <c r="L27" t="n">
-        <v>52048.25</v>
+        <v>52244</v>
       </c>
       <c r="M27" t="n">
-        <v>52466.5</v>
+        <v>52756</v>
       </c>
       <c r="N27" t="n">
-        <v>52884.75</v>
+        <v>53268</v>
       </c>
       <c r="O27" t="n">
-        <v>54436</v>
+        <v>53236</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2795,57 +2799,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>52395</v>
+        <v>52780</v>
       </c>
       <c r="C28" t="n">
-        <v>52772</v>
+        <v>53414</v>
       </c>
       <c r="D28" t="n">
-        <v>52124</v>
+        <v>52777</v>
       </c>
       <c r="E28" t="n">
-        <v>52635</v>
+        <v>53334</v>
       </c>
       <c r="F28" t="n">
-        <v>255</v>
+        <v>699</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0133</v>
       </c>
       <c r="H28" t="n">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="I28" t="n">
-        <v>50980</v>
+        <v>51476</v>
       </c>
       <c r="J28" t="n">
-        <v>51764</v>
+        <v>52080.5</v>
       </c>
       <c r="K28" t="n">
-        <v>52004</v>
+        <v>52311</v>
       </c>
       <c r="L28" t="n">
-        <v>52244</v>
+        <v>52541.5</v>
       </c>
       <c r="M28" t="n">
-        <v>52756</v>
+        <v>52959</v>
       </c>
       <c r="N28" t="n">
-        <v>53268</v>
+        <v>53376.5</v>
       </c>
       <c r="O28" t="n">
-        <v>53236</v>
+        <v>53420</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2863,11 +2867,13 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2886,50 +2892,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>52780</v>
+        <v>53381</v>
       </c>
       <c r="C29" t="n">
-        <v>53414</v>
+        <v>54423</v>
       </c>
       <c r="D29" t="n">
-        <v>52777</v>
+        <v>53267</v>
       </c>
       <c r="E29" t="n">
-        <v>53334</v>
+        <v>54268</v>
       </c>
       <c r="F29" t="n">
-        <v>699</v>
+        <v>934</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0175</v>
       </c>
       <c r="H29" t="n">
-        <v>637</v>
+        <v>1156</v>
       </c>
       <c r="I29" t="n">
-        <v>51476</v>
+        <v>52140</v>
       </c>
       <c r="J29" t="n">
-        <v>52080.5</v>
+        <v>52816.25</v>
       </c>
       <c r="K29" t="n">
-        <v>52311</v>
+        <v>53015.5</v>
       </c>
       <c r="L29" t="n">
-        <v>52541.5</v>
+        <v>53214.75</v>
       </c>
       <c r="M29" t="n">
-        <v>52959</v>
+        <v>53652.5</v>
       </c>
       <c r="N29" t="n">
-        <v>53376.5</v>
+        <v>54090.25</v>
       </c>
       <c r="O29" t="n">
-        <v>53420</v>
+        <v>54051</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2955,67 +2961,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W29" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W29" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>53381</v>
+        <v>54369</v>
       </c>
       <c r="C30" t="n">
-        <v>54423</v>
+        <v>54884</v>
       </c>
       <c r="D30" t="n">
-        <v>53267</v>
+        <v>54342</v>
       </c>
       <c r="E30" t="n">
-        <v>54268</v>
+        <v>54494</v>
       </c>
       <c r="F30" t="n">
-        <v>934</v>
+        <v>226</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0042</v>
       </c>
       <c r="H30" t="n">
-        <v>1156</v>
+        <v>542</v>
       </c>
       <c r="I30" t="n">
-        <v>52140</v>
+        <v>52111</v>
       </c>
       <c r="J30" t="n">
-        <v>52816.25</v>
+        <v>53323.5</v>
       </c>
       <c r="K30" t="n">
-        <v>53015.5</v>
+        <v>53690</v>
       </c>
       <c r="L30" t="n">
-        <v>53214.75</v>
+        <v>54056.5</v>
       </c>
       <c r="M30" t="n">
-        <v>53652.5</v>
+        <v>54846</v>
       </c>
       <c r="N30" t="n">
-        <v>54090.25</v>
+        <v>55635.5</v>
       </c>
       <c r="O30" t="n">
-        <v>54051</v>
+        <v>55579</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3033,18 +3037,14 @@
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V30" s="8" t="n">
+        <v/>
       </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
@@ -3056,70 +3056,72 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>54369</v>
+        <v>54555</v>
       </c>
       <c r="C31" t="n">
-        <v>54884</v>
+        <v>54678</v>
       </c>
       <c r="D31" t="n">
-        <v>54342</v>
+        <v>53952</v>
       </c>
       <c r="E31" t="n">
-        <v>54494</v>
+        <v>54013</v>
       </c>
       <c r="F31" t="n">
-        <v>226</v>
+        <v>-481</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>542</v>
+        <v>726</v>
       </c>
       <c r="I31" t="n">
-        <v>52111</v>
+        <v>53800</v>
       </c>
       <c r="J31" t="n">
-        <v>53323.5</v>
+        <v>53892.5</v>
       </c>
       <c r="K31" t="n">
-        <v>53690</v>
+        <v>54223</v>
       </c>
       <c r="L31" t="n">
-        <v>54056.5</v>
+        <v>54553.5</v>
       </c>
       <c r="M31" t="n">
-        <v>54846</v>
+        <v>54765</v>
       </c>
       <c r="N31" t="n">
-        <v>55635.5</v>
+        <v>54976.5</v>
       </c>
       <c r="O31" t="n">
-        <v>55579</v>
+        <v>55426</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
+      <c r="Q31" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
@@ -3131,72 +3133,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>54555</v>
+        <v>54040</v>
       </c>
       <c r="C32" t="n">
-        <v>54678</v>
+        <v>54202</v>
       </c>
       <c r="D32" t="n">
-        <v>53952</v>
+        <v>53879</v>
       </c>
       <c r="E32" t="n">
-        <v>54013</v>
+        <v>54152</v>
       </c>
       <c r="F32" t="n">
-        <v>-481</v>
+        <v>139</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0026</v>
       </c>
       <c r="H32" t="n">
-        <v>726</v>
+        <v>323</v>
       </c>
       <c r="I32" t="n">
-        <v>53800</v>
+        <v>53226</v>
       </c>
       <c r="J32" t="n">
-        <v>53892.5</v>
+        <v>53136</v>
       </c>
       <c r="K32" t="n">
-        <v>54223</v>
+        <v>53650</v>
       </c>
       <c r="L32" t="n">
-        <v>54553.5</v>
+        <v>54164</v>
       </c>
       <c r="M32" t="n">
-        <v>54765</v>
+        <v>54376</v>
       </c>
       <c r="N32" t="n">
-        <v>54976.5</v>
+        <v>54588</v>
       </c>
       <c r="O32" t="n">
-        <v>55426</v>
+        <v>55404</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3215,57 +3217,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>54040</v>
+        <v>54133</v>
       </c>
       <c r="C33" t="n">
-        <v>54202</v>
+        <v>54170</v>
       </c>
       <c r="D33" t="n">
-        <v>53879</v>
+        <v>53952</v>
       </c>
       <c r="E33" t="n">
-        <v>54152</v>
+        <v>54063</v>
       </c>
       <c r="F33" t="n">
-        <v>139</v>
+        <v>-89</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0016</v>
       </c>
       <c r="H33" t="n">
-        <v>323</v>
+        <v>218</v>
       </c>
       <c r="I33" t="n">
-        <v>53226</v>
+        <v>53556</v>
       </c>
       <c r="J33" t="n">
-        <v>53136</v>
+        <v>53884.75</v>
       </c>
       <c r="K33" t="n">
-        <v>53650</v>
+        <v>53990.5</v>
       </c>
       <c r="L33" t="n">
-        <v>54164</v>
+        <v>54096.25</v>
       </c>
       <c r="M33" t="n">
-        <v>54376</v>
+        <v>54313.5</v>
       </c>
       <c r="N33" t="n">
-        <v>54588</v>
+        <v>54530.75</v>
       </c>
       <c r="O33" t="n">
-        <v>55404</v>
+        <v>54525</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3273,8 +3275,10 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
@@ -3304,56 +3308,58 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>54133</v>
+        <v>54049</v>
       </c>
       <c r="C34" t="n">
-        <v>54170</v>
+        <v>54336</v>
       </c>
       <c r="D34" t="n">
-        <v>53952</v>
+        <v>53855</v>
       </c>
       <c r="E34" t="n">
-        <v>54063</v>
+        <v>53880</v>
       </c>
       <c r="F34" t="n">
-        <v>-89</v>
+        <v>-183</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0034</v>
       </c>
       <c r="H34" t="n">
-        <v>218</v>
+        <v>481</v>
       </c>
       <c r="I34" t="n">
-        <v>53556</v>
+        <v>53734</v>
       </c>
       <c r="J34" t="n">
-        <v>53884.75</v>
+        <v>53846</v>
       </c>
       <c r="K34" t="n">
-        <v>53990.5</v>
+        <v>53954</v>
       </c>
       <c r="L34" t="n">
-        <v>54096.25</v>
+        <v>54062</v>
       </c>
       <c r="M34" t="n">
-        <v>54313.5</v>
+        <v>54172</v>
       </c>
       <c r="N34" t="n">
-        <v>54530.75</v>
+        <v>54282</v>
       </c>
       <c r="O34" t="n">
-        <v>54525</v>
+        <v>54388</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
@@ -3362,14 +3368,18 @@
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3388,78 +3398,72 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>54049</v>
+        <v>53903</v>
       </c>
       <c r="C35" t="n">
-        <v>54336</v>
+        <v>54150</v>
       </c>
       <c r="D35" t="n">
-        <v>53855</v>
+        <v>53830</v>
       </c>
       <c r="E35" t="n">
-        <v>53880</v>
+        <v>53871</v>
       </c>
       <c r="F35" t="n">
-        <v>-183</v>
+        <v>-9</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0002</v>
       </c>
       <c r="H35" t="n">
-        <v>481</v>
+        <v>320</v>
       </c>
       <c r="I35" t="n">
-        <v>53734</v>
+        <v>53374</v>
       </c>
       <c r="J35" t="n">
-        <v>53846</v>
+        <v>53291.25</v>
       </c>
       <c r="K35" t="n">
-        <v>53954</v>
+        <v>53639.5</v>
       </c>
       <c r="L35" t="n">
-        <v>54062</v>
+        <v>53987.75</v>
       </c>
       <c r="M35" t="n">
-        <v>54172</v>
+        <v>54120.5</v>
       </c>
       <c r="N35" t="n">
-        <v>54282</v>
+        <v>54253.25</v>
       </c>
       <c r="O35" t="n">
-        <v>54388</v>
+        <v>54817</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3471,57 +3475,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>53903</v>
+        <v>53905</v>
       </c>
       <c r="C36" t="n">
-        <v>54150</v>
+        <v>54149</v>
       </c>
       <c r="D36" t="n">
-        <v>53830</v>
+        <v>53715</v>
       </c>
       <c r="E36" t="n">
-        <v>53871</v>
+        <v>53935</v>
       </c>
       <c r="F36" t="n">
-        <v>-9</v>
+        <v>64</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0012</v>
       </c>
       <c r="H36" t="n">
-        <v>320</v>
+        <v>434</v>
       </c>
       <c r="I36" t="n">
-        <v>53374</v>
+        <v>53510</v>
       </c>
       <c r="J36" t="n">
-        <v>53291.25</v>
+        <v>53491.5</v>
       </c>
       <c r="K36" t="n">
-        <v>53639.5</v>
+        <v>53711</v>
       </c>
       <c r="L36" t="n">
-        <v>53987.75</v>
+        <v>53930.5</v>
       </c>
       <c r="M36" t="n">
-        <v>54120.5</v>
+        <v>54031</v>
       </c>
       <c r="N36" t="n">
-        <v>54253.25</v>
+        <v>54131.5</v>
       </c>
       <c r="O36" t="n">
-        <v>54817</v>
+        <v>54470</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3532,9 +3536,9 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
@@ -3542,8 +3546,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U36" s="8" t="n">
-        <v/>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3555,57 +3561,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>53905</v>
+        <v>53961</v>
       </c>
       <c r="C37" t="n">
-        <v>54149</v>
+        <v>53999</v>
       </c>
       <c r="D37" t="n">
-        <v>53715</v>
+        <v>53745</v>
       </c>
       <c r="E37" t="n">
-        <v>53935</v>
+        <v>53807</v>
       </c>
       <c r="F37" t="n">
-        <v>64</v>
+        <v>-128</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0024</v>
       </c>
       <c r="H37" t="n">
-        <v>434</v>
+        <v>254</v>
       </c>
       <c r="I37" t="n">
-        <v>53510</v>
+        <v>53281</v>
       </c>
       <c r="J37" t="n">
-        <v>53491.5</v>
+        <v>53502.5</v>
       </c>
       <c r="K37" t="n">
-        <v>53711</v>
+        <v>53718</v>
       </c>
       <c r="L37" t="n">
-        <v>53930.5</v>
+        <v>53933.5</v>
       </c>
       <c r="M37" t="n">
-        <v>54031</v>
+        <v>54152</v>
       </c>
       <c r="N37" t="n">
-        <v>54131.5</v>
+        <v>54370.5</v>
       </c>
       <c r="O37" t="n">
-        <v>54470</v>
+        <v>54583</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3613,23 +3619,21 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3648,60 +3652,64 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>53961</v>
+        <v>53790</v>
       </c>
       <c r="C38" t="n">
-        <v>53999</v>
+        <v>53840</v>
       </c>
       <c r="D38" t="n">
-        <v>53745</v>
+        <v>53464</v>
       </c>
       <c r="E38" t="n">
-        <v>53807</v>
+        <v>53544</v>
       </c>
       <c r="F38" t="n">
-        <v>-128</v>
+        <v>-263</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0049</v>
       </c>
       <c r="H38" t="n">
-        <v>254</v>
+        <v>376</v>
       </c>
       <c r="I38" t="n">
-        <v>53281</v>
+        <v>53491</v>
       </c>
       <c r="J38" t="n">
-        <v>53502.5</v>
+        <v>53520.5</v>
       </c>
       <c r="K38" t="n">
-        <v>53718</v>
+        <v>53680</v>
       </c>
       <c r="L38" t="n">
-        <v>53933.5</v>
+        <v>53839.5</v>
       </c>
       <c r="M38" t="n">
-        <v>54152</v>
+        <v>53934</v>
       </c>
       <c r="N38" t="n">
-        <v>54370.5</v>
+        <v>54028.5</v>
       </c>
       <c r="O38" t="n">
-        <v>54583</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
+        <v>54253</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
@@ -3725,71 +3733,67 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>53790</v>
+        <v>53501</v>
       </c>
       <c r="C39" t="n">
-        <v>53840</v>
+        <v>53594</v>
       </c>
       <c r="D39" t="n">
-        <v>53464</v>
+        <v>53311</v>
       </c>
       <c r="E39" t="n">
-        <v>53544</v>
+        <v>53403</v>
       </c>
       <c r="F39" t="n">
-        <v>-263</v>
+        <v>-141</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0026</v>
       </c>
       <c r="H39" t="n">
-        <v>376</v>
+        <v>283</v>
       </c>
       <c r="I39" t="n">
-        <v>53491</v>
+        <v>53088</v>
       </c>
       <c r="J39" t="n">
-        <v>53520.5</v>
+        <v>53114</v>
       </c>
       <c r="K39" t="n">
-        <v>53680</v>
+        <v>53356</v>
       </c>
       <c r="L39" t="n">
-        <v>53839.5</v>
+        <v>53598</v>
       </c>
       <c r="M39" t="n">
-        <v>53934</v>
+        <v>53732</v>
       </c>
       <c r="N39" t="n">
-        <v>54028.5</v>
+        <v>53866</v>
       </c>
       <c r="O39" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q39" s="6" t="inlineStr">
+        <v>54216</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
@@ -3820,50 +3824,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>53501</v>
+        <v>53408</v>
       </c>
       <c r="C40" t="n">
-        <v>53594</v>
+        <v>53780</v>
       </c>
       <c r="D40" t="n">
-        <v>53311</v>
+        <v>53337</v>
       </c>
       <c r="E40" t="n">
-        <v>53403</v>
+        <v>53530</v>
       </c>
       <c r="F40" t="n">
-        <v>-141</v>
+        <v>127</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0026</v>
+        <v>0.0024</v>
       </c>
       <c r="H40" t="n">
-        <v>283</v>
+        <v>443</v>
       </c>
       <c r="I40" t="n">
-        <v>53088</v>
+        <v>53028</v>
       </c>
       <c r="J40" t="n">
-        <v>53114</v>
+        <v>53095.25</v>
       </c>
       <c r="K40" t="n">
-        <v>53356</v>
+        <v>53261.5</v>
       </c>
       <c r="L40" t="n">
-        <v>53598</v>
+        <v>53427.75</v>
       </c>
       <c r="M40" t="n">
-        <v>53732</v>
+        <v>53544.5</v>
       </c>
       <c r="N40" t="n">
-        <v>53866</v>
+        <v>53661.25</v>
       </c>
       <c r="O40" t="n">
-        <v>54216</v>
+        <v>53877</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3871,21 +3875,23 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3895,90 +3901,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>53408</v>
+        <v>53529</v>
       </c>
       <c r="C41" t="n">
-        <v>53780</v>
+        <v>53589</v>
       </c>
       <c r="D41" t="n">
-        <v>53337</v>
+        <v>52812</v>
       </c>
       <c r="E41" t="n">
-        <v>53530</v>
+        <v>52849</v>
       </c>
       <c r="F41" t="n">
-        <v>127</v>
+        <v>-681</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0127</v>
       </c>
       <c r="H41" t="n">
-        <v>443</v>
+        <v>777</v>
       </c>
       <c r="I41" t="n">
-        <v>53028</v>
+        <v>52894</v>
       </c>
       <c r="J41" t="n">
-        <v>53095.25</v>
+        <v>53072.75</v>
       </c>
       <c r="K41" t="n">
-        <v>53261.5</v>
+        <v>53308.5</v>
       </c>
       <c r="L41" t="n">
-        <v>53427.75</v>
+        <v>53544.25</v>
       </c>
       <c r="M41" t="n">
-        <v>53544.5</v>
+        <v>53751.5</v>
       </c>
       <c r="N41" t="n">
-        <v>53661.25</v>
+        <v>53958.75</v>
       </c>
       <c r="O41" t="n">
-        <v>53877</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
+        <v>54223</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U41" s="8" t="inlineStr">
+      <c r="Q41" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W41" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X41" t="inlineStr"/>
@@ -3986,77 +3990,75 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>53529</v>
+        <v>52876</v>
       </c>
       <c r="C42" t="n">
-        <v>53589</v>
+        <v>53418</v>
       </c>
       <c r="D42" t="n">
-        <v>52812</v>
+        <v>52838</v>
       </c>
       <c r="E42" t="n">
-        <v>52849</v>
+        <v>53353</v>
       </c>
       <c r="F42" t="n">
-        <v>-681</v>
+        <v>504</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0095</v>
       </c>
       <c r="H42" t="n">
-        <v>777</v>
+        <v>580</v>
       </c>
       <c r="I42" t="n">
-        <v>52894</v>
+        <v>52035</v>
       </c>
       <c r="J42" t="n">
-        <v>53072.75</v>
+        <v>51896.25</v>
       </c>
       <c r="K42" t="n">
-        <v>53308.5</v>
+        <v>52460.5</v>
       </c>
       <c r="L42" t="n">
-        <v>53544.25</v>
+        <v>53024.75</v>
       </c>
       <c r="M42" t="n">
-        <v>53751.5</v>
+        <v>53237.5</v>
       </c>
       <c r="N42" t="n">
-        <v>53958.75</v>
+        <v>53450.25</v>
       </c>
       <c r="O42" t="n">
-        <v>54223</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
+        <v>54366</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
@@ -4065,55 +4067,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>52876</v>
+        <v>53367</v>
       </c>
       <c r="C43" t="n">
-        <v>53418</v>
+        <v>53567</v>
       </c>
       <c r="D43" t="n">
-        <v>52838</v>
+        <v>53210</v>
       </c>
       <c r="E43" t="n">
-        <v>53353</v>
+        <v>53489</v>
       </c>
       <c r="F43" t="n">
-        <v>504</v>
+        <v>136</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.0025</v>
       </c>
       <c r="H43" t="n">
-        <v>580</v>
+        <v>357</v>
       </c>
       <c r="I43" t="n">
-        <v>52035</v>
+        <v>52258</v>
       </c>
       <c r="J43" t="n">
-        <v>51896.25</v>
+        <v>52885.5</v>
       </c>
       <c r="K43" t="n">
-        <v>52460.5</v>
+        <v>53063</v>
       </c>
       <c r="L43" t="n">
-        <v>53024.75</v>
+        <v>53240.5</v>
       </c>
       <c r="M43" t="n">
-        <v>53237.5</v>
+        <v>53643</v>
       </c>
       <c r="N43" t="n">
-        <v>53450.25</v>
+        <v>54045.5</v>
       </c>
       <c r="O43" t="n">
-        <v>54366</v>
+        <v>53998</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4131,14 +4137,12 @@
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U43" s="8" t="n">
+        <v/>
+      </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
@@ -4149,57 +4153,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>53367</v>
+        <v>53524</v>
       </c>
       <c r="C44" t="n">
-        <v>53567</v>
+        <v>53797</v>
       </c>
       <c r="D44" t="n">
-        <v>53210</v>
+        <v>53426</v>
       </c>
       <c r="E44" t="n">
-        <v>53489</v>
+        <v>53645</v>
       </c>
       <c r="F44" t="n">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0029</v>
       </c>
       <c r="H44" t="n">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="I44" t="n">
-        <v>52258</v>
+        <v>52853</v>
       </c>
       <c r="J44" t="n">
-        <v>52885.5</v>
+        <v>53182.25</v>
       </c>
       <c r="K44" t="n">
-        <v>53063</v>
+        <v>53310.5</v>
       </c>
       <c r="L44" t="n">
-        <v>53240.5</v>
+        <v>53438.75</v>
       </c>
       <c r="M44" t="n">
-        <v>53643</v>
+        <v>53667.5</v>
       </c>
       <c r="N44" t="n">
-        <v>54045.5</v>
+        <v>53896.25</v>
       </c>
       <c r="O44" t="n">
-        <v>53998</v>
+        <v>53924</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4240,50 +4244,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>53524</v>
+        <v>53643</v>
       </c>
       <c r="C45" t="n">
-        <v>53797</v>
+        <v>53778</v>
       </c>
       <c r="D45" t="n">
-        <v>53426</v>
+        <v>53435</v>
       </c>
       <c r="E45" t="n">
-        <v>53645</v>
+        <v>53521</v>
       </c>
       <c r="F45" t="n">
-        <v>156</v>
+        <v>-124</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0023</v>
       </c>
       <c r="H45" t="n">
-        <v>371</v>
+        <v>343</v>
       </c>
       <c r="I45" t="n">
-        <v>52853</v>
+        <v>53055</v>
       </c>
       <c r="J45" t="n">
-        <v>53182.25</v>
+        <v>53290.75</v>
       </c>
       <c r="K45" t="n">
-        <v>53310.5</v>
+        <v>53459.5</v>
       </c>
       <c r="L45" t="n">
-        <v>53438.75</v>
+        <v>53628.25</v>
       </c>
       <c r="M45" t="n">
-        <v>53667.5</v>
+        <v>53830.5</v>
       </c>
       <c r="N45" t="n">
-        <v>53896.25</v>
+        <v>54032.75</v>
       </c>
       <c r="O45" t="n">
-        <v>53924</v>
+        <v>54168</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4291,19 +4295,19 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
+      <c r="R45" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
@@ -4317,57 +4321,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>53643</v>
+        <v>53724</v>
       </c>
       <c r="C46" t="n">
-        <v>53778</v>
+        <v>53811</v>
       </c>
       <c r="D46" t="n">
-        <v>53435</v>
+        <v>53369</v>
       </c>
       <c r="E46" t="n">
-        <v>53521</v>
+        <v>53621</v>
       </c>
       <c r="F46" t="n">
-        <v>-124</v>
+        <v>100</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0019</v>
       </c>
       <c r="H46" t="n">
-        <v>343</v>
+        <v>442</v>
       </c>
       <c r="I46" t="n">
-        <v>53055</v>
+        <v>53092</v>
       </c>
       <c r="J46" t="n">
-        <v>53290.75</v>
+        <v>53135.25</v>
       </c>
       <c r="K46" t="n">
-        <v>53459.5</v>
+        <v>53349.5</v>
       </c>
       <c r="L46" t="n">
-        <v>53628.25</v>
+        <v>53563.75</v>
       </c>
       <c r="M46" t="n">
-        <v>53830.5</v>
+        <v>53692.5</v>
       </c>
       <c r="N46" t="n">
-        <v>54032.75</v>
+        <v>53821.25</v>
       </c>
       <c r="O46" t="n">
-        <v>54168</v>
+        <v>54121</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4375,18 +4379,18 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4401,57 +4405,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>53724</v>
+        <v>53608</v>
       </c>
       <c r="C47" t="n">
-        <v>53811</v>
+        <v>53862</v>
       </c>
       <c r="D47" t="n">
-        <v>53369</v>
+        <v>53513</v>
       </c>
       <c r="E47" t="n">
-        <v>53621</v>
+        <v>53584</v>
       </c>
       <c r="F47" t="n">
-        <v>100</v>
+        <v>-37</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0007</v>
       </c>
       <c r="H47" t="n">
-        <v>442</v>
+        <v>349</v>
       </c>
       <c r="I47" t="n">
-        <v>53092</v>
+        <v>52927</v>
       </c>
       <c r="J47" t="n">
-        <v>53135.25</v>
+        <v>53194.5</v>
       </c>
       <c r="K47" t="n">
-        <v>53349.5</v>
+        <v>53400</v>
       </c>
       <c r="L47" t="n">
-        <v>53563.75</v>
+        <v>53605.5</v>
       </c>
       <c r="M47" t="n">
-        <v>53692.5</v>
+        <v>53842</v>
       </c>
       <c r="N47" t="n">
-        <v>53821.25</v>
+        <v>54078.5</v>
       </c>
       <c r="O47" t="n">
-        <v>54121</v>
+        <v>54253</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4462,9 +4466,9 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
@@ -4492,69 +4496,73 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>53608</v>
+        <v>53664</v>
       </c>
       <c r="C48" t="n">
-        <v>53862</v>
+        <v>53664</v>
       </c>
       <c r="D48" t="n">
-        <v>53513</v>
+        <v>53149</v>
       </c>
       <c r="E48" t="n">
-        <v>53584</v>
+        <v>53240</v>
       </c>
       <c r="F48" t="n">
-        <v>-37</v>
+        <v>-344</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0064</v>
       </c>
       <c r="H48" t="n">
-        <v>349</v>
+        <v>515</v>
       </c>
       <c r="I48" t="n">
-        <v>52927</v>
+        <v>53164</v>
       </c>
       <c r="J48" t="n">
-        <v>53194.5</v>
+        <v>53183.25</v>
       </c>
       <c r="K48" t="n">
-        <v>53400</v>
+        <v>53409.5</v>
       </c>
       <c r="L48" t="n">
-        <v>53605.5</v>
+        <v>53635.75</v>
       </c>
       <c r="M48" t="n">
-        <v>53842</v>
+        <v>53758.5</v>
       </c>
       <c r="N48" t="n">
-        <v>54078.5</v>
+        <v>53881.25</v>
       </c>
       <c r="O48" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+        <v>54211</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4567,73 +4575,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>53664</v>
+        <v>53259</v>
       </c>
       <c r="C49" t="n">
-        <v>53664</v>
+        <v>53343</v>
       </c>
       <c r="D49" t="n">
-        <v>53149</v>
+        <v>52747</v>
       </c>
       <c r="E49" t="n">
-        <v>53240</v>
+        <v>52828</v>
       </c>
       <c r="F49" t="n">
-        <v>-344</v>
+        <v>-412</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0064</v>
+        <v>-0.0077</v>
       </c>
       <c r="H49" t="n">
-        <v>515</v>
+        <v>596</v>
       </c>
       <c r="I49" t="n">
-        <v>53164</v>
+        <v>52634</v>
       </c>
       <c r="J49" t="n">
-        <v>53183.25</v>
+        <v>52641.75</v>
       </c>
       <c r="K49" t="n">
-        <v>53409.5</v>
+        <v>52982.5</v>
       </c>
       <c r="L49" t="n">
-        <v>53635.75</v>
+        <v>53323.25</v>
       </c>
       <c r="M49" t="n">
-        <v>53758.5</v>
+        <v>53497.5</v>
       </c>
       <c r="N49" t="n">
-        <v>53881.25</v>
+        <v>53671.75</v>
       </c>
       <c r="O49" t="n">
-        <v>54211</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q49" s="6" t="inlineStr">
+        <v>54179</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
@@ -4660,50 +4660,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>53259</v>
+        <v>52844</v>
       </c>
       <c r="C50" t="n">
-        <v>53343</v>
+        <v>53283</v>
       </c>
       <c r="D50" t="n">
-        <v>52747</v>
+        <v>52720</v>
       </c>
       <c r="E50" t="n">
-        <v>52828</v>
+        <v>53121</v>
       </c>
       <c r="F50" t="n">
-        <v>-412</v>
+        <v>293</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0077</v>
+        <v>0.0055</v>
       </c>
       <c r="H50" t="n">
-        <v>596</v>
+        <v>563</v>
       </c>
       <c r="I50" t="n">
-        <v>52634</v>
+        <v>52151</v>
       </c>
       <c r="J50" t="n">
-        <v>52641.75</v>
+        <v>52123.5</v>
       </c>
       <c r="K50" t="n">
-        <v>52982.5</v>
+        <v>52530</v>
       </c>
       <c r="L50" t="n">
-        <v>53323.25</v>
+        <v>52936.5</v>
       </c>
       <c r="M50" t="n">
-        <v>53497.5</v>
+        <v>53126</v>
       </c>
       <c r="N50" t="n">
-        <v>53671.75</v>
+        <v>53315.5</v>
       </c>
       <c r="O50" t="n">
-        <v>54179</v>
+        <v>53939</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4711,19 +4711,19 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
       <c r="U50" s="8" t="n">
         <v/>
       </c>
@@ -4735,55 +4735,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>52844</v>
+        <v>53120</v>
       </c>
       <c r="C51" t="n">
-        <v>53283</v>
+        <v>53827</v>
       </c>
       <c r="D51" t="n">
-        <v>52720</v>
+        <v>53093</v>
       </c>
       <c r="E51" t="n">
-        <v>53121</v>
+        <v>53745</v>
       </c>
       <c r="F51" t="n">
-        <v>293</v>
+        <v>624</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0117</v>
       </c>
       <c r="H51" t="n">
-        <v>563</v>
+        <v>734</v>
       </c>
       <c r="I51" t="n">
-        <v>52151</v>
+        <v>52157</v>
       </c>
       <c r="J51" t="n">
-        <v>52123.5</v>
+        <v>52617.75</v>
       </c>
       <c r="K51" t="n">
-        <v>52530</v>
+        <v>52839.5</v>
       </c>
       <c r="L51" t="n">
-        <v>52936.5</v>
+        <v>53061.25</v>
       </c>
       <c r="M51" t="n">
-        <v>53126</v>
+        <v>53402.5</v>
       </c>
       <c r="N51" t="n">
-        <v>53315.5</v>
+        <v>53743.75</v>
       </c>
       <c r="O51" t="n">
-        <v>53939</v>
+        <v>53846</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4801,73 +4805,71 @@
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W51" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>53120</v>
+        <v>53707</v>
       </c>
       <c r="C52" t="n">
-        <v>53827</v>
+        <v>53772</v>
       </c>
       <c r="D52" t="n">
-        <v>53093</v>
+        <v>53235</v>
       </c>
       <c r="E52" t="n">
-        <v>53745</v>
+        <v>53440</v>
       </c>
       <c r="F52" t="n">
-        <v>624</v>
+        <v>-305</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0117</v>
+        <v>-0.0057</v>
       </c>
       <c r="H52" t="n">
-        <v>734</v>
+        <v>537</v>
       </c>
       <c r="I52" t="n">
-        <v>52157</v>
+        <v>52359</v>
       </c>
       <c r="J52" t="n">
-        <v>52617.75</v>
+        <v>53153.5</v>
       </c>
       <c r="K52" t="n">
-        <v>52839.5</v>
+        <v>53378</v>
       </c>
       <c r="L52" t="n">
-        <v>53061.25</v>
+        <v>53602.5</v>
       </c>
       <c r="M52" t="n">
-        <v>53402.5</v>
+        <v>54112</v>
       </c>
       <c r="N52" t="n">
-        <v>53743.75</v>
+        <v>54621.5</v>
       </c>
       <c r="O52" t="n">
-        <v>53846</v>
+        <v>54561</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4875,24 +4877,22 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
@@ -4901,65 +4901,71 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>53707</v>
+        <v>53261</v>
       </c>
       <c r="C53" t="n">
-        <v>53772</v>
+        <v>53336</v>
       </c>
       <c r="D53" t="n">
-        <v>53235</v>
+        <v>52758</v>
       </c>
       <c r="E53" t="n">
-        <v>53440</v>
+        <v>52832</v>
       </c>
       <c r="F53" t="n">
-        <v>-305</v>
+        <v>-608</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0057</v>
+        <v>-0.0114</v>
       </c>
       <c r="H53" t="n">
-        <v>537</v>
+        <v>578</v>
       </c>
       <c r="I53" t="n">
-        <v>52359</v>
+        <v>52698</v>
       </c>
       <c r="J53" t="n">
-        <v>53153.5</v>
+        <v>52871.25</v>
       </c>
       <c r="K53" t="n">
-        <v>53378</v>
+        <v>53171.5</v>
       </c>
       <c r="L53" t="n">
-        <v>53602.5</v>
+        <v>53471.75</v>
       </c>
       <c r="M53" t="n">
-        <v>54112</v>
+        <v>53708.5</v>
       </c>
       <c r="N53" t="n">
-        <v>54621.5</v>
+        <v>53945.25</v>
       </c>
       <c r="O53" t="n">
-        <v>54561</v>
+        <v>54309</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S53" s="10" t="inlineStr">
@@ -4976,76 +4982,70 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W53" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>53261</v>
+        <v>52817</v>
       </c>
       <c r="C54" t="n">
-        <v>53336</v>
+        <v>52859</v>
       </c>
       <c r="D54" t="n">
-        <v>52758</v>
+        <v>52339</v>
       </c>
       <c r="E54" t="n">
-        <v>52832</v>
+        <v>52425</v>
       </c>
       <c r="F54" t="n">
-        <v>-608</v>
+        <v>-407</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0114</v>
+        <v>-0.0077</v>
       </c>
       <c r="H54" t="n">
-        <v>578</v>
+        <v>520</v>
       </c>
       <c r="I54" t="n">
-        <v>52698</v>
+        <v>52180</v>
       </c>
       <c r="J54" t="n">
-        <v>52871.25</v>
+        <v>52146.5</v>
       </c>
       <c r="K54" t="n">
-        <v>53171.5</v>
+        <v>52543</v>
       </c>
       <c r="L54" t="n">
-        <v>53471.75</v>
+        <v>52939.5</v>
       </c>
       <c r="M54" t="n">
-        <v>53708.5</v>
+        <v>53121</v>
       </c>
       <c r="N54" t="n">
-        <v>53945.25</v>
+        <v>53302.5</v>
       </c>
       <c r="O54" t="n">
-        <v>54309</v>
+        <v>53914</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
@@ -5072,50 +5072,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>52817</v>
+        <v>52473</v>
       </c>
       <c r="C55" t="n">
-        <v>52859</v>
+        <v>52676</v>
       </c>
       <c r="D55" t="n">
-        <v>52339</v>
+        <v>51992</v>
       </c>
       <c r="E55" t="n">
-        <v>52425</v>
+        <v>52095</v>
       </c>
       <c r="F55" t="n">
-        <v>-407</v>
+        <v>-330</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0077</v>
+        <v>-0.0063</v>
       </c>
       <c r="H55" t="n">
-        <v>520</v>
+        <v>684</v>
       </c>
       <c r="I55" t="n">
-        <v>52180</v>
+        <v>51819</v>
       </c>
       <c r="J55" t="n">
-        <v>52146.5</v>
+        <v>51818</v>
       </c>
       <c r="K55" t="n">
-        <v>52543</v>
+        <v>52165</v>
       </c>
       <c r="L55" t="n">
-        <v>52939.5</v>
+        <v>52512</v>
       </c>
       <c r="M55" t="n">
-        <v>53121</v>
+        <v>52685</v>
       </c>
       <c r="N55" t="n">
-        <v>53302.5</v>
+        <v>52858</v>
       </c>
       <c r="O55" t="n">
-        <v>53914</v>
+        <v>53379</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5152,50 +5152,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>52473</v>
+        <v>52059</v>
       </c>
       <c r="C56" t="n">
-        <v>52676</v>
+        <v>52739</v>
       </c>
       <c r="D56" t="n">
-        <v>51992</v>
+        <v>52059</v>
       </c>
       <c r="E56" t="n">
-        <v>52095</v>
+        <v>52585</v>
       </c>
       <c r="F56" t="n">
-        <v>-330</v>
+        <v>490</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0063</v>
+        <v>0.0094</v>
       </c>
       <c r="H56" t="n">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="I56" t="n">
-        <v>51819</v>
+        <v>51308</v>
       </c>
       <c r="J56" t="n">
-        <v>51818</v>
+        <v>51291.5</v>
       </c>
       <c r="K56" t="n">
-        <v>52165</v>
+        <v>51753</v>
       </c>
       <c r="L56" t="n">
-        <v>52512</v>
+        <v>52214.5</v>
       </c>
       <c r="M56" t="n">
-        <v>52685</v>
+        <v>52437</v>
       </c>
       <c r="N56" t="n">
-        <v>52858</v>
+        <v>52659.5</v>
       </c>
       <c r="O56" t="n">
-        <v>53379</v>
+        <v>53360</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5203,22 +5203,24 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
@@ -5227,55 +5229,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>52059</v>
+        <v>52376</v>
       </c>
       <c r="C57" t="n">
-        <v>52739</v>
+        <v>52672</v>
       </c>
       <c r="D57" t="n">
-        <v>52059</v>
+        <v>52226</v>
       </c>
       <c r="E57" t="n">
-        <v>52585</v>
+        <v>52440</v>
       </c>
       <c r="F57" t="n">
-        <v>490</v>
+        <v>-145</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0094</v>
+        <v>-0.0028</v>
       </c>
       <c r="H57" t="n">
-        <v>680</v>
+        <v>446</v>
       </c>
       <c r="I57" t="n">
-        <v>51308</v>
+        <v>51379</v>
       </c>
       <c r="J57" t="n">
-        <v>51291.5</v>
+        <v>51998</v>
       </c>
       <c r="K57" t="n">
-        <v>51753</v>
+        <v>52245</v>
       </c>
       <c r="L57" t="n">
-        <v>52214.5</v>
+        <v>52492</v>
       </c>
       <c r="M57" t="n">
-        <v>52437</v>
+        <v>52925</v>
       </c>
       <c r="N57" t="n">
-        <v>52659.5</v>
+        <v>53358</v>
       </c>
       <c r="O57" t="n">
-        <v>53360</v>
+        <v>53419</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5283,23 +5289,21 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
@@ -5311,72 +5315,74 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>52376</v>
+        <v>52499</v>
       </c>
       <c r="C58" t="n">
-        <v>52672</v>
+        <v>52499</v>
       </c>
       <c r="D58" t="n">
-        <v>52226</v>
+        <v>51908</v>
       </c>
       <c r="E58" t="n">
-        <v>52440</v>
+        <v>52115</v>
       </c>
       <c r="F58" t="n">
-        <v>-145</v>
+        <v>-325</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0028</v>
+        <v>-0.0062</v>
       </c>
       <c r="H58" t="n">
-        <v>446</v>
+        <v>591</v>
       </c>
       <c r="I58" t="n">
-        <v>51379</v>
+        <v>51780</v>
       </c>
       <c r="J58" t="n">
-        <v>51998</v>
+        <v>51989.5</v>
       </c>
       <c r="K58" t="n">
-        <v>52245</v>
+        <v>52217</v>
       </c>
       <c r="L58" t="n">
-        <v>52492</v>
+        <v>52444.5</v>
       </c>
       <c r="M58" t="n">
-        <v>52925</v>
+        <v>52663</v>
       </c>
       <c r="N58" t="n">
-        <v>53358</v>
+        <v>52881.5</v>
       </c>
       <c r="O58" t="n">
-        <v>53419</v>
+        <v>53118</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5393,71 +5399,69 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>52499</v>
+        <v>52162</v>
       </c>
       <c r="C59" t="n">
-        <v>52499</v>
+        <v>52298</v>
       </c>
       <c r="D59" t="n">
-        <v>51908</v>
+        <v>51209</v>
       </c>
       <c r="E59" t="n">
-        <v>52115</v>
+        <v>51507</v>
       </c>
       <c r="F59" t="n">
-        <v>-325</v>
+        <v>-608</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0062</v>
+        <v>-0.0117</v>
       </c>
       <c r="H59" t="n">
-        <v>591</v>
+        <v>1089</v>
       </c>
       <c r="I59" t="n">
-        <v>51780</v>
+        <v>51317</v>
       </c>
       <c r="J59" t="n">
-        <v>51989.5</v>
+        <v>51479.75</v>
       </c>
       <c r="K59" t="n">
-        <v>52217</v>
+        <v>51819.5</v>
       </c>
       <c r="L59" t="n">
-        <v>52444.5</v>
+        <v>52159.25</v>
       </c>
       <c r="M59" t="n">
-        <v>52663</v>
+        <v>52410.5</v>
       </c>
       <c r="N59" t="n">
-        <v>52881.5</v>
+        <v>52661.75</v>
       </c>
       <c r="O59" t="n">
-        <v>53118</v>
-      </c>
-      <c r="P59" s="6" t="n">
-        <v/>
+        <v>53090</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q59" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="S59" s="10" t="inlineStr">
@@ -5484,74 +5488,70 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>52162</v>
+        <v>51486</v>
       </c>
       <c r="C60" t="n">
-        <v>52298</v>
+        <v>52169</v>
       </c>
       <c r="D60" t="n">
-        <v>51209</v>
+        <v>51455</v>
       </c>
       <c r="E60" t="n">
-        <v>51507</v>
+        <v>51807</v>
       </c>
       <c r="F60" t="n">
-        <v>-608</v>
+        <v>300</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0117</v>
+        <v>0.0058</v>
       </c>
       <c r="H60" t="n">
-        <v>1089</v>
+        <v>714</v>
       </c>
       <c r="I60" t="n">
-        <v>51317</v>
+        <v>50120</v>
       </c>
       <c r="J60" t="n">
-        <v>51479.75</v>
+        <v>50294.75</v>
       </c>
       <c r="K60" t="n">
-        <v>51819.5</v>
+        <v>50962.5</v>
       </c>
       <c r="L60" t="n">
-        <v>52159.25</v>
+        <v>51630.25</v>
       </c>
       <c r="M60" t="n">
-        <v>52410.5</v>
+        <v>52051.5</v>
       </c>
       <c r="N60" t="n">
-        <v>52661.75</v>
+        <v>52472.75</v>
       </c>
       <c r="O60" t="n">
-        <v>53090</v>
-      </c>
-      <c r="P60" s="6" t="inlineStr">
+        <v>53387</v>
+      </c>
+      <c r="P60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
       <c r="U60" s="8" t="n">
         <v/>
       </c>
@@ -5563,55 +5563,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>51486</v>
+        <v>51800</v>
       </c>
       <c r="C61" t="n">
-        <v>52169</v>
+        <v>51957</v>
       </c>
       <c r="D61" t="n">
-        <v>51455</v>
+        <v>51576</v>
       </c>
       <c r="E61" t="n">
-        <v>51807</v>
+        <v>51761</v>
       </c>
       <c r="F61" t="n">
-        <v>300</v>
+        <v>-46</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0009</v>
       </c>
       <c r="H61" t="n">
-        <v>714</v>
+        <v>381</v>
       </c>
       <c r="I61" t="n">
-        <v>50120</v>
+        <v>50741</v>
       </c>
       <c r="J61" t="n">
-        <v>50294.75</v>
+        <v>51090.5</v>
       </c>
       <c r="K61" t="n">
-        <v>50962.5</v>
+        <v>51450</v>
       </c>
       <c r="L61" t="n">
-        <v>51630.25</v>
+        <v>51809.5</v>
       </c>
       <c r="M61" t="n">
-        <v>52051.5</v>
+        <v>52164</v>
       </c>
       <c r="N61" t="n">
-        <v>52472.75</v>
+        <v>52518.5</v>
       </c>
       <c r="O61" t="n">
-        <v>53387</v>
+        <v>52883</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5622,15 +5626,13 @@
       <c r="R61" s="6" t="n">
         <v/>
       </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5645,57 +5647,57 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>51800</v>
+        <v>52470</v>
       </c>
       <c r="C62" t="n">
-        <v>51957</v>
+        <v>52473</v>
       </c>
       <c r="D62" t="n">
-        <v>51576</v>
+        <v>52452</v>
       </c>
       <c r="E62" t="n">
-        <v>51761</v>
+        <v>52468</v>
       </c>
       <c r="F62" t="n">
-        <v>-46</v>
+        <v>707</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0137</v>
       </c>
       <c r="H62" t="n">
-        <v>381</v>
+        <v>21</v>
       </c>
       <c r="I62" t="n">
-        <v>50741</v>
+        <v>51195</v>
       </c>
       <c r="J62" t="n">
-        <v>51090.5</v>
+        <v>51377.25</v>
       </c>
       <c r="K62" t="n">
-        <v>51450</v>
+        <v>51570.5</v>
       </c>
       <c r="L62" t="n">
-        <v>51809.5</v>
+        <v>51763.75</v>
       </c>
       <c r="M62" t="n">
-        <v>52164</v>
+        <v>51951.5</v>
       </c>
       <c r="N62" t="n">
-        <v>52518.5</v>
+        <v>52139.25</v>
       </c>
       <c r="O62" t="n">
-        <v>52883</v>
+        <v>52338</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5706,116 +5708,32 @@
       <c r="R62" s="6" t="n">
         <v/>
       </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>52085</v>
-      </c>
-      <c r="C63" t="n">
-        <v>52140</v>
-      </c>
-      <c r="D63" t="n">
-        <v>52080</v>
-      </c>
-      <c r="E63" t="n">
-        <v>52079</v>
-      </c>
-      <c r="F63" t="n">
-        <v>318</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0.0061</v>
-      </c>
-      <c r="H63" t="n">
-        <v>60</v>
-      </c>
-      <c r="I63" t="n">
-        <v>51195</v>
-      </c>
-      <c r="J63" t="n">
-        <v>51377.25</v>
-      </c>
-      <c r="K63" t="n">
-        <v>51570.5</v>
-      </c>
-      <c r="L63" t="n">
-        <v>51763.75</v>
-      </c>
-      <c r="M63" t="n">
-        <v>51951.5</v>
-      </c>
-      <c r="N63" t="n">
-        <v>52139.25</v>
-      </c>
-      <c r="O63" t="n">
-        <v>52338</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="7" t="inlineStr">
+      <c r="S62" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T63" s="8" t="inlineStr">
+      <c r="T62" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U63" s="8" t="inlineStr">
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W62" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5658,25 +5658,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>52470</v>
+        <v>52085</v>
       </c>
       <c r="C62" t="n">
-        <v>52473</v>
+        <v>52557</v>
       </c>
       <c r="D62" t="n">
-        <v>52452</v>
+        <v>52080</v>
       </c>
       <c r="E62" t="n">
-        <v>52468</v>
+        <v>52475</v>
       </c>
       <c r="F62" t="n">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0137</v>
+        <v>0.0138</v>
       </c>
       <c r="H62" t="n">
-        <v>21</v>
+        <v>477</v>
       </c>
       <c r="I62" t="n">
         <v>51195</v>
@@ -5734,6 +5734,90 @@
         </is>
       </c>
       <c r="X62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>52470</v>
+      </c>
+      <c r="C63" t="n">
+        <v>52844</v>
+      </c>
+      <c r="D63" t="n">
+        <v>52307</v>
+      </c>
+      <c r="E63" t="n">
+        <v>52423</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-52</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="H63" t="n">
+        <v>537</v>
+      </c>
+      <c r="I63" t="n">
+        <v>51603</v>
+      </c>
+      <c r="J63" t="n">
+        <v>52076.25</v>
+      </c>
+      <c r="K63" t="n">
+        <v>52236.5</v>
+      </c>
+      <c r="L63" t="n">
+        <v>52396.75</v>
+      </c>
+      <c r="M63" t="n">
+        <v>52713.5</v>
+      </c>
+      <c r="N63" t="n">
+        <v>53030.25</v>
+      </c>
+      <c r="O63" t="n">
+        <v>53034</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -5748,19 +5748,19 @@
         <v>52844</v>
       </c>
       <c r="D63" t="n">
-        <v>52307</v>
+        <v>52170</v>
       </c>
       <c r="E63" t="n">
-        <v>52423</v>
+        <v>52228</v>
       </c>
       <c r="F63" t="n">
-        <v>-52</v>
+        <v>-247</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0047</v>
       </c>
       <c r="H63" t="n">
-        <v>537</v>
+        <v>674</v>
       </c>
       <c r="I63" t="n">
         <v>51603</v>
@@ -5789,12 +5789,14 @@
       <c r="Q63" s="6" t="n">
         <v/>
       </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T63" s="8" t="inlineStr">

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52381</v>
+        <v>52439</v>
       </c>
       <c r="C2" t="n">
-        <v>53097</v>
+        <v>52542</v>
       </c>
       <c r="D2" t="n">
-        <v>52215</v>
+        <v>52008</v>
       </c>
       <c r="E2" t="n">
-        <v>52339</v>
+        <v>52209</v>
       </c>
       <c r="F2" t="n">
-        <v>60</v>
+        <v>-130</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0011</v>
+        <v>-0.0025</v>
       </c>
       <c r="H2" t="n">
-        <v>882</v>
+        <v>534</v>
       </c>
       <c r="I2" t="n">
-        <v>51190</v>
+        <v>51333</v>
       </c>
       <c r="J2" t="n">
-        <v>51523.25</v>
+        <v>51298.5</v>
       </c>
       <c r="K2" t="n">
-        <v>51907.5</v>
+        <v>51898</v>
       </c>
       <c r="L2" t="n">
-        <v>52291.75</v>
+        <v>52497.5</v>
       </c>
       <c r="M2" t="n">
-        <v>52650.5</v>
+        <v>52780</v>
       </c>
       <c r="N2" t="n">
-        <v>53009.25</v>
+        <v>53062.5</v>
       </c>
       <c r="O2" t="n">
-        <v>53419</v>
+        <v>53979</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,18 +690,14 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -711,55 +707,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>52439</v>
+        <v>52183</v>
       </c>
       <c r="C3" t="n">
-        <v>52542</v>
+        <v>52700</v>
       </c>
       <c r="D3" t="n">
-        <v>52008</v>
+        <v>52179</v>
       </c>
       <c r="E3" t="n">
-        <v>52209</v>
+        <v>52572</v>
       </c>
       <c r="F3" t="n">
-        <v>-130</v>
+        <v>363</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.007</v>
       </c>
       <c r="H3" t="n">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="I3" t="n">
-        <v>51333</v>
+        <v>51474</v>
       </c>
       <c r="J3" t="n">
-        <v>51298.5</v>
+        <v>51642</v>
       </c>
       <c r="K3" t="n">
-        <v>51898</v>
+        <v>51942</v>
       </c>
       <c r="L3" t="n">
-        <v>52497.5</v>
+        <v>52242</v>
       </c>
       <c r="M3" t="n">
-        <v>52780</v>
+        <v>52476</v>
       </c>
       <c r="N3" t="n">
-        <v>53062.5</v>
+        <v>52710</v>
       </c>
       <c r="O3" t="n">
-        <v>53979</v>
+        <v>53076</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -772,11 +772,13 @@
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -789,59 +791,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>52183</v>
+        <v>52554</v>
       </c>
       <c r="C4" t="n">
-        <v>52700</v>
+        <v>52763</v>
       </c>
       <c r="D4" t="n">
-        <v>52179</v>
+        <v>52383</v>
       </c>
       <c r="E4" t="n">
-        <v>52572</v>
+        <v>52670</v>
       </c>
       <c r="F4" t="n">
-        <v>363</v>
+        <v>98</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.007</v>
+        <v>0.0019</v>
       </c>
       <c r="H4" t="n">
-        <v>521</v>
+        <v>380</v>
       </c>
       <c r="I4" t="n">
-        <v>51474</v>
+        <v>51658</v>
       </c>
       <c r="J4" t="n">
-        <v>51642</v>
+        <v>52117.25</v>
       </c>
       <c r="K4" t="n">
-        <v>51942</v>
+        <v>52311.5</v>
       </c>
       <c r="L4" t="n">
-        <v>52242</v>
+        <v>52505.75</v>
       </c>
       <c r="M4" t="n">
-        <v>52476</v>
+        <v>52832.5</v>
       </c>
       <c r="N4" t="n">
-        <v>52710</v>
+        <v>53159.25</v>
       </c>
       <c r="O4" t="n">
-        <v>53076</v>
+        <v>53221</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -852,7 +850,7 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -878,50 +876,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52554</v>
+        <v>52546</v>
       </c>
       <c r="C5" t="n">
-        <v>52763</v>
+        <v>53105</v>
       </c>
       <c r="D5" t="n">
-        <v>52383</v>
+        <v>52381</v>
       </c>
       <c r="E5" t="n">
-        <v>52670</v>
+        <v>52668</v>
       </c>
       <c r="F5" t="n">
-        <v>98</v>
+        <v>-2</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>380</v>
+        <v>724</v>
       </c>
       <c r="I5" t="n">
-        <v>51658</v>
+        <v>52003</v>
       </c>
       <c r="J5" t="n">
-        <v>52117.25</v>
+        <v>52338.5</v>
       </c>
       <c r="K5" t="n">
-        <v>52311.5</v>
+        <v>52480</v>
       </c>
       <c r="L5" t="n">
-        <v>52505.75</v>
+        <v>52621.5</v>
       </c>
       <c r="M5" t="n">
-        <v>52832.5</v>
+        <v>52860</v>
       </c>
       <c r="N5" t="n">
-        <v>53159.25</v>
+        <v>53098.5</v>
       </c>
       <c r="O5" t="n">
-        <v>53221</v>
+        <v>53143</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -929,21 +927,25 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -953,55 +955,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52546</v>
+        <v>52640</v>
       </c>
       <c r="C6" t="n">
-        <v>53105</v>
+        <v>53218</v>
       </c>
       <c r="D6" t="n">
-        <v>52381</v>
+        <v>52551</v>
       </c>
       <c r="E6" t="n">
-        <v>52668</v>
+        <v>53183</v>
       </c>
       <c r="F6" t="n">
-        <v>-2</v>
+        <v>515</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0</v>
+        <v>0.0098</v>
       </c>
       <c r="H6" t="n">
-        <v>724</v>
+        <v>667</v>
       </c>
       <c r="I6" t="n">
-        <v>52003</v>
+        <v>51657</v>
       </c>
       <c r="J6" t="n">
-        <v>52338.5</v>
+        <v>51906.5</v>
       </c>
       <c r="K6" t="n">
-        <v>52480</v>
+        <v>52306</v>
       </c>
       <c r="L6" t="n">
-        <v>52621.5</v>
+        <v>52705.5</v>
       </c>
       <c r="M6" t="n">
-        <v>52860</v>
+        <v>53030</v>
       </c>
       <c r="N6" t="n">
-        <v>53098.5</v>
+        <v>53354.5</v>
       </c>
       <c r="O6" t="n">
-        <v>53143</v>
+        <v>53829</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1009,25 +1015,21 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
@@ -1037,59 +1039,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>52640</v>
+        <v>53230</v>
       </c>
       <c r="C7" t="n">
-        <v>53218</v>
+        <v>53421</v>
       </c>
       <c r="D7" t="n">
-        <v>52551</v>
+        <v>52962</v>
       </c>
       <c r="E7" t="n">
-        <v>53183</v>
+        <v>53372</v>
       </c>
       <c r="F7" t="n">
-        <v>515</v>
+        <v>189</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0036</v>
       </c>
       <c r="H7" t="n">
-        <v>667</v>
+        <v>459</v>
       </c>
       <c r="I7" t="n">
-        <v>51657</v>
+        <v>51884</v>
       </c>
       <c r="J7" t="n">
-        <v>51906.5</v>
+        <v>52665.25</v>
       </c>
       <c r="K7" t="n">
-        <v>52306</v>
+        <v>52849.5</v>
       </c>
       <c r="L7" t="n">
-        <v>52705.5</v>
+        <v>53033.75</v>
       </c>
       <c r="M7" t="n">
-        <v>53030</v>
+        <v>53516.5</v>
       </c>
       <c r="N7" t="n">
-        <v>53354.5</v>
+        <v>53999.25</v>
       </c>
       <c r="O7" t="n">
-        <v>53829</v>
+        <v>53885</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1100,7 +1098,7 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1126,50 +1124,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>53230</v>
+        <v>53405</v>
       </c>
       <c r="C8" t="n">
-        <v>53421</v>
+        <v>53656</v>
       </c>
       <c r="D8" t="n">
-        <v>52962</v>
+        <v>53076</v>
       </c>
       <c r="E8" t="n">
-        <v>53372</v>
+        <v>53197</v>
       </c>
       <c r="F8" t="n">
-        <v>189</v>
+        <v>-175</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0036</v>
+        <v>-0.0033</v>
       </c>
       <c r="H8" t="n">
-        <v>459</v>
+        <v>580</v>
       </c>
       <c r="I8" t="n">
-        <v>51884</v>
+        <v>52503</v>
       </c>
       <c r="J8" t="n">
-        <v>52665.25</v>
+        <v>53003.25</v>
       </c>
       <c r="K8" t="n">
-        <v>52849.5</v>
+        <v>53142.5</v>
       </c>
       <c r="L8" t="n">
-        <v>53033.75</v>
+        <v>53281.75</v>
       </c>
       <c r="M8" t="n">
-        <v>53516.5</v>
+        <v>53601.5</v>
       </c>
       <c r="N8" t="n">
-        <v>53999.25</v>
+        <v>53921.25</v>
       </c>
       <c r="O8" t="n">
-        <v>53885</v>
+        <v>53880</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1177,17 +1175,19 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U8" s="8" t="n">
@@ -1201,76 +1201,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53405</v>
+        <v>53166</v>
       </c>
       <c r="C9" t="n">
-        <v>53656</v>
+        <v>53207</v>
       </c>
       <c r="D9" t="n">
-        <v>53076</v>
+        <v>52343</v>
       </c>
       <c r="E9" t="n">
-        <v>53197</v>
+        <v>52624</v>
       </c>
       <c r="F9" t="n">
-        <v>-175</v>
+        <v>-573</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0108</v>
       </c>
       <c r="H9" t="n">
-        <v>580</v>
+        <v>864</v>
       </c>
       <c r="I9" t="n">
-        <v>52503</v>
+        <v>52496</v>
       </c>
       <c r="J9" t="n">
-        <v>53003.25</v>
+        <v>52532.5</v>
       </c>
       <c r="K9" t="n">
-        <v>53142.5</v>
+        <v>52907</v>
       </c>
       <c r="L9" t="n">
-        <v>53281.75</v>
+        <v>53281.5</v>
       </c>
       <c r="M9" t="n">
-        <v>53601.5</v>
+        <v>53487</v>
       </c>
       <c r="N9" t="n">
-        <v>53921.25</v>
+        <v>53692.5</v>
       </c>
       <c r="O9" t="n">
-        <v>53880</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
+        <v>54236</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1285,76 +1291,70 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53166</v>
+        <v>52541</v>
       </c>
       <c r="C10" t="n">
-        <v>53207</v>
+        <v>52865</v>
       </c>
       <c r="D10" t="n">
-        <v>52343</v>
+        <v>52501</v>
       </c>
       <c r="E10" t="n">
-        <v>52624</v>
+        <v>52761</v>
       </c>
       <c r="F10" t="n">
-        <v>-573</v>
+        <v>137</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0108</v>
+        <v>0.0026</v>
       </c>
       <c r="H10" t="n">
-        <v>864</v>
+        <v>364</v>
       </c>
       <c r="I10" t="n">
-        <v>52496</v>
+        <v>51479</v>
       </c>
       <c r="J10" t="n">
-        <v>52532.5</v>
+        <v>51684.5</v>
       </c>
       <c r="K10" t="n">
-        <v>52907</v>
+        <v>52192</v>
       </c>
       <c r="L10" t="n">
-        <v>53281.5</v>
+        <v>52699.5</v>
       </c>
       <c r="M10" t="n">
-        <v>53487</v>
+        <v>53056</v>
       </c>
       <c r="N10" t="n">
-        <v>53692.5</v>
+        <v>53412.5</v>
       </c>
       <c r="O10" t="n">
-        <v>54236</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>54071</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1373,57 +1373,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>52541</v>
+        <v>52753</v>
       </c>
       <c r="C11" t="n">
-        <v>52865</v>
+        <v>52992</v>
       </c>
       <c r="D11" t="n">
-        <v>52501</v>
+        <v>52506</v>
       </c>
       <c r="E11" t="n">
-        <v>52761</v>
+        <v>52906</v>
       </c>
       <c r="F11" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0027</v>
       </c>
       <c r="H11" t="n">
-        <v>364</v>
+        <v>486</v>
       </c>
       <c r="I11" t="n">
-        <v>51479</v>
+        <v>52137</v>
       </c>
       <c r="J11" t="n">
-        <v>51684.5</v>
+        <v>52436</v>
       </c>
       <c r="K11" t="n">
-        <v>52192</v>
+        <v>52579</v>
       </c>
       <c r="L11" t="n">
-        <v>52699.5</v>
+        <v>52722</v>
       </c>
       <c r="M11" t="n">
-        <v>53056</v>
+        <v>52943</v>
       </c>
       <c r="N11" t="n">
-        <v>53412.5</v>
+        <v>53164</v>
       </c>
       <c r="O11" t="n">
-        <v>54071</v>
+        <v>53229</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1431,16 +1431,20 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1453,59 +1457,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52753</v>
+        <v>52844</v>
       </c>
       <c r="C12" t="n">
-        <v>52992</v>
+        <v>53113</v>
       </c>
       <c r="D12" t="n">
-        <v>52506</v>
+        <v>52603</v>
       </c>
       <c r="E12" t="n">
-        <v>52906</v>
+        <v>52764</v>
       </c>
       <c r="F12" t="n">
-        <v>145</v>
+        <v>-142</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0027</v>
       </c>
       <c r="H12" t="n">
-        <v>486</v>
+        <v>510</v>
       </c>
       <c r="I12" t="n">
-        <v>52137</v>
+        <v>52020</v>
       </c>
       <c r="J12" t="n">
-        <v>52436</v>
+        <v>52498.5</v>
       </c>
       <c r="K12" t="n">
-        <v>52579</v>
+        <v>52663</v>
       </c>
       <c r="L12" t="n">
-        <v>52722</v>
+        <v>52827.5</v>
       </c>
       <c r="M12" t="n">
-        <v>52943</v>
+        <v>53149</v>
       </c>
       <c r="N12" t="n">
-        <v>53164</v>
+        <v>53470.5</v>
       </c>
       <c r="O12" t="n">
-        <v>53229</v>
+        <v>53478</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1520,13 +1520,11 @@
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1539,55 +1537,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>52844</v>
+        <v>52731</v>
       </c>
       <c r="C13" t="n">
-        <v>53113</v>
+        <v>52981</v>
       </c>
       <c r="D13" t="n">
-        <v>52603</v>
+        <v>52255</v>
       </c>
       <c r="E13" t="n">
-        <v>52764</v>
+        <v>52791</v>
       </c>
       <c r="F13" t="n">
-        <v>-142</v>
+        <v>27</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0005</v>
       </c>
       <c r="H13" t="n">
-        <v>510</v>
+        <v>726</v>
       </c>
       <c r="I13" t="n">
-        <v>52020</v>
+        <v>52093</v>
       </c>
       <c r="J13" t="n">
-        <v>52498.5</v>
+        <v>52207</v>
       </c>
       <c r="K13" t="n">
-        <v>52663</v>
+        <v>52509</v>
       </c>
       <c r="L13" t="n">
-        <v>52827.5</v>
+        <v>52811</v>
       </c>
       <c r="M13" t="n">
-        <v>53149</v>
+        <v>53019</v>
       </c>
       <c r="N13" t="n">
-        <v>53470.5</v>
+        <v>53227</v>
       </c>
       <c r="O13" t="n">
-        <v>53478</v>
+        <v>53623</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1600,7 +1602,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -1621,57 +1623,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>52731</v>
+        <v>52792</v>
       </c>
       <c r="C14" t="n">
-        <v>52981</v>
+        <v>53088</v>
       </c>
       <c r="D14" t="n">
-        <v>52255</v>
+        <v>52680</v>
       </c>
       <c r="E14" t="n">
-        <v>52791</v>
+        <v>52900</v>
       </c>
       <c r="F14" t="n">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0021</v>
       </c>
       <c r="H14" t="n">
-        <v>726</v>
+        <v>408</v>
       </c>
       <c r="I14" t="n">
-        <v>52093</v>
+        <v>51529</v>
       </c>
       <c r="J14" t="n">
-        <v>52207</v>
+        <v>52151.5</v>
       </c>
       <c r="K14" t="n">
-        <v>52509</v>
+        <v>52428</v>
       </c>
       <c r="L14" t="n">
-        <v>52811</v>
+        <v>52704.5</v>
       </c>
       <c r="M14" t="n">
-        <v>53019</v>
+        <v>53154</v>
       </c>
       <c r="N14" t="n">
-        <v>53227</v>
+        <v>53603.5</v>
       </c>
       <c r="O14" t="n">
-        <v>53623</v>
+        <v>53707</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1679,14 +1681,12 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R14" s="6" t="n">
+        <v/>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1703,59 +1703,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52792</v>
+        <v>52919</v>
       </c>
       <c r="C15" t="n">
-        <v>53088</v>
+        <v>53108</v>
       </c>
       <c r="D15" t="n">
-        <v>52680</v>
+        <v>52607</v>
       </c>
       <c r="E15" t="n">
-        <v>52900</v>
+        <v>52786</v>
       </c>
       <c r="F15" t="n">
-        <v>109</v>
+        <v>-114</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0022</v>
       </c>
       <c r="H15" t="n">
-        <v>408</v>
+        <v>501</v>
       </c>
       <c r="I15" t="n">
-        <v>51529</v>
+        <v>52272</v>
       </c>
       <c r="J15" t="n">
-        <v>52151.5</v>
+        <v>52500</v>
       </c>
       <c r="K15" t="n">
-        <v>52428</v>
+        <v>52696</v>
       </c>
       <c r="L15" t="n">
-        <v>52704.5</v>
+        <v>52892</v>
       </c>
       <c r="M15" t="n">
-        <v>53154</v>
+        <v>53104</v>
       </c>
       <c r="N15" t="n">
-        <v>53603.5</v>
+        <v>53316</v>
       </c>
       <c r="O15" t="n">
-        <v>53707</v>
+        <v>53496</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1763,16 +1759,20 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1785,76 +1785,80 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>52919</v>
+        <v>52778</v>
       </c>
       <c r="C16" t="n">
-        <v>53108</v>
+        <v>52835</v>
       </c>
       <c r="D16" t="n">
-        <v>52607</v>
+        <v>52174</v>
       </c>
       <c r="E16" t="n">
-        <v>52786</v>
+        <v>52375</v>
       </c>
       <c r="F16" t="n">
-        <v>-114</v>
+        <v>-411</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0078</v>
       </c>
       <c r="H16" t="n">
-        <v>501</v>
+        <v>661</v>
       </c>
       <c r="I16" t="n">
-        <v>52272</v>
+        <v>52106</v>
       </c>
       <c r="J16" t="n">
-        <v>52500</v>
+        <v>52249.25</v>
       </c>
       <c r="K16" t="n">
-        <v>52696</v>
+        <v>52535.5</v>
       </c>
       <c r="L16" t="n">
-        <v>52892</v>
+        <v>52821.75</v>
       </c>
       <c r="M16" t="n">
-        <v>53104</v>
+        <v>53036.5</v>
       </c>
       <c r="N16" t="n">
-        <v>53316</v>
+        <v>53251.25</v>
       </c>
       <c r="O16" t="n">
-        <v>53496</v>
+        <v>53609</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1869,72 +1873,70 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52778</v>
+        <v>52300</v>
       </c>
       <c r="C17" t="n">
-        <v>52835</v>
+        <v>52633</v>
       </c>
       <c r="D17" t="n">
-        <v>52174</v>
+        <v>51999</v>
       </c>
       <c r="E17" t="n">
-        <v>52375</v>
+        <v>52073</v>
       </c>
       <c r="F17" t="n">
-        <v>-411</v>
+        <v>-302</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0078</v>
+        <v>-0.0058</v>
       </c>
       <c r="H17" t="n">
-        <v>661</v>
+        <v>634</v>
       </c>
       <c r="I17" t="n">
-        <v>52106</v>
+        <v>51513</v>
       </c>
       <c r="J17" t="n">
-        <v>52249.25</v>
+        <v>51649.25</v>
       </c>
       <c r="K17" t="n">
-        <v>52535.5</v>
+        <v>52044.5</v>
       </c>
       <c r="L17" t="n">
-        <v>52821.75</v>
+        <v>52439.75</v>
       </c>
       <c r="M17" t="n">
-        <v>53036.5</v>
+        <v>52705.5</v>
       </c>
       <c r="N17" t="n">
-        <v>53251.25</v>
+        <v>52971.25</v>
       </c>
       <c r="O17" t="n">
-        <v>53609</v>
+        <v>53496</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1962,50 +1964,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52300</v>
+        <v>52091</v>
       </c>
       <c r="C18" t="n">
-        <v>52633</v>
+        <v>52590</v>
       </c>
       <c r="D18" t="n">
-        <v>51999</v>
+        <v>52035</v>
       </c>
       <c r="E18" t="n">
-        <v>52073</v>
+        <v>52443</v>
       </c>
       <c r="F18" t="n">
-        <v>-302</v>
+        <v>370</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.0071</v>
       </c>
       <c r="H18" t="n">
-        <v>634</v>
+        <v>555</v>
       </c>
       <c r="I18" t="n">
-        <v>51513</v>
+        <v>51365</v>
       </c>
       <c r="J18" t="n">
-        <v>51649.25</v>
+        <v>51317.5</v>
       </c>
       <c r="K18" t="n">
-        <v>52044.5</v>
+        <v>51756</v>
       </c>
       <c r="L18" t="n">
-        <v>52439.75</v>
+        <v>52194.5</v>
       </c>
       <c r="M18" t="n">
-        <v>52705.5</v>
+        <v>52390</v>
       </c>
       <c r="N18" t="n">
-        <v>52971.25</v>
+        <v>52585.5</v>
       </c>
       <c r="O18" t="n">
-        <v>53496</v>
+        <v>53267</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2013,21 +2015,23 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2039,57 +2043,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>52091</v>
+        <v>52431</v>
       </c>
       <c r="C19" t="n">
-        <v>52590</v>
+        <v>52721</v>
       </c>
       <c r="D19" t="n">
-        <v>52035</v>
+        <v>52262</v>
       </c>
       <c r="E19" t="n">
-        <v>52443</v>
+        <v>52449</v>
       </c>
       <c r="F19" t="n">
-        <v>370</v>
+        <v>6</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0001</v>
       </c>
       <c r="H19" t="n">
-        <v>555</v>
+        <v>459</v>
       </c>
       <c r="I19" t="n">
-        <v>51365</v>
+        <v>51480</v>
       </c>
       <c r="J19" t="n">
-        <v>51317.5</v>
+        <v>51953.25</v>
       </c>
       <c r="K19" t="n">
-        <v>51756</v>
+        <v>52165.5</v>
       </c>
       <c r="L19" t="n">
-        <v>52194.5</v>
+        <v>52377.75</v>
       </c>
       <c r="M19" t="n">
-        <v>52390</v>
+        <v>52720.5</v>
       </c>
       <c r="N19" t="n">
-        <v>52585.5</v>
+        <v>53063.25</v>
       </c>
       <c r="O19" t="n">
-        <v>53267</v>
+        <v>53145</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2100,21 +2104,19 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
@@ -2123,78 +2125,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>52431</v>
+        <v>52430</v>
       </c>
       <c r="C20" t="n">
-        <v>52721</v>
+        <v>52515</v>
       </c>
       <c r="D20" t="n">
-        <v>52262</v>
+        <v>51720</v>
       </c>
       <c r="E20" t="n">
-        <v>52449</v>
+        <v>51894</v>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>-555</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0106</v>
       </c>
       <c r="H20" t="n">
-        <v>459</v>
+        <v>795</v>
       </c>
       <c r="I20" t="n">
-        <v>51480</v>
+        <v>51803</v>
       </c>
       <c r="J20" t="n">
-        <v>51953.25</v>
+        <v>51968.75</v>
       </c>
       <c r="K20" t="n">
-        <v>52165.5</v>
+        <v>52219.5</v>
       </c>
       <c r="L20" t="n">
-        <v>52377.75</v>
+        <v>52470.25</v>
       </c>
       <c r="M20" t="n">
-        <v>52720.5</v>
+        <v>52678.5</v>
       </c>
       <c r="N20" t="n">
-        <v>53063.25</v>
+        <v>52886.75</v>
       </c>
       <c r="O20" t="n">
-        <v>53145</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+        <v>53180</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2202,9 +2204,9 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W20" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
@@ -2212,74 +2214,70 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>52430</v>
+        <v>51920</v>
       </c>
       <c r="C21" t="n">
-        <v>52515</v>
+        <v>52314</v>
       </c>
       <c r="D21" t="n">
-        <v>51720</v>
+        <v>51846</v>
       </c>
       <c r="E21" t="n">
-        <v>51894</v>
+        <v>52124</v>
       </c>
       <c r="F21" t="n">
-        <v>-555</v>
+        <v>230</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0044</v>
       </c>
       <c r="H21" t="n">
-        <v>795</v>
+        <v>468</v>
       </c>
       <c r="I21" t="n">
-        <v>51803</v>
+        <v>50925</v>
       </c>
       <c r="J21" t="n">
-        <v>51968.75</v>
+        <v>50987.25</v>
       </c>
       <c r="K21" t="n">
-        <v>52219.5</v>
+        <v>51496.5</v>
       </c>
       <c r="L21" t="n">
-        <v>52470.25</v>
+        <v>52005.75</v>
       </c>
       <c r="M21" t="n">
-        <v>52678.5</v>
+        <v>52291.5</v>
       </c>
       <c r="N21" t="n">
-        <v>52886.75</v>
+        <v>52577.25</v>
       </c>
       <c r="O21" t="n">
-        <v>53180</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
+        <v>53310</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
@@ -2291,55 +2289,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>51920</v>
+        <v>52299</v>
       </c>
       <c r="C22" t="n">
-        <v>52314</v>
+        <v>52790</v>
       </c>
       <c r="D22" t="n">
-        <v>51846</v>
+        <v>52173</v>
       </c>
       <c r="E22" t="n">
-        <v>52124</v>
+        <v>52382</v>
       </c>
       <c r="F22" t="n">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0049</v>
       </c>
       <c r="H22" t="n">
-        <v>468</v>
+        <v>617</v>
       </c>
       <c r="I22" t="n">
-        <v>50925</v>
+        <v>51378</v>
       </c>
       <c r="J22" t="n">
-        <v>50987.25</v>
+        <v>51678</v>
       </c>
       <c r="K22" t="n">
-        <v>51496.5</v>
+        <v>51890</v>
       </c>
       <c r="L22" t="n">
-        <v>52005.75</v>
+        <v>52102</v>
       </c>
       <c r="M22" t="n">
-        <v>52291.5</v>
+        <v>52358</v>
       </c>
       <c r="N22" t="n">
-        <v>52577.25</v>
+        <v>52614</v>
       </c>
       <c r="O22" t="n">
-        <v>53310</v>
+        <v>52782</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2350,21 +2352,25 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v/>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W22" s="11" t="inlineStr">
         <is>
@@ -2373,57 +2379,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>52299</v>
+        <v>52405</v>
       </c>
       <c r="C23" t="n">
-        <v>52790</v>
+        <v>53105</v>
       </c>
       <c r="D23" t="n">
-        <v>52173</v>
+        <v>52290</v>
       </c>
       <c r="E23" t="n">
-        <v>52382</v>
+        <v>52944</v>
       </c>
       <c r="F23" t="n">
-        <v>258</v>
+        <v>562</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0107</v>
       </c>
       <c r="H23" t="n">
-        <v>617</v>
+        <v>815</v>
       </c>
       <c r="I23" t="n">
-        <v>51378</v>
+        <v>51556</v>
       </c>
       <c r="J23" t="n">
-        <v>51678</v>
+        <v>51715.25</v>
       </c>
       <c r="K23" t="n">
-        <v>51890</v>
+        <v>52073.5</v>
       </c>
       <c r="L23" t="n">
-        <v>52102</v>
+        <v>52431.75</v>
       </c>
       <c r="M23" t="n">
-        <v>52358</v>
+        <v>52690.5</v>
       </c>
       <c r="N23" t="n">
-        <v>52614</v>
+        <v>52949.25</v>
       </c>
       <c r="O23" t="n">
-        <v>52782</v>
+        <v>53407</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2434,25 +2440,23 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V23" s="8" t="n">
+        <v/>
       </c>
       <c r="W23" s="11" t="inlineStr">
         <is>
@@ -2468,74 +2472,76 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>52405</v>
+        <v>52915</v>
       </c>
       <c r="C24" t="n">
-        <v>53105</v>
+        <v>53033</v>
       </c>
       <c r="D24" t="n">
-        <v>52290</v>
+        <v>51630</v>
       </c>
       <c r="E24" t="n">
-        <v>52944</v>
+        <v>51765</v>
       </c>
       <c r="F24" t="n">
-        <v>562</v>
+        <v>-1179</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0223</v>
       </c>
       <c r="H24" t="n">
-        <v>815</v>
+        <v>1403</v>
       </c>
       <c r="I24" t="n">
-        <v>51556</v>
+        <v>51475</v>
       </c>
       <c r="J24" t="n">
-        <v>51715.25</v>
+        <v>52252.25</v>
       </c>
       <c r="K24" t="n">
-        <v>52073.5</v>
+        <v>52536.5</v>
       </c>
       <c r="L24" t="n">
-        <v>52431.75</v>
+        <v>52820.75</v>
       </c>
       <c r="M24" t="n">
-        <v>52690.5</v>
+        <v>53351.5</v>
       </c>
       <c r="N24" t="n">
-        <v>52949.25</v>
+        <v>53882.25</v>
       </c>
       <c r="O24" t="n">
-        <v>53407</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+        <v>53920</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2545,83 +2551,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>52915</v>
+        <v>51759</v>
       </c>
       <c r="C25" t="n">
-        <v>53033</v>
+        <v>52484</v>
       </c>
       <c r="D25" t="n">
-        <v>51630</v>
+        <v>51732</v>
       </c>
       <c r="E25" t="n">
-        <v>51765</v>
+        <v>52380</v>
       </c>
       <c r="F25" t="n">
-        <v>-1179</v>
+        <v>615</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0119</v>
       </c>
       <c r="H25" t="n">
-        <v>1403</v>
+        <v>752</v>
       </c>
       <c r="I25" t="n">
-        <v>51475</v>
+        <v>50227</v>
       </c>
       <c r="J25" t="n">
-        <v>52252.25</v>
+        <v>50078.75</v>
       </c>
       <c r="K25" t="n">
-        <v>52536.5</v>
+        <v>51063.5</v>
       </c>
       <c r="L25" t="n">
-        <v>52820.75</v>
+        <v>52048.25</v>
       </c>
       <c r="M25" t="n">
-        <v>53351.5</v>
+        <v>52466.5</v>
       </c>
       <c r="N25" t="n">
-        <v>53882.25</v>
+        <v>52884.75</v>
       </c>
       <c r="O25" t="n">
-        <v>53920</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
+        <v>54436</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
       <c r="U25" s="8" t="n">
         <v/>
       </c>
@@ -2633,55 +2631,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>51759</v>
+        <v>52395</v>
       </c>
       <c r="C26" t="n">
-        <v>52484</v>
+        <v>52772</v>
       </c>
       <c r="D26" t="n">
-        <v>51732</v>
+        <v>52124</v>
       </c>
       <c r="E26" t="n">
-        <v>52380</v>
+        <v>52635</v>
       </c>
       <c r="F26" t="n">
-        <v>615</v>
+        <v>255</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0119</v>
+        <v>0.0049</v>
       </c>
       <c r="H26" t="n">
-        <v>752</v>
+        <v>648</v>
       </c>
       <c r="I26" t="n">
-        <v>50227</v>
+        <v>50980</v>
       </c>
       <c r="J26" t="n">
-        <v>50078.75</v>
+        <v>51764</v>
       </c>
       <c r="K26" t="n">
-        <v>51063.5</v>
+        <v>52004</v>
       </c>
       <c r="L26" t="n">
-        <v>52048.25</v>
+        <v>52244</v>
       </c>
       <c r="M26" t="n">
-        <v>52466.5</v>
+        <v>52756</v>
       </c>
       <c r="N26" t="n">
-        <v>52884.75</v>
+        <v>53268</v>
       </c>
       <c r="O26" t="n">
-        <v>54436</v>
+        <v>53236</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2692,7 +2694,7 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
+      <c r="S26" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2715,57 +2717,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>52395</v>
+        <v>52780</v>
       </c>
       <c r="C27" t="n">
-        <v>52772</v>
+        <v>53414</v>
       </c>
       <c r="D27" t="n">
-        <v>52124</v>
+        <v>52777</v>
       </c>
       <c r="E27" t="n">
-        <v>52635</v>
+        <v>53334</v>
       </c>
       <c r="F27" t="n">
-        <v>255</v>
+        <v>699</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0133</v>
       </c>
       <c r="H27" t="n">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="I27" t="n">
-        <v>50980</v>
+        <v>51476</v>
       </c>
       <c r="J27" t="n">
-        <v>51764</v>
+        <v>52080.5</v>
       </c>
       <c r="K27" t="n">
-        <v>52004</v>
+        <v>52311</v>
       </c>
       <c r="L27" t="n">
-        <v>52244</v>
+        <v>52541.5</v>
       </c>
       <c r="M27" t="n">
-        <v>52756</v>
+        <v>52959</v>
       </c>
       <c r="N27" t="n">
-        <v>53268</v>
+        <v>53376.5</v>
       </c>
       <c r="O27" t="n">
-        <v>53236</v>
+        <v>53420</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2776,18 +2778,20 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="7" t="inlineStr">
+      <c r="S27" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2806,50 +2810,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>52780</v>
+        <v>53381</v>
       </c>
       <c r="C28" t="n">
-        <v>53414</v>
+        <v>54423</v>
       </c>
       <c r="D28" t="n">
-        <v>52777</v>
+        <v>53267</v>
       </c>
       <c r="E28" t="n">
-        <v>53334</v>
+        <v>54268</v>
       </c>
       <c r="F28" t="n">
-        <v>699</v>
+        <v>934</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0175</v>
       </c>
       <c r="H28" t="n">
-        <v>637</v>
+        <v>1156</v>
       </c>
       <c r="I28" t="n">
-        <v>51476</v>
+        <v>52140</v>
       </c>
       <c r="J28" t="n">
-        <v>52080.5</v>
+        <v>52816.25</v>
       </c>
       <c r="K28" t="n">
-        <v>52311</v>
+        <v>53015.5</v>
       </c>
       <c r="L28" t="n">
-        <v>52541.5</v>
+        <v>53214.75</v>
       </c>
       <c r="M28" t="n">
-        <v>52959</v>
+        <v>53652.5</v>
       </c>
       <c r="N28" t="n">
-        <v>53376.5</v>
+        <v>54090.25</v>
       </c>
       <c r="O28" t="n">
-        <v>53420</v>
+        <v>54051</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2860,7 +2864,7 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2875,67 +2879,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W28" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W28" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>53381</v>
+        <v>54369</v>
       </c>
       <c r="C29" t="n">
-        <v>54423</v>
+        <v>54884</v>
       </c>
       <c r="D29" t="n">
-        <v>53267</v>
+        <v>54342</v>
       </c>
       <c r="E29" t="n">
-        <v>54268</v>
+        <v>54494</v>
       </c>
       <c r="F29" t="n">
-        <v>934</v>
+        <v>226</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0042</v>
       </c>
       <c r="H29" t="n">
-        <v>1156</v>
+        <v>542</v>
       </c>
       <c r="I29" t="n">
-        <v>52140</v>
+        <v>52111</v>
       </c>
       <c r="J29" t="n">
-        <v>52816.25</v>
+        <v>53323.5</v>
       </c>
       <c r="K29" t="n">
-        <v>53015.5</v>
+        <v>53690</v>
       </c>
       <c r="L29" t="n">
-        <v>53214.75</v>
+        <v>54056.5</v>
       </c>
       <c r="M29" t="n">
-        <v>53652.5</v>
+        <v>54846</v>
       </c>
       <c r="N29" t="n">
-        <v>54090.25</v>
+        <v>55635.5</v>
       </c>
       <c r="O29" t="n">
-        <v>54051</v>
+        <v>55579</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2946,25 +2948,21 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v/>
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
@@ -2976,69 +2974,71 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>54369</v>
+        <v>54555</v>
       </c>
       <c r="C30" t="n">
-        <v>54884</v>
+        <v>54678</v>
       </c>
       <c r="D30" t="n">
-        <v>54342</v>
+        <v>53952</v>
       </c>
       <c r="E30" t="n">
-        <v>54494</v>
+        <v>54013</v>
       </c>
       <c r="F30" t="n">
-        <v>226</v>
+        <v>-481</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>542</v>
+        <v>726</v>
       </c>
       <c r="I30" t="n">
-        <v>52111</v>
+        <v>53800</v>
       </c>
       <c r="J30" t="n">
-        <v>53323.5</v>
+        <v>53892.5</v>
       </c>
       <c r="K30" t="n">
-        <v>53690</v>
+        <v>54223</v>
       </c>
       <c r="L30" t="n">
-        <v>54056.5</v>
+        <v>54553.5</v>
       </c>
       <c r="M30" t="n">
-        <v>54846</v>
+        <v>54765</v>
       </c>
       <c r="N30" t="n">
-        <v>55635.5</v>
+        <v>54976.5</v>
       </c>
       <c r="O30" t="n">
-        <v>55579</v>
+        <v>55426</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3051,72 +3051,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>54555</v>
+        <v>54040</v>
       </c>
       <c r="C31" t="n">
-        <v>54678</v>
+        <v>54202</v>
       </c>
       <c r="D31" t="n">
-        <v>53952</v>
+        <v>53879</v>
       </c>
       <c r="E31" t="n">
-        <v>54013</v>
+        <v>54152</v>
       </c>
       <c r="F31" t="n">
-        <v>-481</v>
+        <v>139</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0026</v>
       </c>
       <c r="H31" t="n">
-        <v>726</v>
+        <v>323</v>
       </c>
       <c r="I31" t="n">
-        <v>53800</v>
+        <v>53226</v>
       </c>
       <c r="J31" t="n">
-        <v>53892.5</v>
+        <v>53136</v>
       </c>
       <c r="K31" t="n">
-        <v>54223</v>
+        <v>53650</v>
       </c>
       <c r="L31" t="n">
-        <v>54553.5</v>
+        <v>54164</v>
       </c>
       <c r="M31" t="n">
-        <v>54765</v>
+        <v>54376</v>
       </c>
       <c r="N31" t="n">
-        <v>54976.5</v>
+        <v>54588</v>
       </c>
       <c r="O31" t="n">
-        <v>55426</v>
+        <v>55404</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3135,57 +3135,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>54040</v>
+        <v>54133</v>
       </c>
       <c r="C32" t="n">
-        <v>54202</v>
+        <v>54170</v>
       </c>
       <c r="D32" t="n">
-        <v>53879</v>
+        <v>53952</v>
       </c>
       <c r="E32" t="n">
-        <v>54152</v>
+        <v>54063</v>
       </c>
       <c r="F32" t="n">
-        <v>139</v>
+        <v>-89</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0016</v>
       </c>
       <c r="H32" t="n">
-        <v>323</v>
+        <v>218</v>
       </c>
       <c r="I32" t="n">
-        <v>53226</v>
+        <v>53556</v>
       </c>
       <c r="J32" t="n">
-        <v>53136</v>
+        <v>53884.75</v>
       </c>
       <c r="K32" t="n">
-        <v>53650</v>
+        <v>53990.5</v>
       </c>
       <c r="L32" t="n">
-        <v>54164</v>
+        <v>54096.25</v>
       </c>
       <c r="M32" t="n">
-        <v>54376</v>
+        <v>54313.5</v>
       </c>
       <c r="N32" t="n">
-        <v>54588</v>
+        <v>54530.75</v>
       </c>
       <c r="O32" t="n">
-        <v>55404</v>
+        <v>54525</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3193,10 +3193,12 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3224,72 +3226,78 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>54133</v>
+        <v>54049</v>
       </c>
       <c r="C33" t="n">
-        <v>54170</v>
+        <v>54336</v>
       </c>
       <c r="D33" t="n">
-        <v>53952</v>
+        <v>53855</v>
       </c>
       <c r="E33" t="n">
-        <v>54063</v>
+        <v>53880</v>
       </c>
       <c r="F33" t="n">
-        <v>-89</v>
+        <v>-183</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0034</v>
       </c>
       <c r="H33" t="n">
-        <v>218</v>
+        <v>481</v>
       </c>
       <c r="I33" t="n">
-        <v>53556</v>
+        <v>53734</v>
       </c>
       <c r="J33" t="n">
-        <v>53884.75</v>
+        <v>53846</v>
       </c>
       <c r="K33" t="n">
-        <v>53990.5</v>
+        <v>53954</v>
       </c>
       <c r="L33" t="n">
-        <v>54096.25</v>
+        <v>54062</v>
       </c>
       <c r="M33" t="n">
-        <v>54313.5</v>
+        <v>54172</v>
       </c>
       <c r="N33" t="n">
-        <v>54530.75</v>
+        <v>54282</v>
       </c>
       <c r="O33" t="n">
-        <v>54525</v>
+        <v>54388</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3308,78 +3316,72 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>54049</v>
+        <v>53903</v>
       </c>
       <c r="C34" t="n">
-        <v>54336</v>
+        <v>54150</v>
       </c>
       <c r="D34" t="n">
-        <v>53855</v>
+        <v>53830</v>
       </c>
       <c r="E34" t="n">
-        <v>53880</v>
+        <v>53871</v>
       </c>
       <c r="F34" t="n">
-        <v>-183</v>
+        <v>-9</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0002</v>
       </c>
       <c r="H34" t="n">
-        <v>481</v>
+        <v>320</v>
       </c>
       <c r="I34" t="n">
-        <v>53734</v>
+        <v>53374</v>
       </c>
       <c r="J34" t="n">
-        <v>53846</v>
+        <v>53291.25</v>
       </c>
       <c r="K34" t="n">
-        <v>53954</v>
+        <v>53639.5</v>
       </c>
       <c r="L34" t="n">
-        <v>54062</v>
+        <v>53987.75</v>
       </c>
       <c r="M34" t="n">
-        <v>54172</v>
+        <v>54120.5</v>
       </c>
       <c r="N34" t="n">
-        <v>54282</v>
+        <v>54253.25</v>
       </c>
       <c r="O34" t="n">
-        <v>54388</v>
+        <v>54817</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3391,57 +3393,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>53903</v>
+        <v>53905</v>
       </c>
       <c r="C35" t="n">
-        <v>54150</v>
+        <v>54149</v>
       </c>
       <c r="D35" t="n">
-        <v>53830</v>
+        <v>53715</v>
       </c>
       <c r="E35" t="n">
-        <v>53871</v>
+        <v>53935</v>
       </c>
       <c r="F35" t="n">
-        <v>-9</v>
+        <v>64</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0012</v>
       </c>
       <c r="H35" t="n">
-        <v>320</v>
+        <v>434</v>
       </c>
       <c r="I35" t="n">
-        <v>53374</v>
+        <v>53510</v>
       </c>
       <c r="J35" t="n">
-        <v>53291.25</v>
+        <v>53491.5</v>
       </c>
       <c r="K35" t="n">
-        <v>53639.5</v>
+        <v>53711</v>
       </c>
       <c r="L35" t="n">
-        <v>53987.75</v>
+        <v>53930.5</v>
       </c>
       <c r="M35" t="n">
-        <v>54120.5</v>
+        <v>54031</v>
       </c>
       <c r="N35" t="n">
-        <v>54253.25</v>
+        <v>54131.5</v>
       </c>
       <c r="O35" t="n">
-        <v>54817</v>
+        <v>54470</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3454,7 +3456,7 @@
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
@@ -3462,8 +3464,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U35" s="8" t="n">
-        <v/>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3475,57 +3479,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>53905</v>
+        <v>53961</v>
       </c>
       <c r="C36" t="n">
-        <v>54149</v>
+        <v>53999</v>
       </c>
       <c r="D36" t="n">
-        <v>53715</v>
+        <v>53745</v>
       </c>
       <c r="E36" t="n">
-        <v>53935</v>
+        <v>53807</v>
       </c>
       <c r="F36" t="n">
-        <v>64</v>
+        <v>-128</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0024</v>
       </c>
       <c r="H36" t="n">
-        <v>434</v>
+        <v>254</v>
       </c>
       <c r="I36" t="n">
-        <v>53510</v>
+        <v>53281</v>
       </c>
       <c r="J36" t="n">
-        <v>53491.5</v>
+        <v>53502.5</v>
       </c>
       <c r="K36" t="n">
-        <v>53711</v>
+        <v>53718</v>
       </c>
       <c r="L36" t="n">
-        <v>53930.5</v>
+        <v>53933.5</v>
       </c>
       <c r="M36" t="n">
-        <v>54031</v>
+        <v>54152</v>
       </c>
       <c r="N36" t="n">
-        <v>54131.5</v>
+        <v>54370.5</v>
       </c>
       <c r="O36" t="n">
-        <v>54470</v>
+        <v>54583</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3533,23 +3537,21 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3568,63 +3570,67 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>53961</v>
+        <v>53790</v>
       </c>
       <c r="C37" t="n">
-        <v>53999</v>
+        <v>53840</v>
       </c>
       <c r="D37" t="n">
-        <v>53745</v>
+        <v>53464</v>
       </c>
       <c r="E37" t="n">
-        <v>53807</v>
+        <v>53544</v>
       </c>
       <c r="F37" t="n">
-        <v>-128</v>
+        <v>-263</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0049</v>
       </c>
       <c r="H37" t="n">
-        <v>254</v>
+        <v>376</v>
       </c>
       <c r="I37" t="n">
-        <v>53281</v>
+        <v>53491</v>
       </c>
       <c r="J37" t="n">
-        <v>53502.5</v>
+        <v>53520.5</v>
       </c>
       <c r="K37" t="n">
-        <v>53718</v>
+        <v>53680</v>
       </c>
       <c r="L37" t="n">
-        <v>53933.5</v>
+        <v>53839.5</v>
       </c>
       <c r="M37" t="n">
-        <v>54152</v>
+        <v>53934</v>
       </c>
       <c r="N37" t="n">
-        <v>54370.5</v>
+        <v>54028.5</v>
       </c>
       <c r="O37" t="n">
-        <v>54583</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
+        <v>54253</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3645,74 +3651,70 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>53790</v>
+        <v>53501</v>
       </c>
       <c r="C38" t="n">
-        <v>53840</v>
+        <v>53594</v>
       </c>
       <c r="D38" t="n">
-        <v>53464</v>
+        <v>53311</v>
       </c>
       <c r="E38" t="n">
-        <v>53544</v>
+        <v>53403</v>
       </c>
       <c r="F38" t="n">
-        <v>-263</v>
+        <v>-141</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0026</v>
       </c>
       <c r="H38" t="n">
-        <v>376</v>
+        <v>283</v>
       </c>
       <c r="I38" t="n">
-        <v>53491</v>
+        <v>53088</v>
       </c>
       <c r="J38" t="n">
-        <v>53520.5</v>
+        <v>53114</v>
       </c>
       <c r="K38" t="n">
-        <v>53680</v>
+        <v>53356</v>
       </c>
       <c r="L38" t="n">
-        <v>53839.5</v>
+        <v>53598</v>
       </c>
       <c r="M38" t="n">
-        <v>53934</v>
+        <v>53732</v>
       </c>
       <c r="N38" t="n">
-        <v>54028.5</v>
+        <v>53866</v>
       </c>
       <c r="O38" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q38" s="6" t="inlineStr">
+        <v>54216</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
+      <c r="S38" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3740,50 +3742,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>53501</v>
+        <v>53408</v>
       </c>
       <c r="C39" t="n">
-        <v>53594</v>
+        <v>53780</v>
       </c>
       <c r="D39" t="n">
-        <v>53311</v>
+        <v>53337</v>
       </c>
       <c r="E39" t="n">
-        <v>53403</v>
+        <v>53530</v>
       </c>
       <c r="F39" t="n">
-        <v>-141</v>
+        <v>127</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0026</v>
+        <v>0.0024</v>
       </c>
       <c r="H39" t="n">
-        <v>283</v>
+        <v>443</v>
       </c>
       <c r="I39" t="n">
-        <v>53088</v>
+        <v>53028</v>
       </c>
       <c r="J39" t="n">
-        <v>53114</v>
+        <v>53095.25</v>
       </c>
       <c r="K39" t="n">
-        <v>53356</v>
+        <v>53261.5</v>
       </c>
       <c r="L39" t="n">
-        <v>53598</v>
+        <v>53427.75</v>
       </c>
       <c r="M39" t="n">
-        <v>53732</v>
+        <v>53544.5</v>
       </c>
       <c r="N39" t="n">
-        <v>53866</v>
+        <v>53661.25</v>
       </c>
       <c r="O39" t="n">
-        <v>54216</v>
+        <v>53877</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3791,21 +3793,23 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3815,90 +3819,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>53408</v>
+        <v>53529</v>
       </c>
       <c r="C40" t="n">
-        <v>53780</v>
+        <v>53589</v>
       </c>
       <c r="D40" t="n">
-        <v>53337</v>
+        <v>52812</v>
       </c>
       <c r="E40" t="n">
-        <v>53530</v>
+        <v>52849</v>
       </c>
       <c r="F40" t="n">
-        <v>127</v>
+        <v>-681</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0127</v>
       </c>
       <c r="H40" t="n">
-        <v>443</v>
+        <v>777</v>
       </c>
       <c r="I40" t="n">
-        <v>53028</v>
+        <v>52894</v>
       </c>
       <c r="J40" t="n">
-        <v>53095.25</v>
+        <v>53072.75</v>
       </c>
       <c r="K40" t="n">
-        <v>53261.5</v>
+        <v>53308.5</v>
       </c>
       <c r="L40" t="n">
-        <v>53427.75</v>
+        <v>53544.25</v>
       </c>
       <c r="M40" t="n">
-        <v>53544.5</v>
+        <v>53751.5</v>
       </c>
       <c r="N40" t="n">
-        <v>53661.25</v>
+        <v>53958.75</v>
       </c>
       <c r="O40" t="n">
-        <v>53877</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+        <v>54223</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W40" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr"/>
@@ -3906,77 +3908,75 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>53529</v>
+        <v>52876</v>
       </c>
       <c r="C41" t="n">
-        <v>53589</v>
+        <v>53418</v>
       </c>
       <c r="D41" t="n">
-        <v>52812</v>
+        <v>52838</v>
       </c>
       <c r="E41" t="n">
-        <v>52849</v>
+        <v>53353</v>
       </c>
       <c r="F41" t="n">
-        <v>-681</v>
+        <v>504</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0095</v>
       </c>
       <c r="H41" t="n">
-        <v>777</v>
+        <v>580</v>
       </c>
       <c r="I41" t="n">
-        <v>52894</v>
+        <v>52035</v>
       </c>
       <c r="J41" t="n">
-        <v>53072.75</v>
+        <v>51896.25</v>
       </c>
       <c r="K41" t="n">
-        <v>53308.5</v>
+        <v>52460.5</v>
       </c>
       <c r="L41" t="n">
-        <v>53544.25</v>
+        <v>53024.75</v>
       </c>
       <c r="M41" t="n">
-        <v>53751.5</v>
+        <v>53237.5</v>
       </c>
       <c r="N41" t="n">
-        <v>53958.75</v>
+        <v>53450.25</v>
       </c>
       <c r="O41" t="n">
-        <v>54223</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
+        <v>54366</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
@@ -3985,55 +3985,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>52876</v>
+        <v>53367</v>
       </c>
       <c r="C42" t="n">
-        <v>53418</v>
+        <v>53567</v>
       </c>
       <c r="D42" t="n">
-        <v>52838</v>
+        <v>53210</v>
       </c>
       <c r="E42" t="n">
-        <v>53353</v>
+        <v>53489</v>
       </c>
       <c r="F42" t="n">
-        <v>504</v>
+        <v>136</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.0025</v>
       </c>
       <c r="H42" t="n">
-        <v>580</v>
+        <v>357</v>
       </c>
       <c r="I42" t="n">
-        <v>52035</v>
+        <v>52258</v>
       </c>
       <c r="J42" t="n">
-        <v>51896.25</v>
+        <v>52885.5</v>
       </c>
       <c r="K42" t="n">
-        <v>52460.5</v>
+        <v>53063</v>
       </c>
       <c r="L42" t="n">
-        <v>53024.75</v>
+        <v>53240.5</v>
       </c>
       <c r="M42" t="n">
-        <v>53237.5</v>
+        <v>53643</v>
       </c>
       <c r="N42" t="n">
-        <v>53450.25</v>
+        <v>54045.5</v>
       </c>
       <c r="O42" t="n">
-        <v>54366</v>
+        <v>53998</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4044,21 +4048,19 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="7" t="inlineStr">
+      <c r="S42" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
@@ -4069,57 +4071,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>53367</v>
+        <v>53524</v>
       </c>
       <c r="C43" t="n">
-        <v>53567</v>
+        <v>53797</v>
       </c>
       <c r="D43" t="n">
-        <v>53210</v>
+        <v>53426</v>
       </c>
       <c r="E43" t="n">
-        <v>53489</v>
+        <v>53645</v>
       </c>
       <c r="F43" t="n">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0029</v>
       </c>
       <c r="H43" t="n">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="I43" t="n">
-        <v>52258</v>
+        <v>52853</v>
       </c>
       <c r="J43" t="n">
-        <v>52885.5</v>
+        <v>53182.25</v>
       </c>
       <c r="K43" t="n">
-        <v>53063</v>
+        <v>53310.5</v>
       </c>
       <c r="L43" t="n">
-        <v>53240.5</v>
+        <v>53438.75</v>
       </c>
       <c r="M43" t="n">
-        <v>53643</v>
+        <v>53667.5</v>
       </c>
       <c r="N43" t="n">
-        <v>54045.5</v>
+        <v>53896.25</v>
       </c>
       <c r="O43" t="n">
-        <v>53998</v>
+        <v>53924</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4130,7 +4132,7 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="7" t="inlineStr">
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4160,50 +4162,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>53524</v>
+        <v>53643</v>
       </c>
       <c r="C44" t="n">
-        <v>53797</v>
+        <v>53778</v>
       </c>
       <c r="D44" t="n">
-        <v>53426</v>
+        <v>53435</v>
       </c>
       <c r="E44" t="n">
-        <v>53645</v>
+        <v>53521</v>
       </c>
       <c r="F44" t="n">
-        <v>156</v>
+        <v>-124</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0023</v>
       </c>
       <c r="H44" t="n">
-        <v>371</v>
+        <v>343</v>
       </c>
       <c r="I44" t="n">
-        <v>52853</v>
+        <v>53055</v>
       </c>
       <c r="J44" t="n">
-        <v>53182.25</v>
+        <v>53290.75</v>
       </c>
       <c r="K44" t="n">
-        <v>53310.5</v>
+        <v>53459.5</v>
       </c>
       <c r="L44" t="n">
-        <v>53438.75</v>
+        <v>53628.25</v>
       </c>
       <c r="M44" t="n">
-        <v>53667.5</v>
+        <v>53830.5</v>
       </c>
       <c r="N44" t="n">
-        <v>53896.25</v>
+        <v>54032.75</v>
       </c>
       <c r="O44" t="n">
-        <v>53924</v>
+        <v>54168</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4211,18 +4213,18 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4237,57 +4239,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>53643</v>
+        <v>53724</v>
       </c>
       <c r="C45" t="n">
-        <v>53778</v>
+        <v>53811</v>
       </c>
       <c r="D45" t="n">
-        <v>53435</v>
+        <v>53369</v>
       </c>
       <c r="E45" t="n">
-        <v>53521</v>
+        <v>53621</v>
       </c>
       <c r="F45" t="n">
-        <v>-124</v>
+        <v>100</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0019</v>
       </c>
       <c r="H45" t="n">
-        <v>343</v>
+        <v>442</v>
       </c>
       <c r="I45" t="n">
-        <v>53055</v>
+        <v>53092</v>
       </c>
       <c r="J45" t="n">
-        <v>53290.75</v>
+        <v>53135.25</v>
       </c>
       <c r="K45" t="n">
-        <v>53459.5</v>
+        <v>53349.5</v>
       </c>
       <c r="L45" t="n">
-        <v>53628.25</v>
+        <v>53563.75</v>
       </c>
       <c r="M45" t="n">
-        <v>53830.5</v>
+        <v>53692.5</v>
       </c>
       <c r="N45" t="n">
-        <v>54032.75</v>
+        <v>53821.25</v>
       </c>
       <c r="O45" t="n">
-        <v>54168</v>
+        <v>54121</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4295,18 +4297,18 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R45" s="6" t="n">
+        <v/>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4321,57 +4323,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>53724</v>
+        <v>53608</v>
       </c>
       <c r="C46" t="n">
-        <v>53811</v>
+        <v>53862</v>
       </c>
       <c r="D46" t="n">
-        <v>53369</v>
+        <v>53513</v>
       </c>
       <c r="E46" t="n">
-        <v>53621</v>
+        <v>53584</v>
       </c>
       <c r="F46" t="n">
-        <v>100</v>
+        <v>-37</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0007</v>
       </c>
       <c r="H46" t="n">
-        <v>442</v>
+        <v>349</v>
       </c>
       <c r="I46" t="n">
-        <v>53092</v>
+        <v>52927</v>
       </c>
       <c r="J46" t="n">
-        <v>53135.25</v>
+        <v>53194.5</v>
       </c>
       <c r="K46" t="n">
-        <v>53349.5</v>
+        <v>53400</v>
       </c>
       <c r="L46" t="n">
-        <v>53563.75</v>
+        <v>53605.5</v>
       </c>
       <c r="M46" t="n">
-        <v>53692.5</v>
+        <v>53842</v>
       </c>
       <c r="N46" t="n">
-        <v>53821.25</v>
+        <v>54078.5</v>
       </c>
       <c r="O46" t="n">
-        <v>54121</v>
+        <v>54253</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4384,7 +4386,7 @@
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
@@ -4412,70 +4414,74 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>53608</v>
+        <v>53664</v>
       </c>
       <c r="C47" t="n">
-        <v>53862</v>
+        <v>53664</v>
       </c>
       <c r="D47" t="n">
-        <v>53513</v>
+        <v>53149</v>
       </c>
       <c r="E47" t="n">
-        <v>53584</v>
+        <v>53240</v>
       </c>
       <c r="F47" t="n">
-        <v>-37</v>
+        <v>-344</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0064</v>
       </c>
       <c r="H47" t="n">
-        <v>349</v>
+        <v>515</v>
       </c>
       <c r="I47" t="n">
-        <v>52927</v>
+        <v>53164</v>
       </c>
       <c r="J47" t="n">
-        <v>53194.5</v>
+        <v>53183.25</v>
       </c>
       <c r="K47" t="n">
-        <v>53400</v>
+        <v>53409.5</v>
       </c>
       <c r="L47" t="n">
-        <v>53605.5</v>
+        <v>53635.75</v>
       </c>
       <c r="M47" t="n">
-        <v>53842</v>
+        <v>53758.5</v>
       </c>
       <c r="N47" t="n">
-        <v>54078.5</v>
+        <v>53881.25</v>
       </c>
       <c r="O47" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
+        <v>54211</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
       <c r="U47" s="8" t="n">
         <v/>
       </c>
@@ -4487,76 +4493,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>53664</v>
+        <v>53259</v>
       </c>
       <c r="C48" t="n">
-        <v>53664</v>
+        <v>53343</v>
       </c>
       <c r="D48" t="n">
-        <v>53149</v>
+        <v>52747</v>
       </c>
       <c r="E48" t="n">
-        <v>53240</v>
+        <v>52828</v>
       </c>
       <c r="F48" t="n">
-        <v>-344</v>
+        <v>-412</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0064</v>
+        <v>-0.0077</v>
       </c>
       <c r="H48" t="n">
-        <v>515</v>
+        <v>596</v>
       </c>
       <c r="I48" t="n">
-        <v>53164</v>
+        <v>52634</v>
       </c>
       <c r="J48" t="n">
-        <v>53183.25</v>
+        <v>52641.75</v>
       </c>
       <c r="K48" t="n">
-        <v>53409.5</v>
+        <v>52982.5</v>
       </c>
       <c r="L48" t="n">
-        <v>53635.75</v>
+        <v>53323.25</v>
       </c>
       <c r="M48" t="n">
-        <v>53758.5</v>
+        <v>53497.5</v>
       </c>
       <c r="N48" t="n">
-        <v>53881.25</v>
+        <v>53671.75</v>
       </c>
       <c r="O48" t="n">
-        <v>54211</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q48" s="6" t="inlineStr">
+        <v>54179</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
+      <c r="S48" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4580,50 +4578,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>53259</v>
+        <v>52844</v>
       </c>
       <c r="C49" t="n">
-        <v>53343</v>
+        <v>53283</v>
       </c>
       <c r="D49" t="n">
-        <v>52747</v>
+        <v>52720</v>
       </c>
       <c r="E49" t="n">
-        <v>52828</v>
+        <v>53121</v>
       </c>
       <c r="F49" t="n">
-        <v>-412</v>
+        <v>293</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0077</v>
+        <v>0.0055</v>
       </c>
       <c r="H49" t="n">
-        <v>596</v>
+        <v>563</v>
       </c>
       <c r="I49" t="n">
-        <v>52634</v>
+        <v>52151</v>
       </c>
       <c r="J49" t="n">
-        <v>52641.75</v>
+        <v>52123.5</v>
       </c>
       <c r="K49" t="n">
-        <v>52982.5</v>
+        <v>52530</v>
       </c>
       <c r="L49" t="n">
-        <v>53323.25</v>
+        <v>52936.5</v>
       </c>
       <c r="M49" t="n">
-        <v>53497.5</v>
+        <v>53126</v>
       </c>
       <c r="N49" t="n">
-        <v>53671.75</v>
+        <v>53315.5</v>
       </c>
       <c r="O49" t="n">
-        <v>54179</v>
+        <v>53939</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4631,19 +4629,19 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
       <c r="U49" s="8" t="n">
         <v/>
       </c>
@@ -4655,55 +4653,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>52844</v>
+        <v>53120</v>
       </c>
       <c r="C50" t="n">
-        <v>53283</v>
+        <v>53827</v>
       </c>
       <c r="D50" t="n">
-        <v>52720</v>
+        <v>53093</v>
       </c>
       <c r="E50" t="n">
-        <v>53121</v>
+        <v>53745</v>
       </c>
       <c r="F50" t="n">
-        <v>293</v>
+        <v>624</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0117</v>
       </c>
       <c r="H50" t="n">
-        <v>563</v>
+        <v>734</v>
       </c>
       <c r="I50" t="n">
-        <v>52151</v>
+        <v>52157</v>
       </c>
       <c r="J50" t="n">
-        <v>52123.5</v>
+        <v>52617.75</v>
       </c>
       <c r="K50" t="n">
-        <v>52530</v>
+        <v>52839.5</v>
       </c>
       <c r="L50" t="n">
-        <v>52936.5</v>
+        <v>53061.25</v>
       </c>
       <c r="M50" t="n">
-        <v>53126</v>
+        <v>53402.5</v>
       </c>
       <c r="N50" t="n">
-        <v>53315.5</v>
+        <v>53743.75</v>
       </c>
       <c r="O50" t="n">
-        <v>53939</v>
+        <v>53846</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4714,80 +4716,78 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="7" t="inlineStr">
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W50" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>53120</v>
+        <v>53707</v>
       </c>
       <c r="C51" t="n">
-        <v>53827</v>
+        <v>53772</v>
       </c>
       <c r="D51" t="n">
-        <v>53093</v>
+        <v>53235</v>
       </c>
       <c r="E51" t="n">
-        <v>53745</v>
+        <v>53440</v>
       </c>
       <c r="F51" t="n">
-        <v>624</v>
+        <v>-305</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0117</v>
+        <v>-0.0057</v>
       </c>
       <c r="H51" t="n">
-        <v>734</v>
+        <v>537</v>
       </c>
       <c r="I51" t="n">
-        <v>52157</v>
+        <v>52359</v>
       </c>
       <c r="J51" t="n">
-        <v>52617.75</v>
+        <v>53153.5</v>
       </c>
       <c r="K51" t="n">
-        <v>52839.5</v>
+        <v>53378</v>
       </c>
       <c r="L51" t="n">
-        <v>53061.25</v>
+        <v>53602.5</v>
       </c>
       <c r="M51" t="n">
-        <v>53402.5</v>
+        <v>54112</v>
       </c>
       <c r="N51" t="n">
-        <v>53743.75</v>
+        <v>54621.5</v>
       </c>
       <c r="O51" t="n">
-        <v>53846</v>
+        <v>54561</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4795,23 +4795,21 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4821,68 +4819,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>53707</v>
+        <v>53261</v>
       </c>
       <c r="C52" t="n">
-        <v>53772</v>
+        <v>53336</v>
       </c>
       <c r="D52" t="n">
-        <v>53235</v>
+        <v>52758</v>
       </c>
       <c r="E52" t="n">
-        <v>53440</v>
+        <v>52832</v>
       </c>
       <c r="F52" t="n">
-        <v>-305</v>
+        <v>-608</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0057</v>
+        <v>-0.0114</v>
       </c>
       <c r="H52" t="n">
-        <v>537</v>
+        <v>578</v>
       </c>
       <c r="I52" t="n">
-        <v>52359</v>
+        <v>52698</v>
       </c>
       <c r="J52" t="n">
-        <v>53153.5</v>
+        <v>52871.25</v>
       </c>
       <c r="K52" t="n">
-        <v>53378</v>
+        <v>53171.5</v>
       </c>
       <c r="L52" t="n">
-        <v>53602.5</v>
+        <v>53471.75</v>
       </c>
       <c r="M52" t="n">
-        <v>54112</v>
+        <v>53708.5</v>
       </c>
       <c r="N52" t="n">
-        <v>54621.5</v>
+        <v>53945.25</v>
       </c>
       <c r="O52" t="n">
-        <v>54561</v>
+        <v>54309</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4896,79 +4900,73 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W52" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>53261</v>
+        <v>52817</v>
       </c>
       <c r="C53" t="n">
-        <v>53336</v>
+        <v>52859</v>
       </c>
       <c r="D53" t="n">
-        <v>52758</v>
+        <v>52339</v>
       </c>
       <c r="E53" t="n">
-        <v>52832</v>
+        <v>52425</v>
       </c>
       <c r="F53" t="n">
-        <v>-608</v>
+        <v>-407</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0114</v>
+        <v>-0.0077</v>
       </c>
       <c r="H53" t="n">
-        <v>578</v>
+        <v>520</v>
       </c>
       <c r="I53" t="n">
-        <v>52698</v>
+        <v>52180</v>
       </c>
       <c r="J53" t="n">
-        <v>52871.25</v>
+        <v>52146.5</v>
       </c>
       <c r="K53" t="n">
-        <v>53171.5</v>
+        <v>52543</v>
       </c>
       <c r="L53" t="n">
-        <v>53471.75</v>
+        <v>52939.5</v>
       </c>
       <c r="M53" t="n">
-        <v>53708.5</v>
+        <v>53121</v>
       </c>
       <c r="N53" t="n">
-        <v>53945.25</v>
+        <v>53302.5</v>
       </c>
       <c r="O53" t="n">
-        <v>54309</v>
+        <v>53914</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4992,50 +4990,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>52817</v>
+        <v>52473</v>
       </c>
       <c r="C54" t="n">
-        <v>52859</v>
+        <v>52676</v>
       </c>
       <c r="D54" t="n">
-        <v>52339</v>
+        <v>51992</v>
       </c>
       <c r="E54" t="n">
-        <v>52425</v>
+        <v>52095</v>
       </c>
       <c r="F54" t="n">
-        <v>-407</v>
+        <v>-330</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0077</v>
+        <v>-0.0063</v>
       </c>
       <c r="H54" t="n">
-        <v>520</v>
+        <v>684</v>
       </c>
       <c r="I54" t="n">
-        <v>52180</v>
+        <v>51819</v>
       </c>
       <c r="J54" t="n">
-        <v>52146.5</v>
+        <v>51818</v>
       </c>
       <c r="K54" t="n">
-        <v>52543</v>
+        <v>52165</v>
       </c>
       <c r="L54" t="n">
-        <v>52939.5</v>
+        <v>52512</v>
       </c>
       <c r="M54" t="n">
-        <v>53121</v>
+        <v>52685</v>
       </c>
       <c r="N54" t="n">
-        <v>53302.5</v>
+        <v>52858</v>
       </c>
       <c r="O54" t="n">
-        <v>53914</v>
+        <v>53379</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5048,7 +5046,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S54" s="10" t="inlineStr">
+      <c r="S54" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5072,50 +5070,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>52473</v>
+        <v>52059</v>
       </c>
       <c r="C55" t="n">
-        <v>52676</v>
+        <v>52739</v>
       </c>
       <c r="D55" t="n">
-        <v>51992</v>
+        <v>52059</v>
       </c>
       <c r="E55" t="n">
-        <v>52095</v>
+        <v>52585</v>
       </c>
       <c r="F55" t="n">
-        <v>-330</v>
+        <v>490</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0063</v>
+        <v>0.0094</v>
       </c>
       <c r="H55" t="n">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="I55" t="n">
-        <v>51819</v>
+        <v>51308</v>
       </c>
       <c r="J55" t="n">
-        <v>51818</v>
+        <v>51291.5</v>
       </c>
       <c r="K55" t="n">
-        <v>52165</v>
+        <v>51753</v>
       </c>
       <c r="L55" t="n">
-        <v>52512</v>
+        <v>52214.5</v>
       </c>
       <c r="M55" t="n">
-        <v>52685</v>
+        <v>52437</v>
       </c>
       <c r="N55" t="n">
-        <v>52858</v>
+        <v>52659.5</v>
       </c>
       <c r="O55" t="n">
-        <v>53379</v>
+        <v>53360</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5123,22 +5121,24 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
@@ -5147,55 +5147,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>52059</v>
+        <v>52376</v>
       </c>
       <c r="C56" t="n">
-        <v>52739</v>
+        <v>52672</v>
       </c>
       <c r="D56" t="n">
-        <v>52059</v>
+        <v>52226</v>
       </c>
       <c r="E56" t="n">
-        <v>52585</v>
+        <v>52440</v>
       </c>
       <c r="F56" t="n">
-        <v>490</v>
+        <v>-145</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0094</v>
+        <v>-0.0028</v>
       </c>
       <c r="H56" t="n">
-        <v>680</v>
+        <v>446</v>
       </c>
       <c r="I56" t="n">
-        <v>51308</v>
+        <v>51379</v>
       </c>
       <c r="J56" t="n">
-        <v>51291.5</v>
+        <v>51998</v>
       </c>
       <c r="K56" t="n">
-        <v>51753</v>
+        <v>52245</v>
       </c>
       <c r="L56" t="n">
-        <v>52214.5</v>
+        <v>52492</v>
       </c>
       <c r="M56" t="n">
-        <v>52437</v>
+        <v>52925</v>
       </c>
       <c r="N56" t="n">
-        <v>52659.5</v>
+        <v>53358</v>
       </c>
       <c r="O56" t="n">
-        <v>53360</v>
+        <v>53419</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5203,23 +5207,21 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5231,72 +5233,74 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>52376</v>
+        <v>52499</v>
       </c>
       <c r="C57" t="n">
-        <v>52672</v>
+        <v>52499</v>
       </c>
       <c r="D57" t="n">
-        <v>52226</v>
+        <v>51908</v>
       </c>
       <c r="E57" t="n">
-        <v>52440</v>
+        <v>52115</v>
       </c>
       <c r="F57" t="n">
-        <v>-145</v>
+        <v>-325</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0028</v>
+        <v>-0.0062</v>
       </c>
       <c r="H57" t="n">
-        <v>446</v>
+        <v>591</v>
       </c>
       <c r="I57" t="n">
-        <v>51379</v>
+        <v>51780</v>
       </c>
       <c r="J57" t="n">
-        <v>51998</v>
+        <v>51989.5</v>
       </c>
       <c r="K57" t="n">
-        <v>52245</v>
+        <v>52217</v>
       </c>
       <c r="L57" t="n">
-        <v>52492</v>
+        <v>52444.5</v>
       </c>
       <c r="M57" t="n">
-        <v>52925</v>
+        <v>52663</v>
       </c>
       <c r="N57" t="n">
-        <v>53358</v>
+        <v>52881.5</v>
       </c>
       <c r="O57" t="n">
-        <v>53419</v>
+        <v>53118</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5313,74 +5317,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>52499</v>
+        <v>52162</v>
       </c>
       <c r="C58" t="n">
-        <v>52499</v>
+        <v>52298</v>
       </c>
       <c r="D58" t="n">
-        <v>51908</v>
+        <v>51209</v>
       </c>
       <c r="E58" t="n">
-        <v>52115</v>
+        <v>51507</v>
       </c>
       <c r="F58" t="n">
-        <v>-325</v>
+        <v>-608</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0062</v>
+        <v>-0.0117</v>
       </c>
       <c r="H58" t="n">
-        <v>591</v>
+        <v>1089</v>
       </c>
       <c r="I58" t="n">
-        <v>51780</v>
+        <v>51317</v>
       </c>
       <c r="J58" t="n">
-        <v>51989.5</v>
+        <v>51479.75</v>
       </c>
       <c r="K58" t="n">
-        <v>52217</v>
+        <v>51819.5</v>
       </c>
       <c r="L58" t="n">
-        <v>52444.5</v>
+        <v>52159.25</v>
       </c>
       <c r="M58" t="n">
-        <v>52663</v>
+        <v>52410.5</v>
       </c>
       <c r="N58" t="n">
-        <v>52881.5</v>
+        <v>52661.75</v>
       </c>
       <c r="O58" t="n">
-        <v>53118</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
+        <v>53090</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q58" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
+      <c r="S58" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5404,74 +5406,70 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>52162</v>
+        <v>51486</v>
       </c>
       <c r="C59" t="n">
-        <v>52298</v>
+        <v>52169</v>
       </c>
       <c r="D59" t="n">
-        <v>51209</v>
+        <v>51455</v>
       </c>
       <c r="E59" t="n">
-        <v>51507</v>
+        <v>51807</v>
       </c>
       <c r="F59" t="n">
-        <v>-608</v>
+        <v>300</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0117</v>
+        <v>0.0058</v>
       </c>
       <c r="H59" t="n">
-        <v>1089</v>
+        <v>714</v>
       </c>
       <c r="I59" t="n">
-        <v>51317</v>
+        <v>50120</v>
       </c>
       <c r="J59" t="n">
-        <v>51479.75</v>
+        <v>50294.75</v>
       </c>
       <c r="K59" t="n">
-        <v>51819.5</v>
+        <v>50962.5</v>
       </c>
       <c r="L59" t="n">
-        <v>52159.25</v>
+        <v>51630.25</v>
       </c>
       <c r="M59" t="n">
-        <v>52410.5</v>
+        <v>52051.5</v>
       </c>
       <c r="N59" t="n">
-        <v>52661.75</v>
+        <v>52472.75</v>
       </c>
       <c r="O59" t="n">
-        <v>53090</v>
-      </c>
-      <c r="P59" s="6" t="inlineStr">
+        <v>53387</v>
+      </c>
+      <c r="P59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
       <c r="U59" s="8" t="n">
         <v/>
       </c>
@@ -5483,55 +5481,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>51486</v>
+        <v>51800</v>
       </c>
       <c r="C60" t="n">
-        <v>52169</v>
+        <v>51957</v>
       </c>
       <c r="D60" t="n">
-        <v>51455</v>
+        <v>51576</v>
       </c>
       <c r="E60" t="n">
-        <v>51807</v>
+        <v>51761</v>
       </c>
       <c r="F60" t="n">
-        <v>300</v>
+        <v>-46</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0009</v>
       </c>
       <c r="H60" t="n">
-        <v>714</v>
+        <v>381</v>
       </c>
       <c r="I60" t="n">
-        <v>50120</v>
+        <v>50741</v>
       </c>
       <c r="J60" t="n">
-        <v>50294.75</v>
+        <v>51090.5</v>
       </c>
       <c r="K60" t="n">
-        <v>50962.5</v>
+        <v>51450</v>
       </c>
       <c r="L60" t="n">
-        <v>51630.25</v>
+        <v>51809.5</v>
       </c>
       <c r="M60" t="n">
-        <v>52051.5</v>
+        <v>52164</v>
       </c>
       <c r="N60" t="n">
-        <v>52472.75</v>
+        <v>52518.5</v>
       </c>
       <c r="O60" t="n">
-        <v>53387</v>
+        <v>52883</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5544,13 +5546,11 @@
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5565,57 +5565,57 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>51800</v>
+        <v>52085</v>
       </c>
       <c r="C61" t="n">
-        <v>51957</v>
+        <v>52557</v>
       </c>
       <c r="D61" t="n">
-        <v>51576</v>
+        <v>52080</v>
       </c>
       <c r="E61" t="n">
-        <v>51761</v>
+        <v>52475</v>
       </c>
       <c r="F61" t="n">
-        <v>-46</v>
+        <v>714</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0138</v>
       </c>
       <c r="H61" t="n">
-        <v>381</v>
+        <v>477</v>
       </c>
       <c r="I61" t="n">
-        <v>50741</v>
+        <v>51195</v>
       </c>
       <c r="J61" t="n">
-        <v>51090.5</v>
+        <v>51377.25</v>
       </c>
       <c r="K61" t="n">
-        <v>51450</v>
+        <v>51570.5</v>
       </c>
       <c r="L61" t="n">
-        <v>51809.5</v>
+        <v>51763.75</v>
       </c>
       <c r="M61" t="n">
-        <v>52164</v>
+        <v>51951.5</v>
       </c>
       <c r="N61" t="n">
-        <v>52518.5</v>
+        <v>52139.25</v>
       </c>
       <c r="O61" t="n">
-        <v>52883</v>
+        <v>52338</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5628,76 +5628,78 @@
       </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W61" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V61" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W61" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>52085</v>
+        <v>52255</v>
       </c>
       <c r="C62" t="n">
-        <v>52557</v>
+        <v>52298</v>
       </c>
       <c r="D62" t="n">
-        <v>52080</v>
+        <v>52255</v>
       </c>
       <c r="E62" t="n">
-        <v>52475</v>
+        <v>52275</v>
       </c>
       <c r="F62" t="n">
-        <v>714</v>
+        <v>-200</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0138</v>
+        <v>-0.0038</v>
       </c>
       <c r="H62" t="n">
-        <v>477</v>
+        <v>43</v>
       </c>
       <c r="I62" t="n">
-        <v>51195</v>
+        <v>51603</v>
       </c>
       <c r="J62" t="n">
-        <v>51377.25</v>
+        <v>52076.25</v>
       </c>
       <c r="K62" t="n">
-        <v>51570.5</v>
+        <v>52236.5</v>
       </c>
       <c r="L62" t="n">
-        <v>51763.75</v>
+        <v>52396.75</v>
       </c>
       <c r="M62" t="n">
-        <v>51951.5</v>
+        <v>52713.5</v>
       </c>
       <c r="N62" t="n">
-        <v>52139.25</v>
+        <v>53030.25</v>
       </c>
       <c r="O62" t="n">
-        <v>52338</v>
+        <v>53034</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5705,119 +5707,33 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
       </c>
       <c r="W62" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>52470</v>
-      </c>
-      <c r="C63" t="n">
-        <v>52844</v>
-      </c>
-      <c r="D63" t="n">
-        <v>52170</v>
-      </c>
-      <c r="E63" t="n">
-        <v>52228</v>
-      </c>
-      <c r="F63" t="n">
-        <v>-247</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>-0.0047</v>
-      </c>
-      <c r="H63" t="n">
-        <v>674</v>
-      </c>
-      <c r="I63" t="n">
-        <v>51603</v>
-      </c>
-      <c r="J63" t="n">
-        <v>52076.25</v>
-      </c>
-      <c r="K63" t="n">
-        <v>52236.5</v>
-      </c>
-      <c r="L63" t="n">
-        <v>52396.75</v>
-      </c>
-      <c r="M63" t="n">
-        <v>52713.5</v>
-      </c>
-      <c r="N63" t="n">
-        <v>53030.25</v>
-      </c>
-      <c r="O63" t="n">
-        <v>53034</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -5666,19 +5666,19 @@
         <v>52298</v>
       </c>
       <c r="D62" t="n">
-        <v>52255</v>
+        <v>52241</v>
       </c>
       <c r="E62" t="n">
-        <v>52275</v>
+        <v>52269</v>
       </c>
       <c r="F62" t="n">
-        <v>-200</v>
+        <v>-206</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0038</v>
+        <v>-0.0039</v>
       </c>
       <c r="H62" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="I62" t="n">
         <v>51603</v>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -5663,22 +5663,22 @@
         <v>52255</v>
       </c>
       <c r="C62" t="n">
-        <v>52298</v>
+        <v>52302</v>
       </c>
       <c r="D62" t="n">
         <v>52241</v>
       </c>
       <c r="E62" t="n">
-        <v>52269</v>
+        <v>52288</v>
       </c>
       <c r="F62" t="n">
-        <v>-206</v>
+        <v>-187</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0039</v>
+        <v>-0.0036</v>
       </c>
       <c r="H62" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I62" t="n">
         <v>51603</v>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -5663,22 +5663,22 @@
         <v>52255</v>
       </c>
       <c r="C62" t="n">
-        <v>52302</v>
+        <v>52325</v>
       </c>
       <c r="D62" t="n">
         <v>52241</v>
       </c>
       <c r="E62" t="n">
-        <v>52288</v>
+        <v>52302</v>
       </c>
       <c r="F62" t="n">
-        <v>-187</v>
+        <v>-173</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0033</v>
       </c>
       <c r="H62" t="n">
-        <v>61</v>
+        <v>84</v>
       </c>
       <c r="I62" t="n">
         <v>51603</v>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -5663,22 +5663,22 @@
         <v>52255</v>
       </c>
       <c r="C62" t="n">
-        <v>52325</v>
+        <v>52332</v>
       </c>
       <c r="D62" t="n">
         <v>52241</v>
       </c>
       <c r="E62" t="n">
-        <v>52302</v>
+        <v>52331</v>
       </c>
       <c r="F62" t="n">
-        <v>-173</v>
+        <v>-144</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0027</v>
       </c>
       <c r="H62" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="I62" t="n">
         <v>51603</v>
@@ -5707,14 +5707,12 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R62" s="6" t="n">
+        <v/>
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5660,25 +5660,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>52255</v>
+        <v>52470</v>
       </c>
       <c r="C62" t="n">
-        <v>52332</v>
+        <v>52844</v>
       </c>
       <c r="D62" t="n">
-        <v>52241</v>
+        <v>52125</v>
       </c>
       <c r="E62" t="n">
-        <v>52331</v>
+        <v>52279</v>
       </c>
       <c r="F62" t="n">
-        <v>-144</v>
+        <v>-196</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0027</v>
+        <v>-0.0037</v>
       </c>
       <c r="H62" t="n">
-        <v>91</v>
+        <v>719</v>
       </c>
       <c r="I62" t="n">
         <v>51603</v>
@@ -5707,16 +5707,20 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5731,7 +5735,91 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>52255</v>
+      </c>
+      <c r="C63" t="n">
+        <v>52371</v>
+      </c>
+      <c r="D63" t="n">
+        <v>52076</v>
+      </c>
+      <c r="E63" t="n">
+        <v>52081</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-198</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>-0.0038</v>
+      </c>
+      <c r="H63" t="n">
+        <v>295</v>
+      </c>
+      <c r="I63" t="n">
+        <v>51406</v>
+      </c>
+      <c r="J63" t="n">
+        <v>51457.25</v>
+      </c>
+      <c r="K63" t="n">
+        <v>51919.5</v>
+      </c>
+      <c r="L63" t="n">
+        <v>52381.75</v>
+      </c>
+      <c r="M63" t="n">
+        <v>52638.5</v>
+      </c>
+      <c r="N63" t="n">
+        <v>52895.25</v>
+      </c>
+      <c r="O63" t="n">
+        <v>53563</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52439</v>
+        <v>52183</v>
       </c>
       <c r="C2" t="n">
-        <v>52542</v>
+        <v>52700</v>
       </c>
       <c r="D2" t="n">
-        <v>52008</v>
+        <v>52179</v>
       </c>
       <c r="E2" t="n">
-        <v>52209</v>
+        <v>52572</v>
       </c>
       <c r="F2" t="n">
-        <v>-130</v>
+        <v>363</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0025</v>
+        <v>0.007</v>
       </c>
       <c r="H2" t="n">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="I2" t="n">
-        <v>51333</v>
+        <v>51474</v>
       </c>
       <c r="J2" t="n">
-        <v>51298.5</v>
+        <v>51642</v>
       </c>
       <c r="K2" t="n">
-        <v>51898</v>
+        <v>51942</v>
       </c>
       <c r="L2" t="n">
-        <v>52497.5</v>
+        <v>52242</v>
       </c>
       <c r="M2" t="n">
-        <v>52780</v>
+        <v>52476</v>
       </c>
       <c r="N2" t="n">
-        <v>53062.5</v>
+        <v>52710</v>
       </c>
       <c r="O2" t="n">
-        <v>53979</v>
+        <v>53076</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,11 +690,13 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -707,59 +709,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>52183</v>
+        <v>52554</v>
       </c>
       <c r="C3" t="n">
-        <v>52700</v>
+        <v>52763</v>
       </c>
       <c r="D3" t="n">
-        <v>52179</v>
+        <v>52383</v>
       </c>
       <c r="E3" t="n">
-        <v>52572</v>
+        <v>52670</v>
       </c>
       <c r="F3" t="n">
-        <v>363</v>
+        <v>98</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.007</v>
+        <v>0.0019</v>
       </c>
       <c r="H3" t="n">
-        <v>521</v>
+        <v>380</v>
       </c>
       <c r="I3" t="n">
-        <v>51474</v>
+        <v>51658</v>
       </c>
       <c r="J3" t="n">
-        <v>51642</v>
+        <v>52117.25</v>
       </c>
       <c r="K3" t="n">
-        <v>51942</v>
+        <v>52311.5</v>
       </c>
       <c r="L3" t="n">
-        <v>52242</v>
+        <v>52505.75</v>
       </c>
       <c r="M3" t="n">
-        <v>52476</v>
+        <v>52832.5</v>
       </c>
       <c r="N3" t="n">
-        <v>52710</v>
+        <v>53159.25</v>
       </c>
       <c r="O3" t="n">
-        <v>53076</v>
+        <v>53221</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -770,7 +768,7 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -796,50 +794,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>52554</v>
+        <v>52546</v>
       </c>
       <c r="C4" t="n">
-        <v>52763</v>
+        <v>53105</v>
       </c>
       <c r="D4" t="n">
-        <v>52383</v>
+        <v>52381</v>
       </c>
       <c r="E4" t="n">
-        <v>52670</v>
+        <v>52668</v>
       </c>
       <c r="F4" t="n">
-        <v>98</v>
+        <v>-2</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0</v>
       </c>
       <c r="H4" t="n">
-        <v>380</v>
+        <v>724</v>
       </c>
       <c r="I4" t="n">
-        <v>51658</v>
+        <v>52003</v>
       </c>
       <c r="J4" t="n">
-        <v>52117.25</v>
+        <v>52338.5</v>
       </c>
       <c r="K4" t="n">
-        <v>52311.5</v>
+        <v>52480</v>
       </c>
       <c r="L4" t="n">
-        <v>52505.75</v>
+        <v>52621.5</v>
       </c>
       <c r="M4" t="n">
-        <v>52832.5</v>
+        <v>52860</v>
       </c>
       <c r="N4" t="n">
-        <v>53159.25</v>
+        <v>53098.5</v>
       </c>
       <c r="O4" t="n">
-        <v>53221</v>
+        <v>53143</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -847,21 +845,25 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
@@ -871,55 +873,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52546</v>
+        <v>52640</v>
       </c>
       <c r="C5" t="n">
-        <v>53105</v>
+        <v>53218</v>
       </c>
       <c r="D5" t="n">
-        <v>52381</v>
+        <v>52551</v>
       </c>
       <c r="E5" t="n">
-        <v>52668</v>
+        <v>53183</v>
       </c>
       <c r="F5" t="n">
-        <v>-2</v>
+        <v>515</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0</v>
+        <v>0.0098</v>
       </c>
       <c r="H5" t="n">
-        <v>724</v>
+        <v>667</v>
       </c>
       <c r="I5" t="n">
-        <v>52003</v>
+        <v>51657</v>
       </c>
       <c r="J5" t="n">
-        <v>52338.5</v>
+        <v>51906.5</v>
       </c>
       <c r="K5" t="n">
-        <v>52480</v>
+        <v>52306</v>
       </c>
       <c r="L5" t="n">
-        <v>52621.5</v>
+        <v>52705.5</v>
       </c>
       <c r="M5" t="n">
-        <v>52860</v>
+        <v>53030</v>
       </c>
       <c r="N5" t="n">
-        <v>53098.5</v>
+        <v>53354.5</v>
       </c>
       <c r="O5" t="n">
-        <v>53143</v>
+        <v>53829</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -927,25 +933,21 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -955,59 +957,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52640</v>
+        <v>53230</v>
       </c>
       <c r="C6" t="n">
-        <v>53218</v>
+        <v>53421</v>
       </c>
       <c r="D6" t="n">
-        <v>52551</v>
+        <v>52962</v>
       </c>
       <c r="E6" t="n">
-        <v>53183</v>
+        <v>53372</v>
       </c>
       <c r="F6" t="n">
-        <v>515</v>
+        <v>189</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0036</v>
       </c>
       <c r="H6" t="n">
-        <v>667</v>
+        <v>459</v>
       </c>
       <c r="I6" t="n">
-        <v>51657</v>
+        <v>51884</v>
       </c>
       <c r="J6" t="n">
-        <v>51906.5</v>
+        <v>52665.25</v>
       </c>
       <c r="K6" t="n">
-        <v>52306</v>
+        <v>52849.5</v>
       </c>
       <c r="L6" t="n">
-        <v>52705.5</v>
+        <v>53033.75</v>
       </c>
       <c r="M6" t="n">
-        <v>53030</v>
+        <v>53516.5</v>
       </c>
       <c r="N6" t="n">
-        <v>53354.5</v>
+        <v>53999.25</v>
       </c>
       <c r="O6" t="n">
-        <v>53829</v>
+        <v>53885</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1018,7 +1016,7 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1044,50 +1042,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>53230</v>
+        <v>53405</v>
       </c>
       <c r="C7" t="n">
-        <v>53421</v>
+        <v>53656</v>
       </c>
       <c r="D7" t="n">
-        <v>52962</v>
+        <v>53076</v>
       </c>
       <c r="E7" t="n">
-        <v>53372</v>
+        <v>53197</v>
       </c>
       <c r="F7" t="n">
-        <v>189</v>
+        <v>-175</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0036</v>
+        <v>-0.0033</v>
       </c>
       <c r="H7" t="n">
-        <v>459</v>
+        <v>580</v>
       </c>
       <c r="I7" t="n">
-        <v>51884</v>
+        <v>52503</v>
       </c>
       <c r="J7" t="n">
-        <v>52665.25</v>
+        <v>53003.25</v>
       </c>
       <c r="K7" t="n">
-        <v>52849.5</v>
+        <v>53142.5</v>
       </c>
       <c r="L7" t="n">
-        <v>53033.75</v>
+        <v>53281.75</v>
       </c>
       <c r="M7" t="n">
-        <v>53516.5</v>
+        <v>53601.5</v>
       </c>
       <c r="N7" t="n">
-        <v>53999.25</v>
+        <v>53921.25</v>
       </c>
       <c r="O7" t="n">
-        <v>53885</v>
+        <v>53880</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1095,17 +1093,19 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U7" s="8" t="n">
@@ -1119,76 +1119,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>53405</v>
+        <v>53166</v>
       </c>
       <c r="C8" t="n">
-        <v>53656</v>
+        <v>53207</v>
       </c>
       <c r="D8" t="n">
-        <v>53076</v>
+        <v>52343</v>
       </c>
       <c r="E8" t="n">
-        <v>53197</v>
+        <v>52624</v>
       </c>
       <c r="F8" t="n">
-        <v>-175</v>
+        <v>-573</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0108</v>
       </c>
       <c r="H8" t="n">
-        <v>580</v>
+        <v>864</v>
       </c>
       <c r="I8" t="n">
-        <v>52503</v>
+        <v>52496</v>
       </c>
       <c r="J8" t="n">
-        <v>53003.25</v>
+        <v>52532.5</v>
       </c>
       <c r="K8" t="n">
-        <v>53142.5</v>
+        <v>52907</v>
       </c>
       <c r="L8" t="n">
-        <v>53281.75</v>
+        <v>53281.5</v>
       </c>
       <c r="M8" t="n">
-        <v>53601.5</v>
+        <v>53487</v>
       </c>
       <c r="N8" t="n">
-        <v>53921.25</v>
+        <v>53692.5</v>
       </c>
       <c r="O8" t="n">
-        <v>53880</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
+        <v>54236</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1203,76 +1209,70 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53166</v>
+        <v>52541</v>
       </c>
       <c r="C9" t="n">
-        <v>53207</v>
+        <v>52865</v>
       </c>
       <c r="D9" t="n">
-        <v>52343</v>
+        <v>52501</v>
       </c>
       <c r="E9" t="n">
-        <v>52624</v>
+        <v>52761</v>
       </c>
       <c r="F9" t="n">
-        <v>-573</v>
+        <v>137</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0108</v>
+        <v>0.0026</v>
       </c>
       <c r="H9" t="n">
-        <v>864</v>
+        <v>364</v>
       </c>
       <c r="I9" t="n">
-        <v>52496</v>
+        <v>51479</v>
       </c>
       <c r="J9" t="n">
-        <v>52532.5</v>
+        <v>51684.5</v>
       </c>
       <c r="K9" t="n">
-        <v>52907</v>
+        <v>52192</v>
       </c>
       <c r="L9" t="n">
-        <v>53281.5</v>
+        <v>52699.5</v>
       </c>
       <c r="M9" t="n">
-        <v>53487</v>
+        <v>53056</v>
       </c>
       <c r="N9" t="n">
-        <v>53692.5</v>
+        <v>53412.5</v>
       </c>
       <c r="O9" t="n">
-        <v>54236</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>54071</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52541</v>
+        <v>52753</v>
       </c>
       <c r="C10" t="n">
-        <v>52865</v>
+        <v>52992</v>
       </c>
       <c r="D10" t="n">
-        <v>52501</v>
+        <v>52506</v>
       </c>
       <c r="E10" t="n">
-        <v>52761</v>
+        <v>52906</v>
       </c>
       <c r="F10" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0027</v>
       </c>
       <c r="H10" t="n">
-        <v>364</v>
+        <v>486</v>
       </c>
       <c r="I10" t="n">
-        <v>51479</v>
+        <v>52137</v>
       </c>
       <c r="J10" t="n">
-        <v>51684.5</v>
+        <v>52436</v>
       </c>
       <c r="K10" t="n">
-        <v>52192</v>
+        <v>52579</v>
       </c>
       <c r="L10" t="n">
-        <v>52699.5</v>
+        <v>52722</v>
       </c>
       <c r="M10" t="n">
-        <v>53056</v>
+        <v>52943</v>
       </c>
       <c r="N10" t="n">
-        <v>53412.5</v>
+        <v>53164</v>
       </c>
       <c r="O10" t="n">
-        <v>54071</v>
+        <v>53229</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1349,16 +1349,20 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1371,59 +1375,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>52753</v>
+        <v>52844</v>
       </c>
       <c r="C11" t="n">
-        <v>52992</v>
+        <v>53113</v>
       </c>
       <c r="D11" t="n">
-        <v>52506</v>
+        <v>52603</v>
       </c>
       <c r="E11" t="n">
-        <v>52906</v>
+        <v>52764</v>
       </c>
       <c r="F11" t="n">
-        <v>145</v>
+        <v>-142</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0027</v>
       </c>
       <c r="H11" t="n">
-        <v>486</v>
+        <v>510</v>
       </c>
       <c r="I11" t="n">
-        <v>52137</v>
+        <v>52020</v>
       </c>
       <c r="J11" t="n">
-        <v>52436</v>
+        <v>52498.5</v>
       </c>
       <c r="K11" t="n">
-        <v>52579</v>
+        <v>52663</v>
       </c>
       <c r="L11" t="n">
-        <v>52722</v>
+        <v>52827.5</v>
       </c>
       <c r="M11" t="n">
-        <v>52943</v>
+        <v>53149</v>
       </c>
       <c r="N11" t="n">
-        <v>53164</v>
+        <v>53470.5</v>
       </c>
       <c r="O11" t="n">
-        <v>53229</v>
+        <v>53478</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1438,13 +1438,11 @@
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1457,55 +1455,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52844</v>
+        <v>52731</v>
       </c>
       <c r="C12" t="n">
-        <v>53113</v>
+        <v>52981</v>
       </c>
       <c r="D12" t="n">
-        <v>52603</v>
+        <v>52255</v>
       </c>
       <c r="E12" t="n">
-        <v>52764</v>
+        <v>52791</v>
       </c>
       <c r="F12" t="n">
-        <v>-142</v>
+        <v>27</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0005</v>
       </c>
       <c r="H12" t="n">
-        <v>510</v>
+        <v>726</v>
       </c>
       <c r="I12" t="n">
-        <v>52020</v>
+        <v>52093</v>
       </c>
       <c r="J12" t="n">
-        <v>52498.5</v>
+        <v>52207</v>
       </c>
       <c r="K12" t="n">
-        <v>52663</v>
+        <v>52509</v>
       </c>
       <c r="L12" t="n">
-        <v>52827.5</v>
+        <v>52811</v>
       </c>
       <c r="M12" t="n">
-        <v>53149</v>
+        <v>53019</v>
       </c>
       <c r="N12" t="n">
-        <v>53470.5</v>
+        <v>53227</v>
       </c>
       <c r="O12" t="n">
-        <v>53478</v>
+        <v>53623</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1518,7 +1520,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S12" s="7" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -1539,57 +1541,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>52731</v>
+        <v>52792</v>
       </c>
       <c r="C13" t="n">
-        <v>52981</v>
+        <v>53088</v>
       </c>
       <c r="D13" t="n">
-        <v>52255</v>
+        <v>52680</v>
       </c>
       <c r="E13" t="n">
-        <v>52791</v>
+        <v>52900</v>
       </c>
       <c r="F13" t="n">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0021</v>
       </c>
       <c r="H13" t="n">
-        <v>726</v>
+        <v>408</v>
       </c>
       <c r="I13" t="n">
-        <v>52093</v>
+        <v>51529</v>
       </c>
       <c r="J13" t="n">
-        <v>52207</v>
+        <v>52151.5</v>
       </c>
       <c r="K13" t="n">
-        <v>52509</v>
+        <v>52428</v>
       </c>
       <c r="L13" t="n">
-        <v>52811</v>
+        <v>52704.5</v>
       </c>
       <c r="M13" t="n">
-        <v>53019</v>
+        <v>53154</v>
       </c>
       <c r="N13" t="n">
-        <v>53227</v>
+        <v>53603.5</v>
       </c>
       <c r="O13" t="n">
-        <v>53623</v>
+        <v>53707</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1597,14 +1599,12 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R13" s="6" t="n">
+        <v/>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1621,59 +1621,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>52792</v>
+        <v>52919</v>
       </c>
       <c r="C14" t="n">
-        <v>53088</v>
+        <v>53108</v>
       </c>
       <c r="D14" t="n">
-        <v>52680</v>
+        <v>52607</v>
       </c>
       <c r="E14" t="n">
-        <v>52900</v>
+        <v>52786</v>
       </c>
       <c r="F14" t="n">
-        <v>109</v>
+        <v>-114</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0022</v>
       </c>
       <c r="H14" t="n">
-        <v>408</v>
+        <v>501</v>
       </c>
       <c r="I14" t="n">
-        <v>51529</v>
+        <v>52272</v>
       </c>
       <c r="J14" t="n">
-        <v>52151.5</v>
+        <v>52500</v>
       </c>
       <c r="K14" t="n">
-        <v>52428</v>
+        <v>52696</v>
       </c>
       <c r="L14" t="n">
-        <v>52704.5</v>
+        <v>52892</v>
       </c>
       <c r="M14" t="n">
-        <v>53154</v>
+        <v>53104</v>
       </c>
       <c r="N14" t="n">
-        <v>53603.5</v>
+        <v>53316</v>
       </c>
       <c r="O14" t="n">
-        <v>53707</v>
+        <v>53496</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1681,16 +1677,20 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1703,76 +1703,80 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52919</v>
+        <v>52778</v>
       </c>
       <c r="C15" t="n">
-        <v>53108</v>
+        <v>52835</v>
       </c>
       <c r="D15" t="n">
-        <v>52607</v>
+        <v>52174</v>
       </c>
       <c r="E15" t="n">
-        <v>52786</v>
+        <v>52375</v>
       </c>
       <c r="F15" t="n">
-        <v>-114</v>
+        <v>-411</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0078</v>
       </c>
       <c r="H15" t="n">
-        <v>501</v>
+        <v>661</v>
       </c>
       <c r="I15" t="n">
-        <v>52272</v>
+        <v>52106</v>
       </c>
       <c r="J15" t="n">
-        <v>52500</v>
+        <v>52249.25</v>
       </c>
       <c r="K15" t="n">
-        <v>52696</v>
+        <v>52535.5</v>
       </c>
       <c r="L15" t="n">
-        <v>52892</v>
+        <v>52821.75</v>
       </c>
       <c r="M15" t="n">
-        <v>53104</v>
+        <v>53036.5</v>
       </c>
       <c r="N15" t="n">
-        <v>53316</v>
+        <v>53251.25</v>
       </c>
       <c r="O15" t="n">
-        <v>53496</v>
+        <v>53609</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1787,72 +1791,70 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>52778</v>
+        <v>52300</v>
       </c>
       <c r="C16" t="n">
-        <v>52835</v>
+        <v>52633</v>
       </c>
       <c r="D16" t="n">
-        <v>52174</v>
+        <v>51999</v>
       </c>
       <c r="E16" t="n">
-        <v>52375</v>
+        <v>52073</v>
       </c>
       <c r="F16" t="n">
-        <v>-411</v>
+        <v>-302</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0078</v>
+        <v>-0.0058</v>
       </c>
       <c r="H16" t="n">
-        <v>661</v>
+        <v>634</v>
       </c>
       <c r="I16" t="n">
-        <v>52106</v>
+        <v>51513</v>
       </c>
       <c r="J16" t="n">
-        <v>52249.25</v>
+        <v>51649.25</v>
       </c>
       <c r="K16" t="n">
-        <v>52535.5</v>
+        <v>52044.5</v>
       </c>
       <c r="L16" t="n">
-        <v>52821.75</v>
+        <v>52439.75</v>
       </c>
       <c r="M16" t="n">
-        <v>53036.5</v>
+        <v>52705.5</v>
       </c>
       <c r="N16" t="n">
-        <v>53251.25</v>
+        <v>52971.25</v>
       </c>
       <c r="O16" t="n">
-        <v>53609</v>
+        <v>53496</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1880,50 +1882,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52300</v>
+        <v>52091</v>
       </c>
       <c r="C17" t="n">
-        <v>52633</v>
+        <v>52590</v>
       </c>
       <c r="D17" t="n">
-        <v>51999</v>
+        <v>52035</v>
       </c>
       <c r="E17" t="n">
-        <v>52073</v>
+        <v>52443</v>
       </c>
       <c r="F17" t="n">
-        <v>-302</v>
+        <v>370</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.0071</v>
       </c>
       <c r="H17" t="n">
-        <v>634</v>
+        <v>555</v>
       </c>
       <c r="I17" t="n">
-        <v>51513</v>
+        <v>51365</v>
       </c>
       <c r="J17" t="n">
-        <v>51649.25</v>
+        <v>51317.5</v>
       </c>
       <c r="K17" t="n">
-        <v>52044.5</v>
+        <v>51756</v>
       </c>
       <c r="L17" t="n">
-        <v>52439.75</v>
+        <v>52194.5</v>
       </c>
       <c r="M17" t="n">
-        <v>52705.5</v>
+        <v>52390</v>
       </c>
       <c r="N17" t="n">
-        <v>52971.25</v>
+        <v>52585.5</v>
       </c>
       <c r="O17" t="n">
-        <v>53496</v>
+        <v>53267</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1931,21 +1933,23 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1957,57 +1961,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52091</v>
+        <v>52431</v>
       </c>
       <c r="C18" t="n">
-        <v>52590</v>
+        <v>52721</v>
       </c>
       <c r="D18" t="n">
-        <v>52035</v>
+        <v>52262</v>
       </c>
       <c r="E18" t="n">
-        <v>52443</v>
+        <v>52449</v>
       </c>
       <c r="F18" t="n">
-        <v>370</v>
+        <v>6</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0001</v>
       </c>
       <c r="H18" t="n">
-        <v>555</v>
+        <v>459</v>
       </c>
       <c r="I18" t="n">
-        <v>51365</v>
+        <v>51480</v>
       </c>
       <c r="J18" t="n">
-        <v>51317.5</v>
+        <v>51953.25</v>
       </c>
       <c r="K18" t="n">
-        <v>51756</v>
+        <v>52165.5</v>
       </c>
       <c r="L18" t="n">
-        <v>52194.5</v>
+        <v>52377.75</v>
       </c>
       <c r="M18" t="n">
-        <v>52390</v>
+        <v>52720.5</v>
       </c>
       <c r="N18" t="n">
-        <v>52585.5</v>
+        <v>53063.25</v>
       </c>
       <c r="O18" t="n">
-        <v>53267</v>
+        <v>53145</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2018,21 +2022,19 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
@@ -2041,78 +2043,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>52431</v>
+        <v>52430</v>
       </c>
       <c r="C19" t="n">
-        <v>52721</v>
+        <v>52515</v>
       </c>
       <c r="D19" t="n">
-        <v>52262</v>
+        <v>51720</v>
       </c>
       <c r="E19" t="n">
-        <v>52449</v>
+        <v>51894</v>
       </c>
       <c r="F19" t="n">
-        <v>6</v>
+        <v>-555</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0106</v>
       </c>
       <c r="H19" t="n">
-        <v>459</v>
+        <v>795</v>
       </c>
       <c r="I19" t="n">
-        <v>51480</v>
+        <v>51803</v>
       </c>
       <c r="J19" t="n">
-        <v>51953.25</v>
+        <v>51968.75</v>
       </c>
       <c r="K19" t="n">
-        <v>52165.5</v>
+        <v>52219.5</v>
       </c>
       <c r="L19" t="n">
-        <v>52377.75</v>
+        <v>52470.25</v>
       </c>
       <c r="M19" t="n">
-        <v>52720.5</v>
+        <v>52678.5</v>
       </c>
       <c r="N19" t="n">
-        <v>53063.25</v>
+        <v>52886.75</v>
       </c>
       <c r="O19" t="n">
-        <v>53145</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+        <v>53180</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2120,9 +2122,9 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W19" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
@@ -2130,74 +2132,70 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>52430</v>
+        <v>51920</v>
       </c>
       <c r="C20" t="n">
-        <v>52515</v>
+        <v>52314</v>
       </c>
       <c r="D20" t="n">
-        <v>51720</v>
+        <v>51846</v>
       </c>
       <c r="E20" t="n">
-        <v>51894</v>
+        <v>52124</v>
       </c>
       <c r="F20" t="n">
-        <v>-555</v>
+        <v>230</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0044</v>
       </c>
       <c r="H20" t="n">
-        <v>795</v>
+        <v>468</v>
       </c>
       <c r="I20" t="n">
-        <v>51803</v>
+        <v>50925</v>
       </c>
       <c r="J20" t="n">
-        <v>51968.75</v>
+        <v>50987.25</v>
       </c>
       <c r="K20" t="n">
-        <v>52219.5</v>
+        <v>51496.5</v>
       </c>
       <c r="L20" t="n">
-        <v>52470.25</v>
+        <v>52005.75</v>
       </c>
       <c r="M20" t="n">
-        <v>52678.5</v>
+        <v>52291.5</v>
       </c>
       <c r="N20" t="n">
-        <v>52886.75</v>
+        <v>52577.25</v>
       </c>
       <c r="O20" t="n">
-        <v>53180</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
+        <v>53310</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
       <c r="U20" s="8" t="n">
         <v/>
       </c>
@@ -2209,55 +2207,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>51920</v>
+        <v>52299</v>
       </c>
       <c r="C21" t="n">
-        <v>52314</v>
+        <v>52790</v>
       </c>
       <c r="D21" t="n">
-        <v>51846</v>
+        <v>52173</v>
       </c>
       <c r="E21" t="n">
-        <v>52124</v>
+        <v>52382</v>
       </c>
       <c r="F21" t="n">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0049</v>
       </c>
       <c r="H21" t="n">
-        <v>468</v>
+        <v>617</v>
       </c>
       <c r="I21" t="n">
-        <v>50925</v>
+        <v>51378</v>
       </c>
       <c r="J21" t="n">
-        <v>50987.25</v>
+        <v>51678</v>
       </c>
       <c r="K21" t="n">
-        <v>51496.5</v>
+        <v>51890</v>
       </c>
       <c r="L21" t="n">
-        <v>52005.75</v>
+        <v>52102</v>
       </c>
       <c r="M21" t="n">
-        <v>52291.5</v>
+        <v>52358</v>
       </c>
       <c r="N21" t="n">
-        <v>52577.25</v>
+        <v>52614</v>
       </c>
       <c r="O21" t="n">
-        <v>53310</v>
+        <v>52782</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2268,21 +2270,25 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v/>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W21" s="11" t="inlineStr">
         <is>
@@ -2291,57 +2297,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>52299</v>
+        <v>52405</v>
       </c>
       <c r="C22" t="n">
-        <v>52790</v>
+        <v>53105</v>
       </c>
       <c r="D22" t="n">
-        <v>52173</v>
+        <v>52290</v>
       </c>
       <c r="E22" t="n">
-        <v>52382</v>
+        <v>52944</v>
       </c>
       <c r="F22" t="n">
-        <v>258</v>
+        <v>562</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0107</v>
       </c>
       <c r="H22" t="n">
-        <v>617</v>
+        <v>815</v>
       </c>
       <c r="I22" t="n">
-        <v>51378</v>
+        <v>51556</v>
       </c>
       <c r="J22" t="n">
-        <v>51678</v>
+        <v>51715.25</v>
       </c>
       <c r="K22" t="n">
-        <v>51890</v>
+        <v>52073.5</v>
       </c>
       <c r="L22" t="n">
-        <v>52102</v>
+        <v>52431.75</v>
       </c>
       <c r="M22" t="n">
-        <v>52358</v>
+        <v>52690.5</v>
       </c>
       <c r="N22" t="n">
-        <v>52614</v>
+        <v>52949.25</v>
       </c>
       <c r="O22" t="n">
-        <v>52782</v>
+        <v>53407</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2352,25 +2358,23 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V22" s="8" t="n">
+        <v/>
       </c>
       <c r="W22" s="11" t="inlineStr">
         <is>
@@ -2386,74 +2390,76 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>52405</v>
+        <v>52915</v>
       </c>
       <c r="C23" t="n">
-        <v>53105</v>
+        <v>53033</v>
       </c>
       <c r="D23" t="n">
-        <v>52290</v>
+        <v>51630</v>
       </c>
       <c r="E23" t="n">
-        <v>52944</v>
+        <v>51765</v>
       </c>
       <c r="F23" t="n">
-        <v>562</v>
+        <v>-1179</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0223</v>
       </c>
       <c r="H23" t="n">
-        <v>815</v>
+        <v>1403</v>
       </c>
       <c r="I23" t="n">
-        <v>51556</v>
+        <v>51475</v>
       </c>
       <c r="J23" t="n">
-        <v>51715.25</v>
+        <v>52252.25</v>
       </c>
       <c r="K23" t="n">
-        <v>52073.5</v>
+        <v>52536.5</v>
       </c>
       <c r="L23" t="n">
-        <v>52431.75</v>
+        <v>52820.75</v>
       </c>
       <c r="M23" t="n">
-        <v>52690.5</v>
+        <v>53351.5</v>
       </c>
       <c r="N23" t="n">
-        <v>52949.25</v>
+        <v>53882.25</v>
       </c>
       <c r="O23" t="n">
-        <v>53407</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+        <v>53920</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2463,83 +2469,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>52915</v>
+        <v>51759</v>
       </c>
       <c r="C24" t="n">
-        <v>53033</v>
+        <v>52484</v>
       </c>
       <c r="D24" t="n">
-        <v>51630</v>
+        <v>51732</v>
       </c>
       <c r="E24" t="n">
-        <v>51765</v>
+        <v>52380</v>
       </c>
       <c r="F24" t="n">
-        <v>-1179</v>
+        <v>615</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0119</v>
       </c>
       <c r="H24" t="n">
-        <v>1403</v>
+        <v>752</v>
       </c>
       <c r="I24" t="n">
-        <v>51475</v>
+        <v>50227</v>
       </c>
       <c r="J24" t="n">
-        <v>52252.25</v>
+        <v>50078.75</v>
       </c>
       <c r="K24" t="n">
-        <v>52536.5</v>
+        <v>51063.5</v>
       </c>
       <c r="L24" t="n">
-        <v>52820.75</v>
+        <v>52048.25</v>
       </c>
       <c r="M24" t="n">
-        <v>53351.5</v>
+        <v>52466.5</v>
       </c>
       <c r="N24" t="n">
-        <v>53882.25</v>
+        <v>52884.75</v>
       </c>
       <c r="O24" t="n">
-        <v>53920</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
+        <v>54436</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
@@ -2551,55 +2549,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>51759</v>
+        <v>52395</v>
       </c>
       <c r="C25" t="n">
-        <v>52484</v>
+        <v>52772</v>
       </c>
       <c r="D25" t="n">
-        <v>51732</v>
+        <v>52124</v>
       </c>
       <c r="E25" t="n">
-        <v>52380</v>
+        <v>52635</v>
       </c>
       <c r="F25" t="n">
-        <v>615</v>
+        <v>255</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0119</v>
+        <v>0.0049</v>
       </c>
       <c r="H25" t="n">
-        <v>752</v>
+        <v>648</v>
       </c>
       <c r="I25" t="n">
-        <v>50227</v>
+        <v>50980</v>
       </c>
       <c r="J25" t="n">
-        <v>50078.75</v>
+        <v>51764</v>
       </c>
       <c r="K25" t="n">
-        <v>51063.5</v>
+        <v>52004</v>
       </c>
       <c r="L25" t="n">
-        <v>52048.25</v>
+        <v>52244</v>
       </c>
       <c r="M25" t="n">
-        <v>52466.5</v>
+        <v>52756</v>
       </c>
       <c r="N25" t="n">
-        <v>52884.75</v>
+        <v>53268</v>
       </c>
       <c r="O25" t="n">
-        <v>54436</v>
+        <v>53236</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2610,7 +2612,7 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
+      <c r="S25" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2633,57 +2635,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>52395</v>
+        <v>52780</v>
       </c>
       <c r="C26" t="n">
-        <v>52772</v>
+        <v>53414</v>
       </c>
       <c r="D26" t="n">
-        <v>52124</v>
+        <v>52777</v>
       </c>
       <c r="E26" t="n">
-        <v>52635</v>
+        <v>53334</v>
       </c>
       <c r="F26" t="n">
-        <v>255</v>
+        <v>699</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0133</v>
       </c>
       <c r="H26" t="n">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="I26" t="n">
-        <v>50980</v>
+        <v>51476</v>
       </c>
       <c r="J26" t="n">
-        <v>51764</v>
+        <v>52080.5</v>
       </c>
       <c r="K26" t="n">
-        <v>52004</v>
+        <v>52311</v>
       </c>
       <c r="L26" t="n">
-        <v>52244</v>
+        <v>52541.5</v>
       </c>
       <c r="M26" t="n">
-        <v>52756</v>
+        <v>52959</v>
       </c>
       <c r="N26" t="n">
-        <v>53268</v>
+        <v>53376.5</v>
       </c>
       <c r="O26" t="n">
-        <v>53236</v>
+        <v>53420</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2694,18 +2696,20 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2724,50 +2728,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>52780</v>
+        <v>53381</v>
       </c>
       <c r="C27" t="n">
-        <v>53414</v>
+        <v>54423</v>
       </c>
       <c r="D27" t="n">
-        <v>52777</v>
+        <v>53267</v>
       </c>
       <c r="E27" t="n">
-        <v>53334</v>
+        <v>54268</v>
       </c>
       <c r="F27" t="n">
-        <v>699</v>
+        <v>934</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0175</v>
       </c>
       <c r="H27" t="n">
-        <v>637</v>
+        <v>1156</v>
       </c>
       <c r="I27" t="n">
-        <v>51476</v>
+        <v>52140</v>
       </c>
       <c r="J27" t="n">
-        <v>52080.5</v>
+        <v>52816.25</v>
       </c>
       <c r="K27" t="n">
-        <v>52311</v>
+        <v>53015.5</v>
       </c>
       <c r="L27" t="n">
-        <v>52541.5</v>
+        <v>53214.75</v>
       </c>
       <c r="M27" t="n">
-        <v>52959</v>
+        <v>53652.5</v>
       </c>
       <c r="N27" t="n">
-        <v>53376.5</v>
+        <v>54090.25</v>
       </c>
       <c r="O27" t="n">
-        <v>53420</v>
+        <v>54051</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2778,7 +2782,7 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2793,67 +2797,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W27" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W27" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>53381</v>
+        <v>54369</v>
       </c>
       <c r="C28" t="n">
-        <v>54423</v>
+        <v>54884</v>
       </c>
       <c r="D28" t="n">
-        <v>53267</v>
+        <v>54342</v>
       </c>
       <c r="E28" t="n">
-        <v>54268</v>
+        <v>54494</v>
       </c>
       <c r="F28" t="n">
-        <v>934</v>
+        <v>226</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0042</v>
       </c>
       <c r="H28" t="n">
-        <v>1156</v>
+        <v>542</v>
       </c>
       <c r="I28" t="n">
-        <v>52140</v>
+        <v>52111</v>
       </c>
       <c r="J28" t="n">
-        <v>52816.25</v>
+        <v>53323.5</v>
       </c>
       <c r="K28" t="n">
-        <v>53015.5</v>
+        <v>53690</v>
       </c>
       <c r="L28" t="n">
-        <v>53214.75</v>
+        <v>54056.5</v>
       </c>
       <c r="M28" t="n">
-        <v>53652.5</v>
+        <v>54846</v>
       </c>
       <c r="N28" t="n">
-        <v>54090.25</v>
+        <v>55635.5</v>
       </c>
       <c r="O28" t="n">
-        <v>54051</v>
+        <v>55579</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2864,25 +2866,21 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
+      <c r="S28" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
@@ -2894,69 +2892,71 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>54369</v>
+        <v>54555</v>
       </c>
       <c r="C29" t="n">
-        <v>54884</v>
+        <v>54678</v>
       </c>
       <c r="D29" t="n">
-        <v>54342</v>
+        <v>53952</v>
       </c>
       <c r="E29" t="n">
-        <v>54494</v>
+        <v>54013</v>
       </c>
       <c r="F29" t="n">
-        <v>226</v>
+        <v>-481</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>542</v>
+        <v>726</v>
       </c>
       <c r="I29" t="n">
-        <v>52111</v>
+        <v>53800</v>
       </c>
       <c r="J29" t="n">
-        <v>53323.5</v>
+        <v>53892.5</v>
       </c>
       <c r="K29" t="n">
-        <v>53690</v>
+        <v>54223</v>
       </c>
       <c r="L29" t="n">
-        <v>54056.5</v>
+        <v>54553.5</v>
       </c>
       <c r="M29" t="n">
-        <v>54846</v>
+        <v>54765</v>
       </c>
       <c r="N29" t="n">
-        <v>55635.5</v>
+        <v>54976.5</v>
       </c>
       <c r="O29" t="n">
-        <v>55579</v>
+        <v>55426</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2969,72 +2969,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>54555</v>
+        <v>54040</v>
       </c>
       <c r="C30" t="n">
-        <v>54678</v>
+        <v>54202</v>
       </c>
       <c r="D30" t="n">
-        <v>53952</v>
+        <v>53879</v>
       </c>
       <c r="E30" t="n">
-        <v>54013</v>
+        <v>54152</v>
       </c>
       <c r="F30" t="n">
-        <v>-481</v>
+        <v>139</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0026</v>
       </c>
       <c r="H30" t="n">
-        <v>726</v>
+        <v>323</v>
       </c>
       <c r="I30" t="n">
-        <v>53800</v>
+        <v>53226</v>
       </c>
       <c r="J30" t="n">
-        <v>53892.5</v>
+        <v>53136</v>
       </c>
       <c r="K30" t="n">
-        <v>54223</v>
+        <v>53650</v>
       </c>
       <c r="L30" t="n">
-        <v>54553.5</v>
+        <v>54164</v>
       </c>
       <c r="M30" t="n">
-        <v>54765</v>
+        <v>54376</v>
       </c>
       <c r="N30" t="n">
-        <v>54976.5</v>
+        <v>54588</v>
       </c>
       <c r="O30" t="n">
-        <v>55426</v>
+        <v>55404</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3053,57 +3053,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>54040</v>
+        <v>54133</v>
       </c>
       <c r="C31" t="n">
-        <v>54202</v>
+        <v>54170</v>
       </c>
       <c r="D31" t="n">
-        <v>53879</v>
+        <v>53952</v>
       </c>
       <c r="E31" t="n">
-        <v>54152</v>
+        <v>54063</v>
       </c>
       <c r="F31" t="n">
-        <v>139</v>
+        <v>-89</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0016</v>
       </c>
       <c r="H31" t="n">
-        <v>323</v>
+        <v>218</v>
       </c>
       <c r="I31" t="n">
-        <v>53226</v>
+        <v>53556</v>
       </c>
       <c r="J31" t="n">
-        <v>53136</v>
+        <v>53884.75</v>
       </c>
       <c r="K31" t="n">
-        <v>53650</v>
+        <v>53990.5</v>
       </c>
       <c r="L31" t="n">
-        <v>54164</v>
+        <v>54096.25</v>
       </c>
       <c r="M31" t="n">
-        <v>54376</v>
+        <v>54313.5</v>
       </c>
       <c r="N31" t="n">
-        <v>54588</v>
+        <v>54530.75</v>
       </c>
       <c r="O31" t="n">
-        <v>55404</v>
+        <v>54525</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3111,10 +3111,12 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3142,72 +3144,78 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>54133</v>
+        <v>54049</v>
       </c>
       <c r="C32" t="n">
-        <v>54170</v>
+        <v>54336</v>
       </c>
       <c r="D32" t="n">
-        <v>53952</v>
+        <v>53855</v>
       </c>
       <c r="E32" t="n">
-        <v>54063</v>
+        <v>53880</v>
       </c>
       <c r="F32" t="n">
-        <v>-89</v>
+        <v>-183</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0034</v>
       </c>
       <c r="H32" t="n">
-        <v>218</v>
+        <v>481</v>
       </c>
       <c r="I32" t="n">
-        <v>53556</v>
+        <v>53734</v>
       </c>
       <c r="J32" t="n">
-        <v>53884.75</v>
+        <v>53846</v>
       </c>
       <c r="K32" t="n">
-        <v>53990.5</v>
+        <v>53954</v>
       </c>
       <c r="L32" t="n">
-        <v>54096.25</v>
+        <v>54062</v>
       </c>
       <c r="M32" t="n">
-        <v>54313.5</v>
+        <v>54172</v>
       </c>
       <c r="N32" t="n">
-        <v>54530.75</v>
+        <v>54282</v>
       </c>
       <c r="O32" t="n">
-        <v>54525</v>
+        <v>54388</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3226,78 +3234,72 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>54049</v>
+        <v>53903</v>
       </c>
       <c r="C33" t="n">
-        <v>54336</v>
+        <v>54150</v>
       </c>
       <c r="D33" t="n">
-        <v>53855</v>
+        <v>53830</v>
       </c>
       <c r="E33" t="n">
-        <v>53880</v>
+        <v>53871</v>
       </c>
       <c r="F33" t="n">
-        <v>-183</v>
+        <v>-9</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0002</v>
       </c>
       <c r="H33" t="n">
-        <v>481</v>
+        <v>320</v>
       </c>
       <c r="I33" t="n">
-        <v>53734</v>
+        <v>53374</v>
       </c>
       <c r="J33" t="n">
-        <v>53846</v>
+        <v>53291.25</v>
       </c>
       <c r="K33" t="n">
-        <v>53954</v>
+        <v>53639.5</v>
       </c>
       <c r="L33" t="n">
-        <v>54062</v>
+        <v>53987.75</v>
       </c>
       <c r="M33" t="n">
-        <v>54172</v>
+        <v>54120.5</v>
       </c>
       <c r="N33" t="n">
-        <v>54282</v>
+        <v>54253.25</v>
       </c>
       <c r="O33" t="n">
-        <v>54388</v>
+        <v>54817</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3309,57 +3311,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>53903</v>
+        <v>53905</v>
       </c>
       <c r="C34" t="n">
-        <v>54150</v>
+        <v>54149</v>
       </c>
       <c r="D34" t="n">
-        <v>53830</v>
+        <v>53715</v>
       </c>
       <c r="E34" t="n">
-        <v>53871</v>
+        <v>53935</v>
       </c>
       <c r="F34" t="n">
-        <v>-9</v>
+        <v>64</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0012</v>
       </c>
       <c r="H34" t="n">
-        <v>320</v>
+        <v>434</v>
       </c>
       <c r="I34" t="n">
-        <v>53374</v>
+        <v>53510</v>
       </c>
       <c r="J34" t="n">
-        <v>53291.25</v>
+        <v>53491.5</v>
       </c>
       <c r="K34" t="n">
-        <v>53639.5</v>
+        <v>53711</v>
       </c>
       <c r="L34" t="n">
-        <v>53987.75</v>
+        <v>53930.5</v>
       </c>
       <c r="M34" t="n">
-        <v>54120.5</v>
+        <v>54031</v>
       </c>
       <c r="N34" t="n">
-        <v>54253.25</v>
+        <v>54131.5</v>
       </c>
       <c r="O34" t="n">
-        <v>54817</v>
+        <v>54470</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3372,7 +3374,7 @@
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
@@ -3380,8 +3382,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U34" s="8" t="n">
-        <v/>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3393,57 +3397,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>53905</v>
+        <v>53961</v>
       </c>
       <c r="C35" t="n">
-        <v>54149</v>
+        <v>53999</v>
       </c>
       <c r="D35" t="n">
-        <v>53715</v>
+        <v>53745</v>
       </c>
       <c r="E35" t="n">
-        <v>53935</v>
+        <v>53807</v>
       </c>
       <c r="F35" t="n">
-        <v>64</v>
+        <v>-128</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0024</v>
       </c>
       <c r="H35" t="n">
-        <v>434</v>
+        <v>254</v>
       </c>
       <c r="I35" t="n">
-        <v>53510</v>
+        <v>53281</v>
       </c>
       <c r="J35" t="n">
-        <v>53491.5</v>
+        <v>53502.5</v>
       </c>
       <c r="K35" t="n">
-        <v>53711</v>
+        <v>53718</v>
       </c>
       <c r="L35" t="n">
-        <v>53930.5</v>
+        <v>53933.5</v>
       </c>
       <c r="M35" t="n">
-        <v>54031</v>
+        <v>54152</v>
       </c>
       <c r="N35" t="n">
-        <v>54131.5</v>
+        <v>54370.5</v>
       </c>
       <c r="O35" t="n">
-        <v>54470</v>
+        <v>54583</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3451,23 +3455,21 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3486,63 +3488,67 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>53961</v>
+        <v>53790</v>
       </c>
       <c r="C36" t="n">
-        <v>53999</v>
+        <v>53840</v>
       </c>
       <c r="D36" t="n">
-        <v>53745</v>
+        <v>53464</v>
       </c>
       <c r="E36" t="n">
-        <v>53807</v>
+        <v>53544</v>
       </c>
       <c r="F36" t="n">
-        <v>-128</v>
+        <v>-263</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0049</v>
       </c>
       <c r="H36" t="n">
-        <v>254</v>
+        <v>376</v>
       </c>
       <c r="I36" t="n">
-        <v>53281</v>
+        <v>53491</v>
       </c>
       <c r="J36" t="n">
-        <v>53502.5</v>
+        <v>53520.5</v>
       </c>
       <c r="K36" t="n">
-        <v>53718</v>
+        <v>53680</v>
       </c>
       <c r="L36" t="n">
-        <v>53933.5</v>
+        <v>53839.5</v>
       </c>
       <c r="M36" t="n">
-        <v>54152</v>
+        <v>53934</v>
       </c>
       <c r="N36" t="n">
-        <v>54370.5</v>
+        <v>54028.5</v>
       </c>
       <c r="O36" t="n">
-        <v>54583</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
+        <v>54253</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3563,74 +3569,70 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>53790</v>
+        <v>53501</v>
       </c>
       <c r="C37" t="n">
-        <v>53840</v>
+        <v>53594</v>
       </c>
       <c r="D37" t="n">
-        <v>53464</v>
+        <v>53311</v>
       </c>
       <c r="E37" t="n">
-        <v>53544</v>
+        <v>53403</v>
       </c>
       <c r="F37" t="n">
-        <v>-263</v>
+        <v>-141</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0026</v>
       </c>
       <c r="H37" t="n">
-        <v>376</v>
+        <v>283</v>
       </c>
       <c r="I37" t="n">
-        <v>53491</v>
+        <v>53088</v>
       </c>
       <c r="J37" t="n">
-        <v>53520.5</v>
+        <v>53114</v>
       </c>
       <c r="K37" t="n">
-        <v>53680</v>
+        <v>53356</v>
       </c>
       <c r="L37" t="n">
-        <v>53839.5</v>
+        <v>53598</v>
       </c>
       <c r="M37" t="n">
-        <v>53934</v>
+        <v>53732</v>
       </c>
       <c r="N37" t="n">
-        <v>54028.5</v>
+        <v>53866</v>
       </c>
       <c r="O37" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q37" s="6" t="inlineStr">
+        <v>54216</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3658,50 +3660,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>53501</v>
+        <v>53408</v>
       </c>
       <c r="C38" t="n">
-        <v>53594</v>
+        <v>53780</v>
       </c>
       <c r="D38" t="n">
-        <v>53311</v>
+        <v>53337</v>
       </c>
       <c r="E38" t="n">
-        <v>53403</v>
+        <v>53530</v>
       </c>
       <c r="F38" t="n">
-        <v>-141</v>
+        <v>127</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0026</v>
+        <v>0.0024</v>
       </c>
       <c r="H38" t="n">
-        <v>283</v>
+        <v>443</v>
       </c>
       <c r="I38" t="n">
-        <v>53088</v>
+        <v>53028</v>
       </c>
       <c r="J38" t="n">
-        <v>53114</v>
+        <v>53095.25</v>
       </c>
       <c r="K38" t="n">
-        <v>53356</v>
+        <v>53261.5</v>
       </c>
       <c r="L38" t="n">
-        <v>53598</v>
+        <v>53427.75</v>
       </c>
       <c r="M38" t="n">
-        <v>53732</v>
+        <v>53544.5</v>
       </c>
       <c r="N38" t="n">
-        <v>53866</v>
+        <v>53661.25</v>
       </c>
       <c r="O38" t="n">
-        <v>54216</v>
+        <v>53877</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3709,21 +3711,23 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3733,90 +3737,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>53408</v>
+        <v>53529</v>
       </c>
       <c r="C39" t="n">
-        <v>53780</v>
+        <v>53589</v>
       </c>
       <c r="D39" t="n">
-        <v>53337</v>
+        <v>52812</v>
       </c>
       <c r="E39" t="n">
-        <v>53530</v>
+        <v>52849</v>
       </c>
       <c r="F39" t="n">
-        <v>127</v>
+        <v>-681</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0127</v>
       </c>
       <c r="H39" t="n">
-        <v>443</v>
+        <v>777</v>
       </c>
       <c r="I39" t="n">
-        <v>53028</v>
+        <v>52894</v>
       </c>
       <c r="J39" t="n">
-        <v>53095.25</v>
+        <v>53072.75</v>
       </c>
       <c r="K39" t="n">
-        <v>53261.5</v>
+        <v>53308.5</v>
       </c>
       <c r="L39" t="n">
-        <v>53427.75</v>
+        <v>53544.25</v>
       </c>
       <c r="M39" t="n">
-        <v>53544.5</v>
+        <v>53751.5</v>
       </c>
       <c r="N39" t="n">
-        <v>53661.25</v>
+        <v>53958.75</v>
       </c>
       <c r="O39" t="n">
-        <v>53877</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+        <v>54223</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W39" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr"/>
@@ -3824,77 +3826,75 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>53529</v>
+        <v>52876</v>
       </c>
       <c r="C40" t="n">
-        <v>53589</v>
+        <v>53418</v>
       </c>
       <c r="D40" t="n">
-        <v>52812</v>
+        <v>52838</v>
       </c>
       <c r="E40" t="n">
-        <v>52849</v>
+        <v>53353</v>
       </c>
       <c r="F40" t="n">
-        <v>-681</v>
+        <v>504</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0095</v>
       </c>
       <c r="H40" t="n">
-        <v>777</v>
+        <v>580</v>
       </c>
       <c r="I40" t="n">
-        <v>52894</v>
+        <v>52035</v>
       </c>
       <c r="J40" t="n">
-        <v>53072.75</v>
+        <v>51896.25</v>
       </c>
       <c r="K40" t="n">
-        <v>53308.5</v>
+        <v>52460.5</v>
       </c>
       <c r="L40" t="n">
-        <v>53544.25</v>
+        <v>53024.75</v>
       </c>
       <c r="M40" t="n">
-        <v>53751.5</v>
+        <v>53237.5</v>
       </c>
       <c r="N40" t="n">
-        <v>53958.75</v>
+        <v>53450.25</v>
       </c>
       <c r="O40" t="n">
-        <v>54223</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
+        <v>54366</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
@@ -3903,55 +3903,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>52876</v>
+        <v>53367</v>
       </c>
       <c r="C41" t="n">
-        <v>53418</v>
+        <v>53567</v>
       </c>
       <c r="D41" t="n">
-        <v>52838</v>
+        <v>53210</v>
       </c>
       <c r="E41" t="n">
-        <v>53353</v>
+        <v>53489</v>
       </c>
       <c r="F41" t="n">
-        <v>504</v>
+        <v>136</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.0025</v>
       </c>
       <c r="H41" t="n">
-        <v>580</v>
+        <v>357</v>
       </c>
       <c r="I41" t="n">
-        <v>52035</v>
+        <v>52258</v>
       </c>
       <c r="J41" t="n">
-        <v>51896.25</v>
+        <v>52885.5</v>
       </c>
       <c r="K41" t="n">
-        <v>52460.5</v>
+        <v>53063</v>
       </c>
       <c r="L41" t="n">
-        <v>53024.75</v>
+        <v>53240.5</v>
       </c>
       <c r="M41" t="n">
-        <v>53237.5</v>
+        <v>53643</v>
       </c>
       <c r="N41" t="n">
-        <v>53450.25</v>
+        <v>54045.5</v>
       </c>
       <c r="O41" t="n">
-        <v>54366</v>
+        <v>53998</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3962,21 +3966,19 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
@@ -3987,57 +3989,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>53367</v>
+        <v>53524</v>
       </c>
       <c r="C42" t="n">
-        <v>53567</v>
+        <v>53797</v>
       </c>
       <c r="D42" t="n">
-        <v>53210</v>
+        <v>53426</v>
       </c>
       <c r="E42" t="n">
-        <v>53489</v>
+        <v>53645</v>
       </c>
       <c r="F42" t="n">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0029</v>
       </c>
       <c r="H42" t="n">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="I42" t="n">
-        <v>52258</v>
+        <v>52853</v>
       </c>
       <c r="J42" t="n">
-        <v>52885.5</v>
+        <v>53182.25</v>
       </c>
       <c r="K42" t="n">
-        <v>53063</v>
+        <v>53310.5</v>
       </c>
       <c r="L42" t="n">
-        <v>53240.5</v>
+        <v>53438.75</v>
       </c>
       <c r="M42" t="n">
-        <v>53643</v>
+        <v>53667.5</v>
       </c>
       <c r="N42" t="n">
-        <v>54045.5</v>
+        <v>53896.25</v>
       </c>
       <c r="O42" t="n">
-        <v>53998</v>
+        <v>53924</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4048,7 +4050,7 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="10" t="inlineStr">
+      <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4078,50 +4080,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>53524</v>
+        <v>53643</v>
       </c>
       <c r="C43" t="n">
-        <v>53797</v>
+        <v>53778</v>
       </c>
       <c r="D43" t="n">
-        <v>53426</v>
+        <v>53435</v>
       </c>
       <c r="E43" t="n">
-        <v>53645</v>
+        <v>53521</v>
       </c>
       <c r="F43" t="n">
-        <v>156</v>
+        <v>-124</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0023</v>
       </c>
       <c r="H43" t="n">
-        <v>371</v>
+        <v>343</v>
       </c>
       <c r="I43" t="n">
-        <v>52853</v>
+        <v>53055</v>
       </c>
       <c r="J43" t="n">
-        <v>53182.25</v>
+        <v>53290.75</v>
       </c>
       <c r="K43" t="n">
-        <v>53310.5</v>
+        <v>53459.5</v>
       </c>
       <c r="L43" t="n">
-        <v>53438.75</v>
+        <v>53628.25</v>
       </c>
       <c r="M43" t="n">
-        <v>53667.5</v>
+        <v>53830.5</v>
       </c>
       <c r="N43" t="n">
-        <v>53896.25</v>
+        <v>54032.75</v>
       </c>
       <c r="O43" t="n">
-        <v>53924</v>
+        <v>54168</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4129,18 +4131,18 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4155,57 +4157,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>53643</v>
+        <v>53724</v>
       </c>
       <c r="C44" t="n">
-        <v>53778</v>
+        <v>53811</v>
       </c>
       <c r="D44" t="n">
-        <v>53435</v>
+        <v>53369</v>
       </c>
       <c r="E44" t="n">
-        <v>53521</v>
+        <v>53621</v>
       </c>
       <c r="F44" t="n">
-        <v>-124</v>
+        <v>100</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0019</v>
       </c>
       <c r="H44" t="n">
-        <v>343</v>
+        <v>442</v>
       </c>
       <c r="I44" t="n">
-        <v>53055</v>
+        <v>53092</v>
       </c>
       <c r="J44" t="n">
-        <v>53290.75</v>
+        <v>53135.25</v>
       </c>
       <c r="K44" t="n">
-        <v>53459.5</v>
+        <v>53349.5</v>
       </c>
       <c r="L44" t="n">
-        <v>53628.25</v>
+        <v>53563.75</v>
       </c>
       <c r="M44" t="n">
-        <v>53830.5</v>
+        <v>53692.5</v>
       </c>
       <c r="N44" t="n">
-        <v>54032.75</v>
+        <v>53821.25</v>
       </c>
       <c r="O44" t="n">
-        <v>54168</v>
+        <v>54121</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4213,18 +4215,18 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R44" s="6" t="n">
+        <v/>
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4239,57 +4241,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>53724</v>
+        <v>53608</v>
       </c>
       <c r="C45" t="n">
-        <v>53811</v>
+        <v>53862</v>
       </c>
       <c r="D45" t="n">
-        <v>53369</v>
+        <v>53513</v>
       </c>
       <c r="E45" t="n">
-        <v>53621</v>
+        <v>53584</v>
       </c>
       <c r="F45" t="n">
-        <v>100</v>
+        <v>-37</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0007</v>
       </c>
       <c r="H45" t="n">
-        <v>442</v>
+        <v>349</v>
       </c>
       <c r="I45" t="n">
-        <v>53092</v>
+        <v>52927</v>
       </c>
       <c r="J45" t="n">
-        <v>53135.25</v>
+        <v>53194.5</v>
       </c>
       <c r="K45" t="n">
-        <v>53349.5</v>
+        <v>53400</v>
       </c>
       <c r="L45" t="n">
-        <v>53563.75</v>
+        <v>53605.5</v>
       </c>
       <c r="M45" t="n">
-        <v>53692.5</v>
+        <v>53842</v>
       </c>
       <c r="N45" t="n">
-        <v>53821.25</v>
+        <v>54078.5</v>
       </c>
       <c r="O45" t="n">
-        <v>54121</v>
+        <v>54253</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4302,7 +4304,7 @@
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
@@ -4330,70 +4332,74 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>53608</v>
+        <v>53664</v>
       </c>
       <c r="C46" t="n">
-        <v>53862</v>
+        <v>53664</v>
       </c>
       <c r="D46" t="n">
-        <v>53513</v>
+        <v>53149</v>
       </c>
       <c r="E46" t="n">
-        <v>53584</v>
+        <v>53240</v>
       </c>
       <c r="F46" t="n">
-        <v>-37</v>
+        <v>-344</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0064</v>
       </c>
       <c r="H46" t="n">
-        <v>349</v>
+        <v>515</v>
       </c>
       <c r="I46" t="n">
-        <v>52927</v>
+        <v>53164</v>
       </c>
       <c r="J46" t="n">
-        <v>53194.5</v>
+        <v>53183.25</v>
       </c>
       <c r="K46" t="n">
-        <v>53400</v>
+        <v>53409.5</v>
       </c>
       <c r="L46" t="n">
-        <v>53605.5</v>
+        <v>53635.75</v>
       </c>
       <c r="M46" t="n">
-        <v>53842</v>
+        <v>53758.5</v>
       </c>
       <c r="N46" t="n">
-        <v>54078.5</v>
+        <v>53881.25</v>
       </c>
       <c r="O46" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
+        <v>54211</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
@@ -4405,76 +4411,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>53664</v>
+        <v>53259</v>
       </c>
       <c r="C47" t="n">
-        <v>53664</v>
+        <v>53343</v>
       </c>
       <c r="D47" t="n">
-        <v>53149</v>
+        <v>52747</v>
       </c>
       <c r="E47" t="n">
-        <v>53240</v>
+        <v>52828</v>
       </c>
       <c r="F47" t="n">
-        <v>-344</v>
+        <v>-412</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0064</v>
+        <v>-0.0077</v>
       </c>
       <c r="H47" t="n">
-        <v>515</v>
+        <v>596</v>
       </c>
       <c r="I47" t="n">
-        <v>53164</v>
+        <v>52634</v>
       </c>
       <c r="J47" t="n">
-        <v>53183.25</v>
+        <v>52641.75</v>
       </c>
       <c r="K47" t="n">
-        <v>53409.5</v>
+        <v>52982.5</v>
       </c>
       <c r="L47" t="n">
-        <v>53635.75</v>
+        <v>53323.25</v>
       </c>
       <c r="M47" t="n">
-        <v>53758.5</v>
+        <v>53497.5</v>
       </c>
       <c r="N47" t="n">
-        <v>53881.25</v>
+        <v>53671.75</v>
       </c>
       <c r="O47" t="n">
-        <v>54211</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
+        <v>54179</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
+      <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4498,50 +4496,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>53259</v>
+        <v>52844</v>
       </c>
       <c r="C48" t="n">
-        <v>53343</v>
+        <v>53283</v>
       </c>
       <c r="D48" t="n">
-        <v>52747</v>
+        <v>52720</v>
       </c>
       <c r="E48" t="n">
-        <v>52828</v>
+        <v>53121</v>
       </c>
       <c r="F48" t="n">
-        <v>-412</v>
+        <v>293</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0077</v>
+        <v>0.0055</v>
       </c>
       <c r="H48" t="n">
-        <v>596</v>
+        <v>563</v>
       </c>
       <c r="I48" t="n">
-        <v>52634</v>
+        <v>52151</v>
       </c>
       <c r="J48" t="n">
-        <v>52641.75</v>
+        <v>52123.5</v>
       </c>
       <c r="K48" t="n">
-        <v>52982.5</v>
+        <v>52530</v>
       </c>
       <c r="L48" t="n">
-        <v>53323.25</v>
+        <v>52936.5</v>
       </c>
       <c r="M48" t="n">
-        <v>53497.5</v>
+        <v>53126</v>
       </c>
       <c r="N48" t="n">
-        <v>53671.75</v>
+        <v>53315.5</v>
       </c>
       <c r="O48" t="n">
-        <v>54179</v>
+        <v>53939</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4549,19 +4547,19 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
       <c r="U48" s="8" t="n">
         <v/>
       </c>
@@ -4573,55 +4571,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>52844</v>
+        <v>53120</v>
       </c>
       <c r="C49" t="n">
-        <v>53283</v>
+        <v>53827</v>
       </c>
       <c r="D49" t="n">
-        <v>52720</v>
+        <v>53093</v>
       </c>
       <c r="E49" t="n">
-        <v>53121</v>
+        <v>53745</v>
       </c>
       <c r="F49" t="n">
-        <v>293</v>
+        <v>624</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0117</v>
       </c>
       <c r="H49" t="n">
-        <v>563</v>
+        <v>734</v>
       </c>
       <c r="I49" t="n">
-        <v>52151</v>
+        <v>52157</v>
       </c>
       <c r="J49" t="n">
-        <v>52123.5</v>
+        <v>52617.75</v>
       </c>
       <c r="K49" t="n">
-        <v>52530</v>
+        <v>52839.5</v>
       </c>
       <c r="L49" t="n">
-        <v>52936.5</v>
+        <v>53061.25</v>
       </c>
       <c r="M49" t="n">
-        <v>53126</v>
+        <v>53402.5</v>
       </c>
       <c r="N49" t="n">
-        <v>53315.5</v>
+        <v>53743.75</v>
       </c>
       <c r="O49" t="n">
-        <v>53939</v>
+        <v>53846</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4632,80 +4634,78 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
+      <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W49" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>53120</v>
+        <v>53707</v>
       </c>
       <c r="C50" t="n">
-        <v>53827</v>
+        <v>53772</v>
       </c>
       <c r="D50" t="n">
-        <v>53093</v>
+        <v>53235</v>
       </c>
       <c r="E50" t="n">
-        <v>53745</v>
+        <v>53440</v>
       </c>
       <c r="F50" t="n">
-        <v>624</v>
+        <v>-305</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0117</v>
+        <v>-0.0057</v>
       </c>
       <c r="H50" t="n">
-        <v>734</v>
+        <v>537</v>
       </c>
       <c r="I50" t="n">
-        <v>52157</v>
+        <v>52359</v>
       </c>
       <c r="J50" t="n">
-        <v>52617.75</v>
+        <v>53153.5</v>
       </c>
       <c r="K50" t="n">
-        <v>52839.5</v>
+        <v>53378</v>
       </c>
       <c r="L50" t="n">
-        <v>53061.25</v>
+        <v>53602.5</v>
       </c>
       <c r="M50" t="n">
-        <v>53402.5</v>
+        <v>54112</v>
       </c>
       <c r="N50" t="n">
-        <v>53743.75</v>
+        <v>54621.5</v>
       </c>
       <c r="O50" t="n">
-        <v>53846</v>
+        <v>54561</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4713,23 +4713,21 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4739,68 +4737,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>53707</v>
+        <v>53261</v>
       </c>
       <c r="C51" t="n">
-        <v>53772</v>
+        <v>53336</v>
       </c>
       <c r="D51" t="n">
-        <v>53235</v>
+        <v>52758</v>
       </c>
       <c r="E51" t="n">
-        <v>53440</v>
+        <v>52832</v>
       </c>
       <c r="F51" t="n">
-        <v>-305</v>
+        <v>-608</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0057</v>
+        <v>-0.0114</v>
       </c>
       <c r="H51" t="n">
-        <v>537</v>
+        <v>578</v>
       </c>
       <c r="I51" t="n">
-        <v>52359</v>
+        <v>52698</v>
       </c>
       <c r="J51" t="n">
-        <v>53153.5</v>
+        <v>52871.25</v>
       </c>
       <c r="K51" t="n">
-        <v>53378</v>
+        <v>53171.5</v>
       </c>
       <c r="L51" t="n">
-        <v>53602.5</v>
+        <v>53471.75</v>
       </c>
       <c r="M51" t="n">
-        <v>54112</v>
+        <v>53708.5</v>
       </c>
       <c r="N51" t="n">
-        <v>54621.5</v>
+        <v>53945.25</v>
       </c>
       <c r="O51" t="n">
-        <v>54561</v>
+        <v>54309</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4814,79 +4818,73 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W51" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>53261</v>
+        <v>52817</v>
       </c>
       <c r="C52" t="n">
-        <v>53336</v>
+        <v>52859</v>
       </c>
       <c r="D52" t="n">
-        <v>52758</v>
+        <v>52339</v>
       </c>
       <c r="E52" t="n">
-        <v>52832</v>
+        <v>52425</v>
       </c>
       <c r="F52" t="n">
-        <v>-608</v>
+        <v>-407</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0114</v>
+        <v>-0.0077</v>
       </c>
       <c r="H52" t="n">
-        <v>578</v>
+        <v>520</v>
       </c>
       <c r="I52" t="n">
-        <v>52698</v>
+        <v>52180</v>
       </c>
       <c r="J52" t="n">
-        <v>52871.25</v>
+        <v>52146.5</v>
       </c>
       <c r="K52" t="n">
-        <v>53171.5</v>
+        <v>52543</v>
       </c>
       <c r="L52" t="n">
-        <v>53471.75</v>
+        <v>52939.5</v>
       </c>
       <c r="M52" t="n">
-        <v>53708.5</v>
+        <v>53121</v>
       </c>
       <c r="N52" t="n">
-        <v>53945.25</v>
+        <v>53302.5</v>
       </c>
       <c r="O52" t="n">
-        <v>54309</v>
+        <v>53914</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4910,50 +4908,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>52817</v>
+        <v>52473</v>
       </c>
       <c r="C53" t="n">
-        <v>52859</v>
+        <v>52676</v>
       </c>
       <c r="D53" t="n">
-        <v>52339</v>
+        <v>51992</v>
       </c>
       <c r="E53" t="n">
-        <v>52425</v>
+        <v>52095</v>
       </c>
       <c r="F53" t="n">
-        <v>-407</v>
+        <v>-330</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0077</v>
+        <v>-0.0063</v>
       </c>
       <c r="H53" t="n">
-        <v>520</v>
+        <v>684</v>
       </c>
       <c r="I53" t="n">
-        <v>52180</v>
+        <v>51819</v>
       </c>
       <c r="J53" t="n">
-        <v>52146.5</v>
+        <v>51818</v>
       </c>
       <c r="K53" t="n">
-        <v>52543</v>
+        <v>52165</v>
       </c>
       <c r="L53" t="n">
-        <v>52939.5</v>
+        <v>52512</v>
       </c>
       <c r="M53" t="n">
-        <v>53121</v>
+        <v>52685</v>
       </c>
       <c r="N53" t="n">
-        <v>53302.5</v>
+        <v>52858</v>
       </c>
       <c r="O53" t="n">
-        <v>53914</v>
+        <v>53379</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4966,7 +4964,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
+      <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4990,50 +4988,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>52473</v>
+        <v>52059</v>
       </c>
       <c r="C54" t="n">
-        <v>52676</v>
+        <v>52739</v>
       </c>
       <c r="D54" t="n">
-        <v>51992</v>
+        <v>52059</v>
       </c>
       <c r="E54" t="n">
-        <v>52095</v>
+        <v>52585</v>
       </c>
       <c r="F54" t="n">
-        <v>-330</v>
+        <v>490</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0063</v>
+        <v>0.0094</v>
       </c>
       <c r="H54" t="n">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="I54" t="n">
-        <v>51819</v>
+        <v>51308</v>
       </c>
       <c r="J54" t="n">
-        <v>51818</v>
+        <v>51291.5</v>
       </c>
       <c r="K54" t="n">
-        <v>52165</v>
+        <v>51753</v>
       </c>
       <c r="L54" t="n">
-        <v>52512</v>
+        <v>52214.5</v>
       </c>
       <c r="M54" t="n">
-        <v>52685</v>
+        <v>52437</v>
       </c>
       <c r="N54" t="n">
-        <v>52858</v>
+        <v>52659.5</v>
       </c>
       <c r="O54" t="n">
-        <v>53379</v>
+        <v>53360</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5041,22 +5039,24 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
@@ -5065,55 +5065,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>52059</v>
+        <v>52376</v>
       </c>
       <c r="C55" t="n">
-        <v>52739</v>
+        <v>52672</v>
       </c>
       <c r="D55" t="n">
-        <v>52059</v>
+        <v>52226</v>
       </c>
       <c r="E55" t="n">
-        <v>52585</v>
+        <v>52440</v>
       </c>
       <c r="F55" t="n">
-        <v>490</v>
+        <v>-145</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0094</v>
+        <v>-0.0028</v>
       </c>
       <c r="H55" t="n">
-        <v>680</v>
+        <v>446</v>
       </c>
       <c r="I55" t="n">
-        <v>51308</v>
+        <v>51379</v>
       </c>
       <c r="J55" t="n">
-        <v>51291.5</v>
+        <v>51998</v>
       </c>
       <c r="K55" t="n">
-        <v>51753</v>
+        <v>52245</v>
       </c>
       <c r="L55" t="n">
-        <v>52214.5</v>
+        <v>52492</v>
       </c>
       <c r="M55" t="n">
-        <v>52437</v>
+        <v>52925</v>
       </c>
       <c r="N55" t="n">
-        <v>52659.5</v>
+        <v>53358</v>
       </c>
       <c r="O55" t="n">
-        <v>53360</v>
+        <v>53419</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5121,23 +5125,21 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
@@ -5149,72 +5151,74 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>52376</v>
+        <v>52499</v>
       </c>
       <c r="C56" t="n">
-        <v>52672</v>
+        <v>52499</v>
       </c>
       <c r="D56" t="n">
-        <v>52226</v>
+        <v>51908</v>
       </c>
       <c r="E56" t="n">
-        <v>52440</v>
+        <v>52115</v>
       </c>
       <c r="F56" t="n">
-        <v>-145</v>
+        <v>-325</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0028</v>
+        <v>-0.0062</v>
       </c>
       <c r="H56" t="n">
-        <v>446</v>
+        <v>591</v>
       </c>
       <c r="I56" t="n">
-        <v>51379</v>
+        <v>51780</v>
       </c>
       <c r="J56" t="n">
-        <v>51998</v>
+        <v>51989.5</v>
       </c>
       <c r="K56" t="n">
-        <v>52245</v>
+        <v>52217</v>
       </c>
       <c r="L56" t="n">
-        <v>52492</v>
+        <v>52444.5</v>
       </c>
       <c r="M56" t="n">
-        <v>52925</v>
+        <v>52663</v>
       </c>
       <c r="N56" t="n">
-        <v>53358</v>
+        <v>52881.5</v>
       </c>
       <c r="O56" t="n">
-        <v>53419</v>
+        <v>53118</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5231,74 +5235,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>52499</v>
+        <v>52162</v>
       </c>
       <c r="C57" t="n">
-        <v>52499</v>
+        <v>52298</v>
       </c>
       <c r="D57" t="n">
-        <v>51908</v>
+        <v>51209</v>
       </c>
       <c r="E57" t="n">
-        <v>52115</v>
+        <v>51507</v>
       </c>
       <c r="F57" t="n">
-        <v>-325</v>
+        <v>-608</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0062</v>
+        <v>-0.0117</v>
       </c>
       <c r="H57" t="n">
-        <v>591</v>
+        <v>1089</v>
       </c>
       <c r="I57" t="n">
-        <v>51780</v>
+        <v>51317</v>
       </c>
       <c r="J57" t="n">
-        <v>51989.5</v>
+        <v>51479.75</v>
       </c>
       <c r="K57" t="n">
-        <v>52217</v>
+        <v>51819.5</v>
       </c>
       <c r="L57" t="n">
-        <v>52444.5</v>
+        <v>52159.25</v>
       </c>
       <c r="M57" t="n">
-        <v>52663</v>
+        <v>52410.5</v>
       </c>
       <c r="N57" t="n">
-        <v>52881.5</v>
+        <v>52661.75</v>
       </c>
       <c r="O57" t="n">
-        <v>53118</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
+        <v>53090</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q57" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5322,74 +5324,70 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>52162</v>
+        <v>51486</v>
       </c>
       <c r="C58" t="n">
-        <v>52298</v>
+        <v>52169</v>
       </c>
       <c r="D58" t="n">
-        <v>51209</v>
+        <v>51455</v>
       </c>
       <c r="E58" t="n">
-        <v>51507</v>
+        <v>51807</v>
       </c>
       <c r="F58" t="n">
-        <v>-608</v>
+        <v>300</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0117</v>
+        <v>0.0058</v>
       </c>
       <c r="H58" t="n">
-        <v>1089</v>
+        <v>714</v>
       </c>
       <c r="I58" t="n">
-        <v>51317</v>
+        <v>50120</v>
       </c>
       <c r="J58" t="n">
-        <v>51479.75</v>
+        <v>50294.75</v>
       </c>
       <c r="K58" t="n">
-        <v>51819.5</v>
+        <v>50962.5</v>
       </c>
       <c r="L58" t="n">
-        <v>52159.25</v>
+        <v>51630.25</v>
       </c>
       <c r="M58" t="n">
-        <v>52410.5</v>
+        <v>52051.5</v>
       </c>
       <c r="N58" t="n">
-        <v>52661.75</v>
+        <v>52472.75</v>
       </c>
       <c r="O58" t="n">
-        <v>53090</v>
-      </c>
-      <c r="P58" s="6" t="inlineStr">
+        <v>53387</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
       <c r="U58" s="8" t="n">
         <v/>
       </c>
@@ -5401,55 +5399,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>51486</v>
+        <v>51800</v>
       </c>
       <c r="C59" t="n">
-        <v>52169</v>
+        <v>51957</v>
       </c>
       <c r="D59" t="n">
-        <v>51455</v>
+        <v>51576</v>
       </c>
       <c r="E59" t="n">
-        <v>51807</v>
+        <v>51761</v>
       </c>
       <c r="F59" t="n">
-        <v>300</v>
+        <v>-46</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0009</v>
       </c>
       <c r="H59" t="n">
-        <v>714</v>
+        <v>381</v>
       </c>
       <c r="I59" t="n">
-        <v>50120</v>
+        <v>50741</v>
       </c>
       <c r="J59" t="n">
-        <v>50294.75</v>
+        <v>51090.5</v>
       </c>
       <c r="K59" t="n">
-        <v>50962.5</v>
+        <v>51450</v>
       </c>
       <c r="L59" t="n">
-        <v>51630.25</v>
+        <v>51809.5</v>
       </c>
       <c r="M59" t="n">
-        <v>52051.5</v>
+        <v>52164</v>
       </c>
       <c r="N59" t="n">
-        <v>52472.75</v>
+        <v>52518.5</v>
       </c>
       <c r="O59" t="n">
-        <v>53387</v>
+        <v>52883</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5462,13 +5464,11 @@
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5483,57 +5483,57 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>51800</v>
+        <v>52085</v>
       </c>
       <c r="C60" t="n">
-        <v>51957</v>
+        <v>52557</v>
       </c>
       <c r="D60" t="n">
-        <v>51576</v>
+        <v>52080</v>
       </c>
       <c r="E60" t="n">
-        <v>51761</v>
+        <v>52475</v>
       </c>
       <c r="F60" t="n">
-        <v>-46</v>
+        <v>714</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0138</v>
       </c>
       <c r="H60" t="n">
-        <v>381</v>
+        <v>477</v>
       </c>
       <c r="I60" t="n">
-        <v>50741</v>
+        <v>51195</v>
       </c>
       <c r="J60" t="n">
-        <v>51090.5</v>
+        <v>51377.25</v>
       </c>
       <c r="K60" t="n">
-        <v>51450</v>
+        <v>51570.5</v>
       </c>
       <c r="L60" t="n">
-        <v>51809.5</v>
+        <v>51763.75</v>
       </c>
       <c r="M60" t="n">
-        <v>52164</v>
+        <v>51951.5</v>
       </c>
       <c r="N60" t="n">
-        <v>52518.5</v>
+        <v>52139.25</v>
       </c>
       <c r="O60" t="n">
-        <v>52883</v>
+        <v>52338</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5546,76 +5546,78 @@
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W60" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V60" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W60" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>52085</v>
+        <v>52470</v>
       </c>
       <c r="C61" t="n">
-        <v>52557</v>
+        <v>52844</v>
       </c>
       <c r="D61" t="n">
-        <v>52080</v>
+        <v>52125</v>
       </c>
       <c r="E61" t="n">
-        <v>52475</v>
+        <v>52279</v>
       </c>
       <c r="F61" t="n">
-        <v>714</v>
+        <v>-196</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0138</v>
+        <v>-0.0037</v>
       </c>
       <c r="H61" t="n">
-        <v>477</v>
+        <v>719</v>
       </c>
       <c r="I61" t="n">
-        <v>51195</v>
+        <v>51603</v>
       </c>
       <c r="J61" t="n">
-        <v>51377.25</v>
+        <v>52076.25</v>
       </c>
       <c r="K61" t="n">
-        <v>51570.5</v>
+        <v>52236.5</v>
       </c>
       <c r="L61" t="n">
-        <v>51763.75</v>
+        <v>52396.75</v>
       </c>
       <c r="M61" t="n">
-        <v>51951.5</v>
+        <v>52713.5</v>
       </c>
       <c r="N61" t="n">
-        <v>52139.25</v>
+        <v>53030.25</v>
       </c>
       <c r="O61" t="n">
-        <v>52338</v>
+        <v>53034</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5623,12 +5625,14 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="n">
-        <v/>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T61" s="8" t="inlineStr">
@@ -5636,70 +5640,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
       </c>
       <c r="W61" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>52470</v>
+        <v>51878</v>
       </c>
       <c r="C62" t="n">
-        <v>52844</v>
+        <v>51900</v>
       </c>
       <c r="D62" t="n">
-        <v>52125</v>
+        <v>51878</v>
       </c>
       <c r="E62" t="n">
-        <v>52279</v>
+        <v>51889</v>
       </c>
       <c r="F62" t="n">
-        <v>-196</v>
+        <v>-390</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0037</v>
+        <v>-0.0075</v>
       </c>
       <c r="H62" t="n">
-        <v>719</v>
+        <v>22</v>
       </c>
       <c r="I62" t="n">
-        <v>51603</v>
+        <v>51406</v>
       </c>
       <c r="J62" t="n">
-        <v>52076.25</v>
+        <v>51457.25</v>
       </c>
       <c r="K62" t="n">
-        <v>52236.5</v>
+        <v>51919.5</v>
       </c>
       <c r="L62" t="n">
-        <v>52396.75</v>
+        <v>52381.75</v>
       </c>
       <c r="M62" t="n">
-        <v>52713.5</v>
+        <v>52638.5</v>
       </c>
       <c r="N62" t="n">
-        <v>53030.25</v>
+        <v>52895.25</v>
       </c>
       <c r="O62" t="n">
-        <v>53034</v>
+        <v>53563</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5712,15 +5716,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S62" s="7" t="inlineStr">
+      <c r="S62" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T62" s="8" t="n">
+        <v/>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5734,90 +5736,6 @@
         </is>
       </c>
       <c r="X62" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>52255</v>
-      </c>
-      <c r="C63" t="n">
-        <v>52371</v>
-      </c>
-      <c r="D63" t="n">
-        <v>52076</v>
-      </c>
-      <c r="E63" t="n">
-        <v>52081</v>
-      </c>
-      <c r="F63" t="n">
-        <v>-198</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>-0.0038</v>
-      </c>
-      <c r="H63" t="n">
-        <v>295</v>
-      </c>
-      <c r="I63" t="n">
-        <v>51406</v>
-      </c>
-      <c r="J63" t="n">
-        <v>51457.25</v>
-      </c>
-      <c r="K63" t="n">
-        <v>51919.5</v>
-      </c>
-      <c r="L63" t="n">
-        <v>52381.75</v>
-      </c>
-      <c r="M63" t="n">
-        <v>52638.5</v>
-      </c>
-      <c r="N63" t="n">
-        <v>52895.25</v>
-      </c>
-      <c r="O63" t="n">
-        <v>53563</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
         <is>
           <t>強警訊</t>
         </is>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52183</v>
+        <v>52554</v>
       </c>
       <c r="C2" t="n">
-        <v>52700</v>
+        <v>52763</v>
       </c>
       <c r="D2" t="n">
-        <v>52179</v>
+        <v>52383</v>
       </c>
       <c r="E2" t="n">
-        <v>52572</v>
+        <v>52670</v>
       </c>
       <c r="F2" t="n">
-        <v>363</v>
+        <v>98</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.007</v>
+        <v>0.0019</v>
       </c>
       <c r="H2" t="n">
-        <v>521</v>
+        <v>380</v>
       </c>
       <c r="I2" t="n">
-        <v>51474</v>
+        <v>51658</v>
       </c>
       <c r="J2" t="n">
-        <v>51642</v>
+        <v>52117.25</v>
       </c>
       <c r="K2" t="n">
-        <v>51942</v>
+        <v>52311.5</v>
       </c>
       <c r="L2" t="n">
-        <v>52242</v>
+        <v>52505.75</v>
       </c>
       <c r="M2" t="n">
-        <v>52476</v>
+        <v>52832.5</v>
       </c>
       <c r="N2" t="n">
-        <v>52710</v>
+        <v>53159.25</v>
       </c>
       <c r="O2" t="n">
-        <v>53076</v>
+        <v>53221</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -714,50 +714,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>52554</v>
+        <v>52546</v>
       </c>
       <c r="C3" t="n">
-        <v>52763</v>
+        <v>53105</v>
       </c>
       <c r="D3" t="n">
-        <v>52383</v>
+        <v>52381</v>
       </c>
       <c r="E3" t="n">
-        <v>52670</v>
+        <v>52668</v>
       </c>
       <c r="F3" t="n">
-        <v>98</v>
+        <v>-2</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0</v>
       </c>
       <c r="H3" t="n">
-        <v>380</v>
+        <v>724</v>
       </c>
       <c r="I3" t="n">
-        <v>51658</v>
+        <v>52003</v>
       </c>
       <c r="J3" t="n">
-        <v>52117.25</v>
+        <v>52338.5</v>
       </c>
       <c r="K3" t="n">
-        <v>52311.5</v>
+        <v>52480</v>
       </c>
       <c r="L3" t="n">
-        <v>52505.75</v>
+        <v>52621.5</v>
       </c>
       <c r="M3" t="n">
-        <v>52832.5</v>
+        <v>52860</v>
       </c>
       <c r="N3" t="n">
-        <v>53159.25</v>
+        <v>53098.5</v>
       </c>
       <c r="O3" t="n">
-        <v>53221</v>
+        <v>53143</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -765,21 +765,25 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -789,55 +793,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>52546</v>
+        <v>52640</v>
       </c>
       <c r="C4" t="n">
-        <v>53105</v>
+        <v>53218</v>
       </c>
       <c r="D4" t="n">
-        <v>52381</v>
+        <v>52551</v>
       </c>
       <c r="E4" t="n">
-        <v>52668</v>
+        <v>53183</v>
       </c>
       <c r="F4" t="n">
-        <v>-2</v>
+        <v>515</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0</v>
+        <v>0.0098</v>
       </c>
       <c r="H4" t="n">
-        <v>724</v>
+        <v>667</v>
       </c>
       <c r="I4" t="n">
-        <v>52003</v>
+        <v>51657</v>
       </c>
       <c r="J4" t="n">
-        <v>52338.5</v>
+        <v>51906.5</v>
       </c>
       <c r="K4" t="n">
-        <v>52480</v>
+        <v>52306</v>
       </c>
       <c r="L4" t="n">
-        <v>52621.5</v>
+        <v>52705.5</v>
       </c>
       <c r="M4" t="n">
-        <v>52860</v>
+        <v>53030</v>
       </c>
       <c r="N4" t="n">
-        <v>53098.5</v>
+        <v>53354.5</v>
       </c>
       <c r="O4" t="n">
-        <v>53143</v>
+        <v>53829</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -845,25 +853,21 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R4" s="6" t="n">
+        <v/>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
@@ -873,59 +877,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52640</v>
+        <v>53230</v>
       </c>
       <c r="C5" t="n">
-        <v>53218</v>
+        <v>53421</v>
       </c>
       <c r="D5" t="n">
-        <v>52551</v>
+        <v>52962</v>
       </c>
       <c r="E5" t="n">
-        <v>53183</v>
+        <v>53372</v>
       </c>
       <c r="F5" t="n">
-        <v>515</v>
+        <v>189</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0036</v>
       </c>
       <c r="H5" t="n">
-        <v>667</v>
+        <v>459</v>
       </c>
       <c r="I5" t="n">
-        <v>51657</v>
+        <v>51884</v>
       </c>
       <c r="J5" t="n">
-        <v>51906.5</v>
+        <v>52665.25</v>
       </c>
       <c r="K5" t="n">
-        <v>52306</v>
+        <v>52849.5</v>
       </c>
       <c r="L5" t="n">
-        <v>52705.5</v>
+        <v>53033.75</v>
       </c>
       <c r="M5" t="n">
-        <v>53030</v>
+        <v>53516.5</v>
       </c>
       <c r="N5" t="n">
-        <v>53354.5</v>
+        <v>53999.25</v>
       </c>
       <c r="O5" t="n">
-        <v>53829</v>
+        <v>53885</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -962,50 +962,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>53230</v>
+        <v>53405</v>
       </c>
       <c r="C6" t="n">
-        <v>53421</v>
+        <v>53656</v>
       </c>
       <c r="D6" t="n">
-        <v>52962</v>
+        <v>53076</v>
       </c>
       <c r="E6" t="n">
-        <v>53372</v>
+        <v>53197</v>
       </c>
       <c r="F6" t="n">
-        <v>189</v>
+        <v>-175</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0036</v>
+        <v>-0.0033</v>
       </c>
       <c r="H6" t="n">
-        <v>459</v>
+        <v>580</v>
       </c>
       <c r="I6" t="n">
-        <v>51884</v>
+        <v>52503</v>
       </c>
       <c r="J6" t="n">
-        <v>52665.25</v>
+        <v>53003.25</v>
       </c>
       <c r="K6" t="n">
-        <v>52849.5</v>
+        <v>53142.5</v>
       </c>
       <c r="L6" t="n">
-        <v>53033.75</v>
+        <v>53281.75</v>
       </c>
       <c r="M6" t="n">
-        <v>53516.5</v>
+        <v>53601.5</v>
       </c>
       <c r="N6" t="n">
-        <v>53999.25</v>
+        <v>53921.25</v>
       </c>
       <c r="O6" t="n">
-        <v>53885</v>
+        <v>53880</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1013,17 +1013,19 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U6" s="8" t="n">
@@ -1037,65 +1039,73 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>53405</v>
+        <v>53166</v>
       </c>
       <c r="C7" t="n">
-        <v>53656</v>
+        <v>53207</v>
       </c>
       <c r="D7" t="n">
-        <v>53076</v>
+        <v>52343</v>
       </c>
       <c r="E7" t="n">
-        <v>53197</v>
+        <v>52624</v>
       </c>
       <c r="F7" t="n">
-        <v>-175</v>
+        <v>-573</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0108</v>
       </c>
       <c r="H7" t="n">
-        <v>580</v>
+        <v>864</v>
       </c>
       <c r="I7" t="n">
-        <v>52503</v>
+        <v>52496</v>
       </c>
       <c r="J7" t="n">
-        <v>53003.25</v>
+        <v>52532.5</v>
       </c>
       <c r="K7" t="n">
-        <v>53142.5</v>
+        <v>52907</v>
       </c>
       <c r="L7" t="n">
-        <v>53281.75</v>
+        <v>53281.5</v>
       </c>
       <c r="M7" t="n">
-        <v>53601.5</v>
+        <v>53487</v>
       </c>
       <c r="N7" t="n">
-        <v>53921.25</v>
+        <v>53692.5</v>
       </c>
       <c r="O7" t="n">
-        <v>53880</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
+        <v>54236</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
@@ -1103,10 +1113,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1121,76 +1129,70 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>53166</v>
+        <v>52541</v>
       </c>
       <c r="C8" t="n">
-        <v>53207</v>
+        <v>52865</v>
       </c>
       <c r="D8" t="n">
-        <v>52343</v>
+        <v>52501</v>
       </c>
       <c r="E8" t="n">
-        <v>52624</v>
+        <v>52761</v>
       </c>
       <c r="F8" t="n">
-        <v>-573</v>
+        <v>137</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0108</v>
+        <v>0.0026</v>
       </c>
       <c r="H8" t="n">
-        <v>864</v>
+        <v>364</v>
       </c>
       <c r="I8" t="n">
-        <v>52496</v>
+        <v>51479</v>
       </c>
       <c r="J8" t="n">
-        <v>52532.5</v>
+        <v>51684.5</v>
       </c>
       <c r="K8" t="n">
-        <v>52907</v>
+        <v>52192</v>
       </c>
       <c r="L8" t="n">
-        <v>53281.5</v>
+        <v>52699.5</v>
       </c>
       <c r="M8" t="n">
-        <v>53487</v>
+        <v>53056</v>
       </c>
       <c r="N8" t="n">
-        <v>53692.5</v>
+        <v>53412.5</v>
       </c>
       <c r="O8" t="n">
-        <v>54236</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>54071</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1209,57 +1211,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52541</v>
+        <v>52753</v>
       </c>
       <c r="C9" t="n">
-        <v>52865</v>
+        <v>52992</v>
       </c>
       <c r="D9" t="n">
-        <v>52501</v>
+        <v>52506</v>
       </c>
       <c r="E9" t="n">
-        <v>52761</v>
+        <v>52906</v>
       </c>
       <c r="F9" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0027</v>
       </c>
       <c r="H9" t="n">
-        <v>364</v>
+        <v>486</v>
       </c>
       <c r="I9" t="n">
-        <v>51479</v>
+        <v>52137</v>
       </c>
       <c r="J9" t="n">
-        <v>51684.5</v>
+        <v>52436</v>
       </c>
       <c r="K9" t="n">
-        <v>52192</v>
+        <v>52579</v>
       </c>
       <c r="L9" t="n">
-        <v>52699.5</v>
+        <v>52722</v>
       </c>
       <c r="M9" t="n">
-        <v>53056</v>
+        <v>52943</v>
       </c>
       <c r="N9" t="n">
-        <v>53412.5</v>
+        <v>53164</v>
       </c>
       <c r="O9" t="n">
-        <v>54071</v>
+        <v>53229</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1267,16 +1269,20 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1289,59 +1295,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52753</v>
+        <v>52844</v>
       </c>
       <c r="C10" t="n">
-        <v>52992</v>
+        <v>53113</v>
       </c>
       <c r="D10" t="n">
-        <v>52506</v>
+        <v>52603</v>
       </c>
       <c r="E10" t="n">
-        <v>52906</v>
+        <v>52764</v>
       </c>
       <c r="F10" t="n">
-        <v>145</v>
+        <v>-142</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0027</v>
       </c>
       <c r="H10" t="n">
-        <v>486</v>
+        <v>510</v>
       </c>
       <c r="I10" t="n">
-        <v>52137</v>
+        <v>52020</v>
       </c>
       <c r="J10" t="n">
-        <v>52436</v>
+        <v>52498.5</v>
       </c>
       <c r="K10" t="n">
-        <v>52579</v>
+        <v>52663</v>
       </c>
       <c r="L10" t="n">
-        <v>52722</v>
+        <v>52827.5</v>
       </c>
       <c r="M10" t="n">
-        <v>52943</v>
+        <v>53149</v>
       </c>
       <c r="N10" t="n">
-        <v>53164</v>
+        <v>53470.5</v>
       </c>
       <c r="O10" t="n">
-        <v>53229</v>
+        <v>53478</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1354,15 +1356,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1375,55 +1375,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>52844</v>
+        <v>52731</v>
       </c>
       <c r="C11" t="n">
-        <v>53113</v>
+        <v>52981</v>
       </c>
       <c r="D11" t="n">
-        <v>52603</v>
+        <v>52255</v>
       </c>
       <c r="E11" t="n">
-        <v>52764</v>
+        <v>52791</v>
       </c>
       <c r="F11" t="n">
-        <v>-142</v>
+        <v>27</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0005</v>
       </c>
       <c r="H11" t="n">
-        <v>510</v>
+        <v>726</v>
       </c>
       <c r="I11" t="n">
-        <v>52020</v>
+        <v>52093</v>
       </c>
       <c r="J11" t="n">
-        <v>52498.5</v>
+        <v>52207</v>
       </c>
       <c r="K11" t="n">
-        <v>52663</v>
+        <v>52509</v>
       </c>
       <c r="L11" t="n">
-        <v>52827.5</v>
+        <v>52811</v>
       </c>
       <c r="M11" t="n">
-        <v>53149</v>
+        <v>53019</v>
       </c>
       <c r="N11" t="n">
-        <v>53470.5</v>
+        <v>53227</v>
       </c>
       <c r="O11" t="n">
-        <v>53478</v>
+        <v>53623</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1457,57 +1461,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52731</v>
+        <v>52792</v>
       </c>
       <c r="C12" t="n">
-        <v>52981</v>
+        <v>53088</v>
       </c>
       <c r="D12" t="n">
-        <v>52255</v>
+        <v>52680</v>
       </c>
       <c r="E12" t="n">
-        <v>52791</v>
+        <v>52900</v>
       </c>
       <c r="F12" t="n">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0021</v>
       </c>
       <c r="H12" t="n">
-        <v>726</v>
+        <v>408</v>
       </c>
       <c r="I12" t="n">
-        <v>52093</v>
+        <v>51529</v>
       </c>
       <c r="J12" t="n">
-        <v>52207</v>
+        <v>52151.5</v>
       </c>
       <c r="K12" t="n">
-        <v>52509</v>
+        <v>52428</v>
       </c>
       <c r="L12" t="n">
-        <v>52811</v>
+        <v>52704.5</v>
       </c>
       <c r="M12" t="n">
-        <v>53019</v>
+        <v>53154</v>
       </c>
       <c r="N12" t="n">
-        <v>53227</v>
+        <v>53603.5</v>
       </c>
       <c r="O12" t="n">
-        <v>53623</v>
+        <v>53707</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1515,14 +1519,12 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1539,59 +1541,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>52792</v>
+        <v>52919</v>
       </c>
       <c r="C13" t="n">
-        <v>53088</v>
+        <v>53108</v>
       </c>
       <c r="D13" t="n">
-        <v>52680</v>
+        <v>52607</v>
       </c>
       <c r="E13" t="n">
-        <v>52900</v>
+        <v>52786</v>
       </c>
       <c r="F13" t="n">
-        <v>109</v>
+        <v>-114</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0022</v>
       </c>
       <c r="H13" t="n">
-        <v>408</v>
+        <v>501</v>
       </c>
       <c r="I13" t="n">
-        <v>51529</v>
+        <v>52272</v>
       </c>
       <c r="J13" t="n">
-        <v>52151.5</v>
+        <v>52500</v>
       </c>
       <c r="K13" t="n">
-        <v>52428</v>
+        <v>52696</v>
       </c>
       <c r="L13" t="n">
-        <v>52704.5</v>
+        <v>52892</v>
       </c>
       <c r="M13" t="n">
-        <v>53154</v>
+        <v>53104</v>
       </c>
       <c r="N13" t="n">
-        <v>53603.5</v>
+        <v>53316</v>
       </c>
       <c r="O13" t="n">
-        <v>53707</v>
+        <v>53496</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1599,16 +1597,20 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1621,65 +1623,71 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>52919</v>
+        <v>52778</v>
       </c>
       <c r="C14" t="n">
-        <v>53108</v>
+        <v>52835</v>
       </c>
       <c r="D14" t="n">
-        <v>52607</v>
+        <v>52174</v>
       </c>
       <c r="E14" t="n">
-        <v>52786</v>
+        <v>52375</v>
       </c>
       <c r="F14" t="n">
-        <v>-114</v>
+        <v>-411</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0078</v>
       </c>
       <c r="H14" t="n">
-        <v>501</v>
+        <v>661</v>
       </c>
       <c r="I14" t="n">
-        <v>52272</v>
+        <v>52106</v>
       </c>
       <c r="J14" t="n">
-        <v>52500</v>
+        <v>52249.25</v>
       </c>
       <c r="K14" t="n">
-        <v>52696</v>
+        <v>52535.5</v>
       </c>
       <c r="L14" t="n">
-        <v>52892</v>
+        <v>52821.75</v>
       </c>
       <c r="M14" t="n">
-        <v>53104</v>
+        <v>53036.5</v>
       </c>
       <c r="N14" t="n">
-        <v>53316</v>
+        <v>53251.25</v>
       </c>
       <c r="O14" t="n">
-        <v>53496</v>
+        <v>53609</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S14" s="10" t="inlineStr">
@@ -1687,10 +1695,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1705,69 +1711,67 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52778</v>
+        <v>52300</v>
       </c>
       <c r="C15" t="n">
-        <v>52835</v>
+        <v>52633</v>
       </c>
       <c r="D15" t="n">
-        <v>52174</v>
+        <v>51999</v>
       </c>
       <c r="E15" t="n">
-        <v>52375</v>
+        <v>52073</v>
       </c>
       <c r="F15" t="n">
-        <v>-411</v>
+        <v>-302</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0078</v>
+        <v>-0.0058</v>
       </c>
       <c r="H15" t="n">
-        <v>661</v>
+        <v>634</v>
       </c>
       <c r="I15" t="n">
-        <v>52106</v>
+        <v>51513</v>
       </c>
       <c r="J15" t="n">
-        <v>52249.25</v>
+        <v>51649.25</v>
       </c>
       <c r="K15" t="n">
-        <v>52535.5</v>
+        <v>52044.5</v>
       </c>
       <c r="L15" t="n">
-        <v>52821.75</v>
+        <v>52439.75</v>
       </c>
       <c r="M15" t="n">
-        <v>53036.5</v>
+        <v>52705.5</v>
       </c>
       <c r="N15" t="n">
-        <v>53251.25</v>
+        <v>52971.25</v>
       </c>
       <c r="O15" t="n">
-        <v>53609</v>
+        <v>53496</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
@@ -1798,50 +1802,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>52300</v>
+        <v>52091</v>
       </c>
       <c r="C16" t="n">
-        <v>52633</v>
+        <v>52590</v>
       </c>
       <c r="D16" t="n">
-        <v>51999</v>
+        <v>52035</v>
       </c>
       <c r="E16" t="n">
-        <v>52073</v>
+        <v>52443</v>
       </c>
       <c r="F16" t="n">
-        <v>-302</v>
+        <v>370</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.0071</v>
       </c>
       <c r="H16" t="n">
-        <v>634</v>
+        <v>555</v>
       </c>
       <c r="I16" t="n">
-        <v>51513</v>
+        <v>51365</v>
       </c>
       <c r="J16" t="n">
-        <v>51649.25</v>
+        <v>51317.5</v>
       </c>
       <c r="K16" t="n">
-        <v>52044.5</v>
+        <v>51756</v>
       </c>
       <c r="L16" t="n">
-        <v>52439.75</v>
+        <v>52194.5</v>
       </c>
       <c r="M16" t="n">
-        <v>52705.5</v>
+        <v>52390</v>
       </c>
       <c r="N16" t="n">
-        <v>52971.25</v>
+        <v>52585.5</v>
       </c>
       <c r="O16" t="n">
-        <v>53496</v>
+        <v>53267</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1849,21 +1853,23 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1875,57 +1881,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52091</v>
+        <v>52431</v>
       </c>
       <c r="C17" t="n">
-        <v>52590</v>
+        <v>52721</v>
       </c>
       <c r="D17" t="n">
-        <v>52035</v>
+        <v>52262</v>
       </c>
       <c r="E17" t="n">
-        <v>52443</v>
+        <v>52449</v>
       </c>
       <c r="F17" t="n">
-        <v>370</v>
+        <v>6</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0001</v>
       </c>
       <c r="H17" t="n">
-        <v>555</v>
+        <v>459</v>
       </c>
       <c r="I17" t="n">
-        <v>51365</v>
+        <v>51480</v>
       </c>
       <c r="J17" t="n">
-        <v>51317.5</v>
+        <v>51953.25</v>
       </c>
       <c r="K17" t="n">
-        <v>51756</v>
+        <v>52165.5</v>
       </c>
       <c r="L17" t="n">
-        <v>52194.5</v>
+        <v>52377.75</v>
       </c>
       <c r="M17" t="n">
-        <v>52390</v>
+        <v>52720.5</v>
       </c>
       <c r="N17" t="n">
-        <v>52585.5</v>
+        <v>53063.25</v>
       </c>
       <c r="O17" t="n">
-        <v>53267</v>
+        <v>53145</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1938,19 +1944,17 @@
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
@@ -1959,88 +1963,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52431</v>
+        <v>52430</v>
       </c>
       <c r="C18" t="n">
-        <v>52721</v>
+        <v>52515</v>
       </c>
       <c r="D18" t="n">
-        <v>52262</v>
+        <v>51720</v>
       </c>
       <c r="E18" t="n">
-        <v>52449</v>
+        <v>51894</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>-555</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0106</v>
       </c>
       <c r="H18" t="n">
-        <v>459</v>
+        <v>795</v>
       </c>
       <c r="I18" t="n">
-        <v>51480</v>
+        <v>51803</v>
       </c>
       <c r="J18" t="n">
-        <v>51953.25</v>
+        <v>51968.75</v>
       </c>
       <c r="K18" t="n">
-        <v>52165.5</v>
+        <v>52219.5</v>
       </c>
       <c r="L18" t="n">
-        <v>52377.75</v>
+        <v>52470.25</v>
       </c>
       <c r="M18" t="n">
-        <v>52720.5</v>
+        <v>52678.5</v>
       </c>
       <c r="N18" t="n">
-        <v>53063.25</v>
+        <v>52886.75</v>
       </c>
       <c r="O18" t="n">
-        <v>53145</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
+        <v>53180</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W18" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
@@ -2048,74 +2052,70 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>52430</v>
+        <v>51920</v>
       </c>
       <c r="C19" t="n">
-        <v>52515</v>
+        <v>52314</v>
       </c>
       <c r="D19" t="n">
-        <v>51720</v>
+        <v>51846</v>
       </c>
       <c r="E19" t="n">
-        <v>51894</v>
+        <v>52124</v>
       </c>
       <c r="F19" t="n">
-        <v>-555</v>
+        <v>230</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0044</v>
       </c>
       <c r="H19" t="n">
-        <v>795</v>
+        <v>468</v>
       </c>
       <c r="I19" t="n">
-        <v>51803</v>
+        <v>50925</v>
       </c>
       <c r="J19" t="n">
-        <v>51968.75</v>
+        <v>50987.25</v>
       </c>
       <c r="K19" t="n">
-        <v>52219.5</v>
+        <v>51496.5</v>
       </c>
       <c r="L19" t="n">
-        <v>52470.25</v>
+        <v>52005.75</v>
       </c>
       <c r="M19" t="n">
-        <v>52678.5</v>
+        <v>52291.5</v>
       </c>
       <c r="N19" t="n">
-        <v>52886.75</v>
+        <v>52577.25</v>
       </c>
       <c r="O19" t="n">
-        <v>53180</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
+        <v>53310</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
       <c r="U19" s="8" t="n">
         <v/>
       </c>
@@ -2127,55 +2127,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>51920</v>
+        <v>52299</v>
       </c>
       <c r="C20" t="n">
-        <v>52314</v>
+        <v>52790</v>
       </c>
       <c r="D20" t="n">
-        <v>51846</v>
+        <v>52173</v>
       </c>
       <c r="E20" t="n">
-        <v>52124</v>
+        <v>52382</v>
       </c>
       <c r="F20" t="n">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0049</v>
       </c>
       <c r="H20" t="n">
-        <v>468</v>
+        <v>617</v>
       </c>
       <c r="I20" t="n">
-        <v>50925</v>
+        <v>51378</v>
       </c>
       <c r="J20" t="n">
-        <v>50987.25</v>
+        <v>51678</v>
       </c>
       <c r="K20" t="n">
-        <v>51496.5</v>
+        <v>51890</v>
       </c>
       <c r="L20" t="n">
-        <v>52005.75</v>
+        <v>52102</v>
       </c>
       <c r="M20" t="n">
-        <v>52291.5</v>
+        <v>52358</v>
       </c>
       <c r="N20" t="n">
-        <v>52577.25</v>
+        <v>52614</v>
       </c>
       <c r="O20" t="n">
-        <v>53310</v>
+        <v>52782</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2188,19 +2192,23 @@
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W20" s="11" t="inlineStr">
         <is>
@@ -2209,57 +2217,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>52299</v>
+        <v>52405</v>
       </c>
       <c r="C21" t="n">
-        <v>52790</v>
+        <v>53105</v>
       </c>
       <c r="D21" t="n">
-        <v>52173</v>
+        <v>52290</v>
       </c>
       <c r="E21" t="n">
-        <v>52382</v>
+        <v>52944</v>
       </c>
       <c r="F21" t="n">
-        <v>258</v>
+        <v>562</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0107</v>
       </c>
       <c r="H21" t="n">
-        <v>617</v>
+        <v>815</v>
       </c>
       <c r="I21" t="n">
-        <v>51378</v>
+        <v>51556</v>
       </c>
       <c r="J21" t="n">
-        <v>51678</v>
+        <v>51715.25</v>
       </c>
       <c r="K21" t="n">
-        <v>51890</v>
+        <v>52073.5</v>
       </c>
       <c r="L21" t="n">
-        <v>52102</v>
+        <v>52431.75</v>
       </c>
       <c r="M21" t="n">
-        <v>52358</v>
+        <v>52690.5</v>
       </c>
       <c r="N21" t="n">
-        <v>52614</v>
+        <v>52949.25</v>
       </c>
       <c r="O21" t="n">
-        <v>52782</v>
+        <v>53407</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2277,18 +2285,16 @@
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="11" t="inlineStr">
         <is>
@@ -2304,74 +2310,76 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>52405</v>
+        <v>52915</v>
       </c>
       <c r="C22" t="n">
-        <v>53105</v>
+        <v>53033</v>
       </c>
       <c r="D22" t="n">
-        <v>52290</v>
+        <v>51630</v>
       </c>
       <c r="E22" t="n">
-        <v>52944</v>
+        <v>51765</v>
       </c>
       <c r="F22" t="n">
-        <v>562</v>
+        <v>-1179</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0223</v>
       </c>
       <c r="H22" t="n">
-        <v>815</v>
+        <v>1403</v>
       </c>
       <c r="I22" t="n">
-        <v>51556</v>
+        <v>51475</v>
       </c>
       <c r="J22" t="n">
-        <v>51715.25</v>
+        <v>52252.25</v>
       </c>
       <c r="K22" t="n">
-        <v>52073.5</v>
+        <v>52536.5</v>
       </c>
       <c r="L22" t="n">
-        <v>52431.75</v>
+        <v>52820.75</v>
       </c>
       <c r="M22" t="n">
-        <v>52690.5</v>
+        <v>53351.5</v>
       </c>
       <c r="N22" t="n">
-        <v>52949.25</v>
+        <v>53882.25</v>
       </c>
       <c r="O22" t="n">
-        <v>53407</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
+        <v>53920</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2381,83 +2389,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>52915</v>
+        <v>51759</v>
       </c>
       <c r="C23" t="n">
-        <v>53033</v>
+        <v>52484</v>
       </c>
       <c r="D23" t="n">
-        <v>51630</v>
+        <v>51732</v>
       </c>
       <c r="E23" t="n">
-        <v>51765</v>
+        <v>52380</v>
       </c>
       <c r="F23" t="n">
-        <v>-1179</v>
+        <v>615</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0119</v>
       </c>
       <c r="H23" t="n">
-        <v>1403</v>
+        <v>752</v>
       </c>
       <c r="I23" t="n">
-        <v>51475</v>
+        <v>50227</v>
       </c>
       <c r="J23" t="n">
-        <v>52252.25</v>
+        <v>50078.75</v>
       </c>
       <c r="K23" t="n">
-        <v>52536.5</v>
+        <v>51063.5</v>
       </c>
       <c r="L23" t="n">
-        <v>52820.75</v>
+        <v>52048.25</v>
       </c>
       <c r="M23" t="n">
-        <v>53351.5</v>
+        <v>52466.5</v>
       </c>
       <c r="N23" t="n">
-        <v>53882.25</v>
+        <v>52884.75</v>
       </c>
       <c r="O23" t="n">
-        <v>53920</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
+        <v>54436</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
@@ -2469,55 +2469,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>51759</v>
+        <v>52395</v>
       </c>
       <c r="C24" t="n">
-        <v>52484</v>
+        <v>52772</v>
       </c>
       <c r="D24" t="n">
-        <v>51732</v>
+        <v>52124</v>
       </c>
       <c r="E24" t="n">
-        <v>52380</v>
+        <v>52635</v>
       </c>
       <c r="F24" t="n">
-        <v>615</v>
+        <v>255</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0119</v>
+        <v>0.0049</v>
       </c>
       <c r="H24" t="n">
-        <v>752</v>
+        <v>648</v>
       </c>
       <c r="I24" t="n">
-        <v>50227</v>
+        <v>50980</v>
       </c>
       <c r="J24" t="n">
-        <v>50078.75</v>
+        <v>51764</v>
       </c>
       <c r="K24" t="n">
-        <v>51063.5</v>
+        <v>52004</v>
       </c>
       <c r="L24" t="n">
-        <v>52048.25</v>
+        <v>52244</v>
       </c>
       <c r="M24" t="n">
-        <v>52466.5</v>
+        <v>52756</v>
       </c>
       <c r="N24" t="n">
-        <v>52884.75</v>
+        <v>53268</v>
       </c>
       <c r="O24" t="n">
-        <v>54436</v>
+        <v>53236</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2551,57 +2555,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>52395</v>
+        <v>52780</v>
       </c>
       <c r="C25" t="n">
-        <v>52772</v>
+        <v>53414</v>
       </c>
       <c r="D25" t="n">
-        <v>52124</v>
+        <v>52777</v>
       </c>
       <c r="E25" t="n">
-        <v>52635</v>
+        <v>53334</v>
       </c>
       <c r="F25" t="n">
-        <v>255</v>
+        <v>699</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0133</v>
       </c>
       <c r="H25" t="n">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="I25" t="n">
-        <v>50980</v>
+        <v>51476</v>
       </c>
       <c r="J25" t="n">
-        <v>51764</v>
+        <v>52080.5</v>
       </c>
       <c r="K25" t="n">
-        <v>52004</v>
+        <v>52311</v>
       </c>
       <c r="L25" t="n">
-        <v>52244</v>
+        <v>52541.5</v>
       </c>
       <c r="M25" t="n">
-        <v>52756</v>
+        <v>52959</v>
       </c>
       <c r="N25" t="n">
-        <v>53268</v>
+        <v>53376.5</v>
       </c>
       <c r="O25" t="n">
-        <v>53236</v>
+        <v>53420</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2619,11 +2623,13 @@
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2642,50 +2648,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>52780</v>
+        <v>53381</v>
       </c>
       <c r="C26" t="n">
-        <v>53414</v>
+        <v>54423</v>
       </c>
       <c r="D26" t="n">
-        <v>52777</v>
+        <v>53267</v>
       </c>
       <c r="E26" t="n">
-        <v>53334</v>
+        <v>54268</v>
       </c>
       <c r="F26" t="n">
-        <v>699</v>
+        <v>934</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0175</v>
       </c>
       <c r="H26" t="n">
-        <v>637</v>
+        <v>1156</v>
       </c>
       <c r="I26" t="n">
-        <v>51476</v>
+        <v>52140</v>
       </c>
       <c r="J26" t="n">
-        <v>52080.5</v>
+        <v>52816.25</v>
       </c>
       <c r="K26" t="n">
-        <v>52311</v>
+        <v>53015.5</v>
       </c>
       <c r="L26" t="n">
-        <v>52541.5</v>
+        <v>53214.75</v>
       </c>
       <c r="M26" t="n">
-        <v>52959</v>
+        <v>53652.5</v>
       </c>
       <c r="N26" t="n">
-        <v>53376.5</v>
+        <v>54090.25</v>
       </c>
       <c r="O26" t="n">
-        <v>53420</v>
+        <v>54051</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2711,67 +2717,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W26" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W26" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>53381</v>
+        <v>54369</v>
       </c>
       <c r="C27" t="n">
-        <v>54423</v>
+        <v>54884</v>
       </c>
       <c r="D27" t="n">
-        <v>53267</v>
+        <v>54342</v>
       </c>
       <c r="E27" t="n">
-        <v>54268</v>
+        <v>54494</v>
       </c>
       <c r="F27" t="n">
-        <v>934</v>
+        <v>226</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0042</v>
       </c>
       <c r="H27" t="n">
-        <v>1156</v>
+        <v>542</v>
       </c>
       <c r="I27" t="n">
-        <v>52140</v>
+        <v>52111</v>
       </c>
       <c r="J27" t="n">
-        <v>52816.25</v>
+        <v>53323.5</v>
       </c>
       <c r="K27" t="n">
-        <v>53015.5</v>
+        <v>53690</v>
       </c>
       <c r="L27" t="n">
-        <v>53214.75</v>
+        <v>54056.5</v>
       </c>
       <c r="M27" t="n">
-        <v>53652.5</v>
+        <v>54846</v>
       </c>
       <c r="N27" t="n">
-        <v>54090.25</v>
+        <v>55635.5</v>
       </c>
       <c r="O27" t="n">
-        <v>54051</v>
+        <v>55579</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2789,18 +2793,14 @@
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
@@ -2812,70 +2812,72 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>54369</v>
+        <v>54555</v>
       </c>
       <c r="C28" t="n">
-        <v>54884</v>
+        <v>54678</v>
       </c>
       <c r="D28" t="n">
-        <v>54342</v>
+        <v>53952</v>
       </c>
       <c r="E28" t="n">
-        <v>54494</v>
+        <v>54013</v>
       </c>
       <c r="F28" t="n">
-        <v>226</v>
+        <v>-481</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>542</v>
+        <v>726</v>
       </c>
       <c r="I28" t="n">
-        <v>52111</v>
+        <v>53800</v>
       </c>
       <c r="J28" t="n">
-        <v>53323.5</v>
+        <v>53892.5</v>
       </c>
       <c r="K28" t="n">
-        <v>53690</v>
+        <v>54223</v>
       </c>
       <c r="L28" t="n">
-        <v>54056.5</v>
+        <v>54553.5</v>
       </c>
       <c r="M28" t="n">
-        <v>54846</v>
+        <v>54765</v>
       </c>
       <c r="N28" t="n">
-        <v>55635.5</v>
+        <v>54976.5</v>
       </c>
       <c r="O28" t="n">
-        <v>55579</v>
+        <v>55426</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
+      <c r="Q28" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
       <c r="U28" s="8" t="n">
         <v/>
       </c>
@@ -2887,72 +2889,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>54555</v>
+        <v>54040</v>
       </c>
       <c r="C29" t="n">
-        <v>54678</v>
+        <v>54202</v>
       </c>
       <c r="D29" t="n">
-        <v>53952</v>
+        <v>53879</v>
       </c>
       <c r="E29" t="n">
-        <v>54013</v>
+        <v>54152</v>
       </c>
       <c r="F29" t="n">
-        <v>-481</v>
+        <v>139</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0026</v>
       </c>
       <c r="H29" t="n">
-        <v>726</v>
+        <v>323</v>
       </c>
       <c r="I29" t="n">
-        <v>53800</v>
+        <v>53226</v>
       </c>
       <c r="J29" t="n">
-        <v>53892.5</v>
+        <v>53136</v>
       </c>
       <c r="K29" t="n">
-        <v>54223</v>
+        <v>53650</v>
       </c>
       <c r="L29" t="n">
-        <v>54553.5</v>
+        <v>54164</v>
       </c>
       <c r="M29" t="n">
-        <v>54765</v>
+        <v>54376</v>
       </c>
       <c r="N29" t="n">
-        <v>54976.5</v>
+        <v>54588</v>
       </c>
       <c r="O29" t="n">
-        <v>55426</v>
+        <v>55404</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2971,57 +2973,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>54040</v>
+        <v>54133</v>
       </c>
       <c r="C30" t="n">
-        <v>54202</v>
+        <v>54170</v>
       </c>
       <c r="D30" t="n">
-        <v>53879</v>
+        <v>53952</v>
       </c>
       <c r="E30" t="n">
-        <v>54152</v>
+        <v>54063</v>
       </c>
       <c r="F30" t="n">
-        <v>139</v>
+        <v>-89</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0016</v>
       </c>
       <c r="H30" t="n">
-        <v>323</v>
+        <v>218</v>
       </c>
       <c r="I30" t="n">
-        <v>53226</v>
+        <v>53556</v>
       </c>
       <c r="J30" t="n">
-        <v>53136</v>
+        <v>53884.75</v>
       </c>
       <c r="K30" t="n">
-        <v>53650</v>
+        <v>53990.5</v>
       </c>
       <c r="L30" t="n">
-        <v>54164</v>
+        <v>54096.25</v>
       </c>
       <c r="M30" t="n">
-        <v>54376</v>
+        <v>54313.5</v>
       </c>
       <c r="N30" t="n">
-        <v>54588</v>
+        <v>54530.75</v>
       </c>
       <c r="O30" t="n">
-        <v>55404</v>
+        <v>54525</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3029,8 +3031,10 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
@@ -3060,56 +3064,58 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>54133</v>
+        <v>54049</v>
       </c>
       <c r="C31" t="n">
-        <v>54170</v>
+        <v>54336</v>
       </c>
       <c r="D31" t="n">
-        <v>53952</v>
+        <v>53855</v>
       </c>
       <c r="E31" t="n">
-        <v>54063</v>
+        <v>53880</v>
       </c>
       <c r="F31" t="n">
-        <v>-89</v>
+        <v>-183</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0034</v>
       </c>
       <c r="H31" t="n">
-        <v>218</v>
+        <v>481</v>
       </c>
       <c r="I31" t="n">
-        <v>53556</v>
+        <v>53734</v>
       </c>
       <c r="J31" t="n">
-        <v>53884.75</v>
+        <v>53846</v>
       </c>
       <c r="K31" t="n">
-        <v>53990.5</v>
+        <v>53954</v>
       </c>
       <c r="L31" t="n">
-        <v>54096.25</v>
+        <v>54062</v>
       </c>
       <c r="M31" t="n">
-        <v>54313.5</v>
+        <v>54172</v>
       </c>
       <c r="N31" t="n">
-        <v>54530.75</v>
+        <v>54282</v>
       </c>
       <c r="O31" t="n">
-        <v>54525</v>
+        <v>54388</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
@@ -3118,14 +3124,18 @@
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3144,78 +3154,72 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>54049</v>
+        <v>53903</v>
       </c>
       <c r="C32" t="n">
-        <v>54336</v>
+        <v>54150</v>
       </c>
       <c r="D32" t="n">
-        <v>53855</v>
+        <v>53830</v>
       </c>
       <c r="E32" t="n">
-        <v>53880</v>
+        <v>53871</v>
       </c>
       <c r="F32" t="n">
-        <v>-183</v>
+        <v>-9</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0002</v>
       </c>
       <c r="H32" t="n">
-        <v>481</v>
+        <v>320</v>
       </c>
       <c r="I32" t="n">
-        <v>53734</v>
+        <v>53374</v>
       </c>
       <c r="J32" t="n">
-        <v>53846</v>
+        <v>53291.25</v>
       </c>
       <c r="K32" t="n">
-        <v>53954</v>
+        <v>53639.5</v>
       </c>
       <c r="L32" t="n">
-        <v>54062</v>
+        <v>53987.75</v>
       </c>
       <c r="M32" t="n">
-        <v>54172</v>
+        <v>54120.5</v>
       </c>
       <c r="N32" t="n">
-        <v>54282</v>
+        <v>54253.25</v>
       </c>
       <c r="O32" t="n">
-        <v>54388</v>
+        <v>54817</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3227,57 +3231,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>53903</v>
+        <v>53905</v>
       </c>
       <c r="C33" t="n">
-        <v>54150</v>
+        <v>54149</v>
       </c>
       <c r="D33" t="n">
-        <v>53830</v>
+        <v>53715</v>
       </c>
       <c r="E33" t="n">
-        <v>53871</v>
+        <v>53935</v>
       </c>
       <c r="F33" t="n">
-        <v>-9</v>
+        <v>64</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0012</v>
       </c>
       <c r="H33" t="n">
-        <v>320</v>
+        <v>434</v>
       </c>
       <c r="I33" t="n">
-        <v>53374</v>
+        <v>53510</v>
       </c>
       <c r="J33" t="n">
-        <v>53291.25</v>
+        <v>53491.5</v>
       </c>
       <c r="K33" t="n">
-        <v>53639.5</v>
+        <v>53711</v>
       </c>
       <c r="L33" t="n">
-        <v>53987.75</v>
+        <v>53930.5</v>
       </c>
       <c r="M33" t="n">
-        <v>54120.5</v>
+        <v>54031</v>
       </c>
       <c r="N33" t="n">
-        <v>54253.25</v>
+        <v>54131.5</v>
       </c>
       <c r="O33" t="n">
-        <v>54817</v>
+        <v>54470</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3288,9 +3292,9 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
@@ -3298,8 +3302,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U33" s="8" t="n">
-        <v/>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3311,57 +3317,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>53905</v>
+        <v>53961</v>
       </c>
       <c r="C34" t="n">
-        <v>54149</v>
+        <v>53999</v>
       </c>
       <c r="D34" t="n">
-        <v>53715</v>
+        <v>53745</v>
       </c>
       <c r="E34" t="n">
-        <v>53935</v>
+        <v>53807</v>
       </c>
       <c r="F34" t="n">
-        <v>64</v>
+        <v>-128</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0024</v>
       </c>
       <c r="H34" t="n">
-        <v>434</v>
+        <v>254</v>
       </c>
       <c r="I34" t="n">
-        <v>53510</v>
+        <v>53281</v>
       </c>
       <c r="J34" t="n">
-        <v>53491.5</v>
+        <v>53502.5</v>
       </c>
       <c r="K34" t="n">
-        <v>53711</v>
+        <v>53718</v>
       </c>
       <c r="L34" t="n">
-        <v>53930.5</v>
+        <v>53933.5</v>
       </c>
       <c r="M34" t="n">
-        <v>54031</v>
+        <v>54152</v>
       </c>
       <c r="N34" t="n">
-        <v>54131.5</v>
+        <v>54370.5</v>
       </c>
       <c r="O34" t="n">
-        <v>54470</v>
+        <v>54583</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3369,23 +3375,21 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3404,60 +3408,64 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>53961</v>
+        <v>53790</v>
       </c>
       <c r="C35" t="n">
-        <v>53999</v>
+        <v>53840</v>
       </c>
       <c r="D35" t="n">
-        <v>53745</v>
+        <v>53464</v>
       </c>
       <c r="E35" t="n">
-        <v>53807</v>
+        <v>53544</v>
       </c>
       <c r="F35" t="n">
-        <v>-128</v>
+        <v>-263</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0049</v>
       </c>
       <c r="H35" t="n">
-        <v>254</v>
+        <v>376</v>
       </c>
       <c r="I35" t="n">
-        <v>53281</v>
+        <v>53491</v>
       </c>
       <c r="J35" t="n">
-        <v>53502.5</v>
+        <v>53520.5</v>
       </c>
       <c r="K35" t="n">
-        <v>53718</v>
+        <v>53680</v>
       </c>
       <c r="L35" t="n">
-        <v>53933.5</v>
+        <v>53839.5</v>
       </c>
       <c r="M35" t="n">
-        <v>54152</v>
+        <v>53934</v>
       </c>
       <c r="N35" t="n">
-        <v>54370.5</v>
+        <v>54028.5</v>
       </c>
       <c r="O35" t="n">
-        <v>54583</v>
-      </c>
-      <c r="P35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
+        <v>54253</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
@@ -3481,71 +3489,67 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>53790</v>
+        <v>53501</v>
       </c>
       <c r="C36" t="n">
-        <v>53840</v>
+        <v>53594</v>
       </c>
       <c r="D36" t="n">
-        <v>53464</v>
+        <v>53311</v>
       </c>
       <c r="E36" t="n">
-        <v>53544</v>
+        <v>53403</v>
       </c>
       <c r="F36" t="n">
-        <v>-263</v>
+        <v>-141</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0026</v>
       </c>
       <c r="H36" t="n">
-        <v>376</v>
+        <v>283</v>
       </c>
       <c r="I36" t="n">
-        <v>53491</v>
+        <v>53088</v>
       </c>
       <c r="J36" t="n">
-        <v>53520.5</v>
+        <v>53114</v>
       </c>
       <c r="K36" t="n">
-        <v>53680</v>
+        <v>53356</v>
       </c>
       <c r="L36" t="n">
-        <v>53839.5</v>
+        <v>53598</v>
       </c>
       <c r="M36" t="n">
-        <v>53934</v>
+        <v>53732</v>
       </c>
       <c r="N36" t="n">
-        <v>54028.5</v>
+        <v>53866</v>
       </c>
       <c r="O36" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q36" s="6" t="inlineStr">
+        <v>54216</v>
+      </c>
+      <c r="P36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
@@ -3576,50 +3580,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>53501</v>
+        <v>53408</v>
       </c>
       <c r="C37" t="n">
-        <v>53594</v>
+        <v>53780</v>
       </c>
       <c r="D37" t="n">
-        <v>53311</v>
+        <v>53337</v>
       </c>
       <c r="E37" t="n">
-        <v>53403</v>
+        <v>53530</v>
       </c>
       <c r="F37" t="n">
-        <v>-141</v>
+        <v>127</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0026</v>
+        <v>0.0024</v>
       </c>
       <c r="H37" t="n">
-        <v>283</v>
+        <v>443</v>
       </c>
       <c r="I37" t="n">
-        <v>53088</v>
+        <v>53028</v>
       </c>
       <c r="J37" t="n">
-        <v>53114</v>
+        <v>53095.25</v>
       </c>
       <c r="K37" t="n">
-        <v>53356</v>
+        <v>53261.5</v>
       </c>
       <c r="L37" t="n">
-        <v>53598</v>
+        <v>53427.75</v>
       </c>
       <c r="M37" t="n">
-        <v>53732</v>
+        <v>53544.5</v>
       </c>
       <c r="N37" t="n">
-        <v>53866</v>
+        <v>53661.25</v>
       </c>
       <c r="O37" t="n">
-        <v>54216</v>
+        <v>53877</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3627,21 +3631,23 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3651,90 +3657,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>53408</v>
+        <v>53529</v>
       </c>
       <c r="C38" t="n">
-        <v>53780</v>
+        <v>53589</v>
       </c>
       <c r="D38" t="n">
-        <v>53337</v>
+        <v>52812</v>
       </c>
       <c r="E38" t="n">
-        <v>53530</v>
+        <v>52849</v>
       </c>
       <c r="F38" t="n">
-        <v>127</v>
+        <v>-681</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0127</v>
       </c>
       <c r="H38" t="n">
-        <v>443</v>
+        <v>777</v>
       </c>
       <c r="I38" t="n">
-        <v>53028</v>
+        <v>52894</v>
       </c>
       <c r="J38" t="n">
-        <v>53095.25</v>
+        <v>53072.75</v>
       </c>
       <c r="K38" t="n">
-        <v>53261.5</v>
+        <v>53308.5</v>
       </c>
       <c r="L38" t="n">
-        <v>53427.75</v>
+        <v>53544.25</v>
       </c>
       <c r="M38" t="n">
-        <v>53544.5</v>
+        <v>53751.5</v>
       </c>
       <c r="N38" t="n">
-        <v>53661.25</v>
+        <v>53958.75</v>
       </c>
       <c r="O38" t="n">
-        <v>53877</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
+        <v>54223</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U38" s="8" t="inlineStr">
+      <c r="Q38" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W38" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr"/>
@@ -3742,77 +3746,75 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>53529</v>
+        <v>52876</v>
       </c>
       <c r="C39" t="n">
-        <v>53589</v>
+        <v>53418</v>
       </c>
       <c r="D39" t="n">
-        <v>52812</v>
+        <v>52838</v>
       </c>
       <c r="E39" t="n">
-        <v>52849</v>
+        <v>53353</v>
       </c>
       <c r="F39" t="n">
-        <v>-681</v>
+        <v>504</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0095</v>
       </c>
       <c r="H39" t="n">
-        <v>777</v>
+        <v>580</v>
       </c>
       <c r="I39" t="n">
-        <v>52894</v>
+        <v>52035</v>
       </c>
       <c r="J39" t="n">
-        <v>53072.75</v>
+        <v>51896.25</v>
       </c>
       <c r="K39" t="n">
-        <v>53308.5</v>
+        <v>52460.5</v>
       </c>
       <c r="L39" t="n">
-        <v>53544.25</v>
+        <v>53024.75</v>
       </c>
       <c r="M39" t="n">
-        <v>53751.5</v>
+        <v>53237.5</v>
       </c>
       <c r="N39" t="n">
-        <v>53958.75</v>
+        <v>53450.25</v>
       </c>
       <c r="O39" t="n">
-        <v>54223</v>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
+        <v>54366</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
@@ -3821,55 +3823,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>52876</v>
+        <v>53367</v>
       </c>
       <c r="C40" t="n">
-        <v>53418</v>
+        <v>53567</v>
       </c>
       <c r="D40" t="n">
-        <v>52838</v>
+        <v>53210</v>
       </c>
       <c r="E40" t="n">
-        <v>53353</v>
+        <v>53489</v>
       </c>
       <c r="F40" t="n">
-        <v>504</v>
+        <v>136</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.0025</v>
       </c>
       <c r="H40" t="n">
-        <v>580</v>
+        <v>357</v>
       </c>
       <c r="I40" t="n">
-        <v>52035</v>
+        <v>52258</v>
       </c>
       <c r="J40" t="n">
-        <v>51896.25</v>
+        <v>52885.5</v>
       </c>
       <c r="K40" t="n">
-        <v>52460.5</v>
+        <v>53063</v>
       </c>
       <c r="L40" t="n">
-        <v>53024.75</v>
+        <v>53240.5</v>
       </c>
       <c r="M40" t="n">
-        <v>53237.5</v>
+        <v>53643</v>
       </c>
       <c r="N40" t="n">
-        <v>53450.25</v>
+        <v>54045.5</v>
       </c>
       <c r="O40" t="n">
-        <v>54366</v>
+        <v>53998</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3887,14 +3893,12 @@
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U40" s="8" t="n">
+        <v/>
+      </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
@@ -3905,57 +3909,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>53367</v>
+        <v>53524</v>
       </c>
       <c r="C41" t="n">
-        <v>53567</v>
+        <v>53797</v>
       </c>
       <c r="D41" t="n">
-        <v>53210</v>
+        <v>53426</v>
       </c>
       <c r="E41" t="n">
-        <v>53489</v>
+        <v>53645</v>
       </c>
       <c r="F41" t="n">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0029</v>
       </c>
       <c r="H41" t="n">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="I41" t="n">
-        <v>52258</v>
+        <v>52853</v>
       </c>
       <c r="J41" t="n">
-        <v>52885.5</v>
+        <v>53182.25</v>
       </c>
       <c r="K41" t="n">
-        <v>53063</v>
+        <v>53310.5</v>
       </c>
       <c r="L41" t="n">
-        <v>53240.5</v>
+        <v>53438.75</v>
       </c>
       <c r="M41" t="n">
-        <v>53643</v>
+        <v>53667.5</v>
       </c>
       <c r="N41" t="n">
-        <v>54045.5</v>
+        <v>53896.25</v>
       </c>
       <c r="O41" t="n">
-        <v>53998</v>
+        <v>53924</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3996,50 +4000,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>53524</v>
+        <v>53643</v>
       </c>
       <c r="C42" t="n">
-        <v>53797</v>
+        <v>53778</v>
       </c>
       <c r="D42" t="n">
-        <v>53426</v>
+        <v>53435</v>
       </c>
       <c r="E42" t="n">
-        <v>53645</v>
+        <v>53521</v>
       </c>
       <c r="F42" t="n">
-        <v>156</v>
+        <v>-124</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0023</v>
       </c>
       <c r="H42" t="n">
-        <v>371</v>
+        <v>343</v>
       </c>
       <c r="I42" t="n">
-        <v>52853</v>
+        <v>53055</v>
       </c>
       <c r="J42" t="n">
-        <v>53182.25</v>
+        <v>53290.75</v>
       </c>
       <c r="K42" t="n">
-        <v>53310.5</v>
+        <v>53459.5</v>
       </c>
       <c r="L42" t="n">
-        <v>53438.75</v>
+        <v>53628.25</v>
       </c>
       <c r="M42" t="n">
-        <v>53667.5</v>
+        <v>53830.5</v>
       </c>
       <c r="N42" t="n">
-        <v>53896.25</v>
+        <v>54032.75</v>
       </c>
       <c r="O42" t="n">
-        <v>53924</v>
+        <v>54168</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4047,19 +4051,19 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
+      <c r="R42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4073,57 +4077,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>53643</v>
+        <v>53724</v>
       </c>
       <c r="C43" t="n">
-        <v>53778</v>
+        <v>53811</v>
       </c>
       <c r="D43" t="n">
-        <v>53435</v>
+        <v>53369</v>
       </c>
       <c r="E43" t="n">
-        <v>53521</v>
+        <v>53621</v>
       </c>
       <c r="F43" t="n">
-        <v>-124</v>
+        <v>100</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0019</v>
       </c>
       <c r="H43" t="n">
-        <v>343</v>
+        <v>442</v>
       </c>
       <c r="I43" t="n">
-        <v>53055</v>
+        <v>53092</v>
       </c>
       <c r="J43" t="n">
-        <v>53290.75</v>
+        <v>53135.25</v>
       </c>
       <c r="K43" t="n">
-        <v>53459.5</v>
+        <v>53349.5</v>
       </c>
       <c r="L43" t="n">
-        <v>53628.25</v>
+        <v>53563.75</v>
       </c>
       <c r="M43" t="n">
-        <v>53830.5</v>
+        <v>53692.5</v>
       </c>
       <c r="N43" t="n">
-        <v>54032.75</v>
+        <v>53821.25</v>
       </c>
       <c r="O43" t="n">
-        <v>54168</v>
+        <v>54121</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4131,18 +4135,18 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4157,57 +4161,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>53724</v>
+        <v>53608</v>
       </c>
       <c r="C44" t="n">
-        <v>53811</v>
+        <v>53862</v>
       </c>
       <c r="D44" t="n">
-        <v>53369</v>
+        <v>53513</v>
       </c>
       <c r="E44" t="n">
-        <v>53621</v>
+        <v>53584</v>
       </c>
       <c r="F44" t="n">
-        <v>100</v>
+        <v>-37</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0007</v>
       </c>
       <c r="H44" t="n">
-        <v>442</v>
+        <v>349</v>
       </c>
       <c r="I44" t="n">
-        <v>53092</v>
+        <v>52927</v>
       </c>
       <c r="J44" t="n">
-        <v>53135.25</v>
+        <v>53194.5</v>
       </c>
       <c r="K44" t="n">
-        <v>53349.5</v>
+        <v>53400</v>
       </c>
       <c r="L44" t="n">
-        <v>53563.75</v>
+        <v>53605.5</v>
       </c>
       <c r="M44" t="n">
-        <v>53692.5</v>
+        <v>53842</v>
       </c>
       <c r="N44" t="n">
-        <v>53821.25</v>
+        <v>54078.5</v>
       </c>
       <c r="O44" t="n">
-        <v>54121</v>
+        <v>54253</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4218,9 +4222,9 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
@@ -4248,69 +4252,73 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>53608</v>
+        <v>53664</v>
       </c>
       <c r="C45" t="n">
-        <v>53862</v>
+        <v>53664</v>
       </c>
       <c r="D45" t="n">
-        <v>53513</v>
+        <v>53149</v>
       </c>
       <c r="E45" t="n">
-        <v>53584</v>
+        <v>53240</v>
       </c>
       <c r="F45" t="n">
-        <v>-37</v>
+        <v>-344</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0064</v>
       </c>
       <c r="H45" t="n">
-        <v>349</v>
+        <v>515</v>
       </c>
       <c r="I45" t="n">
-        <v>52927</v>
+        <v>53164</v>
       </c>
       <c r="J45" t="n">
-        <v>53194.5</v>
+        <v>53183.25</v>
       </c>
       <c r="K45" t="n">
-        <v>53400</v>
+        <v>53409.5</v>
       </c>
       <c r="L45" t="n">
-        <v>53605.5</v>
+        <v>53635.75</v>
       </c>
       <c r="M45" t="n">
-        <v>53842</v>
+        <v>53758.5</v>
       </c>
       <c r="N45" t="n">
-        <v>54078.5</v>
+        <v>53881.25</v>
       </c>
       <c r="O45" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+        <v>54211</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4323,73 +4331,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>53664</v>
+        <v>53259</v>
       </c>
       <c r="C46" t="n">
-        <v>53664</v>
+        <v>53343</v>
       </c>
       <c r="D46" t="n">
-        <v>53149</v>
+        <v>52747</v>
       </c>
       <c r="E46" t="n">
-        <v>53240</v>
+        <v>52828</v>
       </c>
       <c r="F46" t="n">
-        <v>-344</v>
+        <v>-412</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0064</v>
+        <v>-0.0077</v>
       </c>
       <c r="H46" t="n">
-        <v>515</v>
+        <v>596</v>
       </c>
       <c r="I46" t="n">
-        <v>53164</v>
+        <v>52634</v>
       </c>
       <c r="J46" t="n">
-        <v>53183.25</v>
+        <v>52641.75</v>
       </c>
       <c r="K46" t="n">
-        <v>53409.5</v>
+        <v>52982.5</v>
       </c>
       <c r="L46" t="n">
-        <v>53635.75</v>
+        <v>53323.25</v>
       </c>
       <c r="M46" t="n">
-        <v>53758.5</v>
+        <v>53497.5</v>
       </c>
       <c r="N46" t="n">
-        <v>53881.25</v>
+        <v>53671.75</v>
       </c>
       <c r="O46" t="n">
-        <v>54211</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
+        <v>54179</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S46" s="10" t="inlineStr">
@@ -4416,50 +4416,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>53259</v>
+        <v>52844</v>
       </c>
       <c r="C47" t="n">
-        <v>53343</v>
+        <v>53283</v>
       </c>
       <c r="D47" t="n">
-        <v>52747</v>
+        <v>52720</v>
       </c>
       <c r="E47" t="n">
-        <v>52828</v>
+        <v>53121</v>
       </c>
       <c r="F47" t="n">
-        <v>-412</v>
+        <v>293</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0077</v>
+        <v>0.0055</v>
       </c>
       <c r="H47" t="n">
-        <v>596</v>
+        <v>563</v>
       </c>
       <c r="I47" t="n">
-        <v>52634</v>
+        <v>52151</v>
       </c>
       <c r="J47" t="n">
-        <v>52641.75</v>
+        <v>52123.5</v>
       </c>
       <c r="K47" t="n">
-        <v>52982.5</v>
+        <v>52530</v>
       </c>
       <c r="L47" t="n">
-        <v>53323.25</v>
+        <v>52936.5</v>
       </c>
       <c r="M47" t="n">
-        <v>53497.5</v>
+        <v>53126</v>
       </c>
       <c r="N47" t="n">
-        <v>53671.75</v>
+        <v>53315.5</v>
       </c>
       <c r="O47" t="n">
-        <v>54179</v>
+        <v>53939</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4467,19 +4467,19 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
       <c r="U47" s="8" t="n">
         <v/>
       </c>
@@ -4491,55 +4491,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>52844</v>
+        <v>53120</v>
       </c>
       <c r="C48" t="n">
-        <v>53283</v>
+        <v>53827</v>
       </c>
       <c r="D48" t="n">
-        <v>52720</v>
+        <v>53093</v>
       </c>
       <c r="E48" t="n">
-        <v>53121</v>
+        <v>53745</v>
       </c>
       <c r="F48" t="n">
-        <v>293</v>
+        <v>624</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0117</v>
       </c>
       <c r="H48" t="n">
-        <v>563</v>
+        <v>734</v>
       </c>
       <c r="I48" t="n">
-        <v>52151</v>
+        <v>52157</v>
       </c>
       <c r="J48" t="n">
-        <v>52123.5</v>
+        <v>52617.75</v>
       </c>
       <c r="K48" t="n">
-        <v>52530</v>
+        <v>52839.5</v>
       </c>
       <c r="L48" t="n">
-        <v>52936.5</v>
+        <v>53061.25</v>
       </c>
       <c r="M48" t="n">
-        <v>53126</v>
+        <v>53402.5</v>
       </c>
       <c r="N48" t="n">
-        <v>53315.5</v>
+        <v>53743.75</v>
       </c>
       <c r="O48" t="n">
-        <v>53939</v>
+        <v>53846</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4557,73 +4561,71 @@
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W48" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>53120</v>
+        <v>53707</v>
       </c>
       <c r="C49" t="n">
-        <v>53827</v>
+        <v>53772</v>
       </c>
       <c r="D49" t="n">
-        <v>53093</v>
+        <v>53235</v>
       </c>
       <c r="E49" t="n">
-        <v>53745</v>
+        <v>53440</v>
       </c>
       <c r="F49" t="n">
-        <v>624</v>
+        <v>-305</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0117</v>
+        <v>-0.0057</v>
       </c>
       <c r="H49" t="n">
-        <v>734</v>
+        <v>537</v>
       </c>
       <c r="I49" t="n">
-        <v>52157</v>
+        <v>52359</v>
       </c>
       <c r="J49" t="n">
-        <v>52617.75</v>
+        <v>53153.5</v>
       </c>
       <c r="K49" t="n">
-        <v>52839.5</v>
+        <v>53378</v>
       </c>
       <c r="L49" t="n">
-        <v>53061.25</v>
+        <v>53602.5</v>
       </c>
       <c r="M49" t="n">
-        <v>53402.5</v>
+        <v>54112</v>
       </c>
       <c r="N49" t="n">
-        <v>53743.75</v>
+        <v>54621.5</v>
       </c>
       <c r="O49" t="n">
-        <v>53846</v>
+        <v>54561</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4631,24 +4633,22 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
@@ -4657,65 +4657,71 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>53707</v>
+        <v>53261</v>
       </c>
       <c r="C50" t="n">
-        <v>53772</v>
+        <v>53336</v>
       </c>
       <c r="D50" t="n">
-        <v>53235</v>
+        <v>52758</v>
       </c>
       <c r="E50" t="n">
-        <v>53440</v>
+        <v>52832</v>
       </c>
       <c r="F50" t="n">
-        <v>-305</v>
+        <v>-608</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0057</v>
+        <v>-0.0114</v>
       </c>
       <c r="H50" t="n">
-        <v>537</v>
+        <v>578</v>
       </c>
       <c r="I50" t="n">
-        <v>52359</v>
+        <v>52698</v>
       </c>
       <c r="J50" t="n">
-        <v>53153.5</v>
+        <v>52871.25</v>
       </c>
       <c r="K50" t="n">
-        <v>53378</v>
+        <v>53171.5</v>
       </c>
       <c r="L50" t="n">
-        <v>53602.5</v>
+        <v>53471.75</v>
       </c>
       <c r="M50" t="n">
-        <v>54112</v>
+        <v>53708.5</v>
       </c>
       <c r="N50" t="n">
-        <v>54621.5</v>
+        <v>53945.25</v>
       </c>
       <c r="O50" t="n">
-        <v>54561</v>
+        <v>54309</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
@@ -4732,76 +4738,70 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W50" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>53261</v>
+        <v>52817</v>
       </c>
       <c r="C51" t="n">
-        <v>53336</v>
+        <v>52859</v>
       </c>
       <c r="D51" t="n">
-        <v>52758</v>
+        <v>52339</v>
       </c>
       <c r="E51" t="n">
-        <v>52832</v>
+        <v>52425</v>
       </c>
       <c r="F51" t="n">
-        <v>-608</v>
+        <v>-407</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0114</v>
+        <v>-0.0077</v>
       </c>
       <c r="H51" t="n">
-        <v>578</v>
+        <v>520</v>
       </c>
       <c r="I51" t="n">
-        <v>52698</v>
+        <v>52180</v>
       </c>
       <c r="J51" t="n">
-        <v>52871.25</v>
+        <v>52146.5</v>
       </c>
       <c r="K51" t="n">
-        <v>53171.5</v>
+        <v>52543</v>
       </c>
       <c r="L51" t="n">
-        <v>53471.75</v>
+        <v>52939.5</v>
       </c>
       <c r="M51" t="n">
-        <v>53708.5</v>
+        <v>53121</v>
       </c>
       <c r="N51" t="n">
-        <v>53945.25</v>
+        <v>53302.5</v>
       </c>
       <c r="O51" t="n">
-        <v>54309</v>
+        <v>53914</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
@@ -4828,50 +4828,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>52817</v>
+        <v>52473</v>
       </c>
       <c r="C52" t="n">
-        <v>52859</v>
+        <v>52676</v>
       </c>
       <c r="D52" t="n">
-        <v>52339</v>
+        <v>51992</v>
       </c>
       <c r="E52" t="n">
-        <v>52425</v>
+        <v>52095</v>
       </c>
       <c r="F52" t="n">
-        <v>-407</v>
+        <v>-330</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0077</v>
+        <v>-0.0063</v>
       </c>
       <c r="H52" t="n">
-        <v>520</v>
+        <v>684</v>
       </c>
       <c r="I52" t="n">
-        <v>52180</v>
+        <v>51819</v>
       </c>
       <c r="J52" t="n">
-        <v>52146.5</v>
+        <v>51818</v>
       </c>
       <c r="K52" t="n">
-        <v>52543</v>
+        <v>52165</v>
       </c>
       <c r="L52" t="n">
-        <v>52939.5</v>
+        <v>52512</v>
       </c>
       <c r="M52" t="n">
-        <v>53121</v>
+        <v>52685</v>
       </c>
       <c r="N52" t="n">
-        <v>53302.5</v>
+        <v>52858</v>
       </c>
       <c r="O52" t="n">
-        <v>53914</v>
+        <v>53379</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4908,50 +4908,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>52473</v>
+        <v>52059</v>
       </c>
       <c r="C53" t="n">
-        <v>52676</v>
+        <v>52739</v>
       </c>
       <c r="D53" t="n">
-        <v>51992</v>
+        <v>52059</v>
       </c>
       <c r="E53" t="n">
-        <v>52095</v>
+        <v>52585</v>
       </c>
       <c r="F53" t="n">
-        <v>-330</v>
+        <v>490</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0063</v>
+        <v>0.0094</v>
       </c>
       <c r="H53" t="n">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="I53" t="n">
-        <v>51819</v>
+        <v>51308</v>
       </c>
       <c r="J53" t="n">
-        <v>51818</v>
+        <v>51291.5</v>
       </c>
       <c r="K53" t="n">
-        <v>52165</v>
+        <v>51753</v>
       </c>
       <c r="L53" t="n">
-        <v>52512</v>
+        <v>52214.5</v>
       </c>
       <c r="M53" t="n">
-        <v>52685</v>
+        <v>52437</v>
       </c>
       <c r="N53" t="n">
-        <v>52858</v>
+        <v>52659.5</v>
       </c>
       <c r="O53" t="n">
-        <v>53379</v>
+        <v>53360</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4959,22 +4959,24 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
@@ -4983,55 +4985,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>52059</v>
+        <v>52376</v>
       </c>
       <c r="C54" t="n">
-        <v>52739</v>
+        <v>52672</v>
       </c>
       <c r="D54" t="n">
-        <v>52059</v>
+        <v>52226</v>
       </c>
       <c r="E54" t="n">
-        <v>52585</v>
+        <v>52440</v>
       </c>
       <c r="F54" t="n">
-        <v>490</v>
+        <v>-145</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0094</v>
+        <v>-0.0028</v>
       </c>
       <c r="H54" t="n">
-        <v>680</v>
+        <v>446</v>
       </c>
       <c r="I54" t="n">
-        <v>51308</v>
+        <v>51379</v>
       </c>
       <c r="J54" t="n">
-        <v>51291.5</v>
+        <v>51998</v>
       </c>
       <c r="K54" t="n">
-        <v>51753</v>
+        <v>52245</v>
       </c>
       <c r="L54" t="n">
-        <v>52214.5</v>
+        <v>52492</v>
       </c>
       <c r="M54" t="n">
-        <v>52437</v>
+        <v>52925</v>
       </c>
       <c r="N54" t="n">
-        <v>52659.5</v>
+        <v>53358</v>
       </c>
       <c r="O54" t="n">
-        <v>53360</v>
+        <v>53419</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5039,23 +5045,21 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
@@ -5067,72 +5071,74 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>52376</v>
+        <v>52499</v>
       </c>
       <c r="C55" t="n">
-        <v>52672</v>
+        <v>52499</v>
       </c>
       <c r="D55" t="n">
-        <v>52226</v>
+        <v>51908</v>
       </c>
       <c r="E55" t="n">
-        <v>52440</v>
+        <v>52115</v>
       </c>
       <c r="F55" t="n">
-        <v>-145</v>
+        <v>-325</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0028</v>
+        <v>-0.0062</v>
       </c>
       <c r="H55" t="n">
-        <v>446</v>
+        <v>591</v>
       </c>
       <c r="I55" t="n">
-        <v>51379</v>
+        <v>51780</v>
       </c>
       <c r="J55" t="n">
-        <v>51998</v>
+        <v>51989.5</v>
       </c>
       <c r="K55" t="n">
-        <v>52245</v>
+        <v>52217</v>
       </c>
       <c r="L55" t="n">
-        <v>52492</v>
+        <v>52444.5</v>
       </c>
       <c r="M55" t="n">
-        <v>52925</v>
+        <v>52663</v>
       </c>
       <c r="N55" t="n">
-        <v>53358</v>
+        <v>52881.5</v>
       </c>
       <c r="O55" t="n">
-        <v>53419</v>
+        <v>53118</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5149,71 +5155,69 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>52499</v>
+        <v>52162</v>
       </c>
       <c r="C56" t="n">
-        <v>52499</v>
+        <v>52298</v>
       </c>
       <c r="D56" t="n">
-        <v>51908</v>
+        <v>51209</v>
       </c>
       <c r="E56" t="n">
-        <v>52115</v>
+        <v>51507</v>
       </c>
       <c r="F56" t="n">
-        <v>-325</v>
+        <v>-608</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0062</v>
+        <v>-0.0117</v>
       </c>
       <c r="H56" t="n">
-        <v>591</v>
+        <v>1089</v>
       </c>
       <c r="I56" t="n">
-        <v>51780</v>
+        <v>51317</v>
       </c>
       <c r="J56" t="n">
-        <v>51989.5</v>
+        <v>51479.75</v>
       </c>
       <c r="K56" t="n">
-        <v>52217</v>
+        <v>51819.5</v>
       </c>
       <c r="L56" t="n">
-        <v>52444.5</v>
+        <v>52159.25</v>
       </c>
       <c r="M56" t="n">
-        <v>52663</v>
+        <v>52410.5</v>
       </c>
       <c r="N56" t="n">
-        <v>52881.5</v>
+        <v>52661.75</v>
       </c>
       <c r="O56" t="n">
-        <v>53118</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v/>
+        <v>53090</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q56" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
@@ -5240,74 +5244,70 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>52162</v>
+        <v>51486</v>
       </c>
       <c r="C57" t="n">
-        <v>52298</v>
+        <v>52169</v>
       </c>
       <c r="D57" t="n">
-        <v>51209</v>
+        <v>51455</v>
       </c>
       <c r="E57" t="n">
-        <v>51507</v>
+        <v>51807</v>
       </c>
       <c r="F57" t="n">
-        <v>-608</v>
+        <v>300</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0117</v>
+        <v>0.0058</v>
       </c>
       <c r="H57" t="n">
-        <v>1089</v>
+        <v>714</v>
       </c>
       <c r="I57" t="n">
-        <v>51317</v>
+        <v>50120</v>
       </c>
       <c r="J57" t="n">
-        <v>51479.75</v>
+        <v>50294.75</v>
       </c>
       <c r="K57" t="n">
-        <v>51819.5</v>
+        <v>50962.5</v>
       </c>
       <c r="L57" t="n">
-        <v>52159.25</v>
+        <v>51630.25</v>
       </c>
       <c r="M57" t="n">
-        <v>52410.5</v>
+        <v>52051.5</v>
       </c>
       <c r="N57" t="n">
-        <v>52661.75</v>
+        <v>52472.75</v>
       </c>
       <c r="O57" t="n">
-        <v>53090</v>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
+        <v>53387</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
@@ -5319,55 +5319,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>51486</v>
+        <v>51800</v>
       </c>
       <c r="C58" t="n">
-        <v>52169</v>
+        <v>51957</v>
       </c>
       <c r="D58" t="n">
-        <v>51455</v>
+        <v>51576</v>
       </c>
       <c r="E58" t="n">
-        <v>51807</v>
+        <v>51761</v>
       </c>
       <c r="F58" t="n">
-        <v>300</v>
+        <v>-46</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0009</v>
       </c>
       <c r="H58" t="n">
-        <v>714</v>
+        <v>381</v>
       </c>
       <c r="I58" t="n">
-        <v>50120</v>
+        <v>50741</v>
       </c>
       <c r="J58" t="n">
-        <v>50294.75</v>
+        <v>51090.5</v>
       </c>
       <c r="K58" t="n">
-        <v>50962.5</v>
+        <v>51450</v>
       </c>
       <c r="L58" t="n">
-        <v>51630.25</v>
+        <v>51809.5</v>
       </c>
       <c r="M58" t="n">
-        <v>52051.5</v>
+        <v>52164</v>
       </c>
       <c r="N58" t="n">
-        <v>52472.75</v>
+        <v>52518.5</v>
       </c>
       <c r="O58" t="n">
-        <v>53387</v>
+        <v>52883</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5378,15 +5382,13 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5401,57 +5403,57 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>51800</v>
+        <v>52085</v>
       </c>
       <c r="C59" t="n">
-        <v>51957</v>
+        <v>52557</v>
       </c>
       <c r="D59" t="n">
-        <v>51576</v>
+        <v>52080</v>
       </c>
       <c r="E59" t="n">
-        <v>51761</v>
+        <v>52475</v>
       </c>
       <c r="F59" t="n">
-        <v>-46</v>
+        <v>714</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0138</v>
       </c>
       <c r="H59" t="n">
-        <v>381</v>
+        <v>477</v>
       </c>
       <c r="I59" t="n">
-        <v>50741</v>
+        <v>51195</v>
       </c>
       <c r="J59" t="n">
-        <v>51090.5</v>
+        <v>51377.25</v>
       </c>
       <c r="K59" t="n">
-        <v>51450</v>
+        <v>51570.5</v>
       </c>
       <c r="L59" t="n">
-        <v>51809.5</v>
+        <v>51763.75</v>
       </c>
       <c r="M59" t="n">
-        <v>52164</v>
+        <v>51951.5</v>
       </c>
       <c r="N59" t="n">
-        <v>52518.5</v>
+        <v>52139.25</v>
       </c>
       <c r="O59" t="n">
-        <v>52883</v>
+        <v>52338</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5462,78 +5464,80 @@
       <c r="R59" s="6" t="n">
         <v/>
       </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W59" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V59" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W59" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>52085</v>
+        <v>52470</v>
       </c>
       <c r="C60" t="n">
-        <v>52557</v>
+        <v>52844</v>
       </c>
       <c r="D60" t="n">
-        <v>52080</v>
+        <v>52125</v>
       </c>
       <c r="E60" t="n">
-        <v>52475</v>
+        <v>52279</v>
       </c>
       <c r="F60" t="n">
-        <v>714</v>
+        <v>-196</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0138</v>
+        <v>-0.0037</v>
       </c>
       <c r="H60" t="n">
-        <v>477</v>
+        <v>719</v>
       </c>
       <c r="I60" t="n">
-        <v>51195</v>
+        <v>51603</v>
       </c>
       <c r="J60" t="n">
-        <v>51377.25</v>
+        <v>52076.25</v>
       </c>
       <c r="K60" t="n">
-        <v>51570.5</v>
+        <v>52236.5</v>
       </c>
       <c r="L60" t="n">
-        <v>51763.75</v>
+        <v>52396.75</v>
       </c>
       <c r="M60" t="n">
-        <v>51951.5</v>
+        <v>52713.5</v>
       </c>
       <c r="N60" t="n">
-        <v>52139.25</v>
+        <v>53030.25</v>
       </c>
       <c r="O60" t="n">
-        <v>52338</v>
+        <v>53034</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5541,12 +5545,14 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T60" s="8" t="inlineStr">
@@ -5554,70 +5560,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V60" s="8" t="n">
+        <v/>
       </c>
       <c r="W60" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>52470</v>
+        <v>52255</v>
       </c>
       <c r="C61" t="n">
-        <v>52844</v>
+        <v>52371</v>
       </c>
       <c r="D61" t="n">
-        <v>52125</v>
+        <v>51844</v>
       </c>
       <c r="E61" t="n">
-        <v>52279</v>
+        <v>51873</v>
       </c>
       <c r="F61" t="n">
-        <v>-196</v>
+        <v>-406</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0037</v>
+        <v>-0.0078</v>
       </c>
       <c r="H61" t="n">
-        <v>719</v>
+        <v>527</v>
       </c>
       <c r="I61" t="n">
-        <v>51603</v>
+        <v>51406</v>
       </c>
       <c r="J61" t="n">
-        <v>52076.25</v>
+        <v>51457.25</v>
       </c>
       <c r="K61" t="n">
-        <v>52236.5</v>
+        <v>51919.5</v>
       </c>
       <c r="L61" t="n">
-        <v>52396.75</v>
+        <v>52381.75</v>
       </c>
       <c r="M61" t="n">
-        <v>52713.5</v>
+        <v>52638.5</v>
       </c>
       <c r="N61" t="n">
-        <v>53030.25</v>
+        <v>52895.25</v>
       </c>
       <c r="O61" t="n">
-        <v>53034</v>
+        <v>53563</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5635,10 +5641,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T61" s="8" t="n">
+        <v/>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5653,57 +5657,57 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>51878</v>
+        <v>51655</v>
       </c>
       <c r="C62" t="n">
-        <v>51900</v>
+        <v>51695</v>
       </c>
       <c r="D62" t="n">
-        <v>51878</v>
+        <v>51654</v>
       </c>
       <c r="E62" t="n">
-        <v>51889</v>
+        <v>51669</v>
       </c>
       <c r="F62" t="n">
-        <v>-390</v>
+        <v>-204</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0075</v>
+        <v>-0.0039</v>
       </c>
       <c r="H62" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="I62" t="n">
-        <v>51406</v>
+        <v>51317</v>
       </c>
       <c r="J62" t="n">
-        <v>51457.25</v>
+        <v>51228.75</v>
       </c>
       <c r="K62" t="n">
-        <v>51919.5</v>
+        <v>51609.5</v>
       </c>
       <c r="L62" t="n">
-        <v>52381.75</v>
+        <v>51990.25</v>
       </c>
       <c r="M62" t="n">
-        <v>52638.5</v>
+        <v>52136.5</v>
       </c>
       <c r="N62" t="n">
-        <v>52895.25</v>
+        <v>52282.75</v>
       </c>
       <c r="O62" t="n">
-        <v>53563</v>
+        <v>52898</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52554</v>
+        <v>52546</v>
       </c>
       <c r="C2" t="n">
-        <v>52763</v>
+        <v>53105</v>
       </c>
       <c r="D2" t="n">
-        <v>52383</v>
+        <v>52381</v>
       </c>
       <c r="E2" t="n">
-        <v>52670</v>
+        <v>52668</v>
       </c>
       <c r="F2" t="n">
-        <v>98</v>
+        <v>-2</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>380</v>
+        <v>724</v>
       </c>
       <c r="I2" t="n">
-        <v>51658</v>
+        <v>52003</v>
       </c>
       <c r="J2" t="n">
-        <v>52117.25</v>
+        <v>52338.5</v>
       </c>
       <c r="K2" t="n">
-        <v>52311.5</v>
+        <v>52480</v>
       </c>
       <c r="L2" t="n">
-        <v>52505.75</v>
+        <v>52621.5</v>
       </c>
       <c r="M2" t="n">
-        <v>52832.5</v>
+        <v>52860</v>
       </c>
       <c r="N2" t="n">
-        <v>53159.25</v>
+        <v>53098.5</v>
       </c>
       <c r="O2" t="n">
-        <v>53221</v>
+        <v>53143</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,21 +685,25 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -709,55 +713,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>52546</v>
+        <v>52640</v>
       </c>
       <c r="C3" t="n">
-        <v>53105</v>
+        <v>53218</v>
       </c>
       <c r="D3" t="n">
-        <v>52381</v>
+        <v>52551</v>
       </c>
       <c r="E3" t="n">
-        <v>52668</v>
+        <v>53183</v>
       </c>
       <c r="F3" t="n">
-        <v>-2</v>
+        <v>515</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0</v>
+        <v>0.0098</v>
       </c>
       <c r="H3" t="n">
-        <v>724</v>
+        <v>667</v>
       </c>
       <c r="I3" t="n">
-        <v>52003</v>
+        <v>51657</v>
       </c>
       <c r="J3" t="n">
-        <v>52338.5</v>
+        <v>51906.5</v>
       </c>
       <c r="K3" t="n">
-        <v>52480</v>
+        <v>52306</v>
       </c>
       <c r="L3" t="n">
-        <v>52621.5</v>
+        <v>52705.5</v>
       </c>
       <c r="M3" t="n">
-        <v>52860</v>
+        <v>53030</v>
       </c>
       <c r="N3" t="n">
-        <v>53098.5</v>
+        <v>53354.5</v>
       </c>
       <c r="O3" t="n">
-        <v>53143</v>
+        <v>53829</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -765,25 +773,21 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R3" s="6" t="n">
+        <v/>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -793,59 +797,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>52640</v>
+        <v>53230</v>
       </c>
       <c r="C4" t="n">
-        <v>53218</v>
+        <v>53421</v>
       </c>
       <c r="D4" t="n">
-        <v>52551</v>
+        <v>52962</v>
       </c>
       <c r="E4" t="n">
-        <v>53183</v>
+        <v>53372</v>
       </c>
       <c r="F4" t="n">
-        <v>515</v>
+        <v>189</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0036</v>
       </c>
       <c r="H4" t="n">
-        <v>667</v>
+        <v>459</v>
       </c>
       <c r="I4" t="n">
-        <v>51657</v>
+        <v>51884</v>
       </c>
       <c r="J4" t="n">
-        <v>51906.5</v>
+        <v>52665.25</v>
       </c>
       <c r="K4" t="n">
-        <v>52306</v>
+        <v>52849.5</v>
       </c>
       <c r="L4" t="n">
-        <v>52705.5</v>
+        <v>53033.75</v>
       </c>
       <c r="M4" t="n">
-        <v>53030</v>
+        <v>53516.5</v>
       </c>
       <c r="N4" t="n">
-        <v>53354.5</v>
+        <v>53999.25</v>
       </c>
       <c r="O4" t="n">
-        <v>53829</v>
+        <v>53885</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -882,50 +882,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53230</v>
+        <v>53405</v>
       </c>
       <c r="C5" t="n">
-        <v>53421</v>
+        <v>53656</v>
       </c>
       <c r="D5" t="n">
-        <v>52962</v>
+        <v>53076</v>
       </c>
       <c r="E5" t="n">
-        <v>53372</v>
+        <v>53197</v>
       </c>
       <c r="F5" t="n">
-        <v>189</v>
+        <v>-175</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0036</v>
+        <v>-0.0033</v>
       </c>
       <c r="H5" t="n">
-        <v>459</v>
+        <v>580</v>
       </c>
       <c r="I5" t="n">
-        <v>51884</v>
+        <v>52503</v>
       </c>
       <c r="J5" t="n">
-        <v>52665.25</v>
+        <v>53003.25</v>
       </c>
       <c r="K5" t="n">
-        <v>52849.5</v>
+        <v>53142.5</v>
       </c>
       <c r="L5" t="n">
-        <v>53033.75</v>
+        <v>53281.75</v>
       </c>
       <c r="M5" t="n">
-        <v>53516.5</v>
+        <v>53601.5</v>
       </c>
       <c r="N5" t="n">
-        <v>53999.25</v>
+        <v>53921.25</v>
       </c>
       <c r="O5" t="n">
-        <v>53885</v>
+        <v>53880</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -933,17 +933,19 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U5" s="8" t="n">
@@ -957,65 +959,73 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>53405</v>
+        <v>53166</v>
       </c>
       <c r="C6" t="n">
-        <v>53656</v>
+        <v>53207</v>
       </c>
       <c r="D6" t="n">
-        <v>53076</v>
+        <v>52343</v>
       </c>
       <c r="E6" t="n">
-        <v>53197</v>
+        <v>52624</v>
       </c>
       <c r="F6" t="n">
-        <v>-175</v>
+        <v>-573</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0108</v>
       </c>
       <c r="H6" t="n">
-        <v>580</v>
+        <v>864</v>
       </c>
       <c r="I6" t="n">
-        <v>52503</v>
+        <v>52496</v>
       </c>
       <c r="J6" t="n">
-        <v>53003.25</v>
+        <v>52532.5</v>
       </c>
       <c r="K6" t="n">
-        <v>53142.5</v>
+        <v>52907</v>
       </c>
       <c r="L6" t="n">
-        <v>53281.75</v>
+        <v>53281.5</v>
       </c>
       <c r="M6" t="n">
-        <v>53601.5</v>
+        <v>53487</v>
       </c>
       <c r="N6" t="n">
-        <v>53921.25</v>
+        <v>53692.5</v>
       </c>
       <c r="O6" t="n">
-        <v>53880</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
+        <v>54236</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S6" s="10" t="inlineStr">
@@ -1023,10 +1033,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1041,76 +1049,70 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>53166</v>
+        <v>52541</v>
       </c>
       <c r="C7" t="n">
-        <v>53207</v>
+        <v>52865</v>
       </c>
       <c r="D7" t="n">
-        <v>52343</v>
+        <v>52501</v>
       </c>
       <c r="E7" t="n">
-        <v>52624</v>
+        <v>52761</v>
       </c>
       <c r="F7" t="n">
-        <v>-573</v>
+        <v>137</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0108</v>
+        <v>0.0026</v>
       </c>
       <c r="H7" t="n">
-        <v>864</v>
+        <v>364</v>
       </c>
       <c r="I7" t="n">
-        <v>52496</v>
+        <v>51479</v>
       </c>
       <c r="J7" t="n">
-        <v>52532.5</v>
+        <v>51684.5</v>
       </c>
       <c r="K7" t="n">
-        <v>52907</v>
+        <v>52192</v>
       </c>
       <c r="L7" t="n">
-        <v>53281.5</v>
+        <v>52699.5</v>
       </c>
       <c r="M7" t="n">
-        <v>53487</v>
+        <v>53056</v>
       </c>
       <c r="N7" t="n">
-        <v>53692.5</v>
+        <v>53412.5</v>
       </c>
       <c r="O7" t="n">
-        <v>54236</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>54071</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1129,57 +1131,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52541</v>
+        <v>52753</v>
       </c>
       <c r="C8" t="n">
-        <v>52865</v>
+        <v>52992</v>
       </c>
       <c r="D8" t="n">
-        <v>52501</v>
+        <v>52506</v>
       </c>
       <c r="E8" t="n">
-        <v>52761</v>
+        <v>52906</v>
       </c>
       <c r="F8" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0027</v>
       </c>
       <c r="H8" t="n">
-        <v>364</v>
+        <v>486</v>
       </c>
       <c r="I8" t="n">
-        <v>51479</v>
+        <v>52137</v>
       </c>
       <c r="J8" t="n">
-        <v>51684.5</v>
+        <v>52436</v>
       </c>
       <c r="K8" t="n">
-        <v>52192</v>
+        <v>52579</v>
       </c>
       <c r="L8" t="n">
-        <v>52699.5</v>
+        <v>52722</v>
       </c>
       <c r="M8" t="n">
-        <v>53056</v>
+        <v>52943</v>
       </c>
       <c r="N8" t="n">
-        <v>53412.5</v>
+        <v>53164</v>
       </c>
       <c r="O8" t="n">
-        <v>54071</v>
+        <v>53229</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1187,16 +1189,20 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1209,59 +1215,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52753</v>
+        <v>52844</v>
       </c>
       <c r="C9" t="n">
-        <v>52992</v>
+        <v>53113</v>
       </c>
       <c r="D9" t="n">
-        <v>52506</v>
+        <v>52603</v>
       </c>
       <c r="E9" t="n">
-        <v>52906</v>
+        <v>52764</v>
       </c>
       <c r="F9" t="n">
-        <v>145</v>
+        <v>-142</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0027</v>
       </c>
       <c r="H9" t="n">
-        <v>486</v>
+        <v>510</v>
       </c>
       <c r="I9" t="n">
-        <v>52137</v>
+        <v>52020</v>
       </c>
       <c r="J9" t="n">
-        <v>52436</v>
+        <v>52498.5</v>
       </c>
       <c r="K9" t="n">
-        <v>52579</v>
+        <v>52663</v>
       </c>
       <c r="L9" t="n">
-        <v>52722</v>
+        <v>52827.5</v>
       </c>
       <c r="M9" t="n">
-        <v>52943</v>
+        <v>53149</v>
       </c>
       <c r="N9" t="n">
-        <v>53164</v>
+        <v>53470.5</v>
       </c>
       <c r="O9" t="n">
-        <v>53229</v>
+        <v>53478</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1274,15 +1276,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1295,55 +1295,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52844</v>
+        <v>52731</v>
       </c>
       <c r="C10" t="n">
-        <v>53113</v>
+        <v>52981</v>
       </c>
       <c r="D10" t="n">
-        <v>52603</v>
+        <v>52255</v>
       </c>
       <c r="E10" t="n">
-        <v>52764</v>
+        <v>52791</v>
       </c>
       <c r="F10" t="n">
-        <v>-142</v>
+        <v>27</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0005</v>
       </c>
       <c r="H10" t="n">
-        <v>510</v>
+        <v>726</v>
       </c>
       <c r="I10" t="n">
-        <v>52020</v>
+        <v>52093</v>
       </c>
       <c r="J10" t="n">
-        <v>52498.5</v>
+        <v>52207</v>
       </c>
       <c r="K10" t="n">
-        <v>52663</v>
+        <v>52509</v>
       </c>
       <c r="L10" t="n">
-        <v>52827.5</v>
+        <v>52811</v>
       </c>
       <c r="M10" t="n">
-        <v>53149</v>
+        <v>53019</v>
       </c>
       <c r="N10" t="n">
-        <v>53470.5</v>
+        <v>53227</v>
       </c>
       <c r="O10" t="n">
-        <v>53478</v>
+        <v>53623</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1377,57 +1381,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>52731</v>
+        <v>52792</v>
       </c>
       <c r="C11" t="n">
-        <v>52981</v>
+        <v>53088</v>
       </c>
       <c r="D11" t="n">
-        <v>52255</v>
+        <v>52680</v>
       </c>
       <c r="E11" t="n">
-        <v>52791</v>
+        <v>52900</v>
       </c>
       <c r="F11" t="n">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0021</v>
       </c>
       <c r="H11" t="n">
-        <v>726</v>
+        <v>408</v>
       </c>
       <c r="I11" t="n">
-        <v>52093</v>
+        <v>51529</v>
       </c>
       <c r="J11" t="n">
-        <v>52207</v>
+        <v>52151.5</v>
       </c>
       <c r="K11" t="n">
-        <v>52509</v>
+        <v>52428</v>
       </c>
       <c r="L11" t="n">
-        <v>52811</v>
+        <v>52704.5</v>
       </c>
       <c r="M11" t="n">
-        <v>53019</v>
+        <v>53154</v>
       </c>
       <c r="N11" t="n">
-        <v>53227</v>
+        <v>53603.5</v>
       </c>
       <c r="O11" t="n">
-        <v>53623</v>
+        <v>53707</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1435,14 +1439,12 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1459,59 +1461,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52792</v>
+        <v>52919</v>
       </c>
       <c r="C12" t="n">
-        <v>53088</v>
+        <v>53108</v>
       </c>
       <c r="D12" t="n">
-        <v>52680</v>
+        <v>52607</v>
       </c>
       <c r="E12" t="n">
-        <v>52900</v>
+        <v>52786</v>
       </c>
       <c r="F12" t="n">
-        <v>109</v>
+        <v>-114</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0022</v>
       </c>
       <c r="H12" t="n">
-        <v>408</v>
+        <v>501</v>
       </c>
       <c r="I12" t="n">
-        <v>51529</v>
+        <v>52272</v>
       </c>
       <c r="J12" t="n">
-        <v>52151.5</v>
+        <v>52500</v>
       </c>
       <c r="K12" t="n">
-        <v>52428</v>
+        <v>52696</v>
       </c>
       <c r="L12" t="n">
-        <v>52704.5</v>
+        <v>52892</v>
       </c>
       <c r="M12" t="n">
-        <v>53154</v>
+        <v>53104</v>
       </c>
       <c r="N12" t="n">
-        <v>53603.5</v>
+        <v>53316</v>
       </c>
       <c r="O12" t="n">
-        <v>53707</v>
+        <v>53496</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1519,16 +1517,20 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1541,65 +1543,71 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>52919</v>
+        <v>52778</v>
       </c>
       <c r="C13" t="n">
-        <v>53108</v>
+        <v>52835</v>
       </c>
       <c r="D13" t="n">
-        <v>52607</v>
+        <v>52174</v>
       </c>
       <c r="E13" t="n">
-        <v>52786</v>
+        <v>52375</v>
       </c>
       <c r="F13" t="n">
-        <v>-114</v>
+        <v>-411</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0078</v>
       </c>
       <c r="H13" t="n">
-        <v>501</v>
+        <v>661</v>
       </c>
       <c r="I13" t="n">
-        <v>52272</v>
+        <v>52106</v>
       </c>
       <c r="J13" t="n">
-        <v>52500</v>
+        <v>52249.25</v>
       </c>
       <c r="K13" t="n">
-        <v>52696</v>
+        <v>52535.5</v>
       </c>
       <c r="L13" t="n">
-        <v>52892</v>
+        <v>52821.75</v>
       </c>
       <c r="M13" t="n">
-        <v>53104</v>
+        <v>53036.5</v>
       </c>
       <c r="N13" t="n">
-        <v>53316</v>
+        <v>53251.25</v>
       </c>
       <c r="O13" t="n">
-        <v>53496</v>
+        <v>53609</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
@@ -1607,10 +1615,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1625,69 +1631,67 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>52778</v>
+        <v>52300</v>
       </c>
       <c r="C14" t="n">
-        <v>52835</v>
+        <v>52633</v>
       </c>
       <c r="D14" t="n">
-        <v>52174</v>
+        <v>51999</v>
       </c>
       <c r="E14" t="n">
-        <v>52375</v>
+        <v>52073</v>
       </c>
       <c r="F14" t="n">
-        <v>-411</v>
+        <v>-302</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0078</v>
+        <v>-0.0058</v>
       </c>
       <c r="H14" t="n">
-        <v>661</v>
+        <v>634</v>
       </c>
       <c r="I14" t="n">
-        <v>52106</v>
+        <v>51513</v>
       </c>
       <c r="J14" t="n">
-        <v>52249.25</v>
+        <v>51649.25</v>
       </c>
       <c r="K14" t="n">
-        <v>52535.5</v>
+        <v>52044.5</v>
       </c>
       <c r="L14" t="n">
-        <v>52821.75</v>
+        <v>52439.75</v>
       </c>
       <c r="M14" t="n">
-        <v>53036.5</v>
+        <v>52705.5</v>
       </c>
       <c r="N14" t="n">
-        <v>53251.25</v>
+        <v>52971.25</v>
       </c>
       <c r="O14" t="n">
-        <v>53609</v>
+        <v>53496</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S14" s="10" t="inlineStr">
@@ -1718,50 +1722,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52300</v>
+        <v>52091</v>
       </c>
       <c r="C15" t="n">
-        <v>52633</v>
+        <v>52590</v>
       </c>
       <c r="D15" t="n">
-        <v>51999</v>
+        <v>52035</v>
       </c>
       <c r="E15" t="n">
-        <v>52073</v>
+        <v>52443</v>
       </c>
       <c r="F15" t="n">
-        <v>-302</v>
+        <v>370</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.0071</v>
       </c>
       <c r="H15" t="n">
-        <v>634</v>
+        <v>555</v>
       </c>
       <c r="I15" t="n">
-        <v>51513</v>
+        <v>51365</v>
       </c>
       <c r="J15" t="n">
-        <v>51649.25</v>
+        <v>51317.5</v>
       </c>
       <c r="K15" t="n">
-        <v>52044.5</v>
+        <v>51756</v>
       </c>
       <c r="L15" t="n">
-        <v>52439.75</v>
+        <v>52194.5</v>
       </c>
       <c r="M15" t="n">
-        <v>52705.5</v>
+        <v>52390</v>
       </c>
       <c r="N15" t="n">
-        <v>52971.25</v>
+        <v>52585.5</v>
       </c>
       <c r="O15" t="n">
-        <v>53496</v>
+        <v>53267</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1769,21 +1773,23 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1795,57 +1801,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>52091</v>
+        <v>52431</v>
       </c>
       <c r="C16" t="n">
-        <v>52590</v>
+        <v>52721</v>
       </c>
       <c r="D16" t="n">
-        <v>52035</v>
+        <v>52262</v>
       </c>
       <c r="E16" t="n">
-        <v>52443</v>
+        <v>52449</v>
       </c>
       <c r="F16" t="n">
-        <v>370</v>
+        <v>6</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0001</v>
       </c>
       <c r="H16" t="n">
-        <v>555</v>
+        <v>459</v>
       </c>
       <c r="I16" t="n">
-        <v>51365</v>
+        <v>51480</v>
       </c>
       <c r="J16" t="n">
-        <v>51317.5</v>
+        <v>51953.25</v>
       </c>
       <c r="K16" t="n">
-        <v>51756</v>
+        <v>52165.5</v>
       </c>
       <c r="L16" t="n">
-        <v>52194.5</v>
+        <v>52377.75</v>
       </c>
       <c r="M16" t="n">
-        <v>52390</v>
+        <v>52720.5</v>
       </c>
       <c r="N16" t="n">
-        <v>52585.5</v>
+        <v>53063.25</v>
       </c>
       <c r="O16" t="n">
-        <v>53267</v>
+        <v>53145</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1858,19 +1864,17 @@
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
@@ -1879,88 +1883,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52431</v>
+        <v>52430</v>
       </c>
       <c r="C17" t="n">
-        <v>52721</v>
+        <v>52515</v>
       </c>
       <c r="D17" t="n">
-        <v>52262</v>
+        <v>51720</v>
       </c>
       <c r="E17" t="n">
-        <v>52449</v>
+        <v>51894</v>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>-555</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0106</v>
       </c>
       <c r="H17" t="n">
-        <v>459</v>
+        <v>795</v>
       </c>
       <c r="I17" t="n">
-        <v>51480</v>
+        <v>51803</v>
       </c>
       <c r="J17" t="n">
-        <v>51953.25</v>
+        <v>51968.75</v>
       </c>
       <c r="K17" t="n">
-        <v>52165.5</v>
+        <v>52219.5</v>
       </c>
       <c r="L17" t="n">
-        <v>52377.75</v>
+        <v>52470.25</v>
       </c>
       <c r="M17" t="n">
-        <v>52720.5</v>
+        <v>52678.5</v>
       </c>
       <c r="N17" t="n">
-        <v>53063.25</v>
+        <v>52886.75</v>
       </c>
       <c r="O17" t="n">
-        <v>53145</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
+        <v>53180</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
       <c r="U17" s="8" t="n">
         <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W17" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
@@ -1968,74 +1972,70 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52430</v>
+        <v>51920</v>
       </c>
       <c r="C18" t="n">
-        <v>52515</v>
+        <v>52314</v>
       </c>
       <c r="D18" t="n">
-        <v>51720</v>
+        <v>51846</v>
       </c>
       <c r="E18" t="n">
-        <v>51894</v>
+        <v>52124</v>
       </c>
       <c r="F18" t="n">
-        <v>-555</v>
+        <v>230</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0044</v>
       </c>
       <c r="H18" t="n">
-        <v>795</v>
+        <v>468</v>
       </c>
       <c r="I18" t="n">
-        <v>51803</v>
+        <v>50925</v>
       </c>
       <c r="J18" t="n">
-        <v>51968.75</v>
+        <v>50987.25</v>
       </c>
       <c r="K18" t="n">
-        <v>52219.5</v>
+        <v>51496.5</v>
       </c>
       <c r="L18" t="n">
-        <v>52470.25</v>
+        <v>52005.75</v>
       </c>
       <c r="M18" t="n">
-        <v>52678.5</v>
+        <v>52291.5</v>
       </c>
       <c r="N18" t="n">
-        <v>52886.75</v>
+        <v>52577.25</v>
       </c>
       <c r="O18" t="n">
-        <v>53180</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
+        <v>53310</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
@@ -2047,55 +2047,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>51920</v>
+        <v>52299</v>
       </c>
       <c r="C19" t="n">
-        <v>52314</v>
+        <v>52790</v>
       </c>
       <c r="D19" t="n">
-        <v>51846</v>
+        <v>52173</v>
       </c>
       <c r="E19" t="n">
-        <v>52124</v>
+        <v>52382</v>
       </c>
       <c r="F19" t="n">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0049</v>
       </c>
       <c r="H19" t="n">
-        <v>468</v>
+        <v>617</v>
       </c>
       <c r="I19" t="n">
-        <v>50925</v>
+        <v>51378</v>
       </c>
       <c r="J19" t="n">
-        <v>50987.25</v>
+        <v>51678</v>
       </c>
       <c r="K19" t="n">
-        <v>51496.5</v>
+        <v>51890</v>
       </c>
       <c r="L19" t="n">
-        <v>52005.75</v>
+        <v>52102</v>
       </c>
       <c r="M19" t="n">
-        <v>52291.5</v>
+        <v>52358</v>
       </c>
       <c r="N19" t="n">
-        <v>52577.25</v>
+        <v>52614</v>
       </c>
       <c r="O19" t="n">
-        <v>53310</v>
+        <v>52782</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2108,19 +2112,23 @@
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W19" s="11" t="inlineStr">
         <is>
@@ -2129,57 +2137,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>52299</v>
+        <v>52405</v>
       </c>
       <c r="C20" t="n">
-        <v>52790</v>
+        <v>53105</v>
       </c>
       <c r="D20" t="n">
-        <v>52173</v>
+        <v>52290</v>
       </c>
       <c r="E20" t="n">
-        <v>52382</v>
+        <v>52944</v>
       </c>
       <c r="F20" t="n">
-        <v>258</v>
+        <v>562</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0107</v>
       </c>
       <c r="H20" t="n">
-        <v>617</v>
+        <v>815</v>
       </c>
       <c r="I20" t="n">
-        <v>51378</v>
+        <v>51556</v>
       </c>
       <c r="J20" t="n">
-        <v>51678</v>
+        <v>51715.25</v>
       </c>
       <c r="K20" t="n">
-        <v>51890</v>
+        <v>52073.5</v>
       </c>
       <c r="L20" t="n">
-        <v>52102</v>
+        <v>52431.75</v>
       </c>
       <c r="M20" t="n">
-        <v>52358</v>
+        <v>52690.5</v>
       </c>
       <c r="N20" t="n">
-        <v>52614</v>
+        <v>52949.25</v>
       </c>
       <c r="O20" t="n">
-        <v>52782</v>
+        <v>53407</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2197,18 +2205,16 @@
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V20" s="8" t="n">
+        <v/>
       </c>
       <c r="W20" s="11" t="inlineStr">
         <is>
@@ -2224,74 +2230,76 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>52405</v>
+        <v>52915</v>
       </c>
       <c r="C21" t="n">
-        <v>53105</v>
+        <v>53033</v>
       </c>
       <c r="D21" t="n">
-        <v>52290</v>
+        <v>51630</v>
       </c>
       <c r="E21" t="n">
-        <v>52944</v>
+        <v>51765</v>
       </c>
       <c r="F21" t="n">
-        <v>562</v>
+        <v>-1179</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0223</v>
       </c>
       <c r="H21" t="n">
-        <v>815</v>
+        <v>1403</v>
       </c>
       <c r="I21" t="n">
-        <v>51556</v>
+        <v>51475</v>
       </c>
       <c r="J21" t="n">
-        <v>51715.25</v>
+        <v>52252.25</v>
       </c>
       <c r="K21" t="n">
-        <v>52073.5</v>
+        <v>52536.5</v>
       </c>
       <c r="L21" t="n">
-        <v>52431.75</v>
+        <v>52820.75</v>
       </c>
       <c r="M21" t="n">
-        <v>52690.5</v>
+        <v>53351.5</v>
       </c>
       <c r="N21" t="n">
-        <v>52949.25</v>
+        <v>53882.25</v>
       </c>
       <c r="O21" t="n">
-        <v>53407</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
+        <v>53920</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2301,83 +2309,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>52915</v>
+        <v>51759</v>
       </c>
       <c r="C22" t="n">
-        <v>53033</v>
+        <v>52484</v>
       </c>
       <c r="D22" t="n">
-        <v>51630</v>
+        <v>51732</v>
       </c>
       <c r="E22" t="n">
-        <v>51765</v>
+        <v>52380</v>
       </c>
       <c r="F22" t="n">
-        <v>-1179</v>
+        <v>615</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0119</v>
       </c>
       <c r="H22" t="n">
-        <v>1403</v>
+        <v>752</v>
       </c>
       <c r="I22" t="n">
-        <v>51475</v>
+        <v>50227</v>
       </c>
       <c r="J22" t="n">
-        <v>52252.25</v>
+        <v>50078.75</v>
       </c>
       <c r="K22" t="n">
-        <v>52536.5</v>
+        <v>51063.5</v>
       </c>
       <c r="L22" t="n">
-        <v>52820.75</v>
+        <v>52048.25</v>
       </c>
       <c r="M22" t="n">
-        <v>53351.5</v>
+        <v>52466.5</v>
       </c>
       <c r="N22" t="n">
-        <v>53882.25</v>
+        <v>52884.75</v>
       </c>
       <c r="O22" t="n">
-        <v>53920</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
+        <v>54436</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
       <c r="U22" s="8" t="n">
         <v/>
       </c>
@@ -2389,55 +2389,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>51759</v>
+        <v>52395</v>
       </c>
       <c r="C23" t="n">
-        <v>52484</v>
+        <v>52772</v>
       </c>
       <c r="D23" t="n">
-        <v>51732</v>
+        <v>52124</v>
       </c>
       <c r="E23" t="n">
-        <v>52380</v>
+        <v>52635</v>
       </c>
       <c r="F23" t="n">
-        <v>615</v>
+        <v>255</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0119</v>
+        <v>0.0049</v>
       </c>
       <c r="H23" t="n">
-        <v>752</v>
+        <v>648</v>
       </c>
       <c r="I23" t="n">
-        <v>50227</v>
+        <v>50980</v>
       </c>
       <c r="J23" t="n">
-        <v>50078.75</v>
+        <v>51764</v>
       </c>
       <c r="K23" t="n">
-        <v>51063.5</v>
+        <v>52004</v>
       </c>
       <c r="L23" t="n">
-        <v>52048.25</v>
+        <v>52244</v>
       </c>
       <c r="M23" t="n">
-        <v>52466.5</v>
+        <v>52756</v>
       </c>
       <c r="N23" t="n">
-        <v>52884.75</v>
+        <v>53268</v>
       </c>
       <c r="O23" t="n">
-        <v>54436</v>
+        <v>53236</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2471,57 +2475,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>52395</v>
+        <v>52780</v>
       </c>
       <c r="C24" t="n">
-        <v>52772</v>
+        <v>53414</v>
       </c>
       <c r="D24" t="n">
-        <v>52124</v>
+        <v>52777</v>
       </c>
       <c r="E24" t="n">
-        <v>52635</v>
+        <v>53334</v>
       </c>
       <c r="F24" t="n">
-        <v>255</v>
+        <v>699</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0133</v>
       </c>
       <c r="H24" t="n">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="I24" t="n">
-        <v>50980</v>
+        <v>51476</v>
       </c>
       <c r="J24" t="n">
-        <v>51764</v>
+        <v>52080.5</v>
       </c>
       <c r="K24" t="n">
-        <v>52004</v>
+        <v>52311</v>
       </c>
       <c r="L24" t="n">
-        <v>52244</v>
+        <v>52541.5</v>
       </c>
       <c r="M24" t="n">
-        <v>52756</v>
+        <v>52959</v>
       </c>
       <c r="N24" t="n">
-        <v>53268</v>
+        <v>53376.5</v>
       </c>
       <c r="O24" t="n">
-        <v>53236</v>
+        <v>53420</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2539,11 +2543,13 @@
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2562,50 +2568,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>52780</v>
+        <v>53381</v>
       </c>
       <c r="C25" t="n">
-        <v>53414</v>
+        <v>54423</v>
       </c>
       <c r="D25" t="n">
-        <v>52777</v>
+        <v>53267</v>
       </c>
       <c r="E25" t="n">
-        <v>53334</v>
+        <v>54268</v>
       </c>
       <c r="F25" t="n">
-        <v>699</v>
+        <v>934</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0175</v>
       </c>
       <c r="H25" t="n">
-        <v>637</v>
+        <v>1156</v>
       </c>
       <c r="I25" t="n">
-        <v>51476</v>
+        <v>52140</v>
       </c>
       <c r="J25" t="n">
-        <v>52080.5</v>
+        <v>52816.25</v>
       </c>
       <c r="K25" t="n">
-        <v>52311</v>
+        <v>53015.5</v>
       </c>
       <c r="L25" t="n">
-        <v>52541.5</v>
+        <v>53214.75</v>
       </c>
       <c r="M25" t="n">
-        <v>52959</v>
+        <v>53652.5</v>
       </c>
       <c r="N25" t="n">
-        <v>53376.5</v>
+        <v>54090.25</v>
       </c>
       <c r="O25" t="n">
-        <v>53420</v>
+        <v>54051</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2631,67 +2637,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W25" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W25" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>53381</v>
+        <v>54369</v>
       </c>
       <c r="C26" t="n">
-        <v>54423</v>
+        <v>54884</v>
       </c>
       <c r="D26" t="n">
-        <v>53267</v>
+        <v>54342</v>
       </c>
       <c r="E26" t="n">
-        <v>54268</v>
+        <v>54494</v>
       </c>
       <c r="F26" t="n">
-        <v>934</v>
+        <v>226</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0042</v>
       </c>
       <c r="H26" t="n">
-        <v>1156</v>
+        <v>542</v>
       </c>
       <c r="I26" t="n">
-        <v>52140</v>
+        <v>52111</v>
       </c>
       <c r="J26" t="n">
-        <v>52816.25</v>
+        <v>53323.5</v>
       </c>
       <c r="K26" t="n">
-        <v>53015.5</v>
+        <v>53690</v>
       </c>
       <c r="L26" t="n">
-        <v>53214.75</v>
+        <v>54056.5</v>
       </c>
       <c r="M26" t="n">
-        <v>53652.5</v>
+        <v>54846</v>
       </c>
       <c r="N26" t="n">
-        <v>54090.25</v>
+        <v>55635.5</v>
       </c>
       <c r="O26" t="n">
-        <v>54051</v>
+        <v>55579</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2709,18 +2713,14 @@
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
@@ -2732,70 +2732,72 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>54369</v>
+        <v>54555</v>
       </c>
       <c r="C27" t="n">
-        <v>54884</v>
+        <v>54678</v>
       </c>
       <c r="D27" t="n">
-        <v>54342</v>
+        <v>53952</v>
       </c>
       <c r="E27" t="n">
-        <v>54494</v>
+        <v>54013</v>
       </c>
       <c r="F27" t="n">
-        <v>226</v>
+        <v>-481</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>542</v>
+        <v>726</v>
       </c>
       <c r="I27" t="n">
-        <v>52111</v>
+        <v>53800</v>
       </c>
       <c r="J27" t="n">
-        <v>53323.5</v>
+        <v>53892.5</v>
       </c>
       <c r="K27" t="n">
-        <v>53690</v>
+        <v>54223</v>
       </c>
       <c r="L27" t="n">
-        <v>54056.5</v>
+        <v>54553.5</v>
       </c>
       <c r="M27" t="n">
-        <v>54846</v>
+        <v>54765</v>
       </c>
       <c r="N27" t="n">
-        <v>55635.5</v>
+        <v>54976.5</v>
       </c>
       <c r="O27" t="n">
-        <v>55579</v>
+        <v>55426</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
+      <c r="Q27" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
       <c r="U27" s="8" t="n">
         <v/>
       </c>
@@ -2807,72 +2809,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>54555</v>
+        <v>54040</v>
       </c>
       <c r="C28" t="n">
-        <v>54678</v>
+        <v>54202</v>
       </c>
       <c r="D28" t="n">
-        <v>53952</v>
+        <v>53879</v>
       </c>
       <c r="E28" t="n">
-        <v>54013</v>
+        <v>54152</v>
       </c>
       <c r="F28" t="n">
-        <v>-481</v>
+        <v>139</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0026</v>
       </c>
       <c r="H28" t="n">
-        <v>726</v>
+        <v>323</v>
       </c>
       <c r="I28" t="n">
-        <v>53800</v>
+        <v>53226</v>
       </c>
       <c r="J28" t="n">
-        <v>53892.5</v>
+        <v>53136</v>
       </c>
       <c r="K28" t="n">
-        <v>54223</v>
+        <v>53650</v>
       </c>
       <c r="L28" t="n">
-        <v>54553.5</v>
+        <v>54164</v>
       </c>
       <c r="M28" t="n">
-        <v>54765</v>
+        <v>54376</v>
       </c>
       <c r="N28" t="n">
-        <v>54976.5</v>
+        <v>54588</v>
       </c>
       <c r="O28" t="n">
-        <v>55426</v>
+        <v>55404</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2891,57 +2893,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>54040</v>
+        <v>54133</v>
       </c>
       <c r="C29" t="n">
-        <v>54202</v>
+        <v>54170</v>
       </c>
       <c r="D29" t="n">
-        <v>53879</v>
+        <v>53952</v>
       </c>
       <c r="E29" t="n">
-        <v>54152</v>
+        <v>54063</v>
       </c>
       <c r="F29" t="n">
-        <v>139</v>
+        <v>-89</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0016</v>
       </c>
       <c r="H29" t="n">
-        <v>323</v>
+        <v>218</v>
       </c>
       <c r="I29" t="n">
-        <v>53226</v>
+        <v>53556</v>
       </c>
       <c r="J29" t="n">
-        <v>53136</v>
+        <v>53884.75</v>
       </c>
       <c r="K29" t="n">
-        <v>53650</v>
+        <v>53990.5</v>
       </c>
       <c r="L29" t="n">
-        <v>54164</v>
+        <v>54096.25</v>
       </c>
       <c r="M29" t="n">
-        <v>54376</v>
+        <v>54313.5</v>
       </c>
       <c r="N29" t="n">
-        <v>54588</v>
+        <v>54530.75</v>
       </c>
       <c r="O29" t="n">
-        <v>55404</v>
+        <v>54525</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2949,8 +2951,10 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
@@ -2980,56 +2984,58 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>54133</v>
+        <v>54049</v>
       </c>
       <c r="C30" t="n">
-        <v>54170</v>
+        <v>54336</v>
       </c>
       <c r="D30" t="n">
-        <v>53952</v>
+        <v>53855</v>
       </c>
       <c r="E30" t="n">
-        <v>54063</v>
+        <v>53880</v>
       </c>
       <c r="F30" t="n">
-        <v>-89</v>
+        <v>-183</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0034</v>
       </c>
       <c r="H30" t="n">
-        <v>218</v>
+        <v>481</v>
       </c>
       <c r="I30" t="n">
-        <v>53556</v>
+        <v>53734</v>
       </c>
       <c r="J30" t="n">
-        <v>53884.75</v>
+        <v>53846</v>
       </c>
       <c r="K30" t="n">
-        <v>53990.5</v>
+        <v>53954</v>
       </c>
       <c r="L30" t="n">
-        <v>54096.25</v>
+        <v>54062</v>
       </c>
       <c r="M30" t="n">
-        <v>54313.5</v>
+        <v>54172</v>
       </c>
       <c r="N30" t="n">
-        <v>54530.75</v>
+        <v>54282</v>
       </c>
       <c r="O30" t="n">
-        <v>54525</v>
+        <v>54388</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
@@ -3038,14 +3044,18 @@
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3064,78 +3074,72 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>54049</v>
+        <v>53903</v>
       </c>
       <c r="C31" t="n">
-        <v>54336</v>
+        <v>54150</v>
       </c>
       <c r="D31" t="n">
-        <v>53855</v>
+        <v>53830</v>
       </c>
       <c r="E31" t="n">
-        <v>53880</v>
+        <v>53871</v>
       </c>
       <c r="F31" t="n">
-        <v>-183</v>
+        <v>-9</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0002</v>
       </c>
       <c r="H31" t="n">
-        <v>481</v>
+        <v>320</v>
       </c>
       <c r="I31" t="n">
-        <v>53734</v>
+        <v>53374</v>
       </c>
       <c r="J31" t="n">
-        <v>53846</v>
+        <v>53291.25</v>
       </c>
       <c r="K31" t="n">
-        <v>53954</v>
+        <v>53639.5</v>
       </c>
       <c r="L31" t="n">
-        <v>54062</v>
+        <v>53987.75</v>
       </c>
       <c r="M31" t="n">
-        <v>54172</v>
+        <v>54120.5</v>
       </c>
       <c r="N31" t="n">
-        <v>54282</v>
+        <v>54253.25</v>
       </c>
       <c r="O31" t="n">
-        <v>54388</v>
+        <v>54817</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3147,57 +3151,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>53903</v>
+        <v>53905</v>
       </c>
       <c r="C32" t="n">
-        <v>54150</v>
+        <v>54149</v>
       </c>
       <c r="D32" t="n">
-        <v>53830</v>
+        <v>53715</v>
       </c>
       <c r="E32" t="n">
-        <v>53871</v>
+        <v>53935</v>
       </c>
       <c r="F32" t="n">
-        <v>-9</v>
+        <v>64</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0012</v>
       </c>
       <c r="H32" t="n">
-        <v>320</v>
+        <v>434</v>
       </c>
       <c r="I32" t="n">
-        <v>53374</v>
+        <v>53510</v>
       </c>
       <c r="J32" t="n">
-        <v>53291.25</v>
+        <v>53491.5</v>
       </c>
       <c r="K32" t="n">
-        <v>53639.5</v>
+        <v>53711</v>
       </c>
       <c r="L32" t="n">
-        <v>53987.75</v>
+        <v>53930.5</v>
       </c>
       <c r="M32" t="n">
-        <v>54120.5</v>
+        <v>54031</v>
       </c>
       <c r="N32" t="n">
-        <v>54253.25</v>
+        <v>54131.5</v>
       </c>
       <c r="O32" t="n">
-        <v>54817</v>
+        <v>54470</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3208,9 +3212,9 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
@@ -3218,8 +3222,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3231,57 +3237,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>53905</v>
+        <v>53961</v>
       </c>
       <c r="C33" t="n">
-        <v>54149</v>
+        <v>53999</v>
       </c>
       <c r="D33" t="n">
-        <v>53715</v>
+        <v>53745</v>
       </c>
       <c r="E33" t="n">
-        <v>53935</v>
+        <v>53807</v>
       </c>
       <c r="F33" t="n">
-        <v>64</v>
+        <v>-128</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0024</v>
       </c>
       <c r="H33" t="n">
-        <v>434</v>
+        <v>254</v>
       </c>
       <c r="I33" t="n">
-        <v>53510</v>
+        <v>53281</v>
       </c>
       <c r="J33" t="n">
-        <v>53491.5</v>
+        <v>53502.5</v>
       </c>
       <c r="K33" t="n">
-        <v>53711</v>
+        <v>53718</v>
       </c>
       <c r="L33" t="n">
-        <v>53930.5</v>
+        <v>53933.5</v>
       </c>
       <c r="M33" t="n">
-        <v>54031</v>
+        <v>54152</v>
       </c>
       <c r="N33" t="n">
-        <v>54131.5</v>
+        <v>54370.5</v>
       </c>
       <c r="O33" t="n">
-        <v>54470</v>
+        <v>54583</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3289,23 +3295,21 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3324,60 +3328,64 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>53961</v>
+        <v>53790</v>
       </c>
       <c r="C34" t="n">
-        <v>53999</v>
+        <v>53840</v>
       </c>
       <c r="D34" t="n">
-        <v>53745</v>
+        <v>53464</v>
       </c>
       <c r="E34" t="n">
-        <v>53807</v>
+        <v>53544</v>
       </c>
       <c r="F34" t="n">
-        <v>-128</v>
+        <v>-263</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0049</v>
       </c>
       <c r="H34" t="n">
-        <v>254</v>
+        <v>376</v>
       </c>
       <c r="I34" t="n">
-        <v>53281</v>
+        <v>53491</v>
       </c>
       <c r="J34" t="n">
-        <v>53502.5</v>
+        <v>53520.5</v>
       </c>
       <c r="K34" t="n">
-        <v>53718</v>
+        <v>53680</v>
       </c>
       <c r="L34" t="n">
-        <v>53933.5</v>
+        <v>53839.5</v>
       </c>
       <c r="M34" t="n">
-        <v>54152</v>
+        <v>53934</v>
       </c>
       <c r="N34" t="n">
-        <v>54370.5</v>
+        <v>54028.5</v>
       </c>
       <c r="O34" t="n">
-        <v>54583</v>
-      </c>
-      <c r="P34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
+        <v>54253</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
@@ -3401,71 +3409,67 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>53790</v>
+        <v>53501</v>
       </c>
       <c r="C35" t="n">
-        <v>53840</v>
+        <v>53594</v>
       </c>
       <c r="D35" t="n">
-        <v>53464</v>
+        <v>53311</v>
       </c>
       <c r="E35" t="n">
-        <v>53544</v>
+        <v>53403</v>
       </c>
       <c r="F35" t="n">
-        <v>-263</v>
+        <v>-141</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0026</v>
       </c>
       <c r="H35" t="n">
-        <v>376</v>
+        <v>283</v>
       </c>
       <c r="I35" t="n">
-        <v>53491</v>
+        <v>53088</v>
       </c>
       <c r="J35" t="n">
-        <v>53520.5</v>
+        <v>53114</v>
       </c>
       <c r="K35" t="n">
-        <v>53680</v>
+        <v>53356</v>
       </c>
       <c r="L35" t="n">
-        <v>53839.5</v>
+        <v>53598</v>
       </c>
       <c r="M35" t="n">
-        <v>53934</v>
+        <v>53732</v>
       </c>
       <c r="N35" t="n">
-        <v>54028.5</v>
+        <v>53866</v>
       </c>
       <c r="O35" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q35" s="6" t="inlineStr">
+        <v>54216</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
@@ -3496,50 +3500,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>53501</v>
+        <v>53408</v>
       </c>
       <c r="C36" t="n">
-        <v>53594</v>
+        <v>53780</v>
       </c>
       <c r="D36" t="n">
-        <v>53311</v>
+        <v>53337</v>
       </c>
       <c r="E36" t="n">
-        <v>53403</v>
+        <v>53530</v>
       </c>
       <c r="F36" t="n">
-        <v>-141</v>
+        <v>127</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0026</v>
+        <v>0.0024</v>
       </c>
       <c r="H36" t="n">
-        <v>283</v>
+        <v>443</v>
       </c>
       <c r="I36" t="n">
-        <v>53088</v>
+        <v>53028</v>
       </c>
       <c r="J36" t="n">
-        <v>53114</v>
+        <v>53095.25</v>
       </c>
       <c r="K36" t="n">
-        <v>53356</v>
+        <v>53261.5</v>
       </c>
       <c r="L36" t="n">
-        <v>53598</v>
+        <v>53427.75</v>
       </c>
       <c r="M36" t="n">
-        <v>53732</v>
+        <v>53544.5</v>
       </c>
       <c r="N36" t="n">
-        <v>53866</v>
+        <v>53661.25</v>
       </c>
       <c r="O36" t="n">
-        <v>54216</v>
+        <v>53877</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3547,21 +3551,23 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3571,90 +3577,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>53408</v>
+        <v>53529</v>
       </c>
       <c r="C37" t="n">
-        <v>53780</v>
+        <v>53589</v>
       </c>
       <c r="D37" t="n">
-        <v>53337</v>
+        <v>52812</v>
       </c>
       <c r="E37" t="n">
-        <v>53530</v>
+        <v>52849</v>
       </c>
       <c r="F37" t="n">
-        <v>127</v>
+        <v>-681</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0127</v>
       </c>
       <c r="H37" t="n">
-        <v>443</v>
+        <v>777</v>
       </c>
       <c r="I37" t="n">
-        <v>53028</v>
+        <v>52894</v>
       </c>
       <c r="J37" t="n">
-        <v>53095.25</v>
+        <v>53072.75</v>
       </c>
       <c r="K37" t="n">
-        <v>53261.5</v>
+        <v>53308.5</v>
       </c>
       <c r="L37" t="n">
-        <v>53427.75</v>
+        <v>53544.25</v>
       </c>
       <c r="M37" t="n">
-        <v>53544.5</v>
+        <v>53751.5</v>
       </c>
       <c r="N37" t="n">
-        <v>53661.25</v>
+        <v>53958.75</v>
       </c>
       <c r="O37" t="n">
-        <v>53877</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
+        <v>54223</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U37" s="8" t="inlineStr">
+      <c r="Q37" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W37" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr"/>
@@ -3662,77 +3666,75 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>53529</v>
+        <v>52876</v>
       </c>
       <c r="C38" t="n">
-        <v>53589</v>
+        <v>53418</v>
       </c>
       <c r="D38" t="n">
-        <v>52812</v>
+        <v>52838</v>
       </c>
       <c r="E38" t="n">
-        <v>52849</v>
+        <v>53353</v>
       </c>
       <c r="F38" t="n">
-        <v>-681</v>
+        <v>504</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0095</v>
       </c>
       <c r="H38" t="n">
-        <v>777</v>
+        <v>580</v>
       </c>
       <c r="I38" t="n">
-        <v>52894</v>
+        <v>52035</v>
       </c>
       <c r="J38" t="n">
-        <v>53072.75</v>
+        <v>51896.25</v>
       </c>
       <c r="K38" t="n">
-        <v>53308.5</v>
+        <v>52460.5</v>
       </c>
       <c r="L38" t="n">
-        <v>53544.25</v>
+        <v>53024.75</v>
       </c>
       <c r="M38" t="n">
-        <v>53751.5</v>
+        <v>53237.5</v>
       </c>
       <c r="N38" t="n">
-        <v>53958.75</v>
+        <v>53450.25</v>
       </c>
       <c r="O38" t="n">
-        <v>54223</v>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
+        <v>54366</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
@@ -3741,55 +3743,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>52876</v>
+        <v>53367</v>
       </c>
       <c r="C39" t="n">
-        <v>53418</v>
+        <v>53567</v>
       </c>
       <c r="D39" t="n">
-        <v>52838</v>
+        <v>53210</v>
       </c>
       <c r="E39" t="n">
-        <v>53353</v>
+        <v>53489</v>
       </c>
       <c r="F39" t="n">
-        <v>504</v>
+        <v>136</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.0025</v>
       </c>
       <c r="H39" t="n">
-        <v>580</v>
+        <v>357</v>
       </c>
       <c r="I39" t="n">
-        <v>52035</v>
+        <v>52258</v>
       </c>
       <c r="J39" t="n">
-        <v>51896.25</v>
+        <v>52885.5</v>
       </c>
       <c r="K39" t="n">
-        <v>52460.5</v>
+        <v>53063</v>
       </c>
       <c r="L39" t="n">
-        <v>53024.75</v>
+        <v>53240.5</v>
       </c>
       <c r="M39" t="n">
-        <v>53237.5</v>
+        <v>53643</v>
       </c>
       <c r="N39" t="n">
-        <v>53450.25</v>
+        <v>54045.5</v>
       </c>
       <c r="O39" t="n">
-        <v>54366</v>
+        <v>53998</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3807,14 +3813,12 @@
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
@@ -3825,57 +3829,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>53367</v>
+        <v>53524</v>
       </c>
       <c r="C40" t="n">
-        <v>53567</v>
+        <v>53797</v>
       </c>
       <c r="D40" t="n">
-        <v>53210</v>
+        <v>53426</v>
       </c>
       <c r="E40" t="n">
-        <v>53489</v>
+        <v>53645</v>
       </c>
       <c r="F40" t="n">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0029</v>
       </c>
       <c r="H40" t="n">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="I40" t="n">
-        <v>52258</v>
+        <v>52853</v>
       </c>
       <c r="J40" t="n">
-        <v>52885.5</v>
+        <v>53182.25</v>
       </c>
       <c r="K40" t="n">
-        <v>53063</v>
+        <v>53310.5</v>
       </c>
       <c r="L40" t="n">
-        <v>53240.5</v>
+        <v>53438.75</v>
       </c>
       <c r="M40" t="n">
-        <v>53643</v>
+        <v>53667.5</v>
       </c>
       <c r="N40" t="n">
-        <v>54045.5</v>
+        <v>53896.25</v>
       </c>
       <c r="O40" t="n">
-        <v>53998</v>
+        <v>53924</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3916,50 +3920,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>53524</v>
+        <v>53643</v>
       </c>
       <c r="C41" t="n">
-        <v>53797</v>
+        <v>53778</v>
       </c>
       <c r="D41" t="n">
-        <v>53426</v>
+        <v>53435</v>
       </c>
       <c r="E41" t="n">
-        <v>53645</v>
+        <v>53521</v>
       </c>
       <c r="F41" t="n">
-        <v>156</v>
+        <v>-124</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0023</v>
       </c>
       <c r="H41" t="n">
-        <v>371</v>
+        <v>343</v>
       </c>
       <c r="I41" t="n">
-        <v>52853</v>
+        <v>53055</v>
       </c>
       <c r="J41" t="n">
-        <v>53182.25</v>
+        <v>53290.75</v>
       </c>
       <c r="K41" t="n">
-        <v>53310.5</v>
+        <v>53459.5</v>
       </c>
       <c r="L41" t="n">
-        <v>53438.75</v>
+        <v>53628.25</v>
       </c>
       <c r="M41" t="n">
-        <v>53667.5</v>
+        <v>53830.5</v>
       </c>
       <c r="N41" t="n">
-        <v>53896.25</v>
+        <v>54032.75</v>
       </c>
       <c r="O41" t="n">
-        <v>53924</v>
+        <v>54168</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3967,19 +3971,19 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
+      <c r="R41" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
@@ -3993,57 +3997,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>53643</v>
+        <v>53724</v>
       </c>
       <c r="C42" t="n">
-        <v>53778</v>
+        <v>53811</v>
       </c>
       <c r="D42" t="n">
-        <v>53435</v>
+        <v>53369</v>
       </c>
       <c r="E42" t="n">
-        <v>53521</v>
+        <v>53621</v>
       </c>
       <c r="F42" t="n">
-        <v>-124</v>
+        <v>100</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0019</v>
       </c>
       <c r="H42" t="n">
-        <v>343</v>
+        <v>442</v>
       </c>
       <c r="I42" t="n">
-        <v>53055</v>
+        <v>53092</v>
       </c>
       <c r="J42" t="n">
-        <v>53290.75</v>
+        <v>53135.25</v>
       </c>
       <c r="K42" t="n">
-        <v>53459.5</v>
+        <v>53349.5</v>
       </c>
       <c r="L42" t="n">
-        <v>53628.25</v>
+        <v>53563.75</v>
       </c>
       <c r="M42" t="n">
-        <v>53830.5</v>
+        <v>53692.5</v>
       </c>
       <c r="N42" t="n">
-        <v>54032.75</v>
+        <v>53821.25</v>
       </c>
       <c r="O42" t="n">
-        <v>54168</v>
+        <v>54121</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4051,18 +4055,18 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4077,57 +4081,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>53724</v>
+        <v>53608</v>
       </c>
       <c r="C43" t="n">
-        <v>53811</v>
+        <v>53862</v>
       </c>
       <c r="D43" t="n">
-        <v>53369</v>
+        <v>53513</v>
       </c>
       <c r="E43" t="n">
-        <v>53621</v>
+        <v>53584</v>
       </c>
       <c r="F43" t="n">
-        <v>100</v>
+        <v>-37</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0007</v>
       </c>
       <c r="H43" t="n">
-        <v>442</v>
+        <v>349</v>
       </c>
       <c r="I43" t="n">
-        <v>53092</v>
+        <v>52927</v>
       </c>
       <c r="J43" t="n">
-        <v>53135.25</v>
+        <v>53194.5</v>
       </c>
       <c r="K43" t="n">
-        <v>53349.5</v>
+        <v>53400</v>
       </c>
       <c r="L43" t="n">
-        <v>53563.75</v>
+        <v>53605.5</v>
       </c>
       <c r="M43" t="n">
-        <v>53692.5</v>
+        <v>53842</v>
       </c>
       <c r="N43" t="n">
-        <v>53821.25</v>
+        <v>54078.5</v>
       </c>
       <c r="O43" t="n">
-        <v>54121</v>
+        <v>54253</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4138,9 +4142,9 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
@@ -4168,69 +4172,73 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>53608</v>
+        <v>53664</v>
       </c>
       <c r="C44" t="n">
-        <v>53862</v>
+        <v>53664</v>
       </c>
       <c r="D44" t="n">
-        <v>53513</v>
+        <v>53149</v>
       </c>
       <c r="E44" t="n">
-        <v>53584</v>
+        <v>53240</v>
       </c>
       <c r="F44" t="n">
-        <v>-37</v>
+        <v>-344</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0064</v>
       </c>
       <c r="H44" t="n">
-        <v>349</v>
+        <v>515</v>
       </c>
       <c r="I44" t="n">
-        <v>52927</v>
+        <v>53164</v>
       </c>
       <c r="J44" t="n">
-        <v>53194.5</v>
+        <v>53183.25</v>
       </c>
       <c r="K44" t="n">
-        <v>53400</v>
+        <v>53409.5</v>
       </c>
       <c r="L44" t="n">
-        <v>53605.5</v>
+        <v>53635.75</v>
       </c>
       <c r="M44" t="n">
-        <v>53842</v>
+        <v>53758.5</v>
       </c>
       <c r="N44" t="n">
-        <v>54078.5</v>
+        <v>53881.25</v>
       </c>
       <c r="O44" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+        <v>54211</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4243,73 +4251,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>53664</v>
+        <v>53259</v>
       </c>
       <c r="C45" t="n">
-        <v>53664</v>
+        <v>53343</v>
       </c>
       <c r="D45" t="n">
-        <v>53149</v>
+        <v>52747</v>
       </c>
       <c r="E45" t="n">
-        <v>53240</v>
+        <v>52828</v>
       </c>
       <c r="F45" t="n">
-        <v>-344</v>
+        <v>-412</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0064</v>
+        <v>-0.0077</v>
       </c>
       <c r="H45" t="n">
-        <v>515</v>
+        <v>596</v>
       </c>
       <c r="I45" t="n">
-        <v>53164</v>
+        <v>52634</v>
       </c>
       <c r="J45" t="n">
-        <v>53183.25</v>
+        <v>52641.75</v>
       </c>
       <c r="K45" t="n">
-        <v>53409.5</v>
+        <v>52982.5</v>
       </c>
       <c r="L45" t="n">
-        <v>53635.75</v>
+        <v>53323.25</v>
       </c>
       <c r="M45" t="n">
-        <v>53758.5</v>
+        <v>53497.5</v>
       </c>
       <c r="N45" t="n">
-        <v>53881.25</v>
+        <v>53671.75</v>
       </c>
       <c r="O45" t="n">
-        <v>54211</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
+        <v>54179</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
@@ -4336,50 +4336,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>53259</v>
+        <v>52844</v>
       </c>
       <c r="C46" t="n">
-        <v>53343</v>
+        <v>53283</v>
       </c>
       <c r="D46" t="n">
-        <v>52747</v>
+        <v>52720</v>
       </c>
       <c r="E46" t="n">
-        <v>52828</v>
+        <v>53121</v>
       </c>
       <c r="F46" t="n">
-        <v>-412</v>
+        <v>293</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0077</v>
+        <v>0.0055</v>
       </c>
       <c r="H46" t="n">
-        <v>596</v>
+        <v>563</v>
       </c>
       <c r="I46" t="n">
-        <v>52634</v>
+        <v>52151</v>
       </c>
       <c r="J46" t="n">
-        <v>52641.75</v>
+        <v>52123.5</v>
       </c>
       <c r="K46" t="n">
-        <v>52982.5</v>
+        <v>52530</v>
       </c>
       <c r="L46" t="n">
-        <v>53323.25</v>
+        <v>52936.5</v>
       </c>
       <c r="M46" t="n">
-        <v>53497.5</v>
+        <v>53126</v>
       </c>
       <c r="N46" t="n">
-        <v>53671.75</v>
+        <v>53315.5</v>
       </c>
       <c r="O46" t="n">
-        <v>54179</v>
+        <v>53939</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4387,19 +4387,19 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
@@ -4411,55 +4411,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>52844</v>
+        <v>53120</v>
       </c>
       <c r="C47" t="n">
-        <v>53283</v>
+        <v>53827</v>
       </c>
       <c r="D47" t="n">
-        <v>52720</v>
+        <v>53093</v>
       </c>
       <c r="E47" t="n">
-        <v>53121</v>
+        <v>53745</v>
       </c>
       <c r="F47" t="n">
-        <v>293</v>
+        <v>624</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0117</v>
       </c>
       <c r="H47" t="n">
-        <v>563</v>
+        <v>734</v>
       </c>
       <c r="I47" t="n">
-        <v>52151</v>
+        <v>52157</v>
       </c>
       <c r="J47" t="n">
-        <v>52123.5</v>
+        <v>52617.75</v>
       </c>
       <c r="K47" t="n">
-        <v>52530</v>
+        <v>52839.5</v>
       </c>
       <c r="L47" t="n">
-        <v>52936.5</v>
+        <v>53061.25</v>
       </c>
       <c r="M47" t="n">
-        <v>53126</v>
+        <v>53402.5</v>
       </c>
       <c r="N47" t="n">
-        <v>53315.5</v>
+        <v>53743.75</v>
       </c>
       <c r="O47" t="n">
-        <v>53939</v>
+        <v>53846</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4477,73 +4481,71 @@
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W47" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>53120</v>
+        <v>53707</v>
       </c>
       <c r="C48" t="n">
-        <v>53827</v>
+        <v>53772</v>
       </c>
       <c r="D48" t="n">
-        <v>53093</v>
+        <v>53235</v>
       </c>
       <c r="E48" t="n">
-        <v>53745</v>
+        <v>53440</v>
       </c>
       <c r="F48" t="n">
-        <v>624</v>
+        <v>-305</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0117</v>
+        <v>-0.0057</v>
       </c>
       <c r="H48" t="n">
-        <v>734</v>
+        <v>537</v>
       </c>
       <c r="I48" t="n">
-        <v>52157</v>
+        <v>52359</v>
       </c>
       <c r="J48" t="n">
-        <v>52617.75</v>
+        <v>53153.5</v>
       </c>
       <c r="K48" t="n">
-        <v>52839.5</v>
+        <v>53378</v>
       </c>
       <c r="L48" t="n">
-        <v>53061.25</v>
+        <v>53602.5</v>
       </c>
       <c r="M48" t="n">
-        <v>53402.5</v>
+        <v>54112</v>
       </c>
       <c r="N48" t="n">
-        <v>53743.75</v>
+        <v>54621.5</v>
       </c>
       <c r="O48" t="n">
-        <v>53846</v>
+        <v>54561</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4551,24 +4553,22 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
+      <c r="R48" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
@@ -4577,65 +4577,71 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>53707</v>
+        <v>53261</v>
       </c>
       <c r="C49" t="n">
-        <v>53772</v>
+        <v>53336</v>
       </c>
       <c r="D49" t="n">
-        <v>53235</v>
+        <v>52758</v>
       </c>
       <c r="E49" t="n">
-        <v>53440</v>
+        <v>52832</v>
       </c>
       <c r="F49" t="n">
-        <v>-305</v>
+        <v>-608</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0057</v>
+        <v>-0.0114</v>
       </c>
       <c r="H49" t="n">
-        <v>537</v>
+        <v>578</v>
       </c>
       <c r="I49" t="n">
-        <v>52359</v>
+        <v>52698</v>
       </c>
       <c r="J49" t="n">
-        <v>53153.5</v>
+        <v>52871.25</v>
       </c>
       <c r="K49" t="n">
-        <v>53378</v>
+        <v>53171.5</v>
       </c>
       <c r="L49" t="n">
-        <v>53602.5</v>
+        <v>53471.75</v>
       </c>
       <c r="M49" t="n">
-        <v>54112</v>
+        <v>53708.5</v>
       </c>
       <c r="N49" t="n">
-        <v>54621.5</v>
+        <v>53945.25</v>
       </c>
       <c r="O49" t="n">
-        <v>54561</v>
+        <v>54309</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
@@ -4652,76 +4658,70 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W49" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>53261</v>
+        <v>52817</v>
       </c>
       <c r="C50" t="n">
-        <v>53336</v>
+        <v>52859</v>
       </c>
       <c r="D50" t="n">
-        <v>52758</v>
+        <v>52339</v>
       </c>
       <c r="E50" t="n">
-        <v>52832</v>
+        <v>52425</v>
       </c>
       <c r="F50" t="n">
-        <v>-608</v>
+        <v>-407</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0114</v>
+        <v>-0.0077</v>
       </c>
       <c r="H50" t="n">
-        <v>578</v>
+        <v>520</v>
       </c>
       <c r="I50" t="n">
-        <v>52698</v>
+        <v>52180</v>
       </c>
       <c r="J50" t="n">
-        <v>52871.25</v>
+        <v>52146.5</v>
       </c>
       <c r="K50" t="n">
-        <v>53171.5</v>
+        <v>52543</v>
       </c>
       <c r="L50" t="n">
-        <v>53471.75</v>
+        <v>52939.5</v>
       </c>
       <c r="M50" t="n">
-        <v>53708.5</v>
+        <v>53121</v>
       </c>
       <c r="N50" t="n">
-        <v>53945.25</v>
+        <v>53302.5</v>
       </c>
       <c r="O50" t="n">
-        <v>54309</v>
+        <v>53914</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
@@ -4748,50 +4748,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>52817</v>
+        <v>52473</v>
       </c>
       <c r="C51" t="n">
-        <v>52859</v>
+        <v>52676</v>
       </c>
       <c r="D51" t="n">
-        <v>52339</v>
+        <v>51992</v>
       </c>
       <c r="E51" t="n">
-        <v>52425</v>
+        <v>52095</v>
       </c>
       <c r="F51" t="n">
-        <v>-407</v>
+        <v>-330</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0077</v>
+        <v>-0.0063</v>
       </c>
       <c r="H51" t="n">
-        <v>520</v>
+        <v>684</v>
       </c>
       <c r="I51" t="n">
-        <v>52180</v>
+        <v>51819</v>
       </c>
       <c r="J51" t="n">
-        <v>52146.5</v>
+        <v>51818</v>
       </c>
       <c r="K51" t="n">
-        <v>52543</v>
+        <v>52165</v>
       </c>
       <c r="L51" t="n">
-        <v>52939.5</v>
+        <v>52512</v>
       </c>
       <c r="M51" t="n">
-        <v>53121</v>
+        <v>52685</v>
       </c>
       <c r="N51" t="n">
-        <v>53302.5</v>
+        <v>52858</v>
       </c>
       <c r="O51" t="n">
-        <v>53914</v>
+        <v>53379</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4828,50 +4828,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>52473</v>
+        <v>52059</v>
       </c>
       <c r="C52" t="n">
-        <v>52676</v>
+        <v>52739</v>
       </c>
       <c r="D52" t="n">
-        <v>51992</v>
+        <v>52059</v>
       </c>
       <c r="E52" t="n">
-        <v>52095</v>
+        <v>52585</v>
       </c>
       <c r="F52" t="n">
-        <v>-330</v>
+        <v>490</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0063</v>
+        <v>0.0094</v>
       </c>
       <c r="H52" t="n">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="I52" t="n">
-        <v>51819</v>
+        <v>51308</v>
       </c>
       <c r="J52" t="n">
-        <v>51818</v>
+        <v>51291.5</v>
       </c>
       <c r="K52" t="n">
-        <v>52165</v>
+        <v>51753</v>
       </c>
       <c r="L52" t="n">
-        <v>52512</v>
+        <v>52214.5</v>
       </c>
       <c r="M52" t="n">
-        <v>52685</v>
+        <v>52437</v>
       </c>
       <c r="N52" t="n">
-        <v>52858</v>
+        <v>52659.5</v>
       </c>
       <c r="O52" t="n">
-        <v>53379</v>
+        <v>53360</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4879,22 +4879,24 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
@@ -4903,55 +4905,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>52059</v>
+        <v>52376</v>
       </c>
       <c r="C53" t="n">
-        <v>52739</v>
+        <v>52672</v>
       </c>
       <c r="D53" t="n">
-        <v>52059</v>
+        <v>52226</v>
       </c>
       <c r="E53" t="n">
-        <v>52585</v>
+        <v>52440</v>
       </c>
       <c r="F53" t="n">
-        <v>490</v>
+        <v>-145</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0094</v>
+        <v>-0.0028</v>
       </c>
       <c r="H53" t="n">
-        <v>680</v>
+        <v>446</v>
       </c>
       <c r="I53" t="n">
-        <v>51308</v>
+        <v>51379</v>
       </c>
       <c r="J53" t="n">
-        <v>51291.5</v>
+        <v>51998</v>
       </c>
       <c r="K53" t="n">
-        <v>51753</v>
+        <v>52245</v>
       </c>
       <c r="L53" t="n">
-        <v>52214.5</v>
+        <v>52492</v>
       </c>
       <c r="M53" t="n">
-        <v>52437</v>
+        <v>52925</v>
       </c>
       <c r="N53" t="n">
-        <v>52659.5</v>
+        <v>53358</v>
       </c>
       <c r="O53" t="n">
-        <v>53360</v>
+        <v>53419</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4959,23 +4965,21 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4987,72 +4991,74 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>52376</v>
+        <v>52499</v>
       </c>
       <c r="C54" t="n">
-        <v>52672</v>
+        <v>52499</v>
       </c>
       <c r="D54" t="n">
-        <v>52226</v>
+        <v>51908</v>
       </c>
       <c r="E54" t="n">
-        <v>52440</v>
+        <v>52115</v>
       </c>
       <c r="F54" t="n">
-        <v>-145</v>
+        <v>-325</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0028</v>
+        <v>-0.0062</v>
       </c>
       <c r="H54" t="n">
-        <v>446</v>
+        <v>591</v>
       </c>
       <c r="I54" t="n">
-        <v>51379</v>
+        <v>51780</v>
       </c>
       <c r="J54" t="n">
-        <v>51998</v>
+        <v>51989.5</v>
       </c>
       <c r="K54" t="n">
-        <v>52245</v>
+        <v>52217</v>
       </c>
       <c r="L54" t="n">
-        <v>52492</v>
+        <v>52444.5</v>
       </c>
       <c r="M54" t="n">
-        <v>52925</v>
+        <v>52663</v>
       </c>
       <c r="N54" t="n">
-        <v>53358</v>
+        <v>52881.5</v>
       </c>
       <c r="O54" t="n">
-        <v>53419</v>
+        <v>53118</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5069,71 +5075,69 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>52499</v>
+        <v>52162</v>
       </c>
       <c r="C55" t="n">
-        <v>52499</v>
+        <v>52298</v>
       </c>
       <c r="D55" t="n">
-        <v>51908</v>
+        <v>51209</v>
       </c>
       <c r="E55" t="n">
-        <v>52115</v>
+        <v>51507</v>
       </c>
       <c r="F55" t="n">
-        <v>-325</v>
+        <v>-608</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0062</v>
+        <v>-0.0117</v>
       </c>
       <c r="H55" t="n">
-        <v>591</v>
+        <v>1089</v>
       </c>
       <c r="I55" t="n">
-        <v>51780</v>
+        <v>51317</v>
       </c>
       <c r="J55" t="n">
-        <v>51989.5</v>
+        <v>51479.75</v>
       </c>
       <c r="K55" t="n">
-        <v>52217</v>
+        <v>51819.5</v>
       </c>
       <c r="L55" t="n">
-        <v>52444.5</v>
+        <v>52159.25</v>
       </c>
       <c r="M55" t="n">
-        <v>52663</v>
+        <v>52410.5</v>
       </c>
       <c r="N55" t="n">
-        <v>52881.5</v>
+        <v>52661.75</v>
       </c>
       <c r="O55" t="n">
-        <v>53118</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v/>
+        <v>53090</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q55" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
@@ -5160,74 +5164,70 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>52162</v>
+        <v>51486</v>
       </c>
       <c r="C56" t="n">
-        <v>52298</v>
+        <v>52169</v>
       </c>
       <c r="D56" t="n">
-        <v>51209</v>
+        <v>51455</v>
       </c>
       <c r="E56" t="n">
-        <v>51507</v>
+        <v>51807</v>
       </c>
       <c r="F56" t="n">
-        <v>-608</v>
+        <v>300</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0117</v>
+        <v>0.0058</v>
       </c>
       <c r="H56" t="n">
-        <v>1089</v>
+        <v>714</v>
       </c>
       <c r="I56" t="n">
-        <v>51317</v>
+        <v>50120</v>
       </c>
       <c r="J56" t="n">
-        <v>51479.75</v>
+        <v>50294.75</v>
       </c>
       <c r="K56" t="n">
-        <v>51819.5</v>
+        <v>50962.5</v>
       </c>
       <c r="L56" t="n">
-        <v>52159.25</v>
+        <v>51630.25</v>
       </c>
       <c r="M56" t="n">
-        <v>52410.5</v>
+        <v>52051.5</v>
       </c>
       <c r="N56" t="n">
-        <v>52661.75</v>
+        <v>52472.75</v>
       </c>
       <c r="O56" t="n">
-        <v>53090</v>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
+        <v>53387</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
       <c r="U56" s="8" t="n">
         <v/>
       </c>
@@ -5239,55 +5239,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>51486</v>
+        <v>51800</v>
       </c>
       <c r="C57" t="n">
-        <v>52169</v>
+        <v>51957</v>
       </c>
       <c r="D57" t="n">
-        <v>51455</v>
+        <v>51576</v>
       </c>
       <c r="E57" t="n">
-        <v>51807</v>
+        <v>51761</v>
       </c>
       <c r="F57" t="n">
-        <v>300</v>
+        <v>-46</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0009</v>
       </c>
       <c r="H57" t="n">
-        <v>714</v>
+        <v>381</v>
       </c>
       <c r="I57" t="n">
-        <v>50120</v>
+        <v>50741</v>
       </c>
       <c r="J57" t="n">
-        <v>50294.75</v>
+        <v>51090.5</v>
       </c>
       <c r="K57" t="n">
-        <v>50962.5</v>
+        <v>51450</v>
       </c>
       <c r="L57" t="n">
-        <v>51630.25</v>
+        <v>51809.5</v>
       </c>
       <c r="M57" t="n">
-        <v>52051.5</v>
+        <v>52164</v>
       </c>
       <c r="N57" t="n">
-        <v>52472.75</v>
+        <v>52518.5</v>
       </c>
       <c r="O57" t="n">
-        <v>53387</v>
+        <v>52883</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5298,15 +5302,13 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5321,57 +5323,57 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>51800</v>
+        <v>52085</v>
       </c>
       <c r="C58" t="n">
-        <v>51957</v>
+        <v>52557</v>
       </c>
       <c r="D58" t="n">
-        <v>51576</v>
+        <v>52080</v>
       </c>
       <c r="E58" t="n">
-        <v>51761</v>
+        <v>52475</v>
       </c>
       <c r="F58" t="n">
-        <v>-46</v>
+        <v>714</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0138</v>
       </c>
       <c r="H58" t="n">
-        <v>381</v>
+        <v>477</v>
       </c>
       <c r="I58" t="n">
-        <v>50741</v>
+        <v>51195</v>
       </c>
       <c r="J58" t="n">
-        <v>51090.5</v>
+        <v>51377.25</v>
       </c>
       <c r="K58" t="n">
-        <v>51450</v>
+        <v>51570.5</v>
       </c>
       <c r="L58" t="n">
-        <v>51809.5</v>
+        <v>51763.75</v>
       </c>
       <c r="M58" t="n">
-        <v>52164</v>
+        <v>51951.5</v>
       </c>
       <c r="N58" t="n">
-        <v>52518.5</v>
+        <v>52139.25</v>
       </c>
       <c r="O58" t="n">
-        <v>52883</v>
+        <v>52338</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5382,78 +5384,80 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>52085</v>
+        <v>52470</v>
       </c>
       <c r="C59" t="n">
-        <v>52557</v>
+        <v>52844</v>
       </c>
       <c r="D59" t="n">
-        <v>52080</v>
+        <v>52125</v>
       </c>
       <c r="E59" t="n">
-        <v>52475</v>
+        <v>52279</v>
       </c>
       <c r="F59" t="n">
-        <v>714</v>
+        <v>-196</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0138</v>
+        <v>-0.0037</v>
       </c>
       <c r="H59" t="n">
-        <v>477</v>
+        <v>719</v>
       </c>
       <c r="I59" t="n">
-        <v>51195</v>
+        <v>51603</v>
       </c>
       <c r="J59" t="n">
-        <v>51377.25</v>
+        <v>52076.25</v>
       </c>
       <c r="K59" t="n">
-        <v>51570.5</v>
+        <v>52236.5</v>
       </c>
       <c r="L59" t="n">
-        <v>51763.75</v>
+        <v>52396.75</v>
       </c>
       <c r="M59" t="n">
-        <v>51951.5</v>
+        <v>52713.5</v>
       </c>
       <c r="N59" t="n">
-        <v>52139.25</v>
+        <v>53030.25</v>
       </c>
       <c r="O59" t="n">
-        <v>52338</v>
+        <v>53034</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5461,12 +5465,14 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T59" s="8" t="inlineStr">
@@ -5474,70 +5480,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V59" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V59" s="8" t="n">
+        <v/>
       </c>
       <c r="W59" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>52470</v>
+        <v>52255</v>
       </c>
       <c r="C60" t="n">
-        <v>52844</v>
+        <v>52371</v>
       </c>
       <c r="D60" t="n">
-        <v>52125</v>
+        <v>51844</v>
       </c>
       <c r="E60" t="n">
-        <v>52279</v>
+        <v>51873</v>
       </c>
       <c r="F60" t="n">
-        <v>-196</v>
+        <v>-406</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0037</v>
+        <v>-0.0078</v>
       </c>
       <c r="H60" t="n">
-        <v>719</v>
+        <v>527</v>
       </c>
       <c r="I60" t="n">
-        <v>51603</v>
+        <v>51406</v>
       </c>
       <c r="J60" t="n">
-        <v>52076.25</v>
+        <v>51457.25</v>
       </c>
       <c r="K60" t="n">
-        <v>52236.5</v>
+        <v>51919.5</v>
       </c>
       <c r="L60" t="n">
-        <v>52396.75</v>
+        <v>52381.75</v>
       </c>
       <c r="M60" t="n">
-        <v>52713.5</v>
+        <v>52638.5</v>
       </c>
       <c r="N60" t="n">
-        <v>53030.25</v>
+        <v>52895.25</v>
       </c>
       <c r="O60" t="n">
-        <v>53034</v>
+        <v>53563</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5555,10 +5561,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T60" s="8" t="n">
+        <v/>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5573,57 +5577,57 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>52255</v>
+        <v>51878</v>
       </c>
       <c r="C61" t="n">
-        <v>52371</v>
+        <v>51905</v>
       </c>
       <c r="D61" t="n">
-        <v>51844</v>
+        <v>51479</v>
       </c>
       <c r="E61" t="n">
-        <v>51873</v>
+        <v>51717</v>
       </c>
       <c r="F61" t="n">
-        <v>-406</v>
+        <v>-156</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0078</v>
+        <v>-0.003</v>
       </c>
       <c r="H61" t="n">
-        <v>527</v>
+        <v>426</v>
       </c>
       <c r="I61" t="n">
-        <v>51406</v>
+        <v>51317</v>
       </c>
       <c r="J61" t="n">
-        <v>51457.25</v>
+        <v>51228.75</v>
       </c>
       <c r="K61" t="n">
-        <v>51919.5</v>
+        <v>51609.5</v>
       </c>
       <c r="L61" t="n">
-        <v>52381.75</v>
+        <v>51990.25</v>
       </c>
       <c r="M61" t="n">
-        <v>52638.5</v>
+        <v>52136.5</v>
       </c>
       <c r="N61" t="n">
-        <v>52895.25</v>
+        <v>52282.75</v>
       </c>
       <c r="O61" t="n">
-        <v>53563</v>
+        <v>52898</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5664,50 +5668,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>51655</v>
       </c>
       <c r="C62" t="n">
-        <v>51695</v>
+        <v>52223</v>
       </c>
       <c r="D62" t="n">
-        <v>51654</v>
+        <v>51610</v>
       </c>
       <c r="E62" t="n">
-        <v>51669</v>
+        <v>52163</v>
       </c>
       <c r="F62" t="n">
-        <v>-204</v>
+        <v>446</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0039</v>
+        <v>0.0086</v>
       </c>
       <c r="H62" t="n">
-        <v>41</v>
+        <v>613</v>
       </c>
       <c r="I62" t="n">
-        <v>51317</v>
+        <v>51053</v>
       </c>
       <c r="J62" t="n">
-        <v>51228.75</v>
+        <v>51303.5</v>
       </c>
       <c r="K62" t="n">
-        <v>51609.5</v>
+        <v>51504</v>
       </c>
       <c r="L62" t="n">
-        <v>51990.25</v>
+        <v>51704.5</v>
       </c>
       <c r="M62" t="n">
-        <v>52136.5</v>
+        <v>51930</v>
       </c>
       <c r="N62" t="n">
-        <v>52282.75</v>
+        <v>52155.5</v>
       </c>
       <c r="O62" t="n">
-        <v>52898</v>
+        <v>52331</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5715,22 +5719,24 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="inlineStr">
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
       <c r="V62" s="8" t="n">
         <v/>
       </c>
@@ -5739,9 +5745,87 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
+      <c r="X62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>52140</v>
+      </c>
+      <c r="C63" t="n">
+        <v>52153</v>
+      </c>
+      <c r="D63" t="n">
+        <v>52054</v>
+      </c>
+      <c r="E63" t="n">
+        <v>52163</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>99</v>
+      </c>
+      <c r="I63" t="n">
+        <v>50997</v>
+      </c>
+      <c r="J63" t="n">
+        <v>51673.25</v>
+      </c>
+      <c r="K63" t="n">
+        <v>51856.5</v>
+      </c>
+      <c r="L63" t="n">
+        <v>52039.75</v>
+      </c>
+      <c r="M63" t="n">
+        <v>52469.5</v>
+      </c>
+      <c r="N63" t="n">
+        <v>52899.25</v>
+      </c>
+      <c r="O63" t="n">
+        <v>52836</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52546</v>
+        <v>52640</v>
       </c>
       <c r="C2" t="n">
-        <v>53105</v>
+        <v>53218</v>
       </c>
       <c r="D2" t="n">
-        <v>52381</v>
+        <v>52551</v>
       </c>
       <c r="E2" t="n">
-        <v>52668</v>
+        <v>53183</v>
       </c>
       <c r="F2" t="n">
-        <v>-2</v>
+        <v>515</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0</v>
+        <v>0.0098</v>
       </c>
       <c r="H2" t="n">
-        <v>724</v>
+        <v>667</v>
       </c>
       <c r="I2" t="n">
-        <v>52003</v>
+        <v>51657</v>
       </c>
       <c r="J2" t="n">
-        <v>52338.5</v>
+        <v>51906.5</v>
       </c>
       <c r="K2" t="n">
-        <v>52480</v>
+        <v>52306</v>
       </c>
       <c r="L2" t="n">
-        <v>52621.5</v>
+        <v>52705.5</v>
       </c>
       <c r="M2" t="n">
-        <v>52860</v>
+        <v>53030</v>
       </c>
       <c r="N2" t="n">
-        <v>53098.5</v>
+        <v>53354.5</v>
       </c>
       <c r="O2" t="n">
-        <v>53143</v>
+        <v>53829</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,25 +685,21 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -713,59 +709,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>52640</v>
+        <v>53230</v>
       </c>
       <c r="C3" t="n">
-        <v>53218</v>
+        <v>53421</v>
       </c>
       <c r="D3" t="n">
-        <v>52551</v>
+        <v>52962</v>
       </c>
       <c r="E3" t="n">
-        <v>53183</v>
+        <v>53372</v>
       </c>
       <c r="F3" t="n">
-        <v>515</v>
+        <v>189</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0036</v>
       </c>
       <c r="H3" t="n">
-        <v>667</v>
+        <v>459</v>
       </c>
       <c r="I3" t="n">
-        <v>51657</v>
+        <v>51884</v>
       </c>
       <c r="J3" t="n">
-        <v>51906.5</v>
+        <v>52665.25</v>
       </c>
       <c r="K3" t="n">
-        <v>52306</v>
+        <v>52849.5</v>
       </c>
       <c r="L3" t="n">
-        <v>52705.5</v>
+        <v>53033.75</v>
       </c>
       <c r="M3" t="n">
-        <v>53030</v>
+        <v>53516.5</v>
       </c>
       <c r="N3" t="n">
-        <v>53354.5</v>
+        <v>53999.25</v>
       </c>
       <c r="O3" t="n">
-        <v>53829</v>
+        <v>53885</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -802,50 +794,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53230</v>
+        <v>53405</v>
       </c>
       <c r="C4" t="n">
-        <v>53421</v>
+        <v>53656</v>
       </c>
       <c r="D4" t="n">
-        <v>52962</v>
+        <v>53076</v>
       </c>
       <c r="E4" t="n">
-        <v>53372</v>
+        <v>53197</v>
       </c>
       <c r="F4" t="n">
-        <v>189</v>
+        <v>-175</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0036</v>
+        <v>-0.0033</v>
       </c>
       <c r="H4" t="n">
-        <v>459</v>
+        <v>580</v>
       </c>
       <c r="I4" t="n">
-        <v>51884</v>
+        <v>52503</v>
       </c>
       <c r="J4" t="n">
-        <v>52665.25</v>
+        <v>53003.25</v>
       </c>
       <c r="K4" t="n">
-        <v>52849.5</v>
+        <v>53142.5</v>
       </c>
       <c r="L4" t="n">
-        <v>53033.75</v>
+        <v>53281.75</v>
       </c>
       <c r="M4" t="n">
-        <v>53516.5</v>
+        <v>53601.5</v>
       </c>
       <c r="N4" t="n">
-        <v>53999.25</v>
+        <v>53921.25</v>
       </c>
       <c r="O4" t="n">
-        <v>53885</v>
+        <v>53880</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -853,17 +845,19 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U4" s="8" t="n">
@@ -877,65 +871,73 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53405</v>
+        <v>53166</v>
       </c>
       <c r="C5" t="n">
-        <v>53656</v>
+        <v>53207</v>
       </c>
       <c r="D5" t="n">
-        <v>53076</v>
+        <v>52343</v>
       </c>
       <c r="E5" t="n">
-        <v>53197</v>
+        <v>52624</v>
       </c>
       <c r="F5" t="n">
-        <v>-175</v>
+        <v>-573</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0108</v>
       </c>
       <c r="H5" t="n">
-        <v>580</v>
+        <v>864</v>
       </c>
       <c r="I5" t="n">
-        <v>52503</v>
+        <v>52496</v>
       </c>
       <c r="J5" t="n">
-        <v>53003.25</v>
+        <v>52532.5</v>
       </c>
       <c r="K5" t="n">
-        <v>53142.5</v>
+        <v>52907</v>
       </c>
       <c r="L5" t="n">
-        <v>53281.75</v>
+        <v>53281.5</v>
       </c>
       <c r="M5" t="n">
-        <v>53601.5</v>
+        <v>53487</v>
       </c>
       <c r="N5" t="n">
-        <v>53921.25</v>
+        <v>53692.5</v>
       </c>
       <c r="O5" t="n">
-        <v>53880</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
+        <v>54236</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S5" s="10" t="inlineStr">
@@ -943,10 +945,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -961,76 +961,70 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>53166</v>
+        <v>52541</v>
       </c>
       <c r="C6" t="n">
-        <v>53207</v>
+        <v>52865</v>
       </c>
       <c r="D6" t="n">
-        <v>52343</v>
+        <v>52501</v>
       </c>
       <c r="E6" t="n">
-        <v>52624</v>
+        <v>52761</v>
       </c>
       <c r="F6" t="n">
-        <v>-573</v>
+        <v>137</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0108</v>
+        <v>0.0026</v>
       </c>
       <c r="H6" t="n">
-        <v>864</v>
+        <v>364</v>
       </c>
       <c r="I6" t="n">
-        <v>52496</v>
+        <v>51479</v>
       </c>
       <c r="J6" t="n">
-        <v>52532.5</v>
+        <v>51684.5</v>
       </c>
       <c r="K6" t="n">
-        <v>52907</v>
+        <v>52192</v>
       </c>
       <c r="L6" t="n">
-        <v>53281.5</v>
+        <v>52699.5</v>
       </c>
       <c r="M6" t="n">
-        <v>53487</v>
+        <v>53056</v>
       </c>
       <c r="N6" t="n">
-        <v>53692.5</v>
+        <v>53412.5</v>
       </c>
       <c r="O6" t="n">
-        <v>54236</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>54071</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1049,57 +1043,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>52541</v>
+        <v>52753</v>
       </c>
       <c r="C7" t="n">
-        <v>52865</v>
+        <v>52992</v>
       </c>
       <c r="D7" t="n">
-        <v>52501</v>
+        <v>52506</v>
       </c>
       <c r="E7" t="n">
-        <v>52761</v>
+        <v>52906</v>
       </c>
       <c r="F7" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0027</v>
       </c>
       <c r="H7" t="n">
-        <v>364</v>
+        <v>486</v>
       </c>
       <c r="I7" t="n">
-        <v>51479</v>
+        <v>52137</v>
       </c>
       <c r="J7" t="n">
-        <v>51684.5</v>
+        <v>52436</v>
       </c>
       <c r="K7" t="n">
-        <v>52192</v>
+        <v>52579</v>
       </c>
       <c r="L7" t="n">
-        <v>52699.5</v>
+        <v>52722</v>
       </c>
       <c r="M7" t="n">
-        <v>53056</v>
+        <v>52943</v>
       </c>
       <c r="N7" t="n">
-        <v>53412.5</v>
+        <v>53164</v>
       </c>
       <c r="O7" t="n">
-        <v>54071</v>
+        <v>53229</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1107,16 +1101,20 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1129,59 +1127,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52753</v>
+        <v>52844</v>
       </c>
       <c r="C8" t="n">
-        <v>52992</v>
+        <v>53113</v>
       </c>
       <c r="D8" t="n">
-        <v>52506</v>
+        <v>52603</v>
       </c>
       <c r="E8" t="n">
-        <v>52906</v>
+        <v>52764</v>
       </c>
       <c r="F8" t="n">
-        <v>145</v>
+        <v>-142</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0027</v>
       </c>
       <c r="H8" t="n">
-        <v>486</v>
+        <v>510</v>
       </c>
       <c r="I8" t="n">
-        <v>52137</v>
+        <v>52020</v>
       </c>
       <c r="J8" t="n">
-        <v>52436</v>
+        <v>52498.5</v>
       </c>
       <c r="K8" t="n">
-        <v>52579</v>
+        <v>52663</v>
       </c>
       <c r="L8" t="n">
-        <v>52722</v>
+        <v>52827.5</v>
       </c>
       <c r="M8" t="n">
-        <v>52943</v>
+        <v>53149</v>
       </c>
       <c r="N8" t="n">
-        <v>53164</v>
+        <v>53470.5</v>
       </c>
       <c r="O8" t="n">
-        <v>53229</v>
+        <v>53478</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1194,15 +1188,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1215,55 +1207,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52844</v>
+        <v>52731</v>
       </c>
       <c r="C9" t="n">
-        <v>53113</v>
+        <v>52981</v>
       </c>
       <c r="D9" t="n">
-        <v>52603</v>
+        <v>52255</v>
       </c>
       <c r="E9" t="n">
-        <v>52764</v>
+        <v>52791</v>
       </c>
       <c r="F9" t="n">
-        <v>-142</v>
+        <v>27</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0005</v>
       </c>
       <c r="H9" t="n">
-        <v>510</v>
+        <v>726</v>
       </c>
       <c r="I9" t="n">
-        <v>52020</v>
+        <v>52093</v>
       </c>
       <c r="J9" t="n">
-        <v>52498.5</v>
+        <v>52207</v>
       </c>
       <c r="K9" t="n">
-        <v>52663</v>
+        <v>52509</v>
       </c>
       <c r="L9" t="n">
-        <v>52827.5</v>
+        <v>52811</v>
       </c>
       <c r="M9" t="n">
-        <v>53149</v>
+        <v>53019</v>
       </c>
       <c r="N9" t="n">
-        <v>53470.5</v>
+        <v>53227</v>
       </c>
       <c r="O9" t="n">
-        <v>53478</v>
+        <v>53623</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1297,57 +1293,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52731</v>
+        <v>52792</v>
       </c>
       <c r="C10" t="n">
-        <v>52981</v>
+        <v>53088</v>
       </c>
       <c r="D10" t="n">
-        <v>52255</v>
+        <v>52680</v>
       </c>
       <c r="E10" t="n">
-        <v>52791</v>
+        <v>52900</v>
       </c>
       <c r="F10" t="n">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0021</v>
       </c>
       <c r="H10" t="n">
-        <v>726</v>
+        <v>408</v>
       </c>
       <c r="I10" t="n">
-        <v>52093</v>
+        <v>51529</v>
       </c>
       <c r="J10" t="n">
-        <v>52207</v>
+        <v>52151.5</v>
       </c>
       <c r="K10" t="n">
-        <v>52509</v>
+        <v>52428</v>
       </c>
       <c r="L10" t="n">
-        <v>52811</v>
+        <v>52704.5</v>
       </c>
       <c r="M10" t="n">
-        <v>53019</v>
+        <v>53154</v>
       </c>
       <c r="N10" t="n">
-        <v>53227</v>
+        <v>53603.5</v>
       </c>
       <c r="O10" t="n">
-        <v>53623</v>
+        <v>53707</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1355,14 +1351,12 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1379,59 +1373,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>52792</v>
+        <v>52919</v>
       </c>
       <c r="C11" t="n">
-        <v>53088</v>
+        <v>53108</v>
       </c>
       <c r="D11" t="n">
-        <v>52680</v>
+        <v>52607</v>
       </c>
       <c r="E11" t="n">
-        <v>52900</v>
+        <v>52786</v>
       </c>
       <c r="F11" t="n">
-        <v>109</v>
+        <v>-114</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0022</v>
       </c>
       <c r="H11" t="n">
-        <v>408</v>
+        <v>501</v>
       </c>
       <c r="I11" t="n">
-        <v>51529</v>
+        <v>52272</v>
       </c>
       <c r="J11" t="n">
-        <v>52151.5</v>
+        <v>52500</v>
       </c>
       <c r="K11" t="n">
-        <v>52428</v>
+        <v>52696</v>
       </c>
       <c r="L11" t="n">
-        <v>52704.5</v>
+        <v>52892</v>
       </c>
       <c r="M11" t="n">
-        <v>53154</v>
+        <v>53104</v>
       </c>
       <c r="N11" t="n">
-        <v>53603.5</v>
+        <v>53316</v>
       </c>
       <c r="O11" t="n">
-        <v>53707</v>
+        <v>53496</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1439,16 +1429,20 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1461,65 +1455,71 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52919</v>
+        <v>52778</v>
       </c>
       <c r="C12" t="n">
-        <v>53108</v>
+        <v>52835</v>
       </c>
       <c r="D12" t="n">
-        <v>52607</v>
+        <v>52174</v>
       </c>
       <c r="E12" t="n">
-        <v>52786</v>
+        <v>52375</v>
       </c>
       <c r="F12" t="n">
-        <v>-114</v>
+        <v>-411</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0078</v>
       </c>
       <c r="H12" t="n">
-        <v>501</v>
+        <v>661</v>
       </c>
       <c r="I12" t="n">
-        <v>52272</v>
+        <v>52106</v>
       </c>
       <c r="J12" t="n">
-        <v>52500</v>
+        <v>52249.25</v>
       </c>
       <c r="K12" t="n">
-        <v>52696</v>
+        <v>52535.5</v>
       </c>
       <c r="L12" t="n">
-        <v>52892</v>
+        <v>52821.75</v>
       </c>
       <c r="M12" t="n">
-        <v>53104</v>
+        <v>53036.5</v>
       </c>
       <c r="N12" t="n">
-        <v>53316</v>
+        <v>53251.25</v>
       </c>
       <c r="O12" t="n">
-        <v>53496</v>
+        <v>53609</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
@@ -1527,10 +1527,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1545,69 +1543,67 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>52778</v>
+        <v>52300</v>
       </c>
       <c r="C13" t="n">
-        <v>52835</v>
+        <v>52633</v>
       </c>
       <c r="D13" t="n">
-        <v>52174</v>
+        <v>51999</v>
       </c>
       <c r="E13" t="n">
-        <v>52375</v>
+        <v>52073</v>
       </c>
       <c r="F13" t="n">
-        <v>-411</v>
+        <v>-302</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0078</v>
+        <v>-0.0058</v>
       </c>
       <c r="H13" t="n">
-        <v>661</v>
+        <v>634</v>
       </c>
       <c r="I13" t="n">
-        <v>52106</v>
+        <v>51513</v>
       </c>
       <c r="J13" t="n">
-        <v>52249.25</v>
+        <v>51649.25</v>
       </c>
       <c r="K13" t="n">
-        <v>52535.5</v>
+        <v>52044.5</v>
       </c>
       <c r="L13" t="n">
-        <v>52821.75</v>
+        <v>52439.75</v>
       </c>
       <c r="M13" t="n">
-        <v>53036.5</v>
+        <v>52705.5</v>
       </c>
       <c r="N13" t="n">
-        <v>53251.25</v>
+        <v>52971.25</v>
       </c>
       <c r="O13" t="n">
-        <v>53609</v>
+        <v>53496</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
@@ -1638,50 +1634,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>52300</v>
+        <v>52091</v>
       </c>
       <c r="C14" t="n">
-        <v>52633</v>
+        <v>52590</v>
       </c>
       <c r="D14" t="n">
-        <v>51999</v>
+        <v>52035</v>
       </c>
       <c r="E14" t="n">
-        <v>52073</v>
+        <v>52443</v>
       </c>
       <c r="F14" t="n">
-        <v>-302</v>
+        <v>370</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.0071</v>
       </c>
       <c r="H14" t="n">
-        <v>634</v>
+        <v>555</v>
       </c>
       <c r="I14" t="n">
-        <v>51513</v>
+        <v>51365</v>
       </c>
       <c r="J14" t="n">
-        <v>51649.25</v>
+        <v>51317.5</v>
       </c>
       <c r="K14" t="n">
-        <v>52044.5</v>
+        <v>51756</v>
       </c>
       <c r="L14" t="n">
-        <v>52439.75</v>
+        <v>52194.5</v>
       </c>
       <c r="M14" t="n">
-        <v>52705.5</v>
+        <v>52390</v>
       </c>
       <c r="N14" t="n">
-        <v>52971.25</v>
+        <v>52585.5</v>
       </c>
       <c r="O14" t="n">
-        <v>53496</v>
+        <v>53267</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1689,21 +1685,23 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1715,57 +1713,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52091</v>
+        <v>52431</v>
       </c>
       <c r="C15" t="n">
-        <v>52590</v>
+        <v>52721</v>
       </c>
       <c r="D15" t="n">
-        <v>52035</v>
+        <v>52262</v>
       </c>
       <c r="E15" t="n">
-        <v>52443</v>
+        <v>52449</v>
       </c>
       <c r="F15" t="n">
-        <v>370</v>
+        <v>6</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0001</v>
       </c>
       <c r="H15" t="n">
-        <v>555</v>
+        <v>459</v>
       </c>
       <c r="I15" t="n">
-        <v>51365</v>
+        <v>51480</v>
       </c>
       <c r="J15" t="n">
-        <v>51317.5</v>
+        <v>51953.25</v>
       </c>
       <c r="K15" t="n">
-        <v>51756</v>
+        <v>52165.5</v>
       </c>
       <c r="L15" t="n">
-        <v>52194.5</v>
+        <v>52377.75</v>
       </c>
       <c r="M15" t="n">
-        <v>52390</v>
+        <v>52720.5</v>
       </c>
       <c r="N15" t="n">
-        <v>52585.5</v>
+        <v>53063.25</v>
       </c>
       <c r="O15" t="n">
-        <v>53267</v>
+        <v>53145</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1778,19 +1776,17 @@
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
@@ -1799,88 +1795,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>52431</v>
+        <v>52430</v>
       </c>
       <c r="C16" t="n">
-        <v>52721</v>
+        <v>52515</v>
       </c>
       <c r="D16" t="n">
-        <v>52262</v>
+        <v>51720</v>
       </c>
       <c r="E16" t="n">
-        <v>52449</v>
+        <v>51894</v>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>-555</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0106</v>
       </c>
       <c r="H16" t="n">
-        <v>459</v>
+        <v>795</v>
       </c>
       <c r="I16" t="n">
-        <v>51480</v>
+        <v>51803</v>
       </c>
       <c r="J16" t="n">
-        <v>51953.25</v>
+        <v>51968.75</v>
       </c>
       <c r="K16" t="n">
-        <v>52165.5</v>
+        <v>52219.5</v>
       </c>
       <c r="L16" t="n">
-        <v>52377.75</v>
+        <v>52470.25</v>
       </c>
       <c r="M16" t="n">
-        <v>52720.5</v>
+        <v>52678.5</v>
       </c>
       <c r="N16" t="n">
-        <v>53063.25</v>
+        <v>52886.75</v>
       </c>
       <c r="O16" t="n">
-        <v>53145</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
+        <v>53180</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W16" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
@@ -1888,74 +1884,70 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52430</v>
+        <v>51920</v>
       </c>
       <c r="C17" t="n">
-        <v>52515</v>
+        <v>52314</v>
       </c>
       <c r="D17" t="n">
-        <v>51720</v>
+        <v>51846</v>
       </c>
       <c r="E17" t="n">
-        <v>51894</v>
+        <v>52124</v>
       </c>
       <c r="F17" t="n">
-        <v>-555</v>
+        <v>230</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0044</v>
       </c>
       <c r="H17" t="n">
-        <v>795</v>
+        <v>468</v>
       </c>
       <c r="I17" t="n">
-        <v>51803</v>
+        <v>50925</v>
       </c>
       <c r="J17" t="n">
-        <v>51968.75</v>
+        <v>50987.25</v>
       </c>
       <c r="K17" t="n">
-        <v>52219.5</v>
+        <v>51496.5</v>
       </c>
       <c r="L17" t="n">
-        <v>52470.25</v>
+        <v>52005.75</v>
       </c>
       <c r="M17" t="n">
-        <v>52678.5</v>
+        <v>52291.5</v>
       </c>
       <c r="N17" t="n">
-        <v>52886.75</v>
+        <v>52577.25</v>
       </c>
       <c r="O17" t="n">
-        <v>53180</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
+        <v>53310</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
       <c r="U17" s="8" t="n">
         <v/>
       </c>
@@ -1967,55 +1959,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>51920</v>
+        <v>52299</v>
       </c>
       <c r="C18" t="n">
-        <v>52314</v>
+        <v>52790</v>
       </c>
       <c r="D18" t="n">
-        <v>51846</v>
+        <v>52173</v>
       </c>
       <c r="E18" t="n">
-        <v>52124</v>
+        <v>52382</v>
       </c>
       <c r="F18" t="n">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0049</v>
       </c>
       <c r="H18" t="n">
-        <v>468</v>
+        <v>617</v>
       </c>
       <c r="I18" t="n">
-        <v>50925</v>
+        <v>51378</v>
       </c>
       <c r="J18" t="n">
-        <v>50987.25</v>
+        <v>51678</v>
       </c>
       <c r="K18" t="n">
-        <v>51496.5</v>
+        <v>51890</v>
       </c>
       <c r="L18" t="n">
-        <v>52005.75</v>
+        <v>52102</v>
       </c>
       <c r="M18" t="n">
-        <v>52291.5</v>
+        <v>52358</v>
       </c>
       <c r="N18" t="n">
-        <v>52577.25</v>
+        <v>52614</v>
       </c>
       <c r="O18" t="n">
-        <v>53310</v>
+        <v>52782</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2028,19 +2024,23 @@
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W18" s="11" t="inlineStr">
         <is>
@@ -2049,57 +2049,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>52299</v>
+        <v>52405</v>
       </c>
       <c r="C19" t="n">
-        <v>52790</v>
+        <v>53105</v>
       </c>
       <c r="D19" t="n">
-        <v>52173</v>
+        <v>52290</v>
       </c>
       <c r="E19" t="n">
-        <v>52382</v>
+        <v>52944</v>
       </c>
       <c r="F19" t="n">
-        <v>258</v>
+        <v>562</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0107</v>
       </c>
       <c r="H19" t="n">
-        <v>617</v>
+        <v>815</v>
       </c>
       <c r="I19" t="n">
-        <v>51378</v>
+        <v>51556</v>
       </c>
       <c r="J19" t="n">
-        <v>51678</v>
+        <v>51715.25</v>
       </c>
       <c r="K19" t="n">
-        <v>51890</v>
+        <v>52073.5</v>
       </c>
       <c r="L19" t="n">
-        <v>52102</v>
+        <v>52431.75</v>
       </c>
       <c r="M19" t="n">
-        <v>52358</v>
+        <v>52690.5</v>
       </c>
       <c r="N19" t="n">
-        <v>52614</v>
+        <v>52949.25</v>
       </c>
       <c r="O19" t="n">
-        <v>52782</v>
+        <v>53407</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2117,18 +2117,16 @@
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V19" s="8" t="n">
+        <v/>
       </c>
       <c r="W19" s="11" t="inlineStr">
         <is>
@@ -2144,74 +2142,76 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>52405</v>
+        <v>52915</v>
       </c>
       <c r="C20" t="n">
-        <v>53105</v>
+        <v>53033</v>
       </c>
       <c r="D20" t="n">
-        <v>52290</v>
+        <v>51630</v>
       </c>
       <c r="E20" t="n">
-        <v>52944</v>
+        <v>51765</v>
       </c>
       <c r="F20" t="n">
-        <v>562</v>
+        <v>-1179</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0223</v>
       </c>
       <c r="H20" t="n">
-        <v>815</v>
+        <v>1403</v>
       </c>
       <c r="I20" t="n">
-        <v>51556</v>
+        <v>51475</v>
       </c>
       <c r="J20" t="n">
-        <v>51715.25</v>
+        <v>52252.25</v>
       </c>
       <c r="K20" t="n">
-        <v>52073.5</v>
+        <v>52536.5</v>
       </c>
       <c r="L20" t="n">
-        <v>52431.75</v>
+        <v>52820.75</v>
       </c>
       <c r="M20" t="n">
-        <v>52690.5</v>
+        <v>53351.5</v>
       </c>
       <c r="N20" t="n">
-        <v>52949.25</v>
+        <v>53882.25</v>
       </c>
       <c r="O20" t="n">
-        <v>53407</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
+        <v>53920</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2221,83 +2221,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>52915</v>
+        <v>51759</v>
       </c>
       <c r="C21" t="n">
-        <v>53033</v>
+        <v>52484</v>
       </c>
       <c r="D21" t="n">
-        <v>51630</v>
+        <v>51732</v>
       </c>
       <c r="E21" t="n">
-        <v>51765</v>
+        <v>52380</v>
       </c>
       <c r="F21" t="n">
-        <v>-1179</v>
+        <v>615</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0119</v>
       </c>
       <c r="H21" t="n">
-        <v>1403</v>
+        <v>752</v>
       </c>
       <c r="I21" t="n">
-        <v>51475</v>
+        <v>50227</v>
       </c>
       <c r="J21" t="n">
-        <v>52252.25</v>
+        <v>50078.75</v>
       </c>
       <c r="K21" t="n">
-        <v>52536.5</v>
+        <v>51063.5</v>
       </c>
       <c r="L21" t="n">
-        <v>52820.75</v>
+        <v>52048.25</v>
       </c>
       <c r="M21" t="n">
-        <v>53351.5</v>
+        <v>52466.5</v>
       </c>
       <c r="N21" t="n">
-        <v>53882.25</v>
+        <v>52884.75</v>
       </c>
       <c r="O21" t="n">
-        <v>53920</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
+        <v>54436</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
@@ -2309,55 +2301,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>51759</v>
+        <v>52395</v>
       </c>
       <c r="C22" t="n">
-        <v>52484</v>
+        <v>52772</v>
       </c>
       <c r="D22" t="n">
-        <v>51732</v>
+        <v>52124</v>
       </c>
       <c r="E22" t="n">
-        <v>52380</v>
+        <v>52635</v>
       </c>
       <c r="F22" t="n">
-        <v>615</v>
+        <v>255</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0119</v>
+        <v>0.0049</v>
       </c>
       <c r="H22" t="n">
-        <v>752</v>
+        <v>648</v>
       </c>
       <c r="I22" t="n">
-        <v>50227</v>
+        <v>50980</v>
       </c>
       <c r="J22" t="n">
-        <v>50078.75</v>
+        <v>51764</v>
       </c>
       <c r="K22" t="n">
-        <v>51063.5</v>
+        <v>52004</v>
       </c>
       <c r="L22" t="n">
-        <v>52048.25</v>
+        <v>52244</v>
       </c>
       <c r="M22" t="n">
-        <v>52466.5</v>
+        <v>52756</v>
       </c>
       <c r="N22" t="n">
-        <v>52884.75</v>
+        <v>53268</v>
       </c>
       <c r="O22" t="n">
-        <v>54436</v>
+        <v>53236</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2391,57 +2387,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>52395</v>
+        <v>52780</v>
       </c>
       <c r="C23" t="n">
-        <v>52772</v>
+        <v>53414</v>
       </c>
       <c r="D23" t="n">
-        <v>52124</v>
+        <v>52777</v>
       </c>
       <c r="E23" t="n">
-        <v>52635</v>
+        <v>53334</v>
       </c>
       <c r="F23" t="n">
-        <v>255</v>
+        <v>699</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0133</v>
       </c>
       <c r="H23" t="n">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="I23" t="n">
-        <v>50980</v>
+        <v>51476</v>
       </c>
       <c r="J23" t="n">
-        <v>51764</v>
+        <v>52080.5</v>
       </c>
       <c r="K23" t="n">
-        <v>52004</v>
+        <v>52311</v>
       </c>
       <c r="L23" t="n">
-        <v>52244</v>
+        <v>52541.5</v>
       </c>
       <c r="M23" t="n">
-        <v>52756</v>
+        <v>52959</v>
       </c>
       <c r="N23" t="n">
-        <v>53268</v>
+        <v>53376.5</v>
       </c>
       <c r="O23" t="n">
-        <v>53236</v>
+        <v>53420</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2459,11 +2455,13 @@
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2482,50 +2480,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>52780</v>
+        <v>53381</v>
       </c>
       <c r="C24" t="n">
-        <v>53414</v>
+        <v>54423</v>
       </c>
       <c r="D24" t="n">
-        <v>52777</v>
+        <v>53267</v>
       </c>
       <c r="E24" t="n">
-        <v>53334</v>
+        <v>54268</v>
       </c>
       <c r="F24" t="n">
-        <v>699</v>
+        <v>934</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0175</v>
       </c>
       <c r="H24" t="n">
-        <v>637</v>
+        <v>1156</v>
       </c>
       <c r="I24" t="n">
-        <v>51476</v>
+        <v>52140</v>
       </c>
       <c r="J24" t="n">
-        <v>52080.5</v>
+        <v>52816.25</v>
       </c>
       <c r="K24" t="n">
-        <v>52311</v>
+        <v>53015.5</v>
       </c>
       <c r="L24" t="n">
-        <v>52541.5</v>
+        <v>53214.75</v>
       </c>
       <c r="M24" t="n">
-        <v>52959</v>
+        <v>53652.5</v>
       </c>
       <c r="N24" t="n">
-        <v>53376.5</v>
+        <v>54090.25</v>
       </c>
       <c r="O24" t="n">
-        <v>53420</v>
+        <v>54051</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2551,67 +2549,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W24" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W24" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>53381</v>
+        <v>54369</v>
       </c>
       <c r="C25" t="n">
-        <v>54423</v>
+        <v>54884</v>
       </c>
       <c r="D25" t="n">
-        <v>53267</v>
+        <v>54342</v>
       </c>
       <c r="E25" t="n">
-        <v>54268</v>
+        <v>54494</v>
       </c>
       <c r="F25" t="n">
-        <v>934</v>
+        <v>226</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0042</v>
       </c>
       <c r="H25" t="n">
-        <v>1156</v>
+        <v>542</v>
       </c>
       <c r="I25" t="n">
-        <v>52140</v>
+        <v>52111</v>
       </c>
       <c r="J25" t="n">
-        <v>52816.25</v>
+        <v>53323.5</v>
       </c>
       <c r="K25" t="n">
-        <v>53015.5</v>
+        <v>53690</v>
       </c>
       <c r="L25" t="n">
-        <v>53214.75</v>
+        <v>54056.5</v>
       </c>
       <c r="M25" t="n">
-        <v>53652.5</v>
+        <v>54846</v>
       </c>
       <c r="N25" t="n">
-        <v>54090.25</v>
+        <v>55635.5</v>
       </c>
       <c r="O25" t="n">
-        <v>54051</v>
+        <v>55579</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2629,18 +2625,14 @@
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
@@ -2652,70 +2644,72 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>54369</v>
+        <v>54555</v>
       </c>
       <c r="C26" t="n">
-        <v>54884</v>
+        <v>54678</v>
       </c>
       <c r="D26" t="n">
-        <v>54342</v>
+        <v>53952</v>
       </c>
       <c r="E26" t="n">
-        <v>54494</v>
+        <v>54013</v>
       </c>
       <c r="F26" t="n">
-        <v>226</v>
+        <v>-481</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>542</v>
+        <v>726</v>
       </c>
       <c r="I26" t="n">
-        <v>52111</v>
+        <v>53800</v>
       </c>
       <c r="J26" t="n">
-        <v>53323.5</v>
+        <v>53892.5</v>
       </c>
       <c r="K26" t="n">
-        <v>53690</v>
+        <v>54223</v>
       </c>
       <c r="L26" t="n">
-        <v>54056.5</v>
+        <v>54553.5</v>
       </c>
       <c r="M26" t="n">
-        <v>54846</v>
+        <v>54765</v>
       </c>
       <c r="N26" t="n">
-        <v>55635.5</v>
+        <v>54976.5</v>
       </c>
       <c r="O26" t="n">
-        <v>55579</v>
+        <v>55426</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
+      <c r="Q26" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
       <c r="U26" s="8" t="n">
         <v/>
       </c>
@@ -2727,72 +2721,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>54555</v>
+        <v>54040</v>
       </c>
       <c r="C27" t="n">
-        <v>54678</v>
+        <v>54202</v>
       </c>
       <c r="D27" t="n">
-        <v>53952</v>
+        <v>53879</v>
       </c>
       <c r="E27" t="n">
-        <v>54013</v>
+        <v>54152</v>
       </c>
       <c r="F27" t="n">
-        <v>-481</v>
+        <v>139</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0026</v>
       </c>
       <c r="H27" t="n">
-        <v>726</v>
+        <v>323</v>
       </c>
       <c r="I27" t="n">
-        <v>53800</v>
+        <v>53226</v>
       </c>
       <c r="J27" t="n">
-        <v>53892.5</v>
+        <v>53136</v>
       </c>
       <c r="K27" t="n">
-        <v>54223</v>
+        <v>53650</v>
       </c>
       <c r="L27" t="n">
-        <v>54553.5</v>
+        <v>54164</v>
       </c>
       <c r="M27" t="n">
-        <v>54765</v>
+        <v>54376</v>
       </c>
       <c r="N27" t="n">
-        <v>54976.5</v>
+        <v>54588</v>
       </c>
       <c r="O27" t="n">
-        <v>55426</v>
+        <v>55404</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2811,57 +2805,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>54040</v>
+        <v>54133</v>
       </c>
       <c r="C28" t="n">
-        <v>54202</v>
+        <v>54170</v>
       </c>
       <c r="D28" t="n">
-        <v>53879</v>
+        <v>53952</v>
       </c>
       <c r="E28" t="n">
-        <v>54152</v>
+        <v>54063</v>
       </c>
       <c r="F28" t="n">
-        <v>139</v>
+        <v>-89</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0016</v>
       </c>
       <c r="H28" t="n">
-        <v>323</v>
+        <v>218</v>
       </c>
       <c r="I28" t="n">
-        <v>53226</v>
+        <v>53556</v>
       </c>
       <c r="J28" t="n">
-        <v>53136</v>
+        <v>53884.75</v>
       </c>
       <c r="K28" t="n">
-        <v>53650</v>
+        <v>53990.5</v>
       </c>
       <c r="L28" t="n">
-        <v>54164</v>
+        <v>54096.25</v>
       </c>
       <c r="M28" t="n">
-        <v>54376</v>
+        <v>54313.5</v>
       </c>
       <c r="N28" t="n">
-        <v>54588</v>
+        <v>54530.75</v>
       </c>
       <c r="O28" t="n">
-        <v>55404</v>
+        <v>54525</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2869,8 +2863,10 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
@@ -2900,56 +2896,58 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>54133</v>
+        <v>54049</v>
       </c>
       <c r="C29" t="n">
-        <v>54170</v>
+        <v>54336</v>
       </c>
       <c r="D29" t="n">
-        <v>53952</v>
+        <v>53855</v>
       </c>
       <c r="E29" t="n">
-        <v>54063</v>
+        <v>53880</v>
       </c>
       <c r="F29" t="n">
-        <v>-89</v>
+        <v>-183</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0034</v>
       </c>
       <c r="H29" t="n">
-        <v>218</v>
+        <v>481</v>
       </c>
       <c r="I29" t="n">
-        <v>53556</v>
+        <v>53734</v>
       </c>
       <c r="J29" t="n">
-        <v>53884.75</v>
+        <v>53846</v>
       </c>
       <c r="K29" t="n">
-        <v>53990.5</v>
+        <v>53954</v>
       </c>
       <c r="L29" t="n">
-        <v>54096.25</v>
+        <v>54062</v>
       </c>
       <c r="M29" t="n">
-        <v>54313.5</v>
+        <v>54172</v>
       </c>
       <c r="N29" t="n">
-        <v>54530.75</v>
+        <v>54282</v>
       </c>
       <c r="O29" t="n">
-        <v>54525</v>
+        <v>54388</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
@@ -2958,14 +2956,18 @@
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2984,78 +2986,72 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>54049</v>
+        <v>53903</v>
       </c>
       <c r="C30" t="n">
-        <v>54336</v>
+        <v>54150</v>
       </c>
       <c r="D30" t="n">
-        <v>53855</v>
+        <v>53830</v>
       </c>
       <c r="E30" t="n">
-        <v>53880</v>
+        <v>53871</v>
       </c>
       <c r="F30" t="n">
-        <v>-183</v>
+        <v>-9</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0002</v>
       </c>
       <c r="H30" t="n">
-        <v>481</v>
+        <v>320</v>
       </c>
       <c r="I30" t="n">
-        <v>53734</v>
+        <v>53374</v>
       </c>
       <c r="J30" t="n">
-        <v>53846</v>
+        <v>53291.25</v>
       </c>
       <c r="K30" t="n">
-        <v>53954</v>
+        <v>53639.5</v>
       </c>
       <c r="L30" t="n">
-        <v>54062</v>
+        <v>53987.75</v>
       </c>
       <c r="M30" t="n">
-        <v>54172</v>
+        <v>54120.5</v>
       </c>
       <c r="N30" t="n">
-        <v>54282</v>
+        <v>54253.25</v>
       </c>
       <c r="O30" t="n">
-        <v>54388</v>
+        <v>54817</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3067,57 +3063,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>53903</v>
+        <v>53905</v>
       </c>
       <c r="C31" t="n">
-        <v>54150</v>
+        <v>54149</v>
       </c>
       <c r="D31" t="n">
-        <v>53830</v>
+        <v>53715</v>
       </c>
       <c r="E31" t="n">
-        <v>53871</v>
+        <v>53935</v>
       </c>
       <c r="F31" t="n">
-        <v>-9</v>
+        <v>64</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0012</v>
       </c>
       <c r="H31" t="n">
-        <v>320</v>
+        <v>434</v>
       </c>
       <c r="I31" t="n">
-        <v>53374</v>
+        <v>53510</v>
       </c>
       <c r="J31" t="n">
-        <v>53291.25</v>
+        <v>53491.5</v>
       </c>
       <c r="K31" t="n">
-        <v>53639.5</v>
+        <v>53711</v>
       </c>
       <c r="L31" t="n">
-        <v>53987.75</v>
+        <v>53930.5</v>
       </c>
       <c r="M31" t="n">
-        <v>54120.5</v>
+        <v>54031</v>
       </c>
       <c r="N31" t="n">
-        <v>54253.25</v>
+        <v>54131.5</v>
       </c>
       <c r="O31" t="n">
-        <v>54817</v>
+        <v>54470</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3128,9 +3124,9 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
@@ -3138,8 +3134,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U31" s="8" t="n">
-        <v/>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3151,57 +3149,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>53905</v>
+        <v>53961</v>
       </c>
       <c r="C32" t="n">
-        <v>54149</v>
+        <v>53999</v>
       </c>
       <c r="D32" t="n">
-        <v>53715</v>
+        <v>53745</v>
       </c>
       <c r="E32" t="n">
-        <v>53935</v>
+        <v>53807</v>
       </c>
       <c r="F32" t="n">
-        <v>64</v>
+        <v>-128</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0024</v>
       </c>
       <c r="H32" t="n">
-        <v>434</v>
+        <v>254</v>
       </c>
       <c r="I32" t="n">
-        <v>53510</v>
+        <v>53281</v>
       </c>
       <c r="J32" t="n">
-        <v>53491.5</v>
+        <v>53502.5</v>
       </c>
       <c r="K32" t="n">
-        <v>53711</v>
+        <v>53718</v>
       </c>
       <c r="L32" t="n">
-        <v>53930.5</v>
+        <v>53933.5</v>
       </c>
       <c r="M32" t="n">
-        <v>54031</v>
+        <v>54152</v>
       </c>
       <c r="N32" t="n">
-        <v>54131.5</v>
+        <v>54370.5</v>
       </c>
       <c r="O32" t="n">
-        <v>54470</v>
+        <v>54583</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3209,23 +3207,21 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3244,60 +3240,64 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>53961</v>
+        <v>53790</v>
       </c>
       <c r="C33" t="n">
-        <v>53999</v>
+        <v>53840</v>
       </c>
       <c r="D33" t="n">
-        <v>53745</v>
+        <v>53464</v>
       </c>
       <c r="E33" t="n">
-        <v>53807</v>
+        <v>53544</v>
       </c>
       <c r="F33" t="n">
-        <v>-128</v>
+        <v>-263</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0049</v>
       </c>
       <c r="H33" t="n">
-        <v>254</v>
+        <v>376</v>
       </c>
       <c r="I33" t="n">
-        <v>53281</v>
+        <v>53491</v>
       </c>
       <c r="J33" t="n">
-        <v>53502.5</v>
+        <v>53520.5</v>
       </c>
       <c r="K33" t="n">
-        <v>53718</v>
+        <v>53680</v>
       </c>
       <c r="L33" t="n">
-        <v>53933.5</v>
+        <v>53839.5</v>
       </c>
       <c r="M33" t="n">
-        <v>54152</v>
+        <v>53934</v>
       </c>
       <c r="N33" t="n">
-        <v>54370.5</v>
+        <v>54028.5</v>
       </c>
       <c r="O33" t="n">
-        <v>54583</v>
-      </c>
-      <c r="P33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
+        <v>54253</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S33" s="10" t="inlineStr">
@@ -3321,71 +3321,67 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>53790</v>
+        <v>53501</v>
       </c>
       <c r="C34" t="n">
-        <v>53840</v>
+        <v>53594</v>
       </c>
       <c r="D34" t="n">
-        <v>53464</v>
+        <v>53311</v>
       </c>
       <c r="E34" t="n">
-        <v>53544</v>
+        <v>53403</v>
       </c>
       <c r="F34" t="n">
-        <v>-263</v>
+        <v>-141</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0026</v>
       </c>
       <c r="H34" t="n">
-        <v>376</v>
+        <v>283</v>
       </c>
       <c r="I34" t="n">
-        <v>53491</v>
+        <v>53088</v>
       </c>
       <c r="J34" t="n">
-        <v>53520.5</v>
+        <v>53114</v>
       </c>
       <c r="K34" t="n">
-        <v>53680</v>
+        <v>53356</v>
       </c>
       <c r="L34" t="n">
-        <v>53839.5</v>
+        <v>53598</v>
       </c>
       <c r="M34" t="n">
-        <v>53934</v>
+        <v>53732</v>
       </c>
       <c r="N34" t="n">
-        <v>54028.5</v>
+        <v>53866</v>
       </c>
       <c r="O34" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q34" s="6" t="inlineStr">
+        <v>54216</v>
+      </c>
+      <c r="P34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
@@ -3416,50 +3412,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>53501</v>
+        <v>53408</v>
       </c>
       <c r="C35" t="n">
-        <v>53594</v>
+        <v>53780</v>
       </c>
       <c r="D35" t="n">
-        <v>53311</v>
+        <v>53337</v>
       </c>
       <c r="E35" t="n">
-        <v>53403</v>
+        <v>53530</v>
       </c>
       <c r="F35" t="n">
-        <v>-141</v>
+        <v>127</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0026</v>
+        <v>0.0024</v>
       </c>
       <c r="H35" t="n">
-        <v>283</v>
+        <v>443</v>
       </c>
       <c r="I35" t="n">
-        <v>53088</v>
+        <v>53028</v>
       </c>
       <c r="J35" t="n">
-        <v>53114</v>
+        <v>53095.25</v>
       </c>
       <c r="K35" t="n">
-        <v>53356</v>
+        <v>53261.5</v>
       </c>
       <c r="L35" t="n">
-        <v>53598</v>
+        <v>53427.75</v>
       </c>
       <c r="M35" t="n">
-        <v>53732</v>
+        <v>53544.5</v>
       </c>
       <c r="N35" t="n">
-        <v>53866</v>
+        <v>53661.25</v>
       </c>
       <c r="O35" t="n">
-        <v>54216</v>
+        <v>53877</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3467,21 +3463,23 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3491,90 +3489,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>53408</v>
+        <v>53529</v>
       </c>
       <c r="C36" t="n">
-        <v>53780</v>
+        <v>53589</v>
       </c>
       <c r="D36" t="n">
-        <v>53337</v>
+        <v>52812</v>
       </c>
       <c r="E36" t="n">
-        <v>53530</v>
+        <v>52849</v>
       </c>
       <c r="F36" t="n">
-        <v>127</v>
+        <v>-681</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0127</v>
       </c>
       <c r="H36" t="n">
-        <v>443</v>
+        <v>777</v>
       </c>
       <c r="I36" t="n">
-        <v>53028</v>
+        <v>52894</v>
       </c>
       <c r="J36" t="n">
-        <v>53095.25</v>
+        <v>53072.75</v>
       </c>
       <c r="K36" t="n">
-        <v>53261.5</v>
+        <v>53308.5</v>
       </c>
       <c r="L36" t="n">
-        <v>53427.75</v>
+        <v>53544.25</v>
       </c>
       <c r="M36" t="n">
-        <v>53544.5</v>
+        <v>53751.5</v>
       </c>
       <c r="N36" t="n">
-        <v>53661.25</v>
+        <v>53958.75</v>
       </c>
       <c r="O36" t="n">
-        <v>53877</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
+        <v>54223</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U36" s="8" t="inlineStr">
+      <c r="Q36" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W36" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr"/>
@@ -3582,77 +3578,75 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>53529</v>
+        <v>52876</v>
       </c>
       <c r="C37" t="n">
-        <v>53589</v>
+        <v>53418</v>
       </c>
       <c r="D37" t="n">
-        <v>52812</v>
+        <v>52838</v>
       </c>
       <c r="E37" t="n">
-        <v>52849</v>
+        <v>53353</v>
       </c>
       <c r="F37" t="n">
-        <v>-681</v>
+        <v>504</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0095</v>
       </c>
       <c r="H37" t="n">
-        <v>777</v>
+        <v>580</v>
       </c>
       <c r="I37" t="n">
-        <v>52894</v>
+        <v>52035</v>
       </c>
       <c r="J37" t="n">
-        <v>53072.75</v>
+        <v>51896.25</v>
       </c>
       <c r="K37" t="n">
-        <v>53308.5</v>
+        <v>52460.5</v>
       </c>
       <c r="L37" t="n">
-        <v>53544.25</v>
+        <v>53024.75</v>
       </c>
       <c r="M37" t="n">
-        <v>53751.5</v>
+        <v>53237.5</v>
       </c>
       <c r="N37" t="n">
-        <v>53958.75</v>
+        <v>53450.25</v>
       </c>
       <c r="O37" t="n">
-        <v>54223</v>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
+        <v>54366</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
@@ -3661,55 +3655,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>52876</v>
+        <v>53367</v>
       </c>
       <c r="C38" t="n">
-        <v>53418</v>
+        <v>53567</v>
       </c>
       <c r="D38" t="n">
-        <v>52838</v>
+        <v>53210</v>
       </c>
       <c r="E38" t="n">
-        <v>53353</v>
+        <v>53489</v>
       </c>
       <c r="F38" t="n">
-        <v>504</v>
+        <v>136</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.0025</v>
       </c>
       <c r="H38" t="n">
-        <v>580</v>
+        <v>357</v>
       </c>
       <c r="I38" t="n">
-        <v>52035</v>
+        <v>52258</v>
       </c>
       <c r="J38" t="n">
-        <v>51896.25</v>
+        <v>52885.5</v>
       </c>
       <c r="K38" t="n">
-        <v>52460.5</v>
+        <v>53063</v>
       </c>
       <c r="L38" t="n">
-        <v>53024.75</v>
+        <v>53240.5</v>
       </c>
       <c r="M38" t="n">
-        <v>53237.5</v>
+        <v>53643</v>
       </c>
       <c r="N38" t="n">
-        <v>53450.25</v>
+        <v>54045.5</v>
       </c>
       <c r="O38" t="n">
-        <v>54366</v>
+        <v>53998</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3727,14 +3725,12 @@
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
@@ -3745,57 +3741,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>53367</v>
+        <v>53524</v>
       </c>
       <c r="C39" t="n">
-        <v>53567</v>
+        <v>53797</v>
       </c>
       <c r="D39" t="n">
-        <v>53210</v>
+        <v>53426</v>
       </c>
       <c r="E39" t="n">
-        <v>53489</v>
+        <v>53645</v>
       </c>
       <c r="F39" t="n">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0029</v>
       </c>
       <c r="H39" t="n">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="I39" t="n">
-        <v>52258</v>
+        <v>52853</v>
       </c>
       <c r="J39" t="n">
-        <v>52885.5</v>
+        <v>53182.25</v>
       </c>
       <c r="K39" t="n">
-        <v>53063</v>
+        <v>53310.5</v>
       </c>
       <c r="L39" t="n">
-        <v>53240.5</v>
+        <v>53438.75</v>
       </c>
       <c r="M39" t="n">
-        <v>53643</v>
+        <v>53667.5</v>
       </c>
       <c r="N39" t="n">
-        <v>54045.5</v>
+        <v>53896.25</v>
       </c>
       <c r="O39" t="n">
-        <v>53998</v>
+        <v>53924</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3836,50 +3832,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>53524</v>
+        <v>53643</v>
       </c>
       <c r="C40" t="n">
-        <v>53797</v>
+        <v>53778</v>
       </c>
       <c r="D40" t="n">
-        <v>53426</v>
+        <v>53435</v>
       </c>
       <c r="E40" t="n">
-        <v>53645</v>
+        <v>53521</v>
       </c>
       <c r="F40" t="n">
-        <v>156</v>
+        <v>-124</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0023</v>
       </c>
       <c r="H40" t="n">
-        <v>371</v>
+        <v>343</v>
       </c>
       <c r="I40" t="n">
-        <v>52853</v>
+        <v>53055</v>
       </c>
       <c r="J40" t="n">
-        <v>53182.25</v>
+        <v>53290.75</v>
       </c>
       <c r="K40" t="n">
-        <v>53310.5</v>
+        <v>53459.5</v>
       </c>
       <c r="L40" t="n">
-        <v>53438.75</v>
+        <v>53628.25</v>
       </c>
       <c r="M40" t="n">
-        <v>53667.5</v>
+        <v>53830.5</v>
       </c>
       <c r="N40" t="n">
-        <v>53896.25</v>
+        <v>54032.75</v>
       </c>
       <c r="O40" t="n">
-        <v>53924</v>
+        <v>54168</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3887,19 +3883,19 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
+      <c r="R40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
@@ -3913,57 +3909,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>53643</v>
+        <v>53724</v>
       </c>
       <c r="C41" t="n">
-        <v>53778</v>
+        <v>53811</v>
       </c>
       <c r="D41" t="n">
-        <v>53435</v>
+        <v>53369</v>
       </c>
       <c r="E41" t="n">
-        <v>53521</v>
+        <v>53621</v>
       </c>
       <c r="F41" t="n">
-        <v>-124</v>
+        <v>100</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0019</v>
       </c>
       <c r="H41" t="n">
-        <v>343</v>
+        <v>442</v>
       </c>
       <c r="I41" t="n">
-        <v>53055</v>
+        <v>53092</v>
       </c>
       <c r="J41" t="n">
-        <v>53290.75</v>
+        <v>53135.25</v>
       </c>
       <c r="K41" t="n">
-        <v>53459.5</v>
+        <v>53349.5</v>
       </c>
       <c r="L41" t="n">
-        <v>53628.25</v>
+        <v>53563.75</v>
       </c>
       <c r="M41" t="n">
-        <v>53830.5</v>
+        <v>53692.5</v>
       </c>
       <c r="N41" t="n">
-        <v>54032.75</v>
+        <v>53821.25</v>
       </c>
       <c r="O41" t="n">
-        <v>54168</v>
+        <v>54121</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3971,18 +3967,18 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3997,57 +3993,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>53724</v>
+        <v>53608</v>
       </c>
       <c r="C42" t="n">
-        <v>53811</v>
+        <v>53862</v>
       </c>
       <c r="D42" t="n">
-        <v>53369</v>
+        <v>53513</v>
       </c>
       <c r="E42" t="n">
-        <v>53621</v>
+        <v>53584</v>
       </c>
       <c r="F42" t="n">
-        <v>100</v>
+        <v>-37</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0007</v>
       </c>
       <c r="H42" t="n">
-        <v>442</v>
+        <v>349</v>
       </c>
       <c r="I42" t="n">
-        <v>53092</v>
+        <v>52927</v>
       </c>
       <c r="J42" t="n">
-        <v>53135.25</v>
+        <v>53194.5</v>
       </c>
       <c r="K42" t="n">
-        <v>53349.5</v>
+        <v>53400</v>
       </c>
       <c r="L42" t="n">
-        <v>53563.75</v>
+        <v>53605.5</v>
       </c>
       <c r="M42" t="n">
-        <v>53692.5</v>
+        <v>53842</v>
       </c>
       <c r="N42" t="n">
-        <v>53821.25</v>
+        <v>54078.5</v>
       </c>
       <c r="O42" t="n">
-        <v>54121</v>
+        <v>54253</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4058,9 +4054,9 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
@@ -4088,69 +4084,73 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>53608</v>
+        <v>53664</v>
       </c>
       <c r="C43" t="n">
-        <v>53862</v>
+        <v>53664</v>
       </c>
       <c r="D43" t="n">
-        <v>53513</v>
+        <v>53149</v>
       </c>
       <c r="E43" t="n">
-        <v>53584</v>
+        <v>53240</v>
       </c>
       <c r="F43" t="n">
-        <v>-37</v>
+        <v>-344</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0064</v>
       </c>
       <c r="H43" t="n">
-        <v>349</v>
+        <v>515</v>
       </c>
       <c r="I43" t="n">
-        <v>52927</v>
+        <v>53164</v>
       </c>
       <c r="J43" t="n">
-        <v>53194.5</v>
+        <v>53183.25</v>
       </c>
       <c r="K43" t="n">
-        <v>53400</v>
+        <v>53409.5</v>
       </c>
       <c r="L43" t="n">
-        <v>53605.5</v>
+        <v>53635.75</v>
       </c>
       <c r="M43" t="n">
-        <v>53842</v>
+        <v>53758.5</v>
       </c>
       <c r="N43" t="n">
-        <v>54078.5</v>
+        <v>53881.25</v>
       </c>
       <c r="O43" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+        <v>54211</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4163,73 +4163,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>53664</v>
+        <v>53259</v>
       </c>
       <c r="C44" t="n">
-        <v>53664</v>
+        <v>53343</v>
       </c>
       <c r="D44" t="n">
-        <v>53149</v>
+        <v>52747</v>
       </c>
       <c r="E44" t="n">
-        <v>53240</v>
+        <v>52828</v>
       </c>
       <c r="F44" t="n">
-        <v>-344</v>
+        <v>-412</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0064</v>
+        <v>-0.0077</v>
       </c>
       <c r="H44" t="n">
-        <v>515</v>
+        <v>596</v>
       </c>
       <c r="I44" t="n">
-        <v>53164</v>
+        <v>52634</v>
       </c>
       <c r="J44" t="n">
-        <v>53183.25</v>
+        <v>52641.75</v>
       </c>
       <c r="K44" t="n">
-        <v>53409.5</v>
+        <v>52982.5</v>
       </c>
       <c r="L44" t="n">
-        <v>53635.75</v>
+        <v>53323.25</v>
       </c>
       <c r="M44" t="n">
-        <v>53758.5</v>
+        <v>53497.5</v>
       </c>
       <c r="N44" t="n">
-        <v>53881.25</v>
+        <v>53671.75</v>
       </c>
       <c r="O44" t="n">
-        <v>54211</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
+        <v>54179</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
@@ -4256,50 +4248,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>53259</v>
+        <v>52844</v>
       </c>
       <c r="C45" t="n">
-        <v>53343</v>
+        <v>53283</v>
       </c>
       <c r="D45" t="n">
-        <v>52747</v>
+        <v>52720</v>
       </c>
       <c r="E45" t="n">
-        <v>52828</v>
+        <v>53121</v>
       </c>
       <c r="F45" t="n">
-        <v>-412</v>
+        <v>293</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0077</v>
+        <v>0.0055</v>
       </c>
       <c r="H45" t="n">
-        <v>596</v>
+        <v>563</v>
       </c>
       <c r="I45" t="n">
-        <v>52634</v>
+        <v>52151</v>
       </c>
       <c r="J45" t="n">
-        <v>52641.75</v>
+        <v>52123.5</v>
       </c>
       <c r="K45" t="n">
-        <v>52982.5</v>
+        <v>52530</v>
       </c>
       <c r="L45" t="n">
-        <v>53323.25</v>
+        <v>52936.5</v>
       </c>
       <c r="M45" t="n">
-        <v>53497.5</v>
+        <v>53126</v>
       </c>
       <c r="N45" t="n">
-        <v>53671.75</v>
+        <v>53315.5</v>
       </c>
       <c r="O45" t="n">
-        <v>54179</v>
+        <v>53939</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4307,19 +4299,19 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
@@ -4331,55 +4323,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>52844</v>
+        <v>53120</v>
       </c>
       <c r="C46" t="n">
-        <v>53283</v>
+        <v>53827</v>
       </c>
       <c r="D46" t="n">
-        <v>52720</v>
+        <v>53093</v>
       </c>
       <c r="E46" t="n">
-        <v>53121</v>
+        <v>53745</v>
       </c>
       <c r="F46" t="n">
-        <v>293</v>
+        <v>624</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0117</v>
       </c>
       <c r="H46" t="n">
-        <v>563</v>
+        <v>734</v>
       </c>
       <c r="I46" t="n">
-        <v>52151</v>
+        <v>52157</v>
       </c>
       <c r="J46" t="n">
-        <v>52123.5</v>
+        <v>52617.75</v>
       </c>
       <c r="K46" t="n">
-        <v>52530</v>
+        <v>52839.5</v>
       </c>
       <c r="L46" t="n">
-        <v>52936.5</v>
+        <v>53061.25</v>
       </c>
       <c r="M46" t="n">
-        <v>53126</v>
+        <v>53402.5</v>
       </c>
       <c r="N46" t="n">
-        <v>53315.5</v>
+        <v>53743.75</v>
       </c>
       <c r="O46" t="n">
-        <v>53939</v>
+        <v>53846</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4397,73 +4393,71 @@
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W46" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>53120</v>
+        <v>53707</v>
       </c>
       <c r="C47" t="n">
-        <v>53827</v>
+        <v>53772</v>
       </c>
       <c r="D47" t="n">
-        <v>53093</v>
+        <v>53235</v>
       </c>
       <c r="E47" t="n">
-        <v>53745</v>
+        <v>53440</v>
       </c>
       <c r="F47" t="n">
-        <v>624</v>
+        <v>-305</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0117</v>
+        <v>-0.0057</v>
       </c>
       <c r="H47" t="n">
-        <v>734</v>
+        <v>537</v>
       </c>
       <c r="I47" t="n">
-        <v>52157</v>
+        <v>52359</v>
       </c>
       <c r="J47" t="n">
-        <v>52617.75</v>
+        <v>53153.5</v>
       </c>
       <c r="K47" t="n">
-        <v>52839.5</v>
+        <v>53378</v>
       </c>
       <c r="L47" t="n">
-        <v>53061.25</v>
+        <v>53602.5</v>
       </c>
       <c r="M47" t="n">
-        <v>53402.5</v>
+        <v>54112</v>
       </c>
       <c r="N47" t="n">
-        <v>53743.75</v>
+        <v>54621.5</v>
       </c>
       <c r="O47" t="n">
-        <v>53846</v>
+        <v>54561</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4471,24 +4465,22 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
+      <c r="R47" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
@@ -4497,65 +4489,71 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>53707</v>
+        <v>53261</v>
       </c>
       <c r="C48" t="n">
-        <v>53772</v>
+        <v>53336</v>
       </c>
       <c r="D48" t="n">
-        <v>53235</v>
+        <v>52758</v>
       </c>
       <c r="E48" t="n">
-        <v>53440</v>
+        <v>52832</v>
       </c>
       <c r="F48" t="n">
-        <v>-305</v>
+        <v>-608</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0057</v>
+        <v>-0.0114</v>
       </c>
       <c r="H48" t="n">
-        <v>537</v>
+        <v>578</v>
       </c>
       <c r="I48" t="n">
-        <v>52359</v>
+        <v>52698</v>
       </c>
       <c r="J48" t="n">
-        <v>53153.5</v>
+        <v>52871.25</v>
       </c>
       <c r="K48" t="n">
-        <v>53378</v>
+        <v>53171.5</v>
       </c>
       <c r="L48" t="n">
-        <v>53602.5</v>
+        <v>53471.75</v>
       </c>
       <c r="M48" t="n">
-        <v>54112</v>
+        <v>53708.5</v>
       </c>
       <c r="N48" t="n">
-        <v>54621.5</v>
+        <v>53945.25</v>
       </c>
       <c r="O48" t="n">
-        <v>54561</v>
+        <v>54309</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
@@ -4572,76 +4570,70 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W48" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>53261</v>
+        <v>52817</v>
       </c>
       <c r="C49" t="n">
-        <v>53336</v>
+        <v>52859</v>
       </c>
       <c r="D49" t="n">
-        <v>52758</v>
+        <v>52339</v>
       </c>
       <c r="E49" t="n">
-        <v>52832</v>
+        <v>52425</v>
       </c>
       <c r="F49" t="n">
-        <v>-608</v>
+        <v>-407</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0114</v>
+        <v>-0.0077</v>
       </c>
       <c r="H49" t="n">
-        <v>578</v>
+        <v>520</v>
       </c>
       <c r="I49" t="n">
-        <v>52698</v>
+        <v>52180</v>
       </c>
       <c r="J49" t="n">
-        <v>52871.25</v>
+        <v>52146.5</v>
       </c>
       <c r="K49" t="n">
-        <v>53171.5</v>
+        <v>52543</v>
       </c>
       <c r="L49" t="n">
-        <v>53471.75</v>
+        <v>52939.5</v>
       </c>
       <c r="M49" t="n">
-        <v>53708.5</v>
+        <v>53121</v>
       </c>
       <c r="N49" t="n">
-        <v>53945.25</v>
+        <v>53302.5</v>
       </c>
       <c r="O49" t="n">
-        <v>54309</v>
+        <v>53914</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
@@ -4668,50 +4660,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>52817</v>
+        <v>52473</v>
       </c>
       <c r="C50" t="n">
-        <v>52859</v>
+        <v>52676</v>
       </c>
       <c r="D50" t="n">
-        <v>52339</v>
+        <v>51992</v>
       </c>
       <c r="E50" t="n">
-        <v>52425</v>
+        <v>52095</v>
       </c>
       <c r="F50" t="n">
-        <v>-407</v>
+        <v>-330</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0077</v>
+        <v>-0.0063</v>
       </c>
       <c r="H50" t="n">
-        <v>520</v>
+        <v>684</v>
       </c>
       <c r="I50" t="n">
-        <v>52180</v>
+        <v>51819</v>
       </c>
       <c r="J50" t="n">
-        <v>52146.5</v>
+        <v>51818</v>
       </c>
       <c r="K50" t="n">
-        <v>52543</v>
+        <v>52165</v>
       </c>
       <c r="L50" t="n">
-        <v>52939.5</v>
+        <v>52512</v>
       </c>
       <c r="M50" t="n">
-        <v>53121</v>
+        <v>52685</v>
       </c>
       <c r="N50" t="n">
-        <v>53302.5</v>
+        <v>52858</v>
       </c>
       <c r="O50" t="n">
-        <v>53914</v>
+        <v>53379</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4748,50 +4740,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>52473</v>
+        <v>52059</v>
       </c>
       <c r="C51" t="n">
-        <v>52676</v>
+        <v>52739</v>
       </c>
       <c r="D51" t="n">
-        <v>51992</v>
+        <v>52059</v>
       </c>
       <c r="E51" t="n">
-        <v>52095</v>
+        <v>52585</v>
       </c>
       <c r="F51" t="n">
-        <v>-330</v>
+        <v>490</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0063</v>
+        <v>0.0094</v>
       </c>
       <c r="H51" t="n">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="I51" t="n">
-        <v>51819</v>
+        <v>51308</v>
       </c>
       <c r="J51" t="n">
-        <v>51818</v>
+        <v>51291.5</v>
       </c>
       <c r="K51" t="n">
-        <v>52165</v>
+        <v>51753</v>
       </c>
       <c r="L51" t="n">
-        <v>52512</v>
+        <v>52214.5</v>
       </c>
       <c r="M51" t="n">
-        <v>52685</v>
+        <v>52437</v>
       </c>
       <c r="N51" t="n">
-        <v>52858</v>
+        <v>52659.5</v>
       </c>
       <c r="O51" t="n">
-        <v>53379</v>
+        <v>53360</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4799,22 +4791,24 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
@@ -4823,55 +4817,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>52059</v>
+        <v>52376</v>
       </c>
       <c r="C52" t="n">
-        <v>52739</v>
+        <v>52672</v>
       </c>
       <c r="D52" t="n">
-        <v>52059</v>
+        <v>52226</v>
       </c>
       <c r="E52" t="n">
-        <v>52585</v>
+        <v>52440</v>
       </c>
       <c r="F52" t="n">
-        <v>490</v>
+        <v>-145</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0094</v>
+        <v>-0.0028</v>
       </c>
       <c r="H52" t="n">
-        <v>680</v>
+        <v>446</v>
       </c>
       <c r="I52" t="n">
-        <v>51308</v>
+        <v>51379</v>
       </c>
       <c r="J52" t="n">
-        <v>51291.5</v>
+        <v>51998</v>
       </c>
       <c r="K52" t="n">
-        <v>51753</v>
+        <v>52245</v>
       </c>
       <c r="L52" t="n">
-        <v>52214.5</v>
+        <v>52492</v>
       </c>
       <c r="M52" t="n">
-        <v>52437</v>
+        <v>52925</v>
       </c>
       <c r="N52" t="n">
-        <v>52659.5</v>
+        <v>53358</v>
       </c>
       <c r="O52" t="n">
-        <v>53360</v>
+        <v>53419</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4879,23 +4877,21 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4907,72 +4903,74 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>52376</v>
+        <v>52499</v>
       </c>
       <c r="C53" t="n">
-        <v>52672</v>
+        <v>52499</v>
       </c>
       <c r="D53" t="n">
-        <v>52226</v>
+        <v>51908</v>
       </c>
       <c r="E53" t="n">
-        <v>52440</v>
+        <v>52115</v>
       </c>
       <c r="F53" t="n">
-        <v>-145</v>
+        <v>-325</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0028</v>
+        <v>-0.0062</v>
       </c>
       <c r="H53" t="n">
-        <v>446</v>
+        <v>591</v>
       </c>
       <c r="I53" t="n">
-        <v>51379</v>
+        <v>51780</v>
       </c>
       <c r="J53" t="n">
-        <v>51998</v>
+        <v>51989.5</v>
       </c>
       <c r="K53" t="n">
-        <v>52245</v>
+        <v>52217</v>
       </c>
       <c r="L53" t="n">
-        <v>52492</v>
+        <v>52444.5</v>
       </c>
       <c r="M53" t="n">
-        <v>52925</v>
+        <v>52663</v>
       </c>
       <c r="N53" t="n">
-        <v>53358</v>
+        <v>52881.5</v>
       </c>
       <c r="O53" t="n">
-        <v>53419</v>
+        <v>53118</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4989,71 +4987,69 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>52499</v>
+        <v>52162</v>
       </c>
       <c r="C54" t="n">
-        <v>52499</v>
+        <v>52298</v>
       </c>
       <c r="D54" t="n">
-        <v>51908</v>
+        <v>51209</v>
       </c>
       <c r="E54" t="n">
-        <v>52115</v>
+        <v>51507</v>
       </c>
       <c r="F54" t="n">
-        <v>-325</v>
+        <v>-608</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0062</v>
+        <v>-0.0117</v>
       </c>
       <c r="H54" t="n">
-        <v>591</v>
+        <v>1089</v>
       </c>
       <c r="I54" t="n">
-        <v>51780</v>
+        <v>51317</v>
       </c>
       <c r="J54" t="n">
-        <v>51989.5</v>
+        <v>51479.75</v>
       </c>
       <c r="K54" t="n">
-        <v>52217</v>
+        <v>51819.5</v>
       </c>
       <c r="L54" t="n">
-        <v>52444.5</v>
+        <v>52159.25</v>
       </c>
       <c r="M54" t="n">
-        <v>52663</v>
+        <v>52410.5</v>
       </c>
       <c r="N54" t="n">
-        <v>52881.5</v>
+        <v>52661.75</v>
       </c>
       <c r="O54" t="n">
-        <v>53118</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v/>
+        <v>53090</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q54" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
@@ -5080,74 +5076,70 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>52162</v>
+        <v>51486</v>
       </c>
       <c r="C55" t="n">
-        <v>52298</v>
+        <v>52169</v>
       </c>
       <c r="D55" t="n">
-        <v>51209</v>
+        <v>51455</v>
       </c>
       <c r="E55" t="n">
-        <v>51507</v>
+        <v>51807</v>
       </c>
       <c r="F55" t="n">
-        <v>-608</v>
+        <v>300</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0117</v>
+        <v>0.0058</v>
       </c>
       <c r="H55" t="n">
-        <v>1089</v>
+        <v>714</v>
       </c>
       <c r="I55" t="n">
-        <v>51317</v>
+        <v>50120</v>
       </c>
       <c r="J55" t="n">
-        <v>51479.75</v>
+        <v>50294.75</v>
       </c>
       <c r="K55" t="n">
-        <v>51819.5</v>
+        <v>50962.5</v>
       </c>
       <c r="L55" t="n">
-        <v>52159.25</v>
+        <v>51630.25</v>
       </c>
       <c r="M55" t="n">
-        <v>52410.5</v>
+        <v>52051.5</v>
       </c>
       <c r="N55" t="n">
-        <v>52661.75</v>
+        <v>52472.75</v>
       </c>
       <c r="O55" t="n">
-        <v>53090</v>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
+        <v>53387</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
       <c r="U55" s="8" t="n">
         <v/>
       </c>
@@ -5159,55 +5151,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>51486</v>
+        <v>51800</v>
       </c>
       <c r="C56" t="n">
-        <v>52169</v>
+        <v>51957</v>
       </c>
       <c r="D56" t="n">
-        <v>51455</v>
+        <v>51576</v>
       </c>
       <c r="E56" t="n">
-        <v>51807</v>
+        <v>51761</v>
       </c>
       <c r="F56" t="n">
-        <v>300</v>
+        <v>-46</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0009</v>
       </c>
       <c r="H56" t="n">
-        <v>714</v>
+        <v>381</v>
       </c>
       <c r="I56" t="n">
-        <v>50120</v>
+        <v>50741</v>
       </c>
       <c r="J56" t="n">
-        <v>50294.75</v>
+        <v>51090.5</v>
       </c>
       <c r="K56" t="n">
-        <v>50962.5</v>
+        <v>51450</v>
       </c>
       <c r="L56" t="n">
-        <v>51630.25</v>
+        <v>51809.5</v>
       </c>
       <c r="M56" t="n">
-        <v>52051.5</v>
+        <v>52164</v>
       </c>
       <c r="N56" t="n">
-        <v>52472.75</v>
+        <v>52518.5</v>
       </c>
       <c r="O56" t="n">
-        <v>53387</v>
+        <v>52883</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5218,15 +5214,13 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5241,57 +5235,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>51800</v>
+        <v>52085</v>
       </c>
       <c r="C57" t="n">
-        <v>51957</v>
+        <v>52557</v>
       </c>
       <c r="D57" t="n">
-        <v>51576</v>
+        <v>52080</v>
       </c>
       <c r="E57" t="n">
-        <v>51761</v>
+        <v>52475</v>
       </c>
       <c r="F57" t="n">
-        <v>-46</v>
+        <v>714</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0138</v>
       </c>
       <c r="H57" t="n">
-        <v>381</v>
+        <v>477</v>
       </c>
       <c r="I57" t="n">
-        <v>50741</v>
+        <v>51195</v>
       </c>
       <c r="J57" t="n">
-        <v>51090.5</v>
+        <v>51377.25</v>
       </c>
       <c r="K57" t="n">
-        <v>51450</v>
+        <v>51570.5</v>
       </c>
       <c r="L57" t="n">
-        <v>51809.5</v>
+        <v>51763.75</v>
       </c>
       <c r="M57" t="n">
-        <v>52164</v>
+        <v>51951.5</v>
       </c>
       <c r="N57" t="n">
-        <v>52518.5</v>
+        <v>52139.25</v>
       </c>
       <c r="O57" t="n">
-        <v>52883</v>
+        <v>52338</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5302,78 +5296,80 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W57" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V57" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W57" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>52085</v>
+        <v>52470</v>
       </c>
       <c r="C58" t="n">
-        <v>52557</v>
+        <v>52844</v>
       </c>
       <c r="D58" t="n">
-        <v>52080</v>
+        <v>52125</v>
       </c>
       <c r="E58" t="n">
-        <v>52475</v>
+        <v>52279</v>
       </c>
       <c r="F58" t="n">
-        <v>714</v>
+        <v>-196</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0138</v>
+        <v>-0.0037</v>
       </c>
       <c r="H58" t="n">
-        <v>477</v>
+        <v>719</v>
       </c>
       <c r="I58" t="n">
-        <v>51195</v>
+        <v>51603</v>
       </c>
       <c r="J58" t="n">
-        <v>51377.25</v>
+        <v>52076.25</v>
       </c>
       <c r="K58" t="n">
-        <v>51570.5</v>
+        <v>52236.5</v>
       </c>
       <c r="L58" t="n">
-        <v>51763.75</v>
+        <v>52396.75</v>
       </c>
       <c r="M58" t="n">
-        <v>51951.5</v>
+        <v>52713.5</v>
       </c>
       <c r="N58" t="n">
-        <v>52139.25</v>
+        <v>53030.25</v>
       </c>
       <c r="O58" t="n">
-        <v>52338</v>
+        <v>53034</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5381,12 +5377,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
@@ -5394,70 +5392,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
       </c>
       <c r="W58" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>52470</v>
+        <v>52255</v>
       </c>
       <c r="C59" t="n">
-        <v>52844</v>
+        <v>52371</v>
       </c>
       <c r="D59" t="n">
-        <v>52125</v>
+        <v>51844</v>
       </c>
       <c r="E59" t="n">
-        <v>52279</v>
+        <v>51873</v>
       </c>
       <c r="F59" t="n">
-        <v>-196</v>
+        <v>-406</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0037</v>
+        <v>-0.0078</v>
       </c>
       <c r="H59" t="n">
-        <v>719</v>
+        <v>527</v>
       </c>
       <c r="I59" t="n">
-        <v>51603</v>
+        <v>51406</v>
       </c>
       <c r="J59" t="n">
-        <v>52076.25</v>
+        <v>51457.25</v>
       </c>
       <c r="K59" t="n">
-        <v>52236.5</v>
+        <v>51919.5</v>
       </c>
       <c r="L59" t="n">
-        <v>52396.75</v>
+        <v>52381.75</v>
       </c>
       <c r="M59" t="n">
-        <v>52713.5</v>
+        <v>52638.5</v>
       </c>
       <c r="N59" t="n">
-        <v>53030.25</v>
+        <v>52895.25</v>
       </c>
       <c r="O59" t="n">
-        <v>53034</v>
+        <v>53563</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5475,10 +5473,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T59" s="8" t="n">
+        <v/>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5493,57 +5489,57 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>52255</v>
+        <v>51878</v>
       </c>
       <c r="C60" t="n">
-        <v>52371</v>
+        <v>51905</v>
       </c>
       <c r="D60" t="n">
-        <v>51844</v>
+        <v>51479</v>
       </c>
       <c r="E60" t="n">
-        <v>51873</v>
+        <v>51717</v>
       </c>
       <c r="F60" t="n">
-        <v>-406</v>
+        <v>-156</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0078</v>
+        <v>-0.003</v>
       </c>
       <c r="H60" t="n">
-        <v>527</v>
+        <v>426</v>
       </c>
       <c r="I60" t="n">
-        <v>51406</v>
+        <v>51317</v>
       </c>
       <c r="J60" t="n">
-        <v>51457.25</v>
+        <v>51228.75</v>
       </c>
       <c r="K60" t="n">
-        <v>51919.5</v>
+        <v>51609.5</v>
       </c>
       <c r="L60" t="n">
-        <v>52381.75</v>
+        <v>51990.25</v>
       </c>
       <c r="M60" t="n">
-        <v>52638.5</v>
+        <v>52136.5</v>
       </c>
       <c r="N60" t="n">
-        <v>52895.25</v>
+        <v>52282.75</v>
       </c>
       <c r="O60" t="n">
-        <v>53563</v>
+        <v>52898</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5584,50 +5580,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>51878</v>
+        <v>51655</v>
       </c>
       <c r="C61" t="n">
-        <v>51905</v>
+        <v>52223</v>
       </c>
       <c r="D61" t="n">
-        <v>51479</v>
+        <v>51610</v>
       </c>
       <c r="E61" t="n">
-        <v>51717</v>
+        <v>52163</v>
       </c>
       <c r="F61" t="n">
-        <v>-156</v>
+        <v>446</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.0086</v>
       </c>
       <c r="H61" t="n">
-        <v>426</v>
+        <v>613</v>
       </c>
       <c r="I61" t="n">
-        <v>51317</v>
+        <v>51053</v>
       </c>
       <c r="J61" t="n">
-        <v>51228.75</v>
+        <v>51303.5</v>
       </c>
       <c r="K61" t="n">
-        <v>51609.5</v>
+        <v>51504</v>
       </c>
       <c r="L61" t="n">
-        <v>51990.25</v>
+        <v>51704.5</v>
       </c>
       <c r="M61" t="n">
-        <v>52136.5</v>
+        <v>51930</v>
       </c>
       <c r="N61" t="n">
-        <v>52282.75</v>
+        <v>52155.5</v>
       </c>
       <c r="O61" t="n">
-        <v>52898</v>
+        <v>52331</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5635,22 +5631,24 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
       <c r="V61" s="8" t="n">
         <v/>
       </c>
@@ -5659,59 +5657,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>51655</v>
+        <v>51845</v>
       </c>
       <c r="C62" t="n">
-        <v>52223</v>
+        <v>51848</v>
       </c>
       <c r="D62" t="n">
-        <v>51610</v>
+        <v>51815</v>
       </c>
       <c r="E62" t="n">
-        <v>52163</v>
+        <v>51820</v>
       </c>
       <c r="F62" t="n">
-        <v>446</v>
+        <v>-343</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.0066</v>
       </c>
       <c r="H62" t="n">
-        <v>613</v>
+        <v>33</v>
       </c>
       <c r="I62" t="n">
-        <v>51053</v>
+        <v>50997</v>
       </c>
       <c r="J62" t="n">
-        <v>51303.5</v>
+        <v>51673.25</v>
       </c>
       <c r="K62" t="n">
-        <v>51504</v>
+        <v>51856.5</v>
       </c>
       <c r="L62" t="n">
-        <v>51704.5</v>
+        <v>52039.75</v>
       </c>
       <c r="M62" t="n">
-        <v>51930</v>
+        <v>52469.5</v>
       </c>
       <c r="N62" t="n">
-        <v>52155.5</v>
+        <v>52899.25</v>
       </c>
       <c r="O62" t="n">
-        <v>52331</v>
+        <v>52836</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5719,24 +5713,22 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
+      <c r="R62" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
       <c r="V62" s="8" t="n">
         <v/>
       </c>
@@ -5745,87 +5737,9 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>52140</v>
-      </c>
-      <c r="C63" t="n">
-        <v>52153</v>
-      </c>
-      <c r="D63" t="n">
-        <v>52054</v>
-      </c>
-      <c r="E63" t="n">
-        <v>52163</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>99</v>
-      </c>
-      <c r="I63" t="n">
-        <v>50997</v>
-      </c>
-      <c r="J63" t="n">
-        <v>51673.25</v>
-      </c>
-      <c r="K63" t="n">
-        <v>51856.5</v>
-      </c>
-      <c r="L63" t="n">
-        <v>52039.75</v>
-      </c>
-      <c r="M63" t="n">
-        <v>52469.5</v>
-      </c>
-      <c r="N63" t="n">
-        <v>52899.25</v>
-      </c>
-      <c r="O63" t="n">
-        <v>52836</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52640</v>
+        <v>53230</v>
       </c>
       <c r="C2" t="n">
-        <v>53218</v>
+        <v>53421</v>
       </c>
       <c r="D2" t="n">
-        <v>52551</v>
+        <v>52962</v>
       </c>
       <c r="E2" t="n">
-        <v>53183</v>
+        <v>53372</v>
       </c>
       <c r="F2" t="n">
-        <v>515</v>
+        <v>189</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0098</v>
+        <v>0.0036</v>
       </c>
       <c r="H2" t="n">
-        <v>667</v>
+        <v>459</v>
       </c>
       <c r="I2" t="n">
-        <v>51657</v>
+        <v>51884</v>
       </c>
       <c r="J2" t="n">
-        <v>51906.5</v>
+        <v>52665.25</v>
       </c>
       <c r="K2" t="n">
-        <v>52306</v>
+        <v>52849.5</v>
       </c>
       <c r="L2" t="n">
-        <v>52705.5</v>
+        <v>53033.75</v>
       </c>
       <c r="M2" t="n">
-        <v>53030</v>
+        <v>53516.5</v>
       </c>
       <c r="N2" t="n">
-        <v>53354.5</v>
+        <v>53999.25</v>
       </c>
       <c r="O2" t="n">
-        <v>53829</v>
+        <v>53885</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -714,50 +714,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53230</v>
+        <v>53405</v>
       </c>
       <c r="C3" t="n">
-        <v>53421</v>
+        <v>53656</v>
       </c>
       <c r="D3" t="n">
-        <v>52962</v>
+        <v>53076</v>
       </c>
       <c r="E3" t="n">
-        <v>53372</v>
+        <v>53197</v>
       </c>
       <c r="F3" t="n">
-        <v>189</v>
+        <v>-175</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0036</v>
+        <v>-0.0033</v>
       </c>
       <c r="H3" t="n">
-        <v>459</v>
+        <v>580</v>
       </c>
       <c r="I3" t="n">
-        <v>51884</v>
+        <v>52503</v>
       </c>
       <c r="J3" t="n">
-        <v>52665.25</v>
+        <v>53003.25</v>
       </c>
       <c r="K3" t="n">
-        <v>52849.5</v>
+        <v>53142.5</v>
       </c>
       <c r="L3" t="n">
-        <v>53033.75</v>
+        <v>53281.75</v>
       </c>
       <c r="M3" t="n">
-        <v>53516.5</v>
+        <v>53601.5</v>
       </c>
       <c r="N3" t="n">
-        <v>53999.25</v>
+        <v>53921.25</v>
       </c>
       <c r="O3" t="n">
-        <v>53885</v>
+        <v>53880</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -765,17 +765,19 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U3" s="8" t="n">
@@ -789,65 +791,73 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53405</v>
+        <v>53166</v>
       </c>
       <c r="C4" t="n">
-        <v>53656</v>
+        <v>53207</v>
       </c>
       <c r="D4" t="n">
-        <v>53076</v>
+        <v>52343</v>
       </c>
       <c r="E4" t="n">
-        <v>53197</v>
+        <v>52624</v>
       </c>
       <c r="F4" t="n">
-        <v>-175</v>
+        <v>-573</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0108</v>
       </c>
       <c r="H4" t="n">
-        <v>580</v>
+        <v>864</v>
       </c>
       <c r="I4" t="n">
-        <v>52503</v>
+        <v>52496</v>
       </c>
       <c r="J4" t="n">
-        <v>53003.25</v>
+        <v>52532.5</v>
       </c>
       <c r="K4" t="n">
-        <v>53142.5</v>
+        <v>52907</v>
       </c>
       <c r="L4" t="n">
-        <v>53281.75</v>
+        <v>53281.5</v>
       </c>
       <c r="M4" t="n">
-        <v>53601.5</v>
+        <v>53487</v>
       </c>
       <c r="N4" t="n">
-        <v>53921.25</v>
+        <v>53692.5</v>
       </c>
       <c r="O4" t="n">
-        <v>53880</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
+        <v>54236</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
@@ -855,10 +865,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -873,76 +881,70 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53166</v>
+        <v>52541</v>
       </c>
       <c r="C5" t="n">
-        <v>53207</v>
+        <v>52865</v>
       </c>
       <c r="D5" t="n">
-        <v>52343</v>
+        <v>52501</v>
       </c>
       <c r="E5" t="n">
-        <v>52624</v>
+        <v>52761</v>
       </c>
       <c r="F5" t="n">
-        <v>-573</v>
+        <v>137</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0108</v>
+        <v>0.0026</v>
       </c>
       <c r="H5" t="n">
-        <v>864</v>
+        <v>364</v>
       </c>
       <c r="I5" t="n">
-        <v>52496</v>
+        <v>51479</v>
       </c>
       <c r="J5" t="n">
-        <v>52532.5</v>
+        <v>51684.5</v>
       </c>
       <c r="K5" t="n">
-        <v>52907</v>
+        <v>52192</v>
       </c>
       <c r="L5" t="n">
-        <v>53281.5</v>
+        <v>52699.5</v>
       </c>
       <c r="M5" t="n">
-        <v>53487</v>
+        <v>53056</v>
       </c>
       <c r="N5" t="n">
-        <v>53692.5</v>
+        <v>53412.5</v>
       </c>
       <c r="O5" t="n">
-        <v>54236</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>54071</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -961,57 +963,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52541</v>
+        <v>52753</v>
       </c>
       <c r="C6" t="n">
-        <v>52865</v>
+        <v>52992</v>
       </c>
       <c r="D6" t="n">
-        <v>52501</v>
+        <v>52506</v>
       </c>
       <c r="E6" t="n">
-        <v>52761</v>
+        <v>52906</v>
       </c>
       <c r="F6" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0027</v>
       </c>
       <c r="H6" t="n">
-        <v>364</v>
+        <v>486</v>
       </c>
       <c r="I6" t="n">
-        <v>51479</v>
+        <v>52137</v>
       </c>
       <c r="J6" t="n">
-        <v>51684.5</v>
+        <v>52436</v>
       </c>
       <c r="K6" t="n">
-        <v>52192</v>
+        <v>52579</v>
       </c>
       <c r="L6" t="n">
-        <v>52699.5</v>
+        <v>52722</v>
       </c>
       <c r="M6" t="n">
-        <v>53056</v>
+        <v>52943</v>
       </c>
       <c r="N6" t="n">
-        <v>53412.5</v>
+        <v>53164</v>
       </c>
       <c r="O6" t="n">
-        <v>54071</v>
+        <v>53229</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1019,16 +1021,20 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1041,59 +1047,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>52753</v>
+        <v>52844</v>
       </c>
       <c r="C7" t="n">
-        <v>52992</v>
+        <v>53113</v>
       </c>
       <c r="D7" t="n">
-        <v>52506</v>
+        <v>52603</v>
       </c>
       <c r="E7" t="n">
-        <v>52906</v>
+        <v>52764</v>
       </c>
       <c r="F7" t="n">
-        <v>145</v>
+        <v>-142</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0027</v>
       </c>
       <c r="H7" t="n">
-        <v>486</v>
+        <v>510</v>
       </c>
       <c r="I7" t="n">
-        <v>52137</v>
+        <v>52020</v>
       </c>
       <c r="J7" t="n">
-        <v>52436</v>
+        <v>52498.5</v>
       </c>
       <c r="K7" t="n">
-        <v>52579</v>
+        <v>52663</v>
       </c>
       <c r="L7" t="n">
-        <v>52722</v>
+        <v>52827.5</v>
       </c>
       <c r="M7" t="n">
-        <v>52943</v>
+        <v>53149</v>
       </c>
       <c r="N7" t="n">
-        <v>53164</v>
+        <v>53470.5</v>
       </c>
       <c r="O7" t="n">
-        <v>53229</v>
+        <v>53478</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1106,15 +1108,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1127,55 +1127,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52844</v>
+        <v>52731</v>
       </c>
       <c r="C8" t="n">
-        <v>53113</v>
+        <v>52981</v>
       </c>
       <c r="D8" t="n">
-        <v>52603</v>
+        <v>52255</v>
       </c>
       <c r="E8" t="n">
-        <v>52764</v>
+        <v>52791</v>
       </c>
       <c r="F8" t="n">
-        <v>-142</v>
+        <v>27</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0005</v>
       </c>
       <c r="H8" t="n">
-        <v>510</v>
+        <v>726</v>
       </c>
       <c r="I8" t="n">
-        <v>52020</v>
+        <v>52093</v>
       </c>
       <c r="J8" t="n">
-        <v>52498.5</v>
+        <v>52207</v>
       </c>
       <c r="K8" t="n">
-        <v>52663</v>
+        <v>52509</v>
       </c>
       <c r="L8" t="n">
-        <v>52827.5</v>
+        <v>52811</v>
       </c>
       <c r="M8" t="n">
-        <v>53149</v>
+        <v>53019</v>
       </c>
       <c r="N8" t="n">
-        <v>53470.5</v>
+        <v>53227</v>
       </c>
       <c r="O8" t="n">
-        <v>53478</v>
+        <v>53623</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1209,57 +1213,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52731</v>
+        <v>52792</v>
       </c>
       <c r="C9" t="n">
-        <v>52981</v>
+        <v>53088</v>
       </c>
       <c r="D9" t="n">
-        <v>52255</v>
+        <v>52680</v>
       </c>
       <c r="E9" t="n">
-        <v>52791</v>
+        <v>52900</v>
       </c>
       <c r="F9" t="n">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0021</v>
       </c>
       <c r="H9" t="n">
-        <v>726</v>
+        <v>408</v>
       </c>
       <c r="I9" t="n">
-        <v>52093</v>
+        <v>51529</v>
       </c>
       <c r="J9" t="n">
-        <v>52207</v>
+        <v>52151.5</v>
       </c>
       <c r="K9" t="n">
-        <v>52509</v>
+        <v>52428</v>
       </c>
       <c r="L9" t="n">
-        <v>52811</v>
+        <v>52704.5</v>
       </c>
       <c r="M9" t="n">
-        <v>53019</v>
+        <v>53154</v>
       </c>
       <c r="N9" t="n">
-        <v>53227</v>
+        <v>53603.5</v>
       </c>
       <c r="O9" t="n">
-        <v>53623</v>
+        <v>53707</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1267,14 +1271,12 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1291,59 +1293,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52792</v>
+        <v>52919</v>
       </c>
       <c r="C10" t="n">
-        <v>53088</v>
+        <v>53108</v>
       </c>
       <c r="D10" t="n">
-        <v>52680</v>
+        <v>52607</v>
       </c>
       <c r="E10" t="n">
-        <v>52900</v>
+        <v>52786</v>
       </c>
       <c r="F10" t="n">
-        <v>109</v>
+        <v>-114</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0022</v>
       </c>
       <c r="H10" t="n">
-        <v>408</v>
+        <v>501</v>
       </c>
       <c r="I10" t="n">
-        <v>51529</v>
+        <v>52272</v>
       </c>
       <c r="J10" t="n">
-        <v>52151.5</v>
+        <v>52500</v>
       </c>
       <c r="K10" t="n">
-        <v>52428</v>
+        <v>52696</v>
       </c>
       <c r="L10" t="n">
-        <v>52704.5</v>
+        <v>52892</v>
       </c>
       <c r="M10" t="n">
-        <v>53154</v>
+        <v>53104</v>
       </c>
       <c r="N10" t="n">
-        <v>53603.5</v>
+        <v>53316</v>
       </c>
       <c r="O10" t="n">
-        <v>53707</v>
+        <v>53496</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1351,16 +1349,20 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1373,65 +1375,71 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>52919</v>
+        <v>52778</v>
       </c>
       <c r="C11" t="n">
-        <v>53108</v>
+        <v>52835</v>
       </c>
       <c r="D11" t="n">
-        <v>52607</v>
+        <v>52174</v>
       </c>
       <c r="E11" t="n">
-        <v>52786</v>
+        <v>52375</v>
       </c>
       <c r="F11" t="n">
-        <v>-114</v>
+        <v>-411</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0078</v>
       </c>
       <c r="H11" t="n">
-        <v>501</v>
+        <v>661</v>
       </c>
       <c r="I11" t="n">
-        <v>52272</v>
+        <v>52106</v>
       </c>
       <c r="J11" t="n">
-        <v>52500</v>
+        <v>52249.25</v>
       </c>
       <c r="K11" t="n">
-        <v>52696</v>
+        <v>52535.5</v>
       </c>
       <c r="L11" t="n">
-        <v>52892</v>
+        <v>52821.75</v>
       </c>
       <c r="M11" t="n">
-        <v>53104</v>
+        <v>53036.5</v>
       </c>
       <c r="N11" t="n">
-        <v>53316</v>
+        <v>53251.25</v>
       </c>
       <c r="O11" t="n">
-        <v>53496</v>
+        <v>53609</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
@@ -1439,10 +1447,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1457,69 +1463,67 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52778</v>
+        <v>52300</v>
       </c>
       <c r="C12" t="n">
-        <v>52835</v>
+        <v>52633</v>
       </c>
       <c r="D12" t="n">
-        <v>52174</v>
+        <v>51999</v>
       </c>
       <c r="E12" t="n">
-        <v>52375</v>
+        <v>52073</v>
       </c>
       <c r="F12" t="n">
-        <v>-411</v>
+        <v>-302</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0078</v>
+        <v>-0.0058</v>
       </c>
       <c r="H12" t="n">
-        <v>661</v>
+        <v>634</v>
       </c>
       <c r="I12" t="n">
-        <v>52106</v>
+        <v>51513</v>
       </c>
       <c r="J12" t="n">
-        <v>52249.25</v>
+        <v>51649.25</v>
       </c>
       <c r="K12" t="n">
-        <v>52535.5</v>
+        <v>52044.5</v>
       </c>
       <c r="L12" t="n">
-        <v>52821.75</v>
+        <v>52439.75</v>
       </c>
       <c r="M12" t="n">
-        <v>53036.5</v>
+        <v>52705.5</v>
       </c>
       <c r="N12" t="n">
-        <v>53251.25</v>
+        <v>52971.25</v>
       </c>
       <c r="O12" t="n">
-        <v>53609</v>
+        <v>53496</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
@@ -1550,50 +1554,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>52300</v>
+        <v>52091</v>
       </c>
       <c r="C13" t="n">
-        <v>52633</v>
+        <v>52590</v>
       </c>
       <c r="D13" t="n">
-        <v>51999</v>
+        <v>52035</v>
       </c>
       <c r="E13" t="n">
-        <v>52073</v>
+        <v>52443</v>
       </c>
       <c r="F13" t="n">
-        <v>-302</v>
+        <v>370</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.0071</v>
       </c>
       <c r="H13" t="n">
-        <v>634</v>
+        <v>555</v>
       </c>
       <c r="I13" t="n">
-        <v>51513</v>
+        <v>51365</v>
       </c>
       <c r="J13" t="n">
-        <v>51649.25</v>
+        <v>51317.5</v>
       </c>
       <c r="K13" t="n">
-        <v>52044.5</v>
+        <v>51756</v>
       </c>
       <c r="L13" t="n">
-        <v>52439.75</v>
+        <v>52194.5</v>
       </c>
       <c r="M13" t="n">
-        <v>52705.5</v>
+        <v>52390</v>
       </c>
       <c r="N13" t="n">
-        <v>52971.25</v>
+        <v>52585.5</v>
       </c>
       <c r="O13" t="n">
-        <v>53496</v>
+        <v>53267</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1601,21 +1605,23 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1627,57 +1633,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>52091</v>
+        <v>52431</v>
       </c>
       <c r="C14" t="n">
-        <v>52590</v>
+        <v>52721</v>
       </c>
       <c r="D14" t="n">
-        <v>52035</v>
+        <v>52262</v>
       </c>
       <c r="E14" t="n">
-        <v>52443</v>
+        <v>52449</v>
       </c>
       <c r="F14" t="n">
-        <v>370</v>
+        <v>6</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0001</v>
       </c>
       <c r="H14" t="n">
-        <v>555</v>
+        <v>459</v>
       </c>
       <c r="I14" t="n">
-        <v>51365</v>
+        <v>51480</v>
       </c>
       <c r="J14" t="n">
-        <v>51317.5</v>
+        <v>51953.25</v>
       </c>
       <c r="K14" t="n">
-        <v>51756</v>
+        <v>52165.5</v>
       </c>
       <c r="L14" t="n">
-        <v>52194.5</v>
+        <v>52377.75</v>
       </c>
       <c r="M14" t="n">
-        <v>52390</v>
+        <v>52720.5</v>
       </c>
       <c r="N14" t="n">
-        <v>52585.5</v>
+        <v>53063.25</v>
       </c>
       <c r="O14" t="n">
-        <v>53267</v>
+        <v>53145</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1690,19 +1696,17 @@
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
@@ -1711,88 +1715,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52431</v>
+        <v>52430</v>
       </c>
       <c r="C15" t="n">
-        <v>52721</v>
+        <v>52515</v>
       </c>
       <c r="D15" t="n">
-        <v>52262</v>
+        <v>51720</v>
       </c>
       <c r="E15" t="n">
-        <v>52449</v>
+        <v>51894</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>-555</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0106</v>
       </c>
       <c r="H15" t="n">
-        <v>459</v>
+        <v>795</v>
       </c>
       <c r="I15" t="n">
-        <v>51480</v>
+        <v>51803</v>
       </c>
       <c r="J15" t="n">
-        <v>51953.25</v>
+        <v>51968.75</v>
       </c>
       <c r="K15" t="n">
-        <v>52165.5</v>
+        <v>52219.5</v>
       </c>
       <c r="L15" t="n">
-        <v>52377.75</v>
+        <v>52470.25</v>
       </c>
       <c r="M15" t="n">
-        <v>52720.5</v>
+        <v>52678.5</v>
       </c>
       <c r="N15" t="n">
-        <v>53063.25</v>
+        <v>52886.75</v>
       </c>
       <c r="O15" t="n">
-        <v>53145</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
+        <v>53180</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W15" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
@@ -1800,74 +1804,70 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>52430</v>
+        <v>51920</v>
       </c>
       <c r="C16" t="n">
-        <v>52515</v>
+        <v>52314</v>
       </c>
       <c r="D16" t="n">
-        <v>51720</v>
+        <v>51846</v>
       </c>
       <c r="E16" t="n">
-        <v>51894</v>
+        <v>52124</v>
       </c>
       <c r="F16" t="n">
-        <v>-555</v>
+        <v>230</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0044</v>
       </c>
       <c r="H16" t="n">
-        <v>795</v>
+        <v>468</v>
       </c>
       <c r="I16" t="n">
-        <v>51803</v>
+        <v>50925</v>
       </c>
       <c r="J16" t="n">
-        <v>51968.75</v>
+        <v>50987.25</v>
       </c>
       <c r="K16" t="n">
-        <v>52219.5</v>
+        <v>51496.5</v>
       </c>
       <c r="L16" t="n">
-        <v>52470.25</v>
+        <v>52005.75</v>
       </c>
       <c r="M16" t="n">
-        <v>52678.5</v>
+        <v>52291.5</v>
       </c>
       <c r="N16" t="n">
-        <v>52886.75</v>
+        <v>52577.25</v>
       </c>
       <c r="O16" t="n">
-        <v>53180</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
+        <v>53310</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
@@ -1879,55 +1879,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>51920</v>
+        <v>52299</v>
       </c>
       <c r="C17" t="n">
-        <v>52314</v>
+        <v>52790</v>
       </c>
       <c r="D17" t="n">
-        <v>51846</v>
+        <v>52173</v>
       </c>
       <c r="E17" t="n">
-        <v>52124</v>
+        <v>52382</v>
       </c>
       <c r="F17" t="n">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0049</v>
       </c>
       <c r="H17" t="n">
-        <v>468</v>
+        <v>617</v>
       </c>
       <c r="I17" t="n">
-        <v>50925</v>
+        <v>51378</v>
       </c>
       <c r="J17" t="n">
-        <v>50987.25</v>
+        <v>51678</v>
       </c>
       <c r="K17" t="n">
-        <v>51496.5</v>
+        <v>51890</v>
       </c>
       <c r="L17" t="n">
-        <v>52005.75</v>
+        <v>52102</v>
       </c>
       <c r="M17" t="n">
-        <v>52291.5</v>
+        <v>52358</v>
       </c>
       <c r="N17" t="n">
-        <v>52577.25</v>
+        <v>52614</v>
       </c>
       <c r="O17" t="n">
-        <v>53310</v>
+        <v>52782</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1940,19 +1944,23 @@
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W17" s="11" t="inlineStr">
         <is>
@@ -1961,57 +1969,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52299</v>
+        <v>52405</v>
       </c>
       <c r="C18" t="n">
-        <v>52790</v>
+        <v>53105</v>
       </c>
       <c r="D18" t="n">
-        <v>52173</v>
+        <v>52290</v>
       </c>
       <c r="E18" t="n">
-        <v>52382</v>
+        <v>52944</v>
       </c>
       <c r="F18" t="n">
-        <v>258</v>
+        <v>562</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0107</v>
       </c>
       <c r="H18" t="n">
-        <v>617</v>
+        <v>815</v>
       </c>
       <c r="I18" t="n">
-        <v>51378</v>
+        <v>51556</v>
       </c>
       <c r="J18" t="n">
-        <v>51678</v>
+        <v>51715.25</v>
       </c>
       <c r="K18" t="n">
-        <v>51890</v>
+        <v>52073.5</v>
       </c>
       <c r="L18" t="n">
-        <v>52102</v>
+        <v>52431.75</v>
       </c>
       <c r="M18" t="n">
-        <v>52358</v>
+        <v>52690.5</v>
       </c>
       <c r="N18" t="n">
-        <v>52614</v>
+        <v>52949.25</v>
       </c>
       <c r="O18" t="n">
-        <v>52782</v>
+        <v>53407</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2029,18 +2037,16 @@
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V18" s="8" t="n">
+        <v/>
       </c>
       <c r="W18" s="11" t="inlineStr">
         <is>
@@ -2056,74 +2062,76 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>52405</v>
+        <v>52915</v>
       </c>
       <c r="C19" t="n">
-        <v>53105</v>
+        <v>53033</v>
       </c>
       <c r="D19" t="n">
-        <v>52290</v>
+        <v>51630</v>
       </c>
       <c r="E19" t="n">
-        <v>52944</v>
+        <v>51765</v>
       </c>
       <c r="F19" t="n">
-        <v>562</v>
+        <v>-1179</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0223</v>
       </c>
       <c r="H19" t="n">
-        <v>815</v>
+        <v>1403</v>
       </c>
       <c r="I19" t="n">
-        <v>51556</v>
+        <v>51475</v>
       </c>
       <c r="J19" t="n">
-        <v>51715.25</v>
+        <v>52252.25</v>
       </c>
       <c r="K19" t="n">
-        <v>52073.5</v>
+        <v>52536.5</v>
       </c>
       <c r="L19" t="n">
-        <v>52431.75</v>
+        <v>52820.75</v>
       </c>
       <c r="M19" t="n">
-        <v>52690.5</v>
+        <v>53351.5</v>
       </c>
       <c r="N19" t="n">
-        <v>52949.25</v>
+        <v>53882.25</v>
       </c>
       <c r="O19" t="n">
-        <v>53407</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
+        <v>53920</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2133,83 +2141,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>52915</v>
+        <v>51759</v>
       </c>
       <c r="C20" t="n">
-        <v>53033</v>
+        <v>52484</v>
       </c>
       <c r="D20" t="n">
-        <v>51630</v>
+        <v>51732</v>
       </c>
       <c r="E20" t="n">
-        <v>51765</v>
+        <v>52380</v>
       </c>
       <c r="F20" t="n">
-        <v>-1179</v>
+        <v>615</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0119</v>
       </c>
       <c r="H20" t="n">
-        <v>1403</v>
+        <v>752</v>
       </c>
       <c r="I20" t="n">
-        <v>51475</v>
+        <v>50227</v>
       </c>
       <c r="J20" t="n">
-        <v>52252.25</v>
+        <v>50078.75</v>
       </c>
       <c r="K20" t="n">
-        <v>52536.5</v>
+        <v>51063.5</v>
       </c>
       <c r="L20" t="n">
-        <v>52820.75</v>
+        <v>52048.25</v>
       </c>
       <c r="M20" t="n">
-        <v>53351.5</v>
+        <v>52466.5</v>
       </c>
       <c r="N20" t="n">
-        <v>53882.25</v>
+        <v>52884.75</v>
       </c>
       <c r="O20" t="n">
-        <v>53920</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
+        <v>54436</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
       <c r="U20" s="8" t="n">
         <v/>
       </c>
@@ -2221,55 +2221,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>51759</v>
+        <v>52395</v>
       </c>
       <c r="C21" t="n">
-        <v>52484</v>
+        <v>52772</v>
       </c>
       <c r="D21" t="n">
-        <v>51732</v>
+        <v>52124</v>
       </c>
       <c r="E21" t="n">
-        <v>52380</v>
+        <v>52635</v>
       </c>
       <c r="F21" t="n">
-        <v>615</v>
+        <v>255</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0119</v>
+        <v>0.0049</v>
       </c>
       <c r="H21" t="n">
-        <v>752</v>
+        <v>648</v>
       </c>
       <c r="I21" t="n">
-        <v>50227</v>
+        <v>50980</v>
       </c>
       <c r="J21" t="n">
-        <v>50078.75</v>
+        <v>51764</v>
       </c>
       <c r="K21" t="n">
-        <v>51063.5</v>
+        <v>52004</v>
       </c>
       <c r="L21" t="n">
-        <v>52048.25</v>
+        <v>52244</v>
       </c>
       <c r="M21" t="n">
-        <v>52466.5</v>
+        <v>52756</v>
       </c>
       <c r="N21" t="n">
-        <v>52884.75</v>
+        <v>53268</v>
       </c>
       <c r="O21" t="n">
-        <v>54436</v>
+        <v>53236</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2303,57 +2307,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>52395</v>
+        <v>52780</v>
       </c>
       <c r="C22" t="n">
-        <v>52772</v>
+        <v>53414</v>
       </c>
       <c r="D22" t="n">
-        <v>52124</v>
+        <v>52777</v>
       </c>
       <c r="E22" t="n">
-        <v>52635</v>
+        <v>53334</v>
       </c>
       <c r="F22" t="n">
-        <v>255</v>
+        <v>699</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0133</v>
       </c>
       <c r="H22" t="n">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="I22" t="n">
-        <v>50980</v>
+        <v>51476</v>
       </c>
       <c r="J22" t="n">
-        <v>51764</v>
+        <v>52080.5</v>
       </c>
       <c r="K22" t="n">
-        <v>52004</v>
+        <v>52311</v>
       </c>
       <c r="L22" t="n">
-        <v>52244</v>
+        <v>52541.5</v>
       </c>
       <c r="M22" t="n">
-        <v>52756</v>
+        <v>52959</v>
       </c>
       <c r="N22" t="n">
-        <v>53268</v>
+        <v>53376.5</v>
       </c>
       <c r="O22" t="n">
-        <v>53236</v>
+        <v>53420</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2371,11 +2375,13 @@
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2394,50 +2400,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>52780</v>
+        <v>53381</v>
       </c>
       <c r="C23" t="n">
-        <v>53414</v>
+        <v>54423</v>
       </c>
       <c r="D23" t="n">
-        <v>52777</v>
+        <v>53267</v>
       </c>
       <c r="E23" t="n">
-        <v>53334</v>
+        <v>54268</v>
       </c>
       <c r="F23" t="n">
-        <v>699</v>
+        <v>934</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0175</v>
       </c>
       <c r="H23" t="n">
-        <v>637</v>
+        <v>1156</v>
       </c>
       <c r="I23" t="n">
-        <v>51476</v>
+        <v>52140</v>
       </c>
       <c r="J23" t="n">
-        <v>52080.5</v>
+        <v>52816.25</v>
       </c>
       <c r="K23" t="n">
-        <v>52311</v>
+        <v>53015.5</v>
       </c>
       <c r="L23" t="n">
-        <v>52541.5</v>
+        <v>53214.75</v>
       </c>
       <c r="M23" t="n">
-        <v>52959</v>
+        <v>53652.5</v>
       </c>
       <c r="N23" t="n">
-        <v>53376.5</v>
+        <v>54090.25</v>
       </c>
       <c r="O23" t="n">
-        <v>53420</v>
+        <v>54051</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2463,67 +2469,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W23" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W23" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>53381</v>
+        <v>54369</v>
       </c>
       <c r="C24" t="n">
-        <v>54423</v>
+        <v>54884</v>
       </c>
       <c r="D24" t="n">
-        <v>53267</v>
+        <v>54342</v>
       </c>
       <c r="E24" t="n">
-        <v>54268</v>
+        <v>54494</v>
       </c>
       <c r="F24" t="n">
-        <v>934</v>
+        <v>226</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0042</v>
       </c>
       <c r="H24" t="n">
-        <v>1156</v>
+        <v>542</v>
       </c>
       <c r="I24" t="n">
-        <v>52140</v>
+        <v>52111</v>
       </c>
       <c r="J24" t="n">
-        <v>52816.25</v>
+        <v>53323.5</v>
       </c>
       <c r="K24" t="n">
-        <v>53015.5</v>
+        <v>53690</v>
       </c>
       <c r="L24" t="n">
-        <v>53214.75</v>
+        <v>54056.5</v>
       </c>
       <c r="M24" t="n">
-        <v>53652.5</v>
+        <v>54846</v>
       </c>
       <c r="N24" t="n">
-        <v>54090.25</v>
+        <v>55635.5</v>
       </c>
       <c r="O24" t="n">
-        <v>54051</v>
+        <v>55579</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2541,18 +2545,14 @@
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
@@ -2564,70 +2564,72 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>54369</v>
+        <v>54555</v>
       </c>
       <c r="C25" t="n">
-        <v>54884</v>
+        <v>54678</v>
       </c>
       <c r="D25" t="n">
-        <v>54342</v>
+        <v>53952</v>
       </c>
       <c r="E25" t="n">
-        <v>54494</v>
+        <v>54013</v>
       </c>
       <c r="F25" t="n">
-        <v>226</v>
+        <v>-481</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>542</v>
+        <v>726</v>
       </c>
       <c r="I25" t="n">
-        <v>52111</v>
+        <v>53800</v>
       </c>
       <c r="J25" t="n">
-        <v>53323.5</v>
+        <v>53892.5</v>
       </c>
       <c r="K25" t="n">
-        <v>53690</v>
+        <v>54223</v>
       </c>
       <c r="L25" t="n">
-        <v>54056.5</v>
+        <v>54553.5</v>
       </c>
       <c r="M25" t="n">
-        <v>54846</v>
+        <v>54765</v>
       </c>
       <c r="N25" t="n">
-        <v>55635.5</v>
+        <v>54976.5</v>
       </c>
       <c r="O25" t="n">
-        <v>55579</v>
+        <v>55426</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
+      <c r="Q25" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
       <c r="U25" s="8" t="n">
         <v/>
       </c>
@@ -2639,72 +2641,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>54555</v>
+        <v>54040</v>
       </c>
       <c r="C26" t="n">
-        <v>54678</v>
+        <v>54202</v>
       </c>
       <c r="D26" t="n">
-        <v>53952</v>
+        <v>53879</v>
       </c>
       <c r="E26" t="n">
-        <v>54013</v>
+        <v>54152</v>
       </c>
       <c r="F26" t="n">
-        <v>-481</v>
+        <v>139</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0026</v>
       </c>
       <c r="H26" t="n">
-        <v>726</v>
+        <v>323</v>
       </c>
       <c r="I26" t="n">
-        <v>53800</v>
+        <v>53226</v>
       </c>
       <c r="J26" t="n">
-        <v>53892.5</v>
+        <v>53136</v>
       </c>
       <c r="K26" t="n">
-        <v>54223</v>
+        <v>53650</v>
       </c>
       <c r="L26" t="n">
-        <v>54553.5</v>
+        <v>54164</v>
       </c>
       <c r="M26" t="n">
-        <v>54765</v>
+        <v>54376</v>
       </c>
       <c r="N26" t="n">
-        <v>54976.5</v>
+        <v>54588</v>
       </c>
       <c r="O26" t="n">
-        <v>55426</v>
+        <v>55404</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2723,57 +2725,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>54040</v>
+        <v>54133</v>
       </c>
       <c r="C27" t="n">
-        <v>54202</v>
+        <v>54170</v>
       </c>
       <c r="D27" t="n">
-        <v>53879</v>
+        <v>53952</v>
       </c>
       <c r="E27" t="n">
-        <v>54152</v>
+        <v>54063</v>
       </c>
       <c r="F27" t="n">
-        <v>139</v>
+        <v>-89</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0016</v>
       </c>
       <c r="H27" t="n">
-        <v>323</v>
+        <v>218</v>
       </c>
       <c r="I27" t="n">
-        <v>53226</v>
+        <v>53556</v>
       </c>
       <c r="J27" t="n">
-        <v>53136</v>
+        <v>53884.75</v>
       </c>
       <c r="K27" t="n">
-        <v>53650</v>
+        <v>53990.5</v>
       </c>
       <c r="L27" t="n">
-        <v>54164</v>
+        <v>54096.25</v>
       </c>
       <c r="M27" t="n">
-        <v>54376</v>
+        <v>54313.5</v>
       </c>
       <c r="N27" t="n">
-        <v>54588</v>
+        <v>54530.75</v>
       </c>
       <c r="O27" t="n">
-        <v>55404</v>
+        <v>54525</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2781,8 +2783,10 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
@@ -2812,56 +2816,58 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>54133</v>
+        <v>54049</v>
       </c>
       <c r="C28" t="n">
-        <v>54170</v>
+        <v>54336</v>
       </c>
       <c r="D28" t="n">
-        <v>53952</v>
+        <v>53855</v>
       </c>
       <c r="E28" t="n">
-        <v>54063</v>
+        <v>53880</v>
       </c>
       <c r="F28" t="n">
-        <v>-89</v>
+        <v>-183</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0034</v>
       </c>
       <c r="H28" t="n">
-        <v>218</v>
+        <v>481</v>
       </c>
       <c r="I28" t="n">
-        <v>53556</v>
+        <v>53734</v>
       </c>
       <c r="J28" t="n">
-        <v>53884.75</v>
+        <v>53846</v>
       </c>
       <c r="K28" t="n">
-        <v>53990.5</v>
+        <v>53954</v>
       </c>
       <c r="L28" t="n">
-        <v>54096.25</v>
+        <v>54062</v>
       </c>
       <c r="M28" t="n">
-        <v>54313.5</v>
+        <v>54172</v>
       </c>
       <c r="N28" t="n">
-        <v>54530.75</v>
+        <v>54282</v>
       </c>
       <c r="O28" t="n">
-        <v>54525</v>
+        <v>54388</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
@@ -2870,14 +2876,18 @@
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2896,78 +2906,72 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>54049</v>
+        <v>53903</v>
       </c>
       <c r="C29" t="n">
-        <v>54336</v>
+        <v>54150</v>
       </c>
       <c r="D29" t="n">
-        <v>53855</v>
+        <v>53830</v>
       </c>
       <c r="E29" t="n">
-        <v>53880</v>
+        <v>53871</v>
       </c>
       <c r="F29" t="n">
-        <v>-183</v>
+        <v>-9</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0002</v>
       </c>
       <c r="H29" t="n">
-        <v>481</v>
+        <v>320</v>
       </c>
       <c r="I29" t="n">
-        <v>53734</v>
+        <v>53374</v>
       </c>
       <c r="J29" t="n">
-        <v>53846</v>
+        <v>53291.25</v>
       </c>
       <c r="K29" t="n">
-        <v>53954</v>
+        <v>53639.5</v>
       </c>
       <c r="L29" t="n">
-        <v>54062</v>
+        <v>53987.75</v>
       </c>
       <c r="M29" t="n">
-        <v>54172</v>
+        <v>54120.5</v>
       </c>
       <c r="N29" t="n">
-        <v>54282</v>
+        <v>54253.25</v>
       </c>
       <c r="O29" t="n">
-        <v>54388</v>
+        <v>54817</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2979,57 +2983,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>53903</v>
+        <v>53905</v>
       </c>
       <c r="C30" t="n">
-        <v>54150</v>
+        <v>54149</v>
       </c>
       <c r="D30" t="n">
-        <v>53830</v>
+        <v>53715</v>
       </c>
       <c r="E30" t="n">
-        <v>53871</v>
+        <v>53935</v>
       </c>
       <c r="F30" t="n">
-        <v>-9</v>
+        <v>64</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0012</v>
       </c>
       <c r="H30" t="n">
-        <v>320</v>
+        <v>434</v>
       </c>
       <c r="I30" t="n">
-        <v>53374</v>
+        <v>53510</v>
       </c>
       <c r="J30" t="n">
-        <v>53291.25</v>
+        <v>53491.5</v>
       </c>
       <c r="K30" t="n">
-        <v>53639.5</v>
+        <v>53711</v>
       </c>
       <c r="L30" t="n">
-        <v>53987.75</v>
+        <v>53930.5</v>
       </c>
       <c r="M30" t="n">
-        <v>54120.5</v>
+        <v>54031</v>
       </c>
       <c r="N30" t="n">
-        <v>54253.25</v>
+        <v>54131.5</v>
       </c>
       <c r="O30" t="n">
-        <v>54817</v>
+        <v>54470</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3040,9 +3044,9 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
@@ -3050,8 +3054,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U30" s="8" t="n">
-        <v/>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3063,57 +3069,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>53905</v>
+        <v>53961</v>
       </c>
       <c r="C31" t="n">
-        <v>54149</v>
+        <v>53999</v>
       </c>
       <c r="D31" t="n">
-        <v>53715</v>
+        <v>53745</v>
       </c>
       <c r="E31" t="n">
-        <v>53935</v>
+        <v>53807</v>
       </c>
       <c r="F31" t="n">
-        <v>64</v>
+        <v>-128</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0024</v>
       </c>
       <c r="H31" t="n">
-        <v>434</v>
+        <v>254</v>
       </c>
       <c r="I31" t="n">
-        <v>53510</v>
+        <v>53281</v>
       </c>
       <c r="J31" t="n">
-        <v>53491.5</v>
+        <v>53502.5</v>
       </c>
       <c r="K31" t="n">
-        <v>53711</v>
+        <v>53718</v>
       </c>
       <c r="L31" t="n">
-        <v>53930.5</v>
+        <v>53933.5</v>
       </c>
       <c r="M31" t="n">
-        <v>54031</v>
+        <v>54152</v>
       </c>
       <c r="N31" t="n">
-        <v>54131.5</v>
+        <v>54370.5</v>
       </c>
       <c r="O31" t="n">
-        <v>54470</v>
+        <v>54583</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3121,23 +3127,21 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3156,60 +3160,64 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>53961</v>
+        <v>53790</v>
       </c>
       <c r="C32" t="n">
-        <v>53999</v>
+        <v>53840</v>
       </c>
       <c r="D32" t="n">
-        <v>53745</v>
+        <v>53464</v>
       </c>
       <c r="E32" t="n">
-        <v>53807</v>
+        <v>53544</v>
       </c>
       <c r="F32" t="n">
-        <v>-128</v>
+        <v>-263</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0049</v>
       </c>
       <c r="H32" t="n">
-        <v>254</v>
+        <v>376</v>
       </c>
       <c r="I32" t="n">
-        <v>53281</v>
+        <v>53491</v>
       </c>
       <c r="J32" t="n">
-        <v>53502.5</v>
+        <v>53520.5</v>
       </c>
       <c r="K32" t="n">
-        <v>53718</v>
+        <v>53680</v>
       </c>
       <c r="L32" t="n">
-        <v>53933.5</v>
+        <v>53839.5</v>
       </c>
       <c r="M32" t="n">
-        <v>54152</v>
+        <v>53934</v>
       </c>
       <c r="N32" t="n">
-        <v>54370.5</v>
+        <v>54028.5</v>
       </c>
       <c r="O32" t="n">
-        <v>54583</v>
-      </c>
-      <c r="P32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
+        <v>54253</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S32" s="10" t="inlineStr">
@@ -3233,71 +3241,67 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>53790</v>
+        <v>53501</v>
       </c>
       <c r="C33" t="n">
-        <v>53840</v>
+        <v>53594</v>
       </c>
       <c r="D33" t="n">
-        <v>53464</v>
+        <v>53311</v>
       </c>
       <c r="E33" t="n">
-        <v>53544</v>
+        <v>53403</v>
       </c>
       <c r="F33" t="n">
-        <v>-263</v>
+        <v>-141</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0026</v>
       </c>
       <c r="H33" t="n">
-        <v>376</v>
+        <v>283</v>
       </c>
       <c r="I33" t="n">
-        <v>53491</v>
+        <v>53088</v>
       </c>
       <c r="J33" t="n">
-        <v>53520.5</v>
+        <v>53114</v>
       </c>
       <c r="K33" t="n">
-        <v>53680</v>
+        <v>53356</v>
       </c>
       <c r="L33" t="n">
-        <v>53839.5</v>
+        <v>53598</v>
       </c>
       <c r="M33" t="n">
-        <v>53934</v>
+        <v>53732</v>
       </c>
       <c r="N33" t="n">
-        <v>54028.5</v>
+        <v>53866</v>
       </c>
       <c r="O33" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q33" s="6" t="inlineStr">
+        <v>54216</v>
+      </c>
+      <c r="P33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S33" s="10" t="inlineStr">
@@ -3328,50 +3332,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>53501</v>
+        <v>53408</v>
       </c>
       <c r="C34" t="n">
-        <v>53594</v>
+        <v>53780</v>
       </c>
       <c r="D34" t="n">
-        <v>53311</v>
+        <v>53337</v>
       </c>
       <c r="E34" t="n">
-        <v>53403</v>
+        <v>53530</v>
       </c>
       <c r="F34" t="n">
-        <v>-141</v>
+        <v>127</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0026</v>
+        <v>0.0024</v>
       </c>
       <c r="H34" t="n">
-        <v>283</v>
+        <v>443</v>
       </c>
       <c r="I34" t="n">
-        <v>53088</v>
+        <v>53028</v>
       </c>
       <c r="J34" t="n">
-        <v>53114</v>
+        <v>53095.25</v>
       </c>
       <c r="K34" t="n">
-        <v>53356</v>
+        <v>53261.5</v>
       </c>
       <c r="L34" t="n">
-        <v>53598</v>
+        <v>53427.75</v>
       </c>
       <c r="M34" t="n">
-        <v>53732</v>
+        <v>53544.5</v>
       </c>
       <c r="N34" t="n">
-        <v>53866</v>
+        <v>53661.25</v>
       </c>
       <c r="O34" t="n">
-        <v>54216</v>
+        <v>53877</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3379,21 +3383,23 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3403,90 +3409,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>53408</v>
+        <v>53529</v>
       </c>
       <c r="C35" t="n">
-        <v>53780</v>
+        <v>53589</v>
       </c>
       <c r="D35" t="n">
-        <v>53337</v>
+        <v>52812</v>
       </c>
       <c r="E35" t="n">
-        <v>53530</v>
+        <v>52849</v>
       </c>
       <c r="F35" t="n">
-        <v>127</v>
+        <v>-681</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0127</v>
       </c>
       <c r="H35" t="n">
-        <v>443</v>
+        <v>777</v>
       </c>
       <c r="I35" t="n">
-        <v>53028</v>
+        <v>52894</v>
       </c>
       <c r="J35" t="n">
-        <v>53095.25</v>
+        <v>53072.75</v>
       </c>
       <c r="K35" t="n">
-        <v>53261.5</v>
+        <v>53308.5</v>
       </c>
       <c r="L35" t="n">
-        <v>53427.75</v>
+        <v>53544.25</v>
       </c>
       <c r="M35" t="n">
-        <v>53544.5</v>
+        <v>53751.5</v>
       </c>
       <c r="N35" t="n">
-        <v>53661.25</v>
+        <v>53958.75</v>
       </c>
       <c r="O35" t="n">
-        <v>53877</v>
-      </c>
-      <c r="P35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
+        <v>54223</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U35" s="8" t="inlineStr">
+      <c r="Q35" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W35" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr"/>
@@ -3494,77 +3498,75 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>53529</v>
+        <v>52876</v>
       </c>
       <c r="C36" t="n">
-        <v>53589</v>
+        <v>53418</v>
       </c>
       <c r="D36" t="n">
-        <v>52812</v>
+        <v>52838</v>
       </c>
       <c r="E36" t="n">
-        <v>52849</v>
+        <v>53353</v>
       </c>
       <c r="F36" t="n">
-        <v>-681</v>
+        <v>504</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0095</v>
       </c>
       <c r="H36" t="n">
-        <v>777</v>
+        <v>580</v>
       </c>
       <c r="I36" t="n">
-        <v>52894</v>
+        <v>52035</v>
       </c>
       <c r="J36" t="n">
-        <v>53072.75</v>
+        <v>51896.25</v>
       </c>
       <c r="K36" t="n">
-        <v>53308.5</v>
+        <v>52460.5</v>
       </c>
       <c r="L36" t="n">
-        <v>53544.25</v>
+        <v>53024.75</v>
       </c>
       <c r="M36" t="n">
-        <v>53751.5</v>
+        <v>53237.5</v>
       </c>
       <c r="N36" t="n">
-        <v>53958.75</v>
+        <v>53450.25</v>
       </c>
       <c r="O36" t="n">
-        <v>54223</v>
-      </c>
-      <c r="P36" s="6" t="inlineStr">
+        <v>54366</v>
+      </c>
+      <c r="P36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
@@ -3573,55 +3575,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>52876</v>
+        <v>53367</v>
       </c>
       <c r="C37" t="n">
-        <v>53418</v>
+        <v>53567</v>
       </c>
       <c r="D37" t="n">
-        <v>52838</v>
+        <v>53210</v>
       </c>
       <c r="E37" t="n">
-        <v>53353</v>
+        <v>53489</v>
       </c>
       <c r="F37" t="n">
-        <v>504</v>
+        <v>136</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.0025</v>
       </c>
       <c r="H37" t="n">
-        <v>580</v>
+        <v>357</v>
       </c>
       <c r="I37" t="n">
-        <v>52035</v>
+        <v>52258</v>
       </c>
       <c r="J37" t="n">
-        <v>51896.25</v>
+        <v>52885.5</v>
       </c>
       <c r="K37" t="n">
-        <v>52460.5</v>
+        <v>53063</v>
       </c>
       <c r="L37" t="n">
-        <v>53024.75</v>
+        <v>53240.5</v>
       </c>
       <c r="M37" t="n">
-        <v>53237.5</v>
+        <v>53643</v>
       </c>
       <c r="N37" t="n">
-        <v>53450.25</v>
+        <v>54045.5</v>
       </c>
       <c r="O37" t="n">
-        <v>54366</v>
+        <v>53998</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3639,14 +3645,12 @@
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
@@ -3657,57 +3661,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>53367</v>
+        <v>53524</v>
       </c>
       <c r="C38" t="n">
-        <v>53567</v>
+        <v>53797</v>
       </c>
       <c r="D38" t="n">
-        <v>53210</v>
+        <v>53426</v>
       </c>
       <c r="E38" t="n">
-        <v>53489</v>
+        <v>53645</v>
       </c>
       <c r="F38" t="n">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0029</v>
       </c>
       <c r="H38" t="n">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="I38" t="n">
-        <v>52258</v>
+        <v>52853</v>
       </c>
       <c r="J38" t="n">
-        <v>52885.5</v>
+        <v>53182.25</v>
       </c>
       <c r="K38" t="n">
-        <v>53063</v>
+        <v>53310.5</v>
       </c>
       <c r="L38" t="n">
-        <v>53240.5</v>
+        <v>53438.75</v>
       </c>
       <c r="M38" t="n">
-        <v>53643</v>
+        <v>53667.5</v>
       </c>
       <c r="N38" t="n">
-        <v>54045.5</v>
+        <v>53896.25</v>
       </c>
       <c r="O38" t="n">
-        <v>53998</v>
+        <v>53924</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3748,50 +3752,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>53524</v>
+        <v>53643</v>
       </c>
       <c r="C39" t="n">
-        <v>53797</v>
+        <v>53778</v>
       </c>
       <c r="D39" t="n">
-        <v>53426</v>
+        <v>53435</v>
       </c>
       <c r="E39" t="n">
-        <v>53645</v>
+        <v>53521</v>
       </c>
       <c r="F39" t="n">
-        <v>156</v>
+        <v>-124</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0023</v>
       </c>
       <c r="H39" t="n">
-        <v>371</v>
+        <v>343</v>
       </c>
       <c r="I39" t="n">
-        <v>52853</v>
+        <v>53055</v>
       </c>
       <c r="J39" t="n">
-        <v>53182.25</v>
+        <v>53290.75</v>
       </c>
       <c r="K39" t="n">
-        <v>53310.5</v>
+        <v>53459.5</v>
       </c>
       <c r="L39" t="n">
-        <v>53438.75</v>
+        <v>53628.25</v>
       </c>
       <c r="M39" t="n">
-        <v>53667.5</v>
+        <v>53830.5</v>
       </c>
       <c r="N39" t="n">
-        <v>53896.25</v>
+        <v>54032.75</v>
       </c>
       <c r="O39" t="n">
-        <v>53924</v>
+        <v>54168</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3799,19 +3803,19 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3825,57 +3829,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>53643</v>
+        <v>53724</v>
       </c>
       <c r="C40" t="n">
-        <v>53778</v>
+        <v>53811</v>
       </c>
       <c r="D40" t="n">
-        <v>53435</v>
+        <v>53369</v>
       </c>
       <c r="E40" t="n">
-        <v>53521</v>
+        <v>53621</v>
       </c>
       <c r="F40" t="n">
-        <v>-124</v>
+        <v>100</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0019</v>
       </c>
       <c r="H40" t="n">
-        <v>343</v>
+        <v>442</v>
       </c>
       <c r="I40" t="n">
-        <v>53055</v>
+        <v>53092</v>
       </c>
       <c r="J40" t="n">
-        <v>53290.75</v>
+        <v>53135.25</v>
       </c>
       <c r="K40" t="n">
-        <v>53459.5</v>
+        <v>53349.5</v>
       </c>
       <c r="L40" t="n">
-        <v>53628.25</v>
+        <v>53563.75</v>
       </c>
       <c r="M40" t="n">
-        <v>53830.5</v>
+        <v>53692.5</v>
       </c>
       <c r="N40" t="n">
-        <v>54032.75</v>
+        <v>53821.25</v>
       </c>
       <c r="O40" t="n">
-        <v>54168</v>
+        <v>54121</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3883,18 +3887,18 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3909,57 +3913,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>53724</v>
+        <v>53608</v>
       </c>
       <c r="C41" t="n">
-        <v>53811</v>
+        <v>53862</v>
       </c>
       <c r="D41" t="n">
-        <v>53369</v>
+        <v>53513</v>
       </c>
       <c r="E41" t="n">
-        <v>53621</v>
+        <v>53584</v>
       </c>
       <c r="F41" t="n">
-        <v>100</v>
+        <v>-37</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0007</v>
       </c>
       <c r="H41" t="n">
-        <v>442</v>
+        <v>349</v>
       </c>
       <c r="I41" t="n">
-        <v>53092</v>
+        <v>52927</v>
       </c>
       <c r="J41" t="n">
-        <v>53135.25</v>
+        <v>53194.5</v>
       </c>
       <c r="K41" t="n">
-        <v>53349.5</v>
+        <v>53400</v>
       </c>
       <c r="L41" t="n">
-        <v>53563.75</v>
+        <v>53605.5</v>
       </c>
       <c r="M41" t="n">
-        <v>53692.5</v>
+        <v>53842</v>
       </c>
       <c r="N41" t="n">
-        <v>53821.25</v>
+        <v>54078.5</v>
       </c>
       <c r="O41" t="n">
-        <v>54121</v>
+        <v>54253</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3970,9 +3974,9 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
@@ -4000,69 +4004,73 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>53608</v>
+        <v>53664</v>
       </c>
       <c r="C42" t="n">
-        <v>53862</v>
+        <v>53664</v>
       </c>
       <c r="D42" t="n">
-        <v>53513</v>
+        <v>53149</v>
       </c>
       <c r="E42" t="n">
-        <v>53584</v>
+        <v>53240</v>
       </c>
       <c r="F42" t="n">
-        <v>-37</v>
+        <v>-344</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0064</v>
       </c>
       <c r="H42" t="n">
-        <v>349</v>
+        <v>515</v>
       </c>
       <c r="I42" t="n">
-        <v>52927</v>
+        <v>53164</v>
       </c>
       <c r="J42" t="n">
-        <v>53194.5</v>
+        <v>53183.25</v>
       </c>
       <c r="K42" t="n">
-        <v>53400</v>
+        <v>53409.5</v>
       </c>
       <c r="L42" t="n">
-        <v>53605.5</v>
+        <v>53635.75</v>
       </c>
       <c r="M42" t="n">
-        <v>53842</v>
+        <v>53758.5</v>
       </c>
       <c r="N42" t="n">
-        <v>54078.5</v>
+        <v>53881.25</v>
       </c>
       <c r="O42" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+        <v>54211</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4075,73 +4083,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>53664</v>
+        <v>53259</v>
       </c>
       <c r="C43" t="n">
-        <v>53664</v>
+        <v>53343</v>
       </c>
       <c r="D43" t="n">
-        <v>53149</v>
+        <v>52747</v>
       </c>
       <c r="E43" t="n">
-        <v>53240</v>
+        <v>52828</v>
       </c>
       <c r="F43" t="n">
-        <v>-344</v>
+        <v>-412</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0064</v>
+        <v>-0.0077</v>
       </c>
       <c r="H43" t="n">
-        <v>515</v>
+        <v>596</v>
       </c>
       <c r="I43" t="n">
-        <v>53164</v>
+        <v>52634</v>
       </c>
       <c r="J43" t="n">
-        <v>53183.25</v>
+        <v>52641.75</v>
       </c>
       <c r="K43" t="n">
-        <v>53409.5</v>
+        <v>52982.5</v>
       </c>
       <c r="L43" t="n">
-        <v>53635.75</v>
+        <v>53323.25</v>
       </c>
       <c r="M43" t="n">
-        <v>53758.5</v>
+        <v>53497.5</v>
       </c>
       <c r="N43" t="n">
-        <v>53881.25</v>
+        <v>53671.75</v>
       </c>
       <c r="O43" t="n">
-        <v>54211</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
+        <v>54179</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
@@ -4168,50 +4168,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>53259</v>
+        <v>52844</v>
       </c>
       <c r="C44" t="n">
-        <v>53343</v>
+        <v>53283</v>
       </c>
       <c r="D44" t="n">
-        <v>52747</v>
+        <v>52720</v>
       </c>
       <c r="E44" t="n">
-        <v>52828</v>
+        <v>53121</v>
       </c>
       <c r="F44" t="n">
-        <v>-412</v>
+        <v>293</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0077</v>
+        <v>0.0055</v>
       </c>
       <c r="H44" t="n">
-        <v>596</v>
+        <v>563</v>
       </c>
       <c r="I44" t="n">
-        <v>52634</v>
+        <v>52151</v>
       </c>
       <c r="J44" t="n">
-        <v>52641.75</v>
+        <v>52123.5</v>
       </c>
       <c r="K44" t="n">
-        <v>52982.5</v>
+        <v>52530</v>
       </c>
       <c r="L44" t="n">
-        <v>53323.25</v>
+        <v>52936.5</v>
       </c>
       <c r="M44" t="n">
-        <v>53497.5</v>
+        <v>53126</v>
       </c>
       <c r="N44" t="n">
-        <v>53671.75</v>
+        <v>53315.5</v>
       </c>
       <c r="O44" t="n">
-        <v>54179</v>
+        <v>53939</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4219,19 +4219,19 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
@@ -4243,55 +4243,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>52844</v>
+        <v>53120</v>
       </c>
       <c r="C45" t="n">
-        <v>53283</v>
+        <v>53827</v>
       </c>
       <c r="D45" t="n">
-        <v>52720</v>
+        <v>53093</v>
       </c>
       <c r="E45" t="n">
-        <v>53121</v>
+        <v>53745</v>
       </c>
       <c r="F45" t="n">
-        <v>293</v>
+        <v>624</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0117</v>
       </c>
       <c r="H45" t="n">
-        <v>563</v>
+        <v>734</v>
       </c>
       <c r="I45" t="n">
-        <v>52151</v>
+        <v>52157</v>
       </c>
       <c r="J45" t="n">
-        <v>52123.5</v>
+        <v>52617.75</v>
       </c>
       <c r="K45" t="n">
-        <v>52530</v>
+        <v>52839.5</v>
       </c>
       <c r="L45" t="n">
-        <v>52936.5</v>
+        <v>53061.25</v>
       </c>
       <c r="M45" t="n">
-        <v>53126</v>
+        <v>53402.5</v>
       </c>
       <c r="N45" t="n">
-        <v>53315.5</v>
+        <v>53743.75</v>
       </c>
       <c r="O45" t="n">
-        <v>53939</v>
+        <v>53846</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4309,73 +4313,71 @@
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W45" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>53120</v>
+        <v>53707</v>
       </c>
       <c r="C46" t="n">
-        <v>53827</v>
+        <v>53772</v>
       </c>
       <c r="D46" t="n">
-        <v>53093</v>
+        <v>53235</v>
       </c>
       <c r="E46" t="n">
-        <v>53745</v>
+        <v>53440</v>
       </c>
       <c r="F46" t="n">
-        <v>624</v>
+        <v>-305</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0117</v>
+        <v>-0.0057</v>
       </c>
       <c r="H46" t="n">
-        <v>734</v>
+        <v>537</v>
       </c>
       <c r="I46" t="n">
-        <v>52157</v>
+        <v>52359</v>
       </c>
       <c r="J46" t="n">
-        <v>52617.75</v>
+        <v>53153.5</v>
       </c>
       <c r="K46" t="n">
-        <v>52839.5</v>
+        <v>53378</v>
       </c>
       <c r="L46" t="n">
-        <v>53061.25</v>
+        <v>53602.5</v>
       </c>
       <c r="M46" t="n">
-        <v>53402.5</v>
+        <v>54112</v>
       </c>
       <c r="N46" t="n">
-        <v>53743.75</v>
+        <v>54621.5</v>
       </c>
       <c r="O46" t="n">
-        <v>53846</v>
+        <v>54561</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4383,24 +4385,22 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
@@ -4409,65 +4409,71 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>53707</v>
+        <v>53261</v>
       </c>
       <c r="C47" t="n">
-        <v>53772</v>
+        <v>53336</v>
       </c>
       <c r="D47" t="n">
-        <v>53235</v>
+        <v>52758</v>
       </c>
       <c r="E47" t="n">
-        <v>53440</v>
+        <v>52832</v>
       </c>
       <c r="F47" t="n">
-        <v>-305</v>
+        <v>-608</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0057</v>
+        <v>-0.0114</v>
       </c>
       <c r="H47" t="n">
-        <v>537</v>
+        <v>578</v>
       </c>
       <c r="I47" t="n">
-        <v>52359</v>
+        <v>52698</v>
       </c>
       <c r="J47" t="n">
-        <v>53153.5</v>
+        <v>52871.25</v>
       </c>
       <c r="K47" t="n">
-        <v>53378</v>
+        <v>53171.5</v>
       </c>
       <c r="L47" t="n">
-        <v>53602.5</v>
+        <v>53471.75</v>
       </c>
       <c r="M47" t="n">
-        <v>54112</v>
+        <v>53708.5</v>
       </c>
       <c r="N47" t="n">
-        <v>54621.5</v>
+        <v>53945.25</v>
       </c>
       <c r="O47" t="n">
-        <v>54561</v>
+        <v>54309</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
@@ -4484,76 +4490,70 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W47" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>53261</v>
+        <v>52817</v>
       </c>
       <c r="C48" t="n">
-        <v>53336</v>
+        <v>52859</v>
       </c>
       <c r="D48" t="n">
-        <v>52758</v>
+        <v>52339</v>
       </c>
       <c r="E48" t="n">
-        <v>52832</v>
+        <v>52425</v>
       </c>
       <c r="F48" t="n">
-        <v>-608</v>
+        <v>-407</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0114</v>
+        <v>-0.0077</v>
       </c>
       <c r="H48" t="n">
-        <v>578</v>
+        <v>520</v>
       </c>
       <c r="I48" t="n">
-        <v>52698</v>
+        <v>52180</v>
       </c>
       <c r="J48" t="n">
-        <v>52871.25</v>
+        <v>52146.5</v>
       </c>
       <c r="K48" t="n">
-        <v>53171.5</v>
+        <v>52543</v>
       </c>
       <c r="L48" t="n">
-        <v>53471.75</v>
+        <v>52939.5</v>
       </c>
       <c r="M48" t="n">
-        <v>53708.5</v>
+        <v>53121</v>
       </c>
       <c r="N48" t="n">
-        <v>53945.25</v>
+        <v>53302.5</v>
       </c>
       <c r="O48" t="n">
-        <v>54309</v>
+        <v>53914</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
@@ -4580,50 +4580,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>52817</v>
+        <v>52473</v>
       </c>
       <c r="C49" t="n">
-        <v>52859</v>
+        <v>52676</v>
       </c>
       <c r="D49" t="n">
-        <v>52339</v>
+        <v>51992</v>
       </c>
       <c r="E49" t="n">
-        <v>52425</v>
+        <v>52095</v>
       </c>
       <c r="F49" t="n">
-        <v>-407</v>
+        <v>-330</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0077</v>
+        <v>-0.0063</v>
       </c>
       <c r="H49" t="n">
-        <v>520</v>
+        <v>684</v>
       </c>
       <c r="I49" t="n">
-        <v>52180</v>
+        <v>51819</v>
       </c>
       <c r="J49" t="n">
-        <v>52146.5</v>
+        <v>51818</v>
       </c>
       <c r="K49" t="n">
-        <v>52543</v>
+        <v>52165</v>
       </c>
       <c r="L49" t="n">
-        <v>52939.5</v>
+        <v>52512</v>
       </c>
       <c r="M49" t="n">
-        <v>53121</v>
+        <v>52685</v>
       </c>
       <c r="N49" t="n">
-        <v>53302.5</v>
+        <v>52858</v>
       </c>
       <c r="O49" t="n">
-        <v>53914</v>
+        <v>53379</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4660,50 +4660,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>52473</v>
+        <v>52059</v>
       </c>
       <c r="C50" t="n">
-        <v>52676</v>
+        <v>52739</v>
       </c>
       <c r="D50" t="n">
-        <v>51992</v>
+        <v>52059</v>
       </c>
       <c r="E50" t="n">
-        <v>52095</v>
+        <v>52585</v>
       </c>
       <c r="F50" t="n">
-        <v>-330</v>
+        <v>490</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0063</v>
+        <v>0.0094</v>
       </c>
       <c r="H50" t="n">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="I50" t="n">
-        <v>51819</v>
+        <v>51308</v>
       </c>
       <c r="J50" t="n">
-        <v>51818</v>
+        <v>51291.5</v>
       </c>
       <c r="K50" t="n">
-        <v>52165</v>
+        <v>51753</v>
       </c>
       <c r="L50" t="n">
-        <v>52512</v>
+        <v>52214.5</v>
       </c>
       <c r="M50" t="n">
-        <v>52685</v>
+        <v>52437</v>
       </c>
       <c r="N50" t="n">
-        <v>52858</v>
+        <v>52659.5</v>
       </c>
       <c r="O50" t="n">
-        <v>53379</v>
+        <v>53360</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4711,22 +4711,24 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
@@ -4735,55 +4737,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>52059</v>
+        <v>52376</v>
       </c>
       <c r="C51" t="n">
-        <v>52739</v>
+        <v>52672</v>
       </c>
       <c r="D51" t="n">
-        <v>52059</v>
+        <v>52226</v>
       </c>
       <c r="E51" t="n">
-        <v>52585</v>
+        <v>52440</v>
       </c>
       <c r="F51" t="n">
-        <v>490</v>
+        <v>-145</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0094</v>
+        <v>-0.0028</v>
       </c>
       <c r="H51" t="n">
-        <v>680</v>
+        <v>446</v>
       </c>
       <c r="I51" t="n">
-        <v>51308</v>
+        <v>51379</v>
       </c>
       <c r="J51" t="n">
-        <v>51291.5</v>
+        <v>51998</v>
       </c>
       <c r="K51" t="n">
-        <v>51753</v>
+        <v>52245</v>
       </c>
       <c r="L51" t="n">
-        <v>52214.5</v>
+        <v>52492</v>
       </c>
       <c r="M51" t="n">
-        <v>52437</v>
+        <v>52925</v>
       </c>
       <c r="N51" t="n">
-        <v>52659.5</v>
+        <v>53358</v>
       </c>
       <c r="O51" t="n">
-        <v>53360</v>
+        <v>53419</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4791,23 +4797,21 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4819,72 +4823,74 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>52376</v>
+        <v>52499</v>
       </c>
       <c r="C52" t="n">
-        <v>52672</v>
+        <v>52499</v>
       </c>
       <c r="D52" t="n">
-        <v>52226</v>
+        <v>51908</v>
       </c>
       <c r="E52" t="n">
-        <v>52440</v>
+        <v>52115</v>
       </c>
       <c r="F52" t="n">
-        <v>-145</v>
+        <v>-325</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0028</v>
+        <v>-0.0062</v>
       </c>
       <c r="H52" t="n">
-        <v>446</v>
+        <v>591</v>
       </c>
       <c r="I52" t="n">
-        <v>51379</v>
+        <v>51780</v>
       </c>
       <c r="J52" t="n">
-        <v>51998</v>
+        <v>51989.5</v>
       </c>
       <c r="K52" t="n">
-        <v>52245</v>
+        <v>52217</v>
       </c>
       <c r="L52" t="n">
-        <v>52492</v>
+        <v>52444.5</v>
       </c>
       <c r="M52" t="n">
-        <v>52925</v>
+        <v>52663</v>
       </c>
       <c r="N52" t="n">
-        <v>53358</v>
+        <v>52881.5</v>
       </c>
       <c r="O52" t="n">
-        <v>53419</v>
+        <v>53118</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4901,71 +4907,69 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>52499</v>
+        <v>52162</v>
       </c>
       <c r="C53" t="n">
-        <v>52499</v>
+        <v>52298</v>
       </c>
       <c r="D53" t="n">
-        <v>51908</v>
+        <v>51209</v>
       </c>
       <c r="E53" t="n">
-        <v>52115</v>
+        <v>51507</v>
       </c>
       <c r="F53" t="n">
-        <v>-325</v>
+        <v>-608</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0062</v>
+        <v>-0.0117</v>
       </c>
       <c r="H53" t="n">
-        <v>591</v>
+        <v>1089</v>
       </c>
       <c r="I53" t="n">
-        <v>51780</v>
+        <v>51317</v>
       </c>
       <c r="J53" t="n">
-        <v>51989.5</v>
+        <v>51479.75</v>
       </c>
       <c r="K53" t="n">
-        <v>52217</v>
+        <v>51819.5</v>
       </c>
       <c r="L53" t="n">
-        <v>52444.5</v>
+        <v>52159.25</v>
       </c>
       <c r="M53" t="n">
-        <v>52663</v>
+        <v>52410.5</v>
       </c>
       <c r="N53" t="n">
-        <v>52881.5</v>
+        <v>52661.75</v>
       </c>
       <c r="O53" t="n">
-        <v>53118</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
+        <v>53090</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="S53" s="10" t="inlineStr">
@@ -4992,74 +4996,70 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>52162</v>
+        <v>51486</v>
       </c>
       <c r="C54" t="n">
-        <v>52298</v>
+        <v>52169</v>
       </c>
       <c r="D54" t="n">
-        <v>51209</v>
+        <v>51455</v>
       </c>
       <c r="E54" t="n">
-        <v>51507</v>
+        <v>51807</v>
       </c>
       <c r="F54" t="n">
-        <v>-608</v>
+        <v>300</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0117</v>
+        <v>0.0058</v>
       </c>
       <c r="H54" t="n">
-        <v>1089</v>
+        <v>714</v>
       </c>
       <c r="I54" t="n">
-        <v>51317</v>
+        <v>50120</v>
       </c>
       <c r="J54" t="n">
-        <v>51479.75</v>
+        <v>50294.75</v>
       </c>
       <c r="K54" t="n">
-        <v>51819.5</v>
+        <v>50962.5</v>
       </c>
       <c r="L54" t="n">
-        <v>52159.25</v>
+        <v>51630.25</v>
       </c>
       <c r="M54" t="n">
-        <v>52410.5</v>
+        <v>52051.5</v>
       </c>
       <c r="N54" t="n">
-        <v>52661.75</v>
+        <v>52472.75</v>
       </c>
       <c r="O54" t="n">
-        <v>53090</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
+        <v>53387</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
       <c r="U54" s="8" t="n">
         <v/>
       </c>
@@ -5071,55 +5071,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>51486</v>
+        <v>51800</v>
       </c>
       <c r="C55" t="n">
-        <v>52169</v>
+        <v>51957</v>
       </c>
       <c r="D55" t="n">
-        <v>51455</v>
+        <v>51576</v>
       </c>
       <c r="E55" t="n">
-        <v>51807</v>
+        <v>51761</v>
       </c>
       <c r="F55" t="n">
-        <v>300</v>
+        <v>-46</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0009</v>
       </c>
       <c r="H55" t="n">
-        <v>714</v>
+        <v>381</v>
       </c>
       <c r="I55" t="n">
-        <v>50120</v>
+        <v>50741</v>
       </c>
       <c r="J55" t="n">
-        <v>50294.75</v>
+        <v>51090.5</v>
       </c>
       <c r="K55" t="n">
-        <v>50962.5</v>
+        <v>51450</v>
       </c>
       <c r="L55" t="n">
-        <v>51630.25</v>
+        <v>51809.5</v>
       </c>
       <c r="M55" t="n">
-        <v>52051.5</v>
+        <v>52164</v>
       </c>
       <c r="N55" t="n">
-        <v>52472.75</v>
+        <v>52518.5</v>
       </c>
       <c r="O55" t="n">
-        <v>53387</v>
+        <v>52883</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5130,15 +5134,13 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5153,57 +5155,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>51800</v>
+        <v>52085</v>
       </c>
       <c r="C56" t="n">
-        <v>51957</v>
+        <v>52557</v>
       </c>
       <c r="D56" t="n">
-        <v>51576</v>
+        <v>52080</v>
       </c>
       <c r="E56" t="n">
-        <v>51761</v>
+        <v>52475</v>
       </c>
       <c r="F56" t="n">
-        <v>-46</v>
+        <v>714</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0138</v>
       </c>
       <c r="H56" t="n">
-        <v>381</v>
+        <v>477</v>
       </c>
       <c r="I56" t="n">
-        <v>50741</v>
+        <v>51195</v>
       </c>
       <c r="J56" t="n">
-        <v>51090.5</v>
+        <v>51377.25</v>
       </c>
       <c r="K56" t="n">
-        <v>51450</v>
+        <v>51570.5</v>
       </c>
       <c r="L56" t="n">
-        <v>51809.5</v>
+        <v>51763.75</v>
       </c>
       <c r="M56" t="n">
-        <v>52164</v>
+        <v>51951.5</v>
       </c>
       <c r="N56" t="n">
-        <v>52518.5</v>
+        <v>52139.25</v>
       </c>
       <c r="O56" t="n">
-        <v>52883</v>
+        <v>52338</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5214,78 +5216,80 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W56" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W56" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>52085</v>
+        <v>52470</v>
       </c>
       <c r="C57" t="n">
-        <v>52557</v>
+        <v>52844</v>
       </c>
       <c r="D57" t="n">
-        <v>52080</v>
+        <v>52125</v>
       </c>
       <c r="E57" t="n">
-        <v>52475</v>
+        <v>52279</v>
       </c>
       <c r="F57" t="n">
-        <v>714</v>
+        <v>-196</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0138</v>
+        <v>-0.0037</v>
       </c>
       <c r="H57" t="n">
-        <v>477</v>
+        <v>719</v>
       </c>
       <c r="I57" t="n">
-        <v>51195</v>
+        <v>51603</v>
       </c>
       <c r="J57" t="n">
-        <v>51377.25</v>
+        <v>52076.25</v>
       </c>
       <c r="K57" t="n">
-        <v>51570.5</v>
+        <v>52236.5</v>
       </c>
       <c r="L57" t="n">
-        <v>51763.75</v>
+        <v>52396.75</v>
       </c>
       <c r="M57" t="n">
-        <v>51951.5</v>
+        <v>52713.5</v>
       </c>
       <c r="N57" t="n">
-        <v>52139.25</v>
+        <v>53030.25</v>
       </c>
       <c r="O57" t="n">
-        <v>52338</v>
+        <v>53034</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5293,12 +5297,14 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
@@ -5306,70 +5312,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
       </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>52470</v>
+        <v>52255</v>
       </c>
       <c r="C58" t="n">
-        <v>52844</v>
+        <v>52371</v>
       </c>
       <c r="D58" t="n">
-        <v>52125</v>
+        <v>51844</v>
       </c>
       <c r="E58" t="n">
-        <v>52279</v>
+        <v>51873</v>
       </c>
       <c r="F58" t="n">
-        <v>-196</v>
+        <v>-406</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0037</v>
+        <v>-0.0078</v>
       </c>
       <c r="H58" t="n">
-        <v>719</v>
+        <v>527</v>
       </c>
       <c r="I58" t="n">
-        <v>51603</v>
+        <v>51406</v>
       </c>
       <c r="J58" t="n">
-        <v>52076.25</v>
+        <v>51457.25</v>
       </c>
       <c r="K58" t="n">
-        <v>52236.5</v>
+        <v>51919.5</v>
       </c>
       <c r="L58" t="n">
-        <v>52396.75</v>
+        <v>52381.75</v>
       </c>
       <c r="M58" t="n">
-        <v>52713.5</v>
+        <v>52638.5</v>
       </c>
       <c r="N58" t="n">
-        <v>53030.25</v>
+        <v>52895.25</v>
       </c>
       <c r="O58" t="n">
-        <v>53034</v>
+        <v>53563</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5387,10 +5393,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5405,57 +5409,57 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>52255</v>
+        <v>51878</v>
       </c>
       <c r="C59" t="n">
-        <v>52371</v>
+        <v>51905</v>
       </c>
       <c r="D59" t="n">
-        <v>51844</v>
+        <v>51479</v>
       </c>
       <c r="E59" t="n">
-        <v>51873</v>
+        <v>51717</v>
       </c>
       <c r="F59" t="n">
-        <v>-406</v>
+        <v>-156</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0078</v>
+        <v>-0.003</v>
       </c>
       <c r="H59" t="n">
-        <v>527</v>
+        <v>426</v>
       </c>
       <c r="I59" t="n">
-        <v>51406</v>
+        <v>51317</v>
       </c>
       <c r="J59" t="n">
-        <v>51457.25</v>
+        <v>51228.75</v>
       </c>
       <c r="K59" t="n">
-        <v>51919.5</v>
+        <v>51609.5</v>
       </c>
       <c r="L59" t="n">
-        <v>52381.75</v>
+        <v>51990.25</v>
       </c>
       <c r="M59" t="n">
-        <v>52638.5</v>
+        <v>52136.5</v>
       </c>
       <c r="N59" t="n">
-        <v>52895.25</v>
+        <v>52282.75</v>
       </c>
       <c r="O59" t="n">
-        <v>53563</v>
+        <v>52898</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5496,50 +5500,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>51878</v>
+        <v>51655</v>
       </c>
       <c r="C60" t="n">
-        <v>51905</v>
+        <v>52223</v>
       </c>
       <c r="D60" t="n">
-        <v>51479</v>
+        <v>51610</v>
       </c>
       <c r="E60" t="n">
-        <v>51717</v>
+        <v>52163</v>
       </c>
       <c r="F60" t="n">
-        <v>-156</v>
+        <v>446</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.0086</v>
       </c>
       <c r="H60" t="n">
-        <v>426</v>
+        <v>613</v>
       </c>
       <c r="I60" t="n">
-        <v>51317</v>
+        <v>51053</v>
       </c>
       <c r="J60" t="n">
-        <v>51228.75</v>
+        <v>51303.5</v>
       </c>
       <c r="K60" t="n">
-        <v>51609.5</v>
+        <v>51504</v>
       </c>
       <c r="L60" t="n">
-        <v>51990.25</v>
+        <v>51704.5</v>
       </c>
       <c r="M60" t="n">
-        <v>52136.5</v>
+        <v>51930</v>
       </c>
       <c r="N60" t="n">
-        <v>52282.75</v>
+        <v>52155.5</v>
       </c>
       <c r="O60" t="n">
-        <v>52898</v>
+        <v>52331</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5547,22 +5551,24 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="inlineStr">
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U60" s="8" t="n">
-        <v/>
-      </c>
       <c r="V60" s="8" t="n">
         <v/>
       </c>
@@ -5571,59 +5577,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>51655</v>
+        <v>52140</v>
       </c>
       <c r="C61" t="n">
-        <v>52223</v>
+        <v>52153</v>
       </c>
       <c r="D61" t="n">
-        <v>51610</v>
+        <v>51744</v>
       </c>
       <c r="E61" t="n">
-        <v>52163</v>
+        <v>51837</v>
       </c>
       <c r="F61" t="n">
-        <v>446</v>
+        <v>-326</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.0062</v>
       </c>
       <c r="H61" t="n">
-        <v>613</v>
+        <v>409</v>
       </c>
       <c r="I61" t="n">
-        <v>51053</v>
+        <v>50997</v>
       </c>
       <c r="J61" t="n">
-        <v>51303.5</v>
+        <v>51673.25</v>
       </c>
       <c r="K61" t="n">
-        <v>51504</v>
+        <v>51856.5</v>
       </c>
       <c r="L61" t="n">
-        <v>51704.5</v>
+        <v>52039.75</v>
       </c>
       <c r="M61" t="n">
-        <v>51930</v>
+        <v>52469.5</v>
       </c>
       <c r="N61" t="n">
-        <v>52155.5</v>
+        <v>52899.25</v>
       </c>
       <c r="O61" t="n">
-        <v>52331</v>
+        <v>52836</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5631,24 +5633,22 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
+      <c r="R61" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
       <c r="V61" s="8" t="n">
         <v/>
       </c>
@@ -5657,55 +5657,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>51845</v>
+        <v>51765</v>
       </c>
       <c r="C62" t="n">
-        <v>51848</v>
+        <v>51788</v>
       </c>
       <c r="D62" t="n">
-        <v>51815</v>
+        <v>51758</v>
       </c>
       <c r="E62" t="n">
-        <v>51820</v>
+        <v>51787</v>
       </c>
       <c r="F62" t="n">
-        <v>-343</v>
+        <v>-50</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0066</v>
+        <v>-0.001</v>
       </c>
       <c r="H62" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I62" t="n">
-        <v>50997</v>
+        <v>51335</v>
       </c>
       <c r="J62" t="n">
-        <v>51673.25</v>
+        <v>51372.25</v>
       </c>
       <c r="K62" t="n">
-        <v>51856.5</v>
+        <v>51632.5</v>
       </c>
       <c r="L62" t="n">
-        <v>52039.75</v>
+        <v>51892.75</v>
       </c>
       <c r="M62" t="n">
-        <v>52469.5</v>
+        <v>52041.5</v>
       </c>
       <c r="N62" t="n">
-        <v>52899.25</v>
+        <v>52190.25</v>
       </c>
       <c r="O62" t="n">
-        <v>52836</v>
+        <v>52562</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5713,14 +5717,12 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R62" s="6" t="n">
+        <v/>
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53230</v>
+        <v>53405</v>
       </c>
       <c r="C2" t="n">
-        <v>53421</v>
+        <v>53656</v>
       </c>
       <c r="D2" t="n">
-        <v>52962</v>
+        <v>53076</v>
       </c>
       <c r="E2" t="n">
-        <v>53372</v>
+        <v>53197</v>
       </c>
       <c r="F2" t="n">
-        <v>189</v>
+        <v>-175</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0036</v>
+        <v>-0.0033</v>
       </c>
       <c r="H2" t="n">
-        <v>459</v>
+        <v>580</v>
       </c>
       <c r="I2" t="n">
-        <v>51884</v>
+        <v>52503</v>
       </c>
       <c r="J2" t="n">
-        <v>52665.25</v>
+        <v>53003.25</v>
       </c>
       <c r="K2" t="n">
-        <v>52849.5</v>
+        <v>53142.5</v>
       </c>
       <c r="L2" t="n">
-        <v>53033.75</v>
+        <v>53281.75</v>
       </c>
       <c r="M2" t="n">
-        <v>53516.5</v>
+        <v>53601.5</v>
       </c>
       <c r="N2" t="n">
-        <v>53999.25</v>
+        <v>53921.25</v>
       </c>
       <c r="O2" t="n">
-        <v>53885</v>
+        <v>53880</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,17 +685,19 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U2" s="8" t="n">
@@ -709,76 +711,82 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53405</v>
+        <v>53166</v>
       </c>
       <c r="C3" t="n">
-        <v>53656</v>
+        <v>53207</v>
       </c>
       <c r="D3" t="n">
-        <v>53076</v>
+        <v>52343</v>
       </c>
       <c r="E3" t="n">
-        <v>53197</v>
+        <v>52624</v>
       </c>
       <c r="F3" t="n">
-        <v>-175</v>
+        <v>-573</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0108</v>
       </c>
       <c r="H3" t="n">
-        <v>580</v>
+        <v>864</v>
       </c>
       <c r="I3" t="n">
-        <v>52503</v>
+        <v>52496</v>
       </c>
       <c r="J3" t="n">
-        <v>53003.25</v>
+        <v>52532.5</v>
       </c>
       <c r="K3" t="n">
-        <v>53142.5</v>
+        <v>52907</v>
       </c>
       <c r="L3" t="n">
-        <v>53281.75</v>
+        <v>53281.5</v>
       </c>
       <c r="M3" t="n">
-        <v>53601.5</v>
+        <v>53487</v>
       </c>
       <c r="N3" t="n">
-        <v>53921.25</v>
+        <v>53692.5</v>
       </c>
       <c r="O3" t="n">
-        <v>53880</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
+        <v>54236</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -793,76 +801,70 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>53166</v>
+        <v>52541</v>
       </c>
       <c r="C4" t="n">
-        <v>53207</v>
+        <v>52865</v>
       </c>
       <c r="D4" t="n">
-        <v>52343</v>
+        <v>52501</v>
       </c>
       <c r="E4" t="n">
-        <v>52624</v>
+        <v>52761</v>
       </c>
       <c r="F4" t="n">
-        <v>-573</v>
+        <v>137</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0108</v>
+        <v>0.0026</v>
       </c>
       <c r="H4" t="n">
-        <v>864</v>
+        <v>364</v>
       </c>
       <c r="I4" t="n">
-        <v>52496</v>
+        <v>51479</v>
       </c>
       <c r="J4" t="n">
-        <v>52532.5</v>
+        <v>51684.5</v>
       </c>
       <c r="K4" t="n">
-        <v>52907</v>
+        <v>52192</v>
       </c>
       <c r="L4" t="n">
-        <v>53281.5</v>
+        <v>52699.5</v>
       </c>
       <c r="M4" t="n">
-        <v>53487</v>
+        <v>53056</v>
       </c>
       <c r="N4" t="n">
-        <v>53692.5</v>
+        <v>53412.5</v>
       </c>
       <c r="O4" t="n">
-        <v>54236</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>54071</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -881,57 +883,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52541</v>
+        <v>52753</v>
       </c>
       <c r="C5" t="n">
-        <v>52865</v>
+        <v>52992</v>
       </c>
       <c r="D5" t="n">
-        <v>52501</v>
+        <v>52506</v>
       </c>
       <c r="E5" t="n">
-        <v>52761</v>
+        <v>52906</v>
       </c>
       <c r="F5" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0027</v>
       </c>
       <c r="H5" t="n">
-        <v>364</v>
+        <v>486</v>
       </c>
       <c r="I5" t="n">
-        <v>51479</v>
+        <v>52137</v>
       </c>
       <c r="J5" t="n">
-        <v>51684.5</v>
+        <v>52436</v>
       </c>
       <c r="K5" t="n">
-        <v>52192</v>
+        <v>52579</v>
       </c>
       <c r="L5" t="n">
-        <v>52699.5</v>
+        <v>52722</v>
       </c>
       <c r="M5" t="n">
-        <v>53056</v>
+        <v>52943</v>
       </c>
       <c r="N5" t="n">
-        <v>53412.5</v>
+        <v>53164</v>
       </c>
       <c r="O5" t="n">
-        <v>54071</v>
+        <v>53229</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -939,16 +941,20 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -961,59 +967,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52753</v>
+        <v>52844</v>
       </c>
       <c r="C6" t="n">
-        <v>52992</v>
+        <v>53113</v>
       </c>
       <c r="D6" t="n">
-        <v>52506</v>
+        <v>52603</v>
       </c>
       <c r="E6" t="n">
-        <v>52906</v>
+        <v>52764</v>
       </c>
       <c r="F6" t="n">
-        <v>145</v>
+        <v>-142</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0027</v>
       </c>
       <c r="H6" t="n">
-        <v>486</v>
+        <v>510</v>
       </c>
       <c r="I6" t="n">
-        <v>52137</v>
+        <v>52020</v>
       </c>
       <c r="J6" t="n">
-        <v>52436</v>
+        <v>52498.5</v>
       </c>
       <c r="K6" t="n">
-        <v>52579</v>
+        <v>52663</v>
       </c>
       <c r="L6" t="n">
-        <v>52722</v>
+        <v>52827.5</v>
       </c>
       <c r="M6" t="n">
-        <v>52943</v>
+        <v>53149</v>
       </c>
       <c r="N6" t="n">
-        <v>53164</v>
+        <v>53470.5</v>
       </c>
       <c r="O6" t="n">
-        <v>53229</v>
+        <v>53478</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1028,13 +1030,11 @@
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1047,55 +1047,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>52844</v>
+        <v>52731</v>
       </c>
       <c r="C7" t="n">
-        <v>53113</v>
+        <v>52981</v>
       </c>
       <c r="D7" t="n">
-        <v>52603</v>
+        <v>52255</v>
       </c>
       <c r="E7" t="n">
-        <v>52764</v>
+        <v>52791</v>
       </c>
       <c r="F7" t="n">
-        <v>-142</v>
+        <v>27</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0005</v>
       </c>
       <c r="H7" t="n">
-        <v>510</v>
+        <v>726</v>
       </c>
       <c r="I7" t="n">
-        <v>52020</v>
+        <v>52093</v>
       </c>
       <c r="J7" t="n">
-        <v>52498.5</v>
+        <v>52207</v>
       </c>
       <c r="K7" t="n">
-        <v>52663</v>
+        <v>52509</v>
       </c>
       <c r="L7" t="n">
-        <v>52827.5</v>
+        <v>52811</v>
       </c>
       <c r="M7" t="n">
-        <v>53149</v>
+        <v>53019</v>
       </c>
       <c r="N7" t="n">
-        <v>53470.5</v>
+        <v>53227</v>
       </c>
       <c r="O7" t="n">
-        <v>53478</v>
+        <v>53623</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1108,7 +1112,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
+      <c r="S7" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -1129,57 +1133,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52731</v>
+        <v>52792</v>
       </c>
       <c r="C8" t="n">
-        <v>52981</v>
+        <v>53088</v>
       </c>
       <c r="D8" t="n">
-        <v>52255</v>
+        <v>52680</v>
       </c>
       <c r="E8" t="n">
-        <v>52791</v>
+        <v>52900</v>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0021</v>
       </c>
       <c r="H8" t="n">
-        <v>726</v>
+        <v>408</v>
       </c>
       <c r="I8" t="n">
-        <v>52093</v>
+        <v>51529</v>
       </c>
       <c r="J8" t="n">
-        <v>52207</v>
+        <v>52151.5</v>
       </c>
       <c r="K8" t="n">
-        <v>52509</v>
+        <v>52428</v>
       </c>
       <c r="L8" t="n">
-        <v>52811</v>
+        <v>52704.5</v>
       </c>
       <c r="M8" t="n">
-        <v>53019</v>
+        <v>53154</v>
       </c>
       <c r="N8" t="n">
-        <v>53227</v>
+        <v>53603.5</v>
       </c>
       <c r="O8" t="n">
-        <v>53623</v>
+        <v>53707</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1187,14 +1191,12 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R8" s="6" t="n">
+        <v/>
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1211,59 +1213,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52792</v>
+        <v>52919</v>
       </c>
       <c r="C9" t="n">
-        <v>53088</v>
+        <v>53108</v>
       </c>
       <c r="D9" t="n">
-        <v>52680</v>
+        <v>52607</v>
       </c>
       <c r="E9" t="n">
-        <v>52900</v>
+        <v>52786</v>
       </c>
       <c r="F9" t="n">
-        <v>109</v>
+        <v>-114</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0022</v>
       </c>
       <c r="H9" t="n">
-        <v>408</v>
+        <v>501</v>
       </c>
       <c r="I9" t="n">
-        <v>51529</v>
+        <v>52272</v>
       </c>
       <c r="J9" t="n">
-        <v>52151.5</v>
+        <v>52500</v>
       </c>
       <c r="K9" t="n">
-        <v>52428</v>
+        <v>52696</v>
       </c>
       <c r="L9" t="n">
-        <v>52704.5</v>
+        <v>52892</v>
       </c>
       <c r="M9" t="n">
-        <v>53154</v>
+        <v>53104</v>
       </c>
       <c r="N9" t="n">
-        <v>53603.5</v>
+        <v>53316</v>
       </c>
       <c r="O9" t="n">
-        <v>53707</v>
+        <v>53496</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1271,16 +1269,20 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1293,76 +1295,80 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52919</v>
+        <v>52778</v>
       </c>
       <c r="C10" t="n">
-        <v>53108</v>
+        <v>52835</v>
       </c>
       <c r="D10" t="n">
-        <v>52607</v>
+        <v>52174</v>
       </c>
       <c r="E10" t="n">
-        <v>52786</v>
+        <v>52375</v>
       </c>
       <c r="F10" t="n">
-        <v>-114</v>
+        <v>-411</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0078</v>
       </c>
       <c r="H10" t="n">
-        <v>501</v>
+        <v>661</v>
       </c>
       <c r="I10" t="n">
-        <v>52272</v>
+        <v>52106</v>
       </c>
       <c r="J10" t="n">
-        <v>52500</v>
+        <v>52249.25</v>
       </c>
       <c r="K10" t="n">
-        <v>52696</v>
+        <v>52535.5</v>
       </c>
       <c r="L10" t="n">
-        <v>52892</v>
+        <v>52821.75</v>
       </c>
       <c r="M10" t="n">
-        <v>53104</v>
+        <v>53036.5</v>
       </c>
       <c r="N10" t="n">
-        <v>53316</v>
+        <v>53251.25</v>
       </c>
       <c r="O10" t="n">
-        <v>53496</v>
+        <v>53609</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1377,72 +1383,70 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>52778</v>
+        <v>52300</v>
       </c>
       <c r="C11" t="n">
-        <v>52835</v>
+        <v>52633</v>
       </c>
       <c r="D11" t="n">
-        <v>52174</v>
+        <v>51999</v>
       </c>
       <c r="E11" t="n">
-        <v>52375</v>
+        <v>52073</v>
       </c>
       <c r="F11" t="n">
-        <v>-411</v>
+        <v>-302</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0078</v>
+        <v>-0.0058</v>
       </c>
       <c r="H11" t="n">
-        <v>661</v>
+        <v>634</v>
       </c>
       <c r="I11" t="n">
-        <v>52106</v>
+        <v>51513</v>
       </c>
       <c r="J11" t="n">
-        <v>52249.25</v>
+        <v>51649.25</v>
       </c>
       <c r="K11" t="n">
-        <v>52535.5</v>
+        <v>52044.5</v>
       </c>
       <c r="L11" t="n">
-        <v>52821.75</v>
+        <v>52439.75</v>
       </c>
       <c r="M11" t="n">
-        <v>53036.5</v>
+        <v>52705.5</v>
       </c>
       <c r="N11" t="n">
-        <v>53251.25</v>
+        <v>52971.25</v>
       </c>
       <c r="O11" t="n">
-        <v>53609</v>
+        <v>53496</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="S11" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1470,50 +1474,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52300</v>
+        <v>52091</v>
       </c>
       <c r="C12" t="n">
-        <v>52633</v>
+        <v>52590</v>
       </c>
       <c r="D12" t="n">
-        <v>51999</v>
+        <v>52035</v>
       </c>
       <c r="E12" t="n">
-        <v>52073</v>
+        <v>52443</v>
       </c>
       <c r="F12" t="n">
-        <v>-302</v>
+        <v>370</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.0071</v>
       </c>
       <c r="H12" t="n">
-        <v>634</v>
+        <v>555</v>
       </c>
       <c r="I12" t="n">
-        <v>51513</v>
+        <v>51365</v>
       </c>
       <c r="J12" t="n">
-        <v>51649.25</v>
+        <v>51317.5</v>
       </c>
       <c r="K12" t="n">
-        <v>52044.5</v>
+        <v>51756</v>
       </c>
       <c r="L12" t="n">
-        <v>52439.75</v>
+        <v>52194.5</v>
       </c>
       <c r="M12" t="n">
-        <v>52705.5</v>
+        <v>52390</v>
       </c>
       <c r="N12" t="n">
-        <v>52971.25</v>
+        <v>52585.5</v>
       </c>
       <c r="O12" t="n">
-        <v>53496</v>
+        <v>53267</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1521,21 +1525,23 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1547,57 +1553,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>52091</v>
+        <v>52431</v>
       </c>
       <c r="C13" t="n">
-        <v>52590</v>
+        <v>52721</v>
       </c>
       <c r="D13" t="n">
-        <v>52035</v>
+        <v>52262</v>
       </c>
       <c r="E13" t="n">
-        <v>52443</v>
+        <v>52449</v>
       </c>
       <c r="F13" t="n">
-        <v>370</v>
+        <v>6</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0001</v>
       </c>
       <c r="H13" t="n">
-        <v>555</v>
+        <v>459</v>
       </c>
       <c r="I13" t="n">
-        <v>51365</v>
+        <v>51480</v>
       </c>
       <c r="J13" t="n">
-        <v>51317.5</v>
+        <v>51953.25</v>
       </c>
       <c r="K13" t="n">
-        <v>51756</v>
+        <v>52165.5</v>
       </c>
       <c r="L13" t="n">
-        <v>52194.5</v>
+        <v>52377.75</v>
       </c>
       <c r="M13" t="n">
-        <v>52390</v>
+        <v>52720.5</v>
       </c>
       <c r="N13" t="n">
-        <v>52585.5</v>
+        <v>53063.25</v>
       </c>
       <c r="O13" t="n">
-        <v>53267</v>
+        <v>53145</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1608,21 +1614,19 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U13" s="8" t="n">
+        <v/>
+      </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
@@ -1631,78 +1635,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>52431</v>
+        <v>52430</v>
       </c>
       <c r="C14" t="n">
-        <v>52721</v>
+        <v>52515</v>
       </c>
       <c r="D14" t="n">
-        <v>52262</v>
+        <v>51720</v>
       </c>
       <c r="E14" t="n">
-        <v>52449</v>
+        <v>51894</v>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>-555</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0106</v>
       </c>
       <c r="H14" t="n">
-        <v>459</v>
+        <v>795</v>
       </c>
       <c r="I14" t="n">
-        <v>51480</v>
+        <v>51803</v>
       </c>
       <c r="J14" t="n">
-        <v>51953.25</v>
+        <v>51968.75</v>
       </c>
       <c r="K14" t="n">
-        <v>52165.5</v>
+        <v>52219.5</v>
       </c>
       <c r="L14" t="n">
-        <v>52377.75</v>
+        <v>52470.25</v>
       </c>
       <c r="M14" t="n">
-        <v>52720.5</v>
+        <v>52678.5</v>
       </c>
       <c r="N14" t="n">
-        <v>53063.25</v>
+        <v>52886.75</v>
       </c>
       <c r="O14" t="n">
-        <v>53145</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+        <v>53180</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1710,9 +1714,9 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W14" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
@@ -1720,74 +1724,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52430</v>
+        <v>51920</v>
       </c>
       <c r="C15" t="n">
-        <v>52515</v>
+        <v>52314</v>
       </c>
       <c r="D15" t="n">
-        <v>51720</v>
+        <v>51846</v>
       </c>
       <c r="E15" t="n">
-        <v>51894</v>
+        <v>52124</v>
       </c>
       <c r="F15" t="n">
-        <v>-555</v>
+        <v>230</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0044</v>
       </c>
       <c r="H15" t="n">
-        <v>795</v>
+        <v>468</v>
       </c>
       <c r="I15" t="n">
-        <v>51803</v>
+        <v>50925</v>
       </c>
       <c r="J15" t="n">
-        <v>51968.75</v>
+        <v>50987.25</v>
       </c>
       <c r="K15" t="n">
-        <v>52219.5</v>
+        <v>51496.5</v>
       </c>
       <c r="L15" t="n">
-        <v>52470.25</v>
+        <v>52005.75</v>
       </c>
       <c r="M15" t="n">
-        <v>52678.5</v>
+        <v>52291.5</v>
       </c>
       <c r="N15" t="n">
-        <v>52886.75</v>
+        <v>52577.25</v>
       </c>
       <c r="O15" t="n">
-        <v>53180</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
+        <v>53310</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
@@ -1799,55 +1799,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>51920</v>
+        <v>52299</v>
       </c>
       <c r="C16" t="n">
-        <v>52314</v>
+        <v>52790</v>
       </c>
       <c r="D16" t="n">
-        <v>51846</v>
+        <v>52173</v>
       </c>
       <c r="E16" t="n">
-        <v>52124</v>
+        <v>52382</v>
       </c>
       <c r="F16" t="n">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0049</v>
       </c>
       <c r="H16" t="n">
-        <v>468</v>
+        <v>617</v>
       </c>
       <c r="I16" t="n">
-        <v>50925</v>
+        <v>51378</v>
       </c>
       <c r="J16" t="n">
-        <v>50987.25</v>
+        <v>51678</v>
       </c>
       <c r="K16" t="n">
-        <v>51496.5</v>
+        <v>51890</v>
       </c>
       <c r="L16" t="n">
-        <v>52005.75</v>
+        <v>52102</v>
       </c>
       <c r="M16" t="n">
-        <v>52291.5</v>
+        <v>52358</v>
       </c>
       <c r="N16" t="n">
-        <v>52577.25</v>
+        <v>52614</v>
       </c>
       <c r="O16" t="n">
-        <v>53310</v>
+        <v>52782</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1858,21 +1862,25 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v/>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W16" s="11" t="inlineStr">
         <is>
@@ -1881,57 +1889,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52299</v>
+        <v>52405</v>
       </c>
       <c r="C17" t="n">
-        <v>52790</v>
+        <v>53105</v>
       </c>
       <c r="D17" t="n">
-        <v>52173</v>
+        <v>52290</v>
       </c>
       <c r="E17" t="n">
-        <v>52382</v>
+        <v>52944</v>
       </c>
       <c r="F17" t="n">
-        <v>258</v>
+        <v>562</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0107</v>
       </c>
       <c r="H17" t="n">
-        <v>617</v>
+        <v>815</v>
       </c>
       <c r="I17" t="n">
-        <v>51378</v>
+        <v>51556</v>
       </c>
       <c r="J17" t="n">
-        <v>51678</v>
+        <v>51715.25</v>
       </c>
       <c r="K17" t="n">
-        <v>51890</v>
+        <v>52073.5</v>
       </c>
       <c r="L17" t="n">
-        <v>52102</v>
+        <v>52431.75</v>
       </c>
       <c r="M17" t="n">
-        <v>52358</v>
+        <v>52690.5</v>
       </c>
       <c r="N17" t="n">
-        <v>52614</v>
+        <v>52949.25</v>
       </c>
       <c r="O17" t="n">
-        <v>52782</v>
+        <v>53407</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1942,25 +1950,23 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V17" s="8" t="n">
+        <v/>
       </c>
       <c r="W17" s="11" t="inlineStr">
         <is>
@@ -1976,74 +1982,76 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52405</v>
+        <v>52915</v>
       </c>
       <c r="C18" t="n">
-        <v>53105</v>
+        <v>53033</v>
       </c>
       <c r="D18" t="n">
-        <v>52290</v>
+        <v>51630</v>
       </c>
       <c r="E18" t="n">
-        <v>52944</v>
+        <v>51765</v>
       </c>
       <c r="F18" t="n">
-        <v>562</v>
+        <v>-1179</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0223</v>
       </c>
       <c r="H18" t="n">
-        <v>815</v>
+        <v>1403</v>
       </c>
       <c r="I18" t="n">
-        <v>51556</v>
+        <v>51475</v>
       </c>
       <c r="J18" t="n">
-        <v>51715.25</v>
+        <v>52252.25</v>
       </c>
       <c r="K18" t="n">
-        <v>52073.5</v>
+        <v>52536.5</v>
       </c>
       <c r="L18" t="n">
-        <v>52431.75</v>
+        <v>52820.75</v>
       </c>
       <c r="M18" t="n">
-        <v>52690.5</v>
+        <v>53351.5</v>
       </c>
       <c r="N18" t="n">
-        <v>52949.25</v>
+        <v>53882.25</v>
       </c>
       <c r="O18" t="n">
-        <v>53407</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+        <v>53920</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2053,83 +2061,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>52915</v>
+        <v>51759</v>
       </c>
       <c r="C19" t="n">
-        <v>53033</v>
+        <v>52484</v>
       </c>
       <c r="D19" t="n">
-        <v>51630</v>
+        <v>51732</v>
       </c>
       <c r="E19" t="n">
-        <v>51765</v>
+        <v>52380</v>
       </c>
       <c r="F19" t="n">
-        <v>-1179</v>
+        <v>615</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0119</v>
       </c>
       <c r="H19" t="n">
-        <v>1403</v>
+        <v>752</v>
       </c>
       <c r="I19" t="n">
-        <v>51475</v>
+        <v>50227</v>
       </c>
       <c r="J19" t="n">
-        <v>52252.25</v>
+        <v>50078.75</v>
       </c>
       <c r="K19" t="n">
-        <v>52536.5</v>
+        <v>51063.5</v>
       </c>
       <c r="L19" t="n">
-        <v>52820.75</v>
+        <v>52048.25</v>
       </c>
       <c r="M19" t="n">
-        <v>53351.5</v>
+        <v>52466.5</v>
       </c>
       <c r="N19" t="n">
-        <v>53882.25</v>
+        <v>52884.75</v>
       </c>
       <c r="O19" t="n">
-        <v>53920</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
+        <v>54436</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
       <c r="U19" s="8" t="n">
         <v/>
       </c>
@@ -2141,55 +2141,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>51759</v>
+        <v>52395</v>
       </c>
       <c r="C20" t="n">
-        <v>52484</v>
+        <v>52772</v>
       </c>
       <c r="D20" t="n">
-        <v>51732</v>
+        <v>52124</v>
       </c>
       <c r="E20" t="n">
-        <v>52380</v>
+        <v>52635</v>
       </c>
       <c r="F20" t="n">
-        <v>615</v>
+        <v>255</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0119</v>
+        <v>0.0049</v>
       </c>
       <c r="H20" t="n">
-        <v>752</v>
+        <v>648</v>
       </c>
       <c r="I20" t="n">
-        <v>50227</v>
+        <v>50980</v>
       </c>
       <c r="J20" t="n">
-        <v>50078.75</v>
+        <v>51764</v>
       </c>
       <c r="K20" t="n">
-        <v>51063.5</v>
+        <v>52004</v>
       </c>
       <c r="L20" t="n">
-        <v>52048.25</v>
+        <v>52244</v>
       </c>
       <c r="M20" t="n">
-        <v>52466.5</v>
+        <v>52756</v>
       </c>
       <c r="N20" t="n">
-        <v>52884.75</v>
+        <v>53268</v>
       </c>
       <c r="O20" t="n">
-        <v>54436</v>
+        <v>53236</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2200,7 +2204,7 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
+      <c r="S20" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2223,57 +2227,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>52395</v>
+        <v>52780</v>
       </c>
       <c r="C21" t="n">
-        <v>52772</v>
+        <v>53414</v>
       </c>
       <c r="D21" t="n">
-        <v>52124</v>
+        <v>52777</v>
       </c>
       <c r="E21" t="n">
-        <v>52635</v>
+        <v>53334</v>
       </c>
       <c r="F21" t="n">
-        <v>255</v>
+        <v>699</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0133</v>
       </c>
       <c r="H21" t="n">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="I21" t="n">
-        <v>50980</v>
+        <v>51476</v>
       </c>
       <c r="J21" t="n">
-        <v>51764</v>
+        <v>52080.5</v>
       </c>
       <c r="K21" t="n">
-        <v>52004</v>
+        <v>52311</v>
       </c>
       <c r="L21" t="n">
-        <v>52244</v>
+        <v>52541.5</v>
       </c>
       <c r="M21" t="n">
-        <v>52756</v>
+        <v>52959</v>
       </c>
       <c r="N21" t="n">
-        <v>53268</v>
+        <v>53376.5</v>
       </c>
       <c r="O21" t="n">
-        <v>53236</v>
+        <v>53420</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2284,18 +2288,20 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="7" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2314,50 +2320,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>52780</v>
+        <v>53381</v>
       </c>
       <c r="C22" t="n">
-        <v>53414</v>
+        <v>54423</v>
       </c>
       <c r="D22" t="n">
-        <v>52777</v>
+        <v>53267</v>
       </c>
       <c r="E22" t="n">
-        <v>53334</v>
+        <v>54268</v>
       </c>
       <c r="F22" t="n">
-        <v>699</v>
+        <v>934</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0175</v>
       </c>
       <c r="H22" t="n">
-        <v>637</v>
+        <v>1156</v>
       </c>
       <c r="I22" t="n">
-        <v>51476</v>
+        <v>52140</v>
       </c>
       <c r="J22" t="n">
-        <v>52080.5</v>
+        <v>52816.25</v>
       </c>
       <c r="K22" t="n">
-        <v>52311</v>
+        <v>53015.5</v>
       </c>
       <c r="L22" t="n">
-        <v>52541.5</v>
+        <v>53214.75</v>
       </c>
       <c r="M22" t="n">
-        <v>52959</v>
+        <v>53652.5</v>
       </c>
       <c r="N22" t="n">
-        <v>53376.5</v>
+        <v>54090.25</v>
       </c>
       <c r="O22" t="n">
-        <v>53420</v>
+        <v>54051</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2368,7 +2374,7 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2383,67 +2389,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W22" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W22" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>53381</v>
+        <v>54369</v>
       </c>
       <c r="C23" t="n">
-        <v>54423</v>
+        <v>54884</v>
       </c>
       <c r="D23" t="n">
-        <v>53267</v>
+        <v>54342</v>
       </c>
       <c r="E23" t="n">
-        <v>54268</v>
+        <v>54494</v>
       </c>
       <c r="F23" t="n">
-        <v>934</v>
+        <v>226</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0042</v>
       </c>
       <c r="H23" t="n">
-        <v>1156</v>
+        <v>542</v>
       </c>
       <c r="I23" t="n">
-        <v>52140</v>
+        <v>52111</v>
       </c>
       <c r="J23" t="n">
-        <v>52816.25</v>
+        <v>53323.5</v>
       </c>
       <c r="K23" t="n">
-        <v>53015.5</v>
+        <v>53690</v>
       </c>
       <c r="L23" t="n">
-        <v>53214.75</v>
+        <v>54056.5</v>
       </c>
       <c r="M23" t="n">
-        <v>53652.5</v>
+        <v>54846</v>
       </c>
       <c r="N23" t="n">
-        <v>54090.25</v>
+        <v>55635.5</v>
       </c>
       <c r="O23" t="n">
-        <v>54051</v>
+        <v>55579</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2454,25 +2458,21 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
@@ -2484,69 +2484,71 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>54369</v>
+        <v>54555</v>
       </c>
       <c r="C24" t="n">
-        <v>54884</v>
+        <v>54678</v>
       </c>
       <c r="D24" t="n">
-        <v>54342</v>
+        <v>53952</v>
       </c>
       <c r="E24" t="n">
-        <v>54494</v>
+        <v>54013</v>
       </c>
       <c r="F24" t="n">
-        <v>226</v>
+        <v>-481</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>542</v>
+        <v>726</v>
       </c>
       <c r="I24" t="n">
-        <v>52111</v>
+        <v>53800</v>
       </c>
       <c r="J24" t="n">
-        <v>53323.5</v>
+        <v>53892.5</v>
       </c>
       <c r="K24" t="n">
-        <v>53690</v>
+        <v>54223</v>
       </c>
       <c r="L24" t="n">
-        <v>54056.5</v>
+        <v>54553.5</v>
       </c>
       <c r="M24" t="n">
-        <v>54846</v>
+        <v>54765</v>
       </c>
       <c r="N24" t="n">
-        <v>55635.5</v>
+        <v>54976.5</v>
       </c>
       <c r="O24" t="n">
-        <v>55579</v>
+        <v>55426</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2559,72 +2561,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>54555</v>
+        <v>54040</v>
       </c>
       <c r="C25" t="n">
-        <v>54678</v>
+        <v>54202</v>
       </c>
       <c r="D25" t="n">
-        <v>53952</v>
+        <v>53879</v>
       </c>
       <c r="E25" t="n">
-        <v>54013</v>
+        <v>54152</v>
       </c>
       <c r="F25" t="n">
-        <v>-481</v>
+        <v>139</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0026</v>
       </c>
       <c r="H25" t="n">
-        <v>726</v>
+        <v>323</v>
       </c>
       <c r="I25" t="n">
-        <v>53800</v>
+        <v>53226</v>
       </c>
       <c r="J25" t="n">
-        <v>53892.5</v>
+        <v>53136</v>
       </c>
       <c r="K25" t="n">
-        <v>54223</v>
+        <v>53650</v>
       </c>
       <c r="L25" t="n">
-        <v>54553.5</v>
+        <v>54164</v>
       </c>
       <c r="M25" t="n">
-        <v>54765</v>
+        <v>54376</v>
       </c>
       <c r="N25" t="n">
-        <v>54976.5</v>
+        <v>54588</v>
       </c>
       <c r="O25" t="n">
-        <v>55426</v>
+        <v>55404</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2643,57 +2645,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>54040</v>
+        <v>54133</v>
       </c>
       <c r="C26" t="n">
-        <v>54202</v>
+        <v>54170</v>
       </c>
       <c r="D26" t="n">
-        <v>53879</v>
+        <v>53952</v>
       </c>
       <c r="E26" t="n">
-        <v>54152</v>
+        <v>54063</v>
       </c>
       <c r="F26" t="n">
-        <v>139</v>
+        <v>-89</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0016</v>
       </c>
       <c r="H26" t="n">
-        <v>323</v>
+        <v>218</v>
       </c>
       <c r="I26" t="n">
-        <v>53226</v>
+        <v>53556</v>
       </c>
       <c r="J26" t="n">
-        <v>53136</v>
+        <v>53884.75</v>
       </c>
       <c r="K26" t="n">
-        <v>53650</v>
+        <v>53990.5</v>
       </c>
       <c r="L26" t="n">
-        <v>54164</v>
+        <v>54096.25</v>
       </c>
       <c r="M26" t="n">
-        <v>54376</v>
+        <v>54313.5</v>
       </c>
       <c r="N26" t="n">
-        <v>54588</v>
+        <v>54530.75</v>
       </c>
       <c r="O26" t="n">
-        <v>55404</v>
+        <v>54525</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2701,10 +2703,12 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2732,72 +2736,78 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>54133</v>
+        <v>54049</v>
       </c>
       <c r="C27" t="n">
-        <v>54170</v>
+        <v>54336</v>
       </c>
       <c r="D27" t="n">
-        <v>53952</v>
+        <v>53855</v>
       </c>
       <c r="E27" t="n">
-        <v>54063</v>
+        <v>53880</v>
       </c>
       <c r="F27" t="n">
-        <v>-89</v>
+        <v>-183</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0034</v>
       </c>
       <c r="H27" t="n">
-        <v>218</v>
+        <v>481</v>
       </c>
       <c r="I27" t="n">
-        <v>53556</v>
+        <v>53734</v>
       </c>
       <c r="J27" t="n">
-        <v>53884.75</v>
+        <v>53846</v>
       </c>
       <c r="K27" t="n">
-        <v>53990.5</v>
+        <v>53954</v>
       </c>
       <c r="L27" t="n">
-        <v>54096.25</v>
+        <v>54062</v>
       </c>
       <c r="M27" t="n">
-        <v>54313.5</v>
+        <v>54172</v>
       </c>
       <c r="N27" t="n">
-        <v>54530.75</v>
+        <v>54282</v>
       </c>
       <c r="O27" t="n">
-        <v>54525</v>
+        <v>54388</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2816,78 +2826,72 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>54049</v>
+        <v>53903</v>
       </c>
       <c r="C28" t="n">
-        <v>54336</v>
+        <v>54150</v>
       </c>
       <c r="D28" t="n">
-        <v>53855</v>
+        <v>53830</v>
       </c>
       <c r="E28" t="n">
-        <v>53880</v>
+        <v>53871</v>
       </c>
       <c r="F28" t="n">
-        <v>-183</v>
+        <v>-9</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0002</v>
       </c>
       <c r="H28" t="n">
-        <v>481</v>
+        <v>320</v>
       </c>
       <c r="I28" t="n">
-        <v>53734</v>
+        <v>53374</v>
       </c>
       <c r="J28" t="n">
-        <v>53846</v>
+        <v>53291.25</v>
       </c>
       <c r="K28" t="n">
-        <v>53954</v>
+        <v>53639.5</v>
       </c>
       <c r="L28" t="n">
-        <v>54062</v>
+        <v>53987.75</v>
       </c>
       <c r="M28" t="n">
-        <v>54172</v>
+        <v>54120.5</v>
       </c>
       <c r="N28" t="n">
-        <v>54282</v>
+        <v>54253.25</v>
       </c>
       <c r="O28" t="n">
-        <v>54388</v>
+        <v>54817</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2899,57 +2903,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>53903</v>
+        <v>53905</v>
       </c>
       <c r="C29" t="n">
-        <v>54150</v>
+        <v>54149</v>
       </c>
       <c r="D29" t="n">
-        <v>53830</v>
+        <v>53715</v>
       </c>
       <c r="E29" t="n">
-        <v>53871</v>
+        <v>53935</v>
       </c>
       <c r="F29" t="n">
-        <v>-9</v>
+        <v>64</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0012</v>
       </c>
       <c r="H29" t="n">
-        <v>320</v>
+        <v>434</v>
       </c>
       <c r="I29" t="n">
-        <v>53374</v>
+        <v>53510</v>
       </c>
       <c r="J29" t="n">
-        <v>53291.25</v>
+        <v>53491.5</v>
       </c>
       <c r="K29" t="n">
-        <v>53639.5</v>
+        <v>53711</v>
       </c>
       <c r="L29" t="n">
-        <v>53987.75</v>
+        <v>53930.5</v>
       </c>
       <c r="M29" t="n">
-        <v>54120.5</v>
+        <v>54031</v>
       </c>
       <c r="N29" t="n">
-        <v>54253.25</v>
+        <v>54131.5</v>
       </c>
       <c r="O29" t="n">
-        <v>54817</v>
+        <v>54470</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2962,7 +2966,7 @@
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
@@ -2970,8 +2974,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U29" s="8" t="n">
-        <v/>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2983,57 +2989,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>53905</v>
+        <v>53961</v>
       </c>
       <c r="C30" t="n">
-        <v>54149</v>
+        <v>53999</v>
       </c>
       <c r="D30" t="n">
-        <v>53715</v>
+        <v>53745</v>
       </c>
       <c r="E30" t="n">
-        <v>53935</v>
+        <v>53807</v>
       </c>
       <c r="F30" t="n">
-        <v>64</v>
+        <v>-128</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0024</v>
       </c>
       <c r="H30" t="n">
-        <v>434</v>
+        <v>254</v>
       </c>
       <c r="I30" t="n">
-        <v>53510</v>
+        <v>53281</v>
       </c>
       <c r="J30" t="n">
-        <v>53491.5</v>
+        <v>53502.5</v>
       </c>
       <c r="K30" t="n">
-        <v>53711</v>
+        <v>53718</v>
       </c>
       <c r="L30" t="n">
-        <v>53930.5</v>
+        <v>53933.5</v>
       </c>
       <c r="M30" t="n">
-        <v>54031</v>
+        <v>54152</v>
       </c>
       <c r="N30" t="n">
-        <v>54131.5</v>
+        <v>54370.5</v>
       </c>
       <c r="O30" t="n">
-        <v>54470</v>
+        <v>54583</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3041,23 +3047,21 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3076,63 +3080,67 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>53961</v>
+        <v>53790</v>
       </c>
       <c r="C31" t="n">
-        <v>53999</v>
+        <v>53840</v>
       </c>
       <c r="D31" t="n">
-        <v>53745</v>
+        <v>53464</v>
       </c>
       <c r="E31" t="n">
-        <v>53807</v>
+        <v>53544</v>
       </c>
       <c r="F31" t="n">
-        <v>-128</v>
+        <v>-263</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0049</v>
       </c>
       <c r="H31" t="n">
-        <v>254</v>
+        <v>376</v>
       </c>
       <c r="I31" t="n">
-        <v>53281</v>
+        <v>53491</v>
       </c>
       <c r="J31" t="n">
-        <v>53502.5</v>
+        <v>53520.5</v>
       </c>
       <c r="K31" t="n">
-        <v>53718</v>
+        <v>53680</v>
       </c>
       <c r="L31" t="n">
-        <v>53933.5</v>
+        <v>53839.5</v>
       </c>
       <c r="M31" t="n">
-        <v>54152</v>
+        <v>53934</v>
       </c>
       <c r="N31" t="n">
-        <v>54370.5</v>
+        <v>54028.5</v>
       </c>
       <c r="O31" t="n">
-        <v>54583</v>
-      </c>
-      <c r="P31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
+        <v>54253</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3153,74 +3161,70 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>53790</v>
+        <v>53501</v>
       </c>
       <c r="C32" t="n">
-        <v>53840</v>
+        <v>53594</v>
       </c>
       <c r="D32" t="n">
-        <v>53464</v>
+        <v>53311</v>
       </c>
       <c r="E32" t="n">
-        <v>53544</v>
+        <v>53403</v>
       </c>
       <c r="F32" t="n">
-        <v>-263</v>
+        <v>-141</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0026</v>
       </c>
       <c r="H32" t="n">
-        <v>376</v>
+        <v>283</v>
       </c>
       <c r="I32" t="n">
-        <v>53491</v>
+        <v>53088</v>
       </c>
       <c r="J32" t="n">
-        <v>53520.5</v>
+        <v>53114</v>
       </c>
       <c r="K32" t="n">
-        <v>53680</v>
+        <v>53356</v>
       </c>
       <c r="L32" t="n">
-        <v>53839.5</v>
+        <v>53598</v>
       </c>
       <c r="M32" t="n">
-        <v>53934</v>
+        <v>53732</v>
       </c>
       <c r="N32" t="n">
-        <v>54028.5</v>
+        <v>53866</v>
       </c>
       <c r="O32" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q32" s="6" t="inlineStr">
+        <v>54216</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3248,50 +3252,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>53501</v>
+        <v>53408</v>
       </c>
       <c r="C33" t="n">
-        <v>53594</v>
+        <v>53780</v>
       </c>
       <c r="D33" t="n">
-        <v>53311</v>
+        <v>53337</v>
       </c>
       <c r="E33" t="n">
-        <v>53403</v>
+        <v>53530</v>
       </c>
       <c r="F33" t="n">
-        <v>-141</v>
+        <v>127</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0026</v>
+        <v>0.0024</v>
       </c>
       <c r="H33" t="n">
-        <v>283</v>
+        <v>443</v>
       </c>
       <c r="I33" t="n">
-        <v>53088</v>
+        <v>53028</v>
       </c>
       <c r="J33" t="n">
-        <v>53114</v>
+        <v>53095.25</v>
       </c>
       <c r="K33" t="n">
-        <v>53356</v>
+        <v>53261.5</v>
       </c>
       <c r="L33" t="n">
-        <v>53598</v>
+        <v>53427.75</v>
       </c>
       <c r="M33" t="n">
-        <v>53732</v>
+        <v>53544.5</v>
       </c>
       <c r="N33" t="n">
-        <v>53866</v>
+        <v>53661.25</v>
       </c>
       <c r="O33" t="n">
-        <v>54216</v>
+        <v>53877</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3299,21 +3303,23 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3323,90 +3329,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>53408</v>
+        <v>53529</v>
       </c>
       <c r="C34" t="n">
-        <v>53780</v>
+        <v>53589</v>
       </c>
       <c r="D34" t="n">
-        <v>53337</v>
+        <v>52812</v>
       </c>
       <c r="E34" t="n">
-        <v>53530</v>
+        <v>52849</v>
       </c>
       <c r="F34" t="n">
-        <v>127</v>
+        <v>-681</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0127</v>
       </c>
       <c r="H34" t="n">
-        <v>443</v>
+        <v>777</v>
       </c>
       <c r="I34" t="n">
-        <v>53028</v>
+        <v>52894</v>
       </c>
       <c r="J34" t="n">
-        <v>53095.25</v>
+        <v>53072.75</v>
       </c>
       <c r="K34" t="n">
-        <v>53261.5</v>
+        <v>53308.5</v>
       </c>
       <c r="L34" t="n">
-        <v>53427.75</v>
+        <v>53544.25</v>
       </c>
       <c r="M34" t="n">
-        <v>53544.5</v>
+        <v>53751.5</v>
       </c>
       <c r="N34" t="n">
-        <v>53661.25</v>
+        <v>53958.75</v>
       </c>
       <c r="O34" t="n">
-        <v>53877</v>
-      </c>
-      <c r="P34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+        <v>54223</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W34" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X34" t="inlineStr"/>
@@ -3414,77 +3418,75 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>53529</v>
+        <v>52876</v>
       </c>
       <c r="C35" t="n">
-        <v>53589</v>
+        <v>53418</v>
       </c>
       <c r="D35" t="n">
-        <v>52812</v>
+        <v>52838</v>
       </c>
       <c r="E35" t="n">
-        <v>52849</v>
+        <v>53353</v>
       </c>
       <c r="F35" t="n">
-        <v>-681</v>
+        <v>504</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0095</v>
       </c>
       <c r="H35" t="n">
-        <v>777</v>
+        <v>580</v>
       </c>
       <c r="I35" t="n">
-        <v>52894</v>
+        <v>52035</v>
       </c>
       <c r="J35" t="n">
-        <v>53072.75</v>
+        <v>51896.25</v>
       </c>
       <c r="K35" t="n">
-        <v>53308.5</v>
+        <v>52460.5</v>
       </c>
       <c r="L35" t="n">
-        <v>53544.25</v>
+        <v>53024.75</v>
       </c>
       <c r="M35" t="n">
-        <v>53751.5</v>
+        <v>53237.5</v>
       </c>
       <c r="N35" t="n">
-        <v>53958.75</v>
+        <v>53450.25</v>
       </c>
       <c r="O35" t="n">
-        <v>54223</v>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
+        <v>54366</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
@@ -3493,55 +3495,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>52876</v>
+        <v>53367</v>
       </c>
       <c r="C36" t="n">
-        <v>53418</v>
+        <v>53567</v>
       </c>
       <c r="D36" t="n">
-        <v>52838</v>
+        <v>53210</v>
       </c>
       <c r="E36" t="n">
-        <v>53353</v>
+        <v>53489</v>
       </c>
       <c r="F36" t="n">
-        <v>504</v>
+        <v>136</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.0025</v>
       </c>
       <c r="H36" t="n">
-        <v>580</v>
+        <v>357</v>
       </c>
       <c r="I36" t="n">
-        <v>52035</v>
+        <v>52258</v>
       </c>
       <c r="J36" t="n">
-        <v>51896.25</v>
+        <v>52885.5</v>
       </c>
       <c r="K36" t="n">
-        <v>52460.5</v>
+        <v>53063</v>
       </c>
       <c r="L36" t="n">
-        <v>53024.75</v>
+        <v>53240.5</v>
       </c>
       <c r="M36" t="n">
-        <v>53237.5</v>
+        <v>53643</v>
       </c>
       <c r="N36" t="n">
-        <v>53450.25</v>
+        <v>54045.5</v>
       </c>
       <c r="O36" t="n">
-        <v>54366</v>
+        <v>53998</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3552,21 +3558,19 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="7" t="inlineStr">
+      <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
@@ -3577,57 +3581,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>53367</v>
+        <v>53524</v>
       </c>
       <c r="C37" t="n">
-        <v>53567</v>
+        <v>53797</v>
       </c>
       <c r="D37" t="n">
-        <v>53210</v>
+        <v>53426</v>
       </c>
       <c r="E37" t="n">
-        <v>53489</v>
+        <v>53645</v>
       </c>
       <c r="F37" t="n">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0029</v>
       </c>
       <c r="H37" t="n">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="I37" t="n">
-        <v>52258</v>
+        <v>52853</v>
       </c>
       <c r="J37" t="n">
-        <v>52885.5</v>
+        <v>53182.25</v>
       </c>
       <c r="K37" t="n">
-        <v>53063</v>
+        <v>53310.5</v>
       </c>
       <c r="L37" t="n">
-        <v>53240.5</v>
+        <v>53438.75</v>
       </c>
       <c r="M37" t="n">
-        <v>53643</v>
+        <v>53667.5</v>
       </c>
       <c r="N37" t="n">
-        <v>54045.5</v>
+        <v>53896.25</v>
       </c>
       <c r="O37" t="n">
-        <v>53998</v>
+        <v>53924</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3638,7 +3642,7 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="7" t="inlineStr">
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3668,50 +3672,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>53524</v>
+        <v>53643</v>
       </c>
       <c r="C38" t="n">
-        <v>53797</v>
+        <v>53778</v>
       </c>
       <c r="D38" t="n">
-        <v>53426</v>
+        <v>53435</v>
       </c>
       <c r="E38" t="n">
-        <v>53645</v>
+        <v>53521</v>
       </c>
       <c r="F38" t="n">
-        <v>156</v>
+        <v>-124</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0023</v>
       </c>
       <c r="H38" t="n">
-        <v>371</v>
+        <v>343</v>
       </c>
       <c r="I38" t="n">
-        <v>52853</v>
+        <v>53055</v>
       </c>
       <c r="J38" t="n">
-        <v>53182.25</v>
+        <v>53290.75</v>
       </c>
       <c r="K38" t="n">
-        <v>53310.5</v>
+        <v>53459.5</v>
       </c>
       <c r="L38" t="n">
-        <v>53438.75</v>
+        <v>53628.25</v>
       </c>
       <c r="M38" t="n">
-        <v>53667.5</v>
+        <v>53830.5</v>
       </c>
       <c r="N38" t="n">
-        <v>53896.25</v>
+        <v>54032.75</v>
       </c>
       <c r="O38" t="n">
-        <v>53924</v>
+        <v>54168</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3719,18 +3723,18 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3745,57 +3749,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>53643</v>
+        <v>53724</v>
       </c>
       <c r="C39" t="n">
-        <v>53778</v>
+        <v>53811</v>
       </c>
       <c r="D39" t="n">
-        <v>53435</v>
+        <v>53369</v>
       </c>
       <c r="E39" t="n">
-        <v>53521</v>
+        <v>53621</v>
       </c>
       <c r="F39" t="n">
-        <v>-124</v>
+        <v>100</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0019</v>
       </c>
       <c r="H39" t="n">
-        <v>343</v>
+        <v>442</v>
       </c>
       <c r="I39" t="n">
-        <v>53055</v>
+        <v>53092</v>
       </c>
       <c r="J39" t="n">
-        <v>53290.75</v>
+        <v>53135.25</v>
       </c>
       <c r="K39" t="n">
-        <v>53459.5</v>
+        <v>53349.5</v>
       </c>
       <c r="L39" t="n">
-        <v>53628.25</v>
+        <v>53563.75</v>
       </c>
       <c r="M39" t="n">
-        <v>53830.5</v>
+        <v>53692.5</v>
       </c>
       <c r="N39" t="n">
-        <v>54032.75</v>
+        <v>53821.25</v>
       </c>
       <c r="O39" t="n">
-        <v>54168</v>
+        <v>54121</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3803,18 +3807,18 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R39" s="6" t="n">
+        <v/>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3829,57 +3833,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>53724</v>
+        <v>53608</v>
       </c>
       <c r="C40" t="n">
-        <v>53811</v>
+        <v>53862</v>
       </c>
       <c r="D40" t="n">
-        <v>53369</v>
+        <v>53513</v>
       </c>
       <c r="E40" t="n">
-        <v>53621</v>
+        <v>53584</v>
       </c>
       <c r="F40" t="n">
-        <v>100</v>
+        <v>-37</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0007</v>
       </c>
       <c r="H40" t="n">
-        <v>442</v>
+        <v>349</v>
       </c>
       <c r="I40" t="n">
-        <v>53092</v>
+        <v>52927</v>
       </c>
       <c r="J40" t="n">
-        <v>53135.25</v>
+        <v>53194.5</v>
       </c>
       <c r="K40" t="n">
-        <v>53349.5</v>
+        <v>53400</v>
       </c>
       <c r="L40" t="n">
-        <v>53563.75</v>
+        <v>53605.5</v>
       </c>
       <c r="M40" t="n">
-        <v>53692.5</v>
+        <v>53842</v>
       </c>
       <c r="N40" t="n">
-        <v>53821.25</v>
+        <v>54078.5</v>
       </c>
       <c r="O40" t="n">
-        <v>54121</v>
+        <v>54253</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3892,7 +3896,7 @@
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
@@ -3920,70 +3924,74 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>53608</v>
+        <v>53664</v>
       </c>
       <c r="C41" t="n">
-        <v>53862</v>
+        <v>53664</v>
       </c>
       <c r="D41" t="n">
-        <v>53513</v>
+        <v>53149</v>
       </c>
       <c r="E41" t="n">
-        <v>53584</v>
+        <v>53240</v>
       </c>
       <c r="F41" t="n">
-        <v>-37</v>
+        <v>-344</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0064</v>
       </c>
       <c r="H41" t="n">
-        <v>349</v>
+        <v>515</v>
       </c>
       <c r="I41" t="n">
-        <v>52927</v>
+        <v>53164</v>
       </c>
       <c r="J41" t="n">
-        <v>53194.5</v>
+        <v>53183.25</v>
       </c>
       <c r="K41" t="n">
-        <v>53400</v>
+        <v>53409.5</v>
       </c>
       <c r="L41" t="n">
-        <v>53605.5</v>
+        <v>53635.75</v>
       </c>
       <c r="M41" t="n">
-        <v>53842</v>
+        <v>53758.5</v>
       </c>
       <c r="N41" t="n">
-        <v>54078.5</v>
+        <v>53881.25</v>
       </c>
       <c r="O41" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
+        <v>54211</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
@@ -3995,76 +4003,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>53664</v>
+        <v>53259</v>
       </c>
       <c r="C42" t="n">
-        <v>53664</v>
+        <v>53343</v>
       </c>
       <c r="D42" t="n">
-        <v>53149</v>
+        <v>52747</v>
       </c>
       <c r="E42" t="n">
-        <v>53240</v>
+        <v>52828</v>
       </c>
       <c r="F42" t="n">
-        <v>-344</v>
+        <v>-412</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0064</v>
+        <v>-0.0077</v>
       </c>
       <c r="H42" t="n">
-        <v>515</v>
+        <v>596</v>
       </c>
       <c r="I42" t="n">
-        <v>53164</v>
+        <v>52634</v>
       </c>
       <c r="J42" t="n">
-        <v>53183.25</v>
+        <v>52641.75</v>
       </c>
       <c r="K42" t="n">
-        <v>53409.5</v>
+        <v>52982.5</v>
       </c>
       <c r="L42" t="n">
-        <v>53635.75</v>
+        <v>53323.25</v>
       </c>
       <c r="M42" t="n">
-        <v>53758.5</v>
+        <v>53497.5</v>
       </c>
       <c r="N42" t="n">
-        <v>53881.25</v>
+        <v>53671.75</v>
       </c>
       <c r="O42" t="n">
-        <v>54211</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
+        <v>54179</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
+      <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4088,50 +4088,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>53259</v>
+        <v>52844</v>
       </c>
       <c r="C43" t="n">
-        <v>53343</v>
+        <v>53283</v>
       </c>
       <c r="D43" t="n">
-        <v>52747</v>
+        <v>52720</v>
       </c>
       <c r="E43" t="n">
-        <v>52828</v>
+        <v>53121</v>
       </c>
       <c r="F43" t="n">
-        <v>-412</v>
+        <v>293</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0077</v>
+        <v>0.0055</v>
       </c>
       <c r="H43" t="n">
-        <v>596</v>
+        <v>563</v>
       </c>
       <c r="I43" t="n">
-        <v>52634</v>
+        <v>52151</v>
       </c>
       <c r="J43" t="n">
-        <v>52641.75</v>
+        <v>52123.5</v>
       </c>
       <c r="K43" t="n">
-        <v>52982.5</v>
+        <v>52530</v>
       </c>
       <c r="L43" t="n">
-        <v>53323.25</v>
+        <v>52936.5</v>
       </c>
       <c r="M43" t="n">
-        <v>53497.5</v>
+        <v>53126</v>
       </c>
       <c r="N43" t="n">
-        <v>53671.75</v>
+        <v>53315.5</v>
       </c>
       <c r="O43" t="n">
-        <v>54179</v>
+        <v>53939</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4139,19 +4139,19 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
@@ -4163,55 +4163,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>52844</v>
+        <v>53120</v>
       </c>
       <c r="C44" t="n">
-        <v>53283</v>
+        <v>53827</v>
       </c>
       <c r="D44" t="n">
-        <v>52720</v>
+        <v>53093</v>
       </c>
       <c r="E44" t="n">
-        <v>53121</v>
+        <v>53745</v>
       </c>
       <c r="F44" t="n">
-        <v>293</v>
+        <v>624</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0117</v>
       </c>
       <c r="H44" t="n">
-        <v>563</v>
+        <v>734</v>
       </c>
       <c r="I44" t="n">
-        <v>52151</v>
+        <v>52157</v>
       </c>
       <c r="J44" t="n">
-        <v>52123.5</v>
+        <v>52617.75</v>
       </c>
       <c r="K44" t="n">
-        <v>52530</v>
+        <v>52839.5</v>
       </c>
       <c r="L44" t="n">
-        <v>52936.5</v>
+        <v>53061.25</v>
       </c>
       <c r="M44" t="n">
-        <v>53126</v>
+        <v>53402.5</v>
       </c>
       <c r="N44" t="n">
-        <v>53315.5</v>
+        <v>53743.75</v>
       </c>
       <c r="O44" t="n">
-        <v>53939</v>
+        <v>53846</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4222,80 +4226,78 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="7" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W44" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>53120</v>
+        <v>53707</v>
       </c>
       <c r="C45" t="n">
-        <v>53827</v>
+        <v>53772</v>
       </c>
       <c r="D45" t="n">
-        <v>53093</v>
+        <v>53235</v>
       </c>
       <c r="E45" t="n">
-        <v>53745</v>
+        <v>53440</v>
       </c>
       <c r="F45" t="n">
-        <v>624</v>
+        <v>-305</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0117</v>
+        <v>-0.0057</v>
       </c>
       <c r="H45" t="n">
-        <v>734</v>
+        <v>537</v>
       </c>
       <c r="I45" t="n">
-        <v>52157</v>
+        <v>52359</v>
       </c>
       <c r="J45" t="n">
-        <v>52617.75</v>
+        <v>53153.5</v>
       </c>
       <c r="K45" t="n">
-        <v>52839.5</v>
+        <v>53378</v>
       </c>
       <c r="L45" t="n">
-        <v>53061.25</v>
+        <v>53602.5</v>
       </c>
       <c r="M45" t="n">
-        <v>53402.5</v>
+        <v>54112</v>
       </c>
       <c r="N45" t="n">
-        <v>53743.75</v>
+        <v>54621.5</v>
       </c>
       <c r="O45" t="n">
-        <v>53846</v>
+        <v>54561</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4303,23 +4305,21 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4329,68 +4329,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>53707</v>
+        <v>53261</v>
       </c>
       <c r="C46" t="n">
-        <v>53772</v>
+        <v>53336</v>
       </c>
       <c r="D46" t="n">
-        <v>53235</v>
+        <v>52758</v>
       </c>
       <c r="E46" t="n">
-        <v>53440</v>
+        <v>52832</v>
       </c>
       <c r="F46" t="n">
-        <v>-305</v>
+        <v>-608</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0057</v>
+        <v>-0.0114</v>
       </c>
       <c r="H46" t="n">
-        <v>537</v>
+        <v>578</v>
       </c>
       <c r="I46" t="n">
-        <v>52359</v>
+        <v>52698</v>
       </c>
       <c r="J46" t="n">
-        <v>53153.5</v>
+        <v>52871.25</v>
       </c>
       <c r="K46" t="n">
-        <v>53378</v>
+        <v>53171.5</v>
       </c>
       <c r="L46" t="n">
-        <v>53602.5</v>
+        <v>53471.75</v>
       </c>
       <c r="M46" t="n">
-        <v>54112</v>
+        <v>53708.5</v>
       </c>
       <c r="N46" t="n">
-        <v>54621.5</v>
+        <v>53945.25</v>
       </c>
       <c r="O46" t="n">
-        <v>54561</v>
+        <v>54309</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4404,79 +4410,73 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W46" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>53261</v>
+        <v>52817</v>
       </c>
       <c r="C47" t="n">
-        <v>53336</v>
+        <v>52859</v>
       </c>
       <c r="D47" t="n">
-        <v>52758</v>
+        <v>52339</v>
       </c>
       <c r="E47" t="n">
-        <v>52832</v>
+        <v>52425</v>
       </c>
       <c r="F47" t="n">
-        <v>-608</v>
+        <v>-407</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0114</v>
+        <v>-0.0077</v>
       </c>
       <c r="H47" t="n">
-        <v>578</v>
+        <v>520</v>
       </c>
       <c r="I47" t="n">
-        <v>52698</v>
+        <v>52180</v>
       </c>
       <c r="J47" t="n">
-        <v>52871.25</v>
+        <v>52146.5</v>
       </c>
       <c r="K47" t="n">
-        <v>53171.5</v>
+        <v>52543</v>
       </c>
       <c r="L47" t="n">
-        <v>53471.75</v>
+        <v>52939.5</v>
       </c>
       <c r="M47" t="n">
-        <v>53708.5</v>
+        <v>53121</v>
       </c>
       <c r="N47" t="n">
-        <v>53945.25</v>
+        <v>53302.5</v>
       </c>
       <c r="O47" t="n">
-        <v>54309</v>
+        <v>53914</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="S47" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4500,50 +4500,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>52817</v>
+        <v>52473</v>
       </c>
       <c r="C48" t="n">
-        <v>52859</v>
+        <v>52676</v>
       </c>
       <c r="D48" t="n">
-        <v>52339</v>
+        <v>51992</v>
       </c>
       <c r="E48" t="n">
-        <v>52425</v>
+        <v>52095</v>
       </c>
       <c r="F48" t="n">
-        <v>-407</v>
+        <v>-330</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0077</v>
+        <v>-0.0063</v>
       </c>
       <c r="H48" t="n">
-        <v>520</v>
+        <v>684</v>
       </c>
       <c r="I48" t="n">
-        <v>52180</v>
+        <v>51819</v>
       </c>
       <c r="J48" t="n">
-        <v>52146.5</v>
+        <v>51818</v>
       </c>
       <c r="K48" t="n">
-        <v>52543</v>
+        <v>52165</v>
       </c>
       <c r="L48" t="n">
-        <v>52939.5</v>
+        <v>52512</v>
       </c>
       <c r="M48" t="n">
-        <v>53121</v>
+        <v>52685</v>
       </c>
       <c r="N48" t="n">
-        <v>53302.5</v>
+        <v>52858</v>
       </c>
       <c r="O48" t="n">
-        <v>53914</v>
+        <v>53379</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4556,7 +4556,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
+      <c r="S48" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4580,50 +4580,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>52473</v>
+        <v>52059</v>
       </c>
       <c r="C49" t="n">
-        <v>52676</v>
+        <v>52739</v>
       </c>
       <c r="D49" t="n">
-        <v>51992</v>
+        <v>52059</v>
       </c>
       <c r="E49" t="n">
-        <v>52095</v>
+        <v>52585</v>
       </c>
       <c r="F49" t="n">
-        <v>-330</v>
+        <v>490</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0063</v>
+        <v>0.0094</v>
       </c>
       <c r="H49" t="n">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="I49" t="n">
-        <v>51819</v>
+        <v>51308</v>
       </c>
       <c r="J49" t="n">
-        <v>51818</v>
+        <v>51291.5</v>
       </c>
       <c r="K49" t="n">
-        <v>52165</v>
+        <v>51753</v>
       </c>
       <c r="L49" t="n">
-        <v>52512</v>
+        <v>52214.5</v>
       </c>
       <c r="M49" t="n">
-        <v>52685</v>
+        <v>52437</v>
       </c>
       <c r="N49" t="n">
-        <v>52858</v>
+        <v>52659.5</v>
       </c>
       <c r="O49" t="n">
-        <v>53379</v>
+        <v>53360</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4631,22 +4631,24 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
@@ -4655,55 +4657,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>52059</v>
+        <v>52376</v>
       </c>
       <c r="C50" t="n">
-        <v>52739</v>
+        <v>52672</v>
       </c>
       <c r="D50" t="n">
-        <v>52059</v>
+        <v>52226</v>
       </c>
       <c r="E50" t="n">
-        <v>52585</v>
+        <v>52440</v>
       </c>
       <c r="F50" t="n">
-        <v>490</v>
+        <v>-145</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0094</v>
+        <v>-0.0028</v>
       </c>
       <c r="H50" t="n">
-        <v>680</v>
+        <v>446</v>
       </c>
       <c r="I50" t="n">
-        <v>51308</v>
+        <v>51379</v>
       </c>
       <c r="J50" t="n">
-        <v>51291.5</v>
+        <v>51998</v>
       </c>
       <c r="K50" t="n">
-        <v>51753</v>
+        <v>52245</v>
       </c>
       <c r="L50" t="n">
-        <v>52214.5</v>
+        <v>52492</v>
       </c>
       <c r="M50" t="n">
-        <v>52437</v>
+        <v>52925</v>
       </c>
       <c r="N50" t="n">
-        <v>52659.5</v>
+        <v>53358</v>
       </c>
       <c r="O50" t="n">
-        <v>53360</v>
+        <v>53419</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4711,23 +4717,21 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4739,72 +4743,74 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>52376</v>
+        <v>52499</v>
       </c>
       <c r="C51" t="n">
-        <v>52672</v>
+        <v>52499</v>
       </c>
       <c r="D51" t="n">
-        <v>52226</v>
+        <v>51908</v>
       </c>
       <c r="E51" t="n">
-        <v>52440</v>
+        <v>52115</v>
       </c>
       <c r="F51" t="n">
-        <v>-145</v>
+        <v>-325</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0028</v>
+        <v>-0.0062</v>
       </c>
       <c r="H51" t="n">
-        <v>446</v>
+        <v>591</v>
       </c>
       <c r="I51" t="n">
-        <v>51379</v>
+        <v>51780</v>
       </c>
       <c r="J51" t="n">
-        <v>51998</v>
+        <v>51989.5</v>
       </c>
       <c r="K51" t="n">
-        <v>52245</v>
+        <v>52217</v>
       </c>
       <c r="L51" t="n">
-        <v>52492</v>
+        <v>52444.5</v>
       </c>
       <c r="M51" t="n">
-        <v>52925</v>
+        <v>52663</v>
       </c>
       <c r="N51" t="n">
-        <v>53358</v>
+        <v>52881.5</v>
       </c>
       <c r="O51" t="n">
-        <v>53419</v>
+        <v>53118</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4821,74 +4827,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>52499</v>
+        <v>52162</v>
       </c>
       <c r="C52" t="n">
-        <v>52499</v>
+        <v>52298</v>
       </c>
       <c r="D52" t="n">
-        <v>51908</v>
+        <v>51209</v>
       </c>
       <c r="E52" t="n">
-        <v>52115</v>
+        <v>51507</v>
       </c>
       <c r="F52" t="n">
-        <v>-325</v>
+        <v>-608</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0062</v>
+        <v>-0.0117</v>
       </c>
       <c r="H52" t="n">
-        <v>591</v>
+        <v>1089</v>
       </c>
       <c r="I52" t="n">
-        <v>51780</v>
+        <v>51317</v>
       </c>
       <c r="J52" t="n">
-        <v>51989.5</v>
+        <v>51479.75</v>
       </c>
       <c r="K52" t="n">
-        <v>52217</v>
+        <v>51819.5</v>
       </c>
       <c r="L52" t="n">
-        <v>52444.5</v>
+        <v>52159.25</v>
       </c>
       <c r="M52" t="n">
-        <v>52663</v>
+        <v>52410.5</v>
       </c>
       <c r="N52" t="n">
-        <v>52881.5</v>
+        <v>52661.75</v>
       </c>
       <c r="O52" t="n">
-        <v>53118</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
+        <v>53090</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q52" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
+      <c r="S52" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4912,74 +4916,70 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>52162</v>
+        <v>51486</v>
       </c>
       <c r="C53" t="n">
-        <v>52298</v>
+        <v>52169</v>
       </c>
       <c r="D53" t="n">
-        <v>51209</v>
+        <v>51455</v>
       </c>
       <c r="E53" t="n">
-        <v>51507</v>
+        <v>51807</v>
       </c>
       <c r="F53" t="n">
-        <v>-608</v>
+        <v>300</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0117</v>
+        <v>0.0058</v>
       </c>
       <c r="H53" t="n">
-        <v>1089</v>
+        <v>714</v>
       </c>
       <c r="I53" t="n">
-        <v>51317</v>
+        <v>50120</v>
       </c>
       <c r="J53" t="n">
-        <v>51479.75</v>
+        <v>50294.75</v>
       </c>
       <c r="K53" t="n">
-        <v>51819.5</v>
+        <v>50962.5</v>
       </c>
       <c r="L53" t="n">
-        <v>52159.25</v>
+        <v>51630.25</v>
       </c>
       <c r="M53" t="n">
-        <v>52410.5</v>
+        <v>52051.5</v>
       </c>
       <c r="N53" t="n">
-        <v>52661.75</v>
+        <v>52472.75</v>
       </c>
       <c r="O53" t="n">
-        <v>53090</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
+        <v>53387</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
       <c r="U53" s="8" t="n">
         <v/>
       </c>
@@ -4991,55 +4991,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>51486</v>
+        <v>51800</v>
       </c>
       <c r="C54" t="n">
-        <v>52169</v>
+        <v>51957</v>
       </c>
       <c r="D54" t="n">
-        <v>51455</v>
+        <v>51576</v>
       </c>
       <c r="E54" t="n">
-        <v>51807</v>
+        <v>51761</v>
       </c>
       <c r="F54" t="n">
-        <v>300</v>
+        <v>-46</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0009</v>
       </c>
       <c r="H54" t="n">
-        <v>714</v>
+        <v>381</v>
       </c>
       <c r="I54" t="n">
-        <v>50120</v>
+        <v>50741</v>
       </c>
       <c r="J54" t="n">
-        <v>50294.75</v>
+        <v>51090.5</v>
       </c>
       <c r="K54" t="n">
-        <v>50962.5</v>
+        <v>51450</v>
       </c>
       <c r="L54" t="n">
-        <v>51630.25</v>
+        <v>51809.5</v>
       </c>
       <c r="M54" t="n">
-        <v>52051.5</v>
+        <v>52164</v>
       </c>
       <c r="N54" t="n">
-        <v>52472.75</v>
+        <v>52518.5</v>
       </c>
       <c r="O54" t="n">
-        <v>53387</v>
+        <v>52883</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5052,13 +5056,11 @@
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5073,57 +5075,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>51800</v>
+        <v>52085</v>
       </c>
       <c r="C55" t="n">
-        <v>51957</v>
+        <v>52557</v>
       </c>
       <c r="D55" t="n">
-        <v>51576</v>
+        <v>52080</v>
       </c>
       <c r="E55" t="n">
-        <v>51761</v>
+        <v>52475</v>
       </c>
       <c r="F55" t="n">
-        <v>-46</v>
+        <v>714</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0138</v>
       </c>
       <c r="H55" t="n">
-        <v>381</v>
+        <v>477</v>
       </c>
       <c r="I55" t="n">
-        <v>50741</v>
+        <v>51195</v>
       </c>
       <c r="J55" t="n">
-        <v>51090.5</v>
+        <v>51377.25</v>
       </c>
       <c r="K55" t="n">
-        <v>51450</v>
+        <v>51570.5</v>
       </c>
       <c r="L55" t="n">
-        <v>51809.5</v>
+        <v>51763.75</v>
       </c>
       <c r="M55" t="n">
-        <v>52164</v>
+        <v>51951.5</v>
       </c>
       <c r="N55" t="n">
-        <v>52518.5</v>
+        <v>52139.25</v>
       </c>
       <c r="O55" t="n">
-        <v>52883</v>
+        <v>52338</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5136,76 +5138,78 @@
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W55" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W55" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>52085</v>
+        <v>52470</v>
       </c>
       <c r="C56" t="n">
-        <v>52557</v>
+        <v>52844</v>
       </c>
       <c r="D56" t="n">
-        <v>52080</v>
+        <v>52125</v>
       </c>
       <c r="E56" t="n">
-        <v>52475</v>
+        <v>52279</v>
       </c>
       <c r="F56" t="n">
-        <v>714</v>
+        <v>-196</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0138</v>
+        <v>-0.0037</v>
       </c>
       <c r="H56" t="n">
-        <v>477</v>
+        <v>719</v>
       </c>
       <c r="I56" t="n">
-        <v>51195</v>
+        <v>51603</v>
       </c>
       <c r="J56" t="n">
-        <v>51377.25</v>
+        <v>52076.25</v>
       </c>
       <c r="K56" t="n">
-        <v>51570.5</v>
+        <v>52236.5</v>
       </c>
       <c r="L56" t="n">
-        <v>51763.75</v>
+        <v>52396.75</v>
       </c>
       <c r="M56" t="n">
-        <v>51951.5</v>
+        <v>52713.5</v>
       </c>
       <c r="N56" t="n">
-        <v>52139.25</v>
+        <v>53030.25</v>
       </c>
       <c r="O56" t="n">
-        <v>52338</v>
+        <v>53034</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5213,12 +5217,14 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
@@ -5226,70 +5232,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V56" s="8" t="n">
+        <v/>
       </c>
       <c r="W56" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>52470</v>
+        <v>52255</v>
       </c>
       <c r="C57" t="n">
-        <v>52844</v>
+        <v>52371</v>
       </c>
       <c r="D57" t="n">
-        <v>52125</v>
+        <v>51844</v>
       </c>
       <c r="E57" t="n">
-        <v>52279</v>
+        <v>51873</v>
       </c>
       <c r="F57" t="n">
-        <v>-196</v>
+        <v>-406</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0037</v>
+        <v>-0.0078</v>
       </c>
       <c r="H57" t="n">
-        <v>719</v>
+        <v>527</v>
       </c>
       <c r="I57" t="n">
-        <v>51603</v>
+        <v>51406</v>
       </c>
       <c r="J57" t="n">
-        <v>52076.25</v>
+        <v>51457.25</v>
       </c>
       <c r="K57" t="n">
-        <v>52236.5</v>
+        <v>51919.5</v>
       </c>
       <c r="L57" t="n">
-        <v>52396.75</v>
+        <v>52381.75</v>
       </c>
       <c r="M57" t="n">
-        <v>52713.5</v>
+        <v>52638.5</v>
       </c>
       <c r="N57" t="n">
-        <v>53030.25</v>
+        <v>52895.25</v>
       </c>
       <c r="O57" t="n">
-        <v>53034</v>
+        <v>53563</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5302,15 +5308,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5325,57 +5329,57 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>52255</v>
+        <v>51878</v>
       </c>
       <c r="C58" t="n">
-        <v>52371</v>
+        <v>51905</v>
       </c>
       <c r="D58" t="n">
-        <v>51844</v>
+        <v>51479</v>
       </c>
       <c r="E58" t="n">
-        <v>51873</v>
+        <v>51717</v>
       </c>
       <c r="F58" t="n">
-        <v>-406</v>
+        <v>-156</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0078</v>
+        <v>-0.003</v>
       </c>
       <c r="H58" t="n">
-        <v>527</v>
+        <v>426</v>
       </c>
       <c r="I58" t="n">
-        <v>51406</v>
+        <v>51317</v>
       </c>
       <c r="J58" t="n">
-        <v>51457.25</v>
+        <v>51228.75</v>
       </c>
       <c r="K58" t="n">
-        <v>51919.5</v>
+        <v>51609.5</v>
       </c>
       <c r="L58" t="n">
-        <v>52381.75</v>
+        <v>51990.25</v>
       </c>
       <c r="M58" t="n">
-        <v>52638.5</v>
+        <v>52136.5</v>
       </c>
       <c r="N58" t="n">
-        <v>52895.25</v>
+        <v>52282.75</v>
       </c>
       <c r="O58" t="n">
-        <v>53563</v>
+        <v>52898</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5388,7 +5392,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S58" s="10" t="inlineStr">
+      <c r="S58" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5416,50 +5420,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>51878</v>
+        <v>51655</v>
       </c>
       <c r="C59" t="n">
-        <v>51905</v>
+        <v>52223</v>
       </c>
       <c r="D59" t="n">
-        <v>51479</v>
+        <v>51610</v>
       </c>
       <c r="E59" t="n">
-        <v>51717</v>
+        <v>52163</v>
       </c>
       <c r="F59" t="n">
-        <v>-156</v>
+        <v>446</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.0086</v>
       </c>
       <c r="H59" t="n">
-        <v>426</v>
+        <v>613</v>
       </c>
       <c r="I59" t="n">
-        <v>51317</v>
+        <v>51053</v>
       </c>
       <c r="J59" t="n">
-        <v>51228.75</v>
+        <v>51303.5</v>
       </c>
       <c r="K59" t="n">
-        <v>51609.5</v>
+        <v>51504</v>
       </c>
       <c r="L59" t="n">
-        <v>51990.25</v>
+        <v>51704.5</v>
       </c>
       <c r="M59" t="n">
-        <v>52136.5</v>
+        <v>51930</v>
       </c>
       <c r="N59" t="n">
-        <v>52282.75</v>
+        <v>52155.5</v>
       </c>
       <c r="O59" t="n">
-        <v>52898</v>
+        <v>52331</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5467,22 +5471,24 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="inlineStr">
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U59" s="8" t="n">
-        <v/>
-      </c>
       <c r="V59" s="8" t="n">
         <v/>
       </c>
@@ -5491,59 +5497,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>51655</v>
+        <v>52140</v>
       </c>
       <c r="C60" t="n">
-        <v>52223</v>
+        <v>52153</v>
       </c>
       <c r="D60" t="n">
-        <v>51610</v>
+        <v>51744</v>
       </c>
       <c r="E60" t="n">
-        <v>52163</v>
+        <v>51837</v>
       </c>
       <c r="F60" t="n">
-        <v>446</v>
+        <v>-326</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.0062</v>
       </c>
       <c r="H60" t="n">
-        <v>613</v>
+        <v>409</v>
       </c>
       <c r="I60" t="n">
-        <v>51053</v>
+        <v>50997</v>
       </c>
       <c r="J60" t="n">
-        <v>51303.5</v>
+        <v>51673.25</v>
       </c>
       <c r="K60" t="n">
-        <v>51504</v>
+        <v>51856.5</v>
       </c>
       <c r="L60" t="n">
-        <v>51704.5</v>
+        <v>52039.75</v>
       </c>
       <c r="M60" t="n">
-        <v>51930</v>
+        <v>52469.5</v>
       </c>
       <c r="N60" t="n">
-        <v>52155.5</v>
+        <v>52899.25</v>
       </c>
       <c r="O60" t="n">
-        <v>52331</v>
+        <v>52836</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5551,23 +5553,21 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
@@ -5577,55 +5577,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>52140</v>
+        <v>51845</v>
       </c>
       <c r="C61" t="n">
-        <v>52153</v>
+        <v>52002</v>
       </c>
       <c r="D61" t="n">
-        <v>51744</v>
+        <v>51459</v>
       </c>
       <c r="E61" t="n">
-        <v>51837</v>
+        <v>51702</v>
       </c>
       <c r="F61" t="n">
-        <v>-326</v>
+        <v>-135</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0062</v>
+        <v>-0.0026</v>
       </c>
       <c r="H61" t="n">
-        <v>409</v>
+        <v>543</v>
       </c>
       <c r="I61" t="n">
-        <v>50997</v>
+        <v>51335</v>
       </c>
       <c r="J61" t="n">
-        <v>51673.25</v>
+        <v>51372.25</v>
       </c>
       <c r="K61" t="n">
-        <v>51856.5</v>
+        <v>51632.5</v>
       </c>
       <c r="L61" t="n">
-        <v>52039.75</v>
+        <v>51892.75</v>
       </c>
       <c r="M61" t="n">
-        <v>52469.5</v>
+        <v>52041.5</v>
       </c>
       <c r="N61" t="n">
-        <v>52899.25</v>
+        <v>52190.25</v>
       </c>
       <c r="O61" t="n">
-        <v>52836</v>
+        <v>52562</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5638,7 +5642,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S61" s="10" t="inlineStr">
+      <c r="S61" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5659,57 +5663,57 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>51765</v>
+        <v>51335</v>
       </c>
       <c r="C62" t="n">
-        <v>51788</v>
+        <v>51346</v>
       </c>
       <c r="D62" t="n">
-        <v>51758</v>
+        <v>51307</v>
       </c>
       <c r="E62" t="n">
-        <v>51787</v>
+        <v>51335</v>
       </c>
       <c r="F62" t="n">
-        <v>-50</v>
+        <v>-367</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.001</v>
+        <v>-0.0071</v>
       </c>
       <c r="H62" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="I62" t="n">
-        <v>51335</v>
+        <v>50916</v>
       </c>
       <c r="J62" t="n">
-        <v>51372.25</v>
+        <v>51144.75</v>
       </c>
       <c r="K62" t="n">
-        <v>51632.5</v>
+        <v>51430.5</v>
       </c>
       <c r="L62" t="n">
-        <v>51892.75</v>
+        <v>51716.25</v>
       </c>
       <c r="M62" t="n">
-        <v>52041.5</v>
+        <v>51973.5</v>
       </c>
       <c r="N62" t="n">
-        <v>52190.25</v>
+        <v>52230.75</v>
       </c>
       <c r="O62" t="n">
-        <v>52562</v>
+        <v>52545</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5717,12 +5721,14 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5741,7 +5747,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5674,25 +5674,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>51335</v>
+        <v>51765</v>
       </c>
       <c r="C62" t="n">
-        <v>51346</v>
+        <v>51997</v>
       </c>
       <c r="D62" t="n">
-        <v>51307</v>
+        <v>51218</v>
       </c>
       <c r="E62" t="n">
-        <v>51335</v>
+        <v>51278</v>
       </c>
       <c r="F62" t="n">
-        <v>-367</v>
+        <v>-424</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0071</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H62" t="n">
-        <v>39</v>
+        <v>779</v>
       </c>
       <c r="I62" t="n">
         <v>50916</v>
@@ -5718,12 +5718,14 @@
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S62" s="7" t="inlineStr">
@@ -5731,8 +5733,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T62" s="8" t="n">
-        <v/>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5748,6 +5752,88 @@
       <c r="X62" t="inlineStr">
         <is>
           <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>51251</v>
+      </c>
+      <c r="C63" t="n">
+        <v>51255</v>
+      </c>
+      <c r="D63" t="n">
+        <v>51235</v>
+      </c>
+      <c r="E63" t="n">
+        <v>51243</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-35</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>-0.0007</v>
+      </c>
+      <c r="H63" t="n">
+        <v>20</v>
+      </c>
+      <c r="I63" t="n">
+        <v>50439</v>
+      </c>
+      <c r="J63" t="n">
+        <v>50334.25</v>
+      </c>
+      <c r="K63" t="n">
+        <v>50888.5</v>
+      </c>
+      <c r="L63" t="n">
+        <v>51442.75</v>
+      </c>
+      <c r="M63" t="n">
+        <v>51667.5</v>
+      </c>
+      <c r="N63" t="n">
+        <v>51892.25</v>
+      </c>
+      <c r="O63" t="n">
+        <v>52776</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,60 +634,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53405</v>
+        <v>53166</v>
       </c>
       <c r="C2" t="n">
-        <v>53656</v>
+        <v>53207</v>
       </c>
       <c r="D2" t="n">
-        <v>53076</v>
+        <v>52343</v>
       </c>
       <c r="E2" t="n">
-        <v>53197</v>
+        <v>52624</v>
       </c>
       <c r="F2" t="n">
-        <v>-175</v>
+        <v>-573</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0108</v>
       </c>
       <c r="H2" t="n">
-        <v>580</v>
+        <v>864</v>
       </c>
       <c r="I2" t="n">
-        <v>52503</v>
+        <v>52496</v>
       </c>
       <c r="J2" t="n">
-        <v>53003.25</v>
+        <v>52532.5</v>
       </c>
       <c r="K2" t="n">
-        <v>53142.5</v>
+        <v>52907</v>
       </c>
       <c r="L2" t="n">
-        <v>53281.75</v>
+        <v>53281.5</v>
       </c>
       <c r="M2" t="n">
-        <v>53601.5</v>
+        <v>53487</v>
       </c>
       <c r="N2" t="n">
-        <v>53921.25</v>
+        <v>53692.5</v>
       </c>
       <c r="O2" t="n">
-        <v>53880</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+        <v>54236</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
@@ -695,10 +699,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -713,76 +715,70 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53166</v>
+        <v>52541</v>
       </c>
       <c r="C3" t="n">
-        <v>53207</v>
+        <v>52865</v>
       </c>
       <c r="D3" t="n">
-        <v>52343</v>
+        <v>52501</v>
       </c>
       <c r="E3" t="n">
-        <v>52624</v>
+        <v>52761</v>
       </c>
       <c r="F3" t="n">
-        <v>-573</v>
+        <v>137</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0108</v>
+        <v>0.0026</v>
       </c>
       <c r="H3" t="n">
-        <v>864</v>
+        <v>364</v>
       </c>
       <c r="I3" t="n">
-        <v>52496</v>
+        <v>51479</v>
       </c>
       <c r="J3" t="n">
-        <v>52532.5</v>
+        <v>51684.5</v>
       </c>
       <c r="K3" t="n">
-        <v>52907</v>
+        <v>52192</v>
       </c>
       <c r="L3" t="n">
-        <v>53281.5</v>
+        <v>52699.5</v>
       </c>
       <c r="M3" t="n">
-        <v>53487</v>
+        <v>53056</v>
       </c>
       <c r="N3" t="n">
-        <v>53692.5</v>
+        <v>53412.5</v>
       </c>
       <c r="O3" t="n">
-        <v>54236</v>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>54071</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -801,57 +797,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>52541</v>
+        <v>52753</v>
       </c>
       <c r="C4" t="n">
-        <v>52865</v>
+        <v>52992</v>
       </c>
       <c r="D4" t="n">
-        <v>52501</v>
+        <v>52506</v>
       </c>
       <c r="E4" t="n">
-        <v>52761</v>
+        <v>52906</v>
       </c>
       <c r="F4" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0027</v>
       </c>
       <c r="H4" t="n">
-        <v>364</v>
+        <v>486</v>
       </c>
       <c r="I4" t="n">
-        <v>51479</v>
+        <v>52137</v>
       </c>
       <c r="J4" t="n">
-        <v>51684.5</v>
+        <v>52436</v>
       </c>
       <c r="K4" t="n">
-        <v>52192</v>
+        <v>52579</v>
       </c>
       <c r="L4" t="n">
-        <v>52699.5</v>
+        <v>52722</v>
       </c>
       <c r="M4" t="n">
-        <v>53056</v>
+        <v>52943</v>
       </c>
       <c r="N4" t="n">
-        <v>53412.5</v>
+        <v>53164</v>
       </c>
       <c r="O4" t="n">
-        <v>54071</v>
+        <v>53229</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -859,16 +855,20 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -881,59 +881,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52753</v>
+        <v>52844</v>
       </c>
       <c r="C5" t="n">
-        <v>52992</v>
+        <v>53113</v>
       </c>
       <c r="D5" t="n">
-        <v>52506</v>
+        <v>52603</v>
       </c>
       <c r="E5" t="n">
-        <v>52906</v>
+        <v>52764</v>
       </c>
       <c r="F5" t="n">
-        <v>145</v>
+        <v>-142</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0027</v>
       </c>
       <c r="H5" t="n">
-        <v>486</v>
+        <v>510</v>
       </c>
       <c r="I5" t="n">
-        <v>52137</v>
+        <v>52020</v>
       </c>
       <c r="J5" t="n">
-        <v>52436</v>
+        <v>52498.5</v>
       </c>
       <c r="K5" t="n">
-        <v>52579</v>
+        <v>52663</v>
       </c>
       <c r="L5" t="n">
-        <v>52722</v>
+        <v>52827.5</v>
       </c>
       <c r="M5" t="n">
-        <v>52943</v>
+        <v>53149</v>
       </c>
       <c r="N5" t="n">
-        <v>53164</v>
+        <v>53470.5</v>
       </c>
       <c r="O5" t="n">
-        <v>53229</v>
+        <v>53478</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -946,15 +942,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -967,55 +961,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52844</v>
+        <v>52731</v>
       </c>
       <c r="C6" t="n">
-        <v>53113</v>
+        <v>52981</v>
       </c>
       <c r="D6" t="n">
-        <v>52603</v>
+        <v>52255</v>
       </c>
       <c r="E6" t="n">
-        <v>52764</v>
+        <v>52791</v>
       </c>
       <c r="F6" t="n">
-        <v>-142</v>
+        <v>27</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0005</v>
       </c>
       <c r="H6" t="n">
-        <v>510</v>
+        <v>726</v>
       </c>
       <c r="I6" t="n">
-        <v>52020</v>
+        <v>52093</v>
       </c>
       <c r="J6" t="n">
-        <v>52498.5</v>
+        <v>52207</v>
       </c>
       <c r="K6" t="n">
-        <v>52663</v>
+        <v>52509</v>
       </c>
       <c r="L6" t="n">
-        <v>52827.5</v>
+        <v>52811</v>
       </c>
       <c r="M6" t="n">
-        <v>53149</v>
+        <v>53019</v>
       </c>
       <c r="N6" t="n">
-        <v>53470.5</v>
+        <v>53227</v>
       </c>
       <c r="O6" t="n">
-        <v>53478</v>
+        <v>53623</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1049,57 +1047,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>52731</v>
+        <v>52792</v>
       </c>
       <c r="C7" t="n">
-        <v>52981</v>
+        <v>53088</v>
       </c>
       <c r="D7" t="n">
-        <v>52255</v>
+        <v>52680</v>
       </c>
       <c r="E7" t="n">
-        <v>52791</v>
+        <v>52900</v>
       </c>
       <c r="F7" t="n">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0021</v>
       </c>
       <c r="H7" t="n">
-        <v>726</v>
+        <v>408</v>
       </c>
       <c r="I7" t="n">
-        <v>52093</v>
+        <v>51529</v>
       </c>
       <c r="J7" t="n">
-        <v>52207</v>
+        <v>52151.5</v>
       </c>
       <c r="K7" t="n">
-        <v>52509</v>
+        <v>52428</v>
       </c>
       <c r="L7" t="n">
-        <v>52811</v>
+        <v>52704.5</v>
       </c>
       <c r="M7" t="n">
-        <v>53019</v>
+        <v>53154</v>
       </c>
       <c r="N7" t="n">
-        <v>53227</v>
+        <v>53603.5</v>
       </c>
       <c r="O7" t="n">
-        <v>53623</v>
+        <v>53707</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1107,14 +1105,12 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1131,59 +1127,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52792</v>
+        <v>52919</v>
       </c>
       <c r="C8" t="n">
-        <v>53088</v>
+        <v>53108</v>
       </c>
       <c r="D8" t="n">
-        <v>52680</v>
+        <v>52607</v>
       </c>
       <c r="E8" t="n">
-        <v>52900</v>
+        <v>52786</v>
       </c>
       <c r="F8" t="n">
-        <v>109</v>
+        <v>-114</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0022</v>
       </c>
       <c r="H8" t="n">
-        <v>408</v>
+        <v>501</v>
       </c>
       <c r="I8" t="n">
-        <v>51529</v>
+        <v>52272</v>
       </c>
       <c r="J8" t="n">
-        <v>52151.5</v>
+        <v>52500</v>
       </c>
       <c r="K8" t="n">
-        <v>52428</v>
+        <v>52696</v>
       </c>
       <c r="L8" t="n">
-        <v>52704.5</v>
+        <v>52892</v>
       </c>
       <c r="M8" t="n">
-        <v>53154</v>
+        <v>53104</v>
       </c>
       <c r="N8" t="n">
-        <v>53603.5</v>
+        <v>53316</v>
       </c>
       <c r="O8" t="n">
-        <v>53707</v>
+        <v>53496</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1191,16 +1183,20 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1213,65 +1209,71 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52919</v>
+        <v>52778</v>
       </c>
       <c r="C9" t="n">
-        <v>53108</v>
+        <v>52835</v>
       </c>
       <c r="D9" t="n">
-        <v>52607</v>
+        <v>52174</v>
       </c>
       <c r="E9" t="n">
-        <v>52786</v>
+        <v>52375</v>
       </c>
       <c r="F9" t="n">
-        <v>-114</v>
+        <v>-411</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0078</v>
       </c>
       <c r="H9" t="n">
-        <v>501</v>
+        <v>661</v>
       </c>
       <c r="I9" t="n">
-        <v>52272</v>
+        <v>52106</v>
       </c>
       <c r="J9" t="n">
-        <v>52500</v>
+        <v>52249.25</v>
       </c>
       <c r="K9" t="n">
-        <v>52696</v>
+        <v>52535.5</v>
       </c>
       <c r="L9" t="n">
-        <v>52892</v>
+        <v>52821.75</v>
       </c>
       <c r="M9" t="n">
-        <v>53104</v>
+        <v>53036.5</v>
       </c>
       <c r="N9" t="n">
-        <v>53316</v>
+        <v>53251.25</v>
       </c>
       <c r="O9" t="n">
-        <v>53496</v>
+        <v>53609</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
@@ -1279,10 +1281,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1297,69 +1297,67 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52778</v>
+        <v>52300</v>
       </c>
       <c r="C10" t="n">
-        <v>52835</v>
+        <v>52633</v>
       </c>
       <c r="D10" t="n">
-        <v>52174</v>
+        <v>51999</v>
       </c>
       <c r="E10" t="n">
-        <v>52375</v>
+        <v>52073</v>
       </c>
       <c r="F10" t="n">
-        <v>-411</v>
+        <v>-302</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0078</v>
+        <v>-0.0058</v>
       </c>
       <c r="H10" t="n">
-        <v>661</v>
+        <v>634</v>
       </c>
       <c r="I10" t="n">
-        <v>52106</v>
+        <v>51513</v>
       </c>
       <c r="J10" t="n">
-        <v>52249.25</v>
+        <v>51649.25</v>
       </c>
       <c r="K10" t="n">
-        <v>52535.5</v>
+        <v>52044.5</v>
       </c>
       <c r="L10" t="n">
-        <v>52821.75</v>
+        <v>52439.75</v>
       </c>
       <c r="M10" t="n">
-        <v>53036.5</v>
+        <v>52705.5</v>
       </c>
       <c r="N10" t="n">
-        <v>53251.25</v>
+        <v>52971.25</v>
       </c>
       <c r="O10" t="n">
-        <v>53609</v>
+        <v>53496</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S10" s="7" t="inlineStr">
@@ -1390,50 +1388,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>52300</v>
+        <v>52091</v>
       </c>
       <c r="C11" t="n">
-        <v>52633</v>
+        <v>52590</v>
       </c>
       <c r="D11" t="n">
-        <v>51999</v>
+        <v>52035</v>
       </c>
       <c r="E11" t="n">
-        <v>52073</v>
+        <v>52443</v>
       </c>
       <c r="F11" t="n">
-        <v>-302</v>
+        <v>370</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.0071</v>
       </c>
       <c r="H11" t="n">
-        <v>634</v>
+        <v>555</v>
       </c>
       <c r="I11" t="n">
-        <v>51513</v>
+        <v>51365</v>
       </c>
       <c r="J11" t="n">
-        <v>51649.25</v>
+        <v>51317.5</v>
       </c>
       <c r="K11" t="n">
-        <v>52044.5</v>
+        <v>51756</v>
       </c>
       <c r="L11" t="n">
-        <v>52439.75</v>
+        <v>52194.5</v>
       </c>
       <c r="M11" t="n">
-        <v>52705.5</v>
+        <v>52390</v>
       </c>
       <c r="N11" t="n">
-        <v>52971.25</v>
+        <v>52585.5</v>
       </c>
       <c r="O11" t="n">
-        <v>53496</v>
+        <v>53267</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1441,21 +1439,23 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1467,57 +1467,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52091</v>
+        <v>52431</v>
       </c>
       <c r="C12" t="n">
-        <v>52590</v>
+        <v>52721</v>
       </c>
       <c r="D12" t="n">
-        <v>52035</v>
+        <v>52262</v>
       </c>
       <c r="E12" t="n">
-        <v>52443</v>
+        <v>52449</v>
       </c>
       <c r="F12" t="n">
-        <v>370</v>
+        <v>6</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0001</v>
       </c>
       <c r="H12" t="n">
-        <v>555</v>
+        <v>459</v>
       </c>
       <c r="I12" t="n">
-        <v>51365</v>
+        <v>51480</v>
       </c>
       <c r="J12" t="n">
-        <v>51317.5</v>
+        <v>51953.25</v>
       </c>
       <c r="K12" t="n">
-        <v>51756</v>
+        <v>52165.5</v>
       </c>
       <c r="L12" t="n">
-        <v>52194.5</v>
+        <v>52377.75</v>
       </c>
       <c r="M12" t="n">
-        <v>52390</v>
+        <v>52720.5</v>
       </c>
       <c r="N12" t="n">
-        <v>52585.5</v>
+        <v>53063.25</v>
       </c>
       <c r="O12" t="n">
-        <v>53267</v>
+        <v>53145</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1530,19 +1530,17 @@
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
@@ -1551,88 +1549,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>52431</v>
+        <v>52430</v>
       </c>
       <c r="C13" t="n">
-        <v>52721</v>
+        <v>52515</v>
       </c>
       <c r="D13" t="n">
-        <v>52262</v>
+        <v>51720</v>
       </c>
       <c r="E13" t="n">
-        <v>52449</v>
+        <v>51894</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>-555</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0106</v>
       </c>
       <c r="H13" t="n">
-        <v>459</v>
+        <v>795</v>
       </c>
       <c r="I13" t="n">
-        <v>51480</v>
+        <v>51803</v>
       </c>
       <c r="J13" t="n">
-        <v>51953.25</v>
+        <v>51968.75</v>
       </c>
       <c r="K13" t="n">
-        <v>52165.5</v>
+        <v>52219.5</v>
       </c>
       <c r="L13" t="n">
-        <v>52377.75</v>
+        <v>52470.25</v>
       </c>
       <c r="M13" t="n">
-        <v>52720.5</v>
+        <v>52678.5</v>
       </c>
       <c r="N13" t="n">
-        <v>53063.25</v>
+        <v>52886.75</v>
       </c>
       <c r="O13" t="n">
-        <v>53145</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
+        <v>53180</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W13" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr"/>
@@ -1640,74 +1638,70 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>52430</v>
+        <v>51920</v>
       </c>
       <c r="C14" t="n">
-        <v>52515</v>
+        <v>52314</v>
       </c>
       <c r="D14" t="n">
-        <v>51720</v>
+        <v>51846</v>
       </c>
       <c r="E14" t="n">
-        <v>51894</v>
+        <v>52124</v>
       </c>
       <c r="F14" t="n">
-        <v>-555</v>
+        <v>230</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0044</v>
       </c>
       <c r="H14" t="n">
-        <v>795</v>
+        <v>468</v>
       </c>
       <c r="I14" t="n">
-        <v>51803</v>
+        <v>50925</v>
       </c>
       <c r="J14" t="n">
-        <v>51968.75</v>
+        <v>50987.25</v>
       </c>
       <c r="K14" t="n">
-        <v>52219.5</v>
+        <v>51496.5</v>
       </c>
       <c r="L14" t="n">
-        <v>52470.25</v>
+        <v>52005.75</v>
       </c>
       <c r="M14" t="n">
-        <v>52678.5</v>
+        <v>52291.5</v>
       </c>
       <c r="N14" t="n">
-        <v>52886.75</v>
+        <v>52577.25</v>
       </c>
       <c r="O14" t="n">
-        <v>53180</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
+        <v>53310</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
@@ -1719,55 +1713,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>51920</v>
+        <v>52299</v>
       </c>
       <c r="C15" t="n">
-        <v>52314</v>
+        <v>52790</v>
       </c>
       <c r="D15" t="n">
-        <v>51846</v>
+        <v>52173</v>
       </c>
       <c r="E15" t="n">
-        <v>52124</v>
+        <v>52382</v>
       </c>
       <c r="F15" t="n">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0049</v>
       </c>
       <c r="H15" t="n">
-        <v>468</v>
+        <v>617</v>
       </c>
       <c r="I15" t="n">
-        <v>50925</v>
+        <v>51378</v>
       </c>
       <c r="J15" t="n">
-        <v>50987.25</v>
+        <v>51678</v>
       </c>
       <c r="K15" t="n">
-        <v>51496.5</v>
+        <v>51890</v>
       </c>
       <c r="L15" t="n">
-        <v>52005.75</v>
+        <v>52102</v>
       </c>
       <c r="M15" t="n">
-        <v>52291.5</v>
+        <v>52358</v>
       </c>
       <c r="N15" t="n">
-        <v>52577.25</v>
+        <v>52614</v>
       </c>
       <c r="O15" t="n">
-        <v>53310</v>
+        <v>52782</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1780,19 +1778,23 @@
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v/>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W15" s="11" t="inlineStr">
         <is>
@@ -1801,57 +1803,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>52299</v>
+        <v>52405</v>
       </c>
       <c r="C16" t="n">
-        <v>52790</v>
+        <v>53105</v>
       </c>
       <c r="D16" t="n">
-        <v>52173</v>
+        <v>52290</v>
       </c>
       <c r="E16" t="n">
-        <v>52382</v>
+        <v>52944</v>
       </c>
       <c r="F16" t="n">
-        <v>258</v>
+        <v>562</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0107</v>
       </c>
       <c r="H16" t="n">
-        <v>617</v>
+        <v>815</v>
       </c>
       <c r="I16" t="n">
-        <v>51378</v>
+        <v>51556</v>
       </c>
       <c r="J16" t="n">
-        <v>51678</v>
+        <v>51715.25</v>
       </c>
       <c r="K16" t="n">
-        <v>51890</v>
+        <v>52073.5</v>
       </c>
       <c r="L16" t="n">
-        <v>52102</v>
+        <v>52431.75</v>
       </c>
       <c r="M16" t="n">
-        <v>52358</v>
+        <v>52690.5</v>
       </c>
       <c r="N16" t="n">
-        <v>52614</v>
+        <v>52949.25</v>
       </c>
       <c r="O16" t="n">
-        <v>52782</v>
+        <v>53407</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1869,18 +1871,16 @@
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V16" s="8" t="n">
+        <v/>
       </c>
       <c r="W16" s="11" t="inlineStr">
         <is>
@@ -1896,74 +1896,76 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52405</v>
+        <v>52915</v>
       </c>
       <c r="C17" t="n">
-        <v>53105</v>
+        <v>53033</v>
       </c>
       <c r="D17" t="n">
-        <v>52290</v>
+        <v>51630</v>
       </c>
       <c r="E17" t="n">
-        <v>52944</v>
+        <v>51765</v>
       </c>
       <c r="F17" t="n">
-        <v>562</v>
+        <v>-1179</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0223</v>
       </c>
       <c r="H17" t="n">
-        <v>815</v>
+        <v>1403</v>
       </c>
       <c r="I17" t="n">
-        <v>51556</v>
+        <v>51475</v>
       </c>
       <c r="J17" t="n">
-        <v>51715.25</v>
+        <v>52252.25</v>
       </c>
       <c r="K17" t="n">
-        <v>52073.5</v>
+        <v>52536.5</v>
       </c>
       <c r="L17" t="n">
-        <v>52431.75</v>
+        <v>52820.75</v>
       </c>
       <c r="M17" t="n">
-        <v>52690.5</v>
+        <v>53351.5</v>
       </c>
       <c r="N17" t="n">
-        <v>52949.25</v>
+        <v>53882.25</v>
       </c>
       <c r="O17" t="n">
-        <v>53407</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
+        <v>53920</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1973,83 +1975,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>52915</v>
+        <v>51759</v>
       </c>
       <c r="C18" t="n">
-        <v>53033</v>
+        <v>52484</v>
       </c>
       <c r="D18" t="n">
-        <v>51630</v>
+        <v>51732</v>
       </c>
       <c r="E18" t="n">
-        <v>51765</v>
+        <v>52380</v>
       </c>
       <c r="F18" t="n">
-        <v>-1179</v>
+        <v>615</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0119</v>
       </c>
       <c r="H18" t="n">
-        <v>1403</v>
+        <v>752</v>
       </c>
       <c r="I18" t="n">
-        <v>51475</v>
+        <v>50227</v>
       </c>
       <c r="J18" t="n">
-        <v>52252.25</v>
+        <v>50078.75</v>
       </c>
       <c r="K18" t="n">
-        <v>52536.5</v>
+        <v>51063.5</v>
       </c>
       <c r="L18" t="n">
-        <v>52820.75</v>
+        <v>52048.25</v>
       </c>
       <c r="M18" t="n">
-        <v>53351.5</v>
+        <v>52466.5</v>
       </c>
       <c r="N18" t="n">
-        <v>53882.25</v>
+        <v>52884.75</v>
       </c>
       <c r="O18" t="n">
-        <v>53920</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
+        <v>54436</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
@@ -2061,55 +2055,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>51759</v>
+        <v>52395</v>
       </c>
       <c r="C19" t="n">
-        <v>52484</v>
+        <v>52772</v>
       </c>
       <c r="D19" t="n">
-        <v>51732</v>
+        <v>52124</v>
       </c>
       <c r="E19" t="n">
-        <v>52380</v>
+        <v>52635</v>
       </c>
       <c r="F19" t="n">
-        <v>615</v>
+        <v>255</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0119</v>
+        <v>0.0049</v>
       </c>
       <c r="H19" t="n">
-        <v>752</v>
+        <v>648</v>
       </c>
       <c r="I19" t="n">
-        <v>50227</v>
+        <v>50980</v>
       </c>
       <c r="J19" t="n">
-        <v>50078.75</v>
+        <v>51764</v>
       </c>
       <c r="K19" t="n">
-        <v>51063.5</v>
+        <v>52004</v>
       </c>
       <c r="L19" t="n">
-        <v>52048.25</v>
+        <v>52244</v>
       </c>
       <c r="M19" t="n">
-        <v>52466.5</v>
+        <v>52756</v>
       </c>
       <c r="N19" t="n">
-        <v>52884.75</v>
+        <v>53268</v>
       </c>
       <c r="O19" t="n">
-        <v>54436</v>
+        <v>53236</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2143,57 +2141,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>52395</v>
+        <v>52780</v>
       </c>
       <c r="C20" t="n">
-        <v>52772</v>
+        <v>53414</v>
       </c>
       <c r="D20" t="n">
-        <v>52124</v>
+        <v>52777</v>
       </c>
       <c r="E20" t="n">
-        <v>52635</v>
+        <v>53334</v>
       </c>
       <c r="F20" t="n">
-        <v>255</v>
+        <v>699</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0133</v>
       </c>
       <c r="H20" t="n">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="I20" t="n">
-        <v>50980</v>
+        <v>51476</v>
       </c>
       <c r="J20" t="n">
-        <v>51764</v>
+        <v>52080.5</v>
       </c>
       <c r="K20" t="n">
-        <v>52004</v>
+        <v>52311</v>
       </c>
       <c r="L20" t="n">
-        <v>52244</v>
+        <v>52541.5</v>
       </c>
       <c r="M20" t="n">
-        <v>52756</v>
+        <v>52959</v>
       </c>
       <c r="N20" t="n">
-        <v>53268</v>
+        <v>53376.5</v>
       </c>
       <c r="O20" t="n">
-        <v>53236</v>
+        <v>53420</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2211,11 +2209,13 @@
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2234,50 +2234,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>52780</v>
+        <v>53381</v>
       </c>
       <c r="C21" t="n">
-        <v>53414</v>
+        <v>54423</v>
       </c>
       <c r="D21" t="n">
-        <v>52777</v>
+        <v>53267</v>
       </c>
       <c r="E21" t="n">
-        <v>53334</v>
+        <v>54268</v>
       </c>
       <c r="F21" t="n">
-        <v>699</v>
+        <v>934</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0175</v>
       </c>
       <c r="H21" t="n">
-        <v>637</v>
+        <v>1156</v>
       </c>
       <c r="I21" t="n">
-        <v>51476</v>
+        <v>52140</v>
       </c>
       <c r="J21" t="n">
-        <v>52080.5</v>
+        <v>52816.25</v>
       </c>
       <c r="K21" t="n">
-        <v>52311</v>
+        <v>53015.5</v>
       </c>
       <c r="L21" t="n">
-        <v>52541.5</v>
+        <v>53214.75</v>
       </c>
       <c r="M21" t="n">
-        <v>52959</v>
+        <v>53652.5</v>
       </c>
       <c r="N21" t="n">
-        <v>53376.5</v>
+        <v>54090.25</v>
       </c>
       <c r="O21" t="n">
-        <v>53420</v>
+        <v>54051</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2303,67 +2303,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W21" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W21" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>53381</v>
+        <v>54369</v>
       </c>
       <c r="C22" t="n">
-        <v>54423</v>
+        <v>54884</v>
       </c>
       <c r="D22" t="n">
-        <v>53267</v>
+        <v>54342</v>
       </c>
       <c r="E22" t="n">
-        <v>54268</v>
+        <v>54494</v>
       </c>
       <c r="F22" t="n">
-        <v>934</v>
+        <v>226</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0042</v>
       </c>
       <c r="H22" t="n">
-        <v>1156</v>
+        <v>542</v>
       </c>
       <c r="I22" t="n">
-        <v>52140</v>
+        <v>52111</v>
       </c>
       <c r="J22" t="n">
-        <v>52816.25</v>
+        <v>53323.5</v>
       </c>
       <c r="K22" t="n">
-        <v>53015.5</v>
+        <v>53690</v>
       </c>
       <c r="L22" t="n">
-        <v>53214.75</v>
+        <v>54056.5</v>
       </c>
       <c r="M22" t="n">
-        <v>53652.5</v>
+        <v>54846</v>
       </c>
       <c r="N22" t="n">
-        <v>54090.25</v>
+        <v>55635.5</v>
       </c>
       <c r="O22" t="n">
-        <v>54051</v>
+        <v>55579</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2381,18 +2379,14 @@
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
@@ -2404,70 +2398,72 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>54369</v>
+        <v>54555</v>
       </c>
       <c r="C23" t="n">
-        <v>54884</v>
+        <v>54678</v>
       </c>
       <c r="D23" t="n">
-        <v>54342</v>
+        <v>53952</v>
       </c>
       <c r="E23" t="n">
-        <v>54494</v>
+        <v>54013</v>
       </c>
       <c r="F23" t="n">
-        <v>226</v>
+        <v>-481</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>542</v>
+        <v>726</v>
       </c>
       <c r="I23" t="n">
-        <v>52111</v>
+        <v>53800</v>
       </c>
       <c r="J23" t="n">
-        <v>53323.5</v>
+        <v>53892.5</v>
       </c>
       <c r="K23" t="n">
-        <v>53690</v>
+        <v>54223</v>
       </c>
       <c r="L23" t="n">
-        <v>54056.5</v>
+        <v>54553.5</v>
       </c>
       <c r="M23" t="n">
-        <v>54846</v>
+        <v>54765</v>
       </c>
       <c r="N23" t="n">
-        <v>55635.5</v>
+        <v>54976.5</v>
       </c>
       <c r="O23" t="n">
-        <v>55579</v>
+        <v>55426</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
+      <c r="Q23" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
@@ -2479,72 +2475,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>54555</v>
+        <v>54040</v>
       </c>
       <c r="C24" t="n">
-        <v>54678</v>
+        <v>54202</v>
       </c>
       <c r="D24" t="n">
-        <v>53952</v>
+        <v>53879</v>
       </c>
       <c r="E24" t="n">
-        <v>54013</v>
+        <v>54152</v>
       </c>
       <c r="F24" t="n">
-        <v>-481</v>
+        <v>139</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0026</v>
       </c>
       <c r="H24" t="n">
-        <v>726</v>
+        <v>323</v>
       </c>
       <c r="I24" t="n">
-        <v>53800</v>
+        <v>53226</v>
       </c>
       <c r="J24" t="n">
-        <v>53892.5</v>
+        <v>53136</v>
       </c>
       <c r="K24" t="n">
-        <v>54223</v>
+        <v>53650</v>
       </c>
       <c r="L24" t="n">
-        <v>54553.5</v>
+        <v>54164</v>
       </c>
       <c r="M24" t="n">
-        <v>54765</v>
+        <v>54376</v>
       </c>
       <c r="N24" t="n">
-        <v>54976.5</v>
+        <v>54588</v>
       </c>
       <c r="O24" t="n">
-        <v>55426</v>
+        <v>55404</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2563,57 +2559,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>54040</v>
+        <v>54133</v>
       </c>
       <c r="C25" t="n">
-        <v>54202</v>
+        <v>54170</v>
       </c>
       <c r="D25" t="n">
-        <v>53879</v>
+        <v>53952</v>
       </c>
       <c r="E25" t="n">
-        <v>54152</v>
+        <v>54063</v>
       </c>
       <c r="F25" t="n">
-        <v>139</v>
+        <v>-89</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0016</v>
       </c>
       <c r="H25" t="n">
-        <v>323</v>
+        <v>218</v>
       </c>
       <c r="I25" t="n">
-        <v>53226</v>
+        <v>53556</v>
       </c>
       <c r="J25" t="n">
-        <v>53136</v>
+        <v>53884.75</v>
       </c>
       <c r="K25" t="n">
-        <v>53650</v>
+        <v>53990.5</v>
       </c>
       <c r="L25" t="n">
-        <v>54164</v>
+        <v>54096.25</v>
       </c>
       <c r="M25" t="n">
-        <v>54376</v>
+        <v>54313.5</v>
       </c>
       <c r="N25" t="n">
-        <v>54588</v>
+        <v>54530.75</v>
       </c>
       <c r="O25" t="n">
-        <v>55404</v>
+        <v>54525</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2621,8 +2617,10 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
@@ -2652,56 +2650,58 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>54133</v>
+        <v>54049</v>
       </c>
       <c r="C26" t="n">
-        <v>54170</v>
+        <v>54336</v>
       </c>
       <c r="D26" t="n">
-        <v>53952</v>
+        <v>53855</v>
       </c>
       <c r="E26" t="n">
-        <v>54063</v>
+        <v>53880</v>
       </c>
       <c r="F26" t="n">
-        <v>-89</v>
+        <v>-183</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0034</v>
       </c>
       <c r="H26" t="n">
-        <v>218</v>
+        <v>481</v>
       </c>
       <c r="I26" t="n">
-        <v>53556</v>
+        <v>53734</v>
       </c>
       <c r="J26" t="n">
-        <v>53884.75</v>
+        <v>53846</v>
       </c>
       <c r="K26" t="n">
-        <v>53990.5</v>
+        <v>53954</v>
       </c>
       <c r="L26" t="n">
-        <v>54096.25</v>
+        <v>54062</v>
       </c>
       <c r="M26" t="n">
-        <v>54313.5</v>
+        <v>54172</v>
       </c>
       <c r="N26" t="n">
-        <v>54530.75</v>
+        <v>54282</v>
       </c>
       <c r="O26" t="n">
-        <v>54525</v>
+        <v>54388</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
@@ -2710,14 +2710,18 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2736,78 +2740,72 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>54049</v>
+        <v>53903</v>
       </c>
       <c r="C27" t="n">
-        <v>54336</v>
+        <v>54150</v>
       </c>
       <c r="D27" t="n">
-        <v>53855</v>
+        <v>53830</v>
       </c>
       <c r="E27" t="n">
-        <v>53880</v>
+        <v>53871</v>
       </c>
       <c r="F27" t="n">
-        <v>-183</v>
+        <v>-9</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0002</v>
       </c>
       <c r="H27" t="n">
-        <v>481</v>
+        <v>320</v>
       </c>
       <c r="I27" t="n">
-        <v>53734</v>
+        <v>53374</v>
       </c>
       <c r="J27" t="n">
-        <v>53846</v>
+        <v>53291.25</v>
       </c>
       <c r="K27" t="n">
-        <v>53954</v>
+        <v>53639.5</v>
       </c>
       <c r="L27" t="n">
-        <v>54062</v>
+        <v>53987.75</v>
       </c>
       <c r="M27" t="n">
-        <v>54172</v>
+        <v>54120.5</v>
       </c>
       <c r="N27" t="n">
-        <v>54282</v>
+        <v>54253.25</v>
       </c>
       <c r="O27" t="n">
-        <v>54388</v>
+        <v>54817</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2819,57 +2817,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>53903</v>
+        <v>53905</v>
       </c>
       <c r="C28" t="n">
-        <v>54150</v>
+        <v>54149</v>
       </c>
       <c r="D28" t="n">
-        <v>53830</v>
+        <v>53715</v>
       </c>
       <c r="E28" t="n">
-        <v>53871</v>
+        <v>53935</v>
       </c>
       <c r="F28" t="n">
-        <v>-9</v>
+        <v>64</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0012</v>
       </c>
       <c r="H28" t="n">
-        <v>320</v>
+        <v>434</v>
       </c>
       <c r="I28" t="n">
-        <v>53374</v>
+        <v>53510</v>
       </c>
       <c r="J28" t="n">
-        <v>53291.25</v>
+        <v>53491.5</v>
       </c>
       <c r="K28" t="n">
-        <v>53639.5</v>
+        <v>53711</v>
       </c>
       <c r="L28" t="n">
-        <v>53987.75</v>
+        <v>53930.5</v>
       </c>
       <c r="M28" t="n">
-        <v>54120.5</v>
+        <v>54031</v>
       </c>
       <c r="N28" t="n">
-        <v>54253.25</v>
+        <v>54131.5</v>
       </c>
       <c r="O28" t="n">
-        <v>54817</v>
+        <v>54470</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2880,9 +2878,9 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
@@ -2890,8 +2888,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U28" s="8" t="n">
-        <v/>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2903,57 +2903,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>53905</v>
+        <v>53961</v>
       </c>
       <c r="C29" t="n">
-        <v>54149</v>
+        <v>53999</v>
       </c>
       <c r="D29" t="n">
-        <v>53715</v>
+        <v>53745</v>
       </c>
       <c r="E29" t="n">
-        <v>53935</v>
+        <v>53807</v>
       </c>
       <c r="F29" t="n">
-        <v>64</v>
+        <v>-128</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0024</v>
       </c>
       <c r="H29" t="n">
-        <v>434</v>
+        <v>254</v>
       </c>
       <c r="I29" t="n">
-        <v>53510</v>
+        <v>53281</v>
       </c>
       <c r="J29" t="n">
-        <v>53491.5</v>
+        <v>53502.5</v>
       </c>
       <c r="K29" t="n">
-        <v>53711</v>
+        <v>53718</v>
       </c>
       <c r="L29" t="n">
-        <v>53930.5</v>
+        <v>53933.5</v>
       </c>
       <c r="M29" t="n">
-        <v>54031</v>
+        <v>54152</v>
       </c>
       <c r="N29" t="n">
-        <v>54131.5</v>
+        <v>54370.5</v>
       </c>
       <c r="O29" t="n">
-        <v>54470</v>
+        <v>54583</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2961,23 +2961,21 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2996,60 +2994,64 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>53961</v>
+        <v>53790</v>
       </c>
       <c r="C30" t="n">
-        <v>53999</v>
+        <v>53840</v>
       </c>
       <c r="D30" t="n">
-        <v>53745</v>
+        <v>53464</v>
       </c>
       <c r="E30" t="n">
-        <v>53807</v>
+        <v>53544</v>
       </c>
       <c r="F30" t="n">
-        <v>-128</v>
+        <v>-263</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0049</v>
       </c>
       <c r="H30" t="n">
-        <v>254</v>
+        <v>376</v>
       </c>
       <c r="I30" t="n">
-        <v>53281</v>
+        <v>53491</v>
       </c>
       <c r="J30" t="n">
-        <v>53502.5</v>
+        <v>53520.5</v>
       </c>
       <c r="K30" t="n">
-        <v>53718</v>
+        <v>53680</v>
       </c>
       <c r="L30" t="n">
-        <v>53933.5</v>
+        <v>53839.5</v>
       </c>
       <c r="M30" t="n">
-        <v>54152</v>
+        <v>53934</v>
       </c>
       <c r="N30" t="n">
-        <v>54370.5</v>
+        <v>54028.5</v>
       </c>
       <c r="O30" t="n">
-        <v>54583</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
+        <v>54253</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S30" s="7" t="inlineStr">
@@ -3073,71 +3075,67 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>53790</v>
+        <v>53501</v>
       </c>
       <c r="C31" t="n">
-        <v>53840</v>
+        <v>53594</v>
       </c>
       <c r="D31" t="n">
-        <v>53464</v>
+        <v>53311</v>
       </c>
       <c r="E31" t="n">
-        <v>53544</v>
+        <v>53403</v>
       </c>
       <c r="F31" t="n">
-        <v>-263</v>
+        <v>-141</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0026</v>
       </c>
       <c r="H31" t="n">
-        <v>376</v>
+        <v>283</v>
       </c>
       <c r="I31" t="n">
-        <v>53491</v>
+        <v>53088</v>
       </c>
       <c r="J31" t="n">
-        <v>53520.5</v>
+        <v>53114</v>
       </c>
       <c r="K31" t="n">
-        <v>53680</v>
+        <v>53356</v>
       </c>
       <c r="L31" t="n">
-        <v>53839.5</v>
+        <v>53598</v>
       </c>
       <c r="M31" t="n">
-        <v>53934</v>
+        <v>53732</v>
       </c>
       <c r="N31" t="n">
-        <v>54028.5</v>
+        <v>53866</v>
       </c>
       <c r="O31" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q31" s="6" t="inlineStr">
+        <v>54216</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S31" s="7" t="inlineStr">
@@ -3168,50 +3166,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>53501</v>
+        <v>53408</v>
       </c>
       <c r="C32" t="n">
-        <v>53594</v>
+        <v>53780</v>
       </c>
       <c r="D32" t="n">
-        <v>53311</v>
+        <v>53337</v>
       </c>
       <c r="E32" t="n">
-        <v>53403</v>
+        <v>53530</v>
       </c>
       <c r="F32" t="n">
-        <v>-141</v>
+        <v>127</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0026</v>
+        <v>0.0024</v>
       </c>
       <c r="H32" t="n">
-        <v>283</v>
+        <v>443</v>
       </c>
       <c r="I32" t="n">
-        <v>53088</v>
+        <v>53028</v>
       </c>
       <c r="J32" t="n">
-        <v>53114</v>
+        <v>53095.25</v>
       </c>
       <c r="K32" t="n">
-        <v>53356</v>
+        <v>53261.5</v>
       </c>
       <c r="L32" t="n">
-        <v>53598</v>
+        <v>53427.75</v>
       </c>
       <c r="M32" t="n">
-        <v>53732</v>
+        <v>53544.5</v>
       </c>
       <c r="N32" t="n">
-        <v>53866</v>
+        <v>53661.25</v>
       </c>
       <c r="O32" t="n">
-        <v>54216</v>
+        <v>53877</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3219,21 +3217,23 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3243,90 +3243,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>53408</v>
+        <v>53529</v>
       </c>
       <c r="C33" t="n">
-        <v>53780</v>
+        <v>53589</v>
       </c>
       <c r="D33" t="n">
-        <v>53337</v>
+        <v>52812</v>
       </c>
       <c r="E33" t="n">
-        <v>53530</v>
+        <v>52849</v>
       </c>
       <c r="F33" t="n">
-        <v>127</v>
+        <v>-681</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0127</v>
       </c>
       <c r="H33" t="n">
-        <v>443</v>
+        <v>777</v>
       </c>
       <c r="I33" t="n">
-        <v>53028</v>
+        <v>52894</v>
       </c>
       <c r="J33" t="n">
-        <v>53095.25</v>
+        <v>53072.75</v>
       </c>
       <c r="K33" t="n">
-        <v>53261.5</v>
+        <v>53308.5</v>
       </c>
       <c r="L33" t="n">
-        <v>53427.75</v>
+        <v>53544.25</v>
       </c>
       <c r="M33" t="n">
-        <v>53544.5</v>
+        <v>53751.5</v>
       </c>
       <c r="N33" t="n">
-        <v>53661.25</v>
+        <v>53958.75</v>
       </c>
       <c r="O33" t="n">
-        <v>53877</v>
-      </c>
-      <c r="P33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
+        <v>54223</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U33" s="8" t="inlineStr">
+      <c r="Q33" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W33" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X33" t="inlineStr"/>
@@ -3334,77 +3332,75 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>53529</v>
+        <v>52876</v>
       </c>
       <c r="C34" t="n">
-        <v>53589</v>
+        <v>53418</v>
       </c>
       <c r="D34" t="n">
-        <v>52812</v>
+        <v>52838</v>
       </c>
       <c r="E34" t="n">
-        <v>52849</v>
+        <v>53353</v>
       </c>
       <c r="F34" t="n">
-        <v>-681</v>
+        <v>504</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0095</v>
       </c>
       <c r="H34" t="n">
-        <v>777</v>
+        <v>580</v>
       </c>
       <c r="I34" t="n">
-        <v>52894</v>
+        <v>52035</v>
       </c>
       <c r="J34" t="n">
-        <v>53072.75</v>
+        <v>51896.25</v>
       </c>
       <c r="K34" t="n">
-        <v>53308.5</v>
+        <v>52460.5</v>
       </c>
       <c r="L34" t="n">
-        <v>53544.25</v>
+        <v>53024.75</v>
       </c>
       <c r="M34" t="n">
-        <v>53751.5</v>
+        <v>53237.5</v>
       </c>
       <c r="N34" t="n">
-        <v>53958.75</v>
+        <v>53450.25</v>
       </c>
       <c r="O34" t="n">
-        <v>54223</v>
-      </c>
-      <c r="P34" s="6" t="inlineStr">
+        <v>54366</v>
+      </c>
+      <c r="P34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
@@ -3413,55 +3409,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>52876</v>
+        <v>53367</v>
       </c>
       <c r="C35" t="n">
-        <v>53418</v>
+        <v>53567</v>
       </c>
       <c r="D35" t="n">
-        <v>52838</v>
+        <v>53210</v>
       </c>
       <c r="E35" t="n">
-        <v>53353</v>
+        <v>53489</v>
       </c>
       <c r="F35" t="n">
-        <v>504</v>
+        <v>136</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.0025</v>
       </c>
       <c r="H35" t="n">
-        <v>580</v>
+        <v>357</v>
       </c>
       <c r="I35" t="n">
-        <v>52035</v>
+        <v>52258</v>
       </c>
       <c r="J35" t="n">
-        <v>51896.25</v>
+        <v>52885.5</v>
       </c>
       <c r="K35" t="n">
-        <v>52460.5</v>
+        <v>53063</v>
       </c>
       <c r="L35" t="n">
-        <v>53024.75</v>
+        <v>53240.5</v>
       </c>
       <c r="M35" t="n">
-        <v>53237.5</v>
+        <v>53643</v>
       </c>
       <c r="N35" t="n">
-        <v>53450.25</v>
+        <v>54045.5</v>
       </c>
       <c r="O35" t="n">
-        <v>54366</v>
+        <v>53998</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3479,14 +3479,12 @@
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
@@ -3497,57 +3495,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>53367</v>
+        <v>53524</v>
       </c>
       <c r="C36" t="n">
-        <v>53567</v>
+        <v>53797</v>
       </c>
       <c r="D36" t="n">
-        <v>53210</v>
+        <v>53426</v>
       </c>
       <c r="E36" t="n">
-        <v>53489</v>
+        <v>53645</v>
       </c>
       <c r="F36" t="n">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0029</v>
       </c>
       <c r="H36" t="n">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="I36" t="n">
-        <v>52258</v>
+        <v>52853</v>
       </c>
       <c r="J36" t="n">
-        <v>52885.5</v>
+        <v>53182.25</v>
       </c>
       <c r="K36" t="n">
-        <v>53063</v>
+        <v>53310.5</v>
       </c>
       <c r="L36" t="n">
-        <v>53240.5</v>
+        <v>53438.75</v>
       </c>
       <c r="M36" t="n">
-        <v>53643</v>
+        <v>53667.5</v>
       </c>
       <c r="N36" t="n">
-        <v>54045.5</v>
+        <v>53896.25</v>
       </c>
       <c r="O36" t="n">
-        <v>53998</v>
+        <v>53924</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3588,50 +3586,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>53524</v>
+        <v>53643</v>
       </c>
       <c r="C37" t="n">
-        <v>53797</v>
+        <v>53778</v>
       </c>
       <c r="D37" t="n">
-        <v>53426</v>
+        <v>53435</v>
       </c>
       <c r="E37" t="n">
-        <v>53645</v>
+        <v>53521</v>
       </c>
       <c r="F37" t="n">
-        <v>156</v>
+        <v>-124</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0023</v>
       </c>
       <c r="H37" t="n">
-        <v>371</v>
+        <v>343</v>
       </c>
       <c r="I37" t="n">
-        <v>52853</v>
+        <v>53055</v>
       </c>
       <c r="J37" t="n">
-        <v>53182.25</v>
+        <v>53290.75</v>
       </c>
       <c r="K37" t="n">
-        <v>53310.5</v>
+        <v>53459.5</v>
       </c>
       <c r="L37" t="n">
-        <v>53438.75</v>
+        <v>53628.25</v>
       </c>
       <c r="M37" t="n">
-        <v>53667.5</v>
+        <v>53830.5</v>
       </c>
       <c r="N37" t="n">
-        <v>53896.25</v>
+        <v>54032.75</v>
       </c>
       <c r="O37" t="n">
-        <v>53924</v>
+        <v>54168</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3639,19 +3637,19 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
@@ -3665,57 +3663,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>53643</v>
+        <v>53724</v>
       </c>
       <c r="C38" t="n">
-        <v>53778</v>
+        <v>53811</v>
       </c>
       <c r="D38" t="n">
-        <v>53435</v>
+        <v>53369</v>
       </c>
       <c r="E38" t="n">
-        <v>53521</v>
+        <v>53621</v>
       </c>
       <c r="F38" t="n">
-        <v>-124</v>
+        <v>100</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0019</v>
       </c>
       <c r="H38" t="n">
-        <v>343</v>
+        <v>442</v>
       </c>
       <c r="I38" t="n">
-        <v>53055</v>
+        <v>53092</v>
       </c>
       <c r="J38" t="n">
-        <v>53290.75</v>
+        <v>53135.25</v>
       </c>
       <c r="K38" t="n">
-        <v>53459.5</v>
+        <v>53349.5</v>
       </c>
       <c r="L38" t="n">
-        <v>53628.25</v>
+        <v>53563.75</v>
       </c>
       <c r="M38" t="n">
-        <v>53830.5</v>
+        <v>53692.5</v>
       </c>
       <c r="N38" t="n">
-        <v>54032.75</v>
+        <v>53821.25</v>
       </c>
       <c r="O38" t="n">
-        <v>54168</v>
+        <v>54121</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3723,18 +3721,18 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3749,57 +3747,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>53724</v>
+        <v>53608</v>
       </c>
       <c r="C39" t="n">
-        <v>53811</v>
+        <v>53862</v>
       </c>
       <c r="D39" t="n">
-        <v>53369</v>
+        <v>53513</v>
       </c>
       <c r="E39" t="n">
-        <v>53621</v>
+        <v>53584</v>
       </c>
       <c r="F39" t="n">
-        <v>100</v>
+        <v>-37</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0007</v>
       </c>
       <c r="H39" t="n">
-        <v>442</v>
+        <v>349</v>
       </c>
       <c r="I39" t="n">
-        <v>53092</v>
+        <v>52927</v>
       </c>
       <c r="J39" t="n">
-        <v>53135.25</v>
+        <v>53194.5</v>
       </c>
       <c r="K39" t="n">
-        <v>53349.5</v>
+        <v>53400</v>
       </c>
       <c r="L39" t="n">
-        <v>53563.75</v>
+        <v>53605.5</v>
       </c>
       <c r="M39" t="n">
-        <v>53692.5</v>
+        <v>53842</v>
       </c>
       <c r="N39" t="n">
-        <v>53821.25</v>
+        <v>54078.5</v>
       </c>
       <c r="O39" t="n">
-        <v>54121</v>
+        <v>54253</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3810,9 +3808,9 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
@@ -3840,69 +3838,73 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>53608</v>
+        <v>53664</v>
       </c>
       <c r="C40" t="n">
-        <v>53862</v>
+        <v>53664</v>
       </c>
       <c r="D40" t="n">
-        <v>53513</v>
+        <v>53149</v>
       </c>
       <c r="E40" t="n">
-        <v>53584</v>
+        <v>53240</v>
       </c>
       <c r="F40" t="n">
-        <v>-37</v>
+        <v>-344</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0064</v>
       </c>
       <c r="H40" t="n">
-        <v>349</v>
+        <v>515</v>
       </c>
       <c r="I40" t="n">
-        <v>52927</v>
+        <v>53164</v>
       </c>
       <c r="J40" t="n">
-        <v>53194.5</v>
+        <v>53183.25</v>
       </c>
       <c r="K40" t="n">
-        <v>53400</v>
+        <v>53409.5</v>
       </c>
       <c r="L40" t="n">
-        <v>53605.5</v>
+        <v>53635.75</v>
       </c>
       <c r="M40" t="n">
-        <v>53842</v>
+        <v>53758.5</v>
       </c>
       <c r="N40" t="n">
-        <v>54078.5</v>
+        <v>53881.25</v>
       </c>
       <c r="O40" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+        <v>54211</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3915,73 +3917,65 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>53664</v>
+        <v>53259</v>
       </c>
       <c r="C41" t="n">
-        <v>53664</v>
+        <v>53343</v>
       </c>
       <c r="D41" t="n">
-        <v>53149</v>
+        <v>52747</v>
       </c>
       <c r="E41" t="n">
-        <v>53240</v>
+        <v>52828</v>
       </c>
       <c r="F41" t="n">
-        <v>-344</v>
+        <v>-412</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0064</v>
+        <v>-0.0077</v>
       </c>
       <c r="H41" t="n">
-        <v>515</v>
+        <v>596</v>
       </c>
       <c r="I41" t="n">
-        <v>53164</v>
+        <v>52634</v>
       </c>
       <c r="J41" t="n">
-        <v>53183.25</v>
+        <v>52641.75</v>
       </c>
       <c r="K41" t="n">
-        <v>53409.5</v>
+        <v>52982.5</v>
       </c>
       <c r="L41" t="n">
-        <v>53635.75</v>
+        <v>53323.25</v>
       </c>
       <c r="M41" t="n">
-        <v>53758.5</v>
+        <v>53497.5</v>
       </c>
       <c r="N41" t="n">
-        <v>53881.25</v>
+        <v>53671.75</v>
       </c>
       <c r="O41" t="n">
-        <v>54211</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
+        <v>54179</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S41" s="7" t="inlineStr">
@@ -4008,50 +4002,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>53259</v>
+        <v>52844</v>
       </c>
       <c r="C42" t="n">
-        <v>53343</v>
+        <v>53283</v>
       </c>
       <c r="D42" t="n">
-        <v>52747</v>
+        <v>52720</v>
       </c>
       <c r="E42" t="n">
-        <v>52828</v>
+        <v>53121</v>
       </c>
       <c r="F42" t="n">
-        <v>-412</v>
+        <v>293</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0077</v>
+        <v>0.0055</v>
       </c>
       <c r="H42" t="n">
-        <v>596</v>
+        <v>563</v>
       </c>
       <c r="I42" t="n">
-        <v>52634</v>
+        <v>52151</v>
       </c>
       <c r="J42" t="n">
-        <v>52641.75</v>
+        <v>52123.5</v>
       </c>
       <c r="K42" t="n">
-        <v>52982.5</v>
+        <v>52530</v>
       </c>
       <c r="L42" t="n">
-        <v>53323.25</v>
+        <v>52936.5</v>
       </c>
       <c r="M42" t="n">
-        <v>53497.5</v>
+        <v>53126</v>
       </c>
       <c r="N42" t="n">
-        <v>53671.75</v>
+        <v>53315.5</v>
       </c>
       <c r="O42" t="n">
-        <v>54179</v>
+        <v>53939</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4059,19 +4053,19 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4083,55 +4077,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>52844</v>
+        <v>53120</v>
       </c>
       <c r="C43" t="n">
-        <v>53283</v>
+        <v>53827</v>
       </c>
       <c r="D43" t="n">
-        <v>52720</v>
+        <v>53093</v>
       </c>
       <c r="E43" t="n">
-        <v>53121</v>
+        <v>53745</v>
       </c>
       <c r="F43" t="n">
-        <v>293</v>
+        <v>624</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0117</v>
       </c>
       <c r="H43" t="n">
-        <v>563</v>
+        <v>734</v>
       </c>
       <c r="I43" t="n">
-        <v>52151</v>
+        <v>52157</v>
       </c>
       <c r="J43" t="n">
-        <v>52123.5</v>
+        <v>52617.75</v>
       </c>
       <c r="K43" t="n">
-        <v>52530</v>
+        <v>52839.5</v>
       </c>
       <c r="L43" t="n">
-        <v>52936.5</v>
+        <v>53061.25</v>
       </c>
       <c r="M43" t="n">
-        <v>53126</v>
+        <v>53402.5</v>
       </c>
       <c r="N43" t="n">
-        <v>53315.5</v>
+        <v>53743.75</v>
       </c>
       <c r="O43" t="n">
-        <v>53939</v>
+        <v>53846</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4149,73 +4147,71 @@
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W43" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>53120</v>
+        <v>53707</v>
       </c>
       <c r="C44" t="n">
-        <v>53827</v>
+        <v>53772</v>
       </c>
       <c r="D44" t="n">
-        <v>53093</v>
+        <v>53235</v>
       </c>
       <c r="E44" t="n">
-        <v>53745</v>
+        <v>53440</v>
       </c>
       <c r="F44" t="n">
-        <v>624</v>
+        <v>-305</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0117</v>
+        <v>-0.0057</v>
       </c>
       <c r="H44" t="n">
-        <v>734</v>
+        <v>537</v>
       </c>
       <c r="I44" t="n">
-        <v>52157</v>
+        <v>52359</v>
       </c>
       <c r="J44" t="n">
-        <v>52617.75</v>
+        <v>53153.5</v>
       </c>
       <c r="K44" t="n">
-        <v>52839.5</v>
+        <v>53378</v>
       </c>
       <c r="L44" t="n">
-        <v>53061.25</v>
+        <v>53602.5</v>
       </c>
       <c r="M44" t="n">
-        <v>53402.5</v>
+        <v>54112</v>
       </c>
       <c r="N44" t="n">
-        <v>53743.75</v>
+        <v>54621.5</v>
       </c>
       <c r="O44" t="n">
-        <v>53846</v>
+        <v>54561</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4223,24 +4219,22 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
@@ -4249,65 +4243,71 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>53707</v>
+        <v>53261</v>
       </c>
       <c r="C45" t="n">
-        <v>53772</v>
+        <v>53336</v>
       </c>
       <c r="D45" t="n">
-        <v>53235</v>
+        <v>52758</v>
       </c>
       <c r="E45" t="n">
-        <v>53440</v>
+        <v>52832</v>
       </c>
       <c r="F45" t="n">
-        <v>-305</v>
+        <v>-608</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0057</v>
+        <v>-0.0114</v>
       </c>
       <c r="H45" t="n">
-        <v>537</v>
+        <v>578</v>
       </c>
       <c r="I45" t="n">
-        <v>52359</v>
+        <v>52698</v>
       </c>
       <c r="J45" t="n">
-        <v>53153.5</v>
+        <v>52871.25</v>
       </c>
       <c r="K45" t="n">
-        <v>53378</v>
+        <v>53171.5</v>
       </c>
       <c r="L45" t="n">
-        <v>53602.5</v>
+        <v>53471.75</v>
       </c>
       <c r="M45" t="n">
-        <v>54112</v>
+        <v>53708.5</v>
       </c>
       <c r="N45" t="n">
-        <v>54621.5</v>
+        <v>53945.25</v>
       </c>
       <c r="O45" t="n">
-        <v>54561</v>
+        <v>54309</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
@@ -4324,76 +4324,70 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W45" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>53261</v>
+        <v>52817</v>
       </c>
       <c r="C46" t="n">
-        <v>53336</v>
+        <v>52859</v>
       </c>
       <c r="D46" t="n">
-        <v>52758</v>
+        <v>52339</v>
       </c>
       <c r="E46" t="n">
-        <v>52832</v>
+        <v>52425</v>
       </c>
       <c r="F46" t="n">
-        <v>-608</v>
+        <v>-407</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0114</v>
+        <v>-0.0077</v>
       </c>
       <c r="H46" t="n">
-        <v>578</v>
+        <v>520</v>
       </c>
       <c r="I46" t="n">
-        <v>52698</v>
+        <v>52180</v>
       </c>
       <c r="J46" t="n">
-        <v>52871.25</v>
+        <v>52146.5</v>
       </c>
       <c r="K46" t="n">
-        <v>53171.5</v>
+        <v>52543</v>
       </c>
       <c r="L46" t="n">
-        <v>53471.75</v>
+        <v>52939.5</v>
       </c>
       <c r="M46" t="n">
-        <v>53708.5</v>
+        <v>53121</v>
       </c>
       <c r="N46" t="n">
-        <v>53945.25</v>
+        <v>53302.5</v>
       </c>
       <c r="O46" t="n">
-        <v>54309</v>
+        <v>53914</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
@@ -4420,50 +4414,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>52817</v>
+        <v>52473</v>
       </c>
       <c r="C47" t="n">
-        <v>52859</v>
+        <v>52676</v>
       </c>
       <c r="D47" t="n">
-        <v>52339</v>
+        <v>51992</v>
       </c>
       <c r="E47" t="n">
-        <v>52425</v>
+        <v>52095</v>
       </c>
       <c r="F47" t="n">
-        <v>-407</v>
+        <v>-330</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0077</v>
+        <v>-0.0063</v>
       </c>
       <c r="H47" t="n">
-        <v>520</v>
+        <v>684</v>
       </c>
       <c r="I47" t="n">
-        <v>52180</v>
+        <v>51819</v>
       </c>
       <c r="J47" t="n">
-        <v>52146.5</v>
+        <v>51818</v>
       </c>
       <c r="K47" t="n">
-        <v>52543</v>
+        <v>52165</v>
       </c>
       <c r="L47" t="n">
-        <v>52939.5</v>
+        <v>52512</v>
       </c>
       <c r="M47" t="n">
-        <v>53121</v>
+        <v>52685</v>
       </c>
       <c r="N47" t="n">
-        <v>53302.5</v>
+        <v>52858</v>
       </c>
       <c r="O47" t="n">
-        <v>53914</v>
+        <v>53379</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4500,50 +4494,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>52473</v>
+        <v>52059</v>
       </c>
       <c r="C48" t="n">
-        <v>52676</v>
+        <v>52739</v>
       </c>
       <c r="D48" t="n">
-        <v>51992</v>
+        <v>52059</v>
       </c>
       <c r="E48" t="n">
-        <v>52095</v>
+        <v>52585</v>
       </c>
       <c r="F48" t="n">
-        <v>-330</v>
+        <v>490</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0063</v>
+        <v>0.0094</v>
       </c>
       <c r="H48" t="n">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="I48" t="n">
-        <v>51819</v>
+        <v>51308</v>
       </c>
       <c r="J48" t="n">
-        <v>51818</v>
+        <v>51291.5</v>
       </c>
       <c r="K48" t="n">
-        <v>52165</v>
+        <v>51753</v>
       </c>
       <c r="L48" t="n">
-        <v>52512</v>
+        <v>52214.5</v>
       </c>
       <c r="M48" t="n">
-        <v>52685</v>
+        <v>52437</v>
       </c>
       <c r="N48" t="n">
-        <v>52858</v>
+        <v>52659.5</v>
       </c>
       <c r="O48" t="n">
-        <v>53379</v>
+        <v>53360</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4551,22 +4545,24 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
@@ -4575,55 +4571,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>52059</v>
+        <v>52376</v>
       </c>
       <c r="C49" t="n">
-        <v>52739</v>
+        <v>52672</v>
       </c>
       <c r="D49" t="n">
-        <v>52059</v>
+        <v>52226</v>
       </c>
       <c r="E49" t="n">
-        <v>52585</v>
+        <v>52440</v>
       </c>
       <c r="F49" t="n">
-        <v>490</v>
+        <v>-145</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0094</v>
+        <v>-0.0028</v>
       </c>
       <c r="H49" t="n">
-        <v>680</v>
+        <v>446</v>
       </c>
       <c r="I49" t="n">
-        <v>51308</v>
+        <v>51379</v>
       </c>
       <c r="J49" t="n">
-        <v>51291.5</v>
+        <v>51998</v>
       </c>
       <c r="K49" t="n">
-        <v>51753</v>
+        <v>52245</v>
       </c>
       <c r="L49" t="n">
-        <v>52214.5</v>
+        <v>52492</v>
       </c>
       <c r="M49" t="n">
-        <v>52437</v>
+        <v>52925</v>
       </c>
       <c r="N49" t="n">
-        <v>52659.5</v>
+        <v>53358</v>
       </c>
       <c r="O49" t="n">
-        <v>53360</v>
+        <v>53419</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4631,23 +4631,21 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4659,72 +4657,74 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>52376</v>
+        <v>52499</v>
       </c>
       <c r="C50" t="n">
-        <v>52672</v>
+        <v>52499</v>
       </c>
       <c r="D50" t="n">
-        <v>52226</v>
+        <v>51908</v>
       </c>
       <c r="E50" t="n">
-        <v>52440</v>
+        <v>52115</v>
       </c>
       <c r="F50" t="n">
-        <v>-145</v>
+        <v>-325</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0028</v>
+        <v>-0.0062</v>
       </c>
       <c r="H50" t="n">
-        <v>446</v>
+        <v>591</v>
       </c>
       <c r="I50" t="n">
-        <v>51379</v>
+        <v>51780</v>
       </c>
       <c r="J50" t="n">
-        <v>51998</v>
+        <v>51989.5</v>
       </c>
       <c r="K50" t="n">
-        <v>52245</v>
+        <v>52217</v>
       </c>
       <c r="L50" t="n">
-        <v>52492</v>
+        <v>52444.5</v>
       </c>
       <c r="M50" t="n">
-        <v>52925</v>
+        <v>52663</v>
       </c>
       <c r="N50" t="n">
-        <v>53358</v>
+        <v>52881.5</v>
       </c>
       <c r="O50" t="n">
-        <v>53419</v>
+        <v>53118</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4741,71 +4741,69 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>52499</v>
+        <v>52162</v>
       </c>
       <c r="C51" t="n">
-        <v>52499</v>
+        <v>52298</v>
       </c>
       <c r="D51" t="n">
-        <v>51908</v>
+        <v>51209</v>
       </c>
       <c r="E51" t="n">
-        <v>52115</v>
+        <v>51507</v>
       </c>
       <c r="F51" t="n">
-        <v>-325</v>
+        <v>-608</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0062</v>
+        <v>-0.0117</v>
       </c>
       <c r="H51" t="n">
-        <v>591</v>
+        <v>1089</v>
       </c>
       <c r="I51" t="n">
-        <v>51780</v>
+        <v>51317</v>
       </c>
       <c r="J51" t="n">
-        <v>51989.5</v>
+        <v>51479.75</v>
       </c>
       <c r="K51" t="n">
-        <v>52217</v>
+        <v>51819.5</v>
       </c>
       <c r="L51" t="n">
-        <v>52444.5</v>
+        <v>52159.25</v>
       </c>
       <c r="M51" t="n">
-        <v>52663</v>
+        <v>52410.5</v>
       </c>
       <c r="N51" t="n">
-        <v>52881.5</v>
+        <v>52661.75</v>
       </c>
       <c r="O51" t="n">
-        <v>53118</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v/>
+        <v>53090</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q51" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
         </is>
       </c>
       <c r="S51" s="7" t="inlineStr">
@@ -4832,74 +4830,70 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>52162</v>
+        <v>51486</v>
       </c>
       <c r="C52" t="n">
-        <v>52298</v>
+        <v>52169</v>
       </c>
       <c r="D52" t="n">
-        <v>51209</v>
+        <v>51455</v>
       </c>
       <c r="E52" t="n">
-        <v>51507</v>
+        <v>51807</v>
       </c>
       <c r="F52" t="n">
-        <v>-608</v>
+        <v>300</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0117</v>
+        <v>0.0058</v>
       </c>
       <c r="H52" t="n">
-        <v>1089</v>
+        <v>714</v>
       </c>
       <c r="I52" t="n">
-        <v>51317</v>
+        <v>50120</v>
       </c>
       <c r="J52" t="n">
-        <v>51479.75</v>
+        <v>50294.75</v>
       </c>
       <c r="K52" t="n">
-        <v>51819.5</v>
+        <v>50962.5</v>
       </c>
       <c r="L52" t="n">
-        <v>52159.25</v>
+        <v>51630.25</v>
       </c>
       <c r="M52" t="n">
-        <v>52410.5</v>
+        <v>52051.5</v>
       </c>
       <c r="N52" t="n">
-        <v>52661.75</v>
+        <v>52472.75</v>
       </c>
       <c r="O52" t="n">
-        <v>53090</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
+        <v>53387</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
       <c r="U52" s="8" t="n">
         <v/>
       </c>
@@ -4911,55 +4905,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>51486</v>
+        <v>51800</v>
       </c>
       <c r="C53" t="n">
-        <v>52169</v>
+        <v>51957</v>
       </c>
       <c r="D53" t="n">
-        <v>51455</v>
+        <v>51576</v>
       </c>
       <c r="E53" t="n">
-        <v>51807</v>
+        <v>51761</v>
       </c>
       <c r="F53" t="n">
-        <v>300</v>
+        <v>-46</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0009</v>
       </c>
       <c r="H53" t="n">
-        <v>714</v>
+        <v>381</v>
       </c>
       <c r="I53" t="n">
-        <v>50120</v>
+        <v>50741</v>
       </c>
       <c r="J53" t="n">
-        <v>50294.75</v>
+        <v>51090.5</v>
       </c>
       <c r="K53" t="n">
-        <v>50962.5</v>
+        <v>51450</v>
       </c>
       <c r="L53" t="n">
-        <v>51630.25</v>
+        <v>51809.5</v>
       </c>
       <c r="M53" t="n">
-        <v>52051.5</v>
+        <v>52164</v>
       </c>
       <c r="N53" t="n">
-        <v>52472.75</v>
+        <v>52518.5</v>
       </c>
       <c r="O53" t="n">
-        <v>53387</v>
+        <v>52883</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4970,15 +4968,13 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4993,57 +4989,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>51800</v>
+        <v>52085</v>
       </c>
       <c r="C54" t="n">
-        <v>51957</v>
+        <v>52557</v>
       </c>
       <c r="D54" t="n">
-        <v>51576</v>
+        <v>52080</v>
       </c>
       <c r="E54" t="n">
-        <v>51761</v>
+        <v>52475</v>
       </c>
       <c r="F54" t="n">
-        <v>-46</v>
+        <v>714</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0138</v>
       </c>
       <c r="H54" t="n">
-        <v>381</v>
+        <v>477</v>
       </c>
       <c r="I54" t="n">
-        <v>50741</v>
+        <v>51195</v>
       </c>
       <c r="J54" t="n">
-        <v>51090.5</v>
+        <v>51377.25</v>
       </c>
       <c r="K54" t="n">
-        <v>51450</v>
+        <v>51570.5</v>
       </c>
       <c r="L54" t="n">
-        <v>51809.5</v>
+        <v>51763.75</v>
       </c>
       <c r="M54" t="n">
-        <v>52164</v>
+        <v>51951.5</v>
       </c>
       <c r="N54" t="n">
-        <v>52518.5</v>
+        <v>52139.25</v>
       </c>
       <c r="O54" t="n">
-        <v>52883</v>
+        <v>52338</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5054,78 +5050,80 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W54" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V54" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W54" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>52085</v>
+        <v>52470</v>
       </c>
       <c r="C55" t="n">
-        <v>52557</v>
+        <v>52844</v>
       </c>
       <c r="D55" t="n">
-        <v>52080</v>
+        <v>52125</v>
       </c>
       <c r="E55" t="n">
-        <v>52475</v>
+        <v>52279</v>
       </c>
       <c r="F55" t="n">
-        <v>714</v>
+        <v>-196</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0138</v>
+        <v>-0.0037</v>
       </c>
       <c r="H55" t="n">
-        <v>477</v>
+        <v>719</v>
       </c>
       <c r="I55" t="n">
-        <v>51195</v>
+        <v>51603</v>
       </c>
       <c r="J55" t="n">
-        <v>51377.25</v>
+        <v>52076.25</v>
       </c>
       <c r="K55" t="n">
-        <v>51570.5</v>
+        <v>52236.5</v>
       </c>
       <c r="L55" t="n">
-        <v>51763.75</v>
+        <v>52396.75</v>
       </c>
       <c r="M55" t="n">
-        <v>51951.5</v>
+        <v>52713.5</v>
       </c>
       <c r="N55" t="n">
-        <v>52139.25</v>
+        <v>53030.25</v>
       </c>
       <c r="O55" t="n">
-        <v>52338</v>
+        <v>53034</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5133,12 +5131,14 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
@@ -5146,70 +5146,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v/>
       </c>
       <c r="W55" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>52470</v>
+        <v>52255</v>
       </c>
       <c r="C56" t="n">
-        <v>52844</v>
+        <v>52371</v>
       </c>
       <c r="D56" t="n">
-        <v>52125</v>
+        <v>51844</v>
       </c>
       <c r="E56" t="n">
-        <v>52279</v>
+        <v>51873</v>
       </c>
       <c r="F56" t="n">
-        <v>-196</v>
+        <v>-406</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0037</v>
+        <v>-0.0078</v>
       </c>
       <c r="H56" t="n">
-        <v>719</v>
+        <v>527</v>
       </c>
       <c r="I56" t="n">
-        <v>51603</v>
+        <v>51406</v>
       </c>
       <c r="J56" t="n">
-        <v>52076.25</v>
+        <v>51457.25</v>
       </c>
       <c r="K56" t="n">
-        <v>52236.5</v>
+        <v>51919.5</v>
       </c>
       <c r="L56" t="n">
-        <v>52396.75</v>
+        <v>52381.75</v>
       </c>
       <c r="M56" t="n">
-        <v>52713.5</v>
+        <v>52638.5</v>
       </c>
       <c r="N56" t="n">
-        <v>53030.25</v>
+        <v>52895.25</v>
       </c>
       <c r="O56" t="n">
-        <v>53034</v>
+        <v>53563</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5227,10 +5227,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5245,57 +5243,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>52255</v>
+        <v>51878</v>
       </c>
       <c r="C57" t="n">
-        <v>52371</v>
+        <v>51905</v>
       </c>
       <c r="D57" t="n">
-        <v>51844</v>
+        <v>51479</v>
       </c>
       <c r="E57" t="n">
-        <v>51873</v>
+        <v>51717</v>
       </c>
       <c r="F57" t="n">
-        <v>-406</v>
+        <v>-156</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0078</v>
+        <v>-0.003</v>
       </c>
       <c r="H57" t="n">
-        <v>527</v>
+        <v>426</v>
       </c>
       <c r="I57" t="n">
-        <v>51406</v>
+        <v>51317</v>
       </c>
       <c r="J57" t="n">
-        <v>51457.25</v>
+        <v>51228.75</v>
       </c>
       <c r="K57" t="n">
-        <v>51919.5</v>
+        <v>51609.5</v>
       </c>
       <c r="L57" t="n">
-        <v>52381.75</v>
+        <v>51990.25</v>
       </c>
       <c r="M57" t="n">
-        <v>52638.5</v>
+        <v>52136.5</v>
       </c>
       <c r="N57" t="n">
-        <v>52895.25</v>
+        <v>52282.75</v>
       </c>
       <c r="O57" t="n">
-        <v>53563</v>
+        <v>52898</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5336,50 +5334,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>51878</v>
+        <v>51655</v>
       </c>
       <c r="C58" t="n">
-        <v>51905</v>
+        <v>52223</v>
       </c>
       <c r="D58" t="n">
-        <v>51479</v>
+        <v>51610</v>
       </c>
       <c r="E58" t="n">
-        <v>51717</v>
+        <v>52163</v>
       </c>
       <c r="F58" t="n">
-        <v>-156</v>
+        <v>446</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.0086</v>
       </c>
       <c r="H58" t="n">
-        <v>426</v>
+        <v>613</v>
       </c>
       <c r="I58" t="n">
-        <v>51317</v>
+        <v>51053</v>
       </c>
       <c r="J58" t="n">
-        <v>51228.75</v>
+        <v>51303.5</v>
       </c>
       <c r="K58" t="n">
-        <v>51609.5</v>
+        <v>51504</v>
       </c>
       <c r="L58" t="n">
-        <v>51990.25</v>
+        <v>51704.5</v>
       </c>
       <c r="M58" t="n">
-        <v>52136.5</v>
+        <v>51930</v>
       </c>
       <c r="N58" t="n">
-        <v>52282.75</v>
+        <v>52155.5</v>
       </c>
       <c r="O58" t="n">
-        <v>52898</v>
+        <v>52331</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5387,22 +5385,24 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
       <c r="V58" s="8" t="n">
         <v/>
       </c>
@@ -5411,59 +5411,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>51655</v>
+        <v>52140</v>
       </c>
       <c r="C59" t="n">
-        <v>52223</v>
+        <v>52153</v>
       </c>
       <c r="D59" t="n">
-        <v>51610</v>
+        <v>51744</v>
       </c>
       <c r="E59" t="n">
-        <v>52163</v>
+        <v>51837</v>
       </c>
       <c r="F59" t="n">
-        <v>446</v>
+        <v>-326</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.0062</v>
       </c>
       <c r="H59" t="n">
-        <v>613</v>
+        <v>409</v>
       </c>
       <c r="I59" t="n">
-        <v>51053</v>
+        <v>50997</v>
       </c>
       <c r="J59" t="n">
-        <v>51303.5</v>
+        <v>51673.25</v>
       </c>
       <c r="K59" t="n">
-        <v>51504</v>
+        <v>51856.5</v>
       </c>
       <c r="L59" t="n">
-        <v>51704.5</v>
+        <v>52039.75</v>
       </c>
       <c r="M59" t="n">
-        <v>51930</v>
+        <v>52469.5</v>
       </c>
       <c r="N59" t="n">
-        <v>52155.5</v>
+        <v>52899.25</v>
       </c>
       <c r="O59" t="n">
-        <v>52331</v>
+        <v>52836</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5471,24 +5467,22 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
+      <c r="R59" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v/>
+      </c>
       <c r="V59" s="8" t="n">
         <v/>
       </c>
@@ -5497,55 +5491,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>52140</v>
+        <v>51845</v>
       </c>
       <c r="C60" t="n">
-        <v>52153</v>
+        <v>52002</v>
       </c>
       <c r="D60" t="n">
-        <v>51744</v>
+        <v>51459</v>
       </c>
       <c r="E60" t="n">
-        <v>51837</v>
+        <v>51702</v>
       </c>
       <c r="F60" t="n">
-        <v>-326</v>
+        <v>-135</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0062</v>
+        <v>-0.0026</v>
       </c>
       <c r="H60" t="n">
-        <v>409</v>
+        <v>543</v>
       </c>
       <c r="I60" t="n">
-        <v>50997</v>
+        <v>51335</v>
       </c>
       <c r="J60" t="n">
-        <v>51673.25</v>
+        <v>51372.25</v>
       </c>
       <c r="K60" t="n">
-        <v>51856.5</v>
+        <v>51632.5</v>
       </c>
       <c r="L60" t="n">
-        <v>52039.75</v>
+        <v>51892.75</v>
       </c>
       <c r="M60" t="n">
-        <v>52469.5</v>
+        <v>52041.5</v>
       </c>
       <c r="N60" t="n">
-        <v>52899.25</v>
+        <v>52190.25</v>
       </c>
       <c r="O60" t="n">
-        <v>52836</v>
+        <v>52562</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5579,67 +5577,69 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>51845</v>
+        <v>51765</v>
       </c>
       <c r="C61" t="n">
-        <v>52002</v>
+        <v>51997</v>
       </c>
       <c r="D61" t="n">
-        <v>51459</v>
+        <v>51218</v>
       </c>
       <c r="E61" t="n">
-        <v>51702</v>
+        <v>51278</v>
       </c>
       <c r="F61" t="n">
-        <v>-135</v>
+        <v>-424</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0026</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H61" t="n">
-        <v>543</v>
+        <v>779</v>
       </c>
       <c r="I61" t="n">
-        <v>51335</v>
+        <v>50916</v>
       </c>
       <c r="J61" t="n">
-        <v>51372.25</v>
+        <v>51144.75</v>
       </c>
       <c r="K61" t="n">
-        <v>51632.5</v>
+        <v>51430.5</v>
       </c>
       <c r="L61" t="n">
-        <v>51892.75</v>
+        <v>51716.25</v>
       </c>
       <c r="M61" t="n">
-        <v>52041.5</v>
+        <v>51973.5</v>
       </c>
       <c r="N61" t="n">
-        <v>52190.25</v>
+        <v>52230.75</v>
       </c>
       <c r="O61" t="n">
-        <v>52562</v>
+        <v>52545</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S61" s="7" t="inlineStr">
@@ -5647,8 +5647,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T61" s="8" t="n">
-        <v/>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5670,58 +5672,56 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>51765</v>
+        <v>51335</v>
       </c>
       <c r="C62" t="n">
-        <v>51997</v>
+        <v>51517</v>
       </c>
       <c r="D62" t="n">
-        <v>51218</v>
+        <v>50859</v>
       </c>
       <c r="E62" t="n">
-        <v>51278</v>
+        <v>51241</v>
       </c>
       <c r="F62" t="n">
-        <v>-424</v>
+        <v>-37</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>-0.0007</v>
       </c>
       <c r="H62" t="n">
-        <v>779</v>
+        <v>658</v>
       </c>
       <c r="I62" t="n">
-        <v>50916</v>
+        <v>50439</v>
       </c>
       <c r="J62" t="n">
-        <v>51144.75</v>
+        <v>50334.25</v>
       </c>
       <c r="K62" t="n">
-        <v>51430.5</v>
+        <v>50888.5</v>
       </c>
       <c r="L62" t="n">
-        <v>51716.25</v>
+        <v>51442.75</v>
       </c>
       <c r="M62" t="n">
-        <v>51973.5</v>
+        <v>51667.5</v>
       </c>
       <c r="N62" t="n">
-        <v>52230.75</v>
+        <v>51892.25</v>
       </c>
       <c r="O62" t="n">
-        <v>52545</v>
+        <v>52776</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q62" s="6" t="n">
+        <v/>
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
@@ -5730,13 +5730,11 @@
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5758,50 +5756,50 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>51251</v>
       </c>
       <c r="C63" t="n">
-        <v>51255</v>
+        <v>51805</v>
       </c>
       <c r="D63" t="n">
-        <v>51235</v>
+        <v>51208</v>
       </c>
       <c r="E63" t="n">
-        <v>51243</v>
+        <v>51477</v>
       </c>
       <c r="F63" t="n">
-        <v>-35</v>
+        <v>236</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0007</v>
+        <v>0.0046</v>
       </c>
       <c r="H63" t="n">
-        <v>20</v>
+        <v>597</v>
       </c>
       <c r="I63" t="n">
-        <v>50439</v>
+        <v>50201</v>
       </c>
       <c r="J63" t="n">
-        <v>50334.25</v>
+        <v>50609.5</v>
       </c>
       <c r="K63" t="n">
-        <v>50888.5</v>
+        <v>50912</v>
       </c>
       <c r="L63" t="n">
-        <v>51442.75</v>
+        <v>51214.5</v>
       </c>
       <c r="M63" t="n">
-        <v>51667.5</v>
+        <v>51570</v>
       </c>
       <c r="N63" t="n">
-        <v>51892.25</v>
+        <v>51925.5</v>
       </c>
       <c r="O63" t="n">
-        <v>52776</v>
+        <v>52175</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5812,28 +5810,108 @@
       <c r="R63" s="6" t="n">
         <v/>
       </c>
-      <c r="S63" s="7" t="inlineStr">
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>51486</v>
+      </c>
+      <c r="C64" t="n">
+        <v>51560</v>
+      </c>
+      <c r="D64" t="n">
+        <v>51486</v>
+      </c>
+      <c r="E64" t="n">
+        <v>51477</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>74</v>
+      </c>
+      <c r="I64" t="n">
+        <v>50611</v>
+      </c>
+      <c r="J64" t="n">
+        <v>50865.25</v>
+      </c>
+      <c r="K64" t="n">
+        <v>51178.5</v>
+      </c>
+      <c r="L64" t="n">
+        <v>51491.75</v>
+      </c>
+      <c r="M64" t="n">
+        <v>51775.5</v>
+      </c>
+      <c r="N64" t="n">
+        <v>52059.25</v>
+      </c>
+      <c r="O64" t="n">
+        <v>52402</v>
+      </c>
+      <c r="P64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="9" t="inlineStr">
+      <c r="T64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W64" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>中警訊</t>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,69 +634,63 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53166</v>
+        <v>52541</v>
       </c>
       <c r="C2" t="n">
-        <v>53207</v>
+        <v>52865</v>
       </c>
       <c r="D2" t="n">
-        <v>52343</v>
+        <v>52501</v>
       </c>
       <c r="E2" t="n">
-        <v>52624</v>
+        <v>52761</v>
       </c>
       <c r="F2" t="n">
-        <v>-573</v>
+        <v>137</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0108</v>
+        <v>0.0026</v>
       </c>
       <c r="H2" t="n">
-        <v>864</v>
+        <v>364</v>
       </c>
       <c r="I2" t="n">
-        <v>52496</v>
+        <v>51479</v>
       </c>
       <c r="J2" t="n">
-        <v>52532.5</v>
+        <v>51684.5</v>
       </c>
       <c r="K2" t="n">
-        <v>52907</v>
+        <v>52192</v>
       </c>
       <c r="L2" t="n">
-        <v>53281.5</v>
+        <v>52699.5</v>
       </c>
       <c r="M2" t="n">
-        <v>53487</v>
+        <v>53056</v>
       </c>
       <c r="N2" t="n">
-        <v>53692.5</v>
+        <v>53412.5</v>
       </c>
       <c r="O2" t="n">
-        <v>54236</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>54071</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -715,57 +709,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>52541</v>
+        <v>52753</v>
       </c>
       <c r="C3" t="n">
-        <v>52865</v>
+        <v>52992</v>
       </c>
       <c r="D3" t="n">
-        <v>52501</v>
+        <v>52506</v>
       </c>
       <c r="E3" t="n">
-        <v>52761</v>
+        <v>52906</v>
       </c>
       <c r="F3" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0027</v>
       </c>
       <c r="H3" t="n">
-        <v>364</v>
+        <v>486</v>
       </c>
       <c r="I3" t="n">
-        <v>51479</v>
+        <v>52137</v>
       </c>
       <c r="J3" t="n">
-        <v>51684.5</v>
+        <v>52436</v>
       </c>
       <c r="K3" t="n">
-        <v>52192</v>
+        <v>52579</v>
       </c>
       <c r="L3" t="n">
-        <v>52699.5</v>
+        <v>52722</v>
       </c>
       <c r="M3" t="n">
-        <v>53056</v>
+        <v>52943</v>
       </c>
       <c r="N3" t="n">
-        <v>53412.5</v>
+        <v>53164</v>
       </c>
       <c r="O3" t="n">
-        <v>54071</v>
+        <v>53229</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -773,16 +767,20 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -795,59 +793,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>52753</v>
+        <v>52844</v>
       </c>
       <c r="C4" t="n">
-        <v>52992</v>
+        <v>53113</v>
       </c>
       <c r="D4" t="n">
-        <v>52506</v>
+        <v>52603</v>
       </c>
       <c r="E4" t="n">
-        <v>52906</v>
+        <v>52764</v>
       </c>
       <c r="F4" t="n">
-        <v>145</v>
+        <v>-142</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0027</v>
       </c>
       <c r="H4" t="n">
-        <v>486</v>
+        <v>510</v>
       </c>
       <c r="I4" t="n">
-        <v>52137</v>
+        <v>52020</v>
       </c>
       <c r="J4" t="n">
-        <v>52436</v>
+        <v>52498.5</v>
       </c>
       <c r="K4" t="n">
-        <v>52579</v>
+        <v>52663</v>
       </c>
       <c r="L4" t="n">
-        <v>52722</v>
+        <v>52827.5</v>
       </c>
       <c r="M4" t="n">
-        <v>52943</v>
+        <v>53149</v>
       </c>
       <c r="N4" t="n">
-        <v>53164</v>
+        <v>53470.5</v>
       </c>
       <c r="O4" t="n">
-        <v>53229</v>
+        <v>53478</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -862,13 +856,11 @@
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -881,55 +873,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52844</v>
+        <v>52731</v>
       </c>
       <c r="C5" t="n">
-        <v>53113</v>
+        <v>52981</v>
       </c>
       <c r="D5" t="n">
-        <v>52603</v>
+        <v>52255</v>
       </c>
       <c r="E5" t="n">
-        <v>52764</v>
+        <v>52791</v>
       </c>
       <c r="F5" t="n">
-        <v>-142</v>
+        <v>27</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0005</v>
       </c>
       <c r="H5" t="n">
-        <v>510</v>
+        <v>726</v>
       </c>
       <c r="I5" t="n">
-        <v>52020</v>
+        <v>52093</v>
       </c>
       <c r="J5" t="n">
-        <v>52498.5</v>
+        <v>52207</v>
       </c>
       <c r="K5" t="n">
-        <v>52663</v>
+        <v>52509</v>
       </c>
       <c r="L5" t="n">
-        <v>52827.5</v>
+        <v>52811</v>
       </c>
       <c r="M5" t="n">
-        <v>53149</v>
+        <v>53019</v>
       </c>
       <c r="N5" t="n">
-        <v>53470.5</v>
+        <v>53227</v>
       </c>
       <c r="O5" t="n">
-        <v>53478</v>
+        <v>53623</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -942,7 +938,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -963,57 +959,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52731</v>
+        <v>52792</v>
       </c>
       <c r="C6" t="n">
-        <v>52981</v>
+        <v>53088</v>
       </c>
       <c r="D6" t="n">
-        <v>52255</v>
+        <v>52680</v>
       </c>
       <c r="E6" t="n">
-        <v>52791</v>
+        <v>52900</v>
       </c>
       <c r="F6" t="n">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0021</v>
       </c>
       <c r="H6" t="n">
-        <v>726</v>
+        <v>408</v>
       </c>
       <c r="I6" t="n">
-        <v>52093</v>
+        <v>51529</v>
       </c>
       <c r="J6" t="n">
-        <v>52207</v>
+        <v>52151.5</v>
       </c>
       <c r="K6" t="n">
-        <v>52509</v>
+        <v>52428</v>
       </c>
       <c r="L6" t="n">
-        <v>52811</v>
+        <v>52704.5</v>
       </c>
       <c r="M6" t="n">
-        <v>53019</v>
+        <v>53154</v>
       </c>
       <c r="N6" t="n">
-        <v>53227</v>
+        <v>53603.5</v>
       </c>
       <c r="O6" t="n">
-        <v>53623</v>
+        <v>53707</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1021,14 +1017,12 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R6" s="6" t="n">
+        <v/>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1045,59 +1039,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>52792</v>
+        <v>52919</v>
       </c>
       <c r="C7" t="n">
-        <v>53088</v>
+        <v>53108</v>
       </c>
       <c r="D7" t="n">
-        <v>52680</v>
+        <v>52607</v>
       </c>
       <c r="E7" t="n">
-        <v>52900</v>
+        <v>52786</v>
       </c>
       <c r="F7" t="n">
-        <v>109</v>
+        <v>-114</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0022</v>
       </c>
       <c r="H7" t="n">
-        <v>408</v>
+        <v>501</v>
       </c>
       <c r="I7" t="n">
-        <v>51529</v>
+        <v>52272</v>
       </c>
       <c r="J7" t="n">
-        <v>52151.5</v>
+        <v>52500</v>
       </c>
       <c r="K7" t="n">
-        <v>52428</v>
+        <v>52696</v>
       </c>
       <c r="L7" t="n">
-        <v>52704.5</v>
+        <v>52892</v>
       </c>
       <c r="M7" t="n">
-        <v>53154</v>
+        <v>53104</v>
       </c>
       <c r="N7" t="n">
-        <v>53603.5</v>
+        <v>53316</v>
       </c>
       <c r="O7" t="n">
-        <v>53707</v>
+        <v>53496</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1105,16 +1095,20 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1127,76 +1121,80 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52919</v>
+        <v>52778</v>
       </c>
       <c r="C8" t="n">
-        <v>53108</v>
+        <v>52835</v>
       </c>
       <c r="D8" t="n">
-        <v>52607</v>
+        <v>52174</v>
       </c>
       <c r="E8" t="n">
-        <v>52786</v>
+        <v>52375</v>
       </c>
       <c r="F8" t="n">
-        <v>-114</v>
+        <v>-411</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0078</v>
       </c>
       <c r="H8" t="n">
-        <v>501</v>
+        <v>661</v>
       </c>
       <c r="I8" t="n">
-        <v>52272</v>
+        <v>52106</v>
       </c>
       <c r="J8" t="n">
-        <v>52500</v>
+        <v>52249.25</v>
       </c>
       <c r="K8" t="n">
-        <v>52696</v>
+        <v>52535.5</v>
       </c>
       <c r="L8" t="n">
-        <v>52892</v>
+        <v>52821.75</v>
       </c>
       <c r="M8" t="n">
-        <v>53104</v>
+        <v>53036.5</v>
       </c>
       <c r="N8" t="n">
-        <v>53316</v>
+        <v>53251.25</v>
       </c>
       <c r="O8" t="n">
-        <v>53496</v>
+        <v>53609</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1211,72 +1209,70 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52778</v>
+        <v>52300</v>
       </c>
       <c r="C9" t="n">
-        <v>52835</v>
+        <v>52633</v>
       </c>
       <c r="D9" t="n">
-        <v>52174</v>
+        <v>51999</v>
       </c>
       <c r="E9" t="n">
-        <v>52375</v>
+        <v>52073</v>
       </c>
       <c r="F9" t="n">
-        <v>-411</v>
+        <v>-302</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0078</v>
+        <v>-0.0058</v>
       </c>
       <c r="H9" t="n">
-        <v>661</v>
+        <v>634</v>
       </c>
       <c r="I9" t="n">
-        <v>52106</v>
+        <v>51513</v>
       </c>
       <c r="J9" t="n">
-        <v>52249.25</v>
+        <v>51649.25</v>
       </c>
       <c r="K9" t="n">
-        <v>52535.5</v>
+        <v>52044.5</v>
       </c>
       <c r="L9" t="n">
-        <v>52821.75</v>
+        <v>52439.75</v>
       </c>
       <c r="M9" t="n">
-        <v>53036.5</v>
+        <v>52705.5</v>
       </c>
       <c r="N9" t="n">
-        <v>53251.25</v>
+        <v>52971.25</v>
       </c>
       <c r="O9" t="n">
-        <v>53609</v>
+        <v>53496</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1304,50 +1300,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52300</v>
+        <v>52091</v>
       </c>
       <c r="C10" t="n">
-        <v>52633</v>
+        <v>52590</v>
       </c>
       <c r="D10" t="n">
-        <v>51999</v>
+        <v>52035</v>
       </c>
       <c r="E10" t="n">
-        <v>52073</v>
+        <v>52443</v>
       </c>
       <c r="F10" t="n">
-        <v>-302</v>
+        <v>370</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.0071</v>
       </c>
       <c r="H10" t="n">
-        <v>634</v>
+        <v>555</v>
       </c>
       <c r="I10" t="n">
-        <v>51513</v>
+        <v>51365</v>
       </c>
       <c r="J10" t="n">
-        <v>51649.25</v>
+        <v>51317.5</v>
       </c>
       <c r="K10" t="n">
-        <v>52044.5</v>
+        <v>51756</v>
       </c>
       <c r="L10" t="n">
-        <v>52439.75</v>
+        <v>52194.5</v>
       </c>
       <c r="M10" t="n">
-        <v>52705.5</v>
+        <v>52390</v>
       </c>
       <c r="N10" t="n">
-        <v>52971.25</v>
+        <v>52585.5</v>
       </c>
       <c r="O10" t="n">
-        <v>53496</v>
+        <v>53267</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1355,21 +1351,23 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1381,57 +1379,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>52091</v>
+        <v>52431</v>
       </c>
       <c r="C11" t="n">
-        <v>52590</v>
+        <v>52721</v>
       </c>
       <c r="D11" t="n">
-        <v>52035</v>
+        <v>52262</v>
       </c>
       <c r="E11" t="n">
-        <v>52443</v>
+        <v>52449</v>
       </c>
       <c r="F11" t="n">
-        <v>370</v>
+        <v>6</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0001</v>
       </c>
       <c r="H11" t="n">
-        <v>555</v>
+        <v>459</v>
       </c>
       <c r="I11" t="n">
-        <v>51365</v>
+        <v>51480</v>
       </c>
       <c r="J11" t="n">
-        <v>51317.5</v>
+        <v>51953.25</v>
       </c>
       <c r="K11" t="n">
-        <v>51756</v>
+        <v>52165.5</v>
       </c>
       <c r="L11" t="n">
-        <v>52194.5</v>
+        <v>52377.75</v>
       </c>
       <c r="M11" t="n">
-        <v>52390</v>
+        <v>52720.5</v>
       </c>
       <c r="N11" t="n">
-        <v>52585.5</v>
+        <v>53063.25</v>
       </c>
       <c r="O11" t="n">
-        <v>53267</v>
+        <v>53145</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1442,21 +1440,19 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U11" s="8" t="n">
+        <v/>
+      </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
@@ -1465,78 +1461,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52431</v>
+        <v>52430</v>
       </c>
       <c r="C12" t="n">
-        <v>52721</v>
+        <v>52515</v>
       </c>
       <c r="D12" t="n">
-        <v>52262</v>
+        <v>51720</v>
       </c>
       <c r="E12" t="n">
-        <v>52449</v>
+        <v>51894</v>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>-555</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0106</v>
       </c>
       <c r="H12" t="n">
-        <v>459</v>
+        <v>795</v>
       </c>
       <c r="I12" t="n">
-        <v>51480</v>
+        <v>51803</v>
       </c>
       <c r="J12" t="n">
-        <v>51953.25</v>
+        <v>51968.75</v>
       </c>
       <c r="K12" t="n">
-        <v>52165.5</v>
+        <v>52219.5</v>
       </c>
       <c r="L12" t="n">
-        <v>52377.75</v>
+        <v>52470.25</v>
       </c>
       <c r="M12" t="n">
-        <v>52720.5</v>
+        <v>52678.5</v>
       </c>
       <c r="N12" t="n">
-        <v>53063.25</v>
+        <v>52886.75</v>
       </c>
       <c r="O12" t="n">
-        <v>53145</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+        <v>53180</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1544,9 +1540,9 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W12" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr"/>
@@ -1554,74 +1550,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>52430</v>
+        <v>51920</v>
       </c>
       <c r="C13" t="n">
-        <v>52515</v>
+        <v>52314</v>
       </c>
       <c r="D13" t="n">
-        <v>51720</v>
+        <v>51846</v>
       </c>
       <c r="E13" t="n">
-        <v>51894</v>
+        <v>52124</v>
       </c>
       <c r="F13" t="n">
-        <v>-555</v>
+        <v>230</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0044</v>
       </c>
       <c r="H13" t="n">
-        <v>795</v>
+        <v>468</v>
       </c>
       <c r="I13" t="n">
-        <v>51803</v>
+        <v>50925</v>
       </c>
       <c r="J13" t="n">
-        <v>51968.75</v>
+        <v>50987.25</v>
       </c>
       <c r="K13" t="n">
-        <v>52219.5</v>
+        <v>51496.5</v>
       </c>
       <c r="L13" t="n">
-        <v>52470.25</v>
+        <v>52005.75</v>
       </c>
       <c r="M13" t="n">
-        <v>52678.5</v>
+        <v>52291.5</v>
       </c>
       <c r="N13" t="n">
-        <v>52886.75</v>
+        <v>52577.25</v>
       </c>
       <c r="O13" t="n">
-        <v>53180</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
+        <v>53310</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
@@ -1633,55 +1625,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>51920</v>
+        <v>52299</v>
       </c>
       <c r="C14" t="n">
-        <v>52314</v>
+        <v>52790</v>
       </c>
       <c r="D14" t="n">
-        <v>51846</v>
+        <v>52173</v>
       </c>
       <c r="E14" t="n">
-        <v>52124</v>
+        <v>52382</v>
       </c>
       <c r="F14" t="n">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0049</v>
       </c>
       <c r="H14" t="n">
-        <v>468</v>
+        <v>617</v>
       </c>
       <c r="I14" t="n">
-        <v>50925</v>
+        <v>51378</v>
       </c>
       <c r="J14" t="n">
-        <v>50987.25</v>
+        <v>51678</v>
       </c>
       <c r="K14" t="n">
-        <v>51496.5</v>
+        <v>51890</v>
       </c>
       <c r="L14" t="n">
-        <v>52005.75</v>
+        <v>52102</v>
       </c>
       <c r="M14" t="n">
-        <v>52291.5</v>
+        <v>52358</v>
       </c>
       <c r="N14" t="n">
-        <v>52577.25</v>
+        <v>52614</v>
       </c>
       <c r="O14" t="n">
-        <v>53310</v>
+        <v>52782</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1692,21 +1688,25 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v/>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W14" s="11" t="inlineStr">
         <is>
@@ -1715,57 +1715,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52299</v>
+        <v>52405</v>
       </c>
       <c r="C15" t="n">
-        <v>52790</v>
+        <v>53105</v>
       </c>
       <c r="D15" t="n">
-        <v>52173</v>
+        <v>52290</v>
       </c>
       <c r="E15" t="n">
-        <v>52382</v>
+        <v>52944</v>
       </c>
       <c r="F15" t="n">
-        <v>258</v>
+        <v>562</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0107</v>
       </c>
       <c r="H15" t="n">
-        <v>617</v>
+        <v>815</v>
       </c>
       <c r="I15" t="n">
-        <v>51378</v>
+        <v>51556</v>
       </c>
       <c r="J15" t="n">
-        <v>51678</v>
+        <v>51715.25</v>
       </c>
       <c r="K15" t="n">
-        <v>51890</v>
+        <v>52073.5</v>
       </c>
       <c r="L15" t="n">
-        <v>52102</v>
+        <v>52431.75</v>
       </c>
       <c r="M15" t="n">
-        <v>52358</v>
+        <v>52690.5</v>
       </c>
       <c r="N15" t="n">
-        <v>52614</v>
+        <v>52949.25</v>
       </c>
       <c r="O15" t="n">
-        <v>52782</v>
+        <v>53407</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1776,25 +1776,23 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V15" s="8" t="n">
+        <v/>
       </c>
       <c r="W15" s="11" t="inlineStr">
         <is>
@@ -1810,74 +1808,76 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>52405</v>
+        <v>52915</v>
       </c>
       <c r="C16" t="n">
-        <v>53105</v>
+        <v>53033</v>
       </c>
       <c r="D16" t="n">
-        <v>52290</v>
+        <v>51630</v>
       </c>
       <c r="E16" t="n">
-        <v>52944</v>
+        <v>51765</v>
       </c>
       <c r="F16" t="n">
-        <v>562</v>
+        <v>-1179</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0223</v>
       </c>
       <c r="H16" t="n">
-        <v>815</v>
+        <v>1403</v>
       </c>
       <c r="I16" t="n">
-        <v>51556</v>
+        <v>51475</v>
       </c>
       <c r="J16" t="n">
-        <v>51715.25</v>
+        <v>52252.25</v>
       </c>
       <c r="K16" t="n">
-        <v>52073.5</v>
+        <v>52536.5</v>
       </c>
       <c r="L16" t="n">
-        <v>52431.75</v>
+        <v>52820.75</v>
       </c>
       <c r="M16" t="n">
-        <v>52690.5</v>
+        <v>53351.5</v>
       </c>
       <c r="N16" t="n">
-        <v>52949.25</v>
+        <v>53882.25</v>
       </c>
       <c r="O16" t="n">
-        <v>53407</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+        <v>53920</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1887,83 +1887,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>52915</v>
+        <v>51759</v>
       </c>
       <c r="C17" t="n">
-        <v>53033</v>
+        <v>52484</v>
       </c>
       <c r="D17" t="n">
-        <v>51630</v>
+        <v>51732</v>
       </c>
       <c r="E17" t="n">
-        <v>51765</v>
+        <v>52380</v>
       </c>
       <c r="F17" t="n">
-        <v>-1179</v>
+        <v>615</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0119</v>
       </c>
       <c r="H17" t="n">
-        <v>1403</v>
+        <v>752</v>
       </c>
       <c r="I17" t="n">
-        <v>51475</v>
+        <v>50227</v>
       </c>
       <c r="J17" t="n">
-        <v>52252.25</v>
+        <v>50078.75</v>
       </c>
       <c r="K17" t="n">
-        <v>52536.5</v>
+        <v>51063.5</v>
       </c>
       <c r="L17" t="n">
-        <v>52820.75</v>
+        <v>52048.25</v>
       </c>
       <c r="M17" t="n">
-        <v>53351.5</v>
+        <v>52466.5</v>
       </c>
       <c r="N17" t="n">
-        <v>53882.25</v>
+        <v>52884.75</v>
       </c>
       <c r="O17" t="n">
-        <v>53920</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
+        <v>54436</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
       <c r="U17" s="8" t="n">
         <v/>
       </c>
@@ -1975,55 +1967,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>51759</v>
+        <v>52395</v>
       </c>
       <c r="C18" t="n">
-        <v>52484</v>
+        <v>52772</v>
       </c>
       <c r="D18" t="n">
-        <v>51732</v>
+        <v>52124</v>
       </c>
       <c r="E18" t="n">
-        <v>52380</v>
+        <v>52635</v>
       </c>
       <c r="F18" t="n">
-        <v>615</v>
+        <v>255</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0119</v>
+        <v>0.0049</v>
       </c>
       <c r="H18" t="n">
-        <v>752</v>
+        <v>648</v>
       </c>
       <c r="I18" t="n">
-        <v>50227</v>
+        <v>50980</v>
       </c>
       <c r="J18" t="n">
-        <v>50078.75</v>
+        <v>51764</v>
       </c>
       <c r="K18" t="n">
-        <v>51063.5</v>
+        <v>52004</v>
       </c>
       <c r="L18" t="n">
-        <v>52048.25</v>
+        <v>52244</v>
       </c>
       <c r="M18" t="n">
-        <v>52466.5</v>
+        <v>52756</v>
       </c>
       <c r="N18" t="n">
-        <v>52884.75</v>
+        <v>53268</v>
       </c>
       <c r="O18" t="n">
-        <v>54436</v>
+        <v>53236</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2034,7 +2030,7 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="10" t="inlineStr">
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2057,57 +2053,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>52395</v>
+        <v>52780</v>
       </c>
       <c r="C19" t="n">
-        <v>52772</v>
+        <v>53414</v>
       </c>
       <c r="D19" t="n">
-        <v>52124</v>
+        <v>52777</v>
       </c>
       <c r="E19" t="n">
-        <v>52635</v>
+        <v>53334</v>
       </c>
       <c r="F19" t="n">
-        <v>255</v>
+        <v>699</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0133</v>
       </c>
       <c r="H19" t="n">
-        <v>648</v>
+        <v>637</v>
       </c>
       <c r="I19" t="n">
-        <v>50980</v>
+        <v>51476</v>
       </c>
       <c r="J19" t="n">
-        <v>51764</v>
+        <v>52080.5</v>
       </c>
       <c r="K19" t="n">
-        <v>52004</v>
+        <v>52311</v>
       </c>
       <c r="L19" t="n">
-        <v>52244</v>
+        <v>52541.5</v>
       </c>
       <c r="M19" t="n">
-        <v>52756</v>
+        <v>52959</v>
       </c>
       <c r="N19" t="n">
-        <v>53268</v>
+        <v>53376.5</v>
       </c>
       <c r="O19" t="n">
-        <v>53236</v>
+        <v>53420</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2118,18 +2114,20 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="S19" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2148,50 +2146,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>52780</v>
+        <v>53381</v>
       </c>
       <c r="C20" t="n">
-        <v>53414</v>
+        <v>54423</v>
       </c>
       <c r="D20" t="n">
-        <v>52777</v>
+        <v>53267</v>
       </c>
       <c r="E20" t="n">
-        <v>53334</v>
+        <v>54268</v>
       </c>
       <c r="F20" t="n">
-        <v>699</v>
+        <v>934</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0133</v>
+        <v>0.0175</v>
       </c>
       <c r="H20" t="n">
-        <v>637</v>
+        <v>1156</v>
       </c>
       <c r="I20" t="n">
-        <v>51476</v>
+        <v>52140</v>
       </c>
       <c r="J20" t="n">
-        <v>52080.5</v>
+        <v>52816.25</v>
       </c>
       <c r="K20" t="n">
-        <v>52311</v>
+        <v>53015.5</v>
       </c>
       <c r="L20" t="n">
-        <v>52541.5</v>
+        <v>53214.75</v>
       </c>
       <c r="M20" t="n">
-        <v>52959</v>
+        <v>53652.5</v>
       </c>
       <c r="N20" t="n">
-        <v>53376.5</v>
+        <v>54090.25</v>
       </c>
       <c r="O20" t="n">
-        <v>53420</v>
+        <v>54051</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2202,7 +2200,7 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2217,67 +2215,65 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W20" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>53381</v>
+        <v>54369</v>
       </c>
       <c r="C21" t="n">
-        <v>54423</v>
+        <v>54884</v>
       </c>
       <c r="D21" t="n">
-        <v>53267</v>
+        <v>54342</v>
       </c>
       <c r="E21" t="n">
-        <v>54268</v>
+        <v>54494</v>
       </c>
       <c r="F21" t="n">
-        <v>934</v>
+        <v>226</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0175</v>
+        <v>0.0042</v>
       </c>
       <c r="H21" t="n">
-        <v>1156</v>
+        <v>542</v>
       </c>
       <c r="I21" t="n">
-        <v>52140</v>
+        <v>52111</v>
       </c>
       <c r="J21" t="n">
-        <v>52816.25</v>
+        <v>53323.5</v>
       </c>
       <c r="K21" t="n">
-        <v>53015.5</v>
+        <v>53690</v>
       </c>
       <c r="L21" t="n">
-        <v>53214.75</v>
+        <v>54056.5</v>
       </c>
       <c r="M21" t="n">
-        <v>53652.5</v>
+        <v>54846</v>
       </c>
       <c r="N21" t="n">
-        <v>54090.25</v>
+        <v>55635.5</v>
       </c>
       <c r="O21" t="n">
-        <v>54051</v>
+        <v>55579</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2288,25 +2284,21 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
@@ -2318,69 +2310,71 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>54369</v>
+        <v>54555</v>
       </c>
       <c r="C22" t="n">
-        <v>54884</v>
+        <v>54678</v>
       </c>
       <c r="D22" t="n">
-        <v>54342</v>
+        <v>53952</v>
       </c>
       <c r="E22" t="n">
-        <v>54494</v>
+        <v>54013</v>
       </c>
       <c r="F22" t="n">
-        <v>226</v>
+        <v>-481</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0042</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>542</v>
+        <v>726</v>
       </c>
       <c r="I22" t="n">
-        <v>52111</v>
+        <v>53800</v>
       </c>
       <c r="J22" t="n">
-        <v>53323.5</v>
+        <v>53892.5</v>
       </c>
       <c r="K22" t="n">
-        <v>53690</v>
+        <v>54223</v>
       </c>
       <c r="L22" t="n">
-        <v>54056.5</v>
+        <v>54553.5</v>
       </c>
       <c r="M22" t="n">
-        <v>54846</v>
+        <v>54765</v>
       </c>
       <c r="N22" t="n">
-        <v>55635.5</v>
+        <v>54976.5</v>
       </c>
       <c r="O22" t="n">
-        <v>55579</v>
+        <v>55426</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2393,72 +2387,72 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>54555</v>
+        <v>54040</v>
       </c>
       <c r="C23" t="n">
-        <v>54678</v>
+        <v>54202</v>
       </c>
       <c r="D23" t="n">
-        <v>53952</v>
+        <v>53879</v>
       </c>
       <c r="E23" t="n">
-        <v>54013</v>
+        <v>54152</v>
       </c>
       <c r="F23" t="n">
-        <v>-481</v>
+        <v>139</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0026</v>
       </c>
       <c r="H23" t="n">
-        <v>726</v>
+        <v>323</v>
       </c>
       <c r="I23" t="n">
-        <v>53800</v>
+        <v>53226</v>
       </c>
       <c r="J23" t="n">
-        <v>53892.5</v>
+        <v>53136</v>
       </c>
       <c r="K23" t="n">
-        <v>54223</v>
+        <v>53650</v>
       </c>
       <c r="L23" t="n">
-        <v>54553.5</v>
+        <v>54164</v>
       </c>
       <c r="M23" t="n">
-        <v>54765</v>
+        <v>54376</v>
       </c>
       <c r="N23" t="n">
-        <v>54976.5</v>
+        <v>54588</v>
       </c>
       <c r="O23" t="n">
-        <v>55426</v>
+        <v>55404</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2477,57 +2471,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>54040</v>
+        <v>54133</v>
       </c>
       <c r="C24" t="n">
-        <v>54202</v>
+        <v>54170</v>
       </c>
       <c r="D24" t="n">
-        <v>53879</v>
+        <v>53952</v>
       </c>
       <c r="E24" t="n">
-        <v>54152</v>
+        <v>54063</v>
       </c>
       <c r="F24" t="n">
-        <v>139</v>
+        <v>-89</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0026</v>
+        <v>-0.0016</v>
       </c>
       <c r="H24" t="n">
-        <v>323</v>
+        <v>218</v>
       </c>
       <c r="I24" t="n">
-        <v>53226</v>
+        <v>53556</v>
       </c>
       <c r="J24" t="n">
-        <v>53136</v>
+        <v>53884.75</v>
       </c>
       <c r="K24" t="n">
-        <v>53650</v>
+        <v>53990.5</v>
       </c>
       <c r="L24" t="n">
-        <v>54164</v>
+        <v>54096.25</v>
       </c>
       <c r="M24" t="n">
-        <v>54376</v>
+        <v>54313.5</v>
       </c>
       <c r="N24" t="n">
-        <v>54588</v>
+        <v>54530.75</v>
       </c>
       <c r="O24" t="n">
-        <v>55404</v>
+        <v>54525</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2535,10 +2529,12 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2566,72 +2562,78 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>54133</v>
+        <v>54049</v>
       </c>
       <c r="C25" t="n">
-        <v>54170</v>
+        <v>54336</v>
       </c>
       <c r="D25" t="n">
-        <v>53952</v>
+        <v>53855</v>
       </c>
       <c r="E25" t="n">
-        <v>54063</v>
+        <v>53880</v>
       </c>
       <c r="F25" t="n">
-        <v>-89</v>
+        <v>-183</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0034</v>
       </c>
       <c r="H25" t="n">
-        <v>218</v>
+        <v>481</v>
       </c>
       <c r="I25" t="n">
-        <v>53556</v>
+        <v>53734</v>
       </c>
       <c r="J25" t="n">
-        <v>53884.75</v>
+        <v>53846</v>
       </c>
       <c r="K25" t="n">
-        <v>53990.5</v>
+        <v>53954</v>
       </c>
       <c r="L25" t="n">
-        <v>54096.25</v>
+        <v>54062</v>
       </c>
       <c r="M25" t="n">
-        <v>54313.5</v>
+        <v>54172</v>
       </c>
       <c r="N25" t="n">
-        <v>54530.75</v>
+        <v>54282</v>
       </c>
       <c r="O25" t="n">
-        <v>54525</v>
+        <v>54388</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2650,78 +2652,72 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>54049</v>
+        <v>53903</v>
       </c>
       <c r="C26" t="n">
-        <v>54336</v>
+        <v>54150</v>
       </c>
       <c r="D26" t="n">
-        <v>53855</v>
+        <v>53830</v>
       </c>
       <c r="E26" t="n">
-        <v>53880</v>
+        <v>53871</v>
       </c>
       <c r="F26" t="n">
-        <v>-183</v>
+        <v>-9</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0002</v>
       </c>
       <c r="H26" t="n">
-        <v>481</v>
+        <v>320</v>
       </c>
       <c r="I26" t="n">
-        <v>53734</v>
+        <v>53374</v>
       </c>
       <c r="J26" t="n">
-        <v>53846</v>
+        <v>53291.25</v>
       </c>
       <c r="K26" t="n">
-        <v>53954</v>
+        <v>53639.5</v>
       </c>
       <c r="L26" t="n">
-        <v>54062</v>
+        <v>53987.75</v>
       </c>
       <c r="M26" t="n">
-        <v>54172</v>
+        <v>54120.5</v>
       </c>
       <c r="N26" t="n">
-        <v>54282</v>
+        <v>54253.25</v>
       </c>
       <c r="O26" t="n">
-        <v>54388</v>
+        <v>54817</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2733,57 +2729,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>53903</v>
+        <v>53905</v>
       </c>
       <c r="C27" t="n">
-        <v>54150</v>
+        <v>54149</v>
       </c>
       <c r="D27" t="n">
-        <v>53830</v>
+        <v>53715</v>
       </c>
       <c r="E27" t="n">
-        <v>53871</v>
+        <v>53935</v>
       </c>
       <c r="F27" t="n">
-        <v>-9</v>
+        <v>64</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0002</v>
+        <v>0.0012</v>
       </c>
       <c r="H27" t="n">
-        <v>320</v>
+        <v>434</v>
       </c>
       <c r="I27" t="n">
-        <v>53374</v>
+        <v>53510</v>
       </c>
       <c r="J27" t="n">
-        <v>53291.25</v>
+        <v>53491.5</v>
       </c>
       <c r="K27" t="n">
-        <v>53639.5</v>
+        <v>53711</v>
       </c>
       <c r="L27" t="n">
-        <v>53987.75</v>
+        <v>53930.5</v>
       </c>
       <c r="M27" t="n">
-        <v>54120.5</v>
+        <v>54031</v>
       </c>
       <c r="N27" t="n">
-        <v>54253.25</v>
+        <v>54131.5</v>
       </c>
       <c r="O27" t="n">
-        <v>54817</v>
+        <v>54470</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2796,7 +2792,7 @@
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
@@ -2804,8 +2800,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U27" s="8" t="n">
-        <v/>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2817,57 +2815,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>53905</v>
+        <v>53961</v>
       </c>
       <c r="C28" t="n">
-        <v>54149</v>
+        <v>53999</v>
       </c>
       <c r="D28" t="n">
-        <v>53715</v>
+        <v>53745</v>
       </c>
       <c r="E28" t="n">
-        <v>53935</v>
+        <v>53807</v>
       </c>
       <c r="F28" t="n">
-        <v>64</v>
+        <v>-128</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0012</v>
+        <v>-0.0024</v>
       </c>
       <c r="H28" t="n">
-        <v>434</v>
+        <v>254</v>
       </c>
       <c r="I28" t="n">
-        <v>53510</v>
+        <v>53281</v>
       </c>
       <c r="J28" t="n">
-        <v>53491.5</v>
+        <v>53502.5</v>
       </c>
       <c r="K28" t="n">
-        <v>53711</v>
+        <v>53718</v>
       </c>
       <c r="L28" t="n">
-        <v>53930.5</v>
+        <v>53933.5</v>
       </c>
       <c r="M28" t="n">
-        <v>54031</v>
+        <v>54152</v>
       </c>
       <c r="N28" t="n">
-        <v>54131.5</v>
+        <v>54370.5</v>
       </c>
       <c r="O28" t="n">
-        <v>54470</v>
+        <v>54583</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2875,23 +2873,21 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2910,63 +2906,67 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>53961</v>
+        <v>53790</v>
       </c>
       <c r="C29" t="n">
-        <v>53999</v>
+        <v>53840</v>
       </c>
       <c r="D29" t="n">
-        <v>53745</v>
+        <v>53464</v>
       </c>
       <c r="E29" t="n">
-        <v>53807</v>
+        <v>53544</v>
       </c>
       <c r="F29" t="n">
-        <v>-128</v>
+        <v>-263</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0049</v>
       </c>
       <c r="H29" t="n">
-        <v>254</v>
+        <v>376</v>
       </c>
       <c r="I29" t="n">
-        <v>53281</v>
+        <v>53491</v>
       </c>
       <c r="J29" t="n">
-        <v>53502.5</v>
+        <v>53520.5</v>
       </c>
       <c r="K29" t="n">
-        <v>53718</v>
+        <v>53680</v>
       </c>
       <c r="L29" t="n">
-        <v>53933.5</v>
+        <v>53839.5</v>
       </c>
       <c r="M29" t="n">
-        <v>54152</v>
+        <v>53934</v>
       </c>
       <c r="N29" t="n">
-        <v>54370.5</v>
+        <v>54028.5</v>
       </c>
       <c r="O29" t="n">
-        <v>54583</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
+        <v>54253</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2987,74 +2987,70 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>53790</v>
+        <v>53501</v>
       </c>
       <c r="C30" t="n">
-        <v>53840</v>
+        <v>53594</v>
       </c>
       <c r="D30" t="n">
-        <v>53464</v>
+        <v>53311</v>
       </c>
       <c r="E30" t="n">
-        <v>53544</v>
+        <v>53403</v>
       </c>
       <c r="F30" t="n">
-        <v>-263</v>
+        <v>-141</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0049</v>
+        <v>-0.0026</v>
       </c>
       <c r="H30" t="n">
-        <v>376</v>
+        <v>283</v>
       </c>
       <c r="I30" t="n">
-        <v>53491</v>
+        <v>53088</v>
       </c>
       <c r="J30" t="n">
-        <v>53520.5</v>
+        <v>53114</v>
       </c>
       <c r="K30" t="n">
-        <v>53680</v>
+        <v>53356</v>
       </c>
       <c r="L30" t="n">
-        <v>53839.5</v>
+        <v>53598</v>
       </c>
       <c r="M30" t="n">
-        <v>53934</v>
+        <v>53732</v>
       </c>
       <c r="N30" t="n">
-        <v>54028.5</v>
+        <v>53866</v>
       </c>
       <c r="O30" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q30" s="6" t="inlineStr">
+        <v>54216</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3082,50 +3078,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>53501</v>
+        <v>53408</v>
       </c>
       <c r="C31" t="n">
-        <v>53594</v>
+        <v>53780</v>
       </c>
       <c r="D31" t="n">
-        <v>53311</v>
+        <v>53337</v>
       </c>
       <c r="E31" t="n">
-        <v>53403</v>
+        <v>53530</v>
       </c>
       <c r="F31" t="n">
-        <v>-141</v>
+        <v>127</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0026</v>
+        <v>0.0024</v>
       </c>
       <c r="H31" t="n">
-        <v>283</v>
+        <v>443</v>
       </c>
       <c r="I31" t="n">
-        <v>53088</v>
+        <v>53028</v>
       </c>
       <c r="J31" t="n">
-        <v>53114</v>
+        <v>53095.25</v>
       </c>
       <c r="K31" t="n">
-        <v>53356</v>
+        <v>53261.5</v>
       </c>
       <c r="L31" t="n">
-        <v>53598</v>
+        <v>53427.75</v>
       </c>
       <c r="M31" t="n">
-        <v>53732</v>
+        <v>53544.5</v>
       </c>
       <c r="N31" t="n">
-        <v>53866</v>
+        <v>53661.25</v>
       </c>
       <c r="O31" t="n">
-        <v>54216</v>
+        <v>53877</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3133,21 +3129,23 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3157,90 +3155,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>53408</v>
+        <v>53529</v>
       </c>
       <c r="C32" t="n">
-        <v>53780</v>
+        <v>53589</v>
       </c>
       <c r="D32" t="n">
-        <v>53337</v>
+        <v>52812</v>
       </c>
       <c r="E32" t="n">
-        <v>53530</v>
+        <v>52849</v>
       </c>
       <c r="F32" t="n">
-        <v>127</v>
+        <v>-681</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0024</v>
+        <v>-0.0127</v>
       </c>
       <c r="H32" t="n">
-        <v>443</v>
+        <v>777</v>
       </c>
       <c r="I32" t="n">
-        <v>53028</v>
+        <v>52894</v>
       </c>
       <c r="J32" t="n">
-        <v>53095.25</v>
+        <v>53072.75</v>
       </c>
       <c r="K32" t="n">
-        <v>53261.5</v>
+        <v>53308.5</v>
       </c>
       <c r="L32" t="n">
-        <v>53427.75</v>
+        <v>53544.25</v>
       </c>
       <c r="M32" t="n">
-        <v>53544.5</v>
+        <v>53751.5</v>
       </c>
       <c r="N32" t="n">
-        <v>53661.25</v>
+        <v>53958.75</v>
       </c>
       <c r="O32" t="n">
-        <v>53877</v>
-      </c>
-      <c r="P32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+        <v>54223</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W32" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr"/>
@@ -3248,77 +3244,75 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>53529</v>
+        <v>52876</v>
       </c>
       <c r="C33" t="n">
-        <v>53589</v>
+        <v>53418</v>
       </c>
       <c r="D33" t="n">
-        <v>52812</v>
+        <v>52838</v>
       </c>
       <c r="E33" t="n">
-        <v>52849</v>
+        <v>53353</v>
       </c>
       <c r="F33" t="n">
-        <v>-681</v>
+        <v>504</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0127</v>
+        <v>0.0095</v>
       </c>
       <c r="H33" t="n">
-        <v>777</v>
+        <v>580</v>
       </c>
       <c r="I33" t="n">
-        <v>52894</v>
+        <v>52035</v>
       </c>
       <c r="J33" t="n">
-        <v>53072.75</v>
+        <v>51896.25</v>
       </c>
       <c r="K33" t="n">
-        <v>53308.5</v>
+        <v>52460.5</v>
       </c>
       <c r="L33" t="n">
-        <v>53544.25</v>
+        <v>53024.75</v>
       </c>
       <c r="M33" t="n">
-        <v>53751.5</v>
+        <v>53237.5</v>
       </c>
       <c r="N33" t="n">
-        <v>53958.75</v>
+        <v>53450.25</v>
       </c>
       <c r="O33" t="n">
-        <v>54223</v>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
+        <v>54366</v>
+      </c>
+      <c r="P33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
@@ -3327,55 +3321,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>52876</v>
+        <v>53367</v>
       </c>
       <c r="C34" t="n">
-        <v>53418</v>
+        <v>53567</v>
       </c>
       <c r="D34" t="n">
-        <v>52838</v>
+        <v>53210</v>
       </c>
       <c r="E34" t="n">
-        <v>53353</v>
+        <v>53489</v>
       </c>
       <c r="F34" t="n">
-        <v>504</v>
+        <v>136</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0095</v>
+        <v>0.0025</v>
       </c>
       <c r="H34" t="n">
-        <v>580</v>
+        <v>357</v>
       </c>
       <c r="I34" t="n">
-        <v>52035</v>
+        <v>52258</v>
       </c>
       <c r="J34" t="n">
-        <v>51896.25</v>
+        <v>52885.5</v>
       </c>
       <c r="K34" t="n">
-        <v>52460.5</v>
+        <v>53063</v>
       </c>
       <c r="L34" t="n">
-        <v>53024.75</v>
+        <v>53240.5</v>
       </c>
       <c r="M34" t="n">
-        <v>53237.5</v>
+        <v>53643</v>
       </c>
       <c r="N34" t="n">
-        <v>53450.25</v>
+        <v>54045.5</v>
       </c>
       <c r="O34" t="n">
-        <v>54366</v>
+        <v>53998</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3386,21 +3384,19 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
@@ -3411,57 +3407,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>53367</v>
+        <v>53524</v>
       </c>
       <c r="C35" t="n">
-        <v>53567</v>
+        <v>53797</v>
       </c>
       <c r="D35" t="n">
-        <v>53210</v>
+        <v>53426</v>
       </c>
       <c r="E35" t="n">
-        <v>53489</v>
+        <v>53645</v>
       </c>
       <c r="F35" t="n">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0025</v>
+        <v>0.0029</v>
       </c>
       <c r="H35" t="n">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="I35" t="n">
-        <v>52258</v>
+        <v>52853</v>
       </c>
       <c r="J35" t="n">
-        <v>52885.5</v>
+        <v>53182.25</v>
       </c>
       <c r="K35" t="n">
-        <v>53063</v>
+        <v>53310.5</v>
       </c>
       <c r="L35" t="n">
-        <v>53240.5</v>
+        <v>53438.75</v>
       </c>
       <c r="M35" t="n">
-        <v>53643</v>
+        <v>53667.5</v>
       </c>
       <c r="N35" t="n">
-        <v>54045.5</v>
+        <v>53896.25</v>
       </c>
       <c r="O35" t="n">
-        <v>53998</v>
+        <v>53924</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3472,7 +3468,7 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="10" t="inlineStr">
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3502,50 +3498,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>53524</v>
+        <v>53643</v>
       </c>
       <c r="C36" t="n">
-        <v>53797</v>
+        <v>53778</v>
       </c>
       <c r="D36" t="n">
-        <v>53426</v>
+        <v>53435</v>
       </c>
       <c r="E36" t="n">
-        <v>53645</v>
+        <v>53521</v>
       </c>
       <c r="F36" t="n">
-        <v>156</v>
+        <v>-124</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0029</v>
+        <v>-0.0023</v>
       </c>
       <c r="H36" t="n">
-        <v>371</v>
+        <v>343</v>
       </c>
       <c r="I36" t="n">
-        <v>52853</v>
+        <v>53055</v>
       </c>
       <c r="J36" t="n">
-        <v>53182.25</v>
+        <v>53290.75</v>
       </c>
       <c r="K36" t="n">
-        <v>53310.5</v>
+        <v>53459.5</v>
       </c>
       <c r="L36" t="n">
-        <v>53438.75</v>
+        <v>53628.25</v>
       </c>
       <c r="M36" t="n">
-        <v>53667.5</v>
+        <v>53830.5</v>
       </c>
       <c r="N36" t="n">
-        <v>53896.25</v>
+        <v>54032.75</v>
       </c>
       <c r="O36" t="n">
-        <v>53924</v>
+        <v>54168</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3553,18 +3549,18 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3579,57 +3575,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>53643</v>
+        <v>53724</v>
       </c>
       <c r="C37" t="n">
-        <v>53778</v>
+        <v>53811</v>
       </c>
       <c r="D37" t="n">
-        <v>53435</v>
+        <v>53369</v>
       </c>
       <c r="E37" t="n">
-        <v>53521</v>
+        <v>53621</v>
       </c>
       <c r="F37" t="n">
-        <v>-124</v>
+        <v>100</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0023</v>
+        <v>0.0019</v>
       </c>
       <c r="H37" t="n">
-        <v>343</v>
+        <v>442</v>
       </c>
       <c r="I37" t="n">
-        <v>53055</v>
+        <v>53092</v>
       </c>
       <c r="J37" t="n">
-        <v>53290.75</v>
+        <v>53135.25</v>
       </c>
       <c r="K37" t="n">
-        <v>53459.5</v>
+        <v>53349.5</v>
       </c>
       <c r="L37" t="n">
-        <v>53628.25</v>
+        <v>53563.75</v>
       </c>
       <c r="M37" t="n">
-        <v>53830.5</v>
+        <v>53692.5</v>
       </c>
       <c r="N37" t="n">
-        <v>54032.75</v>
+        <v>53821.25</v>
       </c>
       <c r="O37" t="n">
-        <v>54168</v>
+        <v>54121</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3637,18 +3633,18 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R37" s="6" t="n">
+        <v/>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3663,57 +3659,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>53724</v>
+        <v>53608</v>
       </c>
       <c r="C38" t="n">
-        <v>53811</v>
+        <v>53862</v>
       </c>
       <c r="D38" t="n">
-        <v>53369</v>
+        <v>53513</v>
       </c>
       <c r="E38" t="n">
-        <v>53621</v>
+        <v>53584</v>
       </c>
       <c r="F38" t="n">
-        <v>100</v>
+        <v>-37</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.0007</v>
       </c>
       <c r="H38" t="n">
-        <v>442</v>
+        <v>349</v>
       </c>
       <c r="I38" t="n">
-        <v>53092</v>
+        <v>52927</v>
       </c>
       <c r="J38" t="n">
-        <v>53135.25</v>
+        <v>53194.5</v>
       </c>
       <c r="K38" t="n">
-        <v>53349.5</v>
+        <v>53400</v>
       </c>
       <c r="L38" t="n">
-        <v>53563.75</v>
+        <v>53605.5</v>
       </c>
       <c r="M38" t="n">
-        <v>53692.5</v>
+        <v>53842</v>
       </c>
       <c r="N38" t="n">
-        <v>53821.25</v>
+        <v>54078.5</v>
       </c>
       <c r="O38" t="n">
-        <v>54121</v>
+        <v>54253</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3726,7 +3722,7 @@
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
@@ -3754,70 +3750,74 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>53608</v>
+        <v>53664</v>
       </c>
       <c r="C39" t="n">
-        <v>53862</v>
+        <v>53664</v>
       </c>
       <c r="D39" t="n">
-        <v>53513</v>
+        <v>53149</v>
       </c>
       <c r="E39" t="n">
-        <v>53584</v>
+        <v>53240</v>
       </c>
       <c r="F39" t="n">
-        <v>-37</v>
+        <v>-344</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0064</v>
       </c>
       <c r="H39" t="n">
-        <v>349</v>
+        <v>515</v>
       </c>
       <c r="I39" t="n">
-        <v>52927</v>
+        <v>53164</v>
       </c>
       <c r="J39" t="n">
-        <v>53194.5</v>
+        <v>53183.25</v>
       </c>
       <c r="K39" t="n">
-        <v>53400</v>
+        <v>53409.5</v>
       </c>
       <c r="L39" t="n">
-        <v>53605.5</v>
+        <v>53635.75</v>
       </c>
       <c r="M39" t="n">
-        <v>53842</v>
+        <v>53758.5</v>
       </c>
       <c r="N39" t="n">
-        <v>54078.5</v>
+        <v>53881.25</v>
       </c>
       <c r="O39" t="n">
-        <v>54253</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
+        <v>54211</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3829,76 +3829,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>53664</v>
+        <v>53259</v>
       </c>
       <c r="C40" t="n">
-        <v>53664</v>
+        <v>53343</v>
       </c>
       <c r="D40" t="n">
-        <v>53149</v>
+        <v>52747</v>
       </c>
       <c r="E40" t="n">
-        <v>53240</v>
+        <v>52828</v>
       </c>
       <c r="F40" t="n">
-        <v>-344</v>
+        <v>-412</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0064</v>
+        <v>-0.0077</v>
       </c>
       <c r="H40" t="n">
-        <v>515</v>
+        <v>596</v>
       </c>
       <c r="I40" t="n">
-        <v>53164</v>
+        <v>52634</v>
       </c>
       <c r="J40" t="n">
-        <v>53183.25</v>
+        <v>52641.75</v>
       </c>
       <c r="K40" t="n">
-        <v>53409.5</v>
+        <v>52982.5</v>
       </c>
       <c r="L40" t="n">
-        <v>53635.75</v>
+        <v>53323.25</v>
       </c>
       <c r="M40" t="n">
-        <v>53758.5</v>
+        <v>53497.5</v>
       </c>
       <c r="N40" t="n">
-        <v>53881.25</v>
+        <v>53671.75</v>
       </c>
       <c r="O40" t="n">
-        <v>54211</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q40" s="6" t="inlineStr">
+        <v>54179</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3922,50 +3914,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>53259</v>
+        <v>52844</v>
       </c>
       <c r="C41" t="n">
-        <v>53343</v>
+        <v>53283</v>
       </c>
       <c r="D41" t="n">
-        <v>52747</v>
+        <v>52720</v>
       </c>
       <c r="E41" t="n">
-        <v>52828</v>
+        <v>53121</v>
       </c>
       <c r="F41" t="n">
-        <v>-412</v>
+        <v>293</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0077</v>
+        <v>0.0055</v>
       </c>
       <c r="H41" t="n">
-        <v>596</v>
+        <v>563</v>
       </c>
       <c r="I41" t="n">
-        <v>52634</v>
+        <v>52151</v>
       </c>
       <c r="J41" t="n">
-        <v>52641.75</v>
+        <v>52123.5</v>
       </c>
       <c r="K41" t="n">
-        <v>52982.5</v>
+        <v>52530</v>
       </c>
       <c r="L41" t="n">
-        <v>53323.25</v>
+        <v>52936.5</v>
       </c>
       <c r="M41" t="n">
-        <v>53497.5</v>
+        <v>53126</v>
       </c>
       <c r="N41" t="n">
-        <v>53671.75</v>
+        <v>53315.5</v>
       </c>
       <c r="O41" t="n">
-        <v>54179</v>
+        <v>53939</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3973,19 +3965,19 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
@@ -3997,55 +3989,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>52844</v>
+        <v>53120</v>
       </c>
       <c r="C42" t="n">
-        <v>53283</v>
+        <v>53827</v>
       </c>
       <c r="D42" t="n">
-        <v>52720</v>
+        <v>53093</v>
       </c>
       <c r="E42" t="n">
-        <v>53121</v>
+        <v>53745</v>
       </c>
       <c r="F42" t="n">
-        <v>293</v>
+        <v>624</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0055</v>
+        <v>0.0117</v>
       </c>
       <c r="H42" t="n">
-        <v>563</v>
+        <v>734</v>
       </c>
       <c r="I42" t="n">
-        <v>52151</v>
+        <v>52157</v>
       </c>
       <c r="J42" t="n">
-        <v>52123.5</v>
+        <v>52617.75</v>
       </c>
       <c r="K42" t="n">
-        <v>52530</v>
+        <v>52839.5</v>
       </c>
       <c r="L42" t="n">
-        <v>52936.5</v>
+        <v>53061.25</v>
       </c>
       <c r="M42" t="n">
-        <v>53126</v>
+        <v>53402.5</v>
       </c>
       <c r="N42" t="n">
-        <v>53315.5</v>
+        <v>53743.75</v>
       </c>
       <c r="O42" t="n">
-        <v>53939</v>
+        <v>53846</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4056,80 +4052,78 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="10" t="inlineStr">
+      <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W42" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>53120</v>
+        <v>53707</v>
       </c>
       <c r="C43" t="n">
-        <v>53827</v>
+        <v>53772</v>
       </c>
       <c r="D43" t="n">
-        <v>53093</v>
+        <v>53235</v>
       </c>
       <c r="E43" t="n">
-        <v>53745</v>
+        <v>53440</v>
       </c>
       <c r="F43" t="n">
-        <v>624</v>
+        <v>-305</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0117</v>
+        <v>-0.0057</v>
       </c>
       <c r="H43" t="n">
-        <v>734</v>
+        <v>537</v>
       </c>
       <c r="I43" t="n">
-        <v>52157</v>
+        <v>52359</v>
       </c>
       <c r="J43" t="n">
-        <v>52617.75</v>
+        <v>53153.5</v>
       </c>
       <c r="K43" t="n">
-        <v>52839.5</v>
+        <v>53378</v>
       </c>
       <c r="L43" t="n">
-        <v>53061.25</v>
+        <v>53602.5</v>
       </c>
       <c r="M43" t="n">
-        <v>53402.5</v>
+        <v>54112</v>
       </c>
       <c r="N43" t="n">
-        <v>53743.75</v>
+        <v>54621.5</v>
       </c>
       <c r="O43" t="n">
-        <v>53846</v>
+        <v>54561</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4137,23 +4131,21 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4163,68 +4155,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>53707</v>
+        <v>53261</v>
       </c>
       <c r="C44" t="n">
-        <v>53772</v>
+        <v>53336</v>
       </c>
       <c r="D44" t="n">
-        <v>53235</v>
+        <v>52758</v>
       </c>
       <c r="E44" t="n">
-        <v>53440</v>
+        <v>52832</v>
       </c>
       <c r="F44" t="n">
-        <v>-305</v>
+        <v>-608</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0057</v>
+        <v>-0.0114</v>
       </c>
       <c r="H44" t="n">
-        <v>537</v>
+        <v>578</v>
       </c>
       <c r="I44" t="n">
-        <v>52359</v>
+        <v>52698</v>
       </c>
       <c r="J44" t="n">
-        <v>53153.5</v>
+        <v>52871.25</v>
       </c>
       <c r="K44" t="n">
-        <v>53378</v>
+        <v>53171.5</v>
       </c>
       <c r="L44" t="n">
-        <v>53602.5</v>
+        <v>53471.75</v>
       </c>
       <c r="M44" t="n">
-        <v>54112</v>
+        <v>53708.5</v>
       </c>
       <c r="N44" t="n">
-        <v>54621.5</v>
+        <v>53945.25</v>
       </c>
       <c r="O44" t="n">
-        <v>54561</v>
+        <v>54309</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4238,79 +4236,73 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W44" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>53261</v>
+        <v>52817</v>
       </c>
       <c r="C45" t="n">
-        <v>53336</v>
+        <v>52859</v>
       </c>
       <c r="D45" t="n">
-        <v>52758</v>
+        <v>52339</v>
       </c>
       <c r="E45" t="n">
-        <v>52832</v>
+        <v>52425</v>
       </c>
       <c r="F45" t="n">
-        <v>-608</v>
+        <v>-407</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0114</v>
+        <v>-0.0077</v>
       </c>
       <c r="H45" t="n">
-        <v>578</v>
+        <v>520</v>
       </c>
       <c r="I45" t="n">
-        <v>52698</v>
+        <v>52180</v>
       </c>
       <c r="J45" t="n">
-        <v>52871.25</v>
+        <v>52146.5</v>
       </c>
       <c r="K45" t="n">
-        <v>53171.5</v>
+        <v>52543</v>
       </c>
       <c r="L45" t="n">
-        <v>53471.75</v>
+        <v>52939.5</v>
       </c>
       <c r="M45" t="n">
-        <v>53708.5</v>
+        <v>53121</v>
       </c>
       <c r="N45" t="n">
-        <v>53945.25</v>
+        <v>53302.5</v>
       </c>
       <c r="O45" t="n">
-        <v>54309</v>
+        <v>53914</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
+      <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4334,50 +4326,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>52817</v>
+        <v>52473</v>
       </c>
       <c r="C46" t="n">
-        <v>52859</v>
+        <v>52676</v>
       </c>
       <c r="D46" t="n">
-        <v>52339</v>
+        <v>51992</v>
       </c>
       <c r="E46" t="n">
-        <v>52425</v>
+        <v>52095</v>
       </c>
       <c r="F46" t="n">
-        <v>-407</v>
+        <v>-330</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0077</v>
+        <v>-0.0063</v>
       </c>
       <c r="H46" t="n">
-        <v>520</v>
+        <v>684</v>
       </c>
       <c r="I46" t="n">
-        <v>52180</v>
+        <v>51819</v>
       </c>
       <c r="J46" t="n">
-        <v>52146.5</v>
+        <v>51818</v>
       </c>
       <c r="K46" t="n">
-        <v>52543</v>
+        <v>52165</v>
       </c>
       <c r="L46" t="n">
-        <v>52939.5</v>
+        <v>52512</v>
       </c>
       <c r="M46" t="n">
-        <v>53121</v>
+        <v>52685</v>
       </c>
       <c r="N46" t="n">
-        <v>53302.5</v>
+        <v>52858</v>
       </c>
       <c r="O46" t="n">
-        <v>53914</v>
+        <v>53379</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4390,7 +4382,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4414,50 +4406,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>52473</v>
+        <v>52059</v>
       </c>
       <c r="C47" t="n">
-        <v>52676</v>
+        <v>52739</v>
       </c>
       <c r="D47" t="n">
-        <v>51992</v>
+        <v>52059</v>
       </c>
       <c r="E47" t="n">
-        <v>52095</v>
+        <v>52585</v>
       </c>
       <c r="F47" t="n">
-        <v>-330</v>
+        <v>490</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0063</v>
+        <v>0.0094</v>
       </c>
       <c r="H47" t="n">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="I47" t="n">
-        <v>51819</v>
+        <v>51308</v>
       </c>
       <c r="J47" t="n">
-        <v>51818</v>
+        <v>51291.5</v>
       </c>
       <c r="K47" t="n">
-        <v>52165</v>
+        <v>51753</v>
       </c>
       <c r="L47" t="n">
-        <v>52512</v>
+        <v>52214.5</v>
       </c>
       <c r="M47" t="n">
-        <v>52685</v>
+        <v>52437</v>
       </c>
       <c r="N47" t="n">
-        <v>52858</v>
+        <v>52659.5</v>
       </c>
       <c r="O47" t="n">
-        <v>53379</v>
+        <v>53360</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4465,22 +4457,24 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
@@ -4489,55 +4483,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>52059</v>
+        <v>52376</v>
       </c>
       <c r="C48" t="n">
-        <v>52739</v>
+        <v>52672</v>
       </c>
       <c r="D48" t="n">
-        <v>52059</v>
+        <v>52226</v>
       </c>
       <c r="E48" t="n">
-        <v>52585</v>
+        <v>52440</v>
       </c>
       <c r="F48" t="n">
-        <v>490</v>
+        <v>-145</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0094</v>
+        <v>-0.0028</v>
       </c>
       <c r="H48" t="n">
-        <v>680</v>
+        <v>446</v>
       </c>
       <c r="I48" t="n">
-        <v>51308</v>
+        <v>51379</v>
       </c>
       <c r="J48" t="n">
-        <v>51291.5</v>
+        <v>51998</v>
       </c>
       <c r="K48" t="n">
-        <v>51753</v>
+        <v>52245</v>
       </c>
       <c r="L48" t="n">
-        <v>52214.5</v>
+        <v>52492</v>
       </c>
       <c r="M48" t="n">
-        <v>52437</v>
+        <v>52925</v>
       </c>
       <c r="N48" t="n">
-        <v>52659.5</v>
+        <v>53358</v>
       </c>
       <c r="O48" t="n">
-        <v>53360</v>
+        <v>53419</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4545,23 +4543,21 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4573,72 +4569,74 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>52376</v>
+        <v>52499</v>
       </c>
       <c r="C49" t="n">
-        <v>52672</v>
+        <v>52499</v>
       </c>
       <c r="D49" t="n">
-        <v>52226</v>
+        <v>51908</v>
       </c>
       <c r="E49" t="n">
-        <v>52440</v>
+        <v>52115</v>
       </c>
       <c r="F49" t="n">
-        <v>-145</v>
+        <v>-325</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0028</v>
+        <v>-0.0062</v>
       </c>
       <c r="H49" t="n">
-        <v>446</v>
+        <v>591</v>
       </c>
       <c r="I49" t="n">
-        <v>51379</v>
+        <v>51780</v>
       </c>
       <c r="J49" t="n">
-        <v>51998</v>
+        <v>51989.5</v>
       </c>
       <c r="K49" t="n">
-        <v>52245</v>
+        <v>52217</v>
       </c>
       <c r="L49" t="n">
-        <v>52492</v>
+        <v>52444.5</v>
       </c>
       <c r="M49" t="n">
-        <v>52925</v>
+        <v>52663</v>
       </c>
       <c r="N49" t="n">
-        <v>53358</v>
+        <v>52881.5</v>
       </c>
       <c r="O49" t="n">
-        <v>53419</v>
+        <v>53118</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4655,74 +4653,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>52499</v>
+        <v>52162</v>
       </c>
       <c r="C50" t="n">
-        <v>52499</v>
+        <v>52298</v>
       </c>
       <c r="D50" t="n">
-        <v>51908</v>
+        <v>51209</v>
       </c>
       <c r="E50" t="n">
-        <v>52115</v>
+        <v>51507</v>
       </c>
       <c r="F50" t="n">
-        <v>-325</v>
+        <v>-608</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0062</v>
+        <v>-0.0117</v>
       </c>
       <c r="H50" t="n">
-        <v>591</v>
+        <v>1089</v>
       </c>
       <c r="I50" t="n">
-        <v>51780</v>
+        <v>51317</v>
       </c>
       <c r="J50" t="n">
-        <v>51989.5</v>
+        <v>51479.75</v>
       </c>
       <c r="K50" t="n">
-        <v>52217</v>
+        <v>51819.5</v>
       </c>
       <c r="L50" t="n">
-        <v>52444.5</v>
+        <v>52159.25</v>
       </c>
       <c r="M50" t="n">
-        <v>52663</v>
+        <v>52410.5</v>
       </c>
       <c r="N50" t="n">
-        <v>52881.5</v>
+        <v>52661.75</v>
       </c>
       <c r="O50" t="n">
-        <v>53118</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
+        <v>53090</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q50" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4746,74 +4742,70 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>52162</v>
+        <v>51486</v>
       </c>
       <c r="C51" t="n">
-        <v>52298</v>
+        <v>52169</v>
       </c>
       <c r="D51" t="n">
-        <v>51209</v>
+        <v>51455</v>
       </c>
       <c r="E51" t="n">
-        <v>51507</v>
+        <v>51807</v>
       </c>
       <c r="F51" t="n">
-        <v>-608</v>
+        <v>300</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0117</v>
+        <v>0.0058</v>
       </c>
       <c r="H51" t="n">
-        <v>1089</v>
+        <v>714</v>
       </c>
       <c r="I51" t="n">
-        <v>51317</v>
+        <v>50120</v>
       </c>
       <c r="J51" t="n">
-        <v>51479.75</v>
+        <v>50294.75</v>
       </c>
       <c r="K51" t="n">
-        <v>51819.5</v>
+        <v>50962.5</v>
       </c>
       <c r="L51" t="n">
-        <v>52159.25</v>
+        <v>51630.25</v>
       </c>
       <c r="M51" t="n">
-        <v>52410.5</v>
+        <v>52051.5</v>
       </c>
       <c r="N51" t="n">
-        <v>52661.75</v>
+        <v>52472.75</v>
       </c>
       <c r="O51" t="n">
-        <v>53090</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
+        <v>53387</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
       <c r="U51" s="8" t="n">
         <v/>
       </c>
@@ -4825,55 +4817,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>51486</v>
+        <v>51800</v>
       </c>
       <c r="C52" t="n">
-        <v>52169</v>
+        <v>51957</v>
       </c>
       <c r="D52" t="n">
-        <v>51455</v>
+        <v>51576</v>
       </c>
       <c r="E52" t="n">
-        <v>51807</v>
+        <v>51761</v>
       </c>
       <c r="F52" t="n">
-        <v>300</v>
+        <v>-46</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0009</v>
       </c>
       <c r="H52" t="n">
-        <v>714</v>
+        <v>381</v>
       </c>
       <c r="I52" t="n">
-        <v>50120</v>
+        <v>50741</v>
       </c>
       <c r="J52" t="n">
-        <v>50294.75</v>
+        <v>51090.5</v>
       </c>
       <c r="K52" t="n">
-        <v>50962.5</v>
+        <v>51450</v>
       </c>
       <c r="L52" t="n">
-        <v>51630.25</v>
+        <v>51809.5</v>
       </c>
       <c r="M52" t="n">
-        <v>52051.5</v>
+        <v>52164</v>
       </c>
       <c r="N52" t="n">
-        <v>52472.75</v>
+        <v>52518.5</v>
       </c>
       <c r="O52" t="n">
-        <v>53387</v>
+        <v>52883</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4886,13 +4882,11 @@
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4907,57 +4901,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>51800</v>
+        <v>52085</v>
       </c>
       <c r="C53" t="n">
-        <v>51957</v>
+        <v>52557</v>
       </c>
       <c r="D53" t="n">
-        <v>51576</v>
+        <v>52080</v>
       </c>
       <c r="E53" t="n">
-        <v>51761</v>
+        <v>52475</v>
       </c>
       <c r="F53" t="n">
-        <v>-46</v>
+        <v>714</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0138</v>
       </c>
       <c r="H53" t="n">
-        <v>381</v>
+        <v>477</v>
       </c>
       <c r="I53" t="n">
-        <v>50741</v>
+        <v>51195</v>
       </c>
       <c r="J53" t="n">
-        <v>51090.5</v>
+        <v>51377.25</v>
       </c>
       <c r="K53" t="n">
-        <v>51450</v>
+        <v>51570.5</v>
       </c>
       <c r="L53" t="n">
-        <v>51809.5</v>
+        <v>51763.75</v>
       </c>
       <c r="M53" t="n">
-        <v>52164</v>
+        <v>51951.5</v>
       </c>
       <c r="N53" t="n">
-        <v>52518.5</v>
+        <v>52139.25</v>
       </c>
       <c r="O53" t="n">
-        <v>52883</v>
+        <v>52338</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4970,76 +4964,78 @@
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W53" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V53" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W53" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>52085</v>
+        <v>52470</v>
       </c>
       <c r="C54" t="n">
-        <v>52557</v>
+        <v>52844</v>
       </c>
       <c r="D54" t="n">
-        <v>52080</v>
+        <v>52125</v>
       </c>
       <c r="E54" t="n">
-        <v>52475</v>
+        <v>52279</v>
       </c>
       <c r="F54" t="n">
-        <v>714</v>
+        <v>-196</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0138</v>
+        <v>-0.0037</v>
       </c>
       <c r="H54" t="n">
-        <v>477</v>
+        <v>719</v>
       </c>
       <c r="I54" t="n">
-        <v>51195</v>
+        <v>51603</v>
       </c>
       <c r="J54" t="n">
-        <v>51377.25</v>
+        <v>52076.25</v>
       </c>
       <c r="K54" t="n">
-        <v>51570.5</v>
+        <v>52236.5</v>
       </c>
       <c r="L54" t="n">
-        <v>51763.75</v>
+        <v>52396.75</v>
       </c>
       <c r="M54" t="n">
-        <v>51951.5</v>
+        <v>52713.5</v>
       </c>
       <c r="N54" t="n">
-        <v>52139.25</v>
+        <v>53030.25</v>
       </c>
       <c r="O54" t="n">
-        <v>52338</v>
+        <v>53034</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5047,12 +5043,14 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="inlineStr">
@@ -5060,70 +5058,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v/>
       </c>
       <c r="W54" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>52470</v>
+        <v>52255</v>
       </c>
       <c r="C55" t="n">
-        <v>52844</v>
+        <v>52371</v>
       </c>
       <c r="D55" t="n">
-        <v>52125</v>
+        <v>51844</v>
       </c>
       <c r="E55" t="n">
-        <v>52279</v>
+        <v>51873</v>
       </c>
       <c r="F55" t="n">
-        <v>-196</v>
+        <v>-406</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0037</v>
+        <v>-0.0078</v>
       </c>
       <c r="H55" t="n">
-        <v>719</v>
+        <v>527</v>
       </c>
       <c r="I55" t="n">
-        <v>51603</v>
+        <v>51406</v>
       </c>
       <c r="J55" t="n">
-        <v>52076.25</v>
+        <v>51457.25</v>
       </c>
       <c r="K55" t="n">
-        <v>52236.5</v>
+        <v>51919.5</v>
       </c>
       <c r="L55" t="n">
-        <v>52396.75</v>
+        <v>52381.75</v>
       </c>
       <c r="M55" t="n">
-        <v>52713.5</v>
+        <v>52638.5</v>
       </c>
       <c r="N55" t="n">
-        <v>53030.25</v>
+        <v>52895.25</v>
       </c>
       <c r="O55" t="n">
-        <v>53034</v>
+        <v>53563</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5136,15 +5134,13 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S55" s="7" t="inlineStr">
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5159,57 +5155,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>52255</v>
+        <v>51878</v>
       </c>
       <c r="C56" t="n">
-        <v>52371</v>
+        <v>51905</v>
       </c>
       <c r="D56" t="n">
-        <v>51844</v>
+        <v>51479</v>
       </c>
       <c r="E56" t="n">
-        <v>51873</v>
+        <v>51717</v>
       </c>
       <c r="F56" t="n">
-        <v>-406</v>
+        <v>-156</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0078</v>
+        <v>-0.003</v>
       </c>
       <c r="H56" t="n">
-        <v>527</v>
+        <v>426</v>
       </c>
       <c r="I56" t="n">
-        <v>51406</v>
+        <v>51317</v>
       </c>
       <c r="J56" t="n">
-        <v>51457.25</v>
+        <v>51228.75</v>
       </c>
       <c r="K56" t="n">
-        <v>51919.5</v>
+        <v>51609.5</v>
       </c>
       <c r="L56" t="n">
-        <v>52381.75</v>
+        <v>51990.25</v>
       </c>
       <c r="M56" t="n">
-        <v>52638.5</v>
+        <v>52136.5</v>
       </c>
       <c r="N56" t="n">
-        <v>52895.25</v>
+        <v>52282.75</v>
       </c>
       <c r="O56" t="n">
-        <v>53563</v>
+        <v>52898</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5222,7 +5218,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S56" s="7" t="inlineStr">
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5250,50 +5246,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>51878</v>
+        <v>51655</v>
       </c>
       <c r="C57" t="n">
-        <v>51905</v>
+        <v>52223</v>
       </c>
       <c r="D57" t="n">
-        <v>51479</v>
+        <v>51610</v>
       </c>
       <c r="E57" t="n">
-        <v>51717</v>
+        <v>52163</v>
       </c>
       <c r="F57" t="n">
-        <v>-156</v>
+        <v>446</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.0086</v>
       </c>
       <c r="H57" t="n">
-        <v>426</v>
+        <v>613</v>
       </c>
       <c r="I57" t="n">
-        <v>51317</v>
+        <v>51053</v>
       </c>
       <c r="J57" t="n">
-        <v>51228.75</v>
+        <v>51303.5</v>
       </c>
       <c r="K57" t="n">
-        <v>51609.5</v>
+        <v>51504</v>
       </c>
       <c r="L57" t="n">
-        <v>51990.25</v>
+        <v>51704.5</v>
       </c>
       <c r="M57" t="n">
-        <v>52136.5</v>
+        <v>51930</v>
       </c>
       <c r="N57" t="n">
-        <v>52282.75</v>
+        <v>52155.5</v>
       </c>
       <c r="O57" t="n">
-        <v>52898</v>
+        <v>52331</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5301,22 +5297,24 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
@@ -5325,59 +5323,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>51655</v>
+        <v>52140</v>
       </c>
       <c r="C58" t="n">
-        <v>52223</v>
+        <v>52153</v>
       </c>
       <c r="D58" t="n">
-        <v>51610</v>
+        <v>51744</v>
       </c>
       <c r="E58" t="n">
-        <v>52163</v>
+        <v>51837</v>
       </c>
       <c r="F58" t="n">
-        <v>446</v>
+        <v>-326</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.0062</v>
       </c>
       <c r="H58" t="n">
-        <v>613</v>
+        <v>409</v>
       </c>
       <c r="I58" t="n">
-        <v>51053</v>
+        <v>50997</v>
       </c>
       <c r="J58" t="n">
-        <v>51303.5</v>
+        <v>51673.25</v>
       </c>
       <c r="K58" t="n">
-        <v>51504</v>
+        <v>51856.5</v>
       </c>
       <c r="L58" t="n">
-        <v>51704.5</v>
+        <v>52039.75</v>
       </c>
       <c r="M58" t="n">
-        <v>51930</v>
+        <v>52469.5</v>
       </c>
       <c r="N58" t="n">
-        <v>52155.5</v>
+        <v>52899.25</v>
       </c>
       <c r="O58" t="n">
-        <v>52331</v>
+        <v>52836</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5385,23 +5379,21 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
@@ -5411,55 +5403,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>52140</v>
+        <v>51845</v>
       </c>
       <c r="C59" t="n">
-        <v>52153</v>
+        <v>52002</v>
       </c>
       <c r="D59" t="n">
-        <v>51744</v>
+        <v>51459</v>
       </c>
       <c r="E59" t="n">
-        <v>51837</v>
+        <v>51702</v>
       </c>
       <c r="F59" t="n">
-        <v>-326</v>
+        <v>-135</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0062</v>
+        <v>-0.0026</v>
       </c>
       <c r="H59" t="n">
-        <v>409</v>
+        <v>543</v>
       </c>
       <c r="I59" t="n">
-        <v>50997</v>
+        <v>51335</v>
       </c>
       <c r="J59" t="n">
-        <v>51673.25</v>
+        <v>51372.25</v>
       </c>
       <c r="K59" t="n">
-        <v>51856.5</v>
+        <v>51632.5</v>
       </c>
       <c r="L59" t="n">
-        <v>52039.75</v>
+        <v>51892.75</v>
       </c>
       <c r="M59" t="n">
-        <v>52469.5</v>
+        <v>52041.5</v>
       </c>
       <c r="N59" t="n">
-        <v>52899.25</v>
+        <v>52190.25</v>
       </c>
       <c r="O59" t="n">
-        <v>52836</v>
+        <v>52562</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5472,7 +5468,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S59" s="7" t="inlineStr">
+      <c r="S59" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5493,76 +5489,80 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>51845</v>
+        <v>51765</v>
       </c>
       <c r="C60" t="n">
-        <v>52002</v>
+        <v>51997</v>
       </c>
       <c r="D60" t="n">
-        <v>51459</v>
+        <v>51218</v>
       </c>
       <c r="E60" t="n">
-        <v>51702</v>
+        <v>51278</v>
       </c>
       <c r="F60" t="n">
-        <v>-135</v>
+        <v>-424</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0026</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H60" t="n">
-        <v>543</v>
+        <v>779</v>
       </c>
       <c r="I60" t="n">
-        <v>51335</v>
+        <v>50916</v>
       </c>
       <c r="J60" t="n">
-        <v>51372.25</v>
+        <v>51144.75</v>
       </c>
       <c r="K60" t="n">
-        <v>51632.5</v>
+        <v>51430.5</v>
       </c>
       <c r="L60" t="n">
-        <v>51892.75</v>
+        <v>51716.25</v>
       </c>
       <c r="M60" t="n">
-        <v>52041.5</v>
+        <v>51973.5</v>
       </c>
       <c r="N60" t="n">
-        <v>52190.25</v>
+        <v>52230.75</v>
       </c>
       <c r="O60" t="n">
-        <v>52562</v>
+        <v>52545</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S60" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T60" s="8" t="n">
-        <v/>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5584,73 +5584,69 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>51765</v>
+        <v>51335</v>
       </c>
       <c r="C61" t="n">
-        <v>51997</v>
+        <v>51517</v>
       </c>
       <c r="D61" t="n">
-        <v>51218</v>
+        <v>50859</v>
       </c>
       <c r="E61" t="n">
-        <v>51278</v>
+        <v>51241</v>
       </c>
       <c r="F61" t="n">
-        <v>-424</v>
+        <v>-37</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>-0.0007</v>
       </c>
       <c r="H61" t="n">
-        <v>779</v>
+        <v>658</v>
       </c>
       <c r="I61" t="n">
-        <v>50916</v>
+        <v>50439</v>
       </c>
       <c r="J61" t="n">
-        <v>51144.75</v>
+        <v>50334.25</v>
       </c>
       <c r="K61" t="n">
-        <v>51430.5</v>
+        <v>50888.5</v>
       </c>
       <c r="L61" t="n">
-        <v>51716.25</v>
+        <v>51442.75</v>
       </c>
       <c r="M61" t="n">
-        <v>51973.5</v>
+        <v>51667.5</v>
       </c>
       <c r="N61" t="n">
-        <v>52230.75</v>
+        <v>51892.25</v>
       </c>
       <c r="O61" t="n">
-        <v>52545</v>
+        <v>52776</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q61" s="6" t="n">
+        <v/>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5672,50 +5668,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>51335</v>
+        <v>51251</v>
       </c>
       <c r="C62" t="n">
-        <v>51517</v>
+        <v>51805</v>
       </c>
       <c r="D62" t="n">
-        <v>50859</v>
+        <v>51208</v>
       </c>
       <c r="E62" t="n">
-        <v>51241</v>
+        <v>51477</v>
       </c>
       <c r="F62" t="n">
-        <v>-37</v>
+        <v>236</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0007</v>
+        <v>0.0046</v>
       </c>
       <c r="H62" t="n">
-        <v>658</v>
+        <v>597</v>
       </c>
       <c r="I62" t="n">
-        <v>50439</v>
+        <v>50201</v>
       </c>
       <c r="J62" t="n">
-        <v>50334.25</v>
+        <v>50609.5</v>
       </c>
       <c r="K62" t="n">
-        <v>50888.5</v>
+        <v>50912</v>
       </c>
       <c r="L62" t="n">
-        <v>51442.75</v>
+        <v>51214.5</v>
       </c>
       <c r="M62" t="n">
-        <v>51667.5</v>
+        <v>51570</v>
       </c>
       <c r="N62" t="n">
-        <v>51892.25</v>
+        <v>51925.5</v>
       </c>
       <c r="O62" t="n">
-        <v>52776</v>
+        <v>52175</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5723,18 +5719,18 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R62" s="6" t="n">
+        <v/>
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5747,59 +5743,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>51251</v>
+        <v>51608</v>
       </c>
       <c r="C63" t="n">
-        <v>51805</v>
+        <v>51625</v>
       </c>
       <c r="D63" t="n">
-        <v>51208</v>
+        <v>51600</v>
       </c>
       <c r="E63" t="n">
-        <v>51477</v>
+        <v>51609</v>
       </c>
       <c r="F63" t="n">
-        <v>236</v>
+        <v>132</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0046</v>
+        <v>0.0026</v>
       </c>
       <c r="H63" t="n">
-        <v>597</v>
+        <v>25</v>
       </c>
       <c r="I63" t="n">
-        <v>50201</v>
+        <v>50611</v>
       </c>
       <c r="J63" t="n">
-        <v>50609.5</v>
+        <v>50865.25</v>
       </c>
       <c r="K63" t="n">
-        <v>50912</v>
+        <v>51178.5</v>
       </c>
       <c r="L63" t="n">
-        <v>51214.5</v>
+        <v>51491.75</v>
       </c>
       <c r="M63" t="n">
-        <v>51570</v>
+        <v>51775.5</v>
       </c>
       <c r="N63" t="n">
-        <v>51925.5</v>
+        <v>52059.25</v>
       </c>
       <c r="O63" t="n">
-        <v>52175</v>
+        <v>52402</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5810,15 +5802,13 @@
       <c r="R63" s="6" t="n">
         <v/>
       </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
       </c>
       <c r="U63" s="8" t="n">
         <v/>
@@ -5831,85 +5821,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>51486</v>
-      </c>
-      <c r="C64" t="n">
-        <v>51560</v>
-      </c>
-      <c r="D64" t="n">
-        <v>51486</v>
-      </c>
-      <c r="E64" t="n">
-        <v>51477</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="n">
-        <v>74</v>
-      </c>
-      <c r="I64" t="n">
-        <v>50611</v>
-      </c>
-      <c r="J64" t="n">
-        <v>50865.25</v>
-      </c>
-      <c r="K64" t="n">
-        <v>51178.5</v>
-      </c>
-      <c r="L64" t="n">
-        <v>51491.75</v>
-      </c>
-      <c r="M64" t="n">
-        <v>51775.5</v>
-      </c>
-      <c r="N64" t="n">
-        <v>52059.25</v>
-      </c>
-      <c r="O64" t="n">
-        <v>52402</v>
-      </c>
-      <c r="P64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W64" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>弱警訊</t>
         </is>

--- a/three_gate/analysis/YM_daily.xlsx
+++ b/three_gate/analysis/YM_daily.xlsx
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>52541</v>
+        <v>52753</v>
       </c>
       <c r="C2" t="n">
-        <v>52865</v>
+        <v>52992</v>
       </c>
       <c r="D2" t="n">
-        <v>52501</v>
+        <v>52506</v>
       </c>
       <c r="E2" t="n">
-        <v>52761</v>
+        <v>52906</v>
       </c>
       <c r="F2" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0027</v>
       </c>
       <c r="H2" t="n">
-        <v>364</v>
+        <v>486</v>
       </c>
       <c r="I2" t="n">
-        <v>51479</v>
+        <v>52137</v>
       </c>
       <c r="J2" t="n">
-        <v>51684.5</v>
+        <v>52436</v>
       </c>
       <c r="K2" t="n">
-        <v>52192</v>
+        <v>52579</v>
       </c>
       <c r="L2" t="n">
-        <v>52699.5</v>
+        <v>52722</v>
       </c>
       <c r="M2" t="n">
-        <v>53056</v>
+        <v>52943</v>
       </c>
       <c r="N2" t="n">
-        <v>53412.5</v>
+        <v>53164</v>
       </c>
       <c r="O2" t="n">
-        <v>54071</v>
+        <v>53229</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,16 +685,20 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -707,59 +711,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>52753</v>
+        <v>52844</v>
       </c>
       <c r="C3" t="n">
-        <v>52992</v>
+        <v>53113</v>
       </c>
       <c r="D3" t="n">
-        <v>52506</v>
+        <v>52603</v>
       </c>
       <c r="E3" t="n">
-        <v>52906</v>
+        <v>52764</v>
       </c>
       <c r="F3" t="n">
-        <v>145</v>
+        <v>-142</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0027</v>
+        <v>-0.0027</v>
       </c>
       <c r="H3" t="n">
-        <v>486</v>
+        <v>510</v>
       </c>
       <c r="I3" t="n">
-        <v>52137</v>
+        <v>52020</v>
       </c>
       <c r="J3" t="n">
-        <v>52436</v>
+        <v>52498.5</v>
       </c>
       <c r="K3" t="n">
-        <v>52579</v>
+        <v>52663</v>
       </c>
       <c r="L3" t="n">
-        <v>52722</v>
+        <v>52827.5</v>
       </c>
       <c r="M3" t="n">
-        <v>52943</v>
+        <v>53149</v>
       </c>
       <c r="N3" t="n">
-        <v>53164</v>
+        <v>53470.5</v>
       </c>
       <c r="O3" t="n">
-        <v>53229</v>
+        <v>53478</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -772,15 +772,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -793,55 +791,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>52844</v>
+        <v>52731</v>
       </c>
       <c r="C4" t="n">
-        <v>53113</v>
+        <v>52981</v>
       </c>
       <c r="D4" t="n">
-        <v>52603</v>
+        <v>52255</v>
       </c>
       <c r="E4" t="n">
-        <v>52764</v>
+        <v>52791</v>
       </c>
       <c r="F4" t="n">
-        <v>-142</v>
+        <v>27</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0027</v>
+        <v>0.0005</v>
       </c>
       <c r="H4" t="n">
-        <v>510</v>
+        <v>726</v>
       </c>
       <c r="I4" t="n">
-        <v>52020</v>
+        <v>52093</v>
       </c>
       <c r="J4" t="n">
-        <v>52498.5</v>
+        <v>52207</v>
       </c>
       <c r="K4" t="n">
-        <v>52663</v>
+        <v>52509</v>
       </c>
       <c r="L4" t="n">
-        <v>52827.5</v>
+        <v>52811</v>
       </c>
       <c r="M4" t="n">
-        <v>53149</v>
+        <v>53019</v>
       </c>
       <c r="N4" t="n">
-        <v>53470.5</v>
+        <v>53227</v>
       </c>
       <c r="O4" t="n">
-        <v>53478</v>
+        <v>53623</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -875,57 +877,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52731</v>
+        <v>52792</v>
       </c>
       <c r="C5" t="n">
-        <v>52981</v>
+        <v>53088</v>
       </c>
       <c r="D5" t="n">
-        <v>52255</v>
+        <v>52680</v>
       </c>
       <c r="E5" t="n">
-        <v>52791</v>
+        <v>52900</v>
       </c>
       <c r="F5" t="n">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0021</v>
       </c>
       <c r="H5" t="n">
-        <v>726</v>
+        <v>408</v>
       </c>
       <c r="I5" t="n">
-        <v>52093</v>
+        <v>51529</v>
       </c>
       <c r="J5" t="n">
-        <v>52207</v>
+        <v>52151.5</v>
       </c>
       <c r="K5" t="n">
-        <v>52509</v>
+        <v>52428</v>
       </c>
       <c r="L5" t="n">
-        <v>52811</v>
+        <v>52704.5</v>
       </c>
       <c r="M5" t="n">
-        <v>53019</v>
+        <v>53154</v>
       </c>
       <c r="N5" t="n">
-        <v>53227</v>
+        <v>53603.5</v>
       </c>
       <c r="O5" t="n">
-        <v>53623</v>
+        <v>53707</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -933,14 +935,12 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -957,59 +957,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>52792</v>
+        <v>52919</v>
       </c>
       <c r="C6" t="n">
-        <v>53088</v>
+        <v>53108</v>
       </c>
       <c r="D6" t="n">
-        <v>52680</v>
+        <v>52607</v>
       </c>
       <c r="E6" t="n">
-        <v>52900</v>
+        <v>52786</v>
       </c>
       <c r="F6" t="n">
-        <v>109</v>
+        <v>-114</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0022</v>
       </c>
       <c r="H6" t="n">
-        <v>408</v>
+        <v>501</v>
       </c>
       <c r="I6" t="n">
-        <v>51529</v>
+        <v>52272</v>
       </c>
       <c r="J6" t="n">
-        <v>52151.5</v>
+        <v>52500</v>
       </c>
       <c r="K6" t="n">
-        <v>52428</v>
+        <v>52696</v>
       </c>
       <c r="L6" t="n">
-        <v>52704.5</v>
+        <v>52892</v>
       </c>
       <c r="M6" t="n">
-        <v>53154</v>
+        <v>53104</v>
       </c>
       <c r="N6" t="n">
-        <v>53603.5</v>
+        <v>53316</v>
       </c>
       <c r="O6" t="n">
-        <v>53707</v>
+        <v>53496</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1017,16 +1013,20 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1039,65 +1039,71 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>52919</v>
+        <v>52778</v>
       </c>
       <c r="C7" t="n">
-        <v>53108</v>
+        <v>52835</v>
       </c>
       <c r="D7" t="n">
-        <v>52607</v>
+        <v>52174</v>
       </c>
       <c r="E7" t="n">
-        <v>52786</v>
+        <v>52375</v>
       </c>
       <c r="F7" t="n">
-        <v>-114</v>
+        <v>-411</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0022</v>
+        <v>-0.0078</v>
       </c>
       <c r="H7" t="n">
-        <v>501</v>
+        <v>661</v>
       </c>
       <c r="I7" t="n">
-        <v>52272</v>
+        <v>52106</v>
       </c>
       <c r="J7" t="n">
-        <v>52500</v>
+        <v>52249.25</v>
       </c>
       <c r="K7" t="n">
-        <v>52696</v>
+        <v>52535.5</v>
       </c>
       <c r="L7" t="n">
-        <v>52892</v>
+        <v>52821.75</v>
       </c>
       <c r="M7" t="n">
-        <v>53104</v>
+        <v>53036.5</v>
       </c>
       <c r="N7" t="n">
-        <v>53316</v>
+        <v>53251.25</v>
       </c>
       <c r="O7" t="n">
-        <v>53496</v>
+        <v>53609</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
@@ -1105,10 +1111,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1123,69 +1127,67 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>52778</v>
+        <v>52300</v>
       </c>
       <c r="C8" t="n">
-        <v>52835</v>
+        <v>52633</v>
       </c>
       <c r="D8" t="n">
-        <v>52174</v>
+        <v>51999</v>
       </c>
       <c r="E8" t="n">
-        <v>52375</v>
+        <v>52073</v>
       </c>
       <c r="F8" t="n">
-        <v>-411</v>
+        <v>-302</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0078</v>
+        <v>-0.0058</v>
       </c>
       <c r="H8" t="n">
-        <v>661</v>
+        <v>634</v>
       </c>
       <c r="I8" t="n">
-        <v>52106</v>
+        <v>51513</v>
       </c>
       <c r="J8" t="n">
-        <v>52249.25</v>
+        <v>51649.25</v>
       </c>
       <c r="K8" t="n">
-        <v>52535.5</v>
+        <v>52044.5</v>
       </c>
       <c r="L8" t="n">
-        <v>52821.75</v>
+        <v>52439.75</v>
       </c>
       <c r="M8" t="n">
-        <v>53036.5</v>
+        <v>52705.5</v>
       </c>
       <c r="N8" t="n">
-        <v>53251.25</v>
+        <v>52971.25</v>
       </c>
       <c r="O8" t="n">
-        <v>53609</v>
+        <v>53496</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S8" s="10" t="inlineStr">
@@ -1216,50 +1218,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52300</v>
+        <v>52091</v>
       </c>
       <c r="C9" t="n">
-        <v>52633</v>
+        <v>52590</v>
       </c>
       <c r="D9" t="n">
-        <v>51999</v>
+        <v>52035</v>
       </c>
       <c r="E9" t="n">
-        <v>52073</v>
+        <v>52443</v>
       </c>
       <c r="F9" t="n">
-        <v>-302</v>
+        <v>370</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0058</v>
+        <v>0.0071</v>
       </c>
       <c r="H9" t="n">
-        <v>634</v>
+        <v>555</v>
       </c>
       <c r="I9" t="n">
-        <v>51513</v>
+        <v>51365</v>
       </c>
       <c r="J9" t="n">
-        <v>51649.25</v>
+        <v>51317.5</v>
       </c>
       <c r="K9" t="n">
-        <v>52044.5</v>
+        <v>51756</v>
       </c>
       <c r="L9" t="n">
-        <v>52439.75</v>
+        <v>52194.5</v>
       </c>
       <c r="M9" t="n">
-        <v>52705.5</v>
+        <v>52390</v>
       </c>
       <c r="N9" t="n">
-        <v>52971.25</v>
+        <v>52585.5</v>
       </c>
       <c r="O9" t="n">
-        <v>53496</v>
+        <v>53267</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1267,21 +1269,23 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1293,57 +1297,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52091</v>
+        <v>52431</v>
       </c>
       <c r="C10" t="n">
-        <v>52590</v>
+        <v>52721</v>
       </c>
       <c r="D10" t="n">
-        <v>52035</v>
+        <v>52262</v>
       </c>
       <c r="E10" t="n">
-        <v>52443</v>
+        <v>52449</v>
       </c>
       <c r="F10" t="n">
-        <v>370</v>
+        <v>6</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.0001</v>
       </c>
       <c r="H10" t="n">
-        <v>555</v>
+        <v>459</v>
       </c>
       <c r="I10" t="n">
-        <v>51365</v>
+        <v>51480</v>
       </c>
       <c r="J10" t="n">
-        <v>51317.5</v>
+        <v>51953.25</v>
       </c>
       <c r="K10" t="n">
-        <v>51756</v>
+        <v>52165.5</v>
       </c>
       <c r="L10" t="n">
-        <v>52194.5</v>
+        <v>52377.75</v>
       </c>
       <c r="M10" t="n">
-        <v>52390</v>
+        <v>52720.5</v>
       </c>
       <c r="N10" t="n">
-        <v>52585.5</v>
+        <v>53063.25</v>
       </c>
       <c r="O10" t="n">
-        <v>53267</v>
+        <v>53145</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1356,19 +1360,17 @@
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
@@ -1377,88 +1379,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>52431</v>
+        <v>52430</v>
       </c>
       <c r="C11" t="n">
-        <v>52721</v>
+        <v>52515</v>
       </c>
       <c r="D11" t="n">
-        <v>52262</v>
+        <v>51720</v>
       </c>
       <c r="E11" t="n">
-        <v>52449</v>
+        <v>51894</v>
       </c>
       <c r="F11" t="n">
-        <v>6</v>
+        <v>-555</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0001</v>
+        <v>-0.0106</v>
       </c>
       <c r="H11" t="n">
-        <v>459</v>
+        <v>795</v>
       </c>
       <c r="I11" t="n">
-        <v>51480</v>
+        <v>51803</v>
       </c>
       <c r="J11" t="n">
-        <v>51953.25</v>
+        <v>51968.75</v>
       </c>
       <c r="K11" t="n">
-        <v>52165.5</v>
+        <v>52219.5</v>
       </c>
       <c r="L11" t="n">
-        <v>52377.75</v>
+        <v>52470.25</v>
       </c>
       <c r="M11" t="n">
-        <v>52720.5</v>
+        <v>52678.5</v>
       </c>
       <c r="N11" t="n">
-        <v>53063.25</v>
+        <v>52886.75</v>
       </c>
       <c r="O11" t="n">
-        <v>53145</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
+        <v>53180</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W11" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X11" t="inlineStr"/>
@@ -1466,74 +1468,70 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>52430</v>
+        <v>51920</v>
       </c>
       <c r="C12" t="n">
-        <v>52515</v>
+        <v>52314</v>
       </c>
       <c r="D12" t="n">
-        <v>51720</v>
+        <v>51846</v>
       </c>
       <c r="E12" t="n">
-        <v>51894</v>
+        <v>52124</v>
       </c>
       <c r="F12" t="n">
-        <v>-555</v>
+        <v>230</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0044</v>
       </c>
       <c r="H12" t="n">
-        <v>795</v>
+        <v>468</v>
       </c>
       <c r="I12" t="n">
-        <v>51803</v>
+        <v>50925</v>
       </c>
       <c r="J12" t="n">
-        <v>51968.75</v>
+        <v>50987.25</v>
       </c>
       <c r="K12" t="n">
-        <v>52219.5</v>
+        <v>51496.5</v>
       </c>
       <c r="L12" t="n">
-        <v>52470.25</v>
+        <v>52005.75</v>
       </c>
       <c r="M12" t="n">
-        <v>52678.5</v>
+        <v>52291.5</v>
       </c>
       <c r="N12" t="n">
-        <v>52886.75</v>
+        <v>52577.25</v>
       </c>
       <c r="O12" t="n">
-        <v>53180</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
+        <v>53310</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1545,55 +1543,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>51920</v>
+        <v>52299</v>
       </c>
       <c r="C13" t="n">
-        <v>52314</v>
+        <v>52790</v>
       </c>
       <c r="D13" t="n">
-        <v>51846</v>
+        <v>52173</v>
       </c>
       <c r="E13" t="n">
-        <v>52124</v>
+        <v>52382</v>
       </c>
       <c r="F13" t="n">
-        <v>230</v>
+        <v>258</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0044</v>
+        <v>0.0049</v>
       </c>
       <c r="H13" t="n">
-        <v>468</v>
+        <v>617</v>
       </c>
       <c r="I13" t="n">
-        <v>50925</v>
+        <v>51378</v>
       </c>
       <c r="J13" t="n">
-        <v>50987.25</v>
+        <v>51678</v>
       </c>
       <c r="K13" t="n">
-        <v>51496.5</v>
+        <v>51890</v>
       </c>
       <c r="L13" t="n">
-        <v>52005.75</v>
+        <v>52102</v>
       </c>
       <c r="M13" t="n">
-        <v>52291.5</v>
+        <v>52358</v>
       </c>
       <c r="N13" t="n">
-        <v>52577.25</v>
+        <v>52614</v>
       </c>
       <c r="O13" t="n">
-        <v>53310</v>
+        <v>52782</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1606,19 +1608,23 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v/>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W13" s="11" t="inlineStr">
         <is>
@@ -1627,57 +1633,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>52299</v>
+        <v>52405</v>
       </c>
       <c r="C14" t="n">
-        <v>52790</v>
+        <v>53105</v>
       </c>
       <c r="D14" t="n">
-        <v>52173</v>
+        <v>52290</v>
       </c>
       <c r="E14" t="n">
-        <v>52382</v>
+        <v>52944</v>
       </c>
       <c r="F14" t="n">
-        <v>258</v>
+        <v>562</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0107</v>
       </c>
       <c r="H14" t="n">
-        <v>617</v>
+        <v>815</v>
       </c>
       <c r="I14" t="n">
-        <v>51378</v>
+        <v>51556</v>
       </c>
       <c r="J14" t="n">
-        <v>51678</v>
+        <v>51715.25</v>
       </c>
       <c r="K14" t="n">
-        <v>51890</v>
+        <v>52073.5</v>
       </c>
       <c r="L14" t="n">
-        <v>52102</v>
+        <v>52431.75</v>
       </c>
       <c r="M14" t="n">
-        <v>52358</v>
+        <v>52690.5</v>
       </c>
       <c r="N14" t="n">
-        <v>52614</v>
+        <v>52949.25</v>
       </c>
       <c r="O14" t="n">
-        <v>52782</v>
+        <v>53407</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1695,18 +1701,16 @@
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V14" s="8" t="n">
+        <v/>
       </c>
       <c r="W14" s="11" t="inlineStr">
         <is>
@@ -1722,74 +1726,76 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>52405</v>
+        <v>52915</v>
       </c>
       <c r="C15" t="n">
-        <v>53105</v>
+        <v>53033</v>
       </c>
       <c r="D15" t="n">
-        <v>52290</v>
+        <v>51630</v>
       </c>
       <c r="E15" t="n">
-        <v>52944</v>
+        <v>51765</v>
       </c>
       <c r="F15" t="n">
-        <v>562</v>
+        <v>-1179</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0223</v>
       </c>
       <c r="H15" t="n">
-        <v>815</v>
+        <v>1403</v>
       </c>
       <c r="I15" t="n">
-        <v>51556</v>
+        <v>51475</v>
       </c>
       <c r="J15" t="n">
-        <v>51715.25</v>
+        <v>52252.25</v>
       </c>
       <c r="K15" t="n">
-        <v>52073.5</v>
+        <v>52536.5</v>
       </c>
       <c r="L15" t="n">
-        <v>52431.75</v>
+        <v>52820.75</v>
       </c>
       <c r="M15" t="n">
-        <v>52690.5</v>
+        <v>53351.5</v>
       </c>
       <c r="N15" t="n">
-        <v>52949.25</v>
+        <v>53882.25</v>
       </c>
       <c r="O15" t="n">
-        <v>53407</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
+        <v>53920</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1799,83 +1805,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>52915</v>
+        <v>51759</v>
       </c>
       <c r="C16" t="n">
-        <v>53033</v>
+        <v>52484</v>
       </c>
       <c r="D16" t="n">
-        <v>51630</v>
+        <v>51732</v>
       </c>
       <c r="E16" t="n">
-        <v>51765</v>
+        <v>52380</v>
       </c>
       <c r="F16" t="n">
-        <v>-1179</v>
+        <v>615</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0223</v>
+        <v>0.0119</v>
       </c>
       <c r="H16" t="n">
-        <v>1403</v>
+        <v>752</v>
       </c>
       <c r="I16" t="n">
-        <v>51475</v>
+        <v>50227</v>
       </c>
       <c r="J16" t="n">
-        <v>52252.25</v>
+        <v>50078.75</v>
       </c>
       <c r="K16" t="n">
-        <v>52536.5</v>
+        <v>51063.5</v>
       </c>
       <c r="L16" t="n">
-        <v>52820.75</v>
+        <v>52048.25</v>
       </c>
       <c r="M16" t="n">
-        <v>53351.5</v>
+        <v>52466.5</v>
       </c>
       <c r="N16" t="n">
-        <v>53882.25</v>
+        <v>52884.75</v>
       </c>
       <c r="O16" t="n">
-        <v>53920</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
+        <v>54436</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
@@ -1887,55 +1885,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>20